--- a/demo_results.xlsx
+++ b/demo_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P6"/>
+  <dimension ref="A1:R6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,35 +464,45 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t>Hold Return %</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Alpha %</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t>Allocation $</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Qty</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Buys</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Holds</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Sells</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Avg Hold (wk)</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>chart_data</t>
         </is>
@@ -505,7 +515,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -513,44 +523,50 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.137</v>
+        <v>0.33</v>
       </c>
       <c r="E2" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F2" t="n">
         <v>50</v>
       </c>
       <c r="G2" t="n">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="H2" t="n">
-        <v>771</v>
+        <v>1007</v>
       </c>
       <c r="I2" t="n">
-        <v>15.4</v>
+        <v>20.1</v>
       </c>
       <c r="J2" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-8.4</v>
+      </c>
+      <c r="L2" t="n">
         <v>5000</v>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
         <v>14</v>
-      </c>
-      <c r="L2" t="n">
-        <v>2</v>
-      </c>
-      <c r="M2" t="n">
-        <v>15</v>
       </c>
       <c r="N2" t="n">
         <v>2</v>
       </c>
       <c r="O2" t="n">
-        <v>8</v>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [262.28, 260.05, 257.22, 259.64, 260.59, 260.57, 255.52, 249.89, 252.59, 254.0, 249.71, 248.73, 247.76, 251.26, 251.41, 252.39, 252.66, 248.57, 246.4, 253.56, 255.39, 255.68, 258.62, 253.27, 258.66, 260.25, 260.24, 258.96, 258.59, 266.18, 263.16, 269.98, 272.8, 265.93, 272.92, 273.18, 270.81, 267.36, 270.46, 269.92, 271.1, 279.88, 276.58, 283.92, 287.25, 287.18, 293.05, 292.68, 294.8, 298.87, 298.21, 300.23, 297.84, 298.97, 302.25, 304.99, 308.82, 308.33, 310.85, 312.51, 312.06, 306.31, 315.2, 310.26, 311.23, 307.34, 301.54, 290.55, 291.58, 295.63, 291.13, 296.42, 299.24, 295.95, 298.01, 297.01, 294.3, 293.08, 275.15, 283.78, 281.74, 289.36, 294.38, 308.63, 312.66, 310.66, 313.39, 316.22, 315.32, 317.31, 314.86, 327.5, 333.26, 333.74, 326.59, 327.74, 325.89, 321.66, 333.02, 336.91], 'signals': ['BUY', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+        <v>17</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>9</v>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [262.28, 260.05, 257.22, 259.64, 260.59, 260.57, 255.52, 249.89, 252.59, 254.0, 249.71, 248.73, 247.76, 251.26, 251.41, 252.39, 252.66, 248.57, 246.4, 253.56, 255.39, 255.68, 258.62, 253.27, 258.66, 260.25, 260.24, 258.96, 258.59, 266.18, 263.16, 269.98, 272.8, 265.93, 272.92, 273.18, 270.81, 267.36, 270.46, 269.92, 271.1, 279.88, 276.58, 283.92, 287.25, 287.18, 293.05, 292.68, 294.8, 298.87, 298.21, 300.23, 297.84, 298.97, 302.25, 304.99, 308.82, 308.33, 310.85, 312.51, 312.06, 306.31, 315.2, 310.26, 311.23, 307.34, 301.54, 290.55, 291.58, 295.63, 291.13, 296.42, 299.24, 295.95, 298.01, 297.01, 294.3, 293.08, 275.15, 283.78, 281.74, 289.36, 294.38, 308.63, 312.66, 310.66, 313.39, 316.22, 315.32, 317.31, 314.86, 327.5, 333.26, 333.74, 326.59, 327.74, 325.89, 321.66, 333.02, 336.91], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
     </row>
@@ -561,7 +577,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -569,44 +585,50 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.569</v>
+        <v>0.916</v>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F3" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="G3" t="n">
-        <v>40</v>
+        <v>55.6</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>-107</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>-2.1</v>
       </c>
       <c r="J3" t="n">
+        <v>-3.8</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L3" t="n">
         <v>5000</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>12</v>
       </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [404.32, 409.79, 408.08, 408.53, 404.88, 404.0, 400.99, 394.7, 399.09, 398.55, 390.94, 388.18, 381.04, 382.17, 371.93, 370.24, 365.18, 356.0, 358.18, 369.37, 368.57, 372.65, 372.07, 371.49, 373.52, 372.26, 370.07, 383.54, 392.26, 410.33, 419.35, 421.88, 417.17, 423.24, 431.98, 414.85, 423.7, 423.9, 428.32, 423.54, 406.9, 413.54, 412.73, 410.49, 413.07, 419.86, 414.22, 411.77, 406.89, 404.33, 408.55, 421.01, 422.62, 416.52, 420.15, 419.09, 418.57, 416.03, 412.67, 426.99, 450.24, 460.52, 441.31, 427.34, 428.05, 416.67, 411.74, 403.41, 397.36, 390.34, 390.74, 399.76, 393.83, 378.91, 379.4, 367.34, 373.94, 365.46, 352.83, 372.97, 368.57, 373.02, 384.28, 390.49, 386.74, 388.84, 383.34, 384.36, 385.1, 390.99, 384.93, 395.63, 401.1, 393.82, 402.29, 397.75, 390.34, 381.58, 381.7, 389.1], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+        <v>15</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>8</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [404.32, 409.79, 408.08, 408.53, 404.88, 404.0, 400.99, 394.7, 399.09, 398.55, 390.94, 388.18, 381.04, 382.17, 371.93, 370.24, 365.18, 356.0, 358.18, 369.37, 368.57, 372.65, 372.07, 371.49, 373.52, 372.26, 370.07, 383.54, 392.26, 410.33, 419.35, 421.88, 417.17, 423.24, 431.98, 414.85, 423.7, 423.9, 428.32, 423.54, 406.9, 413.54, 412.73, 410.49, 413.07, 419.86, 414.22, 411.77, 406.89, 404.33, 408.55, 421.01, 422.62, 416.52, 420.15, 419.09, 418.57, 416.03, 412.67, 426.99, 450.24, 460.52, 441.31, 427.34, 428.05, 416.67, 411.74, 403.41, 397.36, 390.34, 390.74, 399.76, 393.83, 378.91, 379.4, 367.34, 373.94, 365.46, 352.83, 372.97, 368.57, 373.02, 384.28, 390.49, 386.74, 388.84, 383.34, 384.36, 385.1, 390.99, 384.93, 395.63, 401.1, 393.82, 402.29, 397.75, 390.34, 381.58, 381.7, 389.1], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
     </row>
@@ -617,52 +639,58 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">UP  </t>
+          <t>DOWN</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F4" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G4" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="H4" t="n">
-        <v>-272</v>
+        <v>448</v>
       </c>
       <c r="I4" t="n">
-        <v>-5.4</v>
+        <v>9</v>
       </c>
       <c r="J4" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L4" t="n">
         <v>5000</v>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>15</v>
       </c>
-      <c r="L4" t="n">
-        <v>3</v>
-      </c>
-      <c r="M4" t="n">
-        <v>8</v>
-      </c>
       <c r="N4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O4" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [302.74, 300.49, 298.13, 306.18, 306.86, 308.52, 303.37, 302.1, 305.38, 310.73, 307.51, 306.95, 300.82, 301.88, 290.27, 290.76, 280.75, 274.18, 273.34, 287.39, 297.21, 295.59, 299.81, 305.28, 317.13, 318.3, 317.05, 321.12, 332.71, 336.92, 335.82, 341.48, 337.22, 332.09, 339.12, 338.69, 344.19, 350.13, 349.57, 349.73, 384.57, 385.46, 383.02, 388.2, 397.8, 397.75, 400.56, 388.41, 387.12, 402.38, 400.83, 396.54, 396.7, 387.43, 388.68, 387.43, 382.74, 388.65, 388.6, 389.9, 380.11, 376.15, 361.63, 358.78, 371.97, 368.31, 363.31, 364.26, 356.38, 357.77, 359.68, 369.35, 373.25, 363.79, 368.03, 349.68, 346.13, 345.29, 343.71, 337.39, 353.65, 357.37, 361.21, 359.91, 366.46, 367.03, 361.92, 358.89, 357.18, 352.51, 359.51, 370.92, 354.46, 346.77, 351.99, 347.15, 342.09, 317.69, 319.74, 326.56], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+        <v>16</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [302.74, 300.49, 298.13, 306.18, 306.86, 308.52, 303.37, 302.1, 305.38, 310.73, 307.51, 306.95, 300.82, 301.88, 290.27, 290.76, 280.75, 274.18, 273.34, 287.39, 297.21, 295.59, 299.81, 305.28, 317.13, 318.3, 317.05, 321.12, 332.71, 336.92, 335.82, 341.48, 337.22, 332.09, 339.12, 338.69, 344.19, 350.13, 349.57, 349.73, 384.57, 385.46, 383.02, 388.2, 397.8, 397.75, 400.56, 388.41, 387.12, 402.38, 400.83, 396.54, 396.7, 387.43, 388.68, 387.43, 382.74, 388.65, 388.6, 389.9, 380.11, 376.15, 361.63, 358.78, 371.97, 368.31, 363.31, 364.26, 356.38, 357.77, 359.68, 369.35, 373.25, 363.79, 368.03, 349.68, 346.13, 345.29, 343.71, 337.39, 353.65, 357.37, 361.21, 359.91, 366.46, 367.03, 361.92, 358.89, 357.18, 352.51, 359.51, 370.92, 354.46, 346.77, 351.99, 347.15, 342.09, 317.69, 319.74, 326.56], 'signals': ['FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
     </row>
@@ -673,52 +701,58 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">UP  </t>
+          <t>DOWN</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.591</v>
+        <v>0.416</v>
       </c>
       <c r="E5" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H5" t="n">
-        <v>30</v>
+        <v>-164</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6</v>
+        <v>-3.3</v>
       </c>
       <c r="J5" t="n">
+        <v>-23.8</v>
+      </c>
+      <c r="K5" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="L5" t="n">
         <v>5000</v>
       </c>
-      <c r="K5" t="n">
+      <c r="M5" t="n">
         <v>16</v>
       </c>
-      <c r="L5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O5" t="n">
-        <v>1</v>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [405.94, 405.55, 396.73, 398.68, 399.24, 407.82, 395.01, 391.2, 395.56, 399.27, 392.78, 380.3, 367.96, 380.85, 383.03, 385.95, 372.11, 361.83, 355.28, 371.75, 381.26, 360.59, 352.82, 346.65, 343.25, 345.62, 348.95, 352.42, 364.2, 391.95, 388.9, 400.62, 392.5, 386.42, 387.51, 373.72, 376.3, 378.67, 376.02, 372.8, 381.63, 390.82, 392.51, 389.37, 398.73, 411.79, 428.35, 445.0, 433.45, 445.27, 443.3, 422.24, 409.99, 404.11, 417.26, 417.85, 426.01, 433.59, 440.36, 442.1, 435.79, 415.88, 423.74, 423.7, 418.45, 391.0, 408.95, 396.68, 381.59, 399.15, 406.43, 411.15, 404.66, 396.38, 400.49, 405.05, 381.61, 375.53, 375.12, 379.71, 411.84, 420.6, 425.3, 393.45, 419.77, 402.9, 394.06, 406.55, 407.76, 394.76, 396.18, 394.46, 391.06, 380.84, 369.57, 378.93, 374.01, 319.69, 313.03, 309.22], 'signals': ['BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+        <v>2</v>
+      </c>
+      <c r="P5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [405.94, 405.55, 396.73, 398.68, 399.24, 407.82, 395.01, 391.2, 395.56, 399.27, 392.78, 380.3, 367.96, 380.85, 383.03, 385.95, 372.11, 361.83, 355.28, 371.75, 381.26, 360.59, 352.82, 346.65, 343.25, 345.62, 348.95, 352.42, 364.2, 391.95, 388.9, 400.62, 392.5, 386.42, 387.51, 373.72, 376.3, 378.67, 376.02, 372.8, 381.63, 390.82, 392.51, 389.37, 398.73, 411.79, 428.35, 445.0, 433.45, 445.27, 443.3, 422.24, 409.99, 404.11, 417.26, 417.85, 426.01, 433.59, 440.36, 442.1, 435.79, 415.88, 423.74, 423.7, 418.45, 391.0, 408.95, 396.68, 381.59, 399.15, 406.43, 411.15, 404.66, 396.38, 400.49, 405.05, 381.61, 375.53, 375.12, 379.71, 411.84, 420.6, 425.3, 393.45, 419.77, 402.9, 394.06, 406.55, 407.76, 394.76, 396.18, 394.46, 391.06, 380.84, 369.57, 378.93, 374.01, 319.69, 313.03, 309.22], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
     </row>
@@ -729,7 +763,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -737,10 +771,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.376</v>
+        <v>0.436</v>
       </c>
       <c r="E6" t="n">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="F6" t="n">
         <v>70</v>
@@ -749,32 +783,38 @@
         <v>50</v>
       </c>
       <c r="H6" t="n">
-        <v>71</v>
+        <v>866</v>
       </c>
       <c r="I6" t="n">
-        <v>1.4</v>
+        <v>17.3</v>
       </c>
       <c r="J6" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="K6" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="L6" t="n">
         <v>5000</v>
       </c>
-      <c r="K6" t="n">
+      <c r="M6" t="n">
         <v>25</v>
       </c>
-      <c r="L6" t="n">
+      <c r="N6" t="n">
+        <v>6</v>
+      </c>
+      <c r="O6" t="n">
         <v>2</v>
       </c>
-      <c r="M6" t="n">
-        <v>4</v>
-      </c>
-      <c r="N6" t="n">
-        <v>2</v>
-      </c>
-      <c r="O6" t="n">
-        <v>3</v>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [182.82, 183.12, 177.6, 182.43, 184.54, 185.81, 182.93, 180.04, 183.01, 181.72, 180.19, 178.35, 172.5, 175.44, 175.0, 178.47, 171.04, 167.32, 164.98, 174.2, 175.55, 177.18, 177.43, 177.89, 181.87, 183.7, 188.41, 189.09, 196.28, 198.64, 198.12, 201.45, 201.82, 199.65, 202.26, 199.41, 208.03, 216.36, 212.92, 209.01, 199.34, 198.22, 198.25, 196.27, 207.59, 211.25, 214.95, 219.18, 220.52, 225.57, 235.47, 225.06, 222.06, 220.35, 223.21, 219.25, 215.08, 214.61, 212.35, 214.0, 210.89, 224.1, 222.56, 214.5, 218.66, 205.1, 208.64, 208.19, 200.42, 204.87, 205.19, 212.45, 207.41, 204.65, 210.69, 208.65, 200.04, 199.0, 195.74, 192.53, 194.97, 200.09, 197.58, 194.83, 195.55, 196.93, 204.12, 202.78, 210.96, 203.53, 211.8, 212.5, 207.4, 202.81, 203.28, 207.29, 212.06, 208.76, 206.84, 196.51], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+      <c r="P6" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [182.82, 183.12, 177.6, 182.43, 184.54, 185.81, 182.93, 180.04, 183.01, 181.72, 180.19, 178.35, 172.5, 175.44, 175.0, 178.47, 171.04, 167.32, 164.98, 174.2, 175.55, 177.18, 177.43, 177.89, 181.87, 183.7, 188.41, 189.09, 196.28, 198.64, 198.12, 201.45, 201.82, 199.65, 202.26, 199.41, 208.03, 216.36, 212.92, 209.01, 199.34, 198.22, 198.25, 196.27, 207.59, 211.25, 214.95, 219.18, 220.52, 225.57, 235.47, 225.06, 222.06, 220.35, 223.21, 219.25, 215.08, 214.61, 212.35, 214.0, 210.89, 224.1, 222.56, 214.5, 218.66, 205.1, 208.64, 208.19, 200.42, 204.87, 205.19, 212.45, 207.41, 204.65, 210.69, 208.65, 200.04, 199.0, 195.74, 192.53, 194.97, 200.09, 197.58, 194.83, 195.55, 196.93, 204.12, 202.78, 210.96, 203.53, 211.8, 212.5, 207.4, 202.81, 203.28, 207.29, 212.06, 208.76, 206.84, 196.51], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
     </row>

--- a/demo_results.xlsx
+++ b/demo_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R6"/>
+  <dimension ref="A1:R9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.33</v>
+        <v>0.246</v>
       </c>
       <c r="E2" t="n">
         <v>63</v>
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -585,10 +585,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.916</v>
+        <v>0.965</v>
       </c>
       <c r="E3" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F3" t="n">
         <v>50</v>
@@ -597,16 +597,16 @@
         <v>55.6</v>
       </c>
       <c r="H3" t="n">
-        <v>-107</v>
+        <v>-350</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.1</v>
+        <v>-7</v>
       </c>
       <c r="J3" t="n">
         <v>-3.8</v>
       </c>
       <c r="K3" t="n">
-        <v>1.7</v>
+        <v>-3.2</v>
       </c>
       <c r="L3" t="n">
         <v>5000</v>
@@ -615,20 +615,20 @@
         <v>12</v>
       </c>
       <c r="N3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O3" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [404.32, 409.79, 408.08, 408.53, 404.88, 404.0, 400.99, 394.7, 399.09, 398.55, 390.94, 388.18, 381.04, 382.17, 371.93, 370.24, 365.18, 356.0, 358.18, 369.37, 368.57, 372.65, 372.07, 371.49, 373.52, 372.26, 370.07, 383.54, 392.26, 410.33, 419.35, 421.88, 417.17, 423.24, 431.98, 414.85, 423.7, 423.9, 428.32, 423.54, 406.9, 413.54, 412.73, 410.49, 413.07, 419.86, 414.22, 411.77, 406.89, 404.33, 408.55, 421.01, 422.62, 416.52, 420.15, 419.09, 418.57, 416.03, 412.67, 426.99, 450.24, 460.52, 441.31, 427.34, 428.05, 416.67, 411.74, 403.41, 397.36, 390.34, 390.74, 399.76, 393.83, 378.91, 379.4, 367.34, 373.94, 365.46, 352.83, 372.97, 368.57, 373.02, 384.28, 390.49, 386.74, 388.84, 383.34, 384.36, 385.1, 390.99, 384.93, 395.63, 401.1, 393.82, 402.29, 397.75, 390.34, 381.58, 381.7, 389.1], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [404.32, 409.79, 408.08, 408.53, 404.88, 404.0, 400.99, 394.7, 399.09, 398.55, 390.94, 388.18, 381.04, 382.17, 371.93, 370.24, 365.18, 356.0, 358.18, 369.37, 368.57, 372.65, 372.07, 371.49, 373.52, 372.26, 370.07, 383.54, 392.26, 410.33, 419.35, 421.88, 417.17, 423.24, 431.98, 414.85, 423.7, 423.9, 428.32, 423.54, 406.9, 413.54, 412.73, 410.49, 413.07, 419.86, 414.22, 411.77, 406.89, 404.33, 408.55, 421.01, 422.62, 416.52, 420.15, 419.09, 418.57, 416.03, 412.67, 426.99, 450.24, 460.52, 441.31, 427.34, 428.05, 416.67, 411.74, 403.41, 397.36, 390.34, 390.74, 399.76, 393.83, 378.91, 379.4, 367.34, 373.94, 365.46, 352.83, 372.97, 368.57, 373.02, 384.28, 390.49, 386.74, 388.84, 383.34, 384.36, 385.1, 390.99, 384.93, 395.63, 401.1, 393.82, 402.29, 397.75, 390.34, 381.58, 381.7, 389.1], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
     </row>
@@ -639,15 +639,15 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DOWN</t>
+          <t xml:space="preserve">UP  </t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.5</v>
+        <v>0.501</v>
       </c>
       <c r="E4" t="n">
         <v>52</v>
@@ -659,16 +659,16 @@
         <v>50</v>
       </c>
       <c r="H4" t="n">
-        <v>448</v>
+        <v>-31</v>
       </c>
       <c r="I4" t="n">
-        <v>9</v>
+        <v>-0.6</v>
       </c>
       <c r="J4" t="n">
         <v>7.9</v>
       </c>
       <c r="K4" t="n">
-        <v>1.1</v>
+        <v>-8.5</v>
       </c>
       <c r="L4" t="n">
         <v>5000</v>
@@ -677,20 +677,20 @@
         <v>15</v>
       </c>
       <c r="N4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O4" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q4" t="n">
-        <v>8.5</v>
+        <v>1</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [302.74, 300.49, 298.13, 306.18, 306.86, 308.52, 303.37, 302.1, 305.38, 310.73, 307.51, 306.95, 300.82, 301.88, 290.27, 290.76, 280.75, 274.18, 273.34, 287.39, 297.21, 295.59, 299.81, 305.28, 317.13, 318.3, 317.05, 321.12, 332.71, 336.92, 335.82, 341.48, 337.22, 332.09, 339.12, 338.69, 344.19, 350.13, 349.57, 349.73, 384.57, 385.46, 383.02, 388.2, 397.8, 397.75, 400.56, 388.41, 387.12, 402.38, 400.83, 396.54, 396.7, 387.43, 388.68, 387.43, 382.74, 388.65, 388.6, 389.9, 380.11, 376.15, 361.63, 358.78, 371.97, 368.31, 363.31, 364.26, 356.38, 357.77, 359.68, 369.35, 373.25, 363.79, 368.03, 349.68, 346.13, 345.29, 343.71, 337.39, 353.65, 357.37, 361.21, 359.91, 366.46, 367.03, 361.92, 358.89, 357.18, 352.51, 359.51, 370.92, 354.46, 346.77, 351.99, 347.15, 342.09, 317.69, 319.74, 326.56], 'signals': ['FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [302.74, 300.49, 298.13, 306.18, 306.86, 308.52, 303.37, 302.1, 305.38, 310.73, 307.51, 306.95, 300.82, 301.88, 290.27, 290.76, 280.75, 274.18, 273.34, 287.39, 297.21, 295.59, 299.81, 305.28, 317.13, 318.3, 317.05, 321.12, 332.71, 336.92, 335.82, 341.48, 337.22, 332.09, 339.12, 338.69, 344.19, 350.13, 349.57, 349.73, 384.57, 385.46, 383.02, 388.2, 397.8, 397.75, 400.56, 388.41, 387.12, 402.38, 400.83, 396.54, 396.7, 387.43, 388.68, 387.43, 382.74, 388.65, 388.6, 389.9, 380.11, 376.15, 361.63, 358.78, 371.97, 368.31, 363.31, 364.26, 356.38, 357.77, 359.68, 369.35, 373.25, 363.79, 368.03, 349.68, 346.13, 345.29, 343.71, 337.39, 353.65, 357.37, 361.21, 359.91, 366.46, 367.03, 361.92, 358.89, 357.18, 352.51, 359.51, 370.92, 354.46, 346.77, 351.99, 347.15, 342.09, 317.69, 319.74, 326.56], 'signals': ['BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'SELL', 'BUY', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
     </row>
@@ -701,7 +701,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -709,28 +709,28 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.416</v>
+        <v>0.404</v>
       </c>
       <c r="E5" t="n">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="F5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G5" t="n">
         <v>40</v>
       </c>
       <c r="H5" t="n">
-        <v>-164</v>
+        <v>-833</v>
       </c>
       <c r="I5" t="n">
-        <v>-3.3</v>
+        <v>-16.7</v>
       </c>
       <c r="J5" t="n">
         <v>-23.8</v>
       </c>
       <c r="K5" t="n">
-        <v>20.5</v>
+        <v>7.1</v>
       </c>
       <c r="L5" t="n">
         <v>5000</v>
@@ -742,17 +742,17 @@
         <v>4</v>
       </c>
       <c r="O5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="P5" t="n">
         <v>4</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [405.94, 405.55, 396.73, 398.68, 399.24, 407.82, 395.01, 391.2, 395.56, 399.27, 392.78, 380.3, 367.96, 380.85, 383.03, 385.95, 372.11, 361.83, 355.28, 371.75, 381.26, 360.59, 352.82, 346.65, 343.25, 345.62, 348.95, 352.42, 364.2, 391.95, 388.9, 400.62, 392.5, 386.42, 387.51, 373.72, 376.3, 378.67, 376.02, 372.8, 381.63, 390.82, 392.51, 389.37, 398.73, 411.79, 428.35, 445.0, 433.45, 445.27, 443.3, 422.24, 409.99, 404.11, 417.26, 417.85, 426.01, 433.59, 440.36, 442.1, 435.79, 415.88, 423.74, 423.7, 418.45, 391.0, 408.95, 396.68, 381.59, 399.15, 406.43, 411.15, 404.66, 396.38, 400.49, 405.05, 381.61, 375.53, 375.12, 379.71, 411.84, 420.6, 425.3, 393.45, 419.77, 402.9, 394.06, 406.55, 407.76, 394.76, 396.18, 394.46, 391.06, 380.84, 369.57, 378.93, 374.01, 319.69, 313.03, 309.22], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [405.94, 405.55, 396.73, 398.68, 399.24, 407.82, 395.01, 391.2, 395.56, 399.27, 392.78, 380.3, 367.96, 380.85, 383.03, 385.95, 372.11, 361.83, 355.28, 371.75, 381.26, 360.59, 352.82, 346.65, 343.25, 345.62, 348.95, 352.42, 364.2, 391.95, 388.9, 400.62, 392.5, 386.42, 387.51, 373.72, 376.3, 378.67, 376.02, 372.8, 381.63, 390.82, 392.51, 389.37, 398.73, 411.79, 428.35, 445.0, 433.45, 445.27, 443.3, 422.24, 409.99, 404.11, 417.26, 417.85, 426.01, 433.59, 440.36, 442.1, 435.79, 415.88, 423.74, 423.7, 418.45, 391.0, 408.95, 396.68, 381.59, 399.15, 406.43, 411.15, 404.66, 396.38, 400.49, 405.05, 381.61, 375.53, 375.12, 379.71, 411.84, 420.6, 425.3, 393.45, 419.77, 402.9, 394.06, 406.55, 407.76, 394.76, 396.18, 394.46, 391.06, 380.84, 369.57, 378.93, 374.01, 319.69, 313.03, 309.22], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -783,16 +783,16 @@
         <v>50</v>
       </c>
       <c r="H6" t="n">
-        <v>866</v>
+        <v>823</v>
       </c>
       <c r="I6" t="n">
-        <v>17.3</v>
+        <v>16.5</v>
       </c>
       <c r="J6" t="n">
         <v>7.5</v>
       </c>
       <c r="K6" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="L6" t="n">
         <v>5000</v>
@@ -804,17 +804,203 @@
         <v>6</v>
       </c>
       <c r="O6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P6" t="n">
         <v>6</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [182.82, 183.12, 177.6, 182.43, 184.54, 185.81, 182.93, 180.04, 183.01, 181.72, 180.19, 178.35, 172.5, 175.44, 175.0, 178.47, 171.04, 167.32, 164.98, 174.2, 175.55, 177.18, 177.43, 177.89, 181.87, 183.7, 188.41, 189.09, 196.28, 198.64, 198.12, 201.45, 201.82, 199.65, 202.26, 199.41, 208.03, 216.36, 212.92, 209.01, 199.34, 198.22, 198.25, 196.27, 207.59, 211.25, 214.95, 219.18, 220.52, 225.57, 235.47, 225.06, 222.06, 220.35, 223.21, 219.25, 215.08, 214.61, 212.35, 214.0, 210.89, 224.1, 222.56, 214.5, 218.66, 205.1, 208.64, 208.19, 200.42, 204.87, 205.19, 212.45, 207.41, 204.65, 210.69, 208.65, 200.04, 199.0, 195.74, 192.53, 194.97, 200.09, 197.58, 194.83, 195.55, 196.93, 204.12, 202.78, 210.96, 203.53, 211.8, 212.5, 207.4, 202.81, 203.28, 207.29, 212.06, 208.76, 206.84, 196.51], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [182.82, 183.12, 177.6, 182.43, 184.54, 185.81, 182.93, 180.04, 183.01, 181.72, 180.19, 178.35, 172.5, 175.44, 175.0, 178.47, 171.04, 167.32, 164.98, 174.2, 175.55, 177.18, 177.43, 177.89, 181.87, 183.7, 188.41, 189.09, 196.28, 198.64, 198.12, 201.45, 201.82, 199.65, 202.26, 199.41, 208.03, 216.36, 212.92, 209.01, 199.34, 198.22, 198.25, 196.27, 207.59, 211.25, 214.95, 219.18, 220.52, 225.57, 235.47, 225.06, 222.06, 220.35, 223.21, 219.25, 215.08, 214.61, 212.35, 214.0, 210.89, 224.1, 222.56, 214.5, 218.66, 205.1, 208.64, 208.19, 200.42, 204.87, 205.19, 212.45, 207.41, 204.65, 210.69, 208.65, 200.04, 199.0, 195.74, 192.53, 194.97, 200.09, 197.58, 194.83, 195.55, 196.93, 204.12, 202.78, 210.96, 203.53, 211.8, 212.5, 207.4, 202.81, 203.28, 207.29, 212.06, 208.76, 206.84, 196.51], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>50</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.373</v>
+      </c>
+      <c r="E7" t="n">
+        <v>49</v>
+      </c>
+      <c r="F7" t="n">
+        <v>70</v>
+      </c>
+      <c r="G7" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-74</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-8.199999999999999</v>
+      </c>
+      <c r="L7" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M7" t="n">
+        <v>21</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3</v>
+      </c>
+      <c r="O7" t="n">
+        <v>6</v>
+      </c>
+      <c r="P7" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [216.82, 218.94, 213.21, 213.49, 214.33, 212.65, 209.53, 207.67, 211.74, 215.2, 209.87, 208.76, 205.37, 210.14, 207.24, 211.71, 207.54, 199.34, 200.95, 208.27, 210.57, 209.77, 212.79, 213.77, 221.25, 233.65, 238.38, 239.89, 249.02, 248.5, 249.7, 250.56, 248.28, 249.91, 255.36, 255.08, 263.99, 261.12, 259.7, 263.04, 265.06, 268.26, 272.05, 273.55, 274.99, 271.17, 272.68, 268.99, 265.82, 270.13, 267.22, 264.14, 264.86, 259.34, 265.01, 268.46, 266.32, 265.29, 271.85, 274.0, 270.64, 261.26, 256.52, 250.02, 253.79, 246.03, 245.22, 244.19, 238.0, 241.51, 238.55, 246.02, 246.0, 237.5, 244.39, 232.79, 234.11, 234.27, 227.01, 232.69, 240.14, 238.34, 241.7, 242.67, 244.16, 245.98, 243.62, 247.04, 245.34, 247.31, 247.49, 254.96, 249.89, 247.23, 249.99, 247.55, 244.85, 233.66, 232.11, 231.39], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>51</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.458</v>
+      </c>
+      <c r="E8" t="n">
+        <v>56</v>
+      </c>
+      <c r="F8" t="n">
+        <v>50</v>
+      </c>
+      <c r="G8" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="H8" t="n">
+        <v>644</v>
+      </c>
+      <c r="I8" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-10.9</v>
+      </c>
+      <c r="K8" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="L8" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M8" t="n">
+        <v>8</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3</v>
+      </c>
+      <c r="O8" t="n">
+        <v>11</v>
+      </c>
+      <c r="P8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [666.54, 659.39, 643.71, 646.24, 652.91, 653.69, 637.04, 612.62, 626.87, 622.08, 615.11, 606.14, 593.11, 603.5, 592.37, 594.34, 547.03, 525.23, 535.88, 571.6, 578.69, 573.93, 572.49, 574.52, 611.85, 627.81, 629.28, 633.94, 661.88, 670.96, 676.24, 687.91, 670.29, 668.22, 674.1, 658.54, 674.4, 677.99, 670.72, 668.5, 611.34, 608.19, 609.84, 604.4, 612.31, 616.24, 609.07, 598.31, 602.44, 616.06, 617.86, 613.66, 610.64, 602.05, 604.5, 606.82, 609.69, 611.77, 634.67, 634.7, 631.92, 599.91, 597.08, 622.4, 626.99, 592.45, 584.85, 584.05, 570.45, 567.9, 566.45, 593.48, 600.21, 567.58, 577.22, 563.85, 562.2, 557.67, 542.87, 550.25, 562.6, 563.29, 612.91, 582.9, 600.29, 615.58, 603.12, 631.48, 669.21, 656.73, 661.04, 681.31, 664.54, 646.01, 645.85, 643.81, 627.17, 606.1, 595.19, 593.87], 'signals': ['FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD']}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>JPM</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>57</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.456</v>
+      </c>
+      <c r="E9" t="n">
+        <v>62</v>
+      </c>
+      <c r="F9" t="n">
+        <v>30</v>
+      </c>
+      <c r="G9" t="n">
+        <v>65</v>
+      </c>
+      <c r="H9" t="n">
+        <v>633</v>
+      </c>
+      <c r="I9" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="J9" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-7.4</v>
+      </c>
+      <c r="L9" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M9" t="n">
+        <v>14</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2</v>
+      </c>
+      <c r="O9" t="n">
+        <v>10</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>6</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [296.53, 290.75, 286.71, 287.15, 285.97, 284.77, 280.19, 280.73, 283.43, 284.15, 284.99, 285.22, 283.82, 287.14, 289.61, 292.6, 288.87, 280.14, 281.06, 291.35, 292.56, 291.79, 294.12, 296.07, 306.59, 308.94, 308.48, 312.27, 309.72, 304.56, 308.56, 308.9, 315.57, 311.6, 311.62, 310.29, 306.9, 310.23, 310.05, 307.86, 311.83, 311.07, 306.27, 308.01, 313.49, 304.9, 300.75, 298.65, 303.51, 298.9, 298.57, 296.47, 299.38, 294.37, 300.63, 301.64, 305.01, 305.36, 297.94, 295.4, 297.97, 295.25, 299.61, 299.5, 309.5, 310.97, 309.71, 311.3, 307.75, 312.08, 319.28, 317.97, 329.65, 331.96, 323.76, 329.99, 332.64, 331.95, 333.62, 327.57, 327.91, 325.86, 332.57, 332.97, 337.72, 339.22, 330.62, 335.47, 336.47, 334.53, 342.89, 346.91, 343.15, 341.1, 338.87, 345.23, 348.21, 349.9, 353.21, 356.2], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
     </row>

--- a/demo_results.xlsx
+++ b/demo_results.xlsx
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.246</v>
+        <v>0.203</v>
       </c>
       <c r="E2" t="n">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="F2" t="n">
         <v>50</v>
@@ -535,16 +535,16 @@
         <v>70</v>
       </c>
       <c r="H2" t="n">
-        <v>1007</v>
+        <v>977</v>
       </c>
       <c r="I2" t="n">
-        <v>20.1</v>
+        <v>19.5</v>
       </c>
       <c r="J2" t="n">
         <v>28.5</v>
       </c>
       <c r="K2" t="n">
-        <v>-8.4</v>
+        <v>-9</v>
       </c>
       <c r="L2" t="n">
         <v>5000</v>
@@ -566,7 +566,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [262.28, 260.05, 257.22, 259.64, 260.59, 260.57, 255.52, 249.89, 252.59, 254.0, 249.71, 248.73, 247.76, 251.26, 251.41, 252.39, 252.66, 248.57, 246.4, 253.56, 255.39, 255.68, 258.62, 253.27, 258.66, 260.25, 260.24, 258.96, 258.59, 266.18, 263.16, 269.98, 272.8, 265.93, 272.92, 273.18, 270.81, 267.36, 270.46, 269.92, 271.1, 279.88, 276.58, 283.92, 287.25, 287.18, 293.05, 292.68, 294.8, 298.87, 298.21, 300.23, 297.84, 298.97, 302.25, 304.99, 308.82, 308.33, 310.85, 312.51, 312.06, 306.31, 315.2, 310.26, 311.23, 307.34, 301.54, 290.55, 291.58, 295.63, 291.13, 296.42, 299.24, 295.95, 298.01, 297.01, 294.3, 293.08, 275.15, 283.78, 281.74, 289.36, 294.38, 308.63, 312.66, 310.66, 313.39, 316.22, 315.32, 317.31, 314.86, 327.5, 333.26, 333.74, 326.59, 327.74, 325.89, 321.66, 333.02, 336.91], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [262.28, 260.05, 257.22, 259.64, 260.59, 260.57, 255.52, 249.89, 252.59, 254.0, 249.71, 248.73, 247.76, 251.26, 251.41, 252.39, 252.66, 248.57, 246.4, 253.56, 255.39, 255.68, 258.62, 253.27, 258.66, 260.25, 260.24, 258.96, 258.59, 266.18, 263.16, 269.98, 272.8, 265.93, 272.92, 273.18, 270.81, 267.36, 270.46, 269.92, 271.1, 279.88, 276.58, 283.92, 287.25, 287.18, 293.05, 292.68, 294.8, 298.87, 298.21, 300.23, 297.84, 298.97, 302.25, 304.99, 308.82, 308.33, 310.85, 312.51, 312.06, 306.31, 315.2, 310.26, 311.23, 307.34, 301.54, 290.55, 291.58, 295.63, 291.13, 296.42, 299.24, 295.95, 298.01, 297.01, 294.3, 293.08, 275.15, 283.78, 281.74, 289.36, 294.38, 308.63, 312.66, 310.66, 313.39, 316.22, 315.32, 317.31, 314.86, 327.5, 333.26, 333.74, 326.59, 327.74, 325.89, 321.66, 333.02, 336.91], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -585,28 +585,28 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.965</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F3" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="G3" t="n">
         <v>55.6</v>
       </c>
       <c r="H3" t="n">
-        <v>-350</v>
+        <v>-316</v>
       </c>
       <c r="I3" t="n">
-        <v>-7</v>
+        <v>-6.3</v>
       </c>
       <c r="J3" t="n">
         <v>-3.8</v>
       </c>
       <c r="K3" t="n">
-        <v>-3.2</v>
+        <v>-2.5</v>
       </c>
       <c r="L3" t="n">
         <v>5000</v>
@@ -618,17 +618,17 @@
         <v>3</v>
       </c>
       <c r="O3" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
       </c>
       <c r="Q3" t="n">
-        <v>5</v>
+        <v>3.3</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [404.32, 409.79, 408.08, 408.53, 404.88, 404.0, 400.99, 394.7, 399.09, 398.55, 390.94, 388.18, 381.04, 382.17, 371.93, 370.24, 365.18, 356.0, 358.18, 369.37, 368.57, 372.65, 372.07, 371.49, 373.52, 372.26, 370.07, 383.54, 392.26, 410.33, 419.35, 421.88, 417.17, 423.24, 431.98, 414.85, 423.7, 423.9, 428.32, 423.54, 406.9, 413.54, 412.73, 410.49, 413.07, 419.86, 414.22, 411.77, 406.89, 404.33, 408.55, 421.01, 422.62, 416.52, 420.15, 419.09, 418.57, 416.03, 412.67, 426.99, 450.24, 460.52, 441.31, 427.34, 428.05, 416.67, 411.74, 403.41, 397.36, 390.34, 390.74, 399.76, 393.83, 378.91, 379.4, 367.34, 373.94, 365.46, 352.83, 372.97, 368.57, 373.02, 384.28, 390.49, 386.74, 388.84, 383.34, 384.36, 385.1, 390.99, 384.93, 395.63, 401.1, 393.82, 402.29, 397.75, 390.34, 381.58, 381.7, 389.1], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [404.32, 409.79, 408.08, 408.53, 404.88, 404.0, 400.99, 394.7, 399.09, 398.55, 390.94, 388.18, 381.04, 382.17, 371.93, 370.24, 365.18, 356.0, 358.18, 369.37, 368.57, 372.65, 372.07, 371.49, 373.52, 372.26, 370.07, 383.54, 392.26, 410.33, 419.35, 421.88, 417.17, 423.24, 431.98, 414.85, 423.7, 423.9, 428.32, 423.54, 406.9, 413.54, 412.73, 410.49, 413.07, 419.86, 414.22, 411.77, 406.89, 404.33, 408.55, 421.01, 422.62, 416.52, 420.15, 419.09, 418.57, 416.03, 412.67, 426.99, 450.24, 460.52, 441.31, 427.34, 428.05, 416.67, 411.74, 403.41, 397.36, 390.34, 390.74, 399.76, 393.83, 378.91, 379.4, 367.34, 373.94, 365.46, 352.83, 372.97, 368.57, 373.02, 384.28, 390.49, 386.74, 388.84, 383.34, 384.36, 385.1, 390.99, 384.93, 395.63, 401.1, 393.82, 402.29, 397.75, 390.34, 381.58, 381.7, 389.1], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
     </row>
@@ -647,10 +647,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.501</v>
+        <v>0.5</v>
       </c>
       <c r="E4" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F4" t="n">
         <v>70</v>
@@ -659,16 +659,16 @@
         <v>50</v>
       </c>
       <c r="H4" t="n">
-        <v>-31</v>
+        <v>316</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.6</v>
+        <v>6.3</v>
       </c>
       <c r="J4" t="n">
         <v>7.9</v>
       </c>
       <c r="K4" t="n">
-        <v>-8.5</v>
+        <v>-1.6</v>
       </c>
       <c r="L4" t="n">
         <v>5000</v>
@@ -677,20 +677,20 @@
         <v>15</v>
       </c>
       <c r="N4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
         <v>1</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [302.74, 300.49, 298.13, 306.18, 306.86, 308.52, 303.37, 302.1, 305.38, 310.73, 307.51, 306.95, 300.82, 301.88, 290.27, 290.76, 280.75, 274.18, 273.34, 287.39, 297.21, 295.59, 299.81, 305.28, 317.13, 318.3, 317.05, 321.12, 332.71, 336.92, 335.82, 341.48, 337.22, 332.09, 339.12, 338.69, 344.19, 350.13, 349.57, 349.73, 384.57, 385.46, 383.02, 388.2, 397.8, 397.75, 400.56, 388.41, 387.12, 402.38, 400.83, 396.54, 396.7, 387.43, 388.68, 387.43, 382.74, 388.65, 388.6, 389.9, 380.11, 376.15, 361.63, 358.78, 371.97, 368.31, 363.31, 364.26, 356.38, 357.77, 359.68, 369.35, 373.25, 363.79, 368.03, 349.68, 346.13, 345.29, 343.71, 337.39, 353.65, 357.37, 361.21, 359.91, 366.46, 367.03, 361.92, 358.89, 357.18, 352.51, 359.51, 370.92, 354.46, 346.77, 351.99, 347.15, 342.09, 317.69, 319.74, 326.56], 'signals': ['BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'SELL', 'BUY', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [302.74, 300.49, 298.13, 306.18, 306.86, 308.52, 303.37, 302.1, 305.38, 310.73, 307.51, 306.95, 300.82, 301.88, 290.27, 290.76, 280.75, 274.18, 273.34, 287.39, 297.21, 295.59, 299.81, 305.28, 317.13, 318.3, 317.05, 321.12, 332.71, 336.92, 335.82, 341.48, 337.22, 332.09, 339.12, 338.69, 344.19, 350.13, 349.57, 349.73, 384.57, 385.46, 383.02, 388.2, 397.8, 397.75, 400.56, 388.41, 387.12, 402.38, 400.83, 396.54, 396.7, 387.43, 388.68, 387.43, 382.74, 388.65, 388.6, 389.9, 380.11, 376.15, 361.63, 358.78, 371.97, 368.31, 363.31, 364.26, 356.38, 357.77, 359.68, 369.35, 373.25, 363.79, 368.03, 349.68, 346.13, 345.29, 343.71, 337.39, 353.65, 357.37, 361.21, 359.91, 366.46, 367.03, 361.92, 358.89, 357.18, 352.51, 359.51, 370.92, 354.46, 346.77, 351.99, 347.15, 342.09, 317.69, 319.74, 326.56], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
     </row>
@@ -701,36 +701,36 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>55</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.392</v>
+      </c>
+      <c r="E5" t="n">
         <v>62</v>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>DOWN</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>0.404</v>
-      </c>
-      <c r="E5" t="n">
-        <v>49</v>
-      </c>
       <c r="F5" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="G5" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>-833</v>
+        <v>-633</v>
       </c>
       <c r="I5" t="n">
-        <v>-16.7</v>
+        <v>-12.7</v>
       </c>
       <c r="J5" t="n">
         <v>-23.8</v>
       </c>
       <c r="K5" t="n">
-        <v>7.1</v>
+        <v>11.1</v>
       </c>
       <c r="L5" t="n">
         <v>5000</v>
@@ -739,20 +739,20 @@
         <v>16</v>
       </c>
       <c r="N5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [405.94, 405.55, 396.73, 398.68, 399.24, 407.82, 395.01, 391.2, 395.56, 399.27, 392.78, 380.3, 367.96, 380.85, 383.03, 385.95, 372.11, 361.83, 355.28, 371.75, 381.26, 360.59, 352.82, 346.65, 343.25, 345.62, 348.95, 352.42, 364.2, 391.95, 388.9, 400.62, 392.5, 386.42, 387.51, 373.72, 376.3, 378.67, 376.02, 372.8, 381.63, 390.82, 392.51, 389.37, 398.73, 411.79, 428.35, 445.0, 433.45, 445.27, 443.3, 422.24, 409.99, 404.11, 417.26, 417.85, 426.01, 433.59, 440.36, 442.1, 435.79, 415.88, 423.74, 423.7, 418.45, 391.0, 408.95, 396.68, 381.59, 399.15, 406.43, 411.15, 404.66, 396.38, 400.49, 405.05, 381.61, 375.53, 375.12, 379.71, 411.84, 420.6, 425.3, 393.45, 419.77, 402.9, 394.06, 406.55, 407.76, 394.76, 396.18, 394.46, 391.06, 380.84, 369.57, 378.93, 374.01, 319.69, 313.03, 309.22], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [405.94, 405.55, 396.73, 398.68, 399.24, 407.82, 395.01, 391.2, 395.56, 399.27, 392.78, 380.3, 367.96, 380.85, 383.03, 385.95, 372.11, 361.83, 355.28, 371.75, 381.26, 360.59, 352.82, 346.65, 343.25, 345.62, 348.95, 352.42, 364.2, 391.95, 388.9, 400.62, 392.5, 386.42, 387.51, 373.72, 376.3, 378.67, 376.02, 372.8, 381.63, 390.82, 392.51, 389.37, 398.73, 411.79, 428.35, 445.0, 433.45, 445.27, 443.3, 422.24, 409.99, 404.11, 417.26, 417.85, 426.01, 433.59, 440.36, 442.1, 435.79, 415.88, 423.74, 423.7, 418.45, 391.0, 408.95, 396.68, 381.59, 399.15, 406.43, 411.15, 404.66, 396.38, 400.49, 405.05, 381.61, 375.53, 375.12, 379.71, 411.84, 420.6, 425.3, 393.45, 419.77, 402.9, 394.06, 406.55, 407.76, 394.76, 396.18, 394.46, 391.06, 380.84, 369.57, 378.93, 374.01, 319.69, 313.03, 309.22], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -771,10 +771,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.436</v>
+        <v>0.444</v>
       </c>
       <c r="E6" t="n">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="F6" t="n">
         <v>70</v>
@@ -783,16 +783,16 @@
         <v>50</v>
       </c>
       <c r="H6" t="n">
-        <v>823</v>
+        <v>180</v>
       </c>
       <c r="I6" t="n">
-        <v>16.5</v>
+        <v>3.6</v>
       </c>
       <c r="J6" t="n">
         <v>7.5</v>
       </c>
       <c r="K6" t="n">
-        <v>9</v>
+        <v>-3.9</v>
       </c>
       <c r="L6" t="n">
         <v>5000</v>
@@ -801,20 +801,20 @@
         <v>25</v>
       </c>
       <c r="N6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O6" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="P6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.5</v>
+        <v>7.5</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [182.82, 183.12, 177.6, 182.43, 184.54, 185.81, 182.93, 180.04, 183.01, 181.72, 180.19, 178.35, 172.5, 175.44, 175.0, 178.47, 171.04, 167.32, 164.98, 174.2, 175.55, 177.18, 177.43, 177.89, 181.87, 183.7, 188.41, 189.09, 196.28, 198.64, 198.12, 201.45, 201.82, 199.65, 202.26, 199.41, 208.03, 216.36, 212.92, 209.01, 199.34, 198.22, 198.25, 196.27, 207.59, 211.25, 214.95, 219.18, 220.52, 225.57, 235.47, 225.06, 222.06, 220.35, 223.21, 219.25, 215.08, 214.61, 212.35, 214.0, 210.89, 224.1, 222.56, 214.5, 218.66, 205.1, 208.64, 208.19, 200.42, 204.87, 205.19, 212.45, 207.41, 204.65, 210.69, 208.65, 200.04, 199.0, 195.74, 192.53, 194.97, 200.09, 197.58, 194.83, 195.55, 196.93, 204.12, 202.78, 210.96, 203.53, 211.8, 212.5, 207.4, 202.81, 203.28, 207.29, 212.06, 208.76, 206.84, 196.51], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [182.82, 183.12, 177.6, 182.43, 184.54, 185.81, 182.93, 180.04, 183.01, 181.72, 180.19, 178.35, 172.5, 175.44, 175.0, 178.47, 171.04, 167.32, 164.98, 174.2, 175.55, 177.18, 177.43, 177.89, 181.87, 183.7, 188.41, 189.09, 196.28, 198.64, 198.12, 201.45, 201.82, 199.65, 202.26, 199.41, 208.03, 216.36, 212.92, 209.01, 199.34, 198.22, 198.25, 196.27, 207.59, 211.25, 214.95, 219.18, 220.52, 225.57, 235.47, 225.06, 222.06, 220.35, 223.21, 219.25, 215.08, 214.61, 212.35, 214.0, 210.89, 224.1, 222.56, 214.5, 218.66, 205.1, 208.64, 208.19, 200.42, 204.87, 205.19, 212.45, 207.41, 204.65, 210.69, 208.65, 200.04, 199.0, 195.74, 192.53, 194.97, 200.09, 197.58, 194.83, 195.55, 196.93, 204.12, 202.78, 210.96, 203.53, 211.8, 212.5, 207.4, 202.81, 203.28, 207.29, 212.06, 208.76, 206.84, 196.51], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -833,28 +833,28 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.373</v>
+        <v>0.348</v>
       </c>
       <c r="E7" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="F7" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="G7" t="n">
         <v>83.3</v>
       </c>
       <c r="H7" t="n">
-        <v>-74</v>
+        <v>-385</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.5</v>
+        <v>-7.7</v>
       </c>
       <c r="J7" t="n">
         <v>6.7</v>
       </c>
       <c r="K7" t="n">
-        <v>-8.199999999999999</v>
+        <v>-14.4</v>
       </c>
       <c r="L7" t="n">
         <v>5000</v>
@@ -863,20 +863,20 @@
         <v>21</v>
       </c>
       <c r="N7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="P7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.7</v>
+        <v>13</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [216.82, 218.94, 213.21, 213.49, 214.33, 212.65, 209.53, 207.67, 211.74, 215.2, 209.87, 208.76, 205.37, 210.14, 207.24, 211.71, 207.54, 199.34, 200.95, 208.27, 210.57, 209.77, 212.79, 213.77, 221.25, 233.65, 238.38, 239.89, 249.02, 248.5, 249.7, 250.56, 248.28, 249.91, 255.36, 255.08, 263.99, 261.12, 259.7, 263.04, 265.06, 268.26, 272.05, 273.55, 274.99, 271.17, 272.68, 268.99, 265.82, 270.13, 267.22, 264.14, 264.86, 259.34, 265.01, 268.46, 266.32, 265.29, 271.85, 274.0, 270.64, 261.26, 256.52, 250.02, 253.79, 246.03, 245.22, 244.19, 238.0, 241.51, 238.55, 246.02, 246.0, 237.5, 244.39, 232.79, 234.11, 234.27, 227.01, 232.69, 240.14, 238.34, 241.7, 242.67, 244.16, 245.98, 243.62, 247.04, 245.34, 247.31, 247.49, 254.96, 249.89, 247.23, 249.99, 247.55, 244.85, 233.66, 232.11, 231.39], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [216.82, 218.94, 213.21, 213.49, 214.33, 212.65, 209.53, 207.67, 211.74, 215.2, 209.87, 208.76, 205.37, 210.14, 207.24, 211.71, 207.54, 199.34, 200.95, 208.27, 210.57, 209.77, 212.79, 213.77, 221.25, 233.65, 238.38, 239.89, 249.02, 248.5, 249.7, 250.56, 248.28, 249.91, 255.36, 255.08, 263.99, 261.12, 259.7, 263.04, 265.06, 268.26, 272.05, 273.55, 274.99, 271.17, 272.68, 268.99, 265.82, 270.13, 267.22, 264.14, 264.86, 259.34, 265.01, 268.46, 266.32, 265.29, 271.85, 274.0, 270.64, 261.26, 256.52, 250.02, 253.79, 246.03, 245.22, 244.19, 238.0, 241.51, 238.55, 246.02, 246.0, 237.5, 244.39, 232.79, 234.11, 234.27, 227.01, 232.69, 240.14, 238.34, 241.7, 242.67, 244.16, 245.98, 243.62, 247.04, 245.34, 247.31, 247.49, 254.96, 249.89, 247.23, 249.99, 247.55, 244.85, 233.66, 232.11, 231.39], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT']}</t>
         </is>
       </c>
     </row>
@@ -887,7 +887,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -895,28 +895,28 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.458</v>
+        <v>0.399</v>
       </c>
       <c r="E8" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F8" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="G8" t="n">
-        <v>33.3</v>
+        <v>35.3</v>
       </c>
       <c r="H8" t="n">
-        <v>644</v>
+        <v>-90</v>
       </c>
       <c r="I8" t="n">
-        <v>12.9</v>
+        <v>-1.8</v>
       </c>
       <c r="J8" t="n">
         <v>-10.9</v>
       </c>
       <c r="K8" t="n">
-        <v>23.8</v>
+        <v>9.1</v>
       </c>
       <c r="L8" t="n">
         <v>5000</v>
@@ -925,20 +925,20 @@
         <v>8</v>
       </c>
       <c r="N8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O8" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="P8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.7</v>
+        <v>1.5</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [666.54, 659.39, 643.71, 646.24, 652.91, 653.69, 637.04, 612.62, 626.87, 622.08, 615.11, 606.14, 593.11, 603.5, 592.37, 594.34, 547.03, 525.23, 535.88, 571.6, 578.69, 573.93, 572.49, 574.52, 611.85, 627.81, 629.28, 633.94, 661.88, 670.96, 676.24, 687.91, 670.29, 668.22, 674.1, 658.54, 674.4, 677.99, 670.72, 668.5, 611.34, 608.19, 609.84, 604.4, 612.31, 616.24, 609.07, 598.31, 602.44, 616.06, 617.86, 613.66, 610.64, 602.05, 604.5, 606.82, 609.69, 611.77, 634.67, 634.7, 631.92, 599.91, 597.08, 622.4, 626.99, 592.45, 584.85, 584.05, 570.45, 567.9, 566.45, 593.48, 600.21, 567.58, 577.22, 563.85, 562.2, 557.67, 542.87, 550.25, 562.6, 563.29, 612.91, 582.9, 600.29, 615.58, 603.12, 631.48, 669.21, 656.73, 661.04, 681.31, 664.54, 646.01, 645.85, 643.81, 627.17, 606.1, 595.19, 593.87], 'signals': ['FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [666.54, 659.39, 643.71, 646.24, 652.91, 653.69, 637.04, 612.62, 626.87, 622.08, 615.11, 606.14, 593.11, 603.5, 592.37, 594.34, 547.03, 525.23, 535.88, 571.6, 578.69, 573.93, 572.49, 574.52, 611.85, 627.81, 629.28, 633.94, 661.88, 670.96, 676.24, 687.91, 670.29, 668.22, 674.1, 658.54, 674.4, 677.99, 670.72, 668.5, 611.34, 608.19, 609.84, 604.4, 612.31, 616.24, 609.07, 598.31, 602.44, 616.06, 617.86, 613.66, 610.64, 602.05, 604.5, 606.82, 609.69, 611.77, 634.67, 634.7, 631.92, 599.91, 597.08, 622.4, 626.99, 592.45, 584.85, 584.05, 570.45, 567.9, 566.45, 593.48, 600.21, 567.58, 577.22, 563.85, 562.2, 557.67, 542.87, 550.25, 562.6, 563.29, 612.91, 582.9, 600.29, 615.58, 603.12, 631.48, 669.21, 656.73, 661.04, 681.31, 664.54, 646.01, 645.85, 643.81, 627.17, 606.1, 595.19, 593.87], 'signals': ['FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'SELL', 'BUY', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT']}</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.456</v>
+        <v>0.461</v>
       </c>
       <c r="E9" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F9" t="n">
         <v>30</v>
@@ -969,16 +969,16 @@
         <v>65</v>
       </c>
       <c r="H9" t="n">
-        <v>633</v>
+        <v>534</v>
       </c>
       <c r="I9" t="n">
-        <v>12.7</v>
+        <v>10.7</v>
       </c>
       <c r="J9" t="n">
         <v>20.1</v>
       </c>
       <c r="K9" t="n">
-        <v>-7.4</v>
+        <v>-9.4</v>
       </c>
       <c r="L9" t="n">
         <v>5000</v>
@@ -987,20 +987,20 @@
         <v>14</v>
       </c>
       <c r="N9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O9" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="P9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q9" t="n">
-        <v>6</v>
+        <v>3.3</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [296.53, 290.75, 286.71, 287.15, 285.97, 284.77, 280.19, 280.73, 283.43, 284.15, 284.99, 285.22, 283.82, 287.14, 289.61, 292.6, 288.87, 280.14, 281.06, 291.35, 292.56, 291.79, 294.12, 296.07, 306.59, 308.94, 308.48, 312.27, 309.72, 304.56, 308.56, 308.9, 315.57, 311.6, 311.62, 310.29, 306.9, 310.23, 310.05, 307.86, 311.83, 311.07, 306.27, 308.01, 313.49, 304.9, 300.75, 298.65, 303.51, 298.9, 298.57, 296.47, 299.38, 294.37, 300.63, 301.64, 305.01, 305.36, 297.94, 295.4, 297.97, 295.25, 299.61, 299.5, 309.5, 310.97, 309.71, 311.3, 307.75, 312.08, 319.28, 317.97, 329.65, 331.96, 323.76, 329.99, 332.64, 331.95, 333.62, 327.57, 327.91, 325.86, 332.57, 332.97, 337.72, 339.22, 330.62, 335.47, 336.47, 334.53, 342.89, 346.91, 343.15, 341.1, 338.87, 345.23, 348.21, 349.9, 353.21, 356.2], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [296.53, 290.75, 286.71, 287.15, 285.97, 284.77, 280.19, 280.73, 283.43, 284.15, 284.99, 285.22, 283.82, 287.14, 289.61, 292.6, 288.87, 280.14, 281.06, 291.35, 292.56, 291.79, 294.12, 296.07, 306.59, 308.94, 308.48, 312.27, 309.72, 304.56, 308.56, 308.9, 315.57, 311.6, 311.62, 310.29, 306.9, 310.23, 310.05, 307.86, 311.83, 311.07, 306.27, 308.01, 313.49, 304.9, 300.75, 298.65, 303.51, 298.9, 298.57, 296.47, 299.38, 294.37, 300.63, 301.64, 305.01, 305.36, 297.94, 295.4, 297.97, 295.25, 299.61, 299.5, 309.5, 310.97, 309.71, 311.3, 307.75, 312.08, 319.28, 317.97, 329.65, 331.96, 323.76, 329.99, 332.64, 331.95, 333.62, 327.57, 327.91, 325.86, 332.57, 332.97, 337.72, 339.22, 330.62, 335.47, 336.47, 334.53, 342.89, 346.91, 343.15, 341.1, 338.87, 345.23, 348.21, 349.9, 353.21, 356.2], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
     </row>

--- a/demo_results.xlsx
+++ b/demo_results.xlsx
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.203</v>
+        <v>0.194</v>
       </c>
       <c r="E2" t="n">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="F2" t="n">
         <v>50</v>
@@ -535,16 +535,16 @@
         <v>70</v>
       </c>
       <c r="H2" t="n">
-        <v>977</v>
+        <v>1045</v>
       </c>
       <c r="I2" t="n">
-        <v>19.5</v>
+        <v>20.9</v>
       </c>
       <c r="J2" t="n">
         <v>28.5</v>
       </c>
       <c r="K2" t="n">
-        <v>-9</v>
+        <v>-7.6</v>
       </c>
       <c r="L2" t="n">
         <v>5000</v>
@@ -553,20 +553,20 @@
         <v>14</v>
       </c>
       <c r="N2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="P2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [262.28, 260.05, 257.22, 259.64, 260.59, 260.57, 255.52, 249.89, 252.59, 254.0, 249.71, 248.73, 247.76, 251.26, 251.41, 252.39, 252.66, 248.57, 246.4, 253.56, 255.39, 255.68, 258.62, 253.27, 258.66, 260.25, 260.24, 258.96, 258.59, 266.18, 263.16, 269.98, 272.8, 265.93, 272.92, 273.18, 270.81, 267.36, 270.46, 269.92, 271.1, 279.88, 276.58, 283.92, 287.25, 287.18, 293.05, 292.68, 294.8, 298.87, 298.21, 300.23, 297.84, 298.97, 302.25, 304.99, 308.82, 308.33, 310.85, 312.51, 312.06, 306.31, 315.2, 310.26, 311.23, 307.34, 301.54, 290.55, 291.58, 295.63, 291.13, 296.42, 299.24, 295.95, 298.01, 297.01, 294.3, 293.08, 275.15, 283.78, 281.74, 289.36, 294.38, 308.63, 312.66, 310.66, 313.39, 316.22, 315.32, 317.31, 314.86, 327.5, 333.26, 333.74, 326.59, 327.74, 325.89, 321.66, 333.02, 336.91], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [262.28, 260.05, 257.22, 259.64, 260.59, 260.57, 255.52, 249.89, 252.59, 254.0, 249.71, 248.73, 247.76, 251.26, 251.41, 252.39, 252.66, 248.57, 246.4, 253.56, 255.39, 255.68, 258.62, 253.27, 258.66, 260.25, 260.24, 258.96, 258.59, 266.18, 263.16, 269.98, 272.8, 265.93, 272.92, 273.18, 270.81, 267.36, 270.46, 269.92, 271.1, 279.88, 276.58, 283.92, 287.25, 287.18, 293.05, 292.68, 294.8, 298.87, 298.21, 300.23, 297.84, 298.97, 302.25, 304.99, 308.82, 308.33, 310.85, 312.51, 312.06, 306.31, 315.2, 310.26, 311.23, 307.34, 301.54, 290.55, 291.58, 295.63, 291.13, 296.42, 299.24, 295.95, 298.01, 297.01, 294.3, 293.08, 275.15, 283.78, 281.74, 289.36, 294.38, 308.63, 312.66, 310.66, 313.39, 316.22, 315.32, 317.31, 314.86, 327.5, 333.26, 333.74, 326.59, 327.74, 325.89, 321.66, 333.02, 336.91], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -585,28 +585,28 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.986</v>
       </c>
       <c r="E3" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F3" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="G3" t="n">
         <v>55.6</v>
       </c>
       <c r="H3" t="n">
-        <v>-316</v>
+        <v>148</v>
       </c>
       <c r="I3" t="n">
-        <v>-6.3</v>
+        <v>3</v>
       </c>
       <c r="J3" t="n">
         <v>-3.8</v>
       </c>
       <c r="K3" t="n">
-        <v>-2.5</v>
+        <v>6.8</v>
       </c>
       <c r="L3" t="n">
         <v>5000</v>
@@ -615,20 +615,20 @@
         <v>12</v>
       </c>
       <c r="N3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.3</v>
+        <v>1</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [404.32, 409.79, 408.08, 408.53, 404.88, 404.0, 400.99, 394.7, 399.09, 398.55, 390.94, 388.18, 381.04, 382.17, 371.93, 370.24, 365.18, 356.0, 358.18, 369.37, 368.57, 372.65, 372.07, 371.49, 373.52, 372.26, 370.07, 383.54, 392.26, 410.33, 419.35, 421.88, 417.17, 423.24, 431.98, 414.85, 423.7, 423.9, 428.32, 423.54, 406.9, 413.54, 412.73, 410.49, 413.07, 419.86, 414.22, 411.77, 406.89, 404.33, 408.55, 421.01, 422.62, 416.52, 420.15, 419.09, 418.57, 416.03, 412.67, 426.99, 450.24, 460.52, 441.31, 427.34, 428.05, 416.67, 411.74, 403.41, 397.36, 390.34, 390.74, 399.76, 393.83, 378.91, 379.4, 367.34, 373.94, 365.46, 352.83, 372.97, 368.57, 373.02, 384.28, 390.49, 386.74, 388.84, 383.34, 384.36, 385.1, 390.99, 384.93, 395.63, 401.1, 393.82, 402.29, 397.75, 390.34, 381.58, 381.7, 389.1], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [404.32, 409.79, 408.08, 408.53, 404.88, 404.0, 400.99, 394.7, 399.09, 398.55, 390.94, 388.18, 381.04, 382.17, 371.93, 370.24, 365.18, 356.0, 358.18, 369.37, 368.57, 372.65, 372.07, 371.49, 373.52, 372.26, 370.07, 383.54, 392.26, 410.33, 419.35, 421.88, 417.17, 423.24, 431.98, 414.85, 423.7, 423.9, 428.32, 423.54, 406.9, 413.54, 412.73, 410.49, 413.07, 419.86, 414.22, 411.77, 406.89, 404.33, 408.55, 421.01, 422.62, 416.52, 420.15, 419.09, 418.57, 416.03, 412.67, 426.99, 450.24, 460.52, 441.31, 427.34, 428.05, 416.67, 411.74, 403.41, 397.36, 390.34, 390.74, 399.76, 393.83, 378.91, 379.4, 367.34, 373.94, 365.46, 352.83, 372.97, 368.57, 373.02, 384.28, 390.49, 386.74, 388.84, 383.34, 384.36, 385.1, 390.99, 384.93, 395.63, 401.1, 393.82, 402.29, 397.75, 390.34, 381.58, 381.7, 389.1], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
     </row>
@@ -639,18 +639,18 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">UP  </t>
+          <t>DOWN</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.5</v>
+        <v>0.49</v>
       </c>
       <c r="E4" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F4" t="n">
         <v>70</v>
@@ -659,16 +659,16 @@
         <v>50</v>
       </c>
       <c r="H4" t="n">
-        <v>316</v>
+        <v>87</v>
       </c>
       <c r="I4" t="n">
-        <v>6.3</v>
+        <v>1.7</v>
       </c>
       <c r="J4" t="n">
         <v>7.9</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.6</v>
+        <v>-6.2</v>
       </c>
       <c r="L4" t="n">
         <v>5000</v>
@@ -690,7 +690,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [302.74, 300.49, 298.13, 306.18, 306.86, 308.52, 303.37, 302.1, 305.38, 310.73, 307.51, 306.95, 300.82, 301.88, 290.27, 290.76, 280.75, 274.18, 273.34, 287.39, 297.21, 295.59, 299.81, 305.28, 317.13, 318.3, 317.05, 321.12, 332.71, 336.92, 335.82, 341.48, 337.22, 332.09, 339.12, 338.69, 344.19, 350.13, 349.57, 349.73, 384.57, 385.46, 383.02, 388.2, 397.8, 397.75, 400.56, 388.41, 387.12, 402.38, 400.83, 396.54, 396.7, 387.43, 388.68, 387.43, 382.74, 388.65, 388.6, 389.9, 380.11, 376.15, 361.63, 358.78, 371.97, 368.31, 363.31, 364.26, 356.38, 357.77, 359.68, 369.35, 373.25, 363.79, 368.03, 349.68, 346.13, 345.29, 343.71, 337.39, 353.65, 357.37, 361.21, 359.91, 366.46, 367.03, 361.92, 358.89, 357.18, 352.51, 359.51, 370.92, 354.46, 346.77, 351.99, 347.15, 342.09, 317.69, 319.74, 326.56], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [302.74, 300.49, 298.13, 306.18, 306.86, 308.52, 303.37, 302.1, 305.38, 310.73, 307.51, 306.95, 300.82, 301.88, 290.27, 290.76, 280.75, 274.18, 273.34, 287.39, 297.21, 295.59, 299.81, 305.28, 317.13, 318.3, 317.05, 321.12, 332.71, 336.92, 335.82, 341.48, 337.22, 332.09, 339.12, 338.69, 344.19, 350.13, 349.57, 349.73, 384.57, 385.46, 383.02, 388.2, 397.8, 397.75, 400.56, 388.41, 387.12, 402.38, 400.83, 396.54, 396.7, 387.43, 388.68, 387.43, 382.74, 388.65, 388.6, 389.9, 380.11, 376.15, 361.63, 358.78, 371.97, 368.31, 363.31, 364.26, 356.38, 357.77, 359.68, 369.35, 373.25, 363.79, 368.03, 349.68, 346.13, 345.29, 343.71, 337.39, 353.65, 357.37, 361.21, 359.91, 366.46, 367.03, 361.92, 358.89, 357.18, 352.51, 359.51, 370.92, 354.46, 346.77, 351.99, 347.15, 342.09, 317.69, 319.74, 326.56], 'signals': ['BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
     </row>
@@ -701,7 +701,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -709,28 +709,28 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.392</v>
+        <v>0.373</v>
       </c>
       <c r="E5" t="n">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="F5" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>-633</v>
+        <v>-549</v>
       </c>
       <c r="I5" t="n">
-        <v>-12.7</v>
+        <v>-11</v>
       </c>
       <c r="J5" t="n">
         <v>-23.8</v>
       </c>
       <c r="K5" t="n">
-        <v>11.1</v>
+        <v>12.8</v>
       </c>
       <c r="L5" t="n">
         <v>5000</v>
@@ -739,20 +739,20 @@
         <v>16</v>
       </c>
       <c r="N5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [405.94, 405.55, 396.73, 398.68, 399.24, 407.82, 395.01, 391.2, 395.56, 399.27, 392.78, 380.3, 367.96, 380.85, 383.03, 385.95, 372.11, 361.83, 355.28, 371.75, 381.26, 360.59, 352.82, 346.65, 343.25, 345.62, 348.95, 352.42, 364.2, 391.95, 388.9, 400.62, 392.5, 386.42, 387.51, 373.72, 376.3, 378.67, 376.02, 372.8, 381.63, 390.82, 392.51, 389.37, 398.73, 411.79, 428.35, 445.0, 433.45, 445.27, 443.3, 422.24, 409.99, 404.11, 417.26, 417.85, 426.01, 433.59, 440.36, 442.1, 435.79, 415.88, 423.74, 423.7, 418.45, 391.0, 408.95, 396.68, 381.59, 399.15, 406.43, 411.15, 404.66, 396.38, 400.49, 405.05, 381.61, 375.53, 375.12, 379.71, 411.84, 420.6, 425.3, 393.45, 419.77, 402.9, 394.06, 406.55, 407.76, 394.76, 396.18, 394.46, 391.06, 380.84, 369.57, 378.93, 374.01, 319.69, 313.03, 309.22], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT']}</t>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [405.94, 405.55, 396.73, 398.68, 399.24, 407.82, 395.01, 391.2, 395.56, 399.27, 392.78, 380.3, 367.96, 380.85, 383.03, 385.95, 372.11, 361.83, 355.28, 371.75, 381.26, 360.59, 352.82, 346.65, 343.25, 345.62, 348.95, 352.42, 364.2, 391.95, 388.9, 400.62, 392.5, 386.42, 387.51, 373.72, 376.3, 378.67, 376.02, 372.8, 381.63, 390.82, 392.51, 389.37, 398.73, 411.79, 428.35, 445.0, 433.45, 445.27, 443.3, 422.24, 409.99, 404.11, 417.26, 417.85, 426.01, 433.59, 440.36, 442.1, 435.79, 415.88, 423.74, 423.7, 418.45, 391.0, 408.95, 396.68, 381.59, 399.15, 406.43, 411.15, 404.66, 396.38, 400.49, 405.05, 381.61, 375.53, 375.12, 379.71, 411.84, 420.6, 425.3, 393.45, 419.77, 402.9, 394.06, 406.55, 407.76, 394.76, 396.18, 394.46, 391.06, 380.84, 369.57, 378.93, 374.01, 319.69, 313.03, 309.22], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -771,10 +771,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.444</v>
+        <v>0.475</v>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="F6" t="n">
         <v>70</v>
@@ -783,16 +783,16 @@
         <v>50</v>
       </c>
       <c r="H6" t="n">
-        <v>180</v>
+        <v>1428</v>
       </c>
       <c r="I6" t="n">
-        <v>3.6</v>
+        <v>28.6</v>
       </c>
       <c r="J6" t="n">
         <v>7.5</v>
       </c>
       <c r="K6" t="n">
-        <v>-3.9</v>
+        <v>21.1</v>
       </c>
       <c r="L6" t="n">
         <v>5000</v>
@@ -801,20 +801,20 @@
         <v>25</v>
       </c>
       <c r="N6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O6" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="P6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.5</v>
+        <v>1.7</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [182.82, 183.12, 177.6, 182.43, 184.54, 185.81, 182.93, 180.04, 183.01, 181.72, 180.19, 178.35, 172.5, 175.44, 175.0, 178.47, 171.04, 167.32, 164.98, 174.2, 175.55, 177.18, 177.43, 177.89, 181.87, 183.7, 188.41, 189.09, 196.28, 198.64, 198.12, 201.45, 201.82, 199.65, 202.26, 199.41, 208.03, 216.36, 212.92, 209.01, 199.34, 198.22, 198.25, 196.27, 207.59, 211.25, 214.95, 219.18, 220.52, 225.57, 235.47, 225.06, 222.06, 220.35, 223.21, 219.25, 215.08, 214.61, 212.35, 214.0, 210.89, 224.1, 222.56, 214.5, 218.66, 205.1, 208.64, 208.19, 200.42, 204.87, 205.19, 212.45, 207.41, 204.65, 210.69, 208.65, 200.04, 199.0, 195.74, 192.53, 194.97, 200.09, 197.58, 194.83, 195.55, 196.93, 204.12, 202.78, 210.96, 203.53, 211.8, 212.5, 207.4, 202.81, 203.28, 207.29, 212.06, 208.76, 206.84, 196.51], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [182.82, 183.12, 177.6, 182.43, 184.54, 185.81, 182.93, 180.04, 183.01, 181.72, 180.19, 178.35, 172.5, 175.44, 175.0, 178.47, 171.04, 167.32, 164.98, 174.2, 175.55, 177.18, 177.43, 177.89, 181.87, 183.7, 188.41, 189.09, 196.28, 198.64, 198.12, 201.45, 201.82, 199.65, 202.26, 199.41, 208.03, 216.36, 212.92, 209.01, 199.34, 198.22, 198.25, 196.27, 207.59, 211.25, 214.95, 219.18, 220.52, 225.57, 235.47, 225.06, 222.06, 220.35, 223.21, 219.25, 215.08, 214.61, 212.35, 214.0, 210.89, 224.1, 222.56, 214.5, 218.66, 205.1, 208.64, 208.19, 200.42, 204.87, 205.19, 212.45, 207.41, 204.65, 210.69, 208.65, 200.04, 199.0, 195.74, 192.53, 194.97, 200.09, 197.58, 194.83, 195.55, 196.93, 204.12, 202.78, 210.96, 203.53, 211.8, 212.5, 207.4, 202.81, 203.28, 207.29, 212.06, 208.76, 206.84, 196.51], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -833,28 +833,28 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.348</v>
+        <v>0.306</v>
       </c>
       <c r="E7" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F7" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="G7" t="n">
         <v>83.3</v>
       </c>
       <c r="H7" t="n">
-        <v>-385</v>
+        <v>-74</v>
       </c>
       <c r="I7" t="n">
-        <v>-7.7</v>
+        <v>-1.5</v>
       </c>
       <c r="J7" t="n">
         <v>6.7</v>
       </c>
       <c r="K7" t="n">
-        <v>-14.4</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="L7" t="n">
         <v>5000</v>
@@ -863,20 +863,20 @@
         <v>21</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O7" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="P7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q7" t="n">
-        <v>13</v>
+        <v>2.7</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [216.82, 218.94, 213.21, 213.49, 214.33, 212.65, 209.53, 207.67, 211.74, 215.2, 209.87, 208.76, 205.37, 210.14, 207.24, 211.71, 207.54, 199.34, 200.95, 208.27, 210.57, 209.77, 212.79, 213.77, 221.25, 233.65, 238.38, 239.89, 249.02, 248.5, 249.7, 250.56, 248.28, 249.91, 255.36, 255.08, 263.99, 261.12, 259.7, 263.04, 265.06, 268.26, 272.05, 273.55, 274.99, 271.17, 272.68, 268.99, 265.82, 270.13, 267.22, 264.14, 264.86, 259.34, 265.01, 268.46, 266.32, 265.29, 271.85, 274.0, 270.64, 261.26, 256.52, 250.02, 253.79, 246.03, 245.22, 244.19, 238.0, 241.51, 238.55, 246.02, 246.0, 237.5, 244.39, 232.79, 234.11, 234.27, 227.01, 232.69, 240.14, 238.34, 241.7, 242.67, 244.16, 245.98, 243.62, 247.04, 245.34, 247.31, 247.49, 254.96, 249.89, 247.23, 249.99, 247.55, 244.85, 233.66, 232.11, 231.39], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT']}</t>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [216.82, 218.94, 213.21, 213.49, 214.33, 212.65, 209.53, 207.67, 211.74, 215.2, 209.87, 208.76, 205.37, 210.14, 207.24, 211.71, 207.54, 199.34, 200.95, 208.27, 210.57, 209.77, 212.79, 213.77, 221.25, 233.65, 238.38, 239.89, 249.02, 248.5, 249.7, 250.56, 248.28, 249.91, 255.36, 255.08, 263.99, 261.12, 259.7, 263.04, 265.06, 268.26, 272.05, 273.55, 274.99, 271.17, 272.68, 268.99, 265.82, 270.13, 267.22, 264.14, 264.86, 259.34, 265.01, 268.46, 266.32, 265.29, 271.85, 274.0, 270.64, 261.26, 256.52, 250.02, 253.79, 246.03, 245.22, 244.19, 238.0, 241.51, 238.55, 246.02, 246.0, 237.5, 244.39, 232.79, 234.11, 234.27, 227.01, 232.69, 240.14, 238.34, 241.7, 242.67, 244.16, 245.98, 243.62, 247.04, 245.34, 247.31, 247.49, 254.96, 249.89, 247.23, 249.99, 247.55, 244.85, 233.66, 232.11, 231.39], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'SELL', 'BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
     </row>
@@ -887,7 +887,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -895,28 +895,28 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.399</v>
+        <v>0.361</v>
       </c>
       <c r="E8" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F8" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="G8" t="n">
-        <v>35.3</v>
+        <v>37.5</v>
       </c>
       <c r="H8" t="n">
-        <v>-90</v>
+        <v>39</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J8" t="n">
         <v>-10.9</v>
       </c>
       <c r="K8" t="n">
-        <v>9.1</v>
+        <v>11.7</v>
       </c>
       <c r="L8" t="n">
         <v>5000</v>
@@ -925,20 +925,20 @@
         <v>8</v>
       </c>
       <c r="N8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
         <v>1</v>
       </c>
-      <c r="P8" t="n">
-        <v>2</v>
-      </c>
       <c r="Q8" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [666.54, 659.39, 643.71, 646.24, 652.91, 653.69, 637.04, 612.62, 626.87, 622.08, 615.11, 606.14, 593.11, 603.5, 592.37, 594.34, 547.03, 525.23, 535.88, 571.6, 578.69, 573.93, 572.49, 574.52, 611.85, 627.81, 629.28, 633.94, 661.88, 670.96, 676.24, 687.91, 670.29, 668.22, 674.1, 658.54, 674.4, 677.99, 670.72, 668.5, 611.34, 608.19, 609.84, 604.4, 612.31, 616.24, 609.07, 598.31, 602.44, 616.06, 617.86, 613.66, 610.64, 602.05, 604.5, 606.82, 609.69, 611.77, 634.67, 634.7, 631.92, 599.91, 597.08, 622.4, 626.99, 592.45, 584.85, 584.05, 570.45, 567.9, 566.45, 593.48, 600.21, 567.58, 577.22, 563.85, 562.2, 557.67, 542.87, 550.25, 562.6, 563.29, 612.91, 582.9, 600.29, 615.58, 603.12, 631.48, 669.21, 656.73, 661.04, 681.31, 664.54, 646.01, 645.85, 643.81, 627.17, 606.1, 595.19, 593.87], 'signals': ['FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'SELL', 'BUY', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT']}</t>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [666.54, 659.39, 643.71, 646.24, 652.91, 653.69, 637.04, 612.62, 626.87, 622.08, 615.11, 606.14, 593.11, 603.5, 592.37, 594.34, 547.03, 525.23, 535.88, 571.6, 578.69, 573.93, 572.49, 574.52, 611.85, 627.81, 629.28, 633.94, 661.88, 670.96, 676.24, 687.91, 670.29, 668.22, 674.1, 658.54, 674.4, 677.99, 670.72, 668.5, 611.34, 608.19, 609.84, 604.4, 612.31, 616.24, 609.07, 598.31, 602.44, 616.06, 617.86, 613.66, 610.64, 602.05, 604.5, 606.82, 609.69, 611.77, 634.67, 634.7, 631.92, 599.91, 597.08, 622.4, 626.99, 592.45, 584.85, 584.05, 570.45, 567.9, 566.45, 593.48, 600.21, 567.58, 577.22, 563.85, 562.2, 557.67, 542.87, 550.25, 562.6, 563.29, 612.91, 582.9, 600.29, 615.58, 603.12, 631.48, 669.21, 656.73, 661.04, 681.31, 664.54, 646.01, 645.85, 643.81, 627.17, 606.1, 595.19, 593.87], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
     </row>
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.461</v>
+        <v>0.464</v>
       </c>
       <c r="E9" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F9" t="n">
         <v>30</v>
@@ -969,16 +969,16 @@
         <v>65</v>
       </c>
       <c r="H9" t="n">
-        <v>534</v>
+        <v>604</v>
       </c>
       <c r="I9" t="n">
-        <v>10.7</v>
+        <v>12.1</v>
       </c>
       <c r="J9" t="n">
         <v>20.1</v>
       </c>
       <c r="K9" t="n">
-        <v>-9.4</v>
+        <v>-8</v>
       </c>
       <c r="L9" t="n">
         <v>5000</v>
@@ -987,20 +987,20 @@
         <v>14</v>
       </c>
       <c r="N9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O9" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="P9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.3</v>
+        <v>6.5</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [296.53, 290.75, 286.71, 287.15, 285.97, 284.77, 280.19, 280.73, 283.43, 284.15, 284.99, 285.22, 283.82, 287.14, 289.61, 292.6, 288.87, 280.14, 281.06, 291.35, 292.56, 291.79, 294.12, 296.07, 306.59, 308.94, 308.48, 312.27, 309.72, 304.56, 308.56, 308.9, 315.57, 311.6, 311.62, 310.29, 306.9, 310.23, 310.05, 307.86, 311.83, 311.07, 306.27, 308.01, 313.49, 304.9, 300.75, 298.65, 303.51, 298.9, 298.57, 296.47, 299.38, 294.37, 300.63, 301.64, 305.01, 305.36, 297.94, 295.4, 297.97, 295.25, 299.61, 299.5, 309.5, 310.97, 309.71, 311.3, 307.75, 312.08, 319.28, 317.97, 329.65, 331.96, 323.76, 329.99, 332.64, 331.95, 333.62, 327.57, 327.91, 325.86, 332.57, 332.97, 337.72, 339.22, 330.62, 335.47, 336.47, 334.53, 342.89, 346.91, 343.15, 341.1, 338.87, 345.23, 348.21, 349.9, 353.21, 356.2], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [296.53, 290.75, 286.71, 287.15, 285.97, 284.77, 280.19, 280.73, 283.43, 284.15, 284.99, 285.22, 283.82, 287.14, 289.61, 292.6, 288.87, 280.14, 281.06, 291.35, 292.56, 291.79, 294.12, 296.07, 306.59, 308.94, 308.48, 312.27, 309.72, 304.56, 308.56, 308.9, 315.57, 311.6, 311.62, 310.29, 306.9, 310.23, 310.05, 307.86, 311.83, 311.07, 306.27, 308.01, 313.49, 304.9, 300.75, 298.65, 303.51, 298.9, 298.57, 296.47, 299.38, 294.37, 300.63, 301.64, 305.01, 305.36, 297.94, 295.4, 297.97, 295.25, 299.61, 299.5, 309.5, 310.97, 309.71, 311.3, 307.75, 312.08, 319.28, 317.97, 329.65, 331.96, 323.76, 329.99, 332.64, 331.95, 333.62, 327.57, 327.91, 325.86, 332.57, 332.97, 337.72, 339.22, 330.62, 335.47, 336.47, 334.53, 342.89, 346.91, 343.15, 341.1, 338.87, 345.23, 348.21, 349.9, 353.21, 356.2], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
     </row>

--- a/demo_results.xlsx
+++ b/demo_results.xlsx
@@ -515,18 +515,18 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DOWN</t>
+          <t xml:space="preserve">UP  </t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.194</v>
+        <v>0.838</v>
       </c>
       <c r="E2" t="n">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="F2" t="n">
         <v>50</v>
@@ -535,16 +535,16 @@
         <v>70</v>
       </c>
       <c r="H2" t="n">
-        <v>1045</v>
+        <v>1031</v>
       </c>
       <c r="I2" t="n">
-        <v>20.9</v>
+        <v>20.6</v>
       </c>
       <c r="J2" t="n">
         <v>28.5</v>
       </c>
       <c r="K2" t="n">
-        <v>-7.6</v>
+        <v>-7.9</v>
       </c>
       <c r="L2" t="n">
         <v>5000</v>
@@ -553,20 +553,20 @@
         <v>14</v>
       </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O2" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="P2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>19</v>
+        <v>8.5</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [262.28, 260.05, 257.22, 259.64, 260.59, 260.57, 255.52, 249.89, 252.59, 254.0, 249.71, 248.73, 247.76, 251.26, 251.41, 252.39, 252.66, 248.57, 246.4, 253.56, 255.39, 255.68, 258.62, 253.27, 258.66, 260.25, 260.24, 258.96, 258.59, 266.18, 263.16, 269.98, 272.8, 265.93, 272.92, 273.18, 270.81, 267.36, 270.46, 269.92, 271.1, 279.88, 276.58, 283.92, 287.25, 287.18, 293.05, 292.68, 294.8, 298.87, 298.21, 300.23, 297.84, 298.97, 302.25, 304.99, 308.82, 308.33, 310.85, 312.51, 312.06, 306.31, 315.2, 310.26, 311.23, 307.34, 301.54, 290.55, 291.58, 295.63, 291.13, 296.42, 299.24, 295.95, 298.01, 297.01, 294.3, 293.08, 275.15, 283.78, 281.74, 289.36, 294.38, 308.63, 312.66, 310.66, 313.39, 316.22, 315.32, 317.31, 314.86, 327.5, 333.26, 333.74, 326.59, 327.74, 325.89, 321.66, 333.02, 336.91], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [262.28, 260.05, 257.22, 259.64, 260.59, 260.57, 255.52, 249.89, 252.59, 254.0, 249.71, 248.73, 247.76, 251.26, 251.41, 252.39, 252.66, 248.57, 246.4, 253.56, 255.39, 255.68, 258.62, 253.27, 258.66, 260.25, 260.24, 258.96, 258.59, 266.18, 263.16, 269.98, 272.8, 265.93, 272.92, 273.18, 270.81, 267.36, 270.46, 269.92, 271.1, 279.88, 276.58, 283.92, 287.25, 287.18, 293.05, 292.68, 294.8, 298.87, 298.21, 300.23, 297.84, 298.97, 302.25, 304.99, 308.82, 308.33, 310.85, 312.51, 312.06, 306.31, 315.2, 310.26, 311.23, 307.34, 301.54, 290.55, 291.58, 295.63, 291.13, 296.42, 299.24, 295.95, 298.01, 297.01, 294.3, 293.08, 275.15, 283.78, 281.74, 289.36, 294.38, 308.63, 312.66, 310.66, 313.39, 316.22, 315.32, 317.31, 314.86, 327.5, 333.26, 333.74, 326.59, 327.74, 325.89, 321.66, 333.02, 336.91], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -585,10 +585,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.986</v>
+        <v>0.957</v>
       </c>
       <c r="E3" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="F3" t="n">
         <v>50</v>
@@ -597,16 +597,16 @@
         <v>55.6</v>
       </c>
       <c r="H3" t="n">
-        <v>148</v>
+        <v>-350</v>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>-7</v>
       </c>
       <c r="J3" t="n">
         <v>-3.8</v>
       </c>
       <c r="K3" t="n">
-        <v>6.8</v>
+        <v>-3.2</v>
       </c>
       <c r="L3" t="n">
         <v>5000</v>
@@ -615,20 +615,20 @@
         <v>12</v>
       </c>
       <c r="N3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="P3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [404.32, 409.79, 408.08, 408.53, 404.88, 404.0, 400.99, 394.7, 399.09, 398.55, 390.94, 388.18, 381.04, 382.17, 371.93, 370.24, 365.18, 356.0, 358.18, 369.37, 368.57, 372.65, 372.07, 371.49, 373.52, 372.26, 370.07, 383.54, 392.26, 410.33, 419.35, 421.88, 417.17, 423.24, 431.98, 414.85, 423.7, 423.9, 428.32, 423.54, 406.9, 413.54, 412.73, 410.49, 413.07, 419.86, 414.22, 411.77, 406.89, 404.33, 408.55, 421.01, 422.62, 416.52, 420.15, 419.09, 418.57, 416.03, 412.67, 426.99, 450.24, 460.52, 441.31, 427.34, 428.05, 416.67, 411.74, 403.41, 397.36, 390.34, 390.74, 399.76, 393.83, 378.91, 379.4, 367.34, 373.94, 365.46, 352.83, 372.97, 368.57, 373.02, 384.28, 390.49, 386.74, 388.84, 383.34, 384.36, 385.1, 390.99, 384.93, 395.63, 401.1, 393.82, 402.29, 397.75, 390.34, 381.58, 381.7, 389.1], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [404.32, 409.79, 408.08, 408.53, 404.88, 404.0, 400.99, 394.7, 399.09, 398.55, 390.94, 388.18, 381.04, 382.17, 371.93, 370.24, 365.18, 356.0, 358.18, 369.37, 368.57, 372.65, 372.07, 371.49, 373.52, 372.26, 370.07, 383.54, 392.26, 410.33, 419.35, 421.88, 417.17, 423.24, 431.98, 414.85, 423.7, 423.9, 428.32, 423.54, 406.9, 413.54, 412.73, 410.49, 413.07, 419.86, 414.22, 411.77, 406.89, 404.33, 408.55, 421.01, 422.62, 416.52, 420.15, 419.09, 418.57, 416.03, 412.67, 426.99, 450.24, 460.52, 441.31, 427.34, 428.05, 416.67, 411.74, 403.41, 397.36, 390.34, 390.74, 399.76, 393.83, 378.91, 379.4, 367.34, 373.94, 365.46, 352.83, 372.97, 368.57, 373.02, 384.28, 390.49, 386.74, 388.84, 383.34, 384.36, 385.1, 390.99, 384.93, 395.63, 401.1, 393.82, 402.29, 397.75, 390.34, 381.58, 381.7, 389.1], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -647,10 +647,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.49</v>
+        <v>0.472</v>
       </c>
       <c r="E4" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F4" t="n">
         <v>70</v>
@@ -690,7 +690,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [302.74, 300.49, 298.13, 306.18, 306.86, 308.52, 303.37, 302.1, 305.38, 310.73, 307.51, 306.95, 300.82, 301.88, 290.27, 290.76, 280.75, 274.18, 273.34, 287.39, 297.21, 295.59, 299.81, 305.28, 317.13, 318.3, 317.05, 321.12, 332.71, 336.92, 335.82, 341.48, 337.22, 332.09, 339.12, 338.69, 344.19, 350.13, 349.57, 349.73, 384.57, 385.46, 383.02, 388.2, 397.8, 397.75, 400.56, 388.41, 387.12, 402.38, 400.83, 396.54, 396.7, 387.43, 388.68, 387.43, 382.74, 388.65, 388.6, 389.9, 380.11, 376.15, 361.63, 358.78, 371.97, 368.31, 363.31, 364.26, 356.38, 357.77, 359.68, 369.35, 373.25, 363.79, 368.03, 349.68, 346.13, 345.29, 343.71, 337.39, 353.65, 357.37, 361.21, 359.91, 366.46, 367.03, 361.92, 358.89, 357.18, 352.51, 359.51, 370.92, 354.46, 346.77, 351.99, 347.15, 342.09, 317.69, 319.74, 326.56], 'signals': ['BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [302.74, 300.49, 298.13, 306.18, 306.86, 308.52, 303.37, 302.1, 305.38, 310.73, 307.51, 306.95, 300.82, 301.88, 290.27, 290.76, 280.75, 274.18, 273.34, 287.39, 297.21, 295.59, 299.81, 305.28, 317.13, 318.3, 317.05, 321.12, 332.71, 336.92, 335.82, 341.48, 337.22, 332.09, 339.12, 338.69, 344.19, 350.13, 349.57, 349.73, 384.57, 385.46, 383.02, 388.2, 397.8, 397.75, 400.56, 388.41, 387.12, 402.38, 400.83, 396.54, 396.7, 387.43, 388.68, 387.43, 382.74, 388.65, 388.6, 389.9, 380.11, 376.15, 361.63, 358.78, 371.97, 368.31, 363.31, 364.26, 356.38, 357.77, 359.68, 369.35, 373.25, 363.79, 368.03, 349.68, 346.13, 345.29, 343.71, 337.39, 353.65, 357.37, 361.21, 359.91, 366.46, 367.03, 361.92, 358.89, 357.18, 352.51, 359.51, 370.92, 354.46, 346.77, 351.99, 347.15, 342.09, 317.69, 319.74, 326.56], 'signals': ['BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
     </row>
@@ -701,36 +701,36 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DOWN</t>
+          <t xml:space="preserve">UP  </t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.373</v>
+        <v>0.654</v>
       </c>
       <c r="E5" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="F5" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>-549</v>
+        <v>-555</v>
       </c>
       <c r="I5" t="n">
-        <v>-11</v>
+        <v>-11.1</v>
       </c>
       <c r="J5" t="n">
         <v>-23.8</v>
       </c>
       <c r="K5" t="n">
-        <v>12.8</v>
+        <v>12.7</v>
       </c>
       <c r="L5" t="n">
         <v>5000</v>
@@ -742,17 +742,17 @@
         <v>5</v>
       </c>
       <c r="O5" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="P5" t="n">
         <v>5</v>
       </c>
       <c r="Q5" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [405.94, 405.55, 396.73, 398.68, 399.24, 407.82, 395.01, 391.2, 395.56, 399.27, 392.78, 380.3, 367.96, 380.85, 383.03, 385.95, 372.11, 361.83, 355.28, 371.75, 381.26, 360.59, 352.82, 346.65, 343.25, 345.62, 348.95, 352.42, 364.2, 391.95, 388.9, 400.62, 392.5, 386.42, 387.51, 373.72, 376.3, 378.67, 376.02, 372.8, 381.63, 390.82, 392.51, 389.37, 398.73, 411.79, 428.35, 445.0, 433.45, 445.27, 443.3, 422.24, 409.99, 404.11, 417.26, 417.85, 426.01, 433.59, 440.36, 442.1, 435.79, 415.88, 423.74, 423.7, 418.45, 391.0, 408.95, 396.68, 381.59, 399.15, 406.43, 411.15, 404.66, 396.38, 400.49, 405.05, 381.61, 375.53, 375.12, 379.71, 411.84, 420.6, 425.3, 393.45, 419.77, 402.9, 394.06, 406.55, 407.76, 394.76, 396.18, 394.46, 391.06, 380.84, 369.57, 378.93, 374.01, 319.69, 313.03, 309.22], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [405.94, 405.55, 396.73, 398.68, 399.24, 407.82, 395.01, 391.2, 395.56, 399.27, 392.78, 380.3, 367.96, 380.85, 383.03, 385.95, 372.11, 361.83, 355.28, 371.75, 381.26, 360.59, 352.82, 346.65, 343.25, 345.62, 348.95, 352.42, 364.2, 391.95, 388.9, 400.62, 392.5, 386.42, 387.51, 373.72, 376.3, 378.67, 376.02, 372.8, 381.63, 390.82, 392.51, 389.37, 398.73, 411.79, 428.35, 445.0, 433.45, 445.27, 443.3, 422.24, 409.99, 404.11, 417.26, 417.85, 426.01, 433.59, 440.36, 442.1, 435.79, 415.88, 423.74, 423.7, 418.45, 391.0, 408.95, 396.68, 381.59, 399.15, 406.43, 411.15, 404.66, 396.38, 400.49, 405.05, 381.61, 375.53, 375.12, 379.71, 411.84, 420.6, 425.3, 393.45, 419.77, 402.9, 394.06, 406.55, 407.76, 394.76, 396.18, 394.46, 391.06, 380.84, 369.57, 378.93, 374.01, 319.69, 313.03, 309.22], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -771,10 +771,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.475</v>
+        <v>0.352</v>
       </c>
       <c r="E6" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F6" t="n">
         <v>70</v>
@@ -783,16 +783,16 @@
         <v>50</v>
       </c>
       <c r="H6" t="n">
-        <v>1428</v>
+        <v>823</v>
       </c>
       <c r="I6" t="n">
-        <v>28.6</v>
+        <v>16.5</v>
       </c>
       <c r="J6" t="n">
         <v>7.5</v>
       </c>
       <c r="K6" t="n">
-        <v>21.1</v>
+        <v>9</v>
       </c>
       <c r="L6" t="n">
         <v>5000</v>
@@ -804,17 +804,17 @@
         <v>6</v>
       </c>
       <c r="O6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P6" t="n">
         <v>6</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [182.82, 183.12, 177.6, 182.43, 184.54, 185.81, 182.93, 180.04, 183.01, 181.72, 180.19, 178.35, 172.5, 175.44, 175.0, 178.47, 171.04, 167.32, 164.98, 174.2, 175.55, 177.18, 177.43, 177.89, 181.87, 183.7, 188.41, 189.09, 196.28, 198.64, 198.12, 201.45, 201.82, 199.65, 202.26, 199.41, 208.03, 216.36, 212.92, 209.01, 199.34, 198.22, 198.25, 196.27, 207.59, 211.25, 214.95, 219.18, 220.52, 225.57, 235.47, 225.06, 222.06, 220.35, 223.21, 219.25, 215.08, 214.61, 212.35, 214.0, 210.89, 224.1, 222.56, 214.5, 218.66, 205.1, 208.64, 208.19, 200.42, 204.87, 205.19, 212.45, 207.41, 204.65, 210.69, 208.65, 200.04, 199.0, 195.74, 192.53, 194.97, 200.09, 197.58, 194.83, 195.55, 196.93, 204.12, 202.78, 210.96, 203.53, 211.8, 212.5, 207.4, 202.81, 203.28, 207.29, 212.06, 208.76, 206.84, 196.51], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [182.82, 183.12, 177.6, 182.43, 184.54, 185.81, 182.93, 180.04, 183.01, 181.72, 180.19, 178.35, 172.5, 175.44, 175.0, 178.47, 171.04, 167.32, 164.98, 174.2, 175.55, 177.18, 177.43, 177.89, 181.87, 183.7, 188.41, 189.09, 196.28, 198.64, 198.12, 201.45, 201.82, 199.65, 202.26, 199.41, 208.03, 216.36, 212.92, 209.01, 199.34, 198.22, 198.25, 196.27, 207.59, 211.25, 214.95, 219.18, 220.52, 225.57, 235.47, 225.06, 222.06, 220.35, 223.21, 219.25, 215.08, 214.61, 212.35, 214.0, 210.89, 224.1, 222.56, 214.5, 218.66, 205.1, 208.64, 208.19, 200.42, 204.87, 205.19, 212.45, 207.41, 204.65, 210.69, 208.65, 200.04, 199.0, 195.74, 192.53, 194.97, 200.09, 197.58, 194.83, 195.55, 196.93, 204.12, 202.78, 210.96, 203.53, 211.8, 212.5, 207.4, 202.81, 203.28, 207.29, 212.06, 208.76, 206.84, 196.51], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
     </row>
@@ -825,36 +825,36 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DOWN</t>
+          <t xml:space="preserve">UP  </t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.306</v>
+        <v>0.738</v>
       </c>
       <c r="E7" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="F7" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="G7" t="n">
         <v>83.3</v>
       </c>
       <c r="H7" t="n">
-        <v>-74</v>
+        <v>188</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.5</v>
+        <v>3.8</v>
       </c>
       <c r="J7" t="n">
         <v>6.7</v>
       </c>
       <c r="K7" t="n">
-        <v>-8.199999999999999</v>
+        <v>-2.9</v>
       </c>
       <c r="L7" t="n">
         <v>5000</v>
@@ -863,20 +863,20 @@
         <v>21</v>
       </c>
       <c r="N7" t="n">
+        <v>2</v>
+      </c>
+      <c r="O7" t="n">
+        <v>4</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q7" t="n">
         <v>3</v>
       </c>
-      <c r="O7" t="n">
-        <v>6</v>
-      </c>
-      <c r="P7" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2.7</v>
-      </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [216.82, 218.94, 213.21, 213.49, 214.33, 212.65, 209.53, 207.67, 211.74, 215.2, 209.87, 208.76, 205.37, 210.14, 207.24, 211.71, 207.54, 199.34, 200.95, 208.27, 210.57, 209.77, 212.79, 213.77, 221.25, 233.65, 238.38, 239.89, 249.02, 248.5, 249.7, 250.56, 248.28, 249.91, 255.36, 255.08, 263.99, 261.12, 259.7, 263.04, 265.06, 268.26, 272.05, 273.55, 274.99, 271.17, 272.68, 268.99, 265.82, 270.13, 267.22, 264.14, 264.86, 259.34, 265.01, 268.46, 266.32, 265.29, 271.85, 274.0, 270.64, 261.26, 256.52, 250.02, 253.79, 246.03, 245.22, 244.19, 238.0, 241.51, 238.55, 246.02, 246.0, 237.5, 244.39, 232.79, 234.11, 234.27, 227.01, 232.69, 240.14, 238.34, 241.7, 242.67, 244.16, 245.98, 243.62, 247.04, 245.34, 247.31, 247.49, 254.96, 249.89, 247.23, 249.99, 247.55, 244.85, 233.66, 232.11, 231.39], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'SELL', 'BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [216.82, 218.94, 213.21, 213.49, 214.33, 212.65, 209.53, 207.67, 211.74, 215.2, 209.87, 208.76, 205.37, 210.14, 207.24, 211.71, 207.54, 199.34, 200.95, 208.27, 210.57, 209.77, 212.79, 213.77, 221.25, 233.65, 238.38, 239.89, 249.02, 248.5, 249.7, 250.56, 248.28, 249.91, 255.36, 255.08, 263.99, 261.12, 259.7, 263.04, 265.06, 268.26, 272.05, 273.55, 274.99, 271.17, 272.68, 268.99, 265.82, 270.13, 267.22, 264.14, 264.86, 259.34, 265.01, 268.46, 266.32, 265.29, 271.85, 274.0, 270.64, 261.26, 256.52, 250.02, 253.79, 246.03, 245.22, 244.19, 238.0, 241.51, 238.55, 246.02, 246.0, 237.5, 244.39, 232.79, 234.11, 234.27, 227.01, 232.69, 240.14, 238.34, 241.7, 242.67, 244.16, 245.98, 243.62, 247.04, 245.34, 247.31, 247.49, 254.96, 249.89, 247.23, 249.99, 247.55, 244.85, 233.66, 232.11, 231.39], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
     </row>
@@ -887,36 +887,36 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DOWN</t>
+          <t xml:space="preserve">UP  </t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.361</v>
+        <v>0.649</v>
       </c>
       <c r="E8" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F8" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="G8" t="n">
-        <v>37.5</v>
+        <v>33.3</v>
       </c>
       <c r="H8" t="n">
-        <v>39</v>
+        <v>-733</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8</v>
+        <v>-14.7</v>
       </c>
       <c r="J8" t="n">
         <v>-10.9</v>
       </c>
       <c r="K8" t="n">
-        <v>11.7</v>
+        <v>-3.8</v>
       </c>
       <c r="L8" t="n">
         <v>5000</v>
@@ -925,20 +925,20 @@
         <v>8</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [666.54, 659.39, 643.71, 646.24, 652.91, 653.69, 637.04, 612.62, 626.87, 622.08, 615.11, 606.14, 593.11, 603.5, 592.37, 594.34, 547.03, 525.23, 535.88, 571.6, 578.69, 573.93, 572.49, 574.52, 611.85, 627.81, 629.28, 633.94, 661.88, 670.96, 676.24, 687.91, 670.29, 668.22, 674.1, 658.54, 674.4, 677.99, 670.72, 668.5, 611.34, 608.19, 609.84, 604.4, 612.31, 616.24, 609.07, 598.31, 602.44, 616.06, 617.86, 613.66, 610.64, 602.05, 604.5, 606.82, 609.69, 611.77, 634.67, 634.7, 631.92, 599.91, 597.08, 622.4, 626.99, 592.45, 584.85, 584.05, 570.45, 567.9, 566.45, 593.48, 600.21, 567.58, 577.22, 563.85, 562.2, 557.67, 542.87, 550.25, 562.6, 563.29, 612.91, 582.9, 600.29, 615.58, 603.12, 631.48, 669.21, 656.73, 661.04, 681.31, 664.54, 646.01, 645.85, 643.81, 627.17, 606.1, 595.19, 593.87], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [666.54, 659.39, 643.71, 646.24, 652.91, 653.69, 637.04, 612.62, 626.87, 622.08, 615.11, 606.14, 593.11, 603.5, 592.37, 594.34, 547.03, 525.23, 535.88, 571.6, 578.69, 573.93, 572.49, 574.52, 611.85, 627.81, 629.28, 633.94, 661.88, 670.96, 676.24, 687.91, 670.29, 668.22, 674.1, 658.54, 674.4, 677.99, 670.72, 668.5, 611.34, 608.19, 609.84, 604.4, 612.31, 616.24, 609.07, 598.31, 602.44, 616.06, 617.86, 613.66, 610.64, 602.05, 604.5, 606.82, 609.69, 611.77, 634.67, 634.7, 631.92, 599.91, 597.08, 622.4, 626.99, 592.45, 584.85, 584.05, 570.45, 567.9, 566.45, 593.48, 600.21, 567.58, 577.22, 563.85, 562.2, 557.67, 542.87, 550.25, 562.6, 563.29, 612.91, 582.9, 600.29, 615.58, 603.12, 631.48, 669.21, 656.73, 661.04, 681.31, 664.54, 646.01, 645.85, 643.81, 627.17, 606.1, 595.19, 593.87], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.464</v>
+        <v>0.267</v>
       </c>
       <c r="E9" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F9" t="n">
         <v>30</v>
@@ -969,16 +969,16 @@
         <v>65</v>
       </c>
       <c r="H9" t="n">
-        <v>604</v>
+        <v>792</v>
       </c>
       <c r="I9" t="n">
-        <v>12.1</v>
+        <v>15.8</v>
       </c>
       <c r="J9" t="n">
         <v>20.1</v>
       </c>
       <c r="K9" t="n">
-        <v>-8</v>
+        <v>-4.3</v>
       </c>
       <c r="L9" t="n">
         <v>5000</v>
@@ -990,17 +990,17 @@
         <v>2</v>
       </c>
       <c r="O9" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="P9" t="n">
         <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [296.53, 290.75, 286.71, 287.15, 285.97, 284.77, 280.19, 280.73, 283.43, 284.15, 284.99, 285.22, 283.82, 287.14, 289.61, 292.6, 288.87, 280.14, 281.06, 291.35, 292.56, 291.79, 294.12, 296.07, 306.59, 308.94, 308.48, 312.27, 309.72, 304.56, 308.56, 308.9, 315.57, 311.6, 311.62, 310.29, 306.9, 310.23, 310.05, 307.86, 311.83, 311.07, 306.27, 308.01, 313.49, 304.9, 300.75, 298.65, 303.51, 298.9, 298.57, 296.47, 299.38, 294.37, 300.63, 301.64, 305.01, 305.36, 297.94, 295.4, 297.97, 295.25, 299.61, 299.5, 309.5, 310.97, 309.71, 311.3, 307.75, 312.08, 319.28, 317.97, 329.65, 331.96, 323.76, 329.99, 332.64, 331.95, 333.62, 327.57, 327.91, 325.86, 332.57, 332.97, 337.72, 339.22, 330.62, 335.47, 336.47, 334.53, 342.89, 346.91, 343.15, 341.1, 338.87, 345.23, 348.21, 349.9, 353.21, 356.2], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [296.53, 290.75, 286.71, 287.15, 285.97, 284.77, 280.19, 280.73, 283.43, 284.15, 284.99, 285.22, 283.82, 287.14, 289.61, 292.6, 288.87, 280.14, 281.06, 291.35, 292.56, 291.79, 294.12, 296.07, 306.59, 308.94, 308.48, 312.27, 309.72, 304.56, 308.56, 308.9, 315.57, 311.6, 311.62, 310.29, 306.9, 310.23, 310.05, 307.86, 311.83, 311.07, 306.27, 308.01, 313.49, 304.9, 300.75, 298.65, 303.51, 298.9, 298.57, 296.47, 299.38, 294.37, 300.63, 301.64, 305.01, 305.36, 297.94, 295.4, 297.97, 295.25, 299.61, 299.5, 309.5, 310.97, 309.71, 311.3, 307.75, 312.08, 319.28, 317.97, 329.65, 331.96, 323.76, 329.99, 332.64, 331.95, 333.62, 327.57, 327.91, 325.86, 332.57, 332.97, 337.72, 339.22, 330.62, 335.47, 336.47, 334.53, 342.89, 346.91, 343.15, 341.1, 338.87, 345.23, 348.21, 349.9, 353.21, 356.2], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
     </row>

--- a/demo_results.xlsx
+++ b/demo_results.xlsx
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.838</v>
+        <v>0.617</v>
       </c>
       <c r="E2" t="n">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="F2" t="n">
         <v>50</v>
@@ -535,16 +535,16 @@
         <v>70</v>
       </c>
       <c r="H2" t="n">
-        <v>1031</v>
+        <v>602</v>
       </c>
       <c r="I2" t="n">
-        <v>20.6</v>
+        <v>12</v>
       </c>
       <c r="J2" t="n">
         <v>28.5</v>
       </c>
       <c r="K2" t="n">
-        <v>-7.9</v>
+        <v>-16.5</v>
       </c>
       <c r="L2" t="n">
         <v>5000</v>
@@ -553,20 +553,20 @@
         <v>14</v>
       </c>
       <c r="N2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q2" t="n">
-        <v>8.5</v>
+        <v>5.7</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [262.28, 260.05, 257.22, 259.64, 260.59, 260.57, 255.52, 249.89, 252.59, 254.0, 249.71, 248.73, 247.76, 251.26, 251.41, 252.39, 252.66, 248.57, 246.4, 253.56, 255.39, 255.68, 258.62, 253.27, 258.66, 260.25, 260.24, 258.96, 258.59, 266.18, 263.16, 269.98, 272.8, 265.93, 272.92, 273.18, 270.81, 267.36, 270.46, 269.92, 271.1, 279.88, 276.58, 283.92, 287.25, 287.18, 293.05, 292.68, 294.8, 298.87, 298.21, 300.23, 297.84, 298.97, 302.25, 304.99, 308.82, 308.33, 310.85, 312.51, 312.06, 306.31, 315.2, 310.26, 311.23, 307.34, 301.54, 290.55, 291.58, 295.63, 291.13, 296.42, 299.24, 295.95, 298.01, 297.01, 294.3, 293.08, 275.15, 283.78, 281.74, 289.36, 294.38, 308.63, 312.66, 310.66, 313.39, 316.22, 315.32, 317.31, 314.86, 327.5, 333.26, 333.74, 326.59, 327.74, 325.89, 321.66, 333.02, 336.91], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [262.28, 260.05, 257.22, 259.64, 260.59, 260.57, 255.52, 249.89, 252.59, 254.0, 249.71, 248.73, 247.76, 251.26, 251.41, 252.39, 252.66, 248.57, 246.4, 253.56, 255.39, 255.68, 258.62, 253.27, 258.66, 260.25, 260.24, 258.96, 258.59, 266.18, 263.16, 269.98, 272.8, 265.93, 272.92, 273.18, 270.81, 267.36, 270.46, 269.92, 271.1, 279.88, 276.58, 283.92, 287.25, 287.18, 293.05, 292.68, 294.8, 298.87, 298.21, 300.23, 297.84, 298.97, 302.25, 304.99, 308.82, 308.33, 310.85, 312.51, 312.06, 306.31, 315.2, 310.26, 311.23, 307.34, 301.54, 290.55, 291.58, 295.63, 291.13, 296.42, 299.24, 295.95, 298.01, 297.01, 294.3, 293.08, 275.15, 283.78, 281.74, 289.36, 294.38, 308.63, 312.66, 310.66, 313.39, 316.22, 315.32, 317.31, 314.86, 327.5, 333.26, 333.74, 326.59, 327.74, 325.89, 321.66, 333.02, 336.91], 'signals': ['BUY', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -585,10 +585,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.957</v>
+        <v>0.916</v>
       </c>
       <c r="E3" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="F3" t="n">
         <v>50</v>
@@ -597,16 +597,16 @@
         <v>55.6</v>
       </c>
       <c r="H3" t="n">
-        <v>-350</v>
+        <v>-136</v>
       </c>
       <c r="I3" t="n">
-        <v>-7</v>
+        <v>-2.7</v>
       </c>
       <c r="J3" t="n">
         <v>-3.8</v>
       </c>
       <c r="K3" t="n">
-        <v>-3.2</v>
+        <v>1.1</v>
       </c>
       <c r="L3" t="n">
         <v>5000</v>
@@ -618,17 +618,17 @@
         <v>3</v>
       </c>
       <c r="O3" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
       </c>
       <c r="Q3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [404.32, 409.79, 408.08, 408.53, 404.88, 404.0, 400.99, 394.7, 399.09, 398.55, 390.94, 388.18, 381.04, 382.17, 371.93, 370.24, 365.18, 356.0, 358.18, 369.37, 368.57, 372.65, 372.07, 371.49, 373.52, 372.26, 370.07, 383.54, 392.26, 410.33, 419.35, 421.88, 417.17, 423.24, 431.98, 414.85, 423.7, 423.9, 428.32, 423.54, 406.9, 413.54, 412.73, 410.49, 413.07, 419.86, 414.22, 411.77, 406.89, 404.33, 408.55, 421.01, 422.62, 416.52, 420.15, 419.09, 418.57, 416.03, 412.67, 426.99, 450.24, 460.52, 441.31, 427.34, 428.05, 416.67, 411.74, 403.41, 397.36, 390.34, 390.74, 399.76, 393.83, 378.91, 379.4, 367.34, 373.94, 365.46, 352.83, 372.97, 368.57, 373.02, 384.28, 390.49, 386.74, 388.84, 383.34, 384.36, 385.1, 390.99, 384.93, 395.63, 401.1, 393.82, 402.29, 397.75, 390.34, 381.58, 381.7, 389.1], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [404.32, 409.79, 408.08, 408.53, 404.88, 404.0, 400.99, 394.7, 399.09, 398.55, 390.94, 388.18, 381.04, 382.17, 371.93, 370.24, 365.18, 356.0, 358.18, 369.37, 368.57, 372.65, 372.07, 371.49, 373.52, 372.26, 370.07, 383.54, 392.26, 410.33, 419.35, 421.88, 417.17, 423.24, 431.98, 414.85, 423.7, 423.9, 428.32, 423.54, 406.9, 413.54, 412.73, 410.49, 413.07, 419.86, 414.22, 411.77, 406.89, 404.33, 408.55, 421.01, 422.62, 416.52, 420.15, 419.09, 418.57, 416.03, 412.67, 426.99, 450.24, 460.52, 441.31, 427.34, 428.05, 416.67, 411.74, 403.41, 397.36, 390.34, 390.74, 399.76, 393.83, 378.91, 379.4, 367.34, 373.94, 365.46, 352.83, 372.97, 368.57, 373.02, 384.28, 390.49, 386.74, 388.84, 383.34, 384.36, 385.1, 390.99, 384.93, 395.63, 401.1, 393.82, 402.29, 397.75, 390.34, 381.58, 381.7, 389.1], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -647,10 +647,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.472</v>
+        <v>0.5</v>
       </c>
       <c r="E4" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F4" t="n">
         <v>70</v>
@@ -659,16 +659,16 @@
         <v>50</v>
       </c>
       <c r="H4" t="n">
-        <v>87</v>
+        <v>351</v>
       </c>
       <c r="I4" t="n">
-        <v>1.7</v>
+        <v>7</v>
       </c>
       <c r="J4" t="n">
         <v>7.9</v>
       </c>
       <c r="K4" t="n">
-        <v>-6.2</v>
+        <v>-0.9</v>
       </c>
       <c r="L4" t="n">
         <v>5000</v>
@@ -677,20 +677,20 @@
         <v>15</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="P4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>5.3</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [302.74, 300.49, 298.13, 306.18, 306.86, 308.52, 303.37, 302.1, 305.38, 310.73, 307.51, 306.95, 300.82, 301.88, 290.27, 290.76, 280.75, 274.18, 273.34, 287.39, 297.21, 295.59, 299.81, 305.28, 317.13, 318.3, 317.05, 321.12, 332.71, 336.92, 335.82, 341.48, 337.22, 332.09, 339.12, 338.69, 344.19, 350.13, 349.57, 349.73, 384.57, 385.46, 383.02, 388.2, 397.8, 397.75, 400.56, 388.41, 387.12, 402.38, 400.83, 396.54, 396.7, 387.43, 388.68, 387.43, 382.74, 388.65, 388.6, 389.9, 380.11, 376.15, 361.63, 358.78, 371.97, 368.31, 363.31, 364.26, 356.38, 357.77, 359.68, 369.35, 373.25, 363.79, 368.03, 349.68, 346.13, 345.29, 343.71, 337.39, 353.65, 357.37, 361.21, 359.91, 366.46, 367.03, 361.92, 358.89, 357.18, 352.51, 359.51, 370.92, 354.46, 346.77, 351.99, 347.15, 342.09, 317.69, 319.74, 326.56], 'signals': ['BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [302.74, 300.49, 298.13, 306.18, 306.86, 308.52, 303.37, 302.1, 305.38, 310.73, 307.51, 306.95, 300.82, 301.88, 290.27, 290.76, 280.75, 274.18, 273.34, 287.39, 297.21, 295.59, 299.81, 305.28, 317.13, 318.3, 317.05, 321.12, 332.71, 336.92, 335.82, 341.48, 337.22, 332.09, 339.12, 338.69, 344.19, 350.13, 349.57, 349.73, 384.57, 385.46, 383.02, 388.2, 397.8, 397.75, 400.56, 388.41, 387.12, 402.38, 400.83, 396.54, 396.7, 387.43, 388.68, 387.43, 382.74, 388.65, 388.6, 389.9, 380.11, 376.15, 361.63, 358.78, 371.97, 368.31, 363.31, 364.26, 356.38, 357.77, 359.68, 369.35, 373.25, 363.79, 368.03, 349.68, 346.13, 345.29, 343.71, 337.39, 353.65, 357.37, 361.21, 359.91, 366.46, 367.03, 361.92, 358.89, 357.18, 352.51, 359.51, 370.92, 354.46, 346.77, 351.99, 347.15, 342.09, 317.69, 319.74, 326.56], 'signals': ['FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
     </row>
@@ -701,36 +701,36 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">UP  </t>
+          <t>DOWN</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.654</v>
+        <v>0.416</v>
       </c>
       <c r="E5" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H5" t="n">
-        <v>-555</v>
+        <v>314</v>
       </c>
       <c r="I5" t="n">
-        <v>-11.1</v>
+        <v>6.3</v>
       </c>
       <c r="J5" t="n">
         <v>-23.8</v>
       </c>
       <c r="K5" t="n">
-        <v>12.7</v>
+        <v>30.1</v>
       </c>
       <c r="L5" t="n">
         <v>5000</v>
@@ -739,20 +739,20 @@
         <v>16</v>
       </c>
       <c r="N5" t="n">
+        <v>6</v>
+      </c>
+      <c r="O5" t="n">
         <v>5</v>
       </c>
-      <c r="O5" t="n">
-        <v>4</v>
-      </c>
       <c r="P5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [405.94, 405.55, 396.73, 398.68, 399.24, 407.82, 395.01, 391.2, 395.56, 399.27, 392.78, 380.3, 367.96, 380.85, 383.03, 385.95, 372.11, 361.83, 355.28, 371.75, 381.26, 360.59, 352.82, 346.65, 343.25, 345.62, 348.95, 352.42, 364.2, 391.95, 388.9, 400.62, 392.5, 386.42, 387.51, 373.72, 376.3, 378.67, 376.02, 372.8, 381.63, 390.82, 392.51, 389.37, 398.73, 411.79, 428.35, 445.0, 433.45, 445.27, 443.3, 422.24, 409.99, 404.11, 417.26, 417.85, 426.01, 433.59, 440.36, 442.1, 435.79, 415.88, 423.74, 423.7, 418.45, 391.0, 408.95, 396.68, 381.59, 399.15, 406.43, 411.15, 404.66, 396.38, 400.49, 405.05, 381.61, 375.53, 375.12, 379.71, 411.84, 420.6, 425.3, 393.45, 419.77, 402.9, 394.06, 406.55, 407.76, 394.76, 396.18, 394.46, 391.06, 380.84, 369.57, 378.93, 374.01, 319.69, 313.03, 309.22], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [405.94, 405.55, 396.73, 398.68, 399.24, 407.82, 395.01, 391.2, 395.56, 399.27, 392.78, 380.3, 367.96, 380.85, 383.03, 385.95, 372.11, 361.83, 355.28, 371.75, 381.26, 360.59, 352.82, 346.65, 343.25, 345.62, 348.95, 352.42, 364.2, 391.95, 388.9, 400.62, 392.5, 386.42, 387.51, 373.72, 376.3, 378.67, 376.02, 372.8, 381.63, 390.82, 392.51, 389.37, 398.73, 411.79, 428.35, 445.0, 433.45, 445.27, 443.3, 422.24, 409.99, 404.11, 417.26, 417.85, 426.01, 433.59, 440.36, 442.1, 435.79, 415.88, 423.74, 423.7, 418.45, 391.0, 408.95, 396.68, 381.59, 399.15, 406.43, 411.15, 404.66, 396.38, 400.49, 405.05, 381.61, 375.53, 375.12, 379.71, 411.84, 420.6, 425.3, 393.45, 419.77, 402.9, 394.06, 406.55, 407.76, 394.76, 396.18, 394.46, 391.06, 380.84, 369.57, 378.93, 374.01, 319.69, 313.03, 309.22], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
     </row>
@@ -763,36 +763,36 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>61</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.436</v>
+      </c>
+      <c r="E6" t="n">
         <v>63</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>DOWN</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>0.352</v>
-      </c>
-      <c r="E6" t="n">
-        <v>65</v>
-      </c>
       <c r="F6" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="G6" t="n">
         <v>50</v>
       </c>
       <c r="H6" t="n">
-        <v>823</v>
+        <v>570</v>
       </c>
       <c r="I6" t="n">
-        <v>16.5</v>
+        <v>11.4</v>
       </c>
       <c r="J6" t="n">
         <v>7.5</v>
       </c>
       <c r="K6" t="n">
-        <v>9</v>
+        <v>3.9</v>
       </c>
       <c r="L6" t="n">
         <v>5000</v>
@@ -801,20 +801,20 @@
         <v>25</v>
       </c>
       <c r="N6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [182.82, 183.12, 177.6, 182.43, 184.54, 185.81, 182.93, 180.04, 183.01, 181.72, 180.19, 178.35, 172.5, 175.44, 175.0, 178.47, 171.04, 167.32, 164.98, 174.2, 175.55, 177.18, 177.43, 177.89, 181.87, 183.7, 188.41, 189.09, 196.28, 198.64, 198.12, 201.45, 201.82, 199.65, 202.26, 199.41, 208.03, 216.36, 212.92, 209.01, 199.34, 198.22, 198.25, 196.27, 207.59, 211.25, 214.95, 219.18, 220.52, 225.57, 235.47, 225.06, 222.06, 220.35, 223.21, 219.25, 215.08, 214.61, 212.35, 214.0, 210.89, 224.1, 222.56, 214.5, 218.66, 205.1, 208.64, 208.19, 200.42, 204.87, 205.19, 212.45, 207.41, 204.65, 210.69, 208.65, 200.04, 199.0, 195.74, 192.53, 194.97, 200.09, 197.58, 194.83, 195.55, 196.93, 204.12, 202.78, 210.96, 203.53, 211.8, 212.5, 207.4, 202.81, 203.28, 207.29, 212.06, 208.76, 206.84, 196.51], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [182.82, 183.12, 177.6, 182.43, 184.54, 185.81, 182.93, 180.04, 183.01, 181.72, 180.19, 178.35, 172.5, 175.44, 175.0, 178.47, 171.04, 167.32, 164.98, 174.2, 175.55, 177.18, 177.43, 177.89, 181.87, 183.7, 188.41, 189.09, 196.28, 198.64, 198.12, 201.45, 201.82, 199.65, 202.26, 199.41, 208.03, 216.36, 212.92, 209.01, 199.34, 198.22, 198.25, 196.27, 207.59, 211.25, 214.95, 219.18, 220.52, 225.57, 235.47, 225.06, 222.06, 220.35, 223.21, 219.25, 215.08, 214.61, 212.35, 214.0, 210.89, 224.1, 222.56, 214.5, 218.66, 205.1, 208.64, 208.19, 200.42, 204.87, 205.19, 212.45, 207.41, 204.65, 210.69, 208.65, 200.04, 199.0, 195.74, 192.53, 194.97, 200.09, 197.58, 194.83, 195.55, 196.93, 204.12, 202.78, 210.96, 203.53, 211.8, 212.5, 207.4, 202.81, 203.28, 207.29, 212.06, 208.76, 206.84, 196.51], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY']}</t>
         </is>
       </c>
     </row>
@@ -825,18 +825,18 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">UP  </t>
+          <t>DOWN</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.738</v>
+        <v>0.373</v>
       </c>
       <c r="E7" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="F7" t="n">
         <v>40</v>
@@ -845,16 +845,16 @@
         <v>83.3</v>
       </c>
       <c r="H7" t="n">
-        <v>188</v>
+        <v>828</v>
       </c>
       <c r="I7" t="n">
-        <v>3.8</v>
+        <v>16.6</v>
       </c>
       <c r="J7" t="n">
         <v>6.7</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.9</v>
+        <v>9.9</v>
       </c>
       <c r="L7" t="n">
         <v>5000</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [216.82, 218.94, 213.21, 213.49, 214.33, 212.65, 209.53, 207.67, 211.74, 215.2, 209.87, 208.76, 205.37, 210.14, 207.24, 211.71, 207.54, 199.34, 200.95, 208.27, 210.57, 209.77, 212.79, 213.77, 221.25, 233.65, 238.38, 239.89, 249.02, 248.5, 249.7, 250.56, 248.28, 249.91, 255.36, 255.08, 263.99, 261.12, 259.7, 263.04, 265.06, 268.26, 272.05, 273.55, 274.99, 271.17, 272.68, 268.99, 265.82, 270.13, 267.22, 264.14, 264.86, 259.34, 265.01, 268.46, 266.32, 265.29, 271.85, 274.0, 270.64, 261.26, 256.52, 250.02, 253.79, 246.03, 245.22, 244.19, 238.0, 241.51, 238.55, 246.02, 246.0, 237.5, 244.39, 232.79, 234.11, 234.27, 227.01, 232.69, 240.14, 238.34, 241.7, 242.67, 244.16, 245.98, 243.62, 247.04, 245.34, 247.31, 247.49, 254.96, 249.89, 247.23, 249.99, 247.55, 244.85, 233.66, 232.11, 231.39], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [216.82, 218.94, 213.21, 213.49, 214.33, 212.65, 209.53, 207.67, 211.74, 215.2, 209.87, 208.76, 205.37, 210.14, 207.24, 211.71, 207.54, 199.34, 200.95, 208.27, 210.57, 209.77, 212.79, 213.77, 221.25, 233.65, 238.38, 239.89, 249.02, 248.5, 249.7, 250.56, 248.28, 249.91, 255.36, 255.08, 263.99, 261.12, 259.7, 263.04, 265.06, 268.26, 272.05, 273.55, 274.99, 271.17, 272.68, 268.99, 265.82, 270.13, 267.22, 264.14, 264.86, 259.34, 265.01, 268.46, 266.32, 265.29, 271.85, 274.0, 270.64, 261.26, 256.52, 250.02, 253.79, 246.03, 245.22, 244.19, 238.0, 241.51, 238.55, 246.02, 246.0, 237.5, 244.39, 232.79, 234.11, 234.27, 227.01, 232.69, 240.14, 238.34, 241.7, 242.67, 244.16, 245.98, 243.62, 247.04, 245.34, 247.31, 247.49, 254.96, 249.89, 247.23, 249.99, 247.55, 244.85, 233.66, 232.11, 231.39], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
     </row>
@@ -887,36 +887,36 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">UP  </t>
+          <t>DOWN</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.649</v>
+        <v>0.458</v>
       </c>
       <c r="E8" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F8" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="G8" t="n">
         <v>33.3</v>
       </c>
       <c r="H8" t="n">
-        <v>-733</v>
+        <v>178</v>
       </c>
       <c r="I8" t="n">
-        <v>-14.7</v>
+        <v>3.6</v>
       </c>
       <c r="J8" t="n">
         <v>-10.9</v>
       </c>
       <c r="K8" t="n">
-        <v>-3.8</v>
+        <v>14.5</v>
       </c>
       <c r="L8" t="n">
         <v>5000</v>
@@ -928,17 +928,17 @@
         <v>4</v>
       </c>
       <c r="O8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="P8" t="n">
         <v>4</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.2</v>
+        <v>3.5</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [666.54, 659.39, 643.71, 646.24, 652.91, 653.69, 637.04, 612.62, 626.87, 622.08, 615.11, 606.14, 593.11, 603.5, 592.37, 594.34, 547.03, 525.23, 535.88, 571.6, 578.69, 573.93, 572.49, 574.52, 611.85, 627.81, 629.28, 633.94, 661.88, 670.96, 676.24, 687.91, 670.29, 668.22, 674.1, 658.54, 674.4, 677.99, 670.72, 668.5, 611.34, 608.19, 609.84, 604.4, 612.31, 616.24, 609.07, 598.31, 602.44, 616.06, 617.86, 613.66, 610.64, 602.05, 604.5, 606.82, 609.69, 611.77, 634.67, 634.7, 631.92, 599.91, 597.08, 622.4, 626.99, 592.45, 584.85, 584.05, 570.45, 567.9, 566.45, 593.48, 600.21, 567.58, 577.22, 563.85, 562.2, 557.67, 542.87, 550.25, 562.6, 563.29, 612.91, 582.9, 600.29, 615.58, 603.12, 631.48, 669.21, 656.73, 661.04, 681.31, 664.54, 646.01, 645.85, 643.81, 627.17, 606.1, 595.19, 593.87], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [666.54, 659.39, 643.71, 646.24, 652.91, 653.69, 637.04, 612.62, 626.87, 622.08, 615.11, 606.14, 593.11, 603.5, 592.37, 594.34, 547.03, 525.23, 535.88, 571.6, 578.69, 573.93, 572.49, 574.52, 611.85, 627.81, 629.28, 633.94, 661.88, 670.96, 676.24, 687.91, 670.29, 668.22, 674.1, 658.54, 674.4, 677.99, 670.72, 668.5, 611.34, 608.19, 609.84, 604.4, 612.31, 616.24, 609.07, 598.31, 602.44, 616.06, 617.86, 613.66, 610.64, 602.05, 604.5, 606.82, 609.69, 611.77, 634.67, 634.7, 631.92, 599.91, 597.08, 622.4, 626.99, 592.45, 584.85, 584.05, 570.45, 567.9, 566.45, 593.48, 600.21, 567.58, 577.22, 563.85, 562.2, 557.67, 542.87, 550.25, 562.6, 563.29, 612.91, 582.9, 600.29, 615.58, 603.12, 631.48, 669.21, 656.73, 661.04, 681.31, 664.54, 646.01, 645.85, 643.81, 627.17, 606.1, 595.19, 593.87], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY']}</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.267</v>
+        <v>0.456</v>
       </c>
       <c r="E9" t="n">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="F9" t="n">
         <v>30</v>
@@ -969,16 +969,16 @@
         <v>65</v>
       </c>
       <c r="H9" t="n">
-        <v>792</v>
+        <v>545</v>
       </c>
       <c r="I9" t="n">
-        <v>15.8</v>
+        <v>10.9</v>
       </c>
       <c r="J9" t="n">
         <v>20.1</v>
       </c>
       <c r="K9" t="n">
-        <v>-4.3</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="L9" t="n">
         <v>5000</v>
@@ -990,17 +990,17 @@
         <v>2</v>
       </c>
       <c r="O9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P9" t="n">
         <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [296.53, 290.75, 286.71, 287.15, 285.97, 284.77, 280.19, 280.73, 283.43, 284.15, 284.99, 285.22, 283.82, 287.14, 289.61, 292.6, 288.87, 280.14, 281.06, 291.35, 292.56, 291.79, 294.12, 296.07, 306.59, 308.94, 308.48, 312.27, 309.72, 304.56, 308.56, 308.9, 315.57, 311.6, 311.62, 310.29, 306.9, 310.23, 310.05, 307.86, 311.83, 311.07, 306.27, 308.01, 313.49, 304.9, 300.75, 298.65, 303.51, 298.9, 298.57, 296.47, 299.38, 294.37, 300.63, 301.64, 305.01, 305.36, 297.94, 295.4, 297.97, 295.25, 299.61, 299.5, 309.5, 310.97, 309.71, 311.3, 307.75, 312.08, 319.28, 317.97, 329.65, 331.96, 323.76, 329.99, 332.64, 331.95, 333.62, 327.57, 327.91, 325.86, 332.57, 332.97, 337.72, 339.22, 330.62, 335.47, 336.47, 334.53, 342.89, 346.91, 343.15, 341.1, 338.87, 345.23, 348.21, 349.9, 353.21, 356.2], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [296.53, 290.75, 286.71, 287.15, 285.97, 284.77, 280.19, 280.73, 283.43, 284.15, 284.99, 285.22, 283.82, 287.14, 289.61, 292.6, 288.87, 280.14, 281.06, 291.35, 292.56, 291.79, 294.12, 296.07, 306.59, 308.94, 308.48, 312.27, 309.72, 304.56, 308.56, 308.9, 315.57, 311.6, 311.62, 310.29, 306.9, 310.23, 310.05, 307.86, 311.83, 311.07, 306.27, 308.01, 313.49, 304.9, 300.75, 298.65, 303.51, 298.9, 298.57, 296.47, 299.38, 294.37, 300.63, 301.64, 305.01, 305.36, 297.94, 295.4, 297.97, 295.25, 299.61, 299.5, 309.5, 310.97, 309.71, 311.3, 307.75, 312.08, 319.28, 317.97, 329.65, 331.96, 323.76, 329.99, 332.64, 331.95, 333.62, 327.57, 327.91, 325.86, 332.57, 332.97, 337.72, 339.22, 330.62, 335.47, 336.47, 334.53, 342.89, 346.91, 343.15, 341.1, 338.87, 345.23, 348.21, 349.9, 353.21, 356.2], 'signals': ['FLAT', 'BUY', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
     </row>

--- a/demo_results.xlsx
+++ b/demo_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R9"/>
+  <dimension ref="A1:R21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.617</v>
+        <v>0.706</v>
       </c>
       <c r="E2" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F2" t="n">
         <v>50</v>
@@ -566,7 +566,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [262.28, 260.05, 257.22, 259.64, 260.59, 260.57, 255.52, 249.89, 252.59, 254.0, 249.71, 248.73, 247.76, 251.26, 251.41, 252.39, 252.66, 248.57, 246.4, 253.56, 255.39, 255.68, 258.62, 253.27, 258.66, 260.25, 260.24, 258.96, 258.59, 266.18, 263.16, 269.98, 272.8, 265.93, 272.92, 273.18, 270.81, 267.36, 270.46, 269.92, 271.1, 279.88, 276.58, 283.92, 287.25, 287.18, 293.05, 292.68, 294.8, 298.87, 298.21, 300.23, 297.84, 298.97, 302.25, 304.99, 308.82, 308.33, 310.85, 312.51, 312.06, 306.31, 315.2, 310.26, 311.23, 307.34, 301.54, 290.55, 291.58, 295.63, 291.13, 296.42, 299.24, 295.95, 298.01, 297.01, 294.3, 293.08, 275.15, 283.78, 281.74, 289.36, 294.38, 308.63, 312.66, 310.66, 313.39, 316.22, 315.32, 317.31, 314.86, 327.5, 333.26, 333.74, 326.59, 327.74, 325.89, 321.66, 333.02, 336.91], 'signals': ['BUY', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [262.28, 260.05, 257.22, 259.64, 260.59, 260.57, 255.52, 249.89, 252.59, 254.0, 249.71, 248.73, 247.76, 251.26, 251.41, 252.39, 252.66, 248.57, 246.4, 253.56, 255.39, 255.68, 258.62, 253.27, 258.66, 260.25, 260.24, 258.96, 258.59, 266.18, 263.16, 269.98, 272.8, 265.93, 272.92, 273.18, 270.81, 267.36, 270.46, 269.92, 271.1, 279.88, 276.58, 283.92, 287.25, 287.18, 293.05, 292.68, 294.8, 298.87, 298.21, 300.23, 297.84, 298.97, 302.25, 304.99, 308.82, 308.33, 310.85, 312.51, 312.06, 306.31, 315.2, 310.26, 311.23, 307.34, 301.54, 290.55, 291.58, 295.63, 291.13, 296.42, 299.24, 295.95, 298.01, 297.01, 294.3, 293.08, 275.15, 283.78, 281.74, 289.36, 294.38, 308.63, 312.66, 310.66, 313.39, 316.22, 315.32, 317.31, 314.86, 327.5, 333.26, 333.74, 326.59, 327.74, 325.89, 321.66, 333.02, 336.91], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'SELL', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -585,28 +585,28 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.916</v>
+        <v>0.965</v>
       </c>
       <c r="E3" t="n">
         <v>56</v>
       </c>
       <c r="F3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="G3" t="n">
         <v>55.6</v>
       </c>
       <c r="H3" t="n">
-        <v>-136</v>
+        <v>782</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.7</v>
+        <v>15.6</v>
       </c>
       <c r="J3" t="n">
         <v>-3.8</v>
       </c>
       <c r="K3" t="n">
-        <v>1.1</v>
+        <v>19.4</v>
       </c>
       <c r="L3" t="n">
         <v>5000</v>
@@ -618,17 +618,17 @@
         <v>3</v>
       </c>
       <c r="O3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
       </c>
       <c r="Q3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [404.32, 409.79, 408.08, 408.53, 404.88, 404.0, 400.99, 394.7, 399.09, 398.55, 390.94, 388.18, 381.04, 382.17, 371.93, 370.24, 365.18, 356.0, 358.18, 369.37, 368.57, 372.65, 372.07, 371.49, 373.52, 372.26, 370.07, 383.54, 392.26, 410.33, 419.35, 421.88, 417.17, 423.24, 431.98, 414.85, 423.7, 423.9, 428.32, 423.54, 406.9, 413.54, 412.73, 410.49, 413.07, 419.86, 414.22, 411.77, 406.89, 404.33, 408.55, 421.01, 422.62, 416.52, 420.15, 419.09, 418.57, 416.03, 412.67, 426.99, 450.24, 460.52, 441.31, 427.34, 428.05, 416.67, 411.74, 403.41, 397.36, 390.34, 390.74, 399.76, 393.83, 378.91, 379.4, 367.34, 373.94, 365.46, 352.83, 372.97, 368.57, 373.02, 384.28, 390.49, 386.74, 388.84, 383.34, 384.36, 385.1, 390.99, 384.93, 395.63, 401.1, 393.82, 402.29, 397.75, 390.34, 381.58, 381.7, 389.1], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [404.32, 409.79, 408.08, 408.53, 404.88, 404.0, 400.99, 394.7, 399.09, 398.55, 390.94, 388.18, 381.04, 382.17, 371.93, 370.24, 365.18, 356.0, 358.18, 369.37, 368.57, 372.65, 372.07, 371.49, 373.52, 372.26, 370.07, 383.54, 392.26, 410.33, 419.35, 421.88, 417.17, 423.24, 431.98, 414.85, 423.7, 423.9, 428.32, 423.54, 406.9, 413.54, 412.73, 410.49, 413.07, 419.86, 414.22, 411.77, 406.89, 404.33, 408.55, 421.01, 422.62, 416.52, 420.15, 419.09, 418.57, 416.03, 412.67, 426.99, 450.24, 460.52, 441.31, 427.34, 428.05, 416.67, 411.74, 403.41, 397.36, 390.34, 390.74, 399.76, 393.83, 378.91, 379.4, 367.34, 373.94, 365.46, 352.83, 372.97, 368.57, 373.02, 384.28, 390.49, 386.74, 388.84, 383.34, 384.36, 385.1, 390.99, 384.93, 395.63, 401.1, 393.82, 402.29, 397.75, 390.34, 381.58, 381.7, 389.1], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
     </row>
@@ -639,18 +639,18 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>59</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UP  </t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.501</v>
+      </c>
+      <c r="E4" t="n">
         <v>53</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>DOWN</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E4" t="n">
-        <v>52</v>
       </c>
       <c r="F4" t="n">
         <v>70</v>
@@ -659,16 +659,16 @@
         <v>50</v>
       </c>
       <c r="H4" t="n">
-        <v>351</v>
+        <v>184</v>
       </c>
       <c r="I4" t="n">
-        <v>7</v>
+        <v>3.7</v>
       </c>
       <c r="J4" t="n">
         <v>7.9</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.9</v>
+        <v>-4.2</v>
       </c>
       <c r="L4" t="n">
         <v>5000</v>
@@ -677,93 +677,93 @@
         <v>15</v>
       </c>
       <c r="N4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O4" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.3</v>
+        <v>1</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [302.74, 300.49, 298.13, 306.18, 306.86, 308.52, 303.37, 302.1, 305.38, 310.73, 307.51, 306.95, 300.82, 301.88, 290.27, 290.76, 280.75, 274.18, 273.34, 287.39, 297.21, 295.59, 299.81, 305.28, 317.13, 318.3, 317.05, 321.12, 332.71, 336.92, 335.82, 341.48, 337.22, 332.09, 339.12, 338.69, 344.19, 350.13, 349.57, 349.73, 384.57, 385.46, 383.02, 388.2, 397.8, 397.75, 400.56, 388.41, 387.12, 402.38, 400.83, 396.54, 396.7, 387.43, 388.68, 387.43, 382.74, 388.65, 388.6, 389.9, 380.11, 376.15, 361.63, 358.78, 371.97, 368.31, 363.31, 364.26, 356.38, 357.77, 359.68, 369.35, 373.25, 363.79, 368.03, 349.68, 346.13, 345.29, 343.71, 337.39, 353.65, 357.37, 361.21, 359.91, 366.46, 367.03, 361.92, 358.89, 357.18, 352.51, 359.51, 370.92, 354.46, 346.77, 351.99, 347.15, 342.09, 317.69, 319.74, 326.56], 'signals': ['FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [302.74, 300.49, 298.13, 306.18, 306.86, 308.52, 303.37, 302.1, 305.38, 310.73, 307.51, 306.95, 300.82, 301.88, 290.27, 290.76, 280.75, 274.18, 273.34, 287.39, 297.21, 295.59, 299.81, 305.28, 317.13, 318.3, 317.05, 321.12, 332.71, 336.92, 335.82, 341.48, 337.22, 332.09, 339.12, 338.69, 344.19, 350.13, 349.57, 349.73, 384.57, 385.46, 383.02, 388.2, 397.8, 397.75, 400.56, 388.41, 387.12, 402.38, 400.83, 396.54, 396.7, 387.43, 388.68, 387.43, 382.74, 388.65, 388.6, 389.9, 380.11, 376.15, 361.63, 358.78, 371.97, 368.31, 363.31, 364.26, 356.38, 357.77, 359.68, 369.35, 373.25, 363.79, 368.03, 349.68, 346.13, 345.29, 343.71, 337.39, 353.65, 357.37, 361.21, 359.91, 366.46, 367.03, 361.92, 358.89, 357.18, 352.51, 359.51, 370.92, 354.46, 346.77, 351.99, 347.15, 342.09, 317.69, 319.74, 326.56], 'signals': ['BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DOWN</t>
+          <t xml:space="preserve">UP  </t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.416</v>
+        <v>0.652</v>
       </c>
       <c r="E5" t="n">
         <v>59</v>
       </c>
       <c r="F5" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="G5" t="n">
-        <v>40</v>
+        <v>83.3</v>
       </c>
       <c r="H5" t="n">
-        <v>314</v>
+        <v>788</v>
       </c>
       <c r="I5" t="n">
-        <v>6.3</v>
+        <v>15.8</v>
       </c>
       <c r="J5" t="n">
-        <v>-23.8</v>
+        <v>6.7</v>
       </c>
       <c r="K5" t="n">
-        <v>30.1</v>
+        <v>9.1</v>
       </c>
       <c r="L5" t="n">
         <v>5000</v>
       </c>
       <c r="M5" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="N5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.7</v>
+        <v>4</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [405.94, 405.55, 396.73, 398.68, 399.24, 407.82, 395.01, 391.2, 395.56, 399.27, 392.78, 380.3, 367.96, 380.85, 383.03, 385.95, 372.11, 361.83, 355.28, 371.75, 381.26, 360.59, 352.82, 346.65, 343.25, 345.62, 348.95, 352.42, 364.2, 391.95, 388.9, 400.62, 392.5, 386.42, 387.51, 373.72, 376.3, 378.67, 376.02, 372.8, 381.63, 390.82, 392.51, 389.37, 398.73, 411.79, 428.35, 445.0, 433.45, 445.27, 443.3, 422.24, 409.99, 404.11, 417.26, 417.85, 426.01, 433.59, 440.36, 442.1, 435.79, 415.88, 423.74, 423.7, 418.45, 391.0, 408.95, 396.68, 381.59, 399.15, 406.43, 411.15, 404.66, 396.38, 400.49, 405.05, 381.61, 375.53, 375.12, 379.71, 411.84, 420.6, 425.3, 393.45, 419.77, 402.9, 394.06, 406.55, 407.76, 394.76, 396.18, 394.46, 391.06, 380.84, 369.57, 378.93, 374.01, 319.69, 313.03, 309.22], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [216.82, 218.94, 213.21, 213.49, 214.33, 212.65, 209.53, 207.67, 211.74, 215.2, 209.87, 208.76, 205.37, 210.14, 207.24, 211.71, 207.54, 199.34, 200.95, 208.27, 210.57, 209.77, 212.79, 213.77, 221.25, 233.65, 238.38, 239.89, 249.02, 248.5, 249.7, 250.56, 248.28, 249.91, 255.36, 255.08, 263.99, 261.12, 259.7, 263.04, 265.06, 268.26, 272.05, 273.55, 274.99, 271.17, 272.68, 268.99, 265.82, 270.13, 267.22, 264.14, 264.86, 259.34, 265.01, 268.46, 266.32, 265.29, 271.85, 274.0, 270.64, 261.26, 256.52, 250.02, 253.79, 246.03, 245.22, 244.19, 238.0, 241.51, 238.55, 246.02, 246.0, 237.5, 244.39, 232.79, 234.11, 234.27, 227.01, 232.69, 240.14, 238.34, 241.7, 242.67, 244.16, 245.98, 243.62, 247.04, 245.34, 247.31, 247.49, 254.96, 249.89, 247.23, 249.99, 247.55, 244.85, 233.66, 232.11, 231.39], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -771,123 +771,123 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.436</v>
+        <v>0.399</v>
       </c>
       <c r="E6" t="n">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F6" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G6" t="n">
-        <v>50</v>
+        <v>35.3</v>
       </c>
       <c r="H6" t="n">
-        <v>570</v>
+        <v>-221</v>
       </c>
       <c r="I6" t="n">
-        <v>11.4</v>
+        <v>-4.4</v>
       </c>
       <c r="J6" t="n">
-        <v>7.5</v>
+        <v>-10.9</v>
       </c>
       <c r="K6" t="n">
-        <v>3.9</v>
+        <v>6.5</v>
       </c>
       <c r="L6" t="n">
         <v>5000</v>
       </c>
       <c r="M6" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="N6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O6" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="P6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [182.82, 183.12, 177.6, 182.43, 184.54, 185.81, 182.93, 180.04, 183.01, 181.72, 180.19, 178.35, 172.5, 175.44, 175.0, 178.47, 171.04, 167.32, 164.98, 174.2, 175.55, 177.18, 177.43, 177.89, 181.87, 183.7, 188.41, 189.09, 196.28, 198.64, 198.12, 201.45, 201.82, 199.65, 202.26, 199.41, 208.03, 216.36, 212.92, 209.01, 199.34, 198.22, 198.25, 196.27, 207.59, 211.25, 214.95, 219.18, 220.52, 225.57, 235.47, 225.06, 222.06, 220.35, 223.21, 219.25, 215.08, 214.61, 212.35, 214.0, 210.89, 224.1, 222.56, 214.5, 218.66, 205.1, 208.64, 208.19, 200.42, 204.87, 205.19, 212.45, 207.41, 204.65, 210.69, 208.65, 200.04, 199.0, 195.74, 192.53, 194.97, 200.09, 197.58, 194.83, 195.55, 196.93, 204.12, 202.78, 210.96, 203.53, 211.8, 212.5, 207.4, 202.81, 203.28, 207.29, 212.06, 208.76, 206.84, 196.51], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY']}</t>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [666.54, 659.39, 643.71, 646.24, 652.91, 653.69, 637.04, 612.62, 626.87, 622.08, 615.11, 606.14, 593.11, 603.5, 592.37, 594.34, 547.03, 525.23, 535.88, 571.6, 578.69, 573.93, 572.49, 574.52, 611.85, 627.81, 629.28, 633.94, 661.88, 670.96, 676.24, 687.91, 670.29, 668.22, 674.1, 658.54, 674.4, 677.99, 670.72, 668.5, 611.34, 608.19, 609.84, 604.4, 612.31, 616.24, 609.07, 598.31, 602.44, 616.06, 617.86, 613.66, 610.64, 602.05, 604.5, 606.82, 609.69, 611.77, 634.67, 634.7, 631.92, 599.91, 597.08, 622.4, 626.99, 592.45, 584.85, 584.05, 570.45, 567.9, 566.45, 593.48, 600.21, 567.58, 577.22, 563.85, 562.2, 557.67, 542.87, 550.25, 562.6, 563.29, 612.91, 582.9, 600.29, 615.58, 603.12, 631.48, 669.21, 656.73, 661.04, 681.31, 664.54, 646.01, 645.85, 643.81, 627.17, 606.1, 595.19, 593.87], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B7" t="n">
+        <v>59</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.436</v>
+      </c>
+      <c r="E7" t="n">
+        <v>59</v>
+      </c>
+      <c r="F7" t="n">
+        <v>80</v>
+      </c>
+      <c r="G7" t="n">
         <v>50</v>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>DOWN</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>0.373</v>
-      </c>
-      <c r="E7" t="n">
-        <v>52</v>
-      </c>
-      <c r="F7" t="n">
-        <v>40</v>
-      </c>
-      <c r="G7" t="n">
-        <v>83.3</v>
-      </c>
       <c r="H7" t="n">
-        <v>828</v>
+        <v>570</v>
       </c>
       <c r="I7" t="n">
-        <v>16.6</v>
+        <v>11.4</v>
       </c>
       <c r="J7" t="n">
-        <v>6.7</v>
+        <v>7.5</v>
       </c>
       <c r="K7" t="n">
-        <v>9.9</v>
+        <v>3.9</v>
       </c>
       <c r="L7" t="n">
         <v>5000</v>
       </c>
       <c r="M7" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="N7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O7" t="n">
         <v>4</v>
       </c>
       <c r="P7" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q7" t="n">
         <v>2</v>
       </c>
-      <c r="Q7" t="n">
-        <v>3</v>
-      </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [216.82, 218.94, 213.21, 213.49, 214.33, 212.65, 209.53, 207.67, 211.74, 215.2, 209.87, 208.76, 205.37, 210.14, 207.24, 211.71, 207.54, 199.34, 200.95, 208.27, 210.57, 209.77, 212.79, 213.77, 221.25, 233.65, 238.38, 239.89, 249.02, 248.5, 249.7, 250.56, 248.28, 249.91, 255.36, 255.08, 263.99, 261.12, 259.7, 263.04, 265.06, 268.26, 272.05, 273.55, 274.99, 271.17, 272.68, 268.99, 265.82, 270.13, 267.22, 264.14, 264.86, 259.34, 265.01, 268.46, 266.32, 265.29, 271.85, 274.0, 270.64, 261.26, 256.52, 250.02, 253.79, 246.03, 245.22, 244.19, 238.0, 241.51, 238.55, 246.02, 246.0, 237.5, 244.39, 232.79, 234.11, 234.27, 227.01, 232.69, 240.14, 238.34, 241.7, 242.67, 244.16, 245.98, 243.62, 247.04, 245.34, 247.31, 247.49, 254.96, 249.89, 247.23, 249.99, 247.55, 244.85, 233.66, 232.11, 231.39], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [182.82, 183.12, 177.6, 182.43, 184.54, 185.81, 182.93, 180.04, 183.01, 181.72, 180.19, 178.35, 172.5, 175.44, 175.0, 178.47, 171.04, 167.32, 164.98, 174.2, 175.55, 177.18, 177.43, 177.89, 181.87, 183.7, 188.41, 189.09, 196.28, 198.64, 198.12, 201.45, 201.82, 199.65, 202.26, 199.41, 208.03, 216.36, 212.92, 209.01, 199.34, 198.22, 198.25, 196.27, 207.59, 211.25, 214.95, 219.18, 220.52, 225.57, 235.47, 225.06, 222.06, 220.35, 223.21, 219.25, 215.08, 214.61, 212.35, 214.0, 210.89, 224.1, 222.56, 214.5, 218.66, 205.1, 208.64, 208.19, 200.42, 204.87, 205.19, 212.45, 207.41, 204.65, 210.69, 208.65, 200.04, 199.0, 195.74, 192.53, 194.97, 200.09, 197.58, 194.83, 195.55, 196.93, 204.12, 202.78, 210.96, 203.53, 211.8, 212.5, 207.4, 202.81, 203.28, 207.29, 212.06, 208.76, 206.84, 196.51], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY']}</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -895,112 +895,856 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.458</v>
+        <v>0.432</v>
       </c>
       <c r="E8" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F8" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="G8" t="n">
-        <v>33.3</v>
+        <v>66.7</v>
       </c>
       <c r="H8" t="n">
-        <v>178</v>
+        <v>1316</v>
       </c>
       <c r="I8" t="n">
-        <v>3.6</v>
+        <v>26.3</v>
       </c>
       <c r="J8" t="n">
-        <v>-10.9</v>
+        <v>144.9</v>
       </c>
       <c r="K8" t="n">
-        <v>14.5</v>
+        <v>-118.6</v>
       </c>
       <c r="L8" t="n">
         <v>5000</v>
       </c>
       <c r="M8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="P8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q8" t="n">
         <v>3.5</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [666.54, 659.39, 643.71, 646.24, 652.91, 653.69, 637.04, 612.62, 626.87, 622.08, 615.11, 606.14, 593.11, 603.5, 592.37, 594.34, 547.03, 525.23, 535.88, 571.6, 578.69, 573.93, 572.49, 574.52, 611.85, 627.81, 629.28, 633.94, 661.88, 670.96, 676.24, 687.91, 670.29, 668.22, 674.1, 658.54, 674.4, 677.99, 670.72, 668.5, 611.34, 608.19, 609.84, 604.4, 612.31, 616.24, 609.07, 598.31, 602.44, 616.06, 617.86, 613.66, 610.64, 602.05, 604.5, 606.82, 609.69, 611.77, 634.67, 634.7, 631.92, 599.91, 597.08, 622.4, 626.99, 592.45, 584.85, 584.05, 570.45, 567.9, 566.45, 593.48, 600.21, 567.58, 577.22, 563.85, 562.2, 557.67, 542.87, 550.25, 562.6, 563.29, 612.91, 582.9, 600.29, 615.58, 603.12, 631.48, 669.21, 656.73, 661.04, 681.31, 664.54, 646.01, 645.85, 643.81, 627.17, 606.1, 595.19, 593.87], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY']}</t>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [202.07, 199.45, 192.43, 202.68, 203.23, 204.83, 197.74, 193.39, 196.58, 196.31, 199.46, 205.27, 201.33, 202.68, 205.37, 220.27, 203.77, 201.99, 196.04, 203.43, 210.21, 217.5, 220.18, 221.53, 231.82, 236.64, 245.04, 246.83, 255.07, 258.12, 278.26, 278.39, 274.95, 284.49, 303.46, 305.33, 347.81, 334.63, 323.21, 337.11, 354.49, 360.54, 341.54, 355.26, 421.39, 408.46, 455.19, 458.79, 448.29, 445.5, 449.7, 424.1, 420.99, 414.05, 447.58, 449.59, 467.51, 503.89, 495.54, 518.09, 516.1, 510.13, 521.54, 542.52, 523.2, 466.38, 490.33, 475.51, 452.4, 488.45, 511.57, 547.26, 507.29, 512.48, 537.37, 551.63, 519.85, 519.74, 532.57, 521.58, 539.49, 580.91, 540.88, 517.82, 552.05, 516.11, 517.41, 546.72, 557.89, 534.39, 548.13, 529.14, 500.94, 495.76, 503.57, 544.43, 552.33, 539.69, 521.95, 494.95], 'signals': ['BUY', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'BUY', 'SELL', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>52</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UP  </t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="E9" t="n">
+        <v>51</v>
+      </c>
+      <c r="F9" t="n">
+        <v>40</v>
+      </c>
+      <c r="G9" t="n">
+        <v>45</v>
+      </c>
+      <c r="H9" t="n">
+        <v>289</v>
+      </c>
+      <c r="I9" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="J9" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-15.3</v>
+      </c>
+      <c r="L9" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M9" t="n">
+        <v>13</v>
+      </c>
+      <c r="N9" t="n">
+        <v>4</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2</v>
+      </c>
+      <c r="P9" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [316.36, 331.55, 329.27, 344.48, 341.32, 340.32, 334.74, 320.98, 323.73, 320.13, 314.77, 318.67, 309.37, 322.0, 317.79, 318.31, 308.93, 300.2, 292.95, 309.02, 312.99, 314.05, 313.93, 333.44, 350.08, 354.35, 370.96, 379.15, 380.18, 396.09, 397.84, 405.9, 399.0, 401.53, 421.98, 419.28, 422.09, 417.54, 399.2, 404.81, 416.77, 420.61, 415.84, 426.68, 424.77, 411.91, 429.32, 427.75, 418.64, 416.13, 439.1, 424.52, 420.05, 410.42, 417.1, 413.91, 413.49, 421.34, 421.19, 425.91, 446.06, 459.24, 480.81, 478.47, 418.25, 385.12, 395.97, 391.54, 371.51, 384.96, 381.47, 393.32, 376.11, 392.28, 410.7, 392.13, 380.15, 382.07, 378.91, 365.02, 372.45, 377.75, 369.34, 360.45, 373.9, 370.78, 388.69, 401.11, 399.97, 384.05, 389.11, 394.28, 374.45, 370.83, 378.16, 386.5, 396.81, 392.47, 381.92, 383.22], 'signals': ['BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>MU</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>64</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.489</v>
+      </c>
+      <c r="E10" t="n">
+        <v>63</v>
+      </c>
+      <c r="F10" t="n">
+        <v>40</v>
+      </c>
+      <c r="G10" t="n">
+        <v>60</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2829</v>
+      </c>
+      <c r="I10" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="J10" t="n">
+        <v>124.7</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-68.09999999999999</v>
+      </c>
+      <c r="L10" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M10" t="n">
+        <v>5</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2</v>
+      </c>
+      <c r="O10" t="n">
+        <v>17</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>9</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [400.54, 396.82, 370.09, 389.1, 402.88, 418.45, 405.12, 425.89, 441.55, 461.43, 461.47, 444.02, 422.66, 404.12, 395.3, 381.87, 355.26, 357.02, 321.75, 337.79, 367.79, 366.18, 377.7, 377.52, 406.67, 421.45, 420.53, 426.49, 465.59, 456.16, 457.16, 455.0, 448.35, 449.31, 487.41, 481.65, 496.64, 524.48, 504.21, 518.38, 517.08, 542.13, 576.36, 640.1, 666.49, 646.53, 746.7, 795.21, 766.46, 803.51, 775.89, 724.55, 681.44, 698.63, 731.88, 761.98, 750.88, 895.74, 928.27, 923.38, 970.85, 1035.34, 1063.94, 1079.4, 995.85, 863.88, 949.13, 935.75, 891.74, 995.72, 981.46, 1087.82, 1020.6, 1043.03, 1133.82, 1211.19, 1051.61, 1048.35, 1213.37, 1132.16, 1145.1, 1154.11, 1032.12, 975.41, 984.75, 938.38, 948.8, 991.64, 979.3, 937.0, 983.12, 904.28, 853.2, 848.95, 865.46, 970.82, 959.48, 990.21, 920.95, 900.2], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>62</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.404</v>
+      </c>
+      <c r="E11" t="n">
+        <v>54</v>
+      </c>
+      <c r="F11" t="n">
+        <v>10</v>
+      </c>
+      <c r="G11" t="n">
+        <v>40</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-243</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-4.9</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-23.8</v>
+      </c>
+      <c r="K11" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="L11" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M11" t="n">
+        <v>16</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [405.94, 405.55, 396.73, 398.68, 399.24, 407.82, 395.01, 391.2, 395.56, 399.27, 392.78, 380.3, 367.96, 380.85, 383.03, 385.95, 372.11, 361.83, 355.28, 371.75, 381.26, 360.59, 352.82, 346.65, 343.25, 345.62, 348.95, 352.42, 364.2, 391.95, 388.9, 400.62, 392.5, 386.42, 387.51, 373.72, 376.3, 378.67, 376.02, 372.8, 381.63, 390.82, 392.51, 389.37, 398.73, 411.79, 428.35, 445.0, 433.45, 445.27, 443.3, 422.24, 409.99, 404.11, 417.26, 417.85, 426.01, 433.59, 440.36, 442.1, 435.79, 415.88, 423.74, 423.7, 418.45, 391.0, 408.95, 396.68, 381.59, 399.15, 406.43, 411.15, 404.66, 396.38, 400.49, 405.05, 381.61, 375.53, 375.12, 379.71, 411.84, 420.6, 425.3, 393.45, 419.77, 402.9, 394.06, 406.55, 407.76, 394.76, 396.18, 394.46, 391.06, 380.84, 369.57, 378.93, 374.01, 319.69, 313.03, 309.22], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>65</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="E12" t="n">
+        <v>60</v>
+      </c>
+      <c r="F12" t="n">
+        <v>80</v>
+      </c>
+      <c r="G12" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-478</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-9.6</v>
+      </c>
+      <c r="J12" t="n">
+        <v>-28.6</v>
+      </c>
+      <c r="K12" t="n">
+        <v>19</v>
+      </c>
+      <c r="L12" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M12" t="n">
+        <v>71</v>
+      </c>
+      <c r="N12" t="n">
+        <v>4</v>
+      </c>
+      <c r="O12" t="n">
+        <v>6</v>
+      </c>
+      <c r="P12" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [98.66, 99.17, 99.02, 98.32, 96.94, 94.89, 94.31, 95.31, 95.2, 94.36, 94.7, 91.74, 91.82, 93.38, 90.92, 92.28, 93.32, 93.43, 92.97, 96.15, 95.55, 98.66, 98.93, 98.82, 99.39, 102.05, 103.01, 103.16, 106.28, 107.71, 107.79, 97.31, 94.83, 92.58, 93.24, 92.82, 92.44, 91.37, 92.27, 92.12, 93.61, 92.06, 91.02, 87.89, 88.27, 88.25, 87.49, 85.45, 87.66, 87.56, 86.94, 87.02, 89.65, 89.33, 88.09, 89.3, 88.6, 87.68, 87.35, 86.36, 86.02, 85.85, 83.33, 81.52, 81.56, 82.18, 82.64, 81.41, 82.0, 81.27, 80.34, 81.67, 78.72, 76.96, 77.38, 72.88, 72.82, 71.84, 70.9, 73.81, 73.78, 71.4, 74.19, 77.65, 76.02, 76.18, 75.59, 75.47, 73.37, 73.83, 73.53, 73.68, 74.35, 68.95, 67.6, 68.67, 68.53, 68.89, 70.09, 70.4], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>52</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UP  </t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0.508</v>
+      </c>
+      <c r="E13" t="n">
+        <v>52</v>
+      </c>
+      <c r="F13" t="n">
+        <v>30</v>
+      </c>
+      <c r="G13" t="n">
+        <v>30</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-1260</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-25.2</v>
+      </c>
+      <c r="J13" t="n">
+        <v>-14.1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-11.1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M13" t="n">
+        <v>38</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3</v>
+      </c>
+      <c r="O13" t="n">
+        <v>5</v>
+      </c>
+      <c r="P13" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [153.19, 152.67, 157.16, 156.43, 151.14, 151.6, 153.5, 150.95, 152.72, 155.08, 152.77, 155.68, 150.68, 160.84, 154.78, 154.96, 147.56, 143.06, 137.55, 146.28, 146.49, 148.46, 147.93, 150.07, 140.76, 130.49, 128.06, 132.37, 135.7, 142.15, 142.76, 146.39, 145.89, 145.97, 152.62, 141.57, 143.09, 143.1, 141.18, 137.97, 139.11, 144.07, 146.03, 135.91, 133.79, 137.05, 137.8, 136.89, 136.0, 130.05, 133.73, 133.99, 135.14, 135.26, 137.15, 137.41, 136.88, 136.6, 132.51, 143.34, 156.54, 160.65, 152.17, 142.2, 141.7, 135.53, 136.47, 132.07, 130.21, 131.08, 127.99, 134.71, 133.25, 130.63, 128.47, 119.5, 116.7, 113.5, 107.27, 112.93, 115.7, 116.67, 125.73, 129.3, 132.54, 134.37, 132.22, 129.04, 126.79, 130.04, 133.72, 133.76, 134.44, 132.38, 134.85, 132.66, 124.57, 123.37, 122.92, 131.53], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD']}</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>52</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="E14" t="n">
+        <v>52</v>
+      </c>
+      <c r="F14" t="n">
+        <v>60</v>
+      </c>
+      <c r="G14" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>-9.6</v>
+      </c>
+      <c r="K14" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="L14" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M14" t="n">
+        <v>28</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [192.1, 200.37, 201.09, 197.78, 193.92, 193.15, 198.27, 191.85, 197.34, 194.32, 193.36, 194.0, 194.39, 194.19, 182.09, 181.04, 184.7, 178.4, 184.09, 185.72, 185.3, 186.23, 184.09, 182.03, 175.48, 170.41, 164.54, 172.38, 170.87, 177.14, 180.75, 181.67, 185.79, 186.63, 189.31, 172.85, 177.7, 179.72, 180.85, 180.75, 176.08, 183.35, 185.0, 186.51, 180.72, 185.86, 181.35, 177.03, 170.87, 165.41, 167.15, 173.06, 179.02, 178.96, 179.64, 175.86, 179.61, 178.62, 177.05, 175.72, 190.61, 209.06, 200.32, 190.12, 188.26, 185.18, 182.08, 174.9, 170.48, 166.45, 165.89, 164.55, 161.71, 155.02, 151.78, 150.12, 153.42, 152.76, 150.19, 158.37, 157.93, 156.66, 163.23, 166.11, 165.65, 169.52, 166.58, 162.5, 163.32, 171.22, 167.56, 167.0, 172.68, 170.77, 173.79, 170.06, 163.0, 156.93, 163.66, 173.6], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CRWD</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>59</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UP  </t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0.726</v>
+      </c>
+      <c r="E15" t="n">
+        <v>54</v>
+      </c>
+      <c r="F15" t="n">
+        <v>100</v>
+      </c>
+      <c r="G15" t="n">
+        <v>70</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2102</v>
+      </c>
+      <c r="I15" t="n">
+        <v>42</v>
+      </c>
+      <c r="J15" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-34.7</v>
+      </c>
+      <c r="L15" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M15" t="n">
+        <v>27</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2</v>
+      </c>
+      <c r="O15" t="n">
+        <v>17</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>9</v>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [101.92, 106.54, 107.25, 108.53, 109.08, 110.51, 110.39, 110.44, 105.96, 108.3, 108.95, 107.04, 102.25, 103.33, 98.25, 96.46, 98.15, 92.39, 95.01, 97.6, 98.33, 99.78, 99.65, 105.81, 106.63, 98.67, 94.75, 100.56, 99.62, 102.79, 104.55, 105.99, 108.29, 112.4, 116.67, 111.35, 112.03, 113.65, 113.75, 113.1, 111.44, 113.91, 117.31, 119.13, 117.02, 126.43, 131.94, 135.57, 136.54, 140.64, 144.99, 148.52, 154.71, 154.22, 162.53, 162.06, 165.87, 167.89, 161.34, 167.75, 182.75, 195.54, 192.24, 186.9, 179.77, 167.76, 164.7, 161.23, 161.93, 172.88, 170.7, 173.23, 169.87, 170.74, 171.21, 168.86, 170.23, 168.26, 169.66, 175.27, 185.73, 190.79, 193.18, 193.98, 199.38, 194.62, 191.12, 198.4, 187.18, 187.91, 210.73, 206.77, 203.76, 203.08, 198.49, 191.15, 188.42, 183.42, 183.28, 180.11], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT']}</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>JPM</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B16" t="n">
+        <v>59</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0.461</v>
+      </c>
+      <c r="E16" t="n">
+        <v>51</v>
+      </c>
+      <c r="F16" t="n">
+        <v>30</v>
+      </c>
+      <c r="G16" t="n">
+        <v>65</v>
+      </c>
+      <c r="H16" t="n">
+        <v>435</v>
+      </c>
+      <c r="I16" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="J16" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-11.4</v>
+      </c>
+      <c r="L16" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M16" t="n">
+        <v>14</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2</v>
+      </c>
+      <c r="O16" t="n">
+        <v>6</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>4</v>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [296.53, 290.75, 286.71, 287.15, 285.97, 284.77, 280.19, 280.73, 283.43, 284.15, 284.99, 285.22, 283.82, 287.14, 289.61, 292.6, 288.87, 280.14, 281.06, 291.35, 292.56, 291.79, 294.12, 296.07, 306.59, 308.94, 308.48, 312.27, 309.72, 304.56, 308.56, 308.9, 315.57, 311.6, 311.62, 310.29, 306.9, 310.23, 310.05, 307.86, 311.83, 311.07, 306.27, 308.01, 313.49, 304.9, 300.75, 298.65, 303.51, 298.9, 298.57, 296.47, 299.38, 294.37, 300.63, 301.64, 305.01, 305.36, 297.94, 295.4, 297.97, 295.25, 299.61, 299.5, 309.5, 310.97, 309.71, 311.3, 307.75, 312.08, 319.28, 317.97, 329.65, 331.96, 323.76, 329.99, 332.64, 331.95, 333.62, 327.57, 327.91, 325.86, 332.57, 332.97, 337.72, 339.22, 330.62, 335.47, 336.47, 334.53, 342.89, 346.91, 343.15, 341.1, 338.87, 345.23, 348.21, 349.9, 353.21, 356.2], 'signals': ['BUY', 'SELL', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>GS</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
         <v>57</v>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UP  </t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0.5659999999999999</v>
+      </c>
+      <c r="E17" t="n">
+        <v>59</v>
+      </c>
+      <c r="F17" t="n">
+        <v>100</v>
+      </c>
+      <c r="G17" t="n">
+        <v>65</v>
+      </c>
+      <c r="H17" t="n">
+        <v>739</v>
+      </c>
+      <c r="I17" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="J17" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="K17" t="n">
+        <v>-6.6</v>
+      </c>
+      <c r="L17" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M17" t="n">
+        <v>4</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>19</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>19</v>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [863.44, 831.79, 817.82, 828.38, 830.15, 820.15, 784.06, 778.78, 791.28, 803.5, 801.95, 805.95, 809.96, 827.62, 832.05, 838.15, 819.03, 799.37, 804.06, 842.28, 856.44, 859.25, 862.25, 860.36, 901.78, 899.75, 903.82, 886.88, 905.64, 895.54, 896.05, 921.89, 937.61, 922.48, 930.74, 927.21, 922.84, 933.7, 922.48, 901.63, 919.72, 919.66, 899.31, 914.86, 933.24, 921.81, 932.37, 940.71, 941.75, 951.23, 964.71, 944.31, 942.21, 924.66, 977.81, 983.83, 992.36, 990.16, 992.1, 1003.95, 1021.06, 1048.58, 1064.58, 1041.02, 1092.61, 1038.68, 1045.0, 1032.01, 1001.29, 1035.64, 1062.75, 1076.17, 1090.67, 1099.14, 1096.56, 1106.37, 1094.44, 1076.91, 1065.09, 1019.61, 1020.21, 1011.37, 1019.61, 1021.0, 1055.29, 1042.98, 1029.64, 1055.97, 1055.18, 1045.91, 1140.0, 1152.07, 1095.46, 1065.22, 1055.03, 1085.56, 1098.2, 1074.72, 1061.23, 1048.23], 'signals': ['BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>COIN</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>57</v>
+      </c>
+      <c r="C18" t="inlineStr">
         <is>
           <t>DOWN</t>
         </is>
       </c>
-      <c r="D9" t="n">
-        <v>0.456</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="D18" t="n">
+        <v>0.353</v>
+      </c>
+      <c r="E18" t="n">
+        <v>57</v>
+      </c>
+      <c r="F18" t="n">
+        <v>50</v>
+      </c>
+      <c r="G18" t="n">
+        <v>40</v>
+      </c>
+      <c r="H18" t="n">
+        <v>173</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-19.8</v>
+      </c>
+      <c r="K18" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="L18" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M18" t="n">
+        <v>29</v>
+      </c>
+      <c r="N18" t="n">
+        <v>5</v>
+      </c>
+      <c r="O18" t="n">
+        <v>2</v>
+      </c>
+      <c r="P18" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [208.93, 205.71, 197.22, 199.79, 196.52, 198.63, 193.23, 195.53, 203.32, 210.23, 202.29, 202.91, 197.5, 200.62, 181.04, 181.1, 173.38, 161.14, 160.79, 174.61, 172.99, 171.46, 174.79, 175.18, 175.09, 169.02, 167.85, 174.53, 184.41, 195.9, 199.83, 206.33, 211.63, 195.95, 206.24, 197.93, 199.77, 196.68, 194.1, 181.73, 187.77, 191.25, 202.99, 197.75, 197.96, 192.96, 201.16, 216.6, 207.64, 201.8, 212.01, 195.43, 189.44, 193.45, 191.29, 193.56, 184.99, 180.01, 173.78, 182.25, 189.03, 182.61, 173.99, 163.22, 164.13, 152.4, 162.11, 155.5, 153.97, 160.43, 159.78, 169.62, 169.27, 164.92, 163.26, 164.84, 158.18, 150.11, 142.52, 149.06, 151.65, 146.19, 159.24, 165.48, 168.87, 163.51, 159.36, 158.44, 159.07, 157.37, 161.5, 167.21, 160.49, 157.12, 160.43, 175.85, 166.12, 161.16, 158.29, 167.49], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>LLY</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>51</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0.398</v>
+      </c>
+      <c r="E19" t="n">
         <v>55</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F19" t="n">
         <v>30</v>
       </c>
-      <c r="G9" t="n">
-        <v>65</v>
-      </c>
-      <c r="H9" t="n">
-        <v>545</v>
-      </c>
-      <c r="I9" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="J9" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>-9.199999999999999</v>
-      </c>
-      <c r="L9" t="n">
-        <v>5000</v>
-      </c>
-      <c r="M9" t="n">
+      <c r="G19" t="n">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="H19" t="n">
+        <v>976</v>
+      </c>
+      <c r="I19" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="J19" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M19" t="n">
+        <v>4</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" t="n">
         <v>14</v>
       </c>
-      <c r="N9" t="n">
-        <v>2</v>
-      </c>
-      <c r="O9" t="n">
-        <v>12</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q9" t="n">
+      <c r="P19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>14</v>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [1001.85, 981.57, 988.63, 1006.66, 999.63, 998.12, 975.57, 983.39, 987.42, 928.75, 916.47, 915.92, 905.14, 908.99, 901.47, 914.74, 895.46, 876.73, 885.11, 918.19, 952.88, 933.97, 925.47, 929.49, 951.66, 953.55, 937.86, 927.95, 920.91, 903.47, 902.44, 925.44, 918.32, 901.47, 919.9, 916.07, 882.44, 866.78, 872.5, 849.75, 932.99, 961.67, 966.27, 987.17, 985.35, 973.28, 946.82, 965.33, 988.17, 1014.0, 1004.97, 1004.92, 988.09, 1021.41, 1018.87, 1041.65, 1065.0, 1064.74, 1082.92, 1126.8, 1105.0, 1082.2, 1064.15, 1078.78, 1125.27, 1131.42, 1149.15, 1144.68, 1136.37, 1160.95, 1133.0, 1129.35, 1122.5, 1112.0, 1098.57, 1102.08, 1107.08, 1117.26, 1127.69, 1208.12, 1229.93, 1199.43, 1191.74, 1213.91, 1200.06, 1235.56, 1215.83, 1216.95, 1188.58, 1181.87, 1152.54, 1156.63, 1169.17, 1179.11, 1146.9, 1175.41, 1163.01, 1185.87, 1196.03, 1197.53], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>58</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UP  </t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0.555</v>
+      </c>
+      <c r="E20" t="n">
+        <v>56</v>
+      </c>
+      <c r="F20" t="n">
+        <v>40</v>
+      </c>
+      <c r="G20" t="n">
+        <v>45</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-27</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="J20" t="n">
+        <v>-7</v>
+      </c>
+      <c r="K20" t="n">
         <v>6.5</v>
       </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [296.53, 290.75, 286.71, 287.15, 285.97, 284.77, 280.19, 280.73, 283.43, 284.15, 284.99, 285.22, 283.82, 287.14, 289.61, 292.6, 288.87, 280.14, 281.06, 291.35, 292.56, 291.79, 294.12, 296.07, 306.59, 308.94, 308.48, 312.27, 309.72, 304.56, 308.56, 308.9, 315.57, 311.6, 311.62, 310.29, 306.9, 310.23, 310.05, 307.86, 311.83, 311.07, 306.27, 308.01, 313.49, 304.9, 300.75, 298.65, 303.51, 298.9, 298.57, 296.47, 299.38, 294.37, 300.63, 301.64, 305.01, 305.36, 297.94, 295.4, 297.97, 295.25, 299.61, 299.5, 309.5, 310.97, 309.71, 311.3, 307.75, 312.08, 319.28, 317.97, 329.65, 331.96, 323.76, 329.99, 332.64, 331.95, 333.62, 327.57, 327.91, 325.86, 332.57, 332.97, 337.72, 339.22, 330.62, 335.47, 336.47, 334.53, 342.89, 346.91, 343.15, 341.1, 338.87, 345.23, 348.21, 349.9, 353.21, 356.2], 'signals': ['FLAT', 'BUY', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+      <c r="L20" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M20" t="n">
+        <v>23</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [227.31, 222.06, 231.11, 225.0, 217.76, 214.1, 204.76, 209.89, 213.47, 210.82, 205.99, 201.18, 195.12, 198.41, 196.42, 199.61, 194.36, 190.52, 189.21, 199.03, 207.32, 208.22, 212.3, 210.0, 217.8, 220.06, 217.63, 222.14, 223.77, 223.93, 218.88, 223.38, 225.08, 219.16, 231.28, 234.15, 232.44, 231.33, 230.72, 224.11, 229.03, 227.38, 221.3, 224.38, 229.93, 231.03, 237.36, 238.21, 236.87, 240.6, 229.21, 220.49, 220.61, 215.01, 222.2, 219.61, 219.02, 218.9, 224.3, 228.78, 231.15, 224.3, 217.7, 210.58, 217.42, 215.45, 215.92, 214.51, 209.0, 221.63, 219.05, 228.95, 227.49, 225.63, 222.72, 220.83, 216.71, 220.25, 218.12, 217.25, 214.69, 216.47, 218.58, 226.49, 234.54, 231.68, 224.95, 223.11, 222.28, 215.51, 217.11, 218.12, 214.34, 214.03, 209.48, 204.8, 208.65, 209.23, 209.52, 211.5], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>UBER</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>67</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UP  </t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0.578</v>
+      </c>
+      <c r="E21" t="n">
+        <v>66</v>
+      </c>
+      <c r="F21" t="n">
+        <v>50</v>
+      </c>
+      <c r="G21" t="n">
+        <v>35</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-415</v>
+      </c>
+      <c r="I21" t="n">
+        <v>-8.300000000000001</v>
+      </c>
+      <c r="J21" t="n">
+        <v>-11.1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="L21" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M21" t="n">
+        <v>73</v>
+      </c>
+      <c r="N21" t="n">
+        <v>4</v>
+      </c>
+      <c r="O21" t="n">
+        <v>8</v>
+      </c>
+      <c r="P21" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3</v>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [76.65, 75.44, 75.13, 73.84, 72.36, 74.97, 72.97, 73.33, 74.66, 77.79, 76.66, 75.34, 73.89, 75.12, 72.34, 73.08, 70.55, 69.18, 69.91, 71.93, 71.71, 71.84, 72.17, 71.73, 72.38, 71.81, 70.48, 72.34, 72.91, 77.28, 76.48, 77.12, 77.49, 77.26, 75.58, 74.7, 74.64, 76.27, 74.11, 74.47, 74.61, 75.12, 73.93, 72.95, 79.17, 76.73, 75.45, 76.15, 76.36, 74.7, 74.69, 75.09, 75.08, 74.09, 74.6, 73.61, 71.82, 70.12, 70.73, 70.92, 70.4, 73.77, 71.62, 71.69, 72.21, 70.71, 70.06, 70.38, 68.61, 69.55, 68.85, 72.85, 73.25, 70.91, 71.64, 71.43, 69.67, 73.85, 72.25, 76.2, 75.5, 72.16, 72.66, 74.43, 72.42, 74.33, 73.6, 74.35, 74.54, 74.26, 72.08, 72.67, 74.04, 72.46, 72.17, 71.55, 70.33, 68.91, 65.94, 68.18], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'SELL', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
     </row>

--- a/demo_results.xlsx
+++ b/demo_results.xlsx
@@ -519,54 +519,54 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UP  </t>
+          <t>DOWN</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.706</v>
+        <v>0.236</v>
       </c>
       <c r="E2" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="F2" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="G2" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="H2" t="n">
-        <v>602</v>
+        <v>872</v>
       </c>
       <c r="I2" t="n">
-        <v>12</v>
+        <v>17.4</v>
       </c>
       <c r="J2" t="n">
-        <v>28.5</v>
+        <v>26.4</v>
       </c>
       <c r="K2" t="n">
-        <v>-16.5</v>
+        <v>-9</v>
       </c>
       <c r="L2" t="n">
         <v>5000</v>
       </c>
       <c r="M2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O2" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="P2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.7</v>
+        <v>2.2</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [262.28, 260.05, 257.22, 259.64, 260.59, 260.57, 255.52, 249.89, 252.59, 254.0, 249.71, 248.73, 247.76, 251.26, 251.41, 252.39, 252.66, 248.57, 246.4, 253.56, 255.39, 255.68, 258.62, 253.27, 258.66, 260.25, 260.24, 258.96, 258.59, 266.18, 263.16, 269.98, 272.8, 265.93, 272.92, 273.18, 270.81, 267.36, 270.46, 269.92, 271.1, 279.88, 276.58, 283.92, 287.25, 287.18, 293.05, 292.68, 294.8, 298.87, 298.21, 300.23, 297.84, 298.97, 302.25, 304.99, 308.82, 308.33, 310.85, 312.51, 312.06, 306.31, 315.2, 310.26, 311.23, 307.34, 301.54, 290.55, 291.58, 295.63, 291.13, 296.42, 299.24, 295.95, 298.01, 297.01, 294.3, 293.08, 275.15, 283.78, 281.74, 289.36, 294.38, 308.63, 312.66, 310.66, 313.39, 316.22, 315.32, 317.31, 314.86, 327.5, 333.26, 333.74, 326.59, 327.74, 325.89, 321.66, 333.02, 336.91], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'SELL', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [263.51, 262.28, 260.05, 257.22, 259.64, 260.59, 260.57, 255.52, 249.89, 252.59, 254.0, 249.71, 248.73, 247.76, 251.26, 251.41, 252.39, 252.66, 248.57, 246.4, 253.56, 255.39, 255.68, 258.62, 253.27, 258.66, 260.25, 260.24, 258.96, 258.59, 266.18, 263.16, 269.98, 272.8, 265.93, 272.92, 273.18, 270.81, 267.36, 270.46, 269.92, 271.1, 279.88, 276.58, 283.92, 287.25, 287.18, 293.05, 292.68, 294.8, 298.87, 298.21, 300.23, 297.84, 298.97, 302.25, 304.99, 308.82, 308.33, 310.85, 312.51, 312.06, 306.31, 315.2, 310.26, 311.23, 307.34, 301.54, 290.55, 291.58, 295.63, 291.13, 296.42, 299.24, 295.95, 298.01, 297.01, 294.3, 293.08, 275.15, 283.78, 281.74, 289.36, 294.38, 308.63, 312.66, 310.66, 313.39, 316.22, 315.32, 317.31, 314.86, 327.5, 333.26, 333.74, 326.59, 327.74, 325.89, 321.66, 333.02], 'signals': ['BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
     </row>
@@ -577,58 +577,58 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">UP  </t>
+          <t>DOWN</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.965</v>
+        <v>0.033</v>
       </c>
       <c r="E3" t="n">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F3" t="n">
         <v>60</v>
       </c>
       <c r="G3" t="n">
-        <v>55.6</v>
+        <v>75</v>
       </c>
       <c r="H3" t="n">
-        <v>782</v>
+        <v>198</v>
       </c>
       <c r="I3" t="n">
-        <v>15.6</v>
+        <v>4</v>
       </c>
       <c r="J3" t="n">
-        <v>-3.8</v>
+        <v>-5.3</v>
       </c>
       <c r="K3" t="n">
-        <v>19.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="L3" t="n">
         <v>5000</v>
       </c>
       <c r="M3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N3" t="n">
         <v>3</v>
       </c>
       <c r="O3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
       </c>
       <c r="Q3" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [404.32, 409.79, 408.08, 408.53, 404.88, 404.0, 400.99, 394.7, 399.09, 398.55, 390.94, 388.18, 381.04, 382.17, 371.93, 370.24, 365.18, 356.0, 358.18, 369.37, 368.57, 372.65, 372.07, 371.49, 373.52, 372.26, 370.07, 383.54, 392.26, 410.33, 419.35, 421.88, 417.17, 423.24, 431.98, 414.85, 423.7, 423.9, 428.32, 423.54, 406.9, 413.54, 412.73, 410.49, 413.07, 419.86, 414.22, 411.77, 406.89, 404.33, 408.55, 421.01, 422.62, 416.52, 420.15, 419.09, 418.57, 416.03, 412.67, 426.99, 450.24, 460.52, 441.31, 427.34, 428.05, 416.67, 411.74, 403.41, 397.36, 390.34, 390.74, 399.76, 393.83, 378.91, 379.4, 367.34, 373.94, 365.46, 352.83, 372.97, 368.57, 373.02, 384.28, 390.49, 386.74, 388.84, 383.34, 384.36, 385.1, 390.99, 384.93, 395.63, 401.1, 393.82, 402.29, 397.75, 390.34, 381.58, 381.7, 389.1], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [403.06, 404.32, 409.79, 408.08, 408.53, 404.88, 404.0, 400.99, 394.7, 399.09, 398.55, 390.94, 388.18, 381.04, 382.17, 371.93, 370.24, 365.18, 356.0, 358.18, 369.37, 368.57, 372.65, 372.07, 371.49, 373.52, 372.26, 370.07, 383.54, 392.26, 410.33, 419.35, 421.88, 417.17, 423.24, 431.98, 414.85, 423.7, 423.9, 428.32, 423.54, 406.9, 413.54, 412.73, 410.49, 413.07, 419.86, 414.22, 411.77, 406.89, 404.33, 408.55, 421.01, 422.62, 416.52, 420.15, 419.09, 418.57, 416.03, 412.67, 426.99, 450.24, 460.52, 441.31, 427.34, 428.05, 416.67, 411.74, 403.41, 397.36, 390.34, 390.74, 399.76, 393.83, 378.91, 379.4, 367.34, 373.94, 365.46, 352.83, 372.97, 368.57, 373.02, 384.28, 390.49, 386.74, 388.84, 383.34, 384.36, 385.1, 390.99, 384.93, 395.63, 401.1, 393.82, 402.29, 397.75, 390.34, 381.58, 381.7], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
     </row>
@@ -647,28 +647,28 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.501</v>
+        <v>0.505</v>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F4" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="G4" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="H4" t="n">
-        <v>184</v>
+        <v>448</v>
       </c>
       <c r="I4" t="n">
-        <v>3.7</v>
+        <v>9</v>
       </c>
       <c r="J4" t="n">
-        <v>7.9</v>
+        <v>5.5</v>
       </c>
       <c r="K4" t="n">
-        <v>-4.2</v>
+        <v>3.5</v>
       </c>
       <c r="L4" t="n">
         <v>5000</v>
@@ -677,20 +677,20 @@
         <v>15</v>
       </c>
       <c r="N4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q4" t="n">
         <v>1</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [302.74, 300.49, 298.13, 306.18, 306.86, 308.52, 303.37, 302.1, 305.38, 310.73, 307.51, 306.95, 300.82, 301.88, 290.27, 290.76, 280.75, 274.18, 273.34, 287.39, 297.21, 295.59, 299.81, 305.28, 317.13, 318.3, 317.05, 321.12, 332.71, 336.92, 335.82, 341.48, 337.22, 332.09, 339.12, 338.69, 344.19, 350.13, 349.57, 349.73, 384.57, 385.46, 383.02, 388.2, 397.8, 397.75, 400.56, 388.41, 387.12, 402.38, 400.83, 396.54, 396.7, 387.43, 388.68, 387.43, 382.74, 388.65, 388.6, 389.9, 380.11, 376.15, 361.63, 358.78, 371.97, 368.31, 363.31, 364.26, 356.38, 357.77, 359.68, 369.35, 373.25, 363.79, 368.03, 349.68, 346.13, 345.29, 343.71, 337.39, 353.65, 357.37, 361.21, 359.91, 366.46, 367.03, 361.92, 358.89, 357.18, 352.51, 359.51, 370.92, 354.46, 346.77, 351.99, 347.15, 342.09, 317.69, 319.74, 326.56], 'signals': ['BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [303.19, 302.74, 300.49, 298.13, 306.18, 306.86, 308.52, 303.37, 302.1, 305.38, 310.73, 307.51, 306.95, 300.82, 301.88, 290.27, 290.76, 280.75, 274.18, 273.34, 287.39, 297.21, 295.59, 299.81, 305.28, 317.13, 318.3, 317.05, 321.12, 332.71, 336.92, 335.82, 341.48, 337.22, 332.09, 339.12, 338.69, 344.19, 350.13, 349.57, 349.73, 384.57, 385.46, 383.02, 388.2, 397.8, 397.75, 400.56, 388.41, 387.12, 402.38, 400.83, 396.54, 396.7, 387.43, 388.68, 387.43, 382.74, 388.65, 388.6, 389.9, 380.11, 376.15, 361.63, 358.78, 371.97, 368.31, 363.31, 364.26, 356.38, 357.77, 359.68, 369.35, 373.25, 363.79, 368.03, 349.68, 346.13, 345.29, 343.71, 337.39, 353.65, 357.37, 361.21, 359.91, 366.46, 367.03, 361.92, 358.89, 357.18, 352.51, 359.51, 370.92, 354.46, 346.77, 351.99, 347.15, 342.09, 317.69, 319.74], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
     </row>
@@ -701,7 +701,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.652</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="E5" t="n">
         <v>59</v>
@@ -718,19 +718,19 @@
         <v>40</v>
       </c>
       <c r="G5" t="n">
-        <v>83.3</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>788</v>
+        <v>797</v>
       </c>
       <c r="I5" t="n">
-        <v>15.8</v>
+        <v>15.9</v>
       </c>
       <c r="J5" t="n">
-        <v>6.7</v>
+        <v>11.2</v>
       </c>
       <c r="K5" t="n">
-        <v>9.1</v>
+        <v>4.7</v>
       </c>
       <c r="L5" t="n">
         <v>5000</v>
@@ -739,20 +739,20 @@
         <v>21</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [216.82, 218.94, 213.21, 213.49, 214.33, 212.65, 209.53, 207.67, 211.74, 215.2, 209.87, 208.76, 205.37, 210.14, 207.24, 211.71, 207.54, 199.34, 200.95, 208.27, 210.57, 209.77, 212.79, 213.77, 221.25, 233.65, 238.38, 239.89, 249.02, 248.5, 249.7, 250.56, 248.28, 249.91, 255.36, 255.08, 263.99, 261.12, 259.7, 263.04, 265.06, 268.26, 272.05, 273.55, 274.99, 271.17, 272.68, 268.99, 265.82, 270.13, 267.22, 264.14, 264.86, 259.34, 265.01, 268.46, 266.32, 265.29, 271.85, 274.0, 270.64, 261.26, 256.52, 250.02, 253.79, 246.03, 245.22, 244.19, 238.0, 241.51, 238.55, 246.02, 246.0, 237.5, 244.39, 232.79, 234.11, 234.27, 227.01, 232.69, 240.14, 238.34, 241.7, 242.67, 244.16, 245.98, 243.62, 247.04, 245.34, 247.31, 247.49, 254.96, 249.89, 247.23, 249.99, 247.55, 244.85, 233.66, 232.11, 231.39], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [208.73, 216.82, 218.94, 213.21, 213.49, 214.33, 212.65, 209.53, 207.67, 211.74, 215.2, 209.87, 208.76, 205.37, 210.14, 207.24, 211.71, 207.54, 199.34, 200.95, 208.27, 210.57, 209.77, 212.79, 213.77, 221.25, 233.65, 238.38, 239.89, 249.02, 248.5, 249.7, 250.56, 248.28, 249.91, 255.36, 255.08, 263.99, 261.12, 259.7, 263.04, 265.06, 268.26, 272.05, 273.55, 274.99, 271.17, 272.68, 268.99, 265.82, 270.13, 267.22, 264.14, 264.86, 259.34, 265.01, 268.46, 266.32, 265.29, 271.85, 274.0, 270.64, 261.26, 256.52, 250.02, 253.79, 246.03, 245.22, 244.19, 238.0, 241.51, 238.55, 246.02, 246.0, 237.5, 244.39, 232.79, 234.11, 234.27, 227.01, 232.69, 240.14, 238.34, 241.7, 242.67, 244.16, 245.98, 243.62, 247.04, 245.34, 247.31, 247.49, 254.96, 249.89, 247.23, 249.99, 247.55, 244.85, 233.66, 232.11], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
     </row>
@@ -763,36 +763,36 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DOWN</t>
+          <t xml:space="preserve">UP  </t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.399</v>
+        <v>0.627</v>
       </c>
       <c r="E6" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F6" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="G6" t="n">
-        <v>35.3</v>
+        <v>38.5</v>
       </c>
       <c r="H6" t="n">
-        <v>-221</v>
+        <v>416</v>
       </c>
       <c r="I6" t="n">
-        <v>-4.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>-10.9</v>
+        <v>-9</v>
       </c>
       <c r="K6" t="n">
-        <v>6.5</v>
+        <v>17.3</v>
       </c>
       <c r="L6" t="n">
         <v>5000</v>
@@ -801,20 +801,20 @@
         <v>8</v>
       </c>
       <c r="N6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O6" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="P6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q6" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [666.54, 659.39, 643.71, 646.24, 652.91, 653.69, 637.04, 612.62, 626.87, 622.08, 615.11, 606.14, 593.11, 603.5, 592.37, 594.34, 547.03, 525.23, 535.88, 571.6, 578.69, 573.93, 572.49, 574.52, 611.85, 627.81, 629.28, 633.94, 661.88, 670.96, 676.24, 687.91, 670.29, 668.22, 674.1, 658.54, 674.4, 677.99, 670.72, 668.5, 611.34, 608.19, 609.84, 604.4, 612.31, 616.24, 609.07, 598.31, 602.44, 616.06, 617.86, 613.66, 610.64, 602.05, 604.5, 606.82, 609.69, 611.77, 634.67, 634.7, 631.92, 599.91, 597.08, 622.4, 626.99, 592.45, 584.85, 584.05, 570.45, 567.9, 566.45, 593.48, 600.21, 567.58, 577.22, 563.85, 562.2, 557.67, 542.87, 550.25, 562.6, 563.29, 612.91, 582.9, 600.29, 615.58, 603.12, 631.48, 669.21, 656.73, 661.04, 681.31, 664.54, 646.01, 645.85, 643.81, 627.17, 606.1, 595.19, 593.87], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [653.91, 666.54, 659.39, 643.71, 646.24, 652.91, 653.69, 637.04, 612.62, 626.87, 622.08, 615.11, 606.14, 593.11, 603.5, 592.37, 594.34, 547.03, 525.23, 535.88, 571.6, 578.69, 573.93, 572.49, 574.52, 611.85, 627.81, 629.28, 633.94, 661.88, 670.96, 676.24, 687.91, 670.29, 668.22, 674.1, 658.54, 674.4, 677.99, 670.72, 668.5, 611.34, 608.19, 609.84, 604.4, 612.31, 616.24, 609.07, 598.31, 602.44, 616.06, 617.86, 613.66, 610.64, 602.05, 604.5, 606.82, 609.69, 611.77, 634.67, 634.7, 631.92, 599.91, 597.08, 622.4, 626.99, 592.45, 584.85, 584.05, 570.45, 567.9, 566.45, 593.48, 600.21, 567.58, 577.22, 563.85, 562.2, 557.67, 542.87, 550.25, 562.6, 563.29, 612.91, 582.9, 600.29, 615.58, 603.12, 631.48, 669.21, 656.73, 661.04, 681.31, 664.54, 646.01, 645.85, 643.81, 627.17, 606.1, 595.19], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -833,50 +833,50 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.436</v>
+        <v>0.424</v>
       </c>
       <c r="E7" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F7" t="n">
         <v>80</v>
       </c>
       <c r="G7" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="H7" t="n">
-        <v>570</v>
+        <v>520</v>
       </c>
       <c r="I7" t="n">
-        <v>11.4</v>
+        <v>10.4</v>
       </c>
       <c r="J7" t="n">
-        <v>7.5</v>
+        <v>15</v>
       </c>
       <c r="K7" t="n">
-        <v>3.9</v>
+        <v>-4.6</v>
       </c>
       <c r="L7" t="n">
         <v>5000</v>
       </c>
       <c r="M7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N7" t="n">
         <v>4</v>
       </c>
       <c r="O7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P7" t="n">
         <v>4</v>
       </c>
       <c r="Q7" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [182.82, 183.12, 177.6, 182.43, 184.54, 185.81, 182.93, 180.04, 183.01, 181.72, 180.19, 178.35, 172.5, 175.44, 175.0, 178.47, 171.04, 167.32, 164.98, 174.2, 175.55, 177.18, 177.43, 177.89, 181.87, 183.7, 188.41, 189.09, 196.28, 198.64, 198.12, 201.45, 201.82, 199.65, 202.26, 199.41, 208.03, 216.36, 212.92, 209.01, 199.34, 198.22, 198.25, 196.27, 207.59, 211.25, 214.95, 219.18, 220.52, 225.57, 235.47, 225.06, 222.06, 220.35, 223.21, 219.25, 215.08, 214.61, 212.35, 214.0, 210.89, 224.1, 222.56, 214.5, 218.66, 205.1, 208.64, 208.19, 200.42, 204.87, 205.19, 212.45, 207.41, 204.65, 210.69, 208.65, 200.04, 199.0, 195.74, 192.53, 194.97, 200.09, 197.58, 194.83, 195.55, 196.93, 204.12, 202.78, 210.96, 203.53, 211.8, 212.5, 207.4, 202.81, 203.28, 207.29, 212.06, 208.76, 206.84, 196.51], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY']}</t>
+          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [179.83, 182.82, 183.12, 177.6, 182.43, 184.54, 185.81, 182.93, 180.04, 183.01, 181.72, 180.19, 178.35, 172.5, 175.44, 175.0, 178.47, 171.04, 167.32, 164.98, 174.2, 175.55, 177.18, 177.43, 177.89, 181.87, 183.7, 188.41, 189.09, 196.28, 198.64, 198.12, 201.45, 201.82, 199.65, 202.26, 199.41, 208.03, 216.36, 212.92, 209.01, 199.34, 198.22, 198.25, 196.27, 207.59, 211.25, 214.95, 219.18, 220.52, 225.57, 235.47, 225.06, 222.06, 220.35, 223.21, 219.25, 215.08, 214.61, 212.35, 214.0, 210.89, 224.1, 222.56, 214.5, 218.66, 205.1, 208.64, 208.19, 200.42, 204.87, 205.19, 212.45, 207.41, 204.65, 210.69, 208.65, 200.04, 199.0, 195.74, 192.53, 194.97, 200.09, 197.58, 194.83, 195.55, 196.93, 204.12, 202.78, 210.96, 203.53, 211.8, 212.5, 207.4, 202.81, 203.28, 207.29, 212.06, 208.76, 206.84], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
     </row>
@@ -887,7 +887,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -895,50 +895,50 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.432</v>
+        <v>0.434</v>
       </c>
       <c r="E8" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F8" t="n">
         <v>70</v>
       </c>
       <c r="G8" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="H8" t="n">
-        <v>1316</v>
+        <v>605</v>
       </c>
       <c r="I8" t="n">
-        <v>26.3</v>
+        <v>12.1</v>
       </c>
       <c r="J8" t="n">
-        <v>144.9</v>
+        <v>173.3</v>
       </c>
       <c r="K8" t="n">
-        <v>-118.6</v>
+        <v>-161.2</v>
       </c>
       <c r="L8" t="n">
         <v>5000</v>
       </c>
       <c r="M8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O8" t="n">
         <v>5</v>
       </c>
       <c r="P8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [202.07, 199.45, 192.43, 202.68, 203.23, 204.83, 197.74, 193.39, 196.58, 196.31, 199.46, 205.27, 201.33, 202.68, 205.37, 220.27, 203.77, 201.99, 196.04, 203.43, 210.21, 217.5, 220.18, 221.53, 231.82, 236.64, 245.04, 246.83, 255.07, 258.12, 278.26, 278.39, 274.95, 284.49, 303.46, 305.33, 347.81, 334.63, 323.21, 337.11, 354.49, 360.54, 341.54, 355.26, 421.39, 408.46, 455.19, 458.79, 448.29, 445.5, 449.7, 424.1, 420.99, 414.05, 447.58, 449.59, 467.51, 503.89, 495.54, 518.09, 516.1, 510.13, 521.54, 542.52, 523.2, 466.38, 490.33, 475.51, 452.4, 488.45, 511.57, 547.26, 507.29, 512.48, 537.37, 551.63, 519.85, 519.74, 532.57, 521.58, 539.49, 580.91, 540.88, 517.82, 552.05, 516.11, 517.41, 546.72, 557.89, 534.39, 548.13, 529.14, 500.94, 495.76, 503.57, 544.43, 552.33, 539.69, 521.95, 494.95], 'signals': ['BUY', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'BUY', 'SELL', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [190.95, 202.07, 199.45, 192.43, 202.68, 203.23, 204.83, 197.74, 193.39, 196.58, 196.31, 199.46, 205.27, 201.33, 202.68, 205.37, 220.27, 203.77, 201.99, 196.04, 203.43, 210.21, 217.5, 220.18, 221.53, 231.82, 236.64, 245.04, 246.83, 255.07, 258.12, 278.26, 278.39, 274.95, 284.49, 303.46, 305.33, 347.81, 334.63, 323.21, 337.11, 354.49, 360.54, 341.54, 355.26, 421.39, 408.46, 455.19, 458.79, 448.29, 445.5, 449.7, 424.1, 420.99, 414.05, 447.58, 449.59, 467.51, 503.89, 495.54, 518.09, 516.1, 510.13, 521.54, 542.52, 523.2, 466.38, 490.33, 475.51, 452.4, 488.45, 511.57, 547.26, 507.29, 512.48, 537.37, 551.63, 519.85, 519.74, 532.57, 521.58, 539.49, 580.91, 540.88, 517.82, 552.05, 516.11, 517.41, 546.72, 557.89, 534.39, 548.13, 529.14, 500.94, 495.76, 503.57, 544.43, 552.33, 539.69, 521.95], 'signals': ['BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'BUY', 'SELL', 'BUY', 'SELL', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
     </row>
@@ -957,28 +957,28 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.64</v>
+        <v>0.639</v>
       </c>
       <c r="E9" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F9" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G9" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="H9" t="n">
-        <v>289</v>
+        <v>159</v>
       </c>
       <c r="I9" t="n">
-        <v>5.8</v>
+        <v>3.2</v>
       </c>
       <c r="J9" t="n">
-        <v>21.1</v>
+        <v>22.1</v>
       </c>
       <c r="K9" t="n">
-        <v>-15.3</v>
+        <v>-18.9</v>
       </c>
       <c r="L9" t="n">
         <v>5000</v>
@@ -987,20 +987,20 @@
         <v>13</v>
       </c>
       <c r="N9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [316.36, 331.55, 329.27, 344.48, 341.32, 340.32, 334.74, 320.98, 323.73, 320.13, 314.77, 318.67, 309.37, 322.0, 317.79, 318.31, 308.93, 300.2, 292.95, 309.02, 312.99, 314.05, 313.93, 333.44, 350.08, 354.35, 370.96, 379.15, 380.18, 396.09, 397.84, 405.9, 399.0, 401.53, 421.98, 419.28, 422.09, 417.54, 399.2, 404.81, 416.77, 420.61, 415.84, 426.68, 424.77, 411.91, 429.32, 427.75, 418.64, 416.13, 439.1, 424.52, 420.05, 410.42, 417.1, 413.91, 413.49, 421.34, 421.19, 425.91, 446.06, 459.24, 480.81, 478.47, 418.25, 385.12, 395.97, 391.54, 371.51, 384.96, 381.47, 393.32, 376.11, 392.28, 410.7, 392.13, 380.15, 382.07, 378.91, 365.02, 372.45, 377.75, 369.34, 360.45, 373.9, 370.78, 388.69, 401.11, 399.97, 384.05, 389.11, 394.28, 374.45, 370.83, 378.16, 386.5, 396.81, 392.47, 381.92, 383.22], 'signals': ['BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [312.69, 316.36, 331.55, 329.27, 344.48, 341.32, 340.32, 334.74, 320.98, 323.73, 320.13, 314.77, 318.67, 309.37, 322.0, 317.79, 318.31, 308.93, 300.2, 292.95, 309.02, 312.99, 314.05, 313.93, 333.44, 350.08, 354.35, 370.96, 379.15, 380.18, 396.09, 397.84, 405.9, 399.0, 401.53, 421.98, 419.28, 422.09, 417.54, 399.2, 404.81, 416.77, 420.61, 415.84, 426.68, 424.77, 411.91, 429.32, 427.75, 418.64, 416.13, 439.1, 424.52, 420.05, 410.42, 417.1, 413.91, 413.49, 421.34, 421.19, 425.91, 446.06, 459.24, 480.81, 478.47, 418.25, 385.12, 395.97, 391.54, 371.51, 384.96, 381.47, 393.32, 376.11, 392.28, 410.7, 392.13, 380.15, 382.07, 378.91, 365.02, 372.45, 377.75, 369.34, 360.45, 373.9, 370.78, 388.69, 401.11, 399.97, 384.05, 389.11, 394.28, 374.45, 370.83, 378.16, 386.5, 396.81, 392.47, 381.92], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
     </row>
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1019,28 +1019,28 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.489</v>
+        <v>0.443</v>
       </c>
       <c r="E10" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F10" t="n">
         <v>40</v>
       </c>
       <c r="G10" t="n">
-        <v>60</v>
+        <v>57.9</v>
       </c>
       <c r="H10" t="n">
-        <v>2829</v>
+        <v>3327</v>
       </c>
       <c r="I10" t="n">
-        <v>56.6</v>
+        <v>66.5</v>
       </c>
       <c r="J10" t="n">
-        <v>124.7</v>
+        <v>142.7</v>
       </c>
       <c r="K10" t="n">
-        <v>-68.09999999999999</v>
+        <v>-76.2</v>
       </c>
       <c r="L10" t="n">
         <v>5000</v>
@@ -1052,17 +1052,17 @@
         <v>2</v>
       </c>
       <c r="O10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P10" t="n">
         <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [400.54, 396.82, 370.09, 389.1, 402.88, 418.45, 405.12, 425.89, 441.55, 461.43, 461.47, 444.02, 422.66, 404.12, 395.3, 381.87, 355.26, 357.02, 321.75, 337.79, 367.79, 366.18, 377.7, 377.52, 406.67, 421.45, 420.53, 426.49, 465.59, 456.16, 457.16, 455.0, 448.35, 449.31, 487.41, 481.65, 496.64, 524.48, 504.21, 518.38, 517.08, 542.13, 576.36, 640.1, 666.49, 646.53, 746.7, 795.21, 766.46, 803.51, 775.89, 724.55, 681.44, 698.63, 731.88, 761.98, 750.88, 895.74, 928.27, 923.38, 970.85, 1035.34, 1063.94, 1079.4, 995.85, 863.88, 949.13, 935.75, 891.74, 995.72, 981.46, 1087.82, 1020.6, 1043.03, 1133.82, 1211.19, 1051.61, 1048.35, 1213.37, 1132.16, 1145.1, 1154.11, 1032.12, 975.41, 984.75, 938.38, 948.8, 991.64, 979.3, 937.0, 983.12, 904.28, 853.2, 848.95, 865.46, 970.82, 959.48, 990.21, 920.95, 900.2], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [379.46, 400.54, 396.82, 370.09, 389.1, 402.88, 418.45, 405.12, 425.89, 441.55, 461.43, 461.47, 444.02, 422.66, 404.12, 395.3, 381.87, 355.26, 357.02, 321.75, 337.79, 367.79, 366.18, 377.7, 377.52, 406.67, 421.45, 420.53, 426.49, 465.59, 456.16, 457.16, 455.0, 448.35, 449.31, 487.41, 481.65, 496.64, 524.48, 504.21, 518.38, 517.08, 542.13, 576.36, 640.1, 666.49, 646.53, 746.7, 795.21, 766.46, 803.51, 775.89, 724.55, 681.44, 698.63, 731.88, 761.98, 750.88, 895.74, 928.27, 923.38, 970.85, 1035.34, 1063.94, 1079.4, 995.85, 863.88, 949.13, 935.75, 891.74, 995.72, 981.46, 1087.82, 1020.6, 1043.03, 1133.82, 1211.19, 1051.61, 1048.35, 1213.37, 1132.16, 1145.1, 1154.11, 1032.12, 975.41, 984.75, 938.38, 948.8, 991.64, 979.3, 937.0, 983.12, 904.28, 853.2, 848.95, 865.46, 970.82, 959.48, 990.21, 920.95], 'signals': ['FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1081,34 +1081,34 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.404</v>
+        <v>0.419</v>
       </c>
       <c r="E11" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="F11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>-243</v>
+        <v>-375</v>
       </c>
       <c r="I11" t="n">
-        <v>-4.9</v>
+        <v>-7.5</v>
       </c>
       <c r="J11" t="n">
-        <v>-23.8</v>
+        <v>-20.2</v>
       </c>
       <c r="K11" t="n">
-        <v>18.9</v>
+        <v>12.7</v>
       </c>
       <c r="L11" t="n">
         <v>5000</v>
       </c>
       <c r="M11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N11" t="n">
         <v>1</v>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [405.94, 405.55, 396.73, 398.68, 399.24, 407.82, 395.01, 391.2, 395.56, 399.27, 392.78, 380.3, 367.96, 380.85, 383.03, 385.95, 372.11, 361.83, 355.28, 371.75, 381.26, 360.59, 352.82, 346.65, 343.25, 345.62, 348.95, 352.42, 364.2, 391.95, 388.9, 400.62, 392.5, 386.42, 387.51, 373.72, 376.3, 378.67, 376.02, 372.8, 381.63, 390.82, 392.51, 389.37, 398.73, 411.79, 428.35, 445.0, 433.45, 445.27, 443.3, 422.24, 409.99, 404.11, 417.26, 417.85, 426.01, 433.59, 440.36, 442.1, 435.79, 415.88, 423.74, 423.7, 418.45, 391.0, 408.95, 396.68, 381.59, 399.15, 406.43, 411.15, 404.66, 396.38, 400.49, 405.05, 381.61, 375.53, 375.12, 379.71, 411.84, 420.6, 425.3, 393.45, 419.77, 402.9, 394.06, 406.55, 407.76, 394.76, 396.18, 394.46, 391.06, 380.84, 369.57, 378.93, 374.01, 319.69, 313.03, 309.22], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [392.43, 405.94, 405.55, 396.73, 398.68, 399.24, 407.82, 395.01, 391.2, 395.56, 399.27, 392.78, 380.3, 367.96, 380.85, 383.03, 385.95, 372.11, 361.83, 355.28, 371.75, 381.26, 360.59, 352.82, 346.65, 343.25, 345.62, 348.95, 352.42, 364.2, 391.95, 388.9, 400.62, 392.5, 386.42, 387.51, 373.72, 376.3, 378.67, 376.02, 372.8, 381.63, 390.82, 392.51, 389.37, 398.73, 411.79, 428.35, 445.0, 433.45, 445.27, 443.3, 422.24, 409.99, 404.11, 417.26, 417.85, 426.01, 433.59, 440.36, 442.1, 435.79, 415.88, 423.74, 423.7, 418.45, 391.0, 408.95, 396.68, 381.59, 399.15, 406.43, 411.15, 404.66, 396.38, 400.49, 405.05, 381.61, 375.53, 375.12, 379.71, 411.84, 420.6, 425.3, 393.45, 419.77, 402.9, 394.06, 406.55, 407.76, 394.76, 396.18, 394.46, 391.06, 380.84, 369.57, 378.93, 374.01, 319.69, 313.03], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
     </row>
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1143,28 +1143,28 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.379</v>
+        <v>0.349</v>
       </c>
       <c r="E12" t="n">
         <v>60</v>
       </c>
       <c r="F12" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="G12" t="n">
-        <v>26.7</v>
+        <v>35.7</v>
       </c>
       <c r="H12" t="n">
-        <v>-478</v>
+        <v>-952</v>
       </c>
       <c r="I12" t="n">
-        <v>-9.6</v>
+        <v>-19</v>
       </c>
       <c r="J12" t="n">
-        <v>-28.6</v>
+        <v>-28.3</v>
       </c>
       <c r="K12" t="n">
-        <v>19</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="L12" t="n">
         <v>5000</v>
@@ -1173,20 +1173,20 @@
         <v>71</v>
       </c>
       <c r="N12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [98.66, 99.17, 99.02, 98.32, 96.94, 94.89, 94.31, 95.31, 95.2, 94.36, 94.7, 91.74, 91.82, 93.38, 90.92, 92.28, 93.32, 93.43, 92.97, 96.15, 95.55, 98.66, 98.93, 98.82, 99.39, 102.05, 103.01, 103.16, 106.28, 107.71, 107.79, 97.31, 94.83, 92.58, 93.24, 92.82, 92.44, 91.37, 92.27, 92.12, 93.61, 92.06, 91.02, 87.89, 88.27, 88.25, 87.49, 85.45, 87.66, 87.56, 86.94, 87.02, 89.65, 89.33, 88.09, 89.3, 88.6, 87.68, 87.35, 86.36, 86.02, 85.85, 83.33, 81.52, 81.56, 82.18, 82.64, 81.41, 82.0, 81.27, 80.34, 81.67, 78.72, 76.96, 77.38, 72.88, 72.82, 71.84, 70.9, 73.81, 73.78, 71.4, 74.19, 77.65, 76.02, 76.18, 75.59, 75.47, 73.37, 73.83, 73.53, 73.68, 74.35, 68.95, 67.6, 68.67, 68.53, 68.89, 70.09, 70.4], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [97.7, 98.66, 99.17, 99.02, 98.32, 96.94, 94.89, 94.31, 95.31, 95.2, 94.36, 94.7, 91.74, 91.82, 93.38, 90.92, 92.28, 93.32, 93.43, 92.97, 96.15, 95.55, 98.66, 98.93, 98.82, 99.39, 102.05, 103.01, 103.16, 106.28, 107.71, 107.79, 97.31, 94.83, 92.58, 93.24, 92.82, 92.44, 91.37, 92.27, 92.12, 93.61, 92.06, 91.02, 87.89, 88.27, 88.25, 87.49, 85.45, 87.66, 87.56, 86.94, 87.02, 89.65, 89.33, 88.09, 89.3, 88.6, 87.68, 87.35, 86.36, 86.02, 85.85, 83.33, 81.52, 81.56, 82.18, 82.64, 81.41, 82.0, 81.27, 80.34, 81.67, 78.72, 76.96, 77.38, 72.88, 72.82, 71.84, 70.9, 73.81, 73.78, 71.4, 74.19, 77.65, 76.02, 76.18, 75.59, 75.47, 73.37, 73.83, 73.53, 73.68, 74.35, 68.95, 67.6, 68.67, 68.53, 68.89, 70.09], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
     </row>
@@ -1201,54 +1201,54 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">UP  </t>
+          <t>DOWN</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.508</v>
+        <v>0.458</v>
       </c>
       <c r="E13" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F13" t="n">
         <v>30</v>
       </c>
       <c r="G13" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H13" t="n">
-        <v>-1260</v>
+        <v>-652</v>
       </c>
       <c r="I13" t="n">
-        <v>-25.2</v>
+        <v>-13</v>
       </c>
       <c r="J13" t="n">
-        <v>-14.1</v>
+        <v>-16.5</v>
       </c>
       <c r="K13" t="n">
-        <v>-11.1</v>
+        <v>3.5</v>
       </c>
       <c r="L13" t="n">
         <v>5000</v>
       </c>
       <c r="M13" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="N13" t="n">
         <v>3</v>
       </c>
       <c r="O13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P13" t="n">
         <v>3</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [153.19, 152.67, 157.16, 156.43, 151.14, 151.6, 153.5, 150.95, 152.72, 155.08, 152.77, 155.68, 150.68, 160.84, 154.78, 154.96, 147.56, 143.06, 137.55, 146.28, 146.49, 148.46, 147.93, 150.07, 140.76, 130.49, 128.06, 132.37, 135.7, 142.15, 142.76, 146.39, 145.89, 145.97, 152.62, 141.57, 143.09, 143.1, 141.18, 137.97, 139.11, 144.07, 146.03, 135.91, 133.79, 137.05, 137.8, 136.89, 136.0, 130.05, 133.73, 133.99, 135.14, 135.26, 137.15, 137.41, 136.88, 136.6, 132.51, 143.34, 156.54, 160.65, 152.17, 142.2, 141.7, 135.53, 136.47, 132.07, 130.21, 131.08, 127.99, 134.71, 133.25, 130.63, 128.47, 119.5, 116.7, 113.5, 107.27, 112.93, 115.7, 116.67, 125.73, 129.3, 132.54, 134.37, 132.22, 129.04, 126.79, 130.04, 133.72, 133.76, 134.44, 132.38, 134.85, 132.66, 124.57, 123.37, 122.92, 131.53], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [147.22, 153.19, 152.67, 157.16, 156.43, 151.14, 151.6, 153.5, 150.95, 152.72, 155.08, 152.77, 155.68, 150.68, 160.84, 154.78, 154.96, 147.56, 143.06, 137.55, 146.28, 146.49, 148.46, 147.93, 150.07, 140.76, 130.49, 128.06, 132.37, 135.7, 142.15, 142.76, 146.39, 145.89, 145.97, 152.62, 141.57, 143.09, 143.1, 141.18, 137.97, 139.11, 144.07, 146.03, 135.91, 133.79, 137.05, 137.8, 136.89, 136.0, 130.05, 133.73, 133.99, 135.14, 135.26, 137.15, 137.41, 136.88, 136.6, 132.51, 143.34, 156.54, 160.65, 152.17, 142.2, 141.7, 135.53, 136.47, 132.07, 130.21, 131.08, 127.99, 134.71, 133.25, 130.63, 128.47, 119.5, 116.7, 113.5, 107.27, 112.93, 115.7, 116.67, 125.73, 129.3, 132.54, 134.37, 132.22, 129.04, 126.79, 130.04, 133.72, 133.76, 134.44, 132.38, 134.85, 132.66, 124.57, 123.37, 122.92], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
     </row>
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1267,16 +1267,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.304</v>
+        <v>0.215</v>
       </c>
       <c r="E14" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F14" t="n">
         <v>60</v>
       </c>
       <c r="G14" t="n">
-        <v>58.3</v>
+        <v>56.2</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1285,16 +1285,16 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>-9.6</v>
+        <v>-16.1</v>
       </c>
       <c r="K14" t="n">
-        <v>9.6</v>
+        <v>16.1</v>
       </c>
       <c r="L14" t="n">
         <v>5000</v>
       </c>
       <c r="M14" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [192.1, 200.37, 201.09, 197.78, 193.92, 193.15, 198.27, 191.85, 197.34, 194.32, 193.36, 194.0, 194.39, 194.19, 182.09, 181.04, 184.7, 178.4, 184.09, 185.72, 185.3, 186.23, 184.09, 182.03, 175.48, 170.41, 164.54, 172.38, 170.87, 177.14, 180.75, 181.67, 185.79, 186.63, 189.31, 172.85, 177.7, 179.72, 180.85, 180.75, 176.08, 183.35, 185.0, 186.51, 180.72, 185.86, 181.35, 177.03, 170.87, 165.41, 167.15, 173.06, 179.02, 178.96, 179.64, 175.86, 179.61, 178.62, 177.05, 175.72, 190.61, 209.06, 200.32, 190.12, 188.26, 185.18, 182.08, 174.9, 170.48, 166.45, 165.89, 164.55, 161.71, 155.02, 151.78, 150.12, 153.42, 152.76, 150.19, 158.37, 157.93, 156.66, 163.23, 166.11, 165.65, 169.52, 166.58, 162.5, 163.32, 171.22, 167.56, 167.0, 172.68, 170.77, 173.79, 170.06, 163.0, 156.93, 163.66, 173.6], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [195.06, 192.1, 200.37, 201.09, 197.78, 193.92, 193.15, 198.27, 191.85, 197.34, 194.32, 193.36, 194.0, 194.39, 194.19, 182.09, 181.04, 184.7, 178.4, 184.09, 185.72, 185.3, 186.23, 184.09, 182.03, 175.48, 170.41, 164.54, 172.38, 170.87, 177.14, 180.75, 181.67, 185.79, 186.63, 189.31, 172.85, 177.7, 179.72, 180.85, 180.75, 176.08, 183.35, 185.0, 186.51, 180.72, 185.86, 181.35, 177.03, 170.87, 165.41, 167.15, 173.06, 179.02, 178.96, 179.64, 175.86, 179.61, 178.62, 177.05, 175.72, 190.61, 209.06, 200.32, 190.12, 188.26, 185.18, 182.08, 174.9, 170.48, 166.45, 165.89, 164.55, 161.71, 155.02, 151.78, 150.12, 153.42, 152.76, 150.19, 158.37, 157.93, 156.66, 163.23, 166.11, 165.65, 169.52, 166.58, 162.5, 163.32, 171.22, 167.56, 167.0, 172.68, 170.77, 173.79, 170.06, 163.0, 156.93, 163.66], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
     </row>
@@ -1329,28 +1329,28 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.726</v>
+        <v>0.75</v>
       </c>
       <c r="E15" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F15" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="G15" t="n">
-        <v>70</v>
+        <v>54.5</v>
       </c>
       <c r="H15" t="n">
-        <v>2102</v>
+        <v>1430</v>
       </c>
       <c r="I15" t="n">
-        <v>42</v>
+        <v>28.6</v>
       </c>
       <c r="J15" t="n">
-        <v>76.7</v>
+        <v>87.3</v>
       </c>
       <c r="K15" t="n">
-        <v>-34.7</v>
+        <v>-58.7</v>
       </c>
       <c r="L15" t="n">
         <v>5000</v>
@@ -1359,20 +1359,20 @@
         <v>27</v>
       </c>
       <c r="N15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O15" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="P15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q15" t="n">
-        <v>9</v>
+        <v>3.8</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [101.92, 106.54, 107.25, 108.53, 109.08, 110.51, 110.39, 110.44, 105.96, 108.3, 108.95, 107.04, 102.25, 103.33, 98.25, 96.46, 98.15, 92.39, 95.01, 97.6, 98.33, 99.78, 99.65, 105.81, 106.63, 98.67, 94.75, 100.56, 99.62, 102.79, 104.55, 105.99, 108.29, 112.4, 116.67, 111.35, 112.03, 113.65, 113.75, 113.1, 111.44, 113.91, 117.31, 119.13, 117.02, 126.43, 131.94, 135.57, 136.54, 140.64, 144.99, 148.52, 154.71, 154.22, 162.53, 162.06, 165.87, 167.89, 161.34, 167.75, 182.75, 195.54, 192.24, 186.9, 179.77, 167.76, 164.7, 161.23, 161.93, 172.88, 170.7, 173.23, 169.87, 170.74, 171.21, 168.86, 170.23, 168.26, 169.66, 175.27, 185.73, 190.79, 193.18, 193.98, 199.38, 194.62, 191.12, 198.4, 187.18, 187.91, 210.73, 206.77, 203.76, 203.08, 198.49, 191.15, 188.42, 183.42, 183.28, 180.11], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT']}</t>
+          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [97.86, 101.92, 106.54, 107.25, 108.53, 109.08, 110.51, 110.39, 110.44, 105.96, 108.3, 108.95, 107.04, 102.25, 103.33, 98.25, 96.46, 98.15, 92.39, 95.01, 97.6, 98.33, 99.78, 99.65, 105.81, 106.63, 98.67, 94.75, 100.56, 99.62, 102.79, 104.55, 105.99, 108.29, 112.4, 116.67, 111.35, 112.03, 113.65, 113.75, 113.1, 111.44, 113.91, 117.31, 119.13, 117.02, 126.43, 131.94, 135.57, 136.54, 140.64, 144.99, 148.52, 154.71, 154.22, 162.53, 162.06, 165.87, 167.89, 161.34, 167.75, 182.75, 195.54, 192.24, 186.9, 179.77, 167.76, 164.7, 161.23, 161.93, 172.88, 170.7, 173.23, 169.87, 170.74, 171.21, 168.86, 170.23, 168.26, 169.66, 175.27, 185.73, 190.79, 193.18, 193.98, 199.38, 194.62, 191.12, 198.4, 187.18, 187.91, 210.73, 206.77, 203.76, 203.08, 198.49, 191.15, 188.42, 183.42, 183.28], 'signals': ['FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1391,28 +1391,28 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.461</v>
+        <v>0.462</v>
       </c>
       <c r="E16" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="F16" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G16" t="n">
         <v>65</v>
       </c>
       <c r="H16" t="n">
-        <v>435</v>
+        <v>285</v>
       </c>
       <c r="I16" t="n">
-        <v>8.699999999999999</v>
+        <v>5.7</v>
       </c>
       <c r="J16" t="n">
-        <v>20.1</v>
+        <v>18.8</v>
       </c>
       <c r="K16" t="n">
-        <v>-11.4</v>
+        <v>-13.1</v>
       </c>
       <c r="L16" t="n">
         <v>5000</v>
@@ -1421,20 +1421,20 @@
         <v>14</v>
       </c>
       <c r="N16" t="n">
+        <v>3</v>
+      </c>
+      <c r="O16" t="n">
         <v>2</v>
       </c>
-      <c r="O16" t="n">
-        <v>6</v>
-      </c>
       <c r="P16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q16" t="n">
-        <v>4</v>
+        <v>1.7</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [296.53, 290.75, 286.71, 287.15, 285.97, 284.77, 280.19, 280.73, 283.43, 284.15, 284.99, 285.22, 283.82, 287.14, 289.61, 292.6, 288.87, 280.14, 281.06, 291.35, 292.56, 291.79, 294.12, 296.07, 306.59, 308.94, 308.48, 312.27, 309.72, 304.56, 308.56, 308.9, 315.57, 311.6, 311.62, 310.29, 306.9, 310.23, 310.05, 307.86, 311.83, 311.07, 306.27, 308.01, 313.49, 304.9, 300.75, 298.65, 303.51, 298.9, 298.57, 296.47, 299.38, 294.37, 300.63, 301.64, 305.01, 305.36, 297.94, 295.4, 297.97, 295.25, 299.61, 299.5, 309.5, 310.97, 309.71, 311.3, 307.75, 312.08, 319.28, 317.97, 329.65, 331.96, 323.76, 329.99, 332.64, 331.95, 333.62, 327.57, 327.91, 325.86, 332.57, 332.97, 337.72, 339.22, 330.62, 335.47, 336.47, 334.53, 342.89, 346.91, 343.15, 341.1, 338.87, 345.23, 348.21, 349.9, 353.21, 356.2], 'signals': ['BUY', 'SELL', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [297.39, 296.53, 290.75, 286.71, 287.15, 285.97, 284.77, 280.19, 280.73, 283.43, 284.15, 284.99, 285.22, 283.82, 287.14, 289.61, 292.6, 288.87, 280.14, 281.06, 291.35, 292.56, 291.79, 294.12, 296.07, 306.59, 308.94, 308.48, 312.27, 309.72, 304.56, 308.56, 308.9, 315.57, 311.6, 311.62, 310.29, 306.9, 310.23, 310.05, 307.86, 311.83, 311.07, 306.27, 308.01, 313.49, 304.9, 300.75, 298.65, 303.51, 298.9, 298.57, 296.47, 299.38, 294.37, 300.63, 301.64, 305.01, 305.36, 297.94, 295.4, 297.97, 295.25, 299.61, 299.5, 309.5, 310.97, 309.71, 311.3, 307.75, 312.08, 319.28, 317.97, 329.65, 331.96, 323.76, 329.99, 332.64, 331.95, 333.62, 327.57, 327.91, 325.86, 332.57, 332.97, 337.72, 339.22, 330.62, 335.47, 336.47, 334.53, 342.89, 346.91, 343.15, 341.1, 338.87, 345.23, 348.21, 349.9, 353.21], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
     </row>
@@ -1445,7 +1445,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1453,28 +1453,28 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.542</v>
       </c>
       <c r="E17" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F17" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G17" t="n">
         <v>65</v>
       </c>
       <c r="H17" t="n">
-        <v>739</v>
+        <v>659</v>
       </c>
       <c r="I17" t="n">
-        <v>14.8</v>
+        <v>13.2</v>
       </c>
       <c r="J17" t="n">
-        <v>21.4</v>
+        <v>23.6</v>
       </c>
       <c r="K17" t="n">
-        <v>-6.6</v>
+        <v>-10.4</v>
       </c>
       <c r="L17" t="n">
         <v>5000</v>
@@ -1483,20 +1483,20 @@
         <v>4</v>
       </c>
       <c r="N17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O17" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="P17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q17" t="n">
-        <v>19</v>
+        <v>5.3</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [863.44, 831.79, 817.82, 828.38, 830.15, 820.15, 784.06, 778.78, 791.28, 803.5, 801.95, 805.95, 809.96, 827.62, 832.05, 838.15, 819.03, 799.37, 804.06, 842.28, 856.44, 859.25, 862.25, 860.36, 901.78, 899.75, 903.82, 886.88, 905.64, 895.54, 896.05, 921.89, 937.61, 922.48, 930.74, 927.21, 922.84, 933.7, 922.48, 901.63, 919.72, 919.66, 899.31, 914.86, 933.24, 921.81, 932.37, 940.71, 941.75, 951.23, 964.71, 944.31, 942.21, 924.66, 977.81, 983.83, 992.36, 990.16, 992.1, 1003.95, 1021.06, 1048.58, 1064.58, 1041.02, 1092.61, 1038.68, 1045.0, 1032.01, 1001.29, 1035.64, 1062.75, 1076.17, 1090.67, 1099.14, 1096.56, 1106.37, 1094.44, 1076.91, 1065.09, 1019.61, 1020.21, 1011.37, 1019.61, 1021.0, 1055.29, 1042.98, 1029.64, 1055.97, 1055.18, 1045.91, 1140.0, 1152.07, 1095.46, 1065.22, 1055.03, 1085.56, 1098.2, 1074.72, 1061.23, 1048.23], 'signals': ['BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [858.8, 863.44, 831.79, 817.82, 828.38, 830.15, 820.15, 784.06, 778.78, 791.28, 803.5, 801.95, 805.95, 809.96, 827.62, 832.05, 838.15, 819.03, 799.37, 804.06, 842.28, 856.44, 859.25, 862.25, 860.36, 901.78, 899.75, 903.82, 886.88, 905.64, 895.54, 896.05, 921.89, 937.61, 922.48, 930.74, 927.21, 922.84, 933.7, 922.48, 901.63, 919.72, 919.66, 899.31, 914.86, 933.24, 921.81, 932.37, 940.71, 941.75, 951.23, 964.71, 944.31, 942.21, 924.66, 977.81, 983.83, 992.36, 990.16, 992.1, 1003.95, 1021.06, 1048.58, 1064.58, 1041.02, 1092.61, 1038.68, 1045.0, 1032.01, 1001.29, 1035.64, 1062.75, 1076.17, 1090.67, 1099.14, 1096.56, 1106.37, 1094.44, 1076.91, 1065.09, 1019.61, 1020.21, 1011.37, 1019.61, 1021.0, 1055.29, 1042.98, 1029.64, 1055.97, 1055.18, 1045.91, 1140.0, 1152.07, 1095.46, 1065.22, 1055.03, 1085.56, 1098.2, 1074.72, 1061.23], 'signals': ['BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
     </row>
@@ -1507,7 +1507,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1515,50 +1515,50 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.353</v>
+        <v>0.323</v>
       </c>
       <c r="E18" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F18" t="n">
+        <v>60</v>
+      </c>
+      <c r="G18" t="n">
         <v>50</v>
       </c>
-      <c r="G18" t="n">
-        <v>40</v>
-      </c>
       <c r="H18" t="n">
-        <v>173</v>
+        <v>-24</v>
       </c>
       <c r="I18" t="n">
-        <v>3.5</v>
+        <v>-0.5</v>
       </c>
       <c r="J18" t="n">
-        <v>-19.8</v>
+        <v>-13.2</v>
       </c>
       <c r="K18" t="n">
-        <v>23.3</v>
+        <v>12.7</v>
       </c>
       <c r="L18" t="n">
         <v>5000</v>
       </c>
       <c r="M18" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="N18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [208.93, 205.71, 197.22, 199.79, 196.52, 198.63, 193.23, 195.53, 203.32, 210.23, 202.29, 202.91, 197.5, 200.62, 181.04, 181.1, 173.38, 161.14, 160.79, 174.61, 172.99, 171.46, 174.79, 175.18, 175.09, 169.02, 167.85, 174.53, 184.41, 195.9, 199.83, 206.33, 211.63, 195.95, 206.24, 197.93, 199.77, 196.68, 194.1, 181.73, 187.77, 191.25, 202.99, 197.75, 197.96, 192.96, 201.16, 216.6, 207.64, 201.8, 212.01, 195.43, 189.44, 193.45, 191.29, 193.56, 184.99, 180.01, 173.78, 182.25, 189.03, 182.61, 173.99, 163.22, 164.13, 152.4, 162.11, 155.5, 153.97, 160.43, 159.78, 169.62, 169.27, 164.92, 163.26, 164.84, 158.18, 150.11, 142.52, 149.06, 151.65, 146.19, 159.24, 165.48, 168.87, 163.51, 159.36, 158.44, 159.07, 157.37, 161.5, 167.21, 160.49, 157.12, 160.43, 175.85, 166.12, 161.16, 158.29, 167.49], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [182.36, 208.93, 205.71, 197.22, 199.79, 196.52, 198.63, 193.23, 195.53, 203.32, 210.23, 202.29, 202.91, 197.5, 200.62, 181.04, 181.1, 173.38, 161.14, 160.79, 174.61, 172.99, 171.46, 174.79, 175.18, 175.09, 169.02, 167.85, 174.53, 184.41, 195.9, 199.83, 206.33, 211.63, 195.95, 206.24, 197.93, 199.77, 196.68, 194.1, 181.73, 187.77, 191.25, 202.99, 197.75, 197.96, 192.96, 201.16, 216.6, 207.64, 201.8, 212.01, 195.43, 189.44, 193.45, 191.29, 193.56, 184.99, 180.01, 173.78, 182.25, 189.03, 182.61, 173.99, 163.22, 164.13, 152.4, 162.11, 155.5, 153.97, 160.43, 159.78, 169.62, 169.27, 164.92, 163.26, 164.84, 158.18, 150.11, 142.52, 149.06, 151.65, 146.19, 159.24, 165.48, 168.87, 163.51, 159.36, 158.44, 159.07, 157.37, 161.5, 167.21, 160.49, 157.12, 160.43, 175.85, 166.12, 161.16, 158.29], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
     </row>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.398</v>
+        <v>0.284</v>
       </c>
       <c r="E19" t="n">
         <v>55</v>
@@ -1586,19 +1586,19 @@
         <v>30</v>
       </c>
       <c r="G19" t="n">
-        <v>68.40000000000001</v>
+        <v>52.6</v>
       </c>
       <c r="H19" t="n">
-        <v>976</v>
+        <v>435</v>
       </c>
       <c r="I19" t="n">
-        <v>19.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>19.5</v>
+        <v>18.9</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>-10.2</v>
       </c>
       <c r="L19" t="n">
         <v>5000</v>
@@ -1607,20 +1607,20 @@
         <v>4</v>
       </c>
       <c r="N19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O19" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="P19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q19" t="n">
-        <v>14</v>
+        <v>6.5</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [1001.85, 981.57, 988.63, 1006.66, 999.63, 998.12, 975.57, 983.39, 987.42, 928.75, 916.47, 915.92, 905.14, 908.99, 901.47, 914.74, 895.46, 876.73, 885.11, 918.19, 952.88, 933.97, 925.47, 929.49, 951.66, 953.55, 937.86, 927.95, 920.91, 903.47, 902.44, 925.44, 918.32, 901.47, 919.9, 916.07, 882.44, 866.78, 872.5, 849.75, 932.99, 961.67, 966.27, 987.17, 985.35, 973.28, 946.82, 965.33, 988.17, 1014.0, 1004.97, 1004.92, 988.09, 1021.41, 1018.87, 1041.65, 1065.0, 1064.74, 1082.92, 1126.8, 1105.0, 1082.2, 1064.15, 1078.78, 1125.27, 1131.42, 1149.15, 1144.68, 1136.37, 1160.95, 1133.0, 1129.35, 1122.5, 1112.0, 1098.57, 1102.08, 1107.08, 1117.26, 1127.69, 1208.12, 1229.93, 1199.43, 1191.74, 1213.91, 1200.06, 1235.56, 1215.83, 1216.95, 1188.58, 1181.87, 1152.54, 1156.63, 1169.17, 1179.11, 1146.9, 1175.41, 1163.01, 1185.87, 1196.03, 1197.53], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [1006.0, 1001.85, 981.57, 988.63, 1006.66, 999.63, 998.12, 975.57, 983.39, 987.42, 928.75, 916.47, 915.92, 905.14, 908.99, 901.47, 914.74, 895.46, 876.73, 885.11, 918.19, 952.88, 933.97, 925.47, 929.49, 951.66, 953.55, 937.86, 927.95, 920.91, 903.47, 902.44, 925.44, 918.32, 901.47, 919.9, 916.07, 882.44, 866.78, 872.5, 849.75, 932.99, 961.67, 966.27, 987.17, 985.35, 973.28, 946.82, 965.33, 988.17, 1014.0, 1004.97, 1004.92, 988.09, 1021.41, 1018.87, 1041.65, 1065.0, 1064.74, 1082.92, 1126.8, 1105.0, 1082.2, 1064.15, 1078.78, 1125.27, 1131.42, 1149.15, 1144.68, 1136.37, 1160.95, 1133.0, 1129.35, 1122.5, 1112.0, 1098.57, 1102.08, 1107.08, 1117.26, 1127.69, 1208.12, 1229.93, 1199.43, 1191.74, 1213.91, 1200.06, 1235.56, 1215.83, 1216.95, 1188.58, 1181.87, 1152.54, 1156.63, 1169.17, 1179.11, 1146.9, 1175.41, 1163.01, 1185.87, 1196.03], 'signals': ['FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
     </row>
@@ -1631,36 +1631,36 @@
         </is>
       </c>
       <c r="B20" t="n">
+        <v>56</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UP  </t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0.5639999999999999</v>
+      </c>
+      <c r="E20" t="n">
         <v>58</v>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UP  </t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>0.555</v>
-      </c>
-      <c r="E20" t="n">
-        <v>56</v>
-      </c>
       <c r="F20" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G20" t="n">
-        <v>45</v>
+        <v>52.6</v>
       </c>
       <c r="H20" t="n">
-        <v>-27</v>
+        <v>169</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.5</v>
+        <v>3.4</v>
       </c>
       <c r="J20" t="n">
-        <v>-7</v>
+        <v>-6.5</v>
       </c>
       <c r="K20" t="n">
-        <v>6.5</v>
+        <v>9.9</v>
       </c>
       <c r="L20" t="n">
         <v>5000</v>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [227.31, 222.06, 231.11, 225.0, 217.76, 214.1, 204.76, 209.89, 213.47, 210.82, 205.99, 201.18, 195.12, 198.41, 196.42, 199.61, 194.36, 190.52, 189.21, 199.03, 207.32, 208.22, 212.3, 210.0, 217.8, 220.06, 217.63, 222.14, 223.77, 223.93, 218.88, 223.38, 225.08, 219.16, 231.28, 234.15, 232.44, 231.33, 230.72, 224.11, 229.03, 227.38, 221.3, 224.38, 229.93, 231.03, 237.36, 238.21, 236.87, 240.6, 229.21, 220.49, 220.61, 215.01, 222.2, 219.61, 219.02, 218.9, 224.3, 228.78, 231.15, 224.3, 217.7, 210.58, 217.42, 215.45, 215.92, 214.51, 209.0, 221.63, 219.05, 228.95, 227.49, 225.63, 222.72, 220.83, 216.71, 220.25, 218.12, 217.25, 214.69, 216.47, 218.58, 226.49, 234.54, 231.68, 224.95, 223.11, 222.28, 215.51, 217.11, 218.12, 214.34, 214.03, 209.48, 204.8, 208.65, 209.23, 209.52, 211.5], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [224.12, 227.31, 222.06, 231.11, 225.0, 217.76, 214.1, 204.76, 209.89, 213.47, 210.82, 205.99, 201.18, 195.12, 198.41, 196.42, 199.61, 194.36, 190.52, 189.21, 199.03, 207.32, 208.22, 212.3, 210.0, 217.8, 220.06, 217.63, 222.14, 223.77, 223.93, 218.88, 223.38, 225.08, 219.16, 231.28, 234.15, 232.44, 231.33, 230.72, 224.11, 229.03, 227.38, 221.3, 224.38, 229.93, 231.03, 237.36, 238.21, 236.87, 240.6, 229.21, 220.49, 220.61, 215.01, 222.2, 219.61, 219.02, 218.9, 224.3, 228.78, 231.15, 224.3, 217.7, 210.58, 217.42, 215.45, 215.92, 214.51, 209.0, 221.63, 219.05, 228.95, 227.49, 225.63, 222.72, 220.83, 216.71, 220.25, 218.12, 217.25, 214.69, 216.47, 218.58, 226.49, 234.54, 231.68, 224.95, 223.11, 222.28, 215.51, 217.11, 218.12, 214.34, 214.03, 209.48, 204.8, 208.65, 209.23, 209.52], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
     </row>
@@ -1693,58 +1693,58 @@
         </is>
       </c>
       <c r="B21" t="n">
+        <v>65</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UP  </t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0.538</v>
+      </c>
+      <c r="E21" t="n">
         <v>67</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UP  </t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>0.578</v>
-      </c>
-      <c r="E21" t="n">
-        <v>66</v>
       </c>
       <c r="F21" t="n">
         <v>50</v>
       </c>
       <c r="G21" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H21" t="n">
-        <v>-415</v>
+        <v>599</v>
       </c>
       <c r="I21" t="n">
-        <v>-8.300000000000001</v>
+        <v>12</v>
       </c>
       <c r="J21" t="n">
-        <v>-11.1</v>
+        <v>-13.6</v>
       </c>
       <c r="K21" t="n">
-        <v>2.8</v>
+        <v>25.6</v>
       </c>
       <c r="L21" t="n">
         <v>5000</v>
       </c>
       <c r="M21" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="N21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O21" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="P21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [76.65, 75.44, 75.13, 73.84, 72.36, 74.97, 72.97, 73.33, 74.66, 77.79, 76.66, 75.34, 73.89, 75.12, 72.34, 73.08, 70.55, 69.18, 69.91, 71.93, 71.71, 71.84, 72.17, 71.73, 72.38, 71.81, 70.48, 72.34, 72.91, 77.28, 76.48, 77.12, 77.49, 77.26, 75.58, 74.7, 74.64, 76.27, 74.11, 74.47, 74.61, 75.12, 73.93, 72.95, 79.17, 76.73, 75.45, 76.15, 76.36, 74.7, 74.69, 75.09, 75.08, 74.09, 74.6, 73.61, 71.82, 70.12, 70.73, 70.92, 70.4, 73.77, 71.62, 71.69, 72.21, 70.71, 70.06, 70.38, 68.61, 69.55, 68.85, 72.85, 73.25, 70.91, 71.64, 71.43, 69.67, 73.85, 72.25, 76.2, 75.5, 72.16, 72.66, 74.43, 72.42, 74.33, 73.6, 74.35, 74.54, 74.26, 72.08, 72.67, 74.04, 72.46, 72.17, 71.55, 70.33, 68.91, 65.94, 68.18], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'SELL', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [76.36, 76.65, 75.44, 75.13, 73.84, 72.36, 74.97, 72.97, 73.33, 74.66, 77.79, 76.66, 75.34, 73.89, 75.12, 72.34, 73.08, 70.55, 69.18, 69.91, 71.93, 71.71, 71.84, 72.17, 71.73, 72.38, 71.81, 70.48, 72.34, 72.91, 77.28, 76.48, 77.12, 77.49, 77.26, 75.58, 74.7, 74.64, 76.27, 74.11, 74.47, 74.61, 75.12, 73.93, 72.95, 79.17, 76.73, 75.45, 76.15, 76.36, 74.7, 74.69, 75.09, 75.08, 74.09, 74.6, 73.61, 71.82, 70.12, 70.73, 70.92, 70.4, 73.77, 71.62, 71.69, 72.21, 70.71, 70.06, 70.38, 68.61, 69.55, 68.85, 72.85, 73.25, 70.91, 71.64, 71.43, 69.67, 73.85, 72.25, 76.2, 75.5, 72.16, 72.66, 74.43, 72.42, 74.33, 73.6, 74.35, 74.54, 74.26, 72.08, 72.67, 74.04, 72.46, 72.17, 71.55, 70.33, 68.91, 65.94], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'SELL', 'BUY', 'SELL', 'BUY', 'SELL', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
     </row>

--- a/demo_results.xlsx
+++ b/demo_results.xlsx
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -523,28 +523,28 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.236</v>
+        <v>0.179</v>
       </c>
       <c r="E2" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="F2" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="G2" t="n">
         <v>65</v>
       </c>
       <c r="H2" t="n">
-        <v>872</v>
+        <v>846</v>
       </c>
       <c r="I2" t="n">
-        <v>17.4</v>
+        <v>16.9</v>
       </c>
       <c r="J2" t="n">
         <v>26.4</v>
       </c>
       <c r="K2" t="n">
-        <v>-9</v>
+        <v>-9.5</v>
       </c>
       <c r="L2" t="n">
         <v>5000</v>
@@ -556,17 +556,17 @@
         <v>4</v>
       </c>
       <c r="O2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P2" t="n">
         <v>4</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [263.51, 262.28, 260.05, 257.22, 259.64, 260.59, 260.57, 255.52, 249.89, 252.59, 254.0, 249.71, 248.73, 247.76, 251.26, 251.41, 252.39, 252.66, 248.57, 246.4, 253.56, 255.39, 255.68, 258.62, 253.27, 258.66, 260.25, 260.24, 258.96, 258.59, 266.18, 263.16, 269.98, 272.8, 265.93, 272.92, 273.18, 270.81, 267.36, 270.46, 269.92, 271.1, 279.88, 276.58, 283.92, 287.25, 287.18, 293.05, 292.68, 294.8, 298.87, 298.21, 300.23, 297.84, 298.97, 302.25, 304.99, 308.82, 308.33, 310.85, 312.51, 312.06, 306.31, 315.2, 310.26, 311.23, 307.34, 301.54, 290.55, 291.58, 295.63, 291.13, 296.42, 299.24, 295.95, 298.01, 297.01, 294.3, 293.08, 275.15, 283.78, 281.74, 289.36, 294.38, 308.63, 312.66, 310.66, 313.39, 316.22, 315.32, 317.31, 314.86, 327.5, 333.26, 333.74, 326.59, 327.74, 325.89, 321.66, 333.02], 'signals': ['BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [263.51, 262.28, 260.05, 257.22, 259.64, 260.59, 260.57, 255.52, 249.89, 252.59, 254.0, 249.71, 248.73, 247.76, 251.26, 251.41, 252.39, 252.66, 248.57, 246.4, 253.56, 255.39, 255.68, 258.62, 253.27, 258.66, 260.25, 260.24, 258.96, 258.59, 266.18, 263.16, 269.98, 272.8, 265.93, 272.92, 273.18, 270.81, 267.36, 270.46, 269.92, 271.1, 279.88, 276.58, 283.92, 287.25, 287.18, 293.05, 292.68, 294.8, 298.87, 298.21, 300.23, 297.84, 298.97, 302.25, 304.99, 308.82, 308.33, 310.85, 312.51, 312.06, 306.31, 315.2, 310.26, 311.23, 307.34, 301.54, 290.55, 291.58, 295.63, 291.13, 296.42, 299.24, 295.95, 298.01, 297.01, 294.3, 293.08, 275.15, 283.78, 281.74, 289.36, 294.38, 308.63, 312.66, 310.66, 313.39, 316.22, 315.32, 317.31, 314.86, 327.5, 333.26, 333.74, 326.59, 327.74, 325.89, 321.66, 333.02], 'signals': ['BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL']}</t>
         </is>
       </c>
     </row>
@@ -585,16 +585,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.033</v>
+        <v>0.036</v>
       </c>
       <c r="E3" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="G3" t="n">
-        <v>75</v>
+        <v>66.7</v>
       </c>
       <c r="H3" t="n">
         <v>198</v>
@@ -628,7 +628,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [403.06, 404.32, 409.79, 408.08, 408.53, 404.88, 404.0, 400.99, 394.7, 399.09, 398.55, 390.94, 388.18, 381.04, 382.17, 371.93, 370.24, 365.18, 356.0, 358.18, 369.37, 368.57, 372.65, 372.07, 371.49, 373.52, 372.26, 370.07, 383.54, 392.26, 410.33, 419.35, 421.88, 417.17, 423.24, 431.98, 414.85, 423.7, 423.9, 428.32, 423.54, 406.9, 413.54, 412.73, 410.49, 413.07, 419.86, 414.22, 411.77, 406.89, 404.33, 408.55, 421.01, 422.62, 416.52, 420.15, 419.09, 418.57, 416.03, 412.67, 426.99, 450.24, 460.52, 441.31, 427.34, 428.05, 416.67, 411.74, 403.41, 397.36, 390.34, 390.74, 399.76, 393.83, 378.91, 379.4, 367.34, 373.94, 365.46, 352.83, 372.97, 368.57, 373.02, 384.28, 390.49, 386.74, 388.84, 383.34, 384.36, 385.1, 390.99, 384.93, 395.63, 401.1, 393.82, 402.29, 397.75, 390.34, 381.58, 381.7], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [403.06, 404.32, 409.79, 408.08, 408.53, 404.88, 404.0, 400.99, 394.7, 399.09, 398.55, 390.94, 388.18, 381.04, 382.17, 371.93, 370.24, 365.18, 356.0, 358.18, 369.37, 368.57, 372.65, 372.07, 371.49, 373.52, 372.26, 370.07, 383.54, 392.26, 410.33, 419.35, 421.88, 417.17, 423.24, 431.98, 414.85, 423.7, 423.9, 428.32, 423.54, 406.9, 413.54, 412.73, 410.49, 413.07, 419.86, 414.22, 411.77, 406.89, 404.33, 408.55, 421.01, 422.62, 416.52, 420.15, 419.09, 418.57, 416.03, 412.67, 426.99, 450.24, 460.52, 441.31, 427.34, 428.05, 416.67, 411.74, 403.41, 397.36, 390.34, 390.74, 399.76, 393.83, 378.91, 379.4, 367.34, 373.94, 365.46, 352.83, 372.97, 368.57, 373.02, 384.28, 390.49, 386.74, 388.84, 383.34, 384.36, 385.1, 390.99, 384.93, 395.63, 401.1, 393.82, 402.29, 397.75, 390.34, 381.58, 381.7], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
     </row>
@@ -643,14 +643,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">UP  </t>
+          <t>DOWN</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.505</v>
+        <v>0.496</v>
       </c>
       <c r="E4" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F4" t="n">
         <v>80</v>
@@ -659,16 +659,16 @@
         <v>55</v>
       </c>
       <c r="H4" t="n">
-        <v>448</v>
+        <v>55</v>
       </c>
       <c r="I4" t="n">
-        <v>9</v>
+        <v>1.1</v>
       </c>
       <c r="J4" t="n">
         <v>5.5</v>
       </c>
       <c r="K4" t="n">
-        <v>3.5</v>
+        <v>-4.4</v>
       </c>
       <c r="L4" t="n">
         <v>5000</v>
@@ -677,20 +677,20 @@
         <v>15</v>
       </c>
       <c r="N4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
         <v>1</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [303.19, 302.74, 300.49, 298.13, 306.18, 306.86, 308.52, 303.37, 302.1, 305.38, 310.73, 307.51, 306.95, 300.82, 301.88, 290.27, 290.76, 280.75, 274.18, 273.34, 287.39, 297.21, 295.59, 299.81, 305.28, 317.13, 318.3, 317.05, 321.12, 332.71, 336.92, 335.82, 341.48, 337.22, 332.09, 339.12, 338.69, 344.19, 350.13, 349.57, 349.73, 384.57, 385.46, 383.02, 388.2, 397.8, 397.75, 400.56, 388.41, 387.12, 402.38, 400.83, 396.54, 396.7, 387.43, 388.68, 387.43, 382.74, 388.65, 388.6, 389.9, 380.11, 376.15, 361.63, 358.78, 371.97, 368.31, 363.31, 364.26, 356.38, 357.77, 359.68, 369.35, 373.25, 363.79, 368.03, 349.68, 346.13, 345.29, 343.71, 337.39, 353.65, 357.37, 361.21, 359.91, 366.46, 367.03, 361.92, 358.89, 357.18, 352.51, 359.51, 370.92, 354.46, 346.77, 351.99, 347.15, 342.09, 317.69, 319.74], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [303.19, 302.74, 300.49, 298.13, 306.18, 306.86, 308.52, 303.37, 302.1, 305.38, 310.73, 307.51, 306.95, 300.82, 301.88, 290.27, 290.76, 280.75, 274.18, 273.34, 287.39, 297.21, 295.59, 299.81, 305.28, 317.13, 318.3, 317.05, 321.12, 332.71, 336.92, 335.82, 341.48, 337.22, 332.09, 339.12, 338.69, 344.19, 350.13, 349.57, 349.73, 384.57, 385.46, 383.02, 388.2, 397.8, 397.75, 400.56, 388.41, 387.12, 402.38, 400.83, 396.54, 396.7, 387.43, 388.68, 387.43, 382.74, 388.65, 388.6, 389.9, 380.11, 376.15, 361.63, 358.78, 371.97, 368.31, 363.31, 364.26, 356.38, 357.77, 359.68, 369.35, 373.25, 363.79, 368.03, 349.68, 346.13, 345.29, 343.71, 337.39, 353.65, 357.37, 361.21, 359.91, 366.46, 367.03, 361.92, 358.89, 357.18, 352.51, 359.51, 370.92, 354.46, 346.77, 351.99, 347.15, 342.09, 317.69, 319.74], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
     </row>
@@ -701,7 +701,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.732</v>
       </c>
       <c r="E5" t="n">
         <v>59</v>
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.627</v>
+        <v>0.62</v>
       </c>
       <c r="E6" t="n">
         <v>56</v>
@@ -780,7 +780,7 @@
         <v>60</v>
       </c>
       <c r="G6" t="n">
-        <v>38.5</v>
+        <v>35.7</v>
       </c>
       <c r="H6" t="n">
         <v>416</v>
@@ -814,7 +814,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [653.91, 666.54, 659.39, 643.71, 646.24, 652.91, 653.69, 637.04, 612.62, 626.87, 622.08, 615.11, 606.14, 593.11, 603.5, 592.37, 594.34, 547.03, 525.23, 535.88, 571.6, 578.69, 573.93, 572.49, 574.52, 611.85, 627.81, 629.28, 633.94, 661.88, 670.96, 676.24, 687.91, 670.29, 668.22, 674.1, 658.54, 674.4, 677.99, 670.72, 668.5, 611.34, 608.19, 609.84, 604.4, 612.31, 616.24, 609.07, 598.31, 602.44, 616.06, 617.86, 613.66, 610.64, 602.05, 604.5, 606.82, 609.69, 611.77, 634.67, 634.7, 631.92, 599.91, 597.08, 622.4, 626.99, 592.45, 584.85, 584.05, 570.45, 567.9, 566.45, 593.48, 600.21, 567.58, 577.22, 563.85, 562.2, 557.67, 542.87, 550.25, 562.6, 563.29, 612.91, 582.9, 600.29, 615.58, 603.12, 631.48, 669.21, 656.73, 661.04, 681.31, 664.54, 646.01, 645.85, 643.81, 627.17, 606.1, 595.19], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT']}</t>
+          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [653.91, 666.54, 659.39, 643.71, 646.24, 652.91, 653.69, 637.04, 612.62, 626.87, 622.08, 615.11, 606.14, 593.11, 603.5, 592.37, 594.34, 547.03, 525.23, 535.88, 571.6, 578.69, 573.93, 572.49, 574.52, 611.85, 627.81, 629.28, 633.94, 661.88, 670.96, 676.24, 687.91, 670.29, 668.22, 674.1, 658.54, 674.4, 677.99, 670.72, 668.5, 611.34, 608.19, 609.84, 604.4, 612.31, 616.24, 609.07, 598.31, 602.44, 616.06, 617.86, 613.66, 610.64, 602.05, 604.5, 606.82, 609.69, 611.77, 634.67, 634.7, 631.92, 599.91, 597.08, 622.4, 626.99, 592.45, 584.85, 584.05, 570.45, 567.9, 566.45, 593.48, 600.21, 567.58, 577.22, 563.85, 562.2, 557.67, 542.87, 550.25, 562.6, 563.29, 612.91, 582.9, 600.29, 615.58, 603.12, 631.48, 669.21, 656.73, 661.04, 681.31, 664.54, 646.01, 645.85, 643.81, 627.17, 606.1, 595.19], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.424</v>
+        <v>0.48</v>
       </c>
       <c r="E7" t="n">
         <v>58</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [179.83, 182.82, 183.12, 177.6, 182.43, 184.54, 185.81, 182.93, 180.04, 183.01, 181.72, 180.19, 178.35, 172.5, 175.44, 175.0, 178.47, 171.04, 167.32, 164.98, 174.2, 175.55, 177.18, 177.43, 177.89, 181.87, 183.7, 188.41, 189.09, 196.28, 198.64, 198.12, 201.45, 201.82, 199.65, 202.26, 199.41, 208.03, 216.36, 212.92, 209.01, 199.34, 198.22, 198.25, 196.27, 207.59, 211.25, 214.95, 219.18, 220.52, 225.57, 235.47, 225.06, 222.06, 220.35, 223.21, 219.25, 215.08, 214.61, 212.35, 214.0, 210.89, 224.1, 222.56, 214.5, 218.66, 205.1, 208.64, 208.19, 200.42, 204.87, 205.19, 212.45, 207.41, 204.65, 210.69, 208.65, 200.04, 199.0, 195.74, 192.53, 194.97, 200.09, 197.58, 194.83, 195.55, 196.93, 204.12, 202.78, 210.96, 203.53, 211.8, 212.5, 207.4, 202.81, 203.28, 207.29, 212.06, 208.76, 206.84], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [179.83, 182.82, 183.12, 177.6, 182.43, 184.54, 185.81, 182.93, 180.04, 183.01, 181.72, 180.19, 178.35, 172.5, 175.44, 175.0, 178.47, 171.04, 167.32, 164.98, 174.2, 175.55, 177.18, 177.43, 177.89, 181.87, 183.7, 188.41, 189.09, 196.28, 198.64, 198.12, 201.45, 201.82, 199.65, 202.26, 199.41, 208.03, 216.36, 212.92, 209.01, 199.34, 198.22, 198.25, 196.27, 207.59, 211.25, 214.95, 219.18, 220.52, 225.57, 235.47, 225.06, 222.06, 220.35, 223.21, 219.25, 215.08, 214.61, 212.35, 214.0, 210.89, 224.1, 222.56, 214.5, 218.66, 205.1, 208.64, 208.19, 200.42, 204.87, 205.19, 212.45, 207.41, 204.65, 210.69, 208.65, 200.04, 199.0, 195.74, 192.53, 194.97, 200.09, 197.58, 194.83, 195.55, 196.93, 204.12, 202.78, 210.96, 203.53, 211.8, 212.5, 207.4, 202.81, 203.28, 207.29, 212.06, 208.76, 206.84], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
     </row>
@@ -895,10 +895,10 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.434</v>
+        <v>0.449</v>
       </c>
       <c r="E8" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F8" t="n">
         <v>70</v>
@@ -938,7 +938,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [190.95, 202.07, 199.45, 192.43, 202.68, 203.23, 204.83, 197.74, 193.39, 196.58, 196.31, 199.46, 205.27, 201.33, 202.68, 205.37, 220.27, 203.77, 201.99, 196.04, 203.43, 210.21, 217.5, 220.18, 221.53, 231.82, 236.64, 245.04, 246.83, 255.07, 258.12, 278.26, 278.39, 274.95, 284.49, 303.46, 305.33, 347.81, 334.63, 323.21, 337.11, 354.49, 360.54, 341.54, 355.26, 421.39, 408.46, 455.19, 458.79, 448.29, 445.5, 449.7, 424.1, 420.99, 414.05, 447.58, 449.59, 467.51, 503.89, 495.54, 518.09, 516.1, 510.13, 521.54, 542.52, 523.2, 466.38, 490.33, 475.51, 452.4, 488.45, 511.57, 547.26, 507.29, 512.48, 537.37, 551.63, 519.85, 519.74, 532.57, 521.58, 539.49, 580.91, 540.88, 517.82, 552.05, 516.11, 517.41, 546.72, 557.89, 534.39, 548.13, 529.14, 500.94, 495.76, 503.57, 544.43, 552.33, 539.69, 521.95], 'signals': ['BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'BUY', 'SELL', 'BUY', 'SELL', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [190.95, 202.07, 199.45, 192.43, 202.68, 203.23, 204.83, 197.74, 193.39, 196.58, 196.31, 199.46, 205.27, 201.33, 202.68, 205.37, 220.27, 203.77, 201.99, 196.04, 203.43, 210.21, 217.5, 220.18, 221.53, 231.82, 236.64, 245.04, 246.83, 255.07, 258.12, 278.26, 278.39, 274.95, 284.49, 303.46, 305.33, 347.81, 334.63, 323.21, 337.11, 354.49, 360.54, 341.54, 355.26, 421.39, 408.46, 455.19, 458.79, 448.29, 445.5, 449.7, 424.1, 420.99, 414.05, 447.58, 449.59, 467.51, 503.89, 495.54, 518.09, 516.1, 510.13, 521.54, 542.52, 523.2, 466.38, 490.33, 475.51, 452.4, 488.45, 511.57, 547.26, 507.29, 512.48, 537.37, 551.63, 519.85, 519.74, 532.57, 521.58, 539.49, 580.91, 540.88, 517.82, 552.05, 516.11, 517.41, 546.72, 557.89, 534.39, 548.13, 529.14, 500.94, 495.76, 503.57, 544.43, 552.33, 539.69, 521.95], 'signals': ['BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.639</v>
+        <v>0.655</v>
       </c>
       <c r="E9" t="n">
         <v>52</v>
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1019,16 +1019,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.443</v>
+        <v>0.456</v>
       </c>
       <c r="E10" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F10" t="n">
         <v>40</v>
       </c>
       <c r="G10" t="n">
-        <v>57.9</v>
+        <v>33.3</v>
       </c>
       <c r="H10" t="n">
         <v>3327</v>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [379.46, 400.54, 396.82, 370.09, 389.1, 402.88, 418.45, 405.12, 425.89, 441.55, 461.43, 461.47, 444.02, 422.66, 404.12, 395.3, 381.87, 355.26, 357.02, 321.75, 337.79, 367.79, 366.18, 377.7, 377.52, 406.67, 421.45, 420.53, 426.49, 465.59, 456.16, 457.16, 455.0, 448.35, 449.31, 487.41, 481.65, 496.64, 524.48, 504.21, 518.38, 517.08, 542.13, 576.36, 640.1, 666.49, 646.53, 746.7, 795.21, 766.46, 803.51, 775.89, 724.55, 681.44, 698.63, 731.88, 761.98, 750.88, 895.74, 928.27, 923.38, 970.85, 1035.34, 1063.94, 1079.4, 995.85, 863.88, 949.13, 935.75, 891.74, 995.72, 981.46, 1087.82, 1020.6, 1043.03, 1133.82, 1211.19, 1051.61, 1048.35, 1213.37, 1132.16, 1145.1, 1154.11, 1032.12, 975.41, 984.75, 938.38, 948.8, 991.64, 979.3, 937.0, 983.12, 904.28, 853.2, 848.95, 865.46, 970.82, 959.48, 990.21, 920.95], 'signals': ['FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [379.46, 400.54, 396.82, 370.09, 389.1, 402.88, 418.45, 405.12, 425.89, 441.55, 461.43, 461.47, 444.02, 422.66, 404.12, 395.3, 381.87, 355.26, 357.02, 321.75, 337.79, 367.79, 366.18, 377.7, 377.52, 406.67, 421.45, 420.53, 426.49, 465.59, 456.16, 457.16, 455.0, 448.35, 449.31, 487.41, 481.65, 496.64, 524.48, 504.21, 518.38, 517.08, 542.13, 576.36, 640.1, 666.49, 646.53, 746.7, 795.21, 766.46, 803.51, 775.89, 724.55, 681.44, 698.63, 731.88, 761.98, 750.88, 895.74, 928.27, 923.38, 970.85, 1035.34, 1063.94, 1079.4, 995.85, 863.88, 949.13, 935.75, 891.74, 995.72, 981.46, 1087.82, 1020.6, 1043.03, 1133.82, 1211.19, 1051.61, 1048.35, 1213.37, 1132.16, 1145.1, 1154.11, 1032.12, 975.41, 984.75, 938.38, 948.8, 991.64, 979.3, 937.0, 983.12, 904.28, 853.2, 848.95, 865.46, 970.82, 959.48, 990.21, 920.95], 'signals': ['FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
     </row>
@@ -1073,36 +1073,36 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>DOWN</t>
+          <t xml:space="preserve">UP  </t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.419</v>
+        <v>0.588</v>
       </c>
       <c r="E11" t="n">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>-375</v>
+        <v>-949</v>
       </c>
       <c r="I11" t="n">
-        <v>-7.5</v>
+        <v>-19</v>
       </c>
       <c r="J11" t="n">
         <v>-20.2</v>
       </c>
       <c r="K11" t="n">
-        <v>12.7</v>
+        <v>1.2</v>
       </c>
       <c r="L11" t="n">
         <v>5000</v>
@@ -1111,20 +1111,20 @@
         <v>15</v>
       </c>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="P11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>3.2</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [392.43, 405.94, 405.55, 396.73, 398.68, 399.24, 407.82, 395.01, 391.2, 395.56, 399.27, 392.78, 380.3, 367.96, 380.85, 383.03, 385.95, 372.11, 361.83, 355.28, 371.75, 381.26, 360.59, 352.82, 346.65, 343.25, 345.62, 348.95, 352.42, 364.2, 391.95, 388.9, 400.62, 392.5, 386.42, 387.51, 373.72, 376.3, 378.67, 376.02, 372.8, 381.63, 390.82, 392.51, 389.37, 398.73, 411.79, 428.35, 445.0, 433.45, 445.27, 443.3, 422.24, 409.99, 404.11, 417.26, 417.85, 426.01, 433.59, 440.36, 442.1, 435.79, 415.88, 423.74, 423.7, 418.45, 391.0, 408.95, 396.68, 381.59, 399.15, 406.43, 411.15, 404.66, 396.38, 400.49, 405.05, 381.61, 375.53, 375.12, 379.71, 411.84, 420.6, 425.3, 393.45, 419.77, 402.9, 394.06, 406.55, 407.76, 394.76, 396.18, 394.46, 391.06, 380.84, 369.57, 378.93, 374.01, 319.69, 313.03], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [392.43, 405.94, 405.55, 396.73, 398.68, 399.24, 407.82, 395.01, 391.2, 395.56, 399.27, 392.78, 380.3, 367.96, 380.85, 383.03, 385.95, 372.11, 361.83, 355.28, 371.75, 381.26, 360.59, 352.82, 346.65, 343.25, 345.62, 348.95, 352.42, 364.2, 391.95, 388.9, 400.62, 392.5, 386.42, 387.51, 373.72, 376.3, 378.67, 376.02, 372.8, 381.63, 390.82, 392.51, 389.37, 398.73, 411.79, 428.35, 445.0, 433.45, 445.27, 443.3, 422.24, 409.99, 404.11, 417.26, 417.85, 426.01, 433.59, 440.36, 442.1, 435.79, 415.88, 423.74, 423.7, 418.45, 391.0, 408.95, 396.68, 381.59, 399.15, 406.43, 411.15, 404.66, 396.38, 400.49, 405.05, 381.61, 375.53, 375.12, 379.71, 411.84, 420.6, 425.3, 393.45, 419.77, 402.9, 394.06, 406.55, 407.76, 394.76, 396.18, 394.46, 391.06, 380.84, 369.57, 378.93, 374.01, 319.69, 313.03], 'signals': ['BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
     </row>
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.349</v>
+        <v>0.315</v>
       </c>
       <c r="E12" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F12" t="n">
         <v>70</v>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [97.7, 98.66, 99.17, 99.02, 98.32, 96.94, 94.89, 94.31, 95.31, 95.2, 94.36, 94.7, 91.74, 91.82, 93.38, 90.92, 92.28, 93.32, 93.43, 92.97, 96.15, 95.55, 98.66, 98.93, 98.82, 99.39, 102.05, 103.01, 103.16, 106.28, 107.71, 107.79, 97.31, 94.83, 92.58, 93.24, 92.82, 92.44, 91.37, 92.27, 92.12, 93.61, 92.06, 91.02, 87.89, 88.27, 88.25, 87.49, 85.45, 87.66, 87.56, 86.94, 87.02, 89.65, 89.33, 88.09, 89.3, 88.6, 87.68, 87.35, 86.36, 86.02, 85.85, 83.33, 81.52, 81.56, 82.18, 82.64, 81.41, 82.0, 81.27, 80.34, 81.67, 78.72, 76.96, 77.38, 72.88, 72.82, 71.84, 70.9, 73.81, 73.78, 71.4, 74.19, 77.65, 76.02, 76.18, 75.59, 75.47, 73.37, 73.83, 73.53, 73.68, 74.35, 68.95, 67.6, 68.67, 68.53, 68.89, 70.09], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [97.7, 98.66, 99.17, 99.02, 98.32, 96.94, 94.89, 94.31, 95.31, 95.2, 94.36, 94.7, 91.74, 91.82, 93.38, 90.92, 92.28, 93.32, 93.43, 92.97, 96.15, 95.55, 98.66, 98.93, 98.82, 99.39, 102.05, 103.01, 103.16, 106.28, 107.71, 107.79, 97.31, 94.83, 92.58, 93.24, 92.82, 92.44, 91.37, 92.27, 92.12, 93.61, 92.06, 91.02, 87.89, 88.27, 88.25, 87.49, 85.45, 87.66, 87.56, 86.94, 87.02, 89.65, 89.33, 88.09, 89.3, 88.6, 87.68, 87.35, 86.36, 86.02, 85.85, 83.33, 81.52, 81.56, 82.18, 82.64, 81.41, 82.0, 81.27, 80.34, 81.67, 78.72, 76.96, 77.38, 72.88, 72.82, 71.84, 70.9, 73.81, 73.78, 71.4, 74.19, 77.65, 76.02, 76.18, 75.59, 75.47, 73.37, 73.83, 73.53, 73.68, 74.35, 68.95, 67.6, 68.67, 68.53, 68.89, 70.09], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
     </row>
@@ -1197,36 +1197,36 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>DOWN</t>
+          <t xml:space="preserve">UP  </t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.458</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F13" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G13" t="n">
         <v>40</v>
       </c>
       <c r="H13" t="n">
-        <v>-652</v>
+        <v>446</v>
       </c>
       <c r="I13" t="n">
-        <v>-13</v>
+        <v>8.9</v>
       </c>
       <c r="J13" t="n">
         <v>-16.5</v>
       </c>
       <c r="K13" t="n">
-        <v>3.5</v>
+        <v>25.4</v>
       </c>
       <c r="L13" t="n">
         <v>5000</v>
@@ -1238,17 +1238,17 @@
         <v>3</v>
       </c>
       <c r="O13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P13" t="n">
         <v>3</v>
       </c>
       <c r="Q13" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [147.22, 153.19, 152.67, 157.16, 156.43, 151.14, 151.6, 153.5, 150.95, 152.72, 155.08, 152.77, 155.68, 150.68, 160.84, 154.78, 154.96, 147.56, 143.06, 137.55, 146.28, 146.49, 148.46, 147.93, 150.07, 140.76, 130.49, 128.06, 132.37, 135.7, 142.15, 142.76, 146.39, 145.89, 145.97, 152.62, 141.57, 143.09, 143.1, 141.18, 137.97, 139.11, 144.07, 146.03, 135.91, 133.79, 137.05, 137.8, 136.89, 136.0, 130.05, 133.73, 133.99, 135.14, 135.26, 137.15, 137.41, 136.88, 136.6, 132.51, 143.34, 156.54, 160.65, 152.17, 142.2, 141.7, 135.53, 136.47, 132.07, 130.21, 131.08, 127.99, 134.71, 133.25, 130.63, 128.47, 119.5, 116.7, 113.5, 107.27, 112.93, 115.7, 116.67, 125.73, 129.3, 132.54, 134.37, 132.22, 129.04, 126.79, 130.04, 133.72, 133.76, 134.44, 132.38, 134.85, 132.66, 124.57, 123.37, 122.92], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [147.22, 153.19, 152.67, 157.16, 156.43, 151.14, 151.6, 153.5, 150.95, 152.72, 155.08, 152.77, 155.68, 150.68, 160.84, 154.78, 154.96, 147.56, 143.06, 137.55, 146.28, 146.49, 148.46, 147.93, 150.07, 140.76, 130.49, 128.06, 132.37, 135.7, 142.15, 142.76, 146.39, 145.89, 145.97, 152.62, 141.57, 143.09, 143.1, 141.18, 137.97, 139.11, 144.07, 146.03, 135.91, 133.79, 137.05, 137.8, 136.89, 136.0, 130.05, 133.73, 133.99, 135.14, 135.26, 137.15, 137.41, 136.88, 136.6, 132.51, 143.34, 156.54, 160.65, 152.17, 142.2, 141.7, 135.53, 136.47, 132.07, 130.21, 131.08, 127.99, 134.71, 133.25, 130.63, 128.47, 119.5, 116.7, 113.5, 107.27, 112.93, 115.7, 116.67, 125.73, 129.3, 132.54, 134.37, 132.22, 129.04, 126.79, 130.04, 133.72, 133.76, 134.44, 132.38, 134.85, 132.66, 124.57, 123.37, 122.92], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
     </row>
@@ -1267,7 +1267,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.215</v>
+        <v>0.14</v>
       </c>
       <c r="E14" t="n">
         <v>53</v>
@@ -1321,36 +1321,36 @@
         </is>
       </c>
       <c r="B15" t="n">
+        <v>58</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UP  </t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0.727</v>
+      </c>
+      <c r="E15" t="n">
         <v>59</v>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UP  </t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E15" t="n">
-        <v>55</v>
-      </c>
       <c r="F15" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="G15" t="n">
         <v>54.5</v>
       </c>
       <c r="H15" t="n">
-        <v>1430</v>
+        <v>1805</v>
       </c>
       <c r="I15" t="n">
-        <v>28.6</v>
+        <v>36.1</v>
       </c>
       <c r="J15" t="n">
         <v>87.3</v>
       </c>
       <c r="K15" t="n">
-        <v>-58.7</v>
+        <v>-51.2</v>
       </c>
       <c r="L15" t="n">
         <v>5000</v>
@@ -1359,20 +1359,20 @@
         <v>27</v>
       </c>
       <c r="N15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O15" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="P15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.8</v>
+        <v>5.3</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [97.86, 101.92, 106.54, 107.25, 108.53, 109.08, 110.51, 110.39, 110.44, 105.96, 108.3, 108.95, 107.04, 102.25, 103.33, 98.25, 96.46, 98.15, 92.39, 95.01, 97.6, 98.33, 99.78, 99.65, 105.81, 106.63, 98.67, 94.75, 100.56, 99.62, 102.79, 104.55, 105.99, 108.29, 112.4, 116.67, 111.35, 112.03, 113.65, 113.75, 113.1, 111.44, 113.91, 117.31, 119.13, 117.02, 126.43, 131.94, 135.57, 136.54, 140.64, 144.99, 148.52, 154.71, 154.22, 162.53, 162.06, 165.87, 167.89, 161.34, 167.75, 182.75, 195.54, 192.24, 186.9, 179.77, 167.76, 164.7, 161.23, 161.93, 172.88, 170.7, 173.23, 169.87, 170.74, 171.21, 168.86, 170.23, 168.26, 169.66, 175.27, 185.73, 190.79, 193.18, 193.98, 199.38, 194.62, 191.12, 198.4, 187.18, 187.91, 210.73, 206.77, 203.76, 203.08, 198.49, 191.15, 188.42, 183.42, 183.28], 'signals': ['FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT']}</t>
+          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [97.86, 101.92, 106.54, 107.25, 108.53, 109.08, 110.51, 110.39, 110.44, 105.96, 108.3, 108.95, 107.04, 102.25, 103.33, 98.25, 96.46, 98.15, 92.39, 95.01, 97.6, 98.33, 99.78, 99.65, 105.81, 106.63, 98.67, 94.75, 100.56, 99.62, 102.79, 104.55, 105.99, 108.29, 112.4, 116.67, 111.35, 112.03, 113.65, 113.75, 113.1, 111.44, 113.91, 117.31, 119.13, 117.02, 126.43, 131.94, 135.57, 136.54, 140.64, 144.99, 148.52, 154.71, 154.22, 162.53, 162.06, 165.87, 167.89, 161.34, 167.75, 182.75, 195.54, 192.24, 186.9, 179.77, 167.76, 164.7, 161.23, 161.93, 172.88, 170.7, 173.23, 169.87, 170.74, 171.21, 168.86, 170.23, 168.26, 169.66, 175.27, 185.73, 190.79, 193.18, 193.98, 199.38, 194.62, 191.12, 198.4, 187.18, 187.91, 210.73, 206.77, 203.76, 203.08, 198.49, 191.15, 188.42, 183.42, 183.28], 'signals': ['FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.462</v>
+        <v>0.326</v>
       </c>
       <c r="E16" t="n">
         <v>56</v>
@@ -1403,16 +1403,16 @@
         <v>65</v>
       </c>
       <c r="H16" t="n">
-        <v>285</v>
+        <v>704</v>
       </c>
       <c r="I16" t="n">
-        <v>5.7</v>
+        <v>14.1</v>
       </c>
       <c r="J16" t="n">
         <v>18.8</v>
       </c>
       <c r="K16" t="n">
-        <v>-13.1</v>
+        <v>-4.7</v>
       </c>
       <c r="L16" t="n">
         <v>5000</v>
@@ -1421,20 +1421,20 @@
         <v>14</v>
       </c>
       <c r="N16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O16" t="n">
+        <v>8</v>
+      </c>
+      <c r="P16" t="n">
         <v>2</v>
       </c>
-      <c r="P16" t="n">
-        <v>3</v>
-      </c>
       <c r="Q16" t="n">
-        <v>1.7</v>
+        <v>5</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [297.39, 296.53, 290.75, 286.71, 287.15, 285.97, 284.77, 280.19, 280.73, 283.43, 284.15, 284.99, 285.22, 283.82, 287.14, 289.61, 292.6, 288.87, 280.14, 281.06, 291.35, 292.56, 291.79, 294.12, 296.07, 306.59, 308.94, 308.48, 312.27, 309.72, 304.56, 308.56, 308.9, 315.57, 311.6, 311.62, 310.29, 306.9, 310.23, 310.05, 307.86, 311.83, 311.07, 306.27, 308.01, 313.49, 304.9, 300.75, 298.65, 303.51, 298.9, 298.57, 296.47, 299.38, 294.37, 300.63, 301.64, 305.01, 305.36, 297.94, 295.4, 297.97, 295.25, 299.61, 299.5, 309.5, 310.97, 309.71, 311.3, 307.75, 312.08, 319.28, 317.97, 329.65, 331.96, 323.76, 329.99, 332.64, 331.95, 333.62, 327.57, 327.91, 325.86, 332.57, 332.97, 337.72, 339.22, 330.62, 335.47, 336.47, 334.53, 342.89, 346.91, 343.15, 341.1, 338.87, 345.23, 348.21, 349.9, 353.21], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [297.39, 296.53, 290.75, 286.71, 287.15, 285.97, 284.77, 280.19, 280.73, 283.43, 284.15, 284.99, 285.22, 283.82, 287.14, 289.61, 292.6, 288.87, 280.14, 281.06, 291.35, 292.56, 291.79, 294.12, 296.07, 306.59, 308.94, 308.48, 312.27, 309.72, 304.56, 308.56, 308.9, 315.57, 311.6, 311.62, 310.29, 306.9, 310.23, 310.05, 307.86, 311.83, 311.07, 306.27, 308.01, 313.49, 304.9, 300.75, 298.65, 303.51, 298.9, 298.57, 296.47, 299.38, 294.37, 300.63, 301.64, 305.01, 305.36, 297.94, 295.4, 297.97, 295.25, 299.61, 299.5, 309.5, 310.97, 309.71, 311.3, 307.75, 312.08, 319.28, 317.97, 329.65, 331.96, 323.76, 329.99, 332.64, 331.95, 333.62, 327.57, 327.91, 325.86, 332.57, 332.97, 337.72, 339.22, 330.62, 335.47, 336.47, 334.53, 342.89, 346.91, 343.15, 341.1, 338.87, 345.23, 348.21, 349.9, 353.21], 'signals': ['FLAT', 'BUY', 'SELL', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'SELL', 'BUY', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
     </row>
@@ -1445,7 +1445,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1453,10 +1453,10 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.542</v>
+        <v>0.585</v>
       </c>
       <c r="E17" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F17" t="n">
         <v>90</v>
@@ -1465,16 +1465,16 @@
         <v>65</v>
       </c>
       <c r="H17" t="n">
-        <v>659</v>
+        <v>810</v>
       </c>
       <c r="I17" t="n">
-        <v>13.2</v>
+        <v>16.2</v>
       </c>
       <c r="J17" t="n">
         <v>23.6</v>
       </c>
       <c r="K17" t="n">
-        <v>-10.4</v>
+        <v>-7.4</v>
       </c>
       <c r="L17" t="n">
         <v>5000</v>
@@ -1483,20 +1483,20 @@
         <v>4</v>
       </c>
       <c r="N17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O17" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="P17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.3</v>
+        <v>19</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [858.8, 863.44, 831.79, 817.82, 828.38, 830.15, 820.15, 784.06, 778.78, 791.28, 803.5, 801.95, 805.95, 809.96, 827.62, 832.05, 838.15, 819.03, 799.37, 804.06, 842.28, 856.44, 859.25, 862.25, 860.36, 901.78, 899.75, 903.82, 886.88, 905.64, 895.54, 896.05, 921.89, 937.61, 922.48, 930.74, 927.21, 922.84, 933.7, 922.48, 901.63, 919.72, 919.66, 899.31, 914.86, 933.24, 921.81, 932.37, 940.71, 941.75, 951.23, 964.71, 944.31, 942.21, 924.66, 977.81, 983.83, 992.36, 990.16, 992.1, 1003.95, 1021.06, 1048.58, 1064.58, 1041.02, 1092.61, 1038.68, 1045.0, 1032.01, 1001.29, 1035.64, 1062.75, 1076.17, 1090.67, 1099.14, 1096.56, 1106.37, 1094.44, 1076.91, 1065.09, 1019.61, 1020.21, 1011.37, 1019.61, 1021.0, 1055.29, 1042.98, 1029.64, 1055.97, 1055.18, 1045.91, 1140.0, 1152.07, 1095.46, 1065.22, 1055.03, 1085.56, 1098.2, 1074.72, 1061.23], 'signals': ['BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [858.8, 863.44, 831.79, 817.82, 828.38, 830.15, 820.15, 784.06, 778.78, 791.28, 803.5, 801.95, 805.95, 809.96, 827.62, 832.05, 838.15, 819.03, 799.37, 804.06, 842.28, 856.44, 859.25, 862.25, 860.36, 901.78, 899.75, 903.82, 886.88, 905.64, 895.54, 896.05, 921.89, 937.61, 922.48, 930.74, 927.21, 922.84, 933.7, 922.48, 901.63, 919.72, 919.66, 899.31, 914.86, 933.24, 921.81, 932.37, 940.71, 941.75, 951.23, 964.71, 944.31, 942.21, 924.66, 977.81, 983.83, 992.36, 990.16, 992.1, 1003.95, 1021.06, 1048.58, 1064.58, 1041.02, 1092.61, 1038.68, 1045.0, 1032.01, 1001.29, 1035.64, 1062.75, 1076.17, 1090.67, 1099.14, 1096.56, 1106.37, 1094.44, 1076.91, 1065.09, 1019.61, 1020.21, 1011.37, 1019.61, 1021.0, 1055.29, 1042.98, 1029.64, 1055.97, 1055.18, 1045.91, 1140.0, 1152.07, 1095.46, 1065.22, 1055.03, 1085.56, 1098.2, 1074.72, 1061.23], 'signals': ['BUY', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
     </row>
@@ -1507,7 +1507,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1515,10 +1515,10 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.323</v>
+        <v>0.288</v>
       </c>
       <c r="E18" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F18" t="n">
         <v>60</v>
@@ -1558,7 +1558,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [182.36, 208.93, 205.71, 197.22, 199.79, 196.52, 198.63, 193.23, 195.53, 203.32, 210.23, 202.29, 202.91, 197.5, 200.62, 181.04, 181.1, 173.38, 161.14, 160.79, 174.61, 172.99, 171.46, 174.79, 175.18, 175.09, 169.02, 167.85, 174.53, 184.41, 195.9, 199.83, 206.33, 211.63, 195.95, 206.24, 197.93, 199.77, 196.68, 194.1, 181.73, 187.77, 191.25, 202.99, 197.75, 197.96, 192.96, 201.16, 216.6, 207.64, 201.8, 212.01, 195.43, 189.44, 193.45, 191.29, 193.56, 184.99, 180.01, 173.78, 182.25, 189.03, 182.61, 173.99, 163.22, 164.13, 152.4, 162.11, 155.5, 153.97, 160.43, 159.78, 169.62, 169.27, 164.92, 163.26, 164.84, 158.18, 150.11, 142.52, 149.06, 151.65, 146.19, 159.24, 165.48, 168.87, 163.51, 159.36, 158.44, 159.07, 157.37, 161.5, 167.21, 160.49, 157.12, 160.43, 175.85, 166.12, 161.16, 158.29], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [182.36, 208.93, 205.71, 197.22, 199.79, 196.52, 198.63, 193.23, 195.53, 203.32, 210.23, 202.29, 202.91, 197.5, 200.62, 181.04, 181.1, 173.38, 161.14, 160.79, 174.61, 172.99, 171.46, 174.79, 175.18, 175.09, 169.02, 167.85, 174.53, 184.41, 195.9, 199.83, 206.33, 211.63, 195.95, 206.24, 197.93, 199.77, 196.68, 194.1, 181.73, 187.77, 191.25, 202.99, 197.75, 197.96, 192.96, 201.16, 216.6, 207.64, 201.8, 212.01, 195.43, 189.44, 193.45, 191.29, 193.56, 184.99, 180.01, 173.78, 182.25, 189.03, 182.61, 173.99, 163.22, 164.13, 152.4, 162.11, 155.5, 153.97, 160.43, 159.78, 169.62, 169.27, 164.92, 163.26, 164.84, 158.18, 150.11, 142.52, 149.06, 151.65, 146.19, 159.24, 165.48, 168.87, 163.51, 159.36, 158.44, 159.07, 157.37, 161.5, 167.21, 160.49, 157.12, 160.43, 175.85, 166.12, 161.16, 158.29], 'signals': ['FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1577,10 +1577,10 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.284</v>
+        <v>0.257</v>
       </c>
       <c r="E19" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F19" t="n">
         <v>30</v>
@@ -1589,16 +1589,16 @@
         <v>52.6</v>
       </c>
       <c r="H19" t="n">
-        <v>435</v>
+        <v>410</v>
       </c>
       <c r="I19" t="n">
-        <v>8.699999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J19" t="n">
         <v>18.9</v>
       </c>
       <c r="K19" t="n">
-        <v>-10.2</v>
+        <v>-10.7</v>
       </c>
       <c r="L19" t="n">
         <v>5000</v>
@@ -1607,20 +1607,20 @@
         <v>4</v>
       </c>
       <c r="N19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O19" t="n">
         <v>12</v>
       </c>
       <c r="P19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q19" t="n">
-        <v>6.5</v>
+        <v>4.7</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [1006.0, 1001.85, 981.57, 988.63, 1006.66, 999.63, 998.12, 975.57, 983.39, 987.42, 928.75, 916.47, 915.92, 905.14, 908.99, 901.47, 914.74, 895.46, 876.73, 885.11, 918.19, 952.88, 933.97, 925.47, 929.49, 951.66, 953.55, 937.86, 927.95, 920.91, 903.47, 902.44, 925.44, 918.32, 901.47, 919.9, 916.07, 882.44, 866.78, 872.5, 849.75, 932.99, 961.67, 966.27, 987.17, 985.35, 973.28, 946.82, 965.33, 988.17, 1014.0, 1004.97, 1004.92, 988.09, 1021.41, 1018.87, 1041.65, 1065.0, 1064.74, 1082.92, 1126.8, 1105.0, 1082.2, 1064.15, 1078.78, 1125.27, 1131.42, 1149.15, 1144.68, 1136.37, 1160.95, 1133.0, 1129.35, 1122.5, 1112.0, 1098.57, 1102.08, 1107.08, 1117.26, 1127.69, 1208.12, 1229.93, 1199.43, 1191.74, 1213.91, 1200.06, 1235.56, 1215.83, 1216.95, 1188.58, 1181.87, 1152.54, 1156.63, 1169.17, 1179.11, 1146.9, 1175.41, 1163.01, 1185.87, 1196.03], 'signals': ['FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [1006.0, 1001.85, 981.57, 988.63, 1006.66, 999.63, 998.12, 975.57, 983.39, 987.42, 928.75, 916.47, 915.92, 905.14, 908.99, 901.47, 914.74, 895.46, 876.73, 885.11, 918.19, 952.88, 933.97, 925.47, 929.49, 951.66, 953.55, 937.86, 927.95, 920.91, 903.47, 902.44, 925.44, 918.32, 901.47, 919.9, 916.07, 882.44, 866.78, 872.5, 849.75, 932.99, 961.67, 966.27, 987.17, 985.35, 973.28, 946.82, 965.33, 988.17, 1014.0, 1004.97, 1004.92, 988.09, 1021.41, 1018.87, 1041.65, 1065.0, 1064.74, 1082.92, 1126.8, 1105.0, 1082.2, 1064.15, 1078.78, 1125.27, 1131.42, 1149.15, 1144.68, 1136.37, 1160.95, 1133.0, 1129.35, 1122.5, 1112.0, 1098.57, 1102.08, 1107.08, 1117.26, 1127.69, 1208.12, 1229.93, 1199.43, 1191.74, 1213.91, 1200.06, 1235.56, 1215.83, 1216.95, 1188.58, 1181.87, 1152.54, 1156.63, 1169.17, 1179.11, 1146.9, 1175.41, 1163.01, 1185.87, 1196.03], 'signals': ['BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F20" t="n">
         <v>50</v>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [224.12, 227.31, 222.06, 231.11, 225.0, 217.76, 214.1, 204.76, 209.89, 213.47, 210.82, 205.99, 201.18, 195.12, 198.41, 196.42, 199.61, 194.36, 190.52, 189.21, 199.03, 207.32, 208.22, 212.3, 210.0, 217.8, 220.06, 217.63, 222.14, 223.77, 223.93, 218.88, 223.38, 225.08, 219.16, 231.28, 234.15, 232.44, 231.33, 230.72, 224.11, 229.03, 227.38, 221.3, 224.38, 229.93, 231.03, 237.36, 238.21, 236.87, 240.6, 229.21, 220.49, 220.61, 215.01, 222.2, 219.61, 219.02, 218.9, 224.3, 228.78, 231.15, 224.3, 217.7, 210.58, 217.42, 215.45, 215.92, 214.51, 209.0, 221.63, 219.05, 228.95, 227.49, 225.63, 222.72, 220.83, 216.71, 220.25, 218.12, 217.25, 214.69, 216.47, 218.58, 226.49, 234.54, 231.68, 224.95, 223.11, 222.28, 215.51, 217.11, 218.12, 214.34, 214.03, 209.48, 204.8, 208.65, 209.23, 209.52], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [224.12, 227.31, 222.06, 231.11, 225.0, 217.76, 214.1, 204.76, 209.89, 213.47, 210.82, 205.99, 201.18, 195.12, 198.41, 196.42, 199.61, 194.36, 190.52, 189.21, 199.03, 207.32, 208.22, 212.3, 210.0, 217.8, 220.06, 217.63, 222.14, 223.77, 223.93, 218.88, 223.38, 225.08, 219.16, 231.28, 234.15, 232.44, 231.33, 230.72, 224.11, 229.03, 227.38, 221.3, 224.38, 229.93, 231.03, 237.36, 238.21, 236.87, 240.6, 229.21, 220.49, 220.61, 215.01, 222.2, 219.61, 219.02, 218.9, 224.3, 228.78, 231.15, 224.3, 217.7, 210.58, 217.42, 215.45, 215.92, 214.51, 209.0, 221.63, 219.05, 228.95, 227.49, 225.63, 222.72, 220.83, 216.71, 220.25, 218.12, 217.25, 214.69, 216.47, 218.58, 226.49, 234.54, 231.68, 224.95, 223.11, 222.28, 215.51, 217.11, 218.12, 214.34, 214.03, 209.48, 204.8, 208.65, 209.23, 209.52], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
     </row>
@@ -1693,7 +1693,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.538</v>
+        <v>0.529</v>
       </c>
       <c r="E21" t="n">
         <v>67</v>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [76.36, 76.65, 75.44, 75.13, 73.84, 72.36, 74.97, 72.97, 73.33, 74.66, 77.79, 76.66, 75.34, 73.89, 75.12, 72.34, 73.08, 70.55, 69.18, 69.91, 71.93, 71.71, 71.84, 72.17, 71.73, 72.38, 71.81, 70.48, 72.34, 72.91, 77.28, 76.48, 77.12, 77.49, 77.26, 75.58, 74.7, 74.64, 76.27, 74.11, 74.47, 74.61, 75.12, 73.93, 72.95, 79.17, 76.73, 75.45, 76.15, 76.36, 74.7, 74.69, 75.09, 75.08, 74.09, 74.6, 73.61, 71.82, 70.12, 70.73, 70.92, 70.4, 73.77, 71.62, 71.69, 72.21, 70.71, 70.06, 70.38, 68.61, 69.55, 68.85, 72.85, 73.25, 70.91, 71.64, 71.43, 69.67, 73.85, 72.25, 76.2, 75.5, 72.16, 72.66, 74.43, 72.42, 74.33, 73.6, 74.35, 74.54, 74.26, 72.08, 72.67, 74.04, 72.46, 72.17, 71.55, 70.33, 68.91, 65.94], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'SELL', 'BUY', 'SELL', 'BUY', 'SELL', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [76.36, 76.65, 75.44, 75.13, 73.84, 72.36, 74.97, 72.97, 73.33, 74.66, 77.79, 76.66, 75.34, 73.89, 75.12, 72.34, 73.08, 70.55, 69.18, 69.91, 71.93, 71.71, 71.84, 72.17, 71.73, 72.38, 71.81, 70.48, 72.34, 72.91, 77.28, 76.48, 77.12, 77.49, 77.26, 75.58, 74.7, 74.64, 76.27, 74.11, 74.47, 74.61, 75.12, 73.93, 72.95, 79.17, 76.73, 75.45, 76.15, 76.36, 74.7, 74.69, 75.09, 75.08, 74.09, 74.6, 73.61, 71.82, 70.12, 70.73, 70.92, 70.4, 73.77, 71.62, 71.69, 72.21, 70.71, 70.06, 70.38, 68.61, 69.55, 68.85, 72.85, 73.25, 70.91, 71.64, 71.43, 69.67, 73.85, 72.25, 76.2, 75.5, 72.16, 72.66, 74.43, 72.42, 74.33, 73.6, 74.35, 74.54, 74.26, 72.08, 72.67, 74.04, 72.46, 72.17, 71.55, 70.33, 68.91, 65.94], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'SELL', 'BUY', 'SELL', 'BUY', 'SELL', 'FLAT', 'BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
     </row>

--- a/demo_results.xlsx
+++ b/demo_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R21"/>
+  <dimension ref="A1:S21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,6 +507,11 @@
           <t>chart_data</t>
         </is>
       </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>current_price</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -519,32 +524,32 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DOWN</t>
+          <t xml:space="preserve">UP  </t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.179</v>
+        <v>0.846</v>
       </c>
       <c r="E2" t="n">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="F2" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="G2" t="n">
         <v>65</v>
       </c>
       <c r="H2" t="n">
-        <v>846</v>
+        <v>609</v>
       </c>
       <c r="I2" t="n">
-        <v>16.9</v>
+        <v>12.2</v>
       </c>
       <c r="J2" t="n">
         <v>26.4</v>
       </c>
       <c r="K2" t="n">
-        <v>-9.5</v>
+        <v>-14.2</v>
       </c>
       <c r="L2" t="n">
         <v>5000</v>
@@ -553,21 +558,24 @@
         <v>15</v>
       </c>
       <c r="N2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O2" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="P2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.8</v>
+        <v>9</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [263.51, 262.28, 260.05, 257.22, 259.64, 260.59, 260.57, 255.52, 249.89, 252.59, 254.0, 249.71, 248.73, 247.76, 251.26, 251.41, 252.39, 252.66, 248.57, 246.4, 253.56, 255.39, 255.68, 258.62, 253.27, 258.66, 260.25, 260.24, 258.96, 258.59, 266.18, 263.16, 269.98, 272.8, 265.93, 272.92, 273.18, 270.81, 267.36, 270.46, 269.92, 271.1, 279.88, 276.58, 283.92, 287.25, 287.18, 293.05, 292.68, 294.8, 298.87, 298.21, 300.23, 297.84, 298.97, 302.25, 304.99, 308.82, 308.33, 310.85, 312.51, 312.06, 306.31, 315.2, 310.26, 311.23, 307.34, 301.54, 290.55, 291.58, 295.63, 291.13, 296.42, 299.24, 295.95, 298.01, 297.01, 294.3, 293.08, 275.15, 283.78, 281.74, 289.36, 294.38, 308.63, 312.66, 310.66, 313.39, 316.22, 315.32, 317.31, 314.86, 327.5, 333.26, 333.74, 326.59, 327.74, 325.89, 321.66, 333.02], 'signals': ['BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL']}</t>
-        </is>
+          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [263.51, 262.28, 260.05, 257.22, 259.64, 260.59, 260.57, 255.52, 249.89, 252.59, 254.0, 249.71, 248.73, 247.76, 251.26, 251.41, 252.39, 252.66, 248.57, 246.4, 253.56, 255.39, 255.68, 258.62, 253.27, 258.66, 260.25, 260.24, 258.96, 258.59, 266.18, 263.16, 269.98, 272.8, 265.93, 272.92, 273.18, 270.81, 267.36, 270.46, 269.92, 271.1, 279.88, 276.58, 283.92, 287.25, 287.18, 293.05, 292.68, 294.8, 298.87, 298.21, 300.23, 297.84, 298.97, 302.25, 304.99, 308.82, 308.33, 310.85, 312.51, 312.06, 306.31, 315.2, 310.26, 311.23, 307.34, 301.54, 290.55, 291.58, 295.63, 291.13, 296.42, 299.24, 295.95, 298.01, 297.01, 294.3, 293.08, 275.15, 283.78, 281.74, 289.36, 294.38, 308.63, 312.66, 310.66, 313.39, 316.22, 315.32, 317.31, 314.86, 327.5, 333.26, 333.74, 326.59, 327.74, 325.89, 321.66, 333.02], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
+        <v>333.02</v>
       </c>
     </row>
     <row r="3">
@@ -585,16 +593,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.036</v>
+        <v>0.04</v>
       </c>
       <c r="E3" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F3" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="G3" t="n">
-        <v>66.7</v>
+        <v>60</v>
       </c>
       <c r="H3" t="n">
         <v>198</v>
@@ -628,8 +636,11 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [403.06, 404.32, 409.79, 408.08, 408.53, 404.88, 404.0, 400.99, 394.7, 399.09, 398.55, 390.94, 388.18, 381.04, 382.17, 371.93, 370.24, 365.18, 356.0, 358.18, 369.37, 368.57, 372.65, 372.07, 371.49, 373.52, 372.26, 370.07, 383.54, 392.26, 410.33, 419.35, 421.88, 417.17, 423.24, 431.98, 414.85, 423.7, 423.9, 428.32, 423.54, 406.9, 413.54, 412.73, 410.49, 413.07, 419.86, 414.22, 411.77, 406.89, 404.33, 408.55, 421.01, 422.62, 416.52, 420.15, 419.09, 418.57, 416.03, 412.67, 426.99, 450.24, 460.52, 441.31, 427.34, 428.05, 416.67, 411.74, 403.41, 397.36, 390.34, 390.74, 399.76, 393.83, 378.91, 379.4, 367.34, 373.94, 365.46, 352.83, 372.97, 368.57, 373.02, 384.28, 390.49, 386.74, 388.84, 383.34, 384.36, 385.1, 390.99, 384.93, 395.63, 401.1, 393.82, 402.29, 397.75, 390.34, 381.58, 381.7], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
-        </is>
+          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [403.06, 404.32, 409.79, 408.08, 408.53, 404.88, 404.0, 400.99, 394.7, 399.09, 398.55, 390.94, 388.18, 381.04, 382.17, 371.93, 370.24, 365.18, 356.0, 358.18, 369.37, 368.57, 372.65, 372.07, 371.49, 373.52, 372.26, 370.07, 383.54, 392.26, 410.33, 419.35, 421.88, 417.17, 423.24, 431.98, 414.85, 423.7, 423.9, 428.32, 423.54, 406.9, 413.54, 412.73, 410.49, 413.07, 419.86, 414.22, 411.77, 406.89, 404.33, 408.55, 421.01, 422.62, 416.52, 420.15, 419.09, 418.57, 416.03, 412.67, 426.99, 450.24, 460.52, 441.31, 427.34, 428.05, 416.67, 411.74, 403.41, 397.36, 390.34, 390.74, 399.76, 393.83, 378.91, 379.4, 367.34, 373.94, 365.46, 352.83, 372.97, 368.57, 373.02, 384.28, 390.49, 386.74, 388.84, 383.34, 384.36, 385.1, 390.99, 384.93, 395.63, 401.1, 393.82, 402.29, 397.75, 390.34, 381.58, 381.7], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
+        <v>381.7</v>
       </c>
     </row>
     <row r="4">
@@ -639,7 +650,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -647,10 +658,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.496</v>
+        <v>0.479</v>
       </c>
       <c r="E4" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="F4" t="n">
         <v>80</v>
@@ -690,8 +701,11 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [303.19, 302.74, 300.49, 298.13, 306.18, 306.86, 308.52, 303.37, 302.1, 305.38, 310.73, 307.51, 306.95, 300.82, 301.88, 290.27, 290.76, 280.75, 274.18, 273.34, 287.39, 297.21, 295.59, 299.81, 305.28, 317.13, 318.3, 317.05, 321.12, 332.71, 336.92, 335.82, 341.48, 337.22, 332.09, 339.12, 338.69, 344.19, 350.13, 349.57, 349.73, 384.57, 385.46, 383.02, 388.2, 397.8, 397.75, 400.56, 388.41, 387.12, 402.38, 400.83, 396.54, 396.7, 387.43, 388.68, 387.43, 382.74, 388.65, 388.6, 389.9, 380.11, 376.15, 361.63, 358.78, 371.97, 368.31, 363.31, 364.26, 356.38, 357.77, 359.68, 369.35, 373.25, 363.79, 368.03, 349.68, 346.13, 345.29, 343.71, 337.39, 353.65, 357.37, 361.21, 359.91, 366.46, 367.03, 361.92, 358.89, 357.18, 352.51, 359.51, 370.92, 354.46, 346.77, 351.99, 347.15, 342.09, 317.69, 319.74], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
-        </is>
+          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [303.19, 302.74, 300.49, 298.13, 306.18, 306.86, 308.52, 303.37, 302.1, 305.38, 310.73, 307.51, 306.95, 300.82, 301.88, 290.27, 290.76, 280.75, 274.18, 273.34, 287.39, 297.21, 295.59, 299.81, 305.28, 317.13, 318.3, 317.05, 321.12, 332.71, 336.92, 335.82, 341.48, 337.22, 332.09, 339.12, 338.69, 344.19, 350.13, 349.57, 349.73, 384.57, 385.46, 383.02, 388.2, 397.8, 397.75, 400.56, 388.41, 387.12, 402.38, 400.83, 396.54, 396.7, 387.43, 388.68, 387.43, 382.74, 388.65, 388.6, 389.9, 380.11, 376.15, 361.63, 358.78, 371.97, 368.31, 363.31, 364.26, 356.38, 357.77, 359.68, 369.35, 373.25, 363.79, 368.03, 349.68, 346.13, 345.29, 343.71, 337.39, 353.65, 357.37, 361.21, 359.91, 366.46, 367.03, 361.92, 358.89, 357.18, 352.51, 359.51, 370.92, 354.46, 346.77, 351.99, 347.15, 342.09, 317.69, 319.74], 'signals': ['BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+        </is>
+      </c>
+      <c r="S4" t="n">
+        <v>319.74</v>
       </c>
     </row>
     <row r="5">
@@ -701,7 +715,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -709,7 +723,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.732</v>
+        <v>0.779</v>
       </c>
       <c r="E5" t="n">
         <v>59</v>
@@ -755,6 +769,9 @@
           <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [208.73, 216.82, 218.94, 213.21, 213.49, 214.33, 212.65, 209.53, 207.67, 211.74, 215.2, 209.87, 208.76, 205.37, 210.14, 207.24, 211.71, 207.54, 199.34, 200.95, 208.27, 210.57, 209.77, 212.79, 213.77, 221.25, 233.65, 238.38, 239.89, 249.02, 248.5, 249.7, 250.56, 248.28, 249.91, 255.36, 255.08, 263.99, 261.12, 259.7, 263.04, 265.06, 268.26, 272.05, 273.55, 274.99, 271.17, 272.68, 268.99, 265.82, 270.13, 267.22, 264.14, 264.86, 259.34, 265.01, 268.46, 266.32, 265.29, 271.85, 274.0, 270.64, 261.26, 256.52, 250.02, 253.79, 246.03, 245.22, 244.19, 238.0, 241.51, 238.55, 246.02, 246.0, 237.5, 244.39, 232.79, 234.11, 234.27, 227.01, 232.69, 240.14, 238.34, 241.7, 242.67, 244.16, 245.98, 243.62, 247.04, 245.34, 247.31, 247.49, 254.96, 249.89, 247.23, 249.99, 247.55, 244.85, 233.66, 232.11], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
+      <c r="S5" t="n">
+        <v>232.11</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -763,36 +780,36 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">UP  </t>
+          <t>DOWN</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.62</v>
+        <v>0.121</v>
       </c>
       <c r="E6" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F6" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="G6" t="n">
         <v>35.7</v>
       </c>
       <c r="H6" t="n">
-        <v>416</v>
+        <v>-547</v>
       </c>
       <c r="I6" t="n">
-        <v>8.300000000000001</v>
+        <v>-10.9</v>
       </c>
       <c r="J6" t="n">
         <v>-9</v>
       </c>
       <c r="K6" t="n">
-        <v>17.3</v>
+        <v>-1.9</v>
       </c>
       <c r="L6" t="n">
         <v>5000</v>
@@ -801,21 +818,24 @@
         <v>8</v>
       </c>
       <c r="N6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O6" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="P6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q6" t="n">
         <v>3</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [653.91, 666.54, 659.39, 643.71, 646.24, 652.91, 653.69, 637.04, 612.62, 626.87, 622.08, 615.11, 606.14, 593.11, 603.5, 592.37, 594.34, 547.03, 525.23, 535.88, 571.6, 578.69, 573.93, 572.49, 574.52, 611.85, 627.81, 629.28, 633.94, 661.88, 670.96, 676.24, 687.91, 670.29, 668.22, 674.1, 658.54, 674.4, 677.99, 670.72, 668.5, 611.34, 608.19, 609.84, 604.4, 612.31, 616.24, 609.07, 598.31, 602.44, 616.06, 617.86, 613.66, 610.64, 602.05, 604.5, 606.82, 609.69, 611.77, 634.67, 634.7, 631.92, 599.91, 597.08, 622.4, 626.99, 592.45, 584.85, 584.05, 570.45, 567.9, 566.45, 593.48, 600.21, 567.58, 577.22, 563.85, 562.2, 557.67, 542.87, 550.25, 562.6, 563.29, 612.91, 582.9, 600.29, 615.58, 603.12, 631.48, 669.21, 656.73, 661.04, 681.31, 664.54, 646.01, 645.85, 643.81, 627.17, 606.1, 595.19], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT']}</t>
-        </is>
+          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [653.91, 666.54, 659.39, 643.71, 646.24, 652.91, 653.69, 637.04, 612.62, 626.87, 622.08, 615.11, 606.14, 593.11, 603.5, 592.37, 594.34, 547.03, 525.23, 535.88, 571.6, 578.69, 573.93, 572.49, 574.52, 611.85, 627.81, 629.28, 633.94, 661.88, 670.96, 676.24, 687.91, 670.29, 668.22, 674.1, 658.54, 674.4, 677.99, 670.72, 668.5, 611.34, 608.19, 609.84, 604.4, 612.31, 616.24, 609.07, 598.31, 602.44, 616.06, 617.86, 613.66, 610.64, 602.05, 604.5, 606.82, 609.69, 611.77, 634.67, 634.7, 631.92, 599.91, 597.08, 622.4, 626.99, 592.45, 584.85, 584.05, 570.45, 567.9, 566.45, 593.48, 600.21, 567.58, 577.22, 563.85, 562.2, 557.67, 542.87, 550.25, 562.6, 563.29, 612.91, 582.9, 600.29, 615.58, 603.12, 631.48, 669.21, 656.73, 661.04, 681.31, 664.54, 646.01, 645.85, 643.81, 627.17, 606.1, 595.19], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+        </is>
+      </c>
+      <c r="S6" t="n">
+        <v>595.1900000000001</v>
       </c>
     </row>
     <row r="7">
@@ -825,7 +845,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -833,10 +853,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.48</v>
+        <v>0.348</v>
       </c>
       <c r="E7" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F7" t="n">
         <v>80</v>
@@ -845,16 +865,16 @@
         <v>55</v>
       </c>
       <c r="H7" t="n">
-        <v>520</v>
+        <v>682</v>
       </c>
       <c r="I7" t="n">
-        <v>10.4</v>
+        <v>13.6</v>
       </c>
       <c r="J7" t="n">
         <v>15</v>
       </c>
       <c r="K7" t="n">
-        <v>-4.6</v>
+        <v>-1.4</v>
       </c>
       <c r="L7" t="n">
         <v>5000</v>
@@ -866,18 +886,21 @@
         <v>4</v>
       </c>
       <c r="O7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P7" t="n">
         <v>4</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [179.83, 182.82, 183.12, 177.6, 182.43, 184.54, 185.81, 182.93, 180.04, 183.01, 181.72, 180.19, 178.35, 172.5, 175.44, 175.0, 178.47, 171.04, 167.32, 164.98, 174.2, 175.55, 177.18, 177.43, 177.89, 181.87, 183.7, 188.41, 189.09, 196.28, 198.64, 198.12, 201.45, 201.82, 199.65, 202.26, 199.41, 208.03, 216.36, 212.92, 209.01, 199.34, 198.22, 198.25, 196.27, 207.59, 211.25, 214.95, 219.18, 220.52, 225.57, 235.47, 225.06, 222.06, 220.35, 223.21, 219.25, 215.08, 214.61, 212.35, 214.0, 210.89, 224.1, 222.56, 214.5, 218.66, 205.1, 208.64, 208.19, 200.42, 204.87, 205.19, 212.45, 207.41, 204.65, 210.69, 208.65, 200.04, 199.0, 195.74, 192.53, 194.97, 200.09, 197.58, 194.83, 195.55, 196.93, 204.12, 202.78, 210.96, 203.53, 211.8, 212.5, 207.4, 202.81, 203.28, 207.29, 212.06, 208.76, 206.84], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
-        </is>
+          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [179.83, 182.82, 183.12, 177.6, 182.43, 184.54, 185.81, 182.93, 180.04, 183.01, 181.72, 180.19, 178.35, 172.5, 175.44, 175.0, 178.47, 171.04, 167.32, 164.98, 174.2, 175.55, 177.18, 177.43, 177.89, 181.87, 183.7, 188.41, 189.09, 196.28, 198.64, 198.12, 201.45, 201.82, 199.65, 202.26, 199.41, 208.03, 216.36, 212.92, 209.01, 199.34, 198.22, 198.25, 196.27, 207.59, 211.25, 214.95, 219.18, 220.52, 225.57, 235.47, 225.06, 222.06, 220.35, 223.21, 219.25, 215.08, 214.61, 212.35, 214.0, 210.89, 224.1, 222.56, 214.5, 218.66, 205.1, 208.64, 208.19, 200.42, 204.87, 205.19, 212.45, 207.41, 204.65, 210.69, 208.65, 200.04, 199.0, 195.74, 192.53, 194.97, 200.09, 197.58, 194.83, 195.55, 196.93, 204.12, 202.78, 210.96, 203.53, 211.8, 212.5, 207.4, 202.81, 203.28, 207.29, 212.06, 208.76, 206.84], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
+        <v>206.84</v>
       </c>
     </row>
     <row r="8">
@@ -887,7 +910,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -895,10 +918,10 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.449</v>
+        <v>0.485</v>
       </c>
       <c r="E8" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F8" t="n">
         <v>70</v>
@@ -907,16 +930,16 @@
         <v>100</v>
       </c>
       <c r="H8" t="n">
-        <v>605</v>
+        <v>2374</v>
       </c>
       <c r="I8" t="n">
-        <v>12.1</v>
+        <v>47.5</v>
       </c>
       <c r="J8" t="n">
         <v>173.3</v>
       </c>
       <c r="K8" t="n">
-        <v>-161.2</v>
+        <v>-125.8</v>
       </c>
       <c r="L8" t="n">
         <v>5000</v>
@@ -928,18 +951,21 @@
         <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [190.95, 202.07, 199.45, 192.43, 202.68, 203.23, 204.83, 197.74, 193.39, 196.58, 196.31, 199.46, 205.27, 201.33, 202.68, 205.37, 220.27, 203.77, 201.99, 196.04, 203.43, 210.21, 217.5, 220.18, 221.53, 231.82, 236.64, 245.04, 246.83, 255.07, 258.12, 278.26, 278.39, 274.95, 284.49, 303.46, 305.33, 347.81, 334.63, 323.21, 337.11, 354.49, 360.54, 341.54, 355.26, 421.39, 408.46, 455.19, 458.79, 448.29, 445.5, 449.7, 424.1, 420.99, 414.05, 447.58, 449.59, 467.51, 503.89, 495.54, 518.09, 516.1, 510.13, 521.54, 542.52, 523.2, 466.38, 490.33, 475.51, 452.4, 488.45, 511.57, 547.26, 507.29, 512.48, 537.37, 551.63, 519.85, 519.74, 532.57, 521.58, 539.49, 580.91, 540.88, 517.82, 552.05, 516.11, 517.41, 546.72, 557.89, 534.39, 548.13, 529.14, 500.94, 495.76, 503.57, 544.43, 552.33, 539.69, 521.95], 'signals': ['BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
-        </is>
+          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [190.95, 202.07, 199.45, 192.43, 202.68, 203.23, 204.83, 197.74, 193.39, 196.58, 196.31, 199.46, 205.27, 201.33, 202.68, 205.37, 220.27, 203.77, 201.99, 196.04, 203.43, 210.21, 217.5, 220.18, 221.53, 231.82, 236.64, 245.04, 246.83, 255.07, 258.12, 278.26, 278.39, 274.95, 284.49, 303.46, 305.33, 347.81, 334.63, 323.21, 337.11, 354.49, 360.54, 341.54, 355.26, 421.39, 408.46, 455.19, 458.79, 448.29, 445.5, 449.7, 424.1, 420.99, 414.05, 447.58, 449.59, 467.51, 503.89, 495.54, 518.09, 516.1, 510.13, 521.54, 542.52, 523.2, 466.38, 490.33, 475.51, 452.4, 488.45, 511.57, 547.26, 507.29, 512.48, 537.37, 551.63, 519.85, 519.74, 532.57, 521.58, 539.49, 580.91, 540.88, 517.82, 552.05, 516.11, 517.41, 546.72, 557.89, 534.39, 548.13, 529.14, 500.94, 495.76, 503.57, 544.43, 552.33, 539.69, 521.95], 'signals': ['FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+        </is>
+      </c>
+      <c r="S8" t="n">
+        <v>521.95</v>
       </c>
     </row>
     <row r="9">
@@ -949,7 +975,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -957,7 +983,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.655</v>
+        <v>0.646</v>
       </c>
       <c r="E9" t="n">
         <v>52</v>
@@ -1003,6 +1029,9 @@
           <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [312.69, 316.36, 331.55, 329.27, 344.48, 341.32, 340.32, 334.74, 320.98, 323.73, 320.13, 314.77, 318.67, 309.37, 322.0, 317.79, 318.31, 308.93, 300.2, 292.95, 309.02, 312.99, 314.05, 313.93, 333.44, 350.08, 354.35, 370.96, 379.15, 380.18, 396.09, 397.84, 405.9, 399.0, 401.53, 421.98, 419.28, 422.09, 417.54, 399.2, 404.81, 416.77, 420.61, 415.84, 426.68, 424.77, 411.91, 429.32, 427.75, 418.64, 416.13, 439.1, 424.52, 420.05, 410.42, 417.1, 413.91, 413.49, 421.34, 421.19, 425.91, 446.06, 459.24, 480.81, 478.47, 418.25, 385.12, 395.97, 391.54, 371.51, 384.96, 381.47, 393.32, 376.11, 392.28, 410.7, 392.13, 380.15, 382.07, 378.91, 365.02, 372.45, 377.75, 369.34, 360.45, 373.9, 370.78, 388.69, 401.11, 399.97, 384.05, 389.11, 394.28, 374.45, 370.83, 378.16, 386.5, 396.81, 392.47, 381.92], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
+      <c r="S9" t="n">
+        <v>381.92</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1011,7 +1040,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1019,16 +1048,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.456</v>
+        <v>0.413</v>
       </c>
       <c r="E10" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F10" t="n">
         <v>40</v>
       </c>
       <c r="G10" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>3327</v>
@@ -1062,8 +1091,11 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [379.46, 400.54, 396.82, 370.09, 389.1, 402.88, 418.45, 405.12, 425.89, 441.55, 461.43, 461.47, 444.02, 422.66, 404.12, 395.3, 381.87, 355.26, 357.02, 321.75, 337.79, 367.79, 366.18, 377.7, 377.52, 406.67, 421.45, 420.53, 426.49, 465.59, 456.16, 457.16, 455.0, 448.35, 449.31, 487.41, 481.65, 496.64, 524.48, 504.21, 518.38, 517.08, 542.13, 576.36, 640.1, 666.49, 646.53, 746.7, 795.21, 766.46, 803.51, 775.89, 724.55, 681.44, 698.63, 731.88, 761.98, 750.88, 895.74, 928.27, 923.38, 970.85, 1035.34, 1063.94, 1079.4, 995.85, 863.88, 949.13, 935.75, 891.74, 995.72, 981.46, 1087.82, 1020.6, 1043.03, 1133.82, 1211.19, 1051.61, 1048.35, 1213.37, 1132.16, 1145.1, 1154.11, 1032.12, 975.41, 984.75, 938.38, 948.8, 991.64, 979.3, 937.0, 983.12, 904.28, 853.2, 848.95, 865.46, 970.82, 959.48, 990.21, 920.95], 'signals': ['FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
-        </is>
+          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [379.46, 400.54, 396.82, 370.09, 389.1, 402.88, 418.45, 405.12, 425.89, 441.55, 461.43, 461.47, 444.02, 422.66, 404.12, 395.3, 381.87, 355.26, 357.02, 321.75, 337.79, 367.79, 366.18, 377.7, 377.52, 406.67, 421.45, 420.53, 426.49, 465.59, 456.16, 457.16, 455.0, 448.35, 449.31, 487.41, 481.65, 496.64, 524.48, 504.21, 518.38, 517.08, 542.13, 576.36, 640.1, 666.49, 646.53, 746.7, 795.21, 766.46, 803.51, 775.89, 724.55, 681.44, 698.63, 731.88, 761.98, 750.88, 895.74, 928.27, 923.38, 970.85, 1035.34, 1063.94, 1079.4, 995.85, 863.88, 949.13, 935.75, 891.74, 995.72, 981.46, 1087.82, 1020.6, 1043.03, 1133.82, 1211.19, 1051.61, 1048.35, 1213.37, 1132.16, 1145.1, 1154.11, 1032.12, 975.41, 984.75, 938.38, 948.8, 991.64, 979.3, 937.0, 983.12, 904.28, 853.2, 848.95, 865.46, 970.82, 959.48, 990.21, 920.95], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+        </is>
+      </c>
+      <c r="S10" t="n">
+        <v>920.95</v>
       </c>
     </row>
     <row r="11">
@@ -1073,7 +1105,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1081,10 +1113,10 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.588</v>
+        <v>0.603</v>
       </c>
       <c r="E11" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F11" t="n">
         <v>50</v>
@@ -1124,8 +1156,11 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [392.43, 405.94, 405.55, 396.73, 398.68, 399.24, 407.82, 395.01, 391.2, 395.56, 399.27, 392.78, 380.3, 367.96, 380.85, 383.03, 385.95, 372.11, 361.83, 355.28, 371.75, 381.26, 360.59, 352.82, 346.65, 343.25, 345.62, 348.95, 352.42, 364.2, 391.95, 388.9, 400.62, 392.5, 386.42, 387.51, 373.72, 376.3, 378.67, 376.02, 372.8, 381.63, 390.82, 392.51, 389.37, 398.73, 411.79, 428.35, 445.0, 433.45, 445.27, 443.3, 422.24, 409.99, 404.11, 417.26, 417.85, 426.01, 433.59, 440.36, 442.1, 435.79, 415.88, 423.74, 423.7, 418.45, 391.0, 408.95, 396.68, 381.59, 399.15, 406.43, 411.15, 404.66, 396.38, 400.49, 405.05, 381.61, 375.53, 375.12, 379.71, 411.84, 420.6, 425.3, 393.45, 419.77, 402.9, 394.06, 406.55, 407.76, 394.76, 396.18, 394.46, 391.06, 380.84, 369.57, 378.93, 374.01, 319.69, 313.03], 'signals': ['BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
-        </is>
+          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [392.43, 405.94, 405.55, 396.73, 398.68, 399.24, 407.82, 395.01, 391.2, 395.56, 399.27, 392.78, 380.3, 367.96, 380.85, 383.03, 385.95, 372.11, 361.83, 355.28, 371.75, 381.26, 360.59, 352.82, 346.65, 343.25, 345.62, 348.95, 352.42, 364.2, 391.95, 388.9, 400.62, 392.5, 386.42, 387.51, 373.72, 376.3, 378.67, 376.02, 372.8, 381.63, 390.82, 392.51, 389.37, 398.73, 411.79, 428.35, 445.0, 433.45, 445.27, 443.3, 422.24, 409.99, 404.11, 417.26, 417.85, 426.01, 433.59, 440.36, 442.1, 435.79, 415.88, 423.74, 423.7, 418.45, 391.0, 408.95, 396.68, 381.59, 399.15, 406.43, 411.15, 404.66, 396.38, 400.49, 405.05, 381.61, 375.53, 375.12, 379.71, 411.84, 420.6, 425.3, 393.45, 419.77, 402.9, 394.06, 406.55, 407.76, 394.76, 396.18, 394.46, 391.06, 380.84, 369.57, 378.93, 374.01, 319.69, 313.03], 'signals': ['BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+        </is>
+      </c>
+      <c r="S11" t="n">
+        <v>313.03</v>
       </c>
     </row>
     <row r="12">
@@ -1135,7 +1170,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1143,10 +1178,10 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.315</v>
+        <v>0.282</v>
       </c>
       <c r="E12" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F12" t="n">
         <v>70</v>
@@ -1186,8 +1221,11 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [97.7, 98.66, 99.17, 99.02, 98.32, 96.94, 94.89, 94.31, 95.31, 95.2, 94.36, 94.7, 91.74, 91.82, 93.38, 90.92, 92.28, 93.32, 93.43, 92.97, 96.15, 95.55, 98.66, 98.93, 98.82, 99.39, 102.05, 103.01, 103.16, 106.28, 107.71, 107.79, 97.31, 94.83, 92.58, 93.24, 92.82, 92.44, 91.37, 92.27, 92.12, 93.61, 92.06, 91.02, 87.89, 88.27, 88.25, 87.49, 85.45, 87.66, 87.56, 86.94, 87.02, 89.65, 89.33, 88.09, 89.3, 88.6, 87.68, 87.35, 86.36, 86.02, 85.85, 83.33, 81.52, 81.56, 82.18, 82.64, 81.41, 82.0, 81.27, 80.34, 81.67, 78.72, 76.96, 77.38, 72.88, 72.82, 71.84, 70.9, 73.81, 73.78, 71.4, 74.19, 77.65, 76.02, 76.18, 75.59, 75.47, 73.37, 73.83, 73.53, 73.68, 74.35, 68.95, 67.6, 68.67, 68.53, 68.89, 70.09], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
-        </is>
+          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [97.7, 98.66, 99.17, 99.02, 98.32, 96.94, 94.89, 94.31, 95.31, 95.2, 94.36, 94.7, 91.74, 91.82, 93.38, 90.92, 92.28, 93.32, 93.43, 92.97, 96.15, 95.55, 98.66, 98.93, 98.82, 99.39, 102.05, 103.01, 103.16, 106.28, 107.71, 107.79, 97.31, 94.83, 92.58, 93.24, 92.82, 92.44, 91.37, 92.27, 92.12, 93.61, 92.06, 91.02, 87.89, 88.27, 88.25, 87.49, 85.45, 87.66, 87.56, 86.94, 87.02, 89.65, 89.33, 88.09, 89.3, 88.6, 87.68, 87.35, 86.36, 86.02, 85.85, 83.33, 81.52, 81.56, 82.18, 82.64, 81.41, 82.0, 81.27, 80.34, 81.67, 78.72, 76.96, 77.38, 72.88, 72.82, 71.84, 70.9, 73.81, 73.78, 71.4, 74.19, 77.65, 76.02, 76.18, 75.59, 75.47, 73.37, 73.83, 73.53, 73.68, 74.35, 68.95, 67.6, 68.67, 68.53, 68.89, 70.09], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+        </is>
+      </c>
+      <c r="S12" t="n">
+        <v>70.09</v>
       </c>
     </row>
     <row r="13">
@@ -1197,7 +1235,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1205,10 +1243,10 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.576</v>
       </c>
       <c r="E13" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F13" t="n">
         <v>20</v>
@@ -1217,16 +1255,16 @@
         <v>40</v>
       </c>
       <c r="H13" t="n">
-        <v>446</v>
+        <v>694</v>
       </c>
       <c r="I13" t="n">
-        <v>8.9</v>
+        <v>13.9</v>
       </c>
       <c r="J13" t="n">
         <v>-16.5</v>
       </c>
       <c r="K13" t="n">
-        <v>25.4</v>
+        <v>30.4</v>
       </c>
       <c r="L13" t="n">
         <v>5000</v>
@@ -1238,18 +1276,21 @@
         <v>3</v>
       </c>
       <c r="O13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P13" t="n">
         <v>3</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [147.22, 153.19, 152.67, 157.16, 156.43, 151.14, 151.6, 153.5, 150.95, 152.72, 155.08, 152.77, 155.68, 150.68, 160.84, 154.78, 154.96, 147.56, 143.06, 137.55, 146.28, 146.49, 148.46, 147.93, 150.07, 140.76, 130.49, 128.06, 132.37, 135.7, 142.15, 142.76, 146.39, 145.89, 145.97, 152.62, 141.57, 143.09, 143.1, 141.18, 137.97, 139.11, 144.07, 146.03, 135.91, 133.79, 137.05, 137.8, 136.89, 136.0, 130.05, 133.73, 133.99, 135.14, 135.26, 137.15, 137.41, 136.88, 136.6, 132.51, 143.34, 156.54, 160.65, 152.17, 142.2, 141.7, 135.53, 136.47, 132.07, 130.21, 131.08, 127.99, 134.71, 133.25, 130.63, 128.47, 119.5, 116.7, 113.5, 107.27, 112.93, 115.7, 116.67, 125.73, 129.3, 132.54, 134.37, 132.22, 129.04, 126.79, 130.04, 133.72, 133.76, 134.44, 132.38, 134.85, 132.66, 124.57, 123.37, 122.92], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
-        </is>
+          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [147.22, 153.19, 152.67, 157.16, 156.43, 151.14, 151.6, 153.5, 150.95, 152.72, 155.08, 152.77, 155.68, 150.68, 160.84, 154.78, 154.96, 147.56, 143.06, 137.55, 146.28, 146.49, 148.46, 147.93, 150.07, 140.76, 130.49, 128.06, 132.37, 135.7, 142.15, 142.76, 146.39, 145.89, 145.97, 152.62, 141.57, 143.09, 143.1, 141.18, 137.97, 139.11, 144.07, 146.03, 135.91, 133.79, 137.05, 137.8, 136.89, 136.0, 130.05, 133.73, 133.99, 135.14, 135.26, 137.15, 137.41, 136.88, 136.6, 132.51, 143.34, 156.54, 160.65, 152.17, 142.2, 141.7, 135.53, 136.47, 132.07, 130.21, 131.08, 127.99, 134.71, 133.25, 130.63, 128.47, 119.5, 116.7, 113.5, 107.27, 112.93, 115.7, 116.67, 125.73, 129.3, 132.54, 134.37, 132.22, 129.04, 126.79, 130.04, 133.72, 133.76, 134.44, 132.38, 134.85, 132.66, 124.57, 123.37, 122.92], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+        </is>
+      </c>
+      <c r="S13" t="n">
+        <v>122.92</v>
       </c>
     </row>
     <row r="14">
@@ -1267,7 +1308,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.14</v>
+        <v>0.094</v>
       </c>
       <c r="E14" t="n">
         <v>53</v>
@@ -1313,6 +1354,9 @@
           <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [195.06, 192.1, 200.37, 201.09, 197.78, 193.92, 193.15, 198.27, 191.85, 197.34, 194.32, 193.36, 194.0, 194.39, 194.19, 182.09, 181.04, 184.7, 178.4, 184.09, 185.72, 185.3, 186.23, 184.09, 182.03, 175.48, 170.41, 164.54, 172.38, 170.87, 177.14, 180.75, 181.67, 185.79, 186.63, 189.31, 172.85, 177.7, 179.72, 180.85, 180.75, 176.08, 183.35, 185.0, 186.51, 180.72, 185.86, 181.35, 177.03, 170.87, 165.41, 167.15, 173.06, 179.02, 178.96, 179.64, 175.86, 179.61, 178.62, 177.05, 175.72, 190.61, 209.06, 200.32, 190.12, 188.26, 185.18, 182.08, 174.9, 170.48, 166.45, 165.89, 164.55, 161.71, 155.02, 151.78, 150.12, 153.42, 152.76, 150.19, 158.37, 157.93, 156.66, 163.23, 166.11, 165.65, 169.52, 166.58, 162.5, 163.32, 171.22, 167.56, 167.0, 172.68, 170.77, 173.79, 170.06, 163.0, 156.93, 163.66], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
+      <c r="S14" t="n">
+        <v>163.66</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1329,28 +1373,28 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.727</v>
+        <v>0.65</v>
       </c>
       <c r="E15" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="F15" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="G15" t="n">
         <v>54.5</v>
       </c>
       <c r="H15" t="n">
-        <v>1805</v>
+        <v>1548</v>
       </c>
       <c r="I15" t="n">
-        <v>36.1</v>
+        <v>31</v>
       </c>
       <c r="J15" t="n">
         <v>87.3</v>
       </c>
       <c r="K15" t="n">
-        <v>-51.2</v>
+        <v>-56.3</v>
       </c>
       <c r="L15" t="n">
         <v>5000</v>
@@ -1359,21 +1403,24 @@
         <v>27</v>
       </c>
       <c r="N15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O15" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="P15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.3</v>
+        <v>1.5</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [97.86, 101.92, 106.54, 107.25, 108.53, 109.08, 110.51, 110.39, 110.44, 105.96, 108.3, 108.95, 107.04, 102.25, 103.33, 98.25, 96.46, 98.15, 92.39, 95.01, 97.6, 98.33, 99.78, 99.65, 105.81, 106.63, 98.67, 94.75, 100.56, 99.62, 102.79, 104.55, 105.99, 108.29, 112.4, 116.67, 111.35, 112.03, 113.65, 113.75, 113.1, 111.44, 113.91, 117.31, 119.13, 117.02, 126.43, 131.94, 135.57, 136.54, 140.64, 144.99, 148.52, 154.71, 154.22, 162.53, 162.06, 165.87, 167.89, 161.34, 167.75, 182.75, 195.54, 192.24, 186.9, 179.77, 167.76, 164.7, 161.23, 161.93, 172.88, 170.7, 173.23, 169.87, 170.74, 171.21, 168.86, 170.23, 168.26, 169.66, 175.27, 185.73, 190.79, 193.18, 193.98, 199.38, 194.62, 191.12, 198.4, 187.18, 187.91, 210.73, 206.77, 203.76, 203.08, 198.49, 191.15, 188.42, 183.42, 183.28], 'signals': ['FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT']}</t>
-        </is>
+          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [97.86, 101.92, 106.54, 107.25, 108.53, 109.08, 110.51, 110.39, 110.44, 105.96, 108.3, 108.95, 107.04, 102.25, 103.33, 98.25, 96.46, 98.15, 92.39, 95.01, 97.6, 98.33, 99.78, 99.65, 105.81, 106.63, 98.67, 94.75, 100.56, 99.62, 102.79, 104.55, 105.99, 108.29, 112.4, 116.67, 111.35, 112.03, 113.65, 113.75, 113.1, 111.44, 113.91, 117.31, 119.13, 117.02, 126.43, 131.94, 135.57, 136.54, 140.64, 144.99, 148.52, 154.71, 154.22, 162.53, 162.06, 165.87, 167.89, 161.34, 167.75, 182.75, 195.54, 192.24, 186.9, 179.77, 167.76, 164.7, 161.23, 161.93, 172.88, 170.7, 173.23, 169.87, 170.74, 171.21, 168.86, 170.23, 168.26, 169.66, 175.27, 185.73, 190.79, 193.18, 193.98, 199.38, 194.62, 191.12, 198.4, 187.18, 187.91, 210.73, 206.77, 203.76, 203.08, 198.49, 191.15, 188.42, 183.42, 183.28], 'signals': ['BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD']}</t>
+        </is>
+      </c>
+      <c r="S15" t="n">
+        <v>183.28</v>
       </c>
     </row>
     <row r="16">
@@ -1383,36 +1430,36 @@
         </is>
       </c>
       <c r="B16" t="n">
+        <v>64</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0.303</v>
+      </c>
+      <c r="E16" t="n">
         <v>60</v>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>DOWN</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>0.326</v>
-      </c>
-      <c r="E16" t="n">
-        <v>56</v>
-      </c>
       <c r="F16" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G16" t="n">
         <v>65</v>
       </c>
       <c r="H16" t="n">
-        <v>704</v>
+        <v>768</v>
       </c>
       <c r="I16" t="n">
-        <v>14.1</v>
+        <v>15.4</v>
       </c>
       <c r="J16" t="n">
         <v>18.8</v>
       </c>
       <c r="K16" t="n">
-        <v>-4.7</v>
+        <v>-3.4</v>
       </c>
       <c r="L16" t="n">
         <v>5000</v>
@@ -1421,21 +1468,24 @@
         <v>14</v>
       </c>
       <c r="N16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O16" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q16" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [297.39, 296.53, 290.75, 286.71, 287.15, 285.97, 284.77, 280.19, 280.73, 283.43, 284.15, 284.99, 285.22, 283.82, 287.14, 289.61, 292.6, 288.87, 280.14, 281.06, 291.35, 292.56, 291.79, 294.12, 296.07, 306.59, 308.94, 308.48, 312.27, 309.72, 304.56, 308.56, 308.9, 315.57, 311.6, 311.62, 310.29, 306.9, 310.23, 310.05, 307.86, 311.83, 311.07, 306.27, 308.01, 313.49, 304.9, 300.75, 298.65, 303.51, 298.9, 298.57, 296.47, 299.38, 294.37, 300.63, 301.64, 305.01, 305.36, 297.94, 295.4, 297.97, 295.25, 299.61, 299.5, 309.5, 310.97, 309.71, 311.3, 307.75, 312.08, 319.28, 317.97, 329.65, 331.96, 323.76, 329.99, 332.64, 331.95, 333.62, 327.57, 327.91, 325.86, 332.57, 332.97, 337.72, 339.22, 330.62, 335.47, 336.47, 334.53, 342.89, 346.91, 343.15, 341.1, 338.87, 345.23, 348.21, 349.9, 353.21], 'signals': ['FLAT', 'BUY', 'SELL', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'SELL', 'BUY', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
-        </is>
+          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [297.39, 296.53, 290.75, 286.71, 287.15, 285.97, 284.77, 280.19, 280.73, 283.43, 284.15, 284.99, 285.22, 283.82, 287.14, 289.61, 292.6, 288.87, 280.14, 281.06, 291.35, 292.56, 291.79, 294.12, 296.07, 306.59, 308.94, 308.48, 312.27, 309.72, 304.56, 308.56, 308.9, 315.57, 311.6, 311.62, 310.29, 306.9, 310.23, 310.05, 307.86, 311.83, 311.07, 306.27, 308.01, 313.49, 304.9, 300.75, 298.65, 303.51, 298.9, 298.57, 296.47, 299.38, 294.37, 300.63, 301.64, 305.01, 305.36, 297.94, 295.4, 297.97, 295.25, 299.61, 299.5, 309.5, 310.97, 309.71, 311.3, 307.75, 312.08, 319.28, 317.97, 329.65, 331.96, 323.76, 329.99, 332.64, 331.95, 333.62, 327.57, 327.91, 325.86, 332.57, 332.97, 337.72, 339.22, 330.62, 335.47, 336.47, 334.53, 342.89, 346.91, 343.15, 341.1, 338.87, 345.23, 348.21, 349.9, 353.21], 'signals': ['FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+        </is>
+      </c>
+      <c r="S16" t="n">
+        <v>353.21</v>
       </c>
     </row>
     <row r="17">
@@ -1445,7 +1495,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1453,7 +1503,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.585</v>
+        <v>0.592</v>
       </c>
       <c r="E17" t="n">
         <v>60</v>
@@ -1499,6 +1549,9 @@
           <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [858.8, 863.44, 831.79, 817.82, 828.38, 830.15, 820.15, 784.06, 778.78, 791.28, 803.5, 801.95, 805.95, 809.96, 827.62, 832.05, 838.15, 819.03, 799.37, 804.06, 842.28, 856.44, 859.25, 862.25, 860.36, 901.78, 899.75, 903.82, 886.88, 905.64, 895.54, 896.05, 921.89, 937.61, 922.48, 930.74, 927.21, 922.84, 933.7, 922.48, 901.63, 919.72, 919.66, 899.31, 914.86, 933.24, 921.81, 932.37, 940.71, 941.75, 951.23, 964.71, 944.31, 942.21, 924.66, 977.81, 983.83, 992.36, 990.16, 992.1, 1003.95, 1021.06, 1048.58, 1064.58, 1041.02, 1092.61, 1038.68, 1045.0, 1032.01, 1001.29, 1035.64, 1062.75, 1076.17, 1090.67, 1099.14, 1096.56, 1106.37, 1094.44, 1076.91, 1065.09, 1019.61, 1020.21, 1011.37, 1019.61, 1021.0, 1055.29, 1042.98, 1029.64, 1055.97, 1055.18, 1045.91, 1140.0, 1152.07, 1095.46, 1065.22, 1055.03, 1085.56, 1098.2, 1074.72, 1061.23], 'signals': ['BUY', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
+      <c r="S17" t="n">
+        <v>1061.23</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1515,10 +1568,10 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.288</v>
+        <v>0.235</v>
       </c>
       <c r="E18" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F18" t="n">
         <v>60</v>
@@ -1527,16 +1580,16 @@
         <v>50</v>
       </c>
       <c r="H18" t="n">
-        <v>-24</v>
+        <v>503</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.5</v>
+        <v>10.1</v>
       </c>
       <c r="J18" t="n">
         <v>-13.2</v>
       </c>
       <c r="K18" t="n">
-        <v>12.7</v>
+        <v>23.3</v>
       </c>
       <c r="L18" t="n">
         <v>5000</v>
@@ -1545,21 +1598,24 @@
         <v>31</v>
       </c>
       <c r="N18" t="n">
+        <v>5</v>
+      </c>
+      <c r="O18" t="n">
         <v>4</v>
       </c>
-      <c r="O18" t="n">
-        <v>3</v>
-      </c>
       <c r="P18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q18" t="n">
         <v>1.8</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [182.36, 208.93, 205.71, 197.22, 199.79, 196.52, 198.63, 193.23, 195.53, 203.32, 210.23, 202.29, 202.91, 197.5, 200.62, 181.04, 181.1, 173.38, 161.14, 160.79, 174.61, 172.99, 171.46, 174.79, 175.18, 175.09, 169.02, 167.85, 174.53, 184.41, 195.9, 199.83, 206.33, 211.63, 195.95, 206.24, 197.93, 199.77, 196.68, 194.1, 181.73, 187.77, 191.25, 202.99, 197.75, 197.96, 192.96, 201.16, 216.6, 207.64, 201.8, 212.01, 195.43, 189.44, 193.45, 191.29, 193.56, 184.99, 180.01, 173.78, 182.25, 189.03, 182.61, 173.99, 163.22, 164.13, 152.4, 162.11, 155.5, 153.97, 160.43, 159.78, 169.62, 169.27, 164.92, 163.26, 164.84, 158.18, 150.11, 142.52, 149.06, 151.65, 146.19, 159.24, 165.48, 168.87, 163.51, 159.36, 158.44, 159.07, 157.37, 161.5, 167.21, 160.49, 157.12, 160.43, 175.85, 166.12, 161.16, 158.29], 'signals': ['FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
-        </is>
+          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [182.36, 208.93, 205.71, 197.22, 199.79, 196.52, 198.63, 193.23, 195.53, 203.32, 210.23, 202.29, 202.91, 197.5, 200.62, 181.04, 181.1, 173.38, 161.14, 160.79, 174.61, 172.99, 171.46, 174.79, 175.18, 175.09, 169.02, 167.85, 174.53, 184.41, 195.9, 199.83, 206.33, 211.63, 195.95, 206.24, 197.93, 199.77, 196.68, 194.1, 181.73, 187.77, 191.25, 202.99, 197.75, 197.96, 192.96, 201.16, 216.6, 207.64, 201.8, 212.01, 195.43, 189.44, 193.45, 191.29, 193.56, 184.99, 180.01, 173.78, 182.25, 189.03, 182.61, 173.99, 163.22, 164.13, 152.4, 162.11, 155.5, 153.97, 160.43, 159.78, 169.62, 169.27, 164.92, 163.26, 164.84, 158.18, 150.11, 142.52, 149.06, 151.65, 146.19, 159.24, 165.48, 168.87, 163.51, 159.36, 158.44, 159.07, 157.37, 161.5, 167.21, 160.49, 157.12, 160.43, 175.85, 166.12, 161.16, 158.29], 'signals': ['BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+        </is>
+      </c>
+      <c r="S18" t="n">
+        <v>158.29</v>
       </c>
     </row>
     <row r="19">
@@ -1569,7 +1625,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1577,7 +1633,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.257</v>
+        <v>0.239</v>
       </c>
       <c r="E19" t="n">
         <v>54</v>
@@ -1623,6 +1679,9 @@
           <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [1006.0, 1001.85, 981.57, 988.63, 1006.66, 999.63, 998.12, 975.57, 983.39, 987.42, 928.75, 916.47, 915.92, 905.14, 908.99, 901.47, 914.74, 895.46, 876.73, 885.11, 918.19, 952.88, 933.97, 925.47, 929.49, 951.66, 953.55, 937.86, 927.95, 920.91, 903.47, 902.44, 925.44, 918.32, 901.47, 919.9, 916.07, 882.44, 866.78, 872.5, 849.75, 932.99, 961.67, 966.27, 987.17, 985.35, 973.28, 946.82, 965.33, 988.17, 1014.0, 1004.97, 1004.92, 988.09, 1021.41, 1018.87, 1041.65, 1065.0, 1064.74, 1082.92, 1126.8, 1105.0, 1082.2, 1064.15, 1078.78, 1125.27, 1131.42, 1149.15, 1144.68, 1136.37, 1160.95, 1133.0, 1129.35, 1122.5, 1112.0, 1098.57, 1102.08, 1107.08, 1117.26, 1127.69, 1208.12, 1229.93, 1199.43, 1191.74, 1213.91, 1200.06, 1235.56, 1215.83, 1216.95, 1188.58, 1181.87, 1152.54, 1156.63, 1169.17, 1179.11, 1146.9, 1175.41, 1163.01, 1185.87, 1196.03], 'signals': ['BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
+      <c r="S19" t="n">
+        <v>1196.03</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1631,7 +1690,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1639,10 +1698,10 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F20" t="n">
         <v>50</v>
@@ -1682,8 +1741,11 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [224.12, 227.31, 222.06, 231.11, 225.0, 217.76, 214.1, 204.76, 209.89, 213.47, 210.82, 205.99, 201.18, 195.12, 198.41, 196.42, 199.61, 194.36, 190.52, 189.21, 199.03, 207.32, 208.22, 212.3, 210.0, 217.8, 220.06, 217.63, 222.14, 223.77, 223.93, 218.88, 223.38, 225.08, 219.16, 231.28, 234.15, 232.44, 231.33, 230.72, 224.11, 229.03, 227.38, 221.3, 224.38, 229.93, 231.03, 237.36, 238.21, 236.87, 240.6, 229.21, 220.49, 220.61, 215.01, 222.2, 219.61, 219.02, 218.9, 224.3, 228.78, 231.15, 224.3, 217.7, 210.58, 217.42, 215.45, 215.92, 214.51, 209.0, 221.63, 219.05, 228.95, 227.49, 225.63, 222.72, 220.83, 216.71, 220.25, 218.12, 217.25, 214.69, 216.47, 218.58, 226.49, 234.54, 231.68, 224.95, 223.11, 222.28, 215.51, 217.11, 218.12, 214.34, 214.03, 209.48, 204.8, 208.65, 209.23, 209.52], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
-        </is>
+          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [224.12, 227.31, 222.06, 231.11, 225.0, 217.76, 214.1, 204.76, 209.89, 213.47, 210.82, 205.99, 201.18, 195.12, 198.41, 196.42, 199.61, 194.36, 190.52, 189.21, 199.03, 207.32, 208.22, 212.3, 210.0, 217.8, 220.06, 217.63, 222.14, 223.77, 223.93, 218.88, 223.38, 225.08, 219.16, 231.28, 234.15, 232.44, 231.33, 230.72, 224.11, 229.03, 227.38, 221.3, 224.38, 229.93, 231.03, 237.36, 238.21, 236.87, 240.6, 229.21, 220.49, 220.61, 215.01, 222.2, 219.61, 219.02, 218.9, 224.3, 228.78, 231.15, 224.3, 217.7, 210.58, 217.42, 215.45, 215.92, 214.51, 209.0, 221.63, 219.05, 228.95, 227.49, 225.63, 222.72, 220.83, 216.71, 220.25, 218.12, 217.25, 214.69, 216.47, 218.58, 226.49, 234.54, 231.68, 224.95, 223.11, 222.28, 215.51, 217.11, 218.12, 214.34, 214.03, 209.48, 204.8, 208.65, 209.23, 209.52], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+        </is>
+      </c>
+      <c r="S20" t="n">
+        <v>209.52</v>
       </c>
     </row>
     <row r="21">
@@ -1693,18 +1755,18 @@
         </is>
       </c>
       <c r="B21" t="n">
+        <v>62</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UP  </t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0.523</v>
+      </c>
+      <c r="E21" t="n">
         <v>64</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UP  </t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>0.529</v>
-      </c>
-      <c r="E21" t="n">
-        <v>67</v>
       </c>
       <c r="F21" t="n">
         <v>50</v>
@@ -1744,8 +1806,11 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [76.36, 76.65, 75.44, 75.13, 73.84, 72.36, 74.97, 72.97, 73.33, 74.66, 77.79, 76.66, 75.34, 73.89, 75.12, 72.34, 73.08, 70.55, 69.18, 69.91, 71.93, 71.71, 71.84, 72.17, 71.73, 72.38, 71.81, 70.48, 72.34, 72.91, 77.28, 76.48, 77.12, 77.49, 77.26, 75.58, 74.7, 74.64, 76.27, 74.11, 74.47, 74.61, 75.12, 73.93, 72.95, 79.17, 76.73, 75.45, 76.15, 76.36, 74.7, 74.69, 75.09, 75.08, 74.09, 74.6, 73.61, 71.82, 70.12, 70.73, 70.92, 70.4, 73.77, 71.62, 71.69, 72.21, 70.71, 70.06, 70.38, 68.61, 69.55, 68.85, 72.85, 73.25, 70.91, 71.64, 71.43, 69.67, 73.85, 72.25, 76.2, 75.5, 72.16, 72.66, 74.43, 72.42, 74.33, 73.6, 74.35, 74.54, 74.26, 72.08, 72.67, 74.04, 72.46, 72.17, 71.55, 70.33, 68.91, 65.94], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'SELL', 'BUY', 'SELL', 'BUY', 'SELL', 'FLAT', 'BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
-        </is>
+          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [76.36, 76.65, 75.44, 75.13, 73.84, 72.36, 74.97, 72.97, 73.33, 74.66, 77.79, 76.66, 75.34, 73.89, 75.12, 72.34, 73.08, 70.55, 69.18, 69.91, 71.93, 71.71, 71.84, 72.17, 71.73, 72.38, 71.81, 70.48, 72.34, 72.91, 77.28, 76.48, 77.12, 77.49, 77.26, 75.58, 74.7, 74.64, 76.27, 74.11, 74.47, 74.61, 75.12, 73.93, 72.95, 79.17, 76.73, 75.45, 76.15, 76.36, 74.7, 74.69, 75.09, 75.08, 74.09, 74.6, 73.61, 71.82, 70.12, 70.73, 70.92, 70.4, 73.77, 71.62, 71.69, 72.21, 70.71, 70.06, 70.38, 68.61, 69.55, 68.85, 72.85, 73.25, 70.91, 71.64, 71.43, 69.67, 73.85, 72.25, 76.2, 75.5, 72.16, 72.66, 74.43, 72.42, 74.33, 73.6, 74.35, 74.54, 74.26, 72.08, 72.67, 74.04, 72.46, 72.17, 71.55, 70.33, 68.91, 65.94], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'SELL', 'BUY', 'SELL', 'BUY', 'SELL', 'FLAT', 'BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+        </is>
+      </c>
+      <c r="S21" t="n">
+        <v>65.94</v>
       </c>
     </row>
   </sheetData>

--- a/demo_results.xlsx
+++ b/demo_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S21"/>
+  <dimension ref="A1:S24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -520,7 +520,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -528,54 +528,54 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.846</v>
+        <v>0.893</v>
       </c>
       <c r="E2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F2" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G2" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H2" t="n">
-        <v>609</v>
+        <v>1045</v>
       </c>
       <c r="I2" t="n">
-        <v>12.2</v>
+        <v>20.9</v>
       </c>
       <c r="J2" t="n">
-        <v>26.4</v>
+        <v>28.5</v>
       </c>
       <c r="K2" t="n">
-        <v>-14.2</v>
+        <v>-7.6</v>
       </c>
       <c r="L2" t="n">
         <v>5000</v>
       </c>
       <c r="M2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="P2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [263.51, 262.28, 260.05, 257.22, 259.64, 260.59, 260.57, 255.52, 249.89, 252.59, 254.0, 249.71, 248.73, 247.76, 251.26, 251.41, 252.39, 252.66, 248.57, 246.4, 253.56, 255.39, 255.68, 258.62, 253.27, 258.66, 260.25, 260.24, 258.96, 258.59, 266.18, 263.16, 269.98, 272.8, 265.93, 272.92, 273.18, 270.81, 267.36, 270.46, 269.92, 271.1, 279.88, 276.58, 283.92, 287.25, 287.18, 293.05, 292.68, 294.8, 298.87, 298.21, 300.23, 297.84, 298.97, 302.25, 304.99, 308.82, 308.33, 310.85, 312.51, 312.06, 306.31, 315.2, 310.26, 311.23, 307.34, 301.54, 290.55, 291.58, 295.63, 291.13, 296.42, 299.24, 295.95, 298.01, 297.01, 294.3, 293.08, 275.15, 283.78, 281.74, 289.36, 294.38, 308.63, 312.66, 310.66, 313.39, 316.22, 315.32, 317.31, 314.86, 327.5, 333.26, 333.74, 326.59, 327.74, 325.89, 321.66, 333.02], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [262.28, 260.05, 257.22, 259.64, 260.59, 260.57, 255.52, 249.89, 252.59, 254.0, 249.71, 248.73, 247.76, 251.26, 251.41, 252.39, 252.66, 248.57, 246.4, 253.56, 255.39, 255.68, 258.62, 253.27, 258.66, 260.25, 260.24, 258.96, 258.59, 266.18, 263.16, 269.98, 272.8, 265.93, 272.92, 273.18, 270.81, 267.36, 270.46, 269.92, 271.1, 279.88, 276.58, 283.92, 287.25, 287.18, 293.05, 292.68, 294.8, 298.87, 298.21, 300.23, 297.84, 298.97, 302.25, 304.99, 308.82, 308.33, 310.85, 312.51, 312.06, 306.31, 315.2, 310.26, 311.23, 307.34, 301.54, 290.55, 291.58, 295.63, 291.13, 296.42, 299.24, 295.95, 298.01, 297.01, 294.3, 293.08, 275.15, 283.78, 281.74, 289.36, 294.38, 308.63, 312.66, 310.66, 313.39, 316.22, 315.32, 317.31, 314.86, 327.5, 333.26, 333.74, 326.59, 327.74, 325.89, 321.66, 333.02, 336.91], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>333.02</v>
+        <v>336.91</v>
       </c>
     </row>
     <row r="3">
@@ -585,62 +585,62 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DOWN</t>
+          <t xml:space="preserve">UP  </t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.04</v>
+        <v>0.977</v>
       </c>
       <c r="E3" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="F3" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="G3" t="n">
-        <v>60</v>
+        <v>55.6</v>
       </c>
       <c r="H3" t="n">
-        <v>198</v>
+        <v>379</v>
       </c>
       <c r="I3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="J3" t="n">
+        <v>-3.8</v>
+      </c>
+      <c r="K3" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="L3" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M3" t="n">
+        <v>12</v>
+      </c>
+      <c r="N3" t="n">
         <v>4</v>
       </c>
-      <c r="J3" t="n">
-        <v>-5.3</v>
-      </c>
-      <c r="K3" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="L3" t="n">
-        <v>5000</v>
-      </c>
-      <c r="M3" t="n">
-        <v>13</v>
-      </c>
-      <c r="N3" t="n">
-        <v>3</v>
-      </c>
       <c r="O3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [403.06, 404.32, 409.79, 408.08, 408.53, 404.88, 404.0, 400.99, 394.7, 399.09, 398.55, 390.94, 388.18, 381.04, 382.17, 371.93, 370.24, 365.18, 356.0, 358.18, 369.37, 368.57, 372.65, 372.07, 371.49, 373.52, 372.26, 370.07, 383.54, 392.26, 410.33, 419.35, 421.88, 417.17, 423.24, 431.98, 414.85, 423.7, 423.9, 428.32, 423.54, 406.9, 413.54, 412.73, 410.49, 413.07, 419.86, 414.22, 411.77, 406.89, 404.33, 408.55, 421.01, 422.62, 416.52, 420.15, 419.09, 418.57, 416.03, 412.67, 426.99, 450.24, 460.52, 441.31, 427.34, 428.05, 416.67, 411.74, 403.41, 397.36, 390.34, 390.74, 399.76, 393.83, 378.91, 379.4, 367.34, 373.94, 365.46, 352.83, 372.97, 368.57, 373.02, 384.28, 390.49, 386.74, 388.84, 383.34, 384.36, 385.1, 390.99, 384.93, 395.63, 401.1, 393.82, 402.29, 397.75, 390.34, 381.58, 381.7], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [404.32, 409.79, 408.08, 408.53, 404.88, 404.0, 400.99, 394.7, 399.09, 398.55, 390.94, 388.18, 381.04, 382.17, 371.93, 370.24, 365.18, 356.0, 358.18, 369.37, 368.57, 372.65, 372.07, 371.49, 373.52, 372.26, 370.07, 383.54, 392.26, 410.33, 419.35, 421.88, 417.17, 423.24, 431.98, 414.85, 423.7, 423.9, 428.32, 423.54, 406.9, 413.54, 412.73, 410.49, 413.07, 419.86, 414.22, 411.77, 406.89, 404.33, 408.55, 421.01, 422.62, 416.52, 420.15, 419.09, 418.57, 416.03, 412.67, 426.99, 450.24, 460.52, 441.31, 427.34, 428.05, 416.67, 411.74, 403.41, 397.36, 390.34, 390.74, 399.76, 393.83, 378.91, 379.4, 367.34, 373.94, 365.46, 352.83, 372.97, 368.57, 373.02, 384.28, 390.49, 386.74, 388.84, 383.34, 384.36, 385.1, 390.99, 384.93, 395.63, 401.1, 393.82, 402.29, 397.75, 390.34, 381.58, 381.7, 389.1], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>381.7</v>
+        <v>389.1</v>
       </c>
     </row>
     <row r="4">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -658,28 +658,28 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.479</v>
+        <v>0.449</v>
       </c>
       <c r="E4" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F4" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="G4" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="H4" t="n">
-        <v>55</v>
+        <v>271</v>
       </c>
       <c r="I4" t="n">
-        <v>1.1</v>
+        <v>5.4</v>
       </c>
       <c r="J4" t="n">
-        <v>5.5</v>
+        <v>7.9</v>
       </c>
       <c r="K4" t="n">
-        <v>-4.4</v>
+        <v>-2.5</v>
       </c>
       <c r="L4" t="n">
         <v>5000</v>
@@ -691,21 +691,21 @@
         <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [303.19, 302.74, 300.49, 298.13, 306.18, 306.86, 308.52, 303.37, 302.1, 305.38, 310.73, 307.51, 306.95, 300.82, 301.88, 290.27, 290.76, 280.75, 274.18, 273.34, 287.39, 297.21, 295.59, 299.81, 305.28, 317.13, 318.3, 317.05, 321.12, 332.71, 336.92, 335.82, 341.48, 337.22, 332.09, 339.12, 338.69, 344.19, 350.13, 349.57, 349.73, 384.57, 385.46, 383.02, 388.2, 397.8, 397.75, 400.56, 388.41, 387.12, 402.38, 400.83, 396.54, 396.7, 387.43, 388.68, 387.43, 382.74, 388.65, 388.6, 389.9, 380.11, 376.15, 361.63, 358.78, 371.97, 368.31, 363.31, 364.26, 356.38, 357.77, 359.68, 369.35, 373.25, 363.79, 368.03, 349.68, 346.13, 345.29, 343.71, 337.39, 353.65, 357.37, 361.21, 359.91, 366.46, 367.03, 361.92, 358.89, 357.18, 352.51, 359.51, 370.92, 354.46, 346.77, 351.99, 347.15, 342.09, 317.69, 319.74], 'signals': ['BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [302.74, 300.49, 298.13, 306.18, 306.86, 308.52, 303.37, 302.1, 305.38, 310.73, 307.51, 306.95, 300.82, 301.88, 290.27, 290.76, 280.75, 274.18, 273.34, 287.39, 297.21, 295.59, 299.81, 305.28, 317.13, 318.3, 317.05, 321.12, 332.71, 336.92, 335.82, 341.48, 337.22, 332.09, 339.12, 338.69, 344.19, 350.13, 349.57, 349.73, 384.57, 385.46, 383.02, 388.2, 397.8, 397.75, 400.56, 388.41, 387.12, 402.38, 400.83, 396.54, 396.7, 387.43, 388.68, 387.43, 382.74, 388.65, 388.6, 389.9, 380.11, 376.15, 361.63, 358.78, 371.97, 368.31, 363.31, 364.26, 356.38, 357.77, 359.68, 369.35, 373.25, 363.79, 368.03, 349.68, 346.13, 345.29, 343.71, 337.39, 353.65, 357.37, 361.21, 359.91, 366.46, 367.03, 361.92, 358.89, 357.18, 352.51, 359.51, 370.92, 354.46, 346.77, 351.99, 347.15, 342.09, 317.69, 319.74, 326.56], 'signals': ['FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>319.74</v>
+        <v>326.56</v>
       </c>
     </row>
     <row r="5">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -723,28 +723,28 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.779</v>
+        <v>0.881</v>
       </c>
       <c r="E5" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F5" t="n">
         <v>40</v>
       </c>
       <c r="G5" t="n">
-        <v>71.40000000000001</v>
+        <v>83.3</v>
       </c>
       <c r="H5" t="n">
-        <v>797</v>
+        <v>788</v>
       </c>
       <c r="I5" t="n">
-        <v>15.9</v>
+        <v>15.8</v>
       </c>
       <c r="J5" t="n">
-        <v>11.2</v>
+        <v>6.7</v>
       </c>
       <c r="K5" t="n">
-        <v>4.7</v>
+        <v>9.1</v>
       </c>
       <c r="L5" t="n">
         <v>5000</v>
@@ -753,24 +753,24 @@
         <v>21</v>
       </c>
       <c r="N5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [208.73, 216.82, 218.94, 213.21, 213.49, 214.33, 212.65, 209.53, 207.67, 211.74, 215.2, 209.87, 208.76, 205.37, 210.14, 207.24, 211.71, 207.54, 199.34, 200.95, 208.27, 210.57, 209.77, 212.79, 213.77, 221.25, 233.65, 238.38, 239.89, 249.02, 248.5, 249.7, 250.56, 248.28, 249.91, 255.36, 255.08, 263.99, 261.12, 259.7, 263.04, 265.06, 268.26, 272.05, 273.55, 274.99, 271.17, 272.68, 268.99, 265.82, 270.13, 267.22, 264.14, 264.86, 259.34, 265.01, 268.46, 266.32, 265.29, 271.85, 274.0, 270.64, 261.26, 256.52, 250.02, 253.79, 246.03, 245.22, 244.19, 238.0, 241.51, 238.55, 246.02, 246.0, 237.5, 244.39, 232.79, 234.11, 234.27, 227.01, 232.69, 240.14, 238.34, 241.7, 242.67, 244.16, 245.98, 243.62, 247.04, 245.34, 247.31, 247.49, 254.96, 249.89, 247.23, 249.99, 247.55, 244.85, 233.66, 232.11], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [216.82, 218.94, 213.21, 213.49, 214.33, 212.65, 209.53, 207.67, 211.74, 215.2, 209.87, 208.76, 205.37, 210.14, 207.24, 211.71, 207.54, 199.34, 200.95, 208.27, 210.57, 209.77, 212.79, 213.77, 221.25, 233.65, 238.38, 239.89, 249.02, 248.5, 249.7, 250.56, 248.28, 249.91, 255.36, 255.08, 263.99, 261.12, 259.7, 263.04, 265.06, 268.26, 272.05, 273.55, 274.99, 271.17, 272.68, 268.99, 265.82, 270.13, 267.22, 264.14, 264.86, 259.34, 265.01, 268.46, 266.32, 265.29, 271.85, 274.0, 270.64, 261.26, 256.52, 250.02, 253.79, 246.03, 245.22, 244.19, 238.0, 241.51, 238.55, 246.02, 246.0, 237.5, 244.39, 232.79, 234.11, 234.27, 227.01, 232.69, 240.14, 238.34, 241.7, 242.67, 244.16, 245.98, 243.62, 247.04, 245.34, 247.31, 247.49, 254.96, 249.89, 247.23, 249.99, 247.55, 244.85, 233.66, 232.11, 231.39], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>232.11</v>
+        <v>231.39</v>
       </c>
     </row>
     <row r="6">
@@ -788,28 +788,28 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.121</v>
+        <v>0.073</v>
       </c>
       <c r="E6" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F6" t="n">
         <v>100</v>
       </c>
       <c r="G6" t="n">
-        <v>35.7</v>
+        <v>33.3</v>
       </c>
       <c r="H6" t="n">
-        <v>-547</v>
+        <v>422</v>
       </c>
       <c r="I6" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="J6" t="n">
         <v>-10.9</v>
       </c>
-      <c r="J6" t="n">
-        <v>-9</v>
-      </c>
       <c r="K6" t="n">
-        <v>-1.9</v>
+        <v>19.3</v>
       </c>
       <c r="L6" t="n">
         <v>5000</v>
@@ -818,24 +818,24 @@
         <v>8</v>
       </c>
       <c r="N6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [653.91, 666.54, 659.39, 643.71, 646.24, 652.91, 653.69, 637.04, 612.62, 626.87, 622.08, 615.11, 606.14, 593.11, 603.5, 592.37, 594.34, 547.03, 525.23, 535.88, 571.6, 578.69, 573.93, 572.49, 574.52, 611.85, 627.81, 629.28, 633.94, 661.88, 670.96, 676.24, 687.91, 670.29, 668.22, 674.1, 658.54, 674.4, 677.99, 670.72, 668.5, 611.34, 608.19, 609.84, 604.4, 612.31, 616.24, 609.07, 598.31, 602.44, 616.06, 617.86, 613.66, 610.64, 602.05, 604.5, 606.82, 609.69, 611.77, 634.67, 634.7, 631.92, 599.91, 597.08, 622.4, 626.99, 592.45, 584.85, 584.05, 570.45, 567.9, 566.45, 593.48, 600.21, 567.58, 577.22, 563.85, 562.2, 557.67, 542.87, 550.25, 562.6, 563.29, 612.91, 582.9, 600.29, 615.58, 603.12, 631.48, 669.21, 656.73, 661.04, 681.31, 664.54, 646.01, 645.85, 643.81, 627.17, 606.1, 595.19], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [666.54, 659.39, 643.71, 646.24, 652.91, 653.69, 637.04, 612.62, 626.87, 622.08, 615.11, 606.14, 593.11, 603.5, 592.37, 594.34, 547.03, 525.23, 535.88, 571.6, 578.69, 573.93, 572.49, 574.52, 611.85, 627.81, 629.28, 633.94, 661.88, 670.96, 676.24, 687.91, 670.29, 668.22, 674.1, 658.54, 674.4, 677.99, 670.72, 668.5, 611.34, 608.19, 609.84, 604.4, 612.31, 616.24, 609.07, 598.31, 602.44, 616.06, 617.86, 613.66, 610.64, 602.05, 604.5, 606.82, 609.69, 611.77, 634.67, 634.7, 631.92, 599.91, 597.08, 622.4, 626.99, 592.45, 584.85, 584.05, 570.45, 567.9, 566.45, 593.48, 600.21, 567.58, 577.22, 563.85, 562.2, 557.67, 542.87, 550.25, 562.6, 563.29, 612.91, 582.9, 600.29, 615.58, 603.12, 631.48, 669.21, 656.73, 661.04, 681.31, 664.54, 646.01, 645.85, 643.81, 627.17, 606.1, 595.19, 593.87], 'signals': ['BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>595.1900000000001</v>
+        <v>593.87</v>
       </c>
     </row>
     <row r="7">
@@ -845,7 +845,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -853,54 +853,54 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.348</v>
+        <v>0.318</v>
       </c>
       <c r="E7" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F7" t="n">
         <v>80</v>
       </c>
       <c r="G7" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="H7" t="n">
-        <v>682</v>
+        <v>570</v>
       </c>
       <c r="I7" t="n">
-        <v>13.6</v>
+        <v>11.4</v>
       </c>
       <c r="J7" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.4</v>
+        <v>3.9</v>
       </c>
       <c r="L7" t="n">
         <v>5000</v>
       </c>
       <c r="M7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N7" t="n">
         <v>4</v>
       </c>
       <c r="O7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P7" t="n">
         <v>4</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [179.83, 182.82, 183.12, 177.6, 182.43, 184.54, 185.81, 182.93, 180.04, 183.01, 181.72, 180.19, 178.35, 172.5, 175.44, 175.0, 178.47, 171.04, 167.32, 164.98, 174.2, 175.55, 177.18, 177.43, 177.89, 181.87, 183.7, 188.41, 189.09, 196.28, 198.64, 198.12, 201.45, 201.82, 199.65, 202.26, 199.41, 208.03, 216.36, 212.92, 209.01, 199.34, 198.22, 198.25, 196.27, 207.59, 211.25, 214.95, 219.18, 220.52, 225.57, 235.47, 225.06, 222.06, 220.35, 223.21, 219.25, 215.08, 214.61, 212.35, 214.0, 210.89, 224.1, 222.56, 214.5, 218.66, 205.1, 208.64, 208.19, 200.42, 204.87, 205.19, 212.45, 207.41, 204.65, 210.69, 208.65, 200.04, 199.0, 195.74, 192.53, 194.97, 200.09, 197.58, 194.83, 195.55, 196.93, 204.12, 202.78, 210.96, 203.53, 211.8, 212.5, 207.4, 202.81, 203.28, 207.29, 212.06, 208.76, 206.84], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [182.82, 183.12, 177.6, 182.43, 184.54, 185.81, 182.93, 180.04, 183.01, 181.72, 180.19, 178.35, 172.5, 175.44, 175.0, 178.47, 171.04, 167.32, 164.98, 174.2, 175.55, 177.18, 177.43, 177.89, 181.87, 183.7, 188.41, 189.09, 196.28, 198.64, 198.12, 201.45, 201.82, 199.65, 202.26, 199.41, 208.03, 216.36, 212.92, 209.01, 199.34, 198.22, 198.25, 196.27, 207.59, 211.25, 214.95, 219.18, 220.52, 225.57, 235.47, 225.06, 222.06, 220.35, 223.21, 219.25, 215.08, 214.61, 212.35, 214.0, 210.89, 224.1, 222.56, 214.5, 218.66, 205.1, 208.64, 208.19, 200.42, 204.87, 205.19, 212.45, 207.41, 204.65, 210.69, 208.65, 200.04, 199.0, 195.74, 192.53, 194.97, 200.09, 197.58, 194.83, 195.55, 196.93, 204.12, 202.78, 210.96, 203.53, 211.8, 212.5, 207.4, 202.81, 203.28, 207.29, 212.06, 208.76, 206.84, 196.51], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY']}</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>206.84</v>
+        <v>196.51</v>
       </c>
     </row>
     <row r="8">
@@ -914,58 +914,58 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DOWN</t>
+          <t xml:space="preserve">UP  </t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.485</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F8" t="n">
         <v>70</v>
       </c>
       <c r="G8" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="H8" t="n">
-        <v>2374</v>
+        <v>2104</v>
       </c>
       <c r="I8" t="n">
-        <v>47.5</v>
+        <v>42.1</v>
       </c>
       <c r="J8" t="n">
-        <v>173.3</v>
+        <v>144.9</v>
       </c>
       <c r="K8" t="n">
-        <v>-125.8</v>
+        <v>-102.8</v>
       </c>
       <c r="L8" t="n">
         <v>5000</v>
       </c>
       <c r="M8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>13</v>
+        <v>6.5</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [190.95, 202.07, 199.45, 192.43, 202.68, 203.23, 204.83, 197.74, 193.39, 196.58, 196.31, 199.46, 205.27, 201.33, 202.68, 205.37, 220.27, 203.77, 201.99, 196.04, 203.43, 210.21, 217.5, 220.18, 221.53, 231.82, 236.64, 245.04, 246.83, 255.07, 258.12, 278.26, 278.39, 274.95, 284.49, 303.46, 305.33, 347.81, 334.63, 323.21, 337.11, 354.49, 360.54, 341.54, 355.26, 421.39, 408.46, 455.19, 458.79, 448.29, 445.5, 449.7, 424.1, 420.99, 414.05, 447.58, 449.59, 467.51, 503.89, 495.54, 518.09, 516.1, 510.13, 521.54, 542.52, 523.2, 466.38, 490.33, 475.51, 452.4, 488.45, 511.57, 547.26, 507.29, 512.48, 537.37, 551.63, 519.85, 519.74, 532.57, 521.58, 539.49, 580.91, 540.88, 517.82, 552.05, 516.11, 517.41, 546.72, 557.89, 534.39, 548.13, 529.14, 500.94, 495.76, 503.57, 544.43, 552.33, 539.69, 521.95], 'signals': ['FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [202.07, 199.45, 192.43, 202.68, 203.23, 204.83, 197.74, 193.39, 196.58, 196.31, 199.46, 205.27, 201.33, 202.68, 205.37, 220.27, 203.77, 201.99, 196.04, 203.43, 210.21, 217.5, 220.18, 221.53, 231.82, 236.64, 245.04, 246.83, 255.07, 258.12, 278.26, 278.39, 274.95, 284.49, 303.46, 305.33, 347.81, 334.63, 323.21, 337.11, 354.49, 360.54, 341.54, 355.26, 421.39, 408.46, 455.19, 458.79, 448.29, 445.5, 449.7, 424.1, 420.99, 414.05, 447.58, 449.59, 467.51, 503.89, 495.54, 518.09, 516.1, 510.13, 521.54, 542.52, 523.2, 466.38, 490.33, 475.51, 452.4, 488.45, 511.57, 547.26, 507.29, 512.48, 537.37, 551.63, 519.85, 519.74, 532.57, 521.58, 539.49, 580.91, 540.88, 517.82, 552.05, 516.11, 517.41, 546.72, 557.89, 534.39, 548.13, 529.14, 500.94, 495.76, 503.57, 544.43, 552.33, 539.69, 521.95, 494.95], 'signals': ['FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>521.95</v>
+        <v>494.95</v>
       </c>
     </row>
     <row r="9">
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -983,28 +983,28 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.646</v>
+        <v>0.699</v>
       </c>
       <c r="E9" t="n">
         <v>52</v>
       </c>
       <c r="F9" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="G9" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="H9" t="n">
-        <v>159</v>
+        <v>289</v>
       </c>
       <c r="I9" t="n">
-        <v>3.2</v>
+        <v>5.8</v>
       </c>
       <c r="J9" t="n">
-        <v>22.1</v>
+        <v>21.1</v>
       </c>
       <c r="K9" t="n">
-        <v>-18.9</v>
+        <v>-15.3</v>
       </c>
       <c r="L9" t="n">
         <v>5000</v>
@@ -1013,24 +1013,24 @@
         <v>13</v>
       </c>
       <c r="N9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [312.69, 316.36, 331.55, 329.27, 344.48, 341.32, 340.32, 334.74, 320.98, 323.73, 320.13, 314.77, 318.67, 309.37, 322.0, 317.79, 318.31, 308.93, 300.2, 292.95, 309.02, 312.99, 314.05, 313.93, 333.44, 350.08, 354.35, 370.96, 379.15, 380.18, 396.09, 397.84, 405.9, 399.0, 401.53, 421.98, 419.28, 422.09, 417.54, 399.2, 404.81, 416.77, 420.61, 415.84, 426.68, 424.77, 411.91, 429.32, 427.75, 418.64, 416.13, 439.1, 424.52, 420.05, 410.42, 417.1, 413.91, 413.49, 421.34, 421.19, 425.91, 446.06, 459.24, 480.81, 478.47, 418.25, 385.12, 395.97, 391.54, 371.51, 384.96, 381.47, 393.32, 376.11, 392.28, 410.7, 392.13, 380.15, 382.07, 378.91, 365.02, 372.45, 377.75, 369.34, 360.45, 373.9, 370.78, 388.69, 401.11, 399.97, 384.05, 389.11, 394.28, 374.45, 370.83, 378.16, 386.5, 396.81, 392.47, 381.92], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [316.36, 331.55, 329.27, 344.48, 341.32, 340.32, 334.74, 320.98, 323.73, 320.13, 314.77, 318.67, 309.37, 322.0, 317.79, 318.31, 308.93, 300.2, 292.95, 309.02, 312.99, 314.05, 313.93, 333.44, 350.08, 354.35, 370.96, 379.15, 380.18, 396.09, 397.84, 405.9, 399.0, 401.53, 421.98, 419.28, 422.09, 417.54, 399.2, 404.81, 416.77, 420.61, 415.84, 426.68, 424.77, 411.91, 429.32, 427.75, 418.64, 416.13, 439.1, 424.52, 420.05, 410.42, 417.1, 413.91, 413.49, 421.34, 421.19, 425.91, 446.06, 459.24, 480.81, 478.47, 418.25, 385.12, 395.97, 391.54, 371.51, 384.96, 381.47, 393.32, 376.11, 392.28, 410.7, 392.13, 380.15, 382.07, 378.91, 365.02, 372.45, 377.75, 369.34, 360.45, 373.9, 370.78, 388.69, 401.11, 399.97, 384.05, 389.11, 394.28, 374.45, 370.83, 378.16, 386.5, 396.81, 392.47, 381.92, 383.22], 'signals': ['BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>381.92</v>
+        <v>383.22</v>
       </c>
     </row>
     <row r="10">
@@ -1040,7 +1040,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1048,28 +1048,28 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.413</v>
+        <v>0.389</v>
       </c>
       <c r="E10" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F10" t="n">
         <v>40</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H10" t="n">
-        <v>3327</v>
+        <v>2922</v>
       </c>
       <c r="I10" t="n">
-        <v>66.5</v>
+        <v>58.4</v>
       </c>
       <c r="J10" t="n">
-        <v>142.7</v>
+        <v>124.7</v>
       </c>
       <c r="K10" t="n">
-        <v>-76.2</v>
+        <v>-66.3</v>
       </c>
       <c r="L10" t="n">
         <v>5000</v>
@@ -1081,21 +1081,21 @@
         <v>2</v>
       </c>
       <c r="O10" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="P10" t="n">
         <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [379.46, 400.54, 396.82, 370.09, 389.1, 402.88, 418.45, 405.12, 425.89, 441.55, 461.43, 461.47, 444.02, 422.66, 404.12, 395.3, 381.87, 355.26, 357.02, 321.75, 337.79, 367.79, 366.18, 377.7, 377.52, 406.67, 421.45, 420.53, 426.49, 465.59, 456.16, 457.16, 455.0, 448.35, 449.31, 487.41, 481.65, 496.64, 524.48, 504.21, 518.38, 517.08, 542.13, 576.36, 640.1, 666.49, 646.53, 746.7, 795.21, 766.46, 803.51, 775.89, 724.55, 681.44, 698.63, 731.88, 761.98, 750.88, 895.74, 928.27, 923.38, 970.85, 1035.34, 1063.94, 1079.4, 995.85, 863.88, 949.13, 935.75, 891.74, 995.72, 981.46, 1087.82, 1020.6, 1043.03, 1133.82, 1211.19, 1051.61, 1048.35, 1213.37, 1132.16, 1145.1, 1154.11, 1032.12, 975.41, 984.75, 938.38, 948.8, 991.64, 979.3, 937.0, 983.12, 904.28, 853.2, 848.95, 865.46, 970.82, 959.48, 990.21, 920.95], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [400.54, 396.82, 370.09, 389.1, 402.88, 418.45, 405.12, 425.89, 441.55, 461.43, 461.47, 444.02, 422.66, 404.12, 395.3, 381.87, 355.26, 357.02, 321.75, 337.79, 367.79, 366.18, 377.7, 377.52, 406.67, 421.45, 420.53, 426.49, 465.59, 456.16, 457.16, 455.0, 448.35, 449.31, 487.41, 481.65, 496.64, 524.48, 504.21, 518.38, 517.08, 542.13, 576.36, 640.1, 666.49, 646.53, 746.7, 795.21, 766.46, 803.51, 775.89, 724.55, 681.44, 698.63, 731.88, 761.98, 750.88, 895.74, 928.27, 923.38, 970.85, 1035.34, 1063.94, 1079.4, 995.85, 863.88, 949.13, 935.75, 891.74, 995.72, 981.46, 1087.82, 1020.6, 1043.03, 1133.82, 1211.19, 1051.61, 1048.35, 1213.37, 1132.16, 1145.1, 1154.11, 1032.12, 975.41, 984.75, 938.38, 948.8, 991.64, 979.3, 937.0, 983.12, 904.28, 853.2, 848.95, 865.46, 970.82, 959.48, 990.21, 920.95, 900.2], 'signals': ['FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
       <c r="S10" t="n">
-        <v>920.95</v>
+        <v>900.2</v>
       </c>
     </row>
     <row r="11">
@@ -1105,62 +1105,62 @@
         </is>
       </c>
       <c r="B11" t="n">
+        <v>55</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UP  </t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.677</v>
+      </c>
+      <c r="E11" t="n">
         <v>52</v>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UP  </t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>0.603</v>
-      </c>
-      <c r="E11" t="n">
-        <v>50</v>
-      </c>
       <c r="F11" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>-949</v>
+        <v>-79</v>
       </c>
       <c r="I11" t="n">
-        <v>-19</v>
+        <v>-1.6</v>
       </c>
       <c r="J11" t="n">
-        <v>-20.2</v>
+        <v>-23.8</v>
       </c>
       <c r="K11" t="n">
-        <v>1.2</v>
+        <v>22.2</v>
       </c>
       <c r="L11" t="n">
         <v>5000</v>
       </c>
       <c r="M11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N11" t="n">
         <v>4</v>
       </c>
       <c r="O11" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="P11" t="n">
         <v>4</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [392.43, 405.94, 405.55, 396.73, 398.68, 399.24, 407.82, 395.01, 391.2, 395.56, 399.27, 392.78, 380.3, 367.96, 380.85, 383.03, 385.95, 372.11, 361.83, 355.28, 371.75, 381.26, 360.59, 352.82, 346.65, 343.25, 345.62, 348.95, 352.42, 364.2, 391.95, 388.9, 400.62, 392.5, 386.42, 387.51, 373.72, 376.3, 378.67, 376.02, 372.8, 381.63, 390.82, 392.51, 389.37, 398.73, 411.79, 428.35, 445.0, 433.45, 445.27, 443.3, 422.24, 409.99, 404.11, 417.26, 417.85, 426.01, 433.59, 440.36, 442.1, 435.79, 415.88, 423.74, 423.7, 418.45, 391.0, 408.95, 396.68, 381.59, 399.15, 406.43, 411.15, 404.66, 396.38, 400.49, 405.05, 381.61, 375.53, 375.12, 379.71, 411.84, 420.6, 425.3, 393.45, 419.77, 402.9, 394.06, 406.55, 407.76, 394.76, 396.18, 394.46, 391.06, 380.84, 369.57, 378.93, 374.01, 319.69, 313.03], 'signals': ['BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [405.94, 405.55, 396.73, 398.68, 399.24, 407.82, 395.01, 391.2, 395.56, 399.27, 392.78, 380.3, 367.96, 380.85, 383.03, 385.95, 372.11, 361.83, 355.28, 371.75, 381.26, 360.59, 352.82, 346.65, 343.25, 345.62, 348.95, 352.42, 364.2, 391.95, 388.9, 400.62, 392.5, 386.42, 387.51, 373.72, 376.3, 378.67, 376.02, 372.8, 381.63, 390.82, 392.51, 389.37, 398.73, 411.79, 428.35, 445.0, 433.45, 445.27, 443.3, 422.24, 409.99, 404.11, 417.26, 417.85, 426.01, 433.59, 440.36, 442.1, 435.79, 415.88, 423.74, 423.7, 418.45, 391.0, 408.95, 396.68, 381.59, 399.15, 406.43, 411.15, 404.66, 396.38, 400.49, 405.05, 381.61, 375.53, 375.12, 379.71, 411.84, 420.6, 425.3, 393.45, 419.77, 402.9, 394.06, 406.55, 407.76, 394.76, 396.18, 394.46, 391.06, 380.84, 369.57, 378.93, 374.01, 319.69, 313.03, 309.22], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
       <c r="S11" t="n">
-        <v>313.03</v>
+        <v>309.22</v>
       </c>
     </row>
     <row r="12">
@@ -1170,7 +1170,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1178,28 +1178,28 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.282</v>
+        <v>0.225</v>
       </c>
       <c r="E12" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F12" t="n">
         <v>70</v>
       </c>
       <c r="G12" t="n">
-        <v>35.7</v>
+        <v>26.7</v>
       </c>
       <c r="H12" t="n">
-        <v>-952</v>
+        <v>-1453</v>
       </c>
       <c r="I12" t="n">
-        <v>-19</v>
+        <v>-29.1</v>
       </c>
       <c r="J12" t="n">
-        <v>-28.3</v>
+        <v>-28.6</v>
       </c>
       <c r="K12" t="n">
-        <v>9.300000000000001</v>
+        <v>-0.5</v>
       </c>
       <c r="L12" t="n">
         <v>5000</v>
@@ -1208,24 +1208,24 @@
         <v>71</v>
       </c>
       <c r="N12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q12" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [97.7, 98.66, 99.17, 99.02, 98.32, 96.94, 94.89, 94.31, 95.31, 95.2, 94.36, 94.7, 91.74, 91.82, 93.38, 90.92, 92.28, 93.32, 93.43, 92.97, 96.15, 95.55, 98.66, 98.93, 98.82, 99.39, 102.05, 103.01, 103.16, 106.28, 107.71, 107.79, 97.31, 94.83, 92.58, 93.24, 92.82, 92.44, 91.37, 92.27, 92.12, 93.61, 92.06, 91.02, 87.89, 88.27, 88.25, 87.49, 85.45, 87.66, 87.56, 86.94, 87.02, 89.65, 89.33, 88.09, 89.3, 88.6, 87.68, 87.35, 86.36, 86.02, 85.85, 83.33, 81.52, 81.56, 82.18, 82.64, 81.41, 82.0, 81.27, 80.34, 81.67, 78.72, 76.96, 77.38, 72.88, 72.82, 71.84, 70.9, 73.81, 73.78, 71.4, 74.19, 77.65, 76.02, 76.18, 75.59, 75.47, 73.37, 73.83, 73.53, 73.68, 74.35, 68.95, 67.6, 68.67, 68.53, 68.89, 70.09], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [98.66, 99.17, 99.02, 98.32, 96.94, 94.89, 94.31, 95.31, 95.2, 94.36, 94.7, 91.74, 91.82, 93.38, 90.92, 92.28, 93.32, 93.43, 92.97, 96.15, 95.55, 98.66, 98.93, 98.82, 99.39, 102.05, 103.01, 103.16, 106.28, 107.71, 107.79, 97.31, 94.83, 92.58, 93.24, 92.82, 92.44, 91.37, 92.27, 92.12, 93.61, 92.06, 91.02, 87.89, 88.27, 88.25, 87.49, 85.45, 87.66, 87.56, 86.94, 87.02, 89.65, 89.33, 88.09, 89.3, 88.6, 87.68, 87.35, 86.36, 86.02, 85.85, 83.33, 81.52, 81.56, 82.18, 82.64, 81.41, 82.0, 81.27, 80.34, 81.67, 78.72, 76.96, 77.38, 72.88, 72.82, 71.84, 70.9, 73.81, 73.78, 71.4, 74.19, 77.65, 76.02, 76.18, 75.59, 75.47, 73.37, 73.83, 73.53, 73.68, 74.35, 68.95, 67.6, 68.67, 68.53, 68.89, 70.09, 70.4], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'SELL', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
       <c r="S12" t="n">
-        <v>70.09</v>
+        <v>70.40000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1235,7 +1235,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1243,34 +1243,34 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.576</v>
+        <v>0.512</v>
       </c>
       <c r="E13" t="n">
         <v>59</v>
       </c>
       <c r="F13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G13" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H13" t="n">
-        <v>694</v>
+        <v>796</v>
       </c>
       <c r="I13" t="n">
-        <v>13.9</v>
+        <v>15.9</v>
       </c>
       <c r="J13" t="n">
-        <v>-16.5</v>
+        <v>-14.1</v>
       </c>
       <c r="K13" t="n">
-        <v>30.4</v>
+        <v>30</v>
       </c>
       <c r="L13" t="n">
         <v>5000</v>
       </c>
       <c r="M13" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="N13" t="n">
         <v>3</v>
@@ -1286,11 +1286,11 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [147.22, 153.19, 152.67, 157.16, 156.43, 151.14, 151.6, 153.5, 150.95, 152.72, 155.08, 152.77, 155.68, 150.68, 160.84, 154.78, 154.96, 147.56, 143.06, 137.55, 146.28, 146.49, 148.46, 147.93, 150.07, 140.76, 130.49, 128.06, 132.37, 135.7, 142.15, 142.76, 146.39, 145.89, 145.97, 152.62, 141.57, 143.09, 143.1, 141.18, 137.97, 139.11, 144.07, 146.03, 135.91, 133.79, 137.05, 137.8, 136.89, 136.0, 130.05, 133.73, 133.99, 135.14, 135.26, 137.15, 137.41, 136.88, 136.6, 132.51, 143.34, 156.54, 160.65, 152.17, 142.2, 141.7, 135.53, 136.47, 132.07, 130.21, 131.08, 127.99, 134.71, 133.25, 130.63, 128.47, 119.5, 116.7, 113.5, 107.27, 112.93, 115.7, 116.67, 125.73, 129.3, 132.54, 134.37, 132.22, 129.04, 126.79, 130.04, 133.72, 133.76, 134.44, 132.38, 134.85, 132.66, 124.57, 123.37, 122.92], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [153.19, 152.67, 157.16, 156.43, 151.14, 151.6, 153.5, 150.95, 152.72, 155.08, 152.77, 155.68, 150.68, 160.84, 154.78, 154.96, 147.56, 143.06, 137.55, 146.28, 146.49, 148.46, 147.93, 150.07, 140.76, 130.49, 128.06, 132.37, 135.7, 142.15, 142.76, 146.39, 145.89, 145.97, 152.62, 141.57, 143.09, 143.1, 141.18, 137.97, 139.11, 144.07, 146.03, 135.91, 133.79, 137.05, 137.8, 136.89, 136.0, 130.05, 133.73, 133.99, 135.14, 135.26, 137.15, 137.41, 136.88, 136.6, 132.51, 143.34, 156.54, 160.65, 152.17, 142.2, 141.7, 135.53, 136.47, 132.07, 130.21, 131.08, 127.99, 134.71, 133.25, 130.63, 128.47, 119.5, 116.7, 113.5, 107.27, 112.93, 115.7, 116.67, 125.73, 129.3, 132.54, 134.37, 132.22, 129.04, 126.79, 130.04, 133.72, 133.76, 134.44, 132.38, 134.85, 132.66, 124.57, 123.37, 122.92, 131.53], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
       <c r="S13" t="n">
-        <v>122.92</v>
+        <v>131.53</v>
       </c>
     </row>
     <row r="14">
@@ -1300,7 +1300,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1308,16 +1308,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.094</v>
+        <v>0.06</v>
       </c>
       <c r="E14" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F14" t="n">
         <v>60</v>
       </c>
       <c r="G14" t="n">
-        <v>56.2</v>
+        <v>57.1</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1326,16 +1326,16 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>-16.1</v>
+        <v>-9.6</v>
       </c>
       <c r="K14" t="n">
-        <v>16.1</v>
+        <v>9.6</v>
       </c>
       <c r="L14" t="n">
         <v>5000</v>
       </c>
       <c r="M14" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1351,11 +1351,11 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [195.06, 192.1, 200.37, 201.09, 197.78, 193.92, 193.15, 198.27, 191.85, 197.34, 194.32, 193.36, 194.0, 194.39, 194.19, 182.09, 181.04, 184.7, 178.4, 184.09, 185.72, 185.3, 186.23, 184.09, 182.03, 175.48, 170.41, 164.54, 172.38, 170.87, 177.14, 180.75, 181.67, 185.79, 186.63, 189.31, 172.85, 177.7, 179.72, 180.85, 180.75, 176.08, 183.35, 185.0, 186.51, 180.72, 185.86, 181.35, 177.03, 170.87, 165.41, 167.15, 173.06, 179.02, 178.96, 179.64, 175.86, 179.61, 178.62, 177.05, 175.72, 190.61, 209.06, 200.32, 190.12, 188.26, 185.18, 182.08, 174.9, 170.48, 166.45, 165.89, 164.55, 161.71, 155.02, 151.78, 150.12, 153.42, 152.76, 150.19, 158.37, 157.93, 156.66, 163.23, 166.11, 165.65, 169.52, 166.58, 162.5, 163.32, 171.22, 167.56, 167.0, 172.68, 170.77, 173.79, 170.06, 163.0, 156.93, 163.66], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [192.1, 200.37, 201.09, 197.78, 193.92, 193.15, 198.27, 191.85, 197.34, 194.32, 193.36, 194.0, 194.39, 194.19, 182.09, 181.04, 184.7, 178.4, 184.09, 185.72, 185.3, 186.23, 184.09, 182.03, 175.48, 170.41, 164.54, 172.38, 170.87, 177.14, 180.75, 181.67, 185.79, 186.63, 189.31, 172.85, 177.7, 179.72, 180.85, 180.75, 176.08, 183.35, 185.0, 186.51, 180.72, 185.86, 181.35, 177.03, 170.87, 165.41, 167.15, 173.06, 179.02, 178.96, 179.64, 175.86, 179.61, 178.62, 177.05, 175.72, 190.61, 209.06, 200.32, 190.12, 188.26, 185.18, 182.08, 174.9, 170.48, 166.45, 165.89, 164.55, 161.71, 155.02, 151.78, 150.12, 153.42, 152.76, 150.19, 158.37, 157.93, 156.66, 163.23, 166.11, 165.65, 169.52, 166.58, 162.5, 163.32, 171.22, 167.56, 167.0, 172.68, 170.77, 173.79, 170.06, 163.0, 156.93, 163.66, 173.6], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
       <c r="S14" t="n">
-        <v>163.66</v>
+        <v>173.6</v>
       </c>
     </row>
     <row r="15">
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1373,28 +1373,28 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.65</v>
+        <v>0.664</v>
       </c>
       <c r="E15" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F15" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="G15" t="n">
-        <v>54.5</v>
+        <v>70</v>
       </c>
       <c r="H15" t="n">
-        <v>1548</v>
+        <v>428</v>
       </c>
       <c r="I15" t="n">
-        <v>31</v>
+        <v>8.6</v>
       </c>
       <c r="J15" t="n">
-        <v>87.3</v>
+        <v>76.7</v>
       </c>
       <c r="K15" t="n">
-        <v>-56.3</v>
+        <v>-68.09999999999999</v>
       </c>
       <c r="L15" t="n">
         <v>5000</v>
@@ -1416,11 +1416,11 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [97.86, 101.92, 106.54, 107.25, 108.53, 109.08, 110.51, 110.39, 110.44, 105.96, 108.3, 108.95, 107.04, 102.25, 103.33, 98.25, 96.46, 98.15, 92.39, 95.01, 97.6, 98.33, 99.78, 99.65, 105.81, 106.63, 98.67, 94.75, 100.56, 99.62, 102.79, 104.55, 105.99, 108.29, 112.4, 116.67, 111.35, 112.03, 113.65, 113.75, 113.1, 111.44, 113.91, 117.31, 119.13, 117.02, 126.43, 131.94, 135.57, 136.54, 140.64, 144.99, 148.52, 154.71, 154.22, 162.53, 162.06, 165.87, 167.89, 161.34, 167.75, 182.75, 195.54, 192.24, 186.9, 179.77, 167.76, 164.7, 161.23, 161.93, 172.88, 170.7, 173.23, 169.87, 170.74, 171.21, 168.86, 170.23, 168.26, 169.66, 175.27, 185.73, 190.79, 193.18, 193.98, 199.38, 194.62, 191.12, 198.4, 187.18, 187.91, 210.73, 206.77, 203.76, 203.08, 198.49, 191.15, 188.42, 183.42, 183.28], 'signals': ['BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [101.92, 106.54, 107.25, 108.53, 109.08, 110.51, 110.39, 110.44, 105.96, 108.3, 108.95, 107.04, 102.25, 103.33, 98.25, 96.46, 98.15, 92.39, 95.01, 97.6, 98.33, 99.78, 99.65, 105.81, 106.63, 98.67, 94.75, 100.56, 99.62, 102.79, 104.55, 105.99, 108.29, 112.4, 116.67, 111.35, 112.03, 113.65, 113.75, 113.1, 111.44, 113.91, 117.31, 119.13, 117.02, 126.43, 131.94, 135.57, 136.54, 140.64, 144.99, 148.52, 154.71, 154.22, 162.53, 162.06, 165.87, 167.89, 161.34, 167.75, 182.75, 195.54, 192.24, 186.9, 179.77, 167.76, 164.7, 161.23, 161.93, 172.88, 170.7, 173.23, 169.87, 170.74, 171.21, 168.86, 170.23, 168.26, 169.66, 175.27, 185.73, 190.79, 193.18, 193.98, 199.38, 194.62, 191.12, 198.4, 187.18, 187.91, 210.73, 206.77, 203.76, 203.08, 198.49, 191.15, 188.42, 183.42, 183.28, 180.11], 'signals': ['BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
       <c r="S15" t="n">
-        <v>183.28</v>
+        <v>180.11</v>
       </c>
     </row>
     <row r="16">
@@ -1430,7 +1430,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1438,10 +1438,10 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.303</v>
+        <v>0.274</v>
       </c>
       <c r="E16" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F16" t="n">
         <v>30</v>
@@ -1450,16 +1450,16 @@
         <v>65</v>
       </c>
       <c r="H16" t="n">
-        <v>768</v>
+        <v>724</v>
       </c>
       <c r="I16" t="n">
-        <v>15.4</v>
+        <v>14.5</v>
       </c>
       <c r="J16" t="n">
-        <v>18.8</v>
+        <v>20.1</v>
       </c>
       <c r="K16" t="n">
-        <v>-3.4</v>
+        <v>-5.6</v>
       </c>
       <c r="L16" t="n">
         <v>5000</v>
@@ -1468,24 +1468,24 @@
         <v>14</v>
       </c>
       <c r="N16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O16" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="P16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [297.39, 296.53, 290.75, 286.71, 287.15, 285.97, 284.77, 280.19, 280.73, 283.43, 284.15, 284.99, 285.22, 283.82, 287.14, 289.61, 292.6, 288.87, 280.14, 281.06, 291.35, 292.56, 291.79, 294.12, 296.07, 306.59, 308.94, 308.48, 312.27, 309.72, 304.56, 308.56, 308.9, 315.57, 311.6, 311.62, 310.29, 306.9, 310.23, 310.05, 307.86, 311.83, 311.07, 306.27, 308.01, 313.49, 304.9, 300.75, 298.65, 303.51, 298.9, 298.57, 296.47, 299.38, 294.37, 300.63, 301.64, 305.01, 305.36, 297.94, 295.4, 297.97, 295.25, 299.61, 299.5, 309.5, 310.97, 309.71, 311.3, 307.75, 312.08, 319.28, 317.97, 329.65, 331.96, 323.76, 329.99, 332.64, 331.95, 333.62, 327.57, 327.91, 325.86, 332.57, 332.97, 337.72, 339.22, 330.62, 335.47, 336.47, 334.53, 342.89, 346.91, 343.15, 341.1, 338.87, 345.23, 348.21, 349.9, 353.21], 'signals': ['FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [296.53, 290.75, 286.71, 287.15, 285.97, 284.77, 280.19, 280.73, 283.43, 284.15, 284.99, 285.22, 283.82, 287.14, 289.61, 292.6, 288.87, 280.14, 281.06, 291.35, 292.56, 291.79, 294.12, 296.07, 306.59, 308.94, 308.48, 312.27, 309.72, 304.56, 308.56, 308.9, 315.57, 311.6, 311.62, 310.29, 306.9, 310.23, 310.05, 307.86, 311.83, 311.07, 306.27, 308.01, 313.49, 304.9, 300.75, 298.65, 303.51, 298.9, 298.57, 296.47, 299.38, 294.37, 300.63, 301.64, 305.01, 305.36, 297.94, 295.4, 297.97, 295.25, 299.61, 299.5, 309.5, 310.97, 309.71, 311.3, 307.75, 312.08, 319.28, 317.97, 329.65, 331.96, 323.76, 329.99, 332.64, 331.95, 333.62, 327.57, 327.91, 325.86, 332.57, 332.97, 337.72, 339.22, 330.62, 335.47, 336.47, 334.53, 342.89, 346.91, 343.15, 341.1, 338.87, 345.23, 348.21, 349.9, 353.21, 356.2], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
       <c r="S16" t="n">
-        <v>353.21</v>
+        <v>356.2</v>
       </c>
     </row>
     <row r="17">
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1503,28 +1503,28 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.592</v>
+        <v>0.644</v>
       </c>
       <c r="E17" t="n">
         <v>60</v>
       </c>
       <c r="F17" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="G17" t="n">
         <v>65</v>
       </c>
       <c r="H17" t="n">
-        <v>810</v>
+        <v>739</v>
       </c>
       <c r="I17" t="n">
-        <v>16.2</v>
+        <v>14.8</v>
       </c>
       <c r="J17" t="n">
-        <v>23.6</v>
+        <v>21.4</v>
       </c>
       <c r="K17" t="n">
-        <v>-7.4</v>
+        <v>-6.6</v>
       </c>
       <c r="L17" t="n">
         <v>5000</v>
@@ -1546,11 +1546,11 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [858.8, 863.44, 831.79, 817.82, 828.38, 830.15, 820.15, 784.06, 778.78, 791.28, 803.5, 801.95, 805.95, 809.96, 827.62, 832.05, 838.15, 819.03, 799.37, 804.06, 842.28, 856.44, 859.25, 862.25, 860.36, 901.78, 899.75, 903.82, 886.88, 905.64, 895.54, 896.05, 921.89, 937.61, 922.48, 930.74, 927.21, 922.84, 933.7, 922.48, 901.63, 919.72, 919.66, 899.31, 914.86, 933.24, 921.81, 932.37, 940.71, 941.75, 951.23, 964.71, 944.31, 942.21, 924.66, 977.81, 983.83, 992.36, 990.16, 992.1, 1003.95, 1021.06, 1048.58, 1064.58, 1041.02, 1092.61, 1038.68, 1045.0, 1032.01, 1001.29, 1035.64, 1062.75, 1076.17, 1090.67, 1099.14, 1096.56, 1106.37, 1094.44, 1076.91, 1065.09, 1019.61, 1020.21, 1011.37, 1019.61, 1021.0, 1055.29, 1042.98, 1029.64, 1055.97, 1055.18, 1045.91, 1140.0, 1152.07, 1095.46, 1065.22, 1055.03, 1085.56, 1098.2, 1074.72, 1061.23], 'signals': ['BUY', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [863.44, 831.79, 817.82, 828.38, 830.15, 820.15, 784.06, 778.78, 791.28, 803.5, 801.95, 805.95, 809.96, 827.62, 832.05, 838.15, 819.03, 799.37, 804.06, 842.28, 856.44, 859.25, 862.25, 860.36, 901.78, 899.75, 903.82, 886.88, 905.64, 895.54, 896.05, 921.89, 937.61, 922.48, 930.74, 927.21, 922.84, 933.7, 922.48, 901.63, 919.72, 919.66, 899.31, 914.86, 933.24, 921.81, 932.37, 940.71, 941.75, 951.23, 964.71, 944.31, 942.21, 924.66, 977.81, 983.83, 992.36, 990.16, 992.1, 1003.95, 1021.06, 1048.58, 1064.58, 1041.02, 1092.61, 1038.68, 1045.0, 1032.01, 1001.29, 1035.64, 1062.75, 1076.17, 1090.67, 1099.14, 1096.56, 1106.37, 1094.44, 1076.91, 1065.09, 1019.61, 1020.21, 1011.37, 1019.61, 1021.0, 1055.29, 1042.98, 1029.64, 1055.97, 1055.18, 1045.91, 1140.0, 1152.07, 1095.46, 1065.22, 1055.03, 1085.56, 1098.2, 1074.72, 1061.23, 1048.23], 'signals': ['BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
       <c r="S17" t="n">
-        <v>1061.23</v>
+        <v>1048.23</v>
       </c>
     </row>
     <row r="18">
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1568,54 +1568,54 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.235</v>
+        <v>0.154</v>
       </c>
       <c r="E18" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F18" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="G18" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H18" t="n">
-        <v>503</v>
+        <v>-276</v>
       </c>
       <c r="I18" t="n">
-        <v>10.1</v>
+        <v>-5.5</v>
       </c>
       <c r="J18" t="n">
-        <v>-13.2</v>
+        <v>-19.8</v>
       </c>
       <c r="K18" t="n">
-        <v>23.3</v>
+        <v>14.3</v>
       </c>
       <c r="L18" t="n">
         <v>5000</v>
       </c>
       <c r="M18" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="N18" t="n">
         <v>5</v>
       </c>
       <c r="O18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P18" t="n">
         <v>5</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [182.36, 208.93, 205.71, 197.22, 199.79, 196.52, 198.63, 193.23, 195.53, 203.32, 210.23, 202.29, 202.91, 197.5, 200.62, 181.04, 181.1, 173.38, 161.14, 160.79, 174.61, 172.99, 171.46, 174.79, 175.18, 175.09, 169.02, 167.85, 174.53, 184.41, 195.9, 199.83, 206.33, 211.63, 195.95, 206.24, 197.93, 199.77, 196.68, 194.1, 181.73, 187.77, 191.25, 202.99, 197.75, 197.96, 192.96, 201.16, 216.6, 207.64, 201.8, 212.01, 195.43, 189.44, 193.45, 191.29, 193.56, 184.99, 180.01, 173.78, 182.25, 189.03, 182.61, 173.99, 163.22, 164.13, 152.4, 162.11, 155.5, 153.97, 160.43, 159.78, 169.62, 169.27, 164.92, 163.26, 164.84, 158.18, 150.11, 142.52, 149.06, 151.65, 146.19, 159.24, 165.48, 168.87, 163.51, 159.36, 158.44, 159.07, 157.37, 161.5, 167.21, 160.49, 157.12, 160.43, 175.85, 166.12, 161.16, 158.29], 'signals': ['BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [208.93, 205.71, 197.22, 199.79, 196.52, 198.63, 193.23, 195.53, 203.32, 210.23, 202.29, 202.91, 197.5, 200.62, 181.04, 181.1, 173.38, 161.14, 160.79, 174.61, 172.99, 171.46, 174.79, 175.18, 175.09, 169.02, 167.85, 174.53, 184.41, 195.9, 199.83, 206.33, 211.63, 195.95, 206.24, 197.93, 199.77, 196.68, 194.1, 181.73, 187.77, 191.25, 202.99, 197.75, 197.96, 192.96, 201.16, 216.6, 207.64, 201.8, 212.01, 195.43, 189.44, 193.45, 191.29, 193.56, 184.99, 180.01, 173.78, 182.25, 189.03, 182.61, 173.99, 163.22, 164.13, 152.4, 162.11, 155.5, 153.97, 160.43, 159.78, 169.62, 169.27, 164.92, 163.26, 164.84, 158.18, 150.11, 142.52, 149.06, 151.65, 146.19, 159.24, 165.48, 168.87, 163.51, 159.36, 158.44, 159.07, 157.37, 161.5, 167.21, 160.49, 157.12, 160.43, 175.85, 166.12, 161.16, 158.29, 167.49], 'signals': ['BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
       <c r="S18" t="n">
-        <v>158.29</v>
+        <v>167.49</v>
       </c>
     </row>
     <row r="19">
@@ -1633,7 +1633,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.239</v>
+        <v>0.219</v>
       </c>
       <c r="E19" t="n">
         <v>54</v>
@@ -1642,19 +1642,19 @@
         <v>30</v>
       </c>
       <c r="G19" t="n">
-        <v>52.6</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>410</v>
+        <v>961</v>
       </c>
       <c r="I19" t="n">
-        <v>8.199999999999999</v>
+        <v>19.2</v>
       </c>
       <c r="J19" t="n">
-        <v>18.9</v>
+        <v>19.5</v>
       </c>
       <c r="K19" t="n">
-        <v>-10.7</v>
+        <v>-0.3</v>
       </c>
       <c r="L19" t="n">
         <v>5000</v>
@@ -1663,24 +1663,24 @@
         <v>4</v>
       </c>
       <c r="N19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O19" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="P19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.7</v>
+        <v>7.5</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [1006.0, 1001.85, 981.57, 988.63, 1006.66, 999.63, 998.12, 975.57, 983.39, 987.42, 928.75, 916.47, 915.92, 905.14, 908.99, 901.47, 914.74, 895.46, 876.73, 885.11, 918.19, 952.88, 933.97, 925.47, 929.49, 951.66, 953.55, 937.86, 927.95, 920.91, 903.47, 902.44, 925.44, 918.32, 901.47, 919.9, 916.07, 882.44, 866.78, 872.5, 849.75, 932.99, 961.67, 966.27, 987.17, 985.35, 973.28, 946.82, 965.33, 988.17, 1014.0, 1004.97, 1004.92, 988.09, 1021.41, 1018.87, 1041.65, 1065.0, 1064.74, 1082.92, 1126.8, 1105.0, 1082.2, 1064.15, 1078.78, 1125.27, 1131.42, 1149.15, 1144.68, 1136.37, 1160.95, 1133.0, 1129.35, 1122.5, 1112.0, 1098.57, 1102.08, 1107.08, 1117.26, 1127.69, 1208.12, 1229.93, 1199.43, 1191.74, 1213.91, 1200.06, 1235.56, 1215.83, 1216.95, 1188.58, 1181.87, 1152.54, 1156.63, 1169.17, 1179.11, 1146.9, 1175.41, 1163.01, 1185.87, 1196.03], 'signals': ['BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [1001.85, 981.57, 988.63, 1006.66, 999.63, 998.12, 975.57, 983.39, 987.42, 928.75, 916.47, 915.92, 905.14, 908.99, 901.47, 914.74, 895.46, 876.73, 885.11, 918.19, 952.88, 933.97, 925.47, 929.49, 951.66, 953.55, 937.86, 927.95, 920.91, 903.47, 902.44, 925.44, 918.32, 901.47, 919.9, 916.07, 882.44, 866.78, 872.5, 849.75, 932.99, 961.67, 966.27, 987.17, 985.35, 973.28, 946.82, 965.33, 988.17, 1014.0, 1004.97, 1004.92, 988.09, 1021.41, 1018.87, 1041.65, 1065.0, 1064.74, 1082.92, 1126.8, 1105.0, 1082.2, 1064.15, 1078.78, 1125.27, 1131.42, 1149.15, 1144.68, 1136.37, 1160.95, 1133.0, 1129.35, 1122.5, 1112.0, 1098.57, 1102.08, 1107.08, 1117.26, 1127.69, 1208.12, 1229.93, 1199.43, 1191.74, 1213.91, 1200.06, 1235.56, 1215.83, 1216.95, 1188.58, 1181.87, 1152.54, 1156.63, 1169.17, 1179.11, 1146.9, 1175.41, 1163.01, 1185.87, 1196.03, 1197.53], 'signals': ['BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
       <c r="S19" t="n">
-        <v>1196.03</v>
+        <v>1197.53</v>
       </c>
     </row>
     <row r="20">
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1698,28 +1698,28 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F20" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="G20" t="n">
-        <v>52.6</v>
+        <v>42.1</v>
       </c>
       <c r="H20" t="n">
-        <v>169</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>-6.5</v>
+        <v>-7</v>
       </c>
       <c r="K20" t="n">
-        <v>9.9</v>
+        <v>7</v>
       </c>
       <c r="L20" t="n">
         <v>5000</v>
@@ -1728,24 +1728,24 @@
         <v>23</v>
       </c>
       <c r="N20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [224.12, 227.31, 222.06, 231.11, 225.0, 217.76, 214.1, 204.76, 209.89, 213.47, 210.82, 205.99, 201.18, 195.12, 198.41, 196.42, 199.61, 194.36, 190.52, 189.21, 199.03, 207.32, 208.22, 212.3, 210.0, 217.8, 220.06, 217.63, 222.14, 223.77, 223.93, 218.88, 223.38, 225.08, 219.16, 231.28, 234.15, 232.44, 231.33, 230.72, 224.11, 229.03, 227.38, 221.3, 224.38, 229.93, 231.03, 237.36, 238.21, 236.87, 240.6, 229.21, 220.49, 220.61, 215.01, 222.2, 219.61, 219.02, 218.9, 224.3, 228.78, 231.15, 224.3, 217.7, 210.58, 217.42, 215.45, 215.92, 214.51, 209.0, 221.63, 219.05, 228.95, 227.49, 225.63, 222.72, 220.83, 216.71, 220.25, 218.12, 217.25, 214.69, 216.47, 218.58, 226.49, 234.54, 231.68, 224.95, 223.11, 222.28, 215.51, 217.11, 218.12, 214.34, 214.03, 209.48, 204.8, 208.65, 209.23, 209.52], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [227.31, 222.06, 231.11, 225.0, 217.76, 214.1, 204.76, 209.89, 213.47, 210.82, 205.99, 201.18, 195.12, 198.41, 196.42, 199.61, 194.36, 190.52, 189.21, 199.03, 207.32, 208.22, 212.3, 210.0, 217.8, 220.06, 217.63, 222.14, 223.77, 223.93, 218.88, 223.38, 225.08, 219.16, 231.28, 234.15, 232.44, 231.33, 230.72, 224.11, 229.03, 227.38, 221.3, 224.38, 229.93, 231.03, 237.36, 238.21, 236.87, 240.6, 229.21, 220.49, 220.61, 215.01, 222.2, 219.61, 219.02, 218.9, 224.3, 228.78, 231.15, 224.3, 217.7, 210.58, 217.42, 215.45, 215.92, 214.51, 209.0, 221.63, 219.05, 228.95, 227.49, 225.63, 222.72, 220.83, 216.71, 220.25, 218.12, 217.25, 214.69, 216.47, 218.58, 226.49, 234.54, 231.68, 224.95, 223.11, 222.28, 215.51, 217.11, 218.12, 214.34, 214.03, 209.48, 204.8, 208.65, 209.23, 209.52, 211.5], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
       <c r="S20" t="n">
-        <v>209.52</v>
+        <v>211.5</v>
       </c>
     </row>
     <row r="21">
@@ -1755,62 +1755,257 @@
         </is>
       </c>
       <c r="B21" t="n">
+        <v>59</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UP  </t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0.588</v>
+      </c>
+      <c r="E21" t="n">
         <v>62</v>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UP  </t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>0.523</v>
-      </c>
-      <c r="E21" t="n">
-        <v>64</v>
-      </c>
       <c r="F21" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="G21" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="H21" t="n">
-        <v>599</v>
+        <v>-315</v>
       </c>
       <c r="I21" t="n">
-        <v>12</v>
+        <v>-6.3</v>
       </c>
       <c r="J21" t="n">
-        <v>-13.6</v>
+        <v>-11.1</v>
       </c>
       <c r="K21" t="n">
-        <v>25.6</v>
+        <v>4.8</v>
       </c>
       <c r="L21" t="n">
         <v>5000</v>
       </c>
       <c r="M21" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="N21" t="n">
         <v>5</v>
       </c>
       <c r="O21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P21" t="n">
         <v>5</v>
       </c>
       <c r="Q21" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-03', '2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24'], 'prices': [76.36, 76.65, 75.44, 75.13, 73.84, 72.36, 74.97, 72.97, 73.33, 74.66, 77.79, 76.66, 75.34, 73.89, 75.12, 72.34, 73.08, 70.55, 69.18, 69.91, 71.93, 71.71, 71.84, 72.17, 71.73, 72.38, 71.81, 70.48, 72.34, 72.91, 77.28, 76.48, 77.12, 77.49, 77.26, 75.58, 74.7, 74.64, 76.27, 74.11, 74.47, 74.61, 75.12, 73.93, 72.95, 79.17, 76.73, 75.45, 76.15, 76.36, 74.7, 74.69, 75.09, 75.08, 74.09, 74.6, 73.61, 71.82, 70.12, 70.73, 70.92, 70.4, 73.77, 71.62, 71.69, 72.21, 70.71, 70.06, 70.38, 68.61, 69.55, 68.85, 72.85, 73.25, 70.91, 71.64, 71.43, 69.67, 73.85, 72.25, 76.2, 75.5, 72.16, 72.66, 74.43, 72.42, 74.33, 73.6, 74.35, 74.54, 74.26, 72.08, 72.67, 74.04, 72.46, 72.17, 71.55, 70.33, 68.91, 65.94], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'SELL', 'BUY', 'SELL', 'BUY', 'SELL', 'FLAT', 'BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [76.65, 75.44, 75.13, 73.84, 72.36, 74.97, 72.97, 73.33, 74.66, 77.79, 76.66, 75.34, 73.89, 75.12, 72.34, 73.08, 70.55, 69.18, 69.91, 71.93, 71.71, 71.84, 72.17, 71.73, 72.38, 71.81, 70.48, 72.34, 72.91, 77.28, 76.48, 77.12, 77.49, 77.26, 75.58, 74.7, 74.64, 76.27, 74.11, 74.47, 74.61, 75.12, 73.93, 72.95, 79.17, 76.73, 75.45, 76.15, 76.36, 74.7, 74.69, 75.09, 75.08, 74.09, 74.6, 73.61, 71.82, 70.12, 70.73, 70.92, 70.4, 73.77, 71.62, 71.69, 72.21, 70.71, 70.06, 70.38, 68.61, 69.55, 68.85, 72.85, 73.25, 70.91, 71.64, 71.43, 69.67, 73.85, 72.25, 76.2, 75.5, 72.16, 72.66, 74.43, 72.42, 74.33, 73.6, 74.35, 74.54, 74.26, 72.08, 72.67, 74.04, 72.46, 72.17, 71.55, 70.33, 68.91, 65.94, 68.18], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'SELL', 'BUY', 'SELL', 'BUY', 'SELL', 'FLAT', 'BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY']}</t>
         </is>
       </c>
       <c r="S21" t="n">
-        <v>65.94</v>
+        <v>68.18000000000001</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>GLW</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>52</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UP  </t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="E22" t="n">
+        <v>53</v>
+      </c>
+      <c r="F22" t="n">
+        <v>10</v>
+      </c>
+      <c r="G22" t="n">
+        <v>45</v>
+      </c>
+      <c r="H22" t="n">
+        <v>538</v>
+      </c>
+      <c r="I22" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="J22" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="K22" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="L22" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M22" t="n">
+        <v>34</v>
+      </c>
+      <c r="N22" t="n">
+        <v>5</v>
+      </c>
+      <c r="O22" t="n">
+        <v>9</v>
+      </c>
+      <c r="P22" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [144.62, 134.53, 123.1, 128.85, 136.01, 131.56, 129.57, 128.92, 131.85, 129.69, 129.66, 132.88, 124.39, 130.77, 141.79, 146.13, 135.11, 136.6, 128.35, 135.76, 142.16, 147.69, 146.28, 148.29, 164.85, 169.54, 170.98, 174.9, 172.56, 168.01, 165.83, 164.13, 165.13, 165.2, 168.5, 169.24, 175.62, 167.75, 152.82, 151.67, 163.99, 158.02, 159.72, 161.85, 181.29, 182.12, 186.65, 207.07, 197.94, 206.19, 207.96, 191.52, 178.28, 175.56, 180.41, 191.6, 193.75, 195.87, 190.6, 182.69, 181.16, 176.7, 200.4, 200.76, 197.7, 177.58, 187.54, 173.94, 168.17, 176.55, 179.2, 187.88, 177.42, 175.4, 194.92, 209.83, 194.07, 205.83, 228.01, 221.05, 255.69, 255.43, 220.63, 196.79, 194.8, 185.38, 184.03, 192.38, 190.89, 183.11, 187.64, 174.41, 158.39, 154.61, 153.1, 162.41, 154.06, 156.06, 146.65, 143.36], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+        </is>
+      </c>
+      <c r="S22" t="n">
+        <v>143.36</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>NBIS</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>62</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="E23" t="n">
+        <v>51</v>
+      </c>
+      <c r="F23" t="n">
+        <v>70</v>
+      </c>
+      <c r="G23" t="n">
+        <v>50</v>
+      </c>
+      <c r="H23" t="n">
+        <v>728</v>
+      </c>
+      <c r="I23" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="J23" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-77.5</v>
+      </c>
+      <c r="L23" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M23" t="n">
+        <v>26</v>
+      </c>
+      <c r="N23" t="n">
+        <v>4</v>
+      </c>
+      <c r="O23" t="n">
+        <v>13</v>
+      </c>
+      <c r="P23" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>4</v>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [97.78, 95.65, 89.33, 94.94, 96.43, 112.0, 108.04, 112.95, 129.85, 116.33, 118.56, 121.52, 117.62, 114.15, 114.91, 115.09, 105.97, 100.82, 92.26, 103.76, 101.95, 108.82, 112.54, 117.4, 125.0, 136.33, 144.97, 154.56, 161.94, 166.77, 165.34, 157.14, 159.16, 156.55, 156.14, 157.08, 147.16, 144.96, 135.51, 141.19, 138.23, 154.49, 176.42, 175.92, 195.09, 184.77, 177.05, 186.1, 179.11, 207.27, 221.15, 219.94, 199.86, 197.73, 191.82, 219.93, 214.77, 208.06, 208.37, 226.34, 231.09, 264.51, 260.58, 251.68, 259.67, 227.81, 218.0, 220.12, 211.69, 222.24, 232.36, 260.07, 265.1, 280.91, 286.69, 283.61, 275.25, 259.66, 256.63, 240.3, 261.15, 276.17, 229.18, 215.62, 213.02, 195.19, 216.48, 216.2, 219.65, 210.51, 194.09, 199.51, 171.77, 177.71, 182.62, 216.92, 218.16, 220.97, 187.77, 187.88], 'signals': ['BUY', 'SELL', 'BUY', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+        </is>
+      </c>
+      <c r="S23" t="n">
+        <v>187.88</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>SPMO</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>68</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UP  </t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0.828</v>
+      </c>
+      <c r="E24" t="n">
+        <v>55</v>
+      </c>
+      <c r="F24" t="n">
+        <v>50</v>
+      </c>
+      <c r="G24" t="n">
+        <v>50</v>
+      </c>
+      <c r="H24" t="n">
+        <v>585</v>
+      </c>
+      <c r="I24" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="J24" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-9.199999999999999</v>
+      </c>
+      <c r="L24" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M24" t="n">
+        <v>34</v>
+      </c>
+      <c r="N24" t="n">
+        <v>3</v>
+      </c>
+      <c r="O24" t="n">
+        <v>13</v>
+      </c>
+      <c r="P24" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>5</v>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [119.74, 119.13, 117.73, 118.78, 118.56, 118.18, 116.66, 115.67, 116.84, 116.84, 115.56, 115.38, 113.29, 114.35, 114.66, 115.14, 111.17, 110.14, 107.67, 111.94, 114.32, 114.56, 115.49, 116.47, 121.17, 122.57, 123.15, 124.4, 126.46, 126.39, 126.55, 128.1, 127.44, 126.46, 128.91, 129.03, 131.32, 131.91, 129.76, 130.57, 133.59, 134.21, 134.23, 137.67, 141.37, 139.09, 143.59, 145.85, 144.23, 146.07, 147.29, 143.26, 141.2, 140.41, 143.09, 144.47, 144.72, 149.57, 149.37, 149.9, 150.36, 152.09, 154.08, 154.85, 152.6, 144.06, 147.65, 147.28, 143.46, 150.35, 152.25, 157.6, 154.38, 155.25, 159.65, 161.66, 154.34, 153.79, 159.64, 154.2, 158.53, 161.54, 155.32, 150.83, 152.98, 149.42, 150.57, 153.08, 153.75, 149.73, 152.86, 150.0, 145.28, 143.89, 144.52, 149.7, 150.07, 149.83, 146.51, 144.75], 'signals': ['FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+        </is>
+      </c>
+      <c r="S24" t="n">
+        <v>144.75</v>
       </c>
     </row>
   </sheetData>

--- a/demo_results.xlsx
+++ b/demo_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S24"/>
+  <dimension ref="A1:S12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -516,76 +516,76 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UP  </t>
+          <t>DOWN</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.893</v>
+        <v>0.455</v>
       </c>
       <c r="E2" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F2" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="G2" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="H2" t="n">
-        <v>1045</v>
+        <v>2154</v>
       </c>
       <c r="I2" t="n">
-        <v>20.9</v>
+        <v>43.1</v>
       </c>
       <c r="J2" t="n">
-        <v>28.5</v>
+        <v>127.9</v>
       </c>
       <c r="K2" t="n">
-        <v>-7.6</v>
+        <v>-84.8</v>
       </c>
       <c r="L2" t="n">
         <v>5000</v>
       </c>
       <c r="M2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O2" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="P2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [262.28, 260.05, 257.22, 259.64, 260.59, 260.57, 255.52, 249.89, 252.59, 254.0, 249.71, 248.73, 247.76, 251.26, 251.41, 252.39, 252.66, 248.57, 246.4, 253.56, 255.39, 255.68, 258.62, 253.27, 258.66, 260.25, 260.24, 258.96, 258.59, 266.18, 263.16, 269.98, 272.8, 265.93, 272.92, 273.18, 270.81, 267.36, 270.46, 269.92, 271.1, 279.88, 276.58, 283.92, 287.25, 287.18, 293.05, 292.68, 294.8, 298.87, 298.21, 300.23, 297.84, 298.97, 302.25, 304.99, 308.82, 308.33, 310.85, 312.51, 312.06, 306.31, 315.2, 310.26, 311.23, 307.34, 301.54, 290.55, 291.58, 295.63, 291.13, 296.42, 299.24, 295.95, 298.01, 297.01, 294.3, 293.08, 275.15, 283.78, 281.74, 289.36, 294.38, 308.63, 312.66, 310.66, 313.39, 316.22, 315.32, 317.31, 314.86, 327.5, 333.26, 333.74, 326.59, 327.74, 325.89, 321.66, 333.02, 336.91], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [199.45, 192.43, 202.68, 203.23, 204.83, 197.74, 193.39, 196.58, 196.31, 199.46, 205.27, 201.33, 202.68, 205.37, 220.27, 203.77, 201.99, 196.04, 203.43, 210.21, 217.5, 220.18, 221.53, 231.82, 236.64, 245.04, 246.83, 255.07, 258.12, 278.26, 278.39, 274.95, 284.49, 303.46, 305.33, 347.81, 334.63, 323.21, 337.11, 354.49, 360.54, 341.54, 355.26, 421.39, 408.46, 455.19, 458.79, 448.29, 445.5, 449.7, 424.1, 420.99, 414.05, 447.58, 449.59, 467.51, 503.89, 495.54, 518.09, 516.1, 510.13, 521.54, 542.52, 523.2, 466.38, 490.33, 475.51, 452.4, 488.45, 511.57, 547.26, 507.29, 512.48, 537.37, 551.63, 519.85, 519.74, 532.57, 521.58, 539.49, 580.91, 540.88, 517.82, 552.05, 516.11, 517.41, 546.72, 557.89, 534.39, 548.13, 529.14, 500.94, 495.76, 503.57, 544.43, 552.33, 539.69, 521.95, 494.95, 454.62], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>336.91</v>
+        <v>454.62</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -593,155 +593,155 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.977</v>
+        <v>0.512</v>
       </c>
       <c r="E3" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="G3" t="n">
-        <v>55.6</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>379</v>
+        <v>1802</v>
       </c>
       <c r="I3" t="n">
-        <v>7.6</v>
+        <v>36</v>
       </c>
       <c r="J3" t="n">
-        <v>-3.8</v>
+        <v>106.8</v>
       </c>
       <c r="K3" t="n">
-        <v>11.4</v>
+        <v>-70.8</v>
       </c>
       <c r="L3" t="n">
         <v>5000</v>
       </c>
       <c r="M3" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="N3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O3" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="P3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.5</v>
+        <v>7.5</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [404.32, 409.79, 408.08, 408.53, 404.88, 404.0, 400.99, 394.7, 399.09, 398.55, 390.94, 388.18, 381.04, 382.17, 371.93, 370.24, 365.18, 356.0, 358.18, 369.37, 368.57, 372.65, 372.07, 371.49, 373.52, 372.26, 370.07, 383.54, 392.26, 410.33, 419.35, 421.88, 417.17, 423.24, 431.98, 414.85, 423.7, 423.9, 428.32, 423.54, 406.9, 413.54, 412.73, 410.49, 413.07, 419.86, 414.22, 411.77, 406.89, 404.33, 408.55, 421.01, 422.62, 416.52, 420.15, 419.09, 418.57, 416.03, 412.67, 426.99, 450.24, 460.52, 441.31, 427.34, 428.05, 416.67, 411.74, 403.41, 397.36, 390.34, 390.74, 399.76, 393.83, 378.91, 379.4, 367.34, 373.94, 365.46, 352.83, 372.97, 368.57, 373.02, 384.28, 390.49, 386.74, 388.84, 383.34, 384.36, 385.1, 390.99, 384.93, 395.63, 401.1, 393.82, 402.29, 397.75, 390.34, 381.58, 381.7, 389.1], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [396.82, 370.09, 389.1, 402.88, 418.45, 405.12, 425.89, 441.55, 461.43, 461.47, 444.02, 422.66, 404.12, 395.3, 381.87, 355.26, 357.02, 321.75, 337.79, 367.79, 366.18, 377.7, 377.52, 406.67, 421.45, 420.53, 426.49, 465.59, 456.16, 457.16, 455.0, 448.35, 449.31, 487.41, 481.65, 496.64, 524.48, 504.21, 518.38, 517.08, 542.13, 576.36, 640.1, 666.49, 646.53, 746.7, 795.21, 766.46, 803.51, 775.89, 724.55, 681.44, 698.63, 731.88, 761.98, 750.88, 895.74, 928.27, 923.38, 970.85, 1035.34, 1063.94, 1079.4, 995.85, 863.88, 949.13, 935.75, 891.74, 995.72, 981.46, 1087.82, 1020.6, 1043.03, 1133.82, 1211.19, 1051.61, 1048.35, 1213.37, 1132.16, 1145.1, 1154.11, 1032.12, 975.41, 984.75, 938.38, 948.8, 991.64, 979.3, 937.0, 983.12, 904.28, 853.2, 848.95, 865.46, 970.82, 959.48, 990.21, 920.95, 900.2, 820.53], 'signals': ['FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>389.1</v>
+        <v>820.53</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DOWN</t>
+          <t xml:space="preserve">UP  </t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.449</v>
+        <v>0.727</v>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="F4" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="G4" t="n">
-        <v>50</v>
+        <v>57.1</v>
       </c>
       <c r="H4" t="n">
-        <v>271</v>
+        <v>2124</v>
       </c>
       <c r="I4" t="n">
-        <v>5.4</v>
+        <v>42.5</v>
       </c>
       <c r="J4" t="n">
-        <v>7.9</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>-2.5</v>
+        <v>-28.1</v>
       </c>
       <c r="L4" t="n">
         <v>5000</v>
       </c>
       <c r="M4" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O4" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="P4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>18</v>
+        <v>8.5</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [302.74, 300.49, 298.13, 306.18, 306.86, 308.52, 303.37, 302.1, 305.38, 310.73, 307.51, 306.95, 300.82, 301.88, 290.27, 290.76, 280.75, 274.18, 273.34, 287.39, 297.21, 295.59, 299.81, 305.28, 317.13, 318.3, 317.05, 321.12, 332.71, 336.92, 335.82, 341.48, 337.22, 332.09, 339.12, 338.69, 344.19, 350.13, 349.57, 349.73, 384.57, 385.46, 383.02, 388.2, 397.8, 397.75, 400.56, 388.41, 387.12, 402.38, 400.83, 396.54, 396.7, 387.43, 388.68, 387.43, 382.74, 388.65, 388.6, 389.9, 380.11, 376.15, 361.63, 358.78, 371.97, 368.31, 363.31, 364.26, 356.38, 357.77, 359.68, 369.35, 373.25, 363.79, 368.03, 349.68, 346.13, 345.29, 343.71, 337.39, 353.65, 357.37, 361.21, 359.91, 366.46, 367.03, 361.92, 358.89, 357.18, 352.51, 359.51, 370.92, 354.46, 346.77, 351.99, 347.15, 342.09, 317.69, 319.74, 326.56], 'signals': ['FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [106.54, 107.25, 108.53, 109.08, 110.51, 110.39, 110.44, 105.96, 108.3, 108.95, 107.04, 102.25, 103.33, 98.25, 96.46, 98.15, 92.39, 95.01, 97.6, 98.33, 99.78, 99.65, 105.81, 106.63, 98.67, 94.75, 100.56, 99.62, 102.79, 104.55, 105.99, 108.29, 112.4, 116.67, 111.35, 112.03, 113.65, 113.75, 113.1, 111.44, 113.91, 117.31, 119.13, 117.02, 126.43, 131.94, 135.57, 136.54, 140.64, 144.99, 148.52, 154.71, 154.22, 162.53, 162.06, 165.87, 167.89, 161.34, 167.75, 182.75, 195.54, 192.24, 186.9, 179.77, 167.76, 164.7, 161.23, 161.93, 172.88, 170.7, 173.23, 169.87, 170.74, 171.21, 168.86, 170.23, 168.26, 169.66, 175.27, 185.73, 190.79, 193.18, 193.98, 199.38, 194.62, 191.12, 198.4, 187.18, 187.91, 210.73, 206.77, 203.76, 203.08, 198.49, 191.15, 188.42, 183.42, 183.28, 180.11, 181.8], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>326.56</v>
+        <v>181.8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">UP  </t>
+          <t>DOWN</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.881</v>
+        <v>0.426</v>
       </c>
       <c r="E5" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="F5" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="G5" t="n">
-        <v>83.3</v>
+        <v>50</v>
       </c>
       <c r="H5" t="n">
-        <v>788</v>
+        <v>836</v>
       </c>
       <c r="I5" t="n">
-        <v>15.8</v>
+        <v>16.7</v>
       </c>
       <c r="J5" t="n">
-        <v>6.7</v>
+        <v>7.6</v>
       </c>
       <c r="K5" t="n">
         <v>9.1</v>
@@ -750,37 +750,37 @@
         <v>5000</v>
       </c>
       <c r="M5" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O5" t="n">
         <v>3</v>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q5" t="n">
-        <v>4</v>
+        <v>1.8</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [216.82, 218.94, 213.21, 213.49, 214.33, 212.65, 209.53, 207.67, 211.74, 215.2, 209.87, 208.76, 205.37, 210.14, 207.24, 211.71, 207.54, 199.34, 200.95, 208.27, 210.57, 209.77, 212.79, 213.77, 221.25, 233.65, 238.38, 239.89, 249.02, 248.5, 249.7, 250.56, 248.28, 249.91, 255.36, 255.08, 263.99, 261.12, 259.7, 263.04, 265.06, 268.26, 272.05, 273.55, 274.99, 271.17, 272.68, 268.99, 265.82, 270.13, 267.22, 264.14, 264.86, 259.34, 265.01, 268.46, 266.32, 265.29, 271.85, 274.0, 270.64, 261.26, 256.52, 250.02, 253.79, 246.03, 245.22, 244.19, 238.0, 241.51, 238.55, 246.02, 246.0, 237.5, 244.39, 232.79, 234.11, 234.27, 227.01, 232.69, 240.14, 238.34, 241.7, 242.67, 244.16, 245.98, 243.62, 247.04, 245.34, 247.31, 247.49, 254.96, 249.89, 247.23, 249.99, 247.55, 244.85, 233.66, 232.11, 231.39], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [183.12, 177.6, 182.43, 184.54, 185.81, 182.93, 180.04, 183.01, 181.72, 180.19, 178.35, 172.5, 175.44, 175.0, 178.47, 171.04, 167.32, 164.98, 174.2, 175.55, 177.18, 177.43, 177.89, 181.87, 183.7, 188.41, 189.09, 196.28, 198.64, 198.12, 201.45, 201.82, 199.65, 202.26, 199.41, 208.03, 216.36, 212.92, 209.01, 199.34, 198.22, 198.25, 196.27, 207.59, 211.25, 214.95, 219.18, 220.52, 225.57, 235.47, 225.06, 222.06, 220.35, 223.21, 219.25, 215.08, 214.61, 212.35, 214.0, 210.89, 224.1, 222.56, 214.5, 218.66, 205.1, 208.64, 208.19, 200.42, 204.87, 205.19, 212.45, 207.41, 204.65, 210.69, 208.65, 200.04, 199.0, 195.74, 192.53, 194.97, 200.09, 197.58, 194.83, 195.55, 196.93, 204.12, 202.78, 210.96, 203.53, 211.8, 212.5, 207.4, 202.81, 203.28, 207.29, 212.06, 208.76, 206.84, 196.51, 197.01], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD']}</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>231.39</v>
+        <v>197.01</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -788,64 +788,64 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.073</v>
+        <v>0.435</v>
       </c>
       <c r="E6" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="F6" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="G6" t="n">
-        <v>33.3</v>
+        <v>45</v>
       </c>
       <c r="H6" t="n">
-        <v>422</v>
+        <v>698</v>
       </c>
       <c r="I6" t="n">
-        <v>8.4</v>
+        <v>14</v>
       </c>
       <c r="J6" t="n">
-        <v>-10.9</v>
+        <v>-19.1</v>
       </c>
       <c r="K6" t="n">
-        <v>19.3</v>
+        <v>33.1</v>
       </c>
       <c r="L6" t="n">
         <v>5000</v>
       </c>
       <c r="M6" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="N6" t="n">
         <v>4</v>
       </c>
       <c r="O6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
         <v>4</v>
       </c>
       <c r="Q6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [666.54, 659.39, 643.71, 646.24, 652.91, 653.69, 637.04, 612.62, 626.87, 622.08, 615.11, 606.14, 593.11, 603.5, 592.37, 594.34, 547.03, 525.23, 535.88, 571.6, 578.69, 573.93, 572.49, 574.52, 611.85, 627.81, 629.28, 633.94, 661.88, 670.96, 676.24, 687.91, 670.29, 668.22, 674.1, 658.54, 674.4, 677.99, 670.72, 668.5, 611.34, 608.19, 609.84, 604.4, 612.31, 616.24, 609.07, 598.31, 602.44, 616.06, 617.86, 613.66, 610.64, 602.05, 604.5, 606.82, 609.69, 611.77, 634.67, 634.7, 631.92, 599.91, 597.08, 622.4, 626.99, 592.45, 584.85, 584.05, 570.45, 567.9, 566.45, 593.48, 600.21, 567.58, 577.22, 563.85, 562.2, 557.67, 542.87, 550.25, 562.6, 563.29, 612.91, 582.9, 600.29, 615.58, 603.12, 631.48, 669.21, 656.73, 661.04, 681.31, 664.54, 646.01, 645.85, 643.81, 627.17, 606.1, 595.19, 593.87], 'signals': ['BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [152.67, 157.16, 156.43, 151.14, 151.6, 153.5, 150.95, 152.72, 155.08, 152.77, 155.68, 150.68, 160.84, 154.78, 154.96, 147.56, 143.06, 137.55, 146.28, 146.49, 148.46, 147.93, 150.07, 140.76, 130.49, 128.06, 132.37, 135.7, 142.15, 142.76, 146.39, 145.89, 145.97, 152.62, 141.57, 143.09, 143.1, 141.18, 137.97, 139.11, 144.07, 146.03, 135.91, 133.79, 137.05, 137.8, 136.89, 136.0, 130.05, 133.73, 133.99, 135.14, 135.26, 137.15, 137.41, 136.88, 136.6, 132.51, 143.34, 156.54, 160.65, 152.17, 142.2, 141.7, 135.53, 136.47, 132.07, 130.21, 131.08, 127.99, 134.71, 133.25, 130.63, 128.47, 119.5, 116.7, 113.5, 107.27, 112.93, 115.7, 116.67, 125.73, 129.3, 132.54, 134.37, 132.22, 129.04, 126.79, 130.04, 133.72, 133.76, 134.44, 132.38, 134.85, 132.66, 124.57, 123.37, 122.92, 131.53, 123.53], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT']}</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>593.87</v>
+        <v>123.53</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -853,1159 +853,379 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.318</v>
+        <v>0.362</v>
       </c>
       <c r="E7" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F7" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="G7" t="n">
-        <v>50</v>
+        <v>46.7</v>
       </c>
       <c r="H7" t="n">
-        <v>570</v>
+        <v>-422</v>
       </c>
       <c r="I7" t="n">
-        <v>11.4</v>
+        <v>-8.4</v>
       </c>
       <c r="J7" t="n">
-        <v>7.5</v>
+        <v>-18.4</v>
       </c>
       <c r="K7" t="n">
-        <v>3.9</v>
+        <v>10</v>
       </c>
       <c r="L7" t="n">
         <v>5000</v>
       </c>
       <c r="M7" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="N7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q7" t="n">
         <v>2</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [182.82, 183.12, 177.6, 182.43, 184.54, 185.81, 182.93, 180.04, 183.01, 181.72, 180.19, 178.35, 172.5, 175.44, 175.0, 178.47, 171.04, 167.32, 164.98, 174.2, 175.55, 177.18, 177.43, 177.89, 181.87, 183.7, 188.41, 189.09, 196.28, 198.64, 198.12, 201.45, 201.82, 199.65, 202.26, 199.41, 208.03, 216.36, 212.92, 209.01, 199.34, 198.22, 198.25, 196.27, 207.59, 211.25, 214.95, 219.18, 220.52, 225.57, 235.47, 225.06, 222.06, 220.35, 223.21, 219.25, 215.08, 214.61, 212.35, 214.0, 210.89, 224.1, 222.56, 214.5, 218.66, 205.1, 208.64, 208.19, 200.42, 204.87, 205.19, 212.45, 207.41, 204.65, 210.69, 208.65, 200.04, 199.0, 195.74, 192.53, 194.97, 200.09, 197.58, 194.83, 195.55, 196.93, 204.12, 202.78, 210.96, 203.53, 211.8, 212.5, 207.4, 202.81, 203.28, 207.29, 212.06, 208.76, 206.84, 196.51], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY']}</t>
+          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [205.71, 197.22, 199.79, 196.52, 198.63, 193.23, 195.53, 203.32, 210.23, 202.29, 202.91, 197.5, 200.62, 181.04, 181.1, 173.38, 161.14, 160.79, 174.61, 172.99, 171.46, 174.79, 175.18, 175.09, 169.02, 167.85, 174.53, 184.41, 195.9, 199.83, 206.33, 211.63, 195.95, 206.24, 197.93, 199.77, 196.68, 194.1, 181.73, 187.77, 191.25, 202.99, 197.75, 197.96, 192.96, 201.16, 216.6, 207.64, 201.8, 212.01, 195.43, 189.44, 193.45, 191.29, 193.56, 184.99, 180.01, 173.78, 182.25, 189.03, 182.61, 173.99, 163.22, 164.13, 152.4, 162.11, 155.5, 153.97, 160.43, 159.78, 169.62, 169.27, 164.92, 163.26, 164.84, 158.18, 150.11, 142.52, 149.06, 151.65, 146.19, 159.24, 165.48, 168.87, 163.51, 159.36, 158.44, 159.07, 157.37, 161.5, 167.21, 160.49, 157.12, 160.43, 175.85, 166.12, 161.16, 158.29, 167.49, 167.9], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>196.51</v>
+        <v>167.9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>NFLX</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">UP  </t>
+          <t>DOWN</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.414</v>
       </c>
       <c r="E8" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F8" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="G8" t="n">
-        <v>66.7</v>
+        <v>33.3</v>
       </c>
       <c r="H8" t="n">
-        <v>2104</v>
+        <v>-293</v>
       </c>
       <c r="I8" t="n">
-        <v>42.1</v>
+        <v>-5.9</v>
       </c>
       <c r="J8" t="n">
-        <v>144.9</v>
+        <v>-27</v>
       </c>
       <c r="K8" t="n">
-        <v>-102.8</v>
+        <v>21.1</v>
       </c>
       <c r="L8" t="n">
         <v>5000</v>
       </c>
       <c r="M8" t="n">
-        <v>10</v>
+        <v>69</v>
       </c>
       <c r="N8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O8" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="P8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.5</v>
+        <v>3</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [202.07, 199.45, 192.43, 202.68, 203.23, 204.83, 197.74, 193.39, 196.58, 196.31, 199.46, 205.27, 201.33, 202.68, 205.37, 220.27, 203.77, 201.99, 196.04, 203.43, 210.21, 217.5, 220.18, 221.53, 231.82, 236.64, 245.04, 246.83, 255.07, 258.12, 278.26, 278.39, 274.95, 284.49, 303.46, 305.33, 347.81, 334.63, 323.21, 337.11, 354.49, 360.54, 341.54, 355.26, 421.39, 408.46, 455.19, 458.79, 448.29, 445.5, 449.7, 424.1, 420.99, 414.05, 447.58, 449.59, 467.51, 503.89, 495.54, 518.09, 516.1, 510.13, 521.54, 542.52, 523.2, 466.38, 490.33, 475.51, 452.4, 488.45, 511.57, 547.26, 507.29, 512.48, 537.37, 551.63, 519.85, 519.74, 532.57, 521.58, 539.49, 580.91, 540.88, 517.82, 552.05, 516.11, 517.41, 546.72, 557.89, 534.39, 548.13, 529.14, 500.94, 495.76, 503.57, 544.43, 552.33, 539.69, 521.95, 494.95], 'signals': ['FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [99.17, 99.02, 98.32, 96.94, 94.89, 94.31, 95.31, 95.2, 94.36, 94.7, 91.74, 91.82, 93.38, 90.92, 92.28, 93.32, 93.43, 92.97, 96.15, 95.55, 98.66, 98.93, 98.82, 99.39, 102.05, 103.01, 103.16, 106.28, 107.71, 107.79, 97.31, 94.83, 92.58, 93.24, 92.82, 92.44, 91.37, 92.27, 92.12, 93.61, 92.06, 91.02, 87.89, 88.27, 88.25, 87.49, 85.45, 87.66, 87.56, 86.94, 87.02, 89.65, 89.33, 88.09, 89.3, 88.6, 87.68, 87.35, 86.36, 86.02, 85.85, 83.33, 81.52, 81.56, 82.18, 82.64, 81.41, 82.0, 81.27, 80.34, 81.67, 78.72, 76.96, 77.38, 72.88, 72.82, 71.84, 70.9, 73.81, 73.78, 71.4, 74.19, 77.65, 76.02, 76.18, 75.59, 75.47, 73.37, 73.83, 73.53, 73.68, 74.35, 68.95, 67.6, 68.67, 68.53, 68.89, 70.09, 70.4, 72.39], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>494.95</v>
+        <v>72.39</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">UP  </t>
+          <t>DOWN</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.699</v>
+        <v>0.415</v>
       </c>
       <c r="E9" t="n">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="F9" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="G9" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H9" t="n">
-        <v>289</v>
+        <v>831</v>
       </c>
       <c r="I9" t="n">
-        <v>5.8</v>
+        <v>16.6</v>
       </c>
       <c r="J9" t="n">
-        <v>21.1</v>
+        <v>30.8</v>
       </c>
       <c r="K9" t="n">
-        <v>-15.3</v>
+        <v>-14.2</v>
       </c>
       <c r="L9" t="n">
         <v>5000</v>
       </c>
       <c r="M9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O9" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="P9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [316.36, 331.55, 329.27, 344.48, 341.32, 340.32, 334.74, 320.98, 323.73, 320.13, 314.77, 318.67, 309.37, 322.0, 317.79, 318.31, 308.93, 300.2, 292.95, 309.02, 312.99, 314.05, 313.93, 333.44, 350.08, 354.35, 370.96, 379.15, 380.18, 396.09, 397.84, 405.9, 399.0, 401.53, 421.98, 419.28, 422.09, 417.54, 399.2, 404.81, 416.77, 420.61, 415.84, 426.68, 424.77, 411.91, 429.32, 427.75, 418.64, 416.13, 439.1, 424.52, 420.05, 410.42, 417.1, 413.91, 413.49, 421.34, 421.19, 425.91, 446.06, 459.24, 480.81, 478.47, 418.25, 385.12, 395.97, 391.54, 371.51, 384.96, 381.47, 393.32, 376.11, 392.28, 410.7, 392.13, 380.15, 382.07, 378.91, 365.02, 372.45, 377.75, 369.34, 360.45, 373.9, 370.78, 388.69, 401.11, 399.97, 384.05, 389.11, 394.28, 374.45, 370.83, 378.16, 386.5, 396.81, 392.47, 381.92, 383.22], 'signals': ['BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [260.05, 257.22, 259.64, 260.59, 260.57, 255.52, 249.89, 252.59, 254.0, 249.71, 248.73, 247.76, 251.26, 251.41, 252.39, 252.66, 248.57, 246.4, 253.56, 255.39, 255.68, 258.62, 253.27, 258.66, 260.25, 260.24, 258.96, 258.59, 266.18, 263.16, 269.98, 272.8, 265.93, 272.92, 273.18, 270.81, 267.36, 270.46, 269.92, 271.1, 279.88, 276.58, 283.92, 287.25, 287.18, 293.05, 292.68, 294.8, 298.87, 298.21, 300.23, 297.84, 298.97, 302.25, 304.99, 308.82, 308.33, 310.85, 312.51, 312.06, 306.31, 315.2, 310.26, 311.23, 307.34, 301.54, 290.55, 291.58, 295.63, 291.13, 296.42, 299.24, 295.95, 298.01, 297.01, 294.3, 293.08, 275.15, 283.78, 281.74, 289.36, 294.38, 308.63, 312.66, 310.66, 313.39, 316.22, 315.32, 317.31, 314.86, 327.5, 333.26, 333.74, 326.59, 327.74, 325.89, 321.66, 333.02, 336.91, 340.08], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>383.22</v>
+        <v>340.08</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>GLW</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>DOWN</t>
+          <t xml:space="preserve">UP  </t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.389</v>
+        <v>0.607</v>
       </c>
       <c r="E10" t="n">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="F10" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="G10" t="n">
         <v>60</v>
       </c>
       <c r="H10" t="n">
-        <v>2922</v>
+        <v>-332</v>
       </c>
       <c r="I10" t="n">
-        <v>58.4</v>
+        <v>-6.6</v>
       </c>
       <c r="J10" t="n">
-        <v>124.7</v>
+        <v>-6.3</v>
       </c>
       <c r="K10" t="n">
-        <v>-66.3</v>
+        <v>-0.3</v>
       </c>
       <c r="L10" t="n">
         <v>5000</v>
       </c>
       <c r="M10" t="n">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="N10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O10" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="P10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>7.5</v>
+        <v>19</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [400.54, 396.82, 370.09, 389.1, 402.88, 418.45, 405.12, 425.89, 441.55, 461.43, 461.47, 444.02, 422.66, 404.12, 395.3, 381.87, 355.26, 357.02, 321.75, 337.79, 367.79, 366.18, 377.7, 377.52, 406.67, 421.45, 420.53, 426.49, 465.59, 456.16, 457.16, 455.0, 448.35, 449.31, 487.41, 481.65, 496.64, 524.48, 504.21, 518.38, 517.08, 542.13, 576.36, 640.1, 666.49, 646.53, 746.7, 795.21, 766.46, 803.51, 775.89, 724.55, 681.44, 698.63, 731.88, 761.98, 750.88, 895.74, 928.27, 923.38, 970.85, 1035.34, 1063.94, 1079.4, 995.85, 863.88, 949.13, 935.75, 891.74, 995.72, 981.46, 1087.82, 1020.6, 1043.03, 1133.82, 1211.19, 1051.61, 1048.35, 1213.37, 1132.16, 1145.1, 1154.11, 1032.12, 975.41, 984.75, 938.38, 948.8, 991.64, 979.3, 937.0, 983.12, 904.28, 853.2, 848.95, 865.46, 970.82, 959.48, 990.21, 920.95, 900.2], 'signals': ['FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [134.53, 123.1, 128.85, 136.01, 131.56, 129.57, 128.92, 131.85, 129.69, 129.66, 132.88, 124.39, 130.77, 141.79, 146.13, 135.11, 136.6, 128.35, 135.76, 142.16, 147.69, 146.28, 148.29, 164.85, 169.54, 170.98, 174.9, 172.56, 168.01, 165.83, 164.13, 165.13, 165.2, 168.5, 169.24, 175.62, 167.75, 152.82, 151.67, 163.99, 158.02, 159.72, 161.85, 181.29, 182.12, 186.65, 207.07, 197.94, 206.19, 207.96, 191.52, 178.28, 175.56, 180.41, 191.6, 193.75, 195.87, 190.6, 182.69, 181.16, 176.7, 200.4, 200.76, 197.7, 177.58, 187.54, 173.94, 168.17, 176.55, 179.2, 187.88, 177.42, 175.4, 194.92, 209.83, 194.07, 205.83, 228.01, 221.05, 255.69, 255.43, 220.63, 196.79, 194.8, 185.38, 184.03, 192.38, 190.89, 183.11, 187.64, 174.41, 158.39, 154.61, 153.1, 162.41, 154.06, 156.06, 146.65, 143.36, 126.01], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
       <c r="S10" t="n">
-        <v>900.2</v>
+        <v>126.01</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">UP  </t>
+          <t>DOWN</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.677</v>
+        <v>0.438</v>
       </c>
       <c r="E11" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="F11" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="H11" t="n">
-        <v>-79</v>
+        <v>1889</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.6</v>
+        <v>37.8</v>
       </c>
       <c r="J11" t="n">
-        <v>-23.8</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>22.2</v>
+        <v>-39.6</v>
       </c>
       <c r="L11" t="n">
         <v>5000</v>
       </c>
       <c r="M11" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="N11" t="n">
         <v>4</v>
       </c>
       <c r="O11" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="P11" t="n">
         <v>4</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [405.94, 405.55, 396.73, 398.68, 399.24, 407.82, 395.01, 391.2, 395.56, 399.27, 392.78, 380.3, 367.96, 380.85, 383.03, 385.95, 372.11, 361.83, 355.28, 371.75, 381.26, 360.59, 352.82, 346.65, 343.25, 345.62, 348.95, 352.42, 364.2, 391.95, 388.9, 400.62, 392.5, 386.42, 387.51, 373.72, 376.3, 378.67, 376.02, 372.8, 381.63, 390.82, 392.51, 389.37, 398.73, 411.79, 428.35, 445.0, 433.45, 445.27, 443.3, 422.24, 409.99, 404.11, 417.26, 417.85, 426.01, 433.59, 440.36, 442.1, 435.79, 415.88, 423.74, 423.7, 418.45, 391.0, 408.95, 396.68, 381.59, 399.15, 406.43, 411.15, 404.66, 396.38, 400.49, 405.05, 381.61, 375.53, 375.12, 379.71, 411.84, 420.6, 425.3, 393.45, 419.77, 402.9, 394.06, 406.55, 407.76, 394.76, 396.18, 394.46, 391.06, 380.84, 369.57, 378.93, 374.01, 319.69, 313.03, 309.22], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [95.65, 89.33, 94.94, 96.43, 112.0, 108.04, 112.95, 129.85, 116.33, 118.56, 121.52, 117.62, 114.15, 114.91, 115.09, 105.97, 100.82, 92.26, 103.76, 101.95, 108.82, 112.54, 117.4, 125.0, 136.33, 144.97, 154.56, 161.94, 166.77, 165.34, 157.14, 159.16, 156.55, 156.14, 157.08, 147.16, 144.96, 135.51, 141.19, 138.23, 154.49, 176.42, 175.92, 195.09, 184.77, 177.05, 186.1, 179.11, 207.27, 221.15, 219.94, 199.86, 197.73, 191.82, 219.93, 214.77, 208.06, 208.37, 226.34, 231.09, 264.51, 260.58, 251.68, 259.67, 227.81, 218.0, 220.12, 211.69, 222.24, 232.36, 260.07, 265.1, 280.91, 286.69, 283.61, 275.25, 259.66, 256.63, 240.3, 261.15, 276.17, 229.18, 215.62, 213.02, 195.19, 216.48, 216.2, 219.65, 210.51, 194.09, 199.51, 171.77, 177.71, 182.62, 216.92, 218.16, 220.97, 187.77, 187.88, 169.69], 'signals': ['FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
       <c r="S11" t="n">
-        <v>309.22</v>
+        <v>169.69</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>SPMO</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>DOWN</t>
+          <t xml:space="preserve">UP  </t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.225</v>
+        <v>0.856</v>
       </c>
       <c r="E12" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F12" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="G12" t="n">
-        <v>26.7</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>-1453</v>
+        <v>313</v>
       </c>
       <c r="I12" t="n">
-        <v>-29.1</v>
+        <v>6.3</v>
       </c>
       <c r="J12" t="n">
-        <v>-28.6</v>
+        <v>18.3</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.5</v>
+        <v>-12</v>
       </c>
       <c r="L12" t="n">
         <v>5000</v>
       </c>
       <c r="M12" t="n">
-        <v>71</v>
+        <v>35</v>
       </c>
       <c r="N12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O12" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="P12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [98.66, 99.17, 99.02, 98.32, 96.94, 94.89, 94.31, 95.31, 95.2, 94.36, 94.7, 91.74, 91.82, 93.38, 90.92, 92.28, 93.32, 93.43, 92.97, 96.15, 95.55, 98.66, 98.93, 98.82, 99.39, 102.05, 103.01, 103.16, 106.28, 107.71, 107.79, 97.31, 94.83, 92.58, 93.24, 92.82, 92.44, 91.37, 92.27, 92.12, 93.61, 92.06, 91.02, 87.89, 88.27, 88.25, 87.49, 85.45, 87.66, 87.56, 86.94, 87.02, 89.65, 89.33, 88.09, 89.3, 88.6, 87.68, 87.35, 86.36, 86.02, 85.85, 83.33, 81.52, 81.56, 82.18, 82.64, 81.41, 82.0, 81.27, 80.34, 81.67, 78.72, 76.96, 77.38, 72.88, 72.82, 71.84, 70.9, 73.81, 73.78, 71.4, 74.19, 77.65, 76.02, 76.18, 75.59, 75.47, 73.37, 73.83, 73.53, 73.68, 74.35, 68.95, 67.6, 68.67, 68.53, 68.89, 70.09, 70.4], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'SELL', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [119.13, 117.73, 118.78, 118.56, 118.18, 116.66, 115.67, 116.84, 116.84, 115.56, 115.38, 113.29, 114.35, 114.66, 115.14, 111.17, 110.14, 107.67, 111.94, 114.32, 114.56, 115.49, 116.47, 121.17, 122.57, 123.15, 124.4, 126.46, 126.39, 126.55, 128.1, 127.44, 126.46, 128.91, 129.03, 131.32, 131.91, 129.76, 130.57, 133.59, 134.21, 134.23, 137.67, 141.37, 139.09, 143.59, 145.85, 144.23, 146.07, 147.29, 143.26, 141.2, 140.41, 143.09, 144.47, 144.72, 149.57, 149.37, 149.9, 150.36, 152.09, 154.08, 154.85, 152.6, 144.06, 147.65, 147.28, 143.46, 150.35, 152.25, 157.6, 154.38, 155.25, 159.65, 161.66, 154.34, 153.79, 159.64, 154.2, 158.53, 161.54, 155.32, 150.83, 152.98, 149.42, 150.57, 153.08, 153.75, 149.73, 152.86, 150.0, 145.28, 143.89, 144.52, 149.7, 150.07, 149.83, 146.51, 144.75, 140.95], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
       <c r="S12" t="n">
-        <v>70.40000000000001</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>PLTR</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>56</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UP  </t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>0.512</v>
-      </c>
-      <c r="E13" t="n">
-        <v>59</v>
-      </c>
-      <c r="F13" t="n">
-        <v>10</v>
-      </c>
-      <c r="G13" t="n">
-        <v>30</v>
-      </c>
-      <c r="H13" t="n">
-        <v>796</v>
-      </c>
-      <c r="I13" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="J13" t="n">
-        <v>-14.1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>30</v>
-      </c>
-      <c r="L13" t="n">
-        <v>5000</v>
-      </c>
-      <c r="M13" t="n">
-        <v>38</v>
-      </c>
-      <c r="N13" t="n">
-        <v>3</v>
-      </c>
-      <c r="O13" t="n">
-        <v>6</v>
-      </c>
-      <c r="P13" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>3</v>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [153.19, 152.67, 157.16, 156.43, 151.14, 151.6, 153.5, 150.95, 152.72, 155.08, 152.77, 155.68, 150.68, 160.84, 154.78, 154.96, 147.56, 143.06, 137.55, 146.28, 146.49, 148.46, 147.93, 150.07, 140.76, 130.49, 128.06, 132.37, 135.7, 142.15, 142.76, 146.39, 145.89, 145.97, 152.62, 141.57, 143.09, 143.1, 141.18, 137.97, 139.11, 144.07, 146.03, 135.91, 133.79, 137.05, 137.8, 136.89, 136.0, 130.05, 133.73, 133.99, 135.14, 135.26, 137.15, 137.41, 136.88, 136.6, 132.51, 143.34, 156.54, 160.65, 152.17, 142.2, 141.7, 135.53, 136.47, 132.07, 130.21, 131.08, 127.99, 134.71, 133.25, 130.63, 128.47, 119.5, 116.7, 113.5, 107.27, 112.93, 115.7, 116.67, 125.73, 129.3, 132.54, 134.37, 132.22, 129.04, 126.79, 130.04, 133.72, 133.76, 134.44, 132.38, 134.85, 132.66, 124.57, 123.37, 122.92, 131.53], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
-        </is>
-      </c>
-      <c r="S13" t="n">
-        <v>131.53</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>CRM</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>52</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>DOWN</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="E14" t="n">
-        <v>52</v>
-      </c>
-      <c r="F14" t="n">
-        <v>60</v>
-      </c>
-      <c r="G14" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>-9.6</v>
-      </c>
-      <c r="K14" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="L14" t="n">
-        <v>5000</v>
-      </c>
-      <c r="M14" t="n">
-        <v>28</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [192.1, 200.37, 201.09, 197.78, 193.92, 193.15, 198.27, 191.85, 197.34, 194.32, 193.36, 194.0, 194.39, 194.19, 182.09, 181.04, 184.7, 178.4, 184.09, 185.72, 185.3, 186.23, 184.09, 182.03, 175.48, 170.41, 164.54, 172.38, 170.87, 177.14, 180.75, 181.67, 185.79, 186.63, 189.31, 172.85, 177.7, 179.72, 180.85, 180.75, 176.08, 183.35, 185.0, 186.51, 180.72, 185.86, 181.35, 177.03, 170.87, 165.41, 167.15, 173.06, 179.02, 178.96, 179.64, 175.86, 179.61, 178.62, 177.05, 175.72, 190.61, 209.06, 200.32, 190.12, 188.26, 185.18, 182.08, 174.9, 170.48, 166.45, 165.89, 164.55, 161.71, 155.02, 151.78, 150.12, 153.42, 152.76, 150.19, 158.37, 157.93, 156.66, 163.23, 166.11, 165.65, 169.52, 166.58, 162.5, 163.32, 171.22, 167.56, 167.0, 172.68, 170.77, 173.79, 170.06, 163.0, 156.93, 163.66, 173.6], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
-        </is>
-      </c>
-      <c r="S14" t="n">
-        <v>173.6</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>CRWD</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>61</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UP  </t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>0.664</v>
-      </c>
-      <c r="E15" t="n">
-        <v>50</v>
-      </c>
-      <c r="F15" t="n">
-        <v>70</v>
-      </c>
-      <c r="G15" t="n">
-        <v>70</v>
-      </c>
-      <c r="H15" t="n">
-        <v>428</v>
-      </c>
-      <c r="I15" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="J15" t="n">
-        <v>76.7</v>
-      </c>
-      <c r="K15" t="n">
-        <v>-68.09999999999999</v>
-      </c>
-      <c r="L15" t="n">
-        <v>5000</v>
-      </c>
-      <c r="M15" t="n">
-        <v>27</v>
-      </c>
-      <c r="N15" t="n">
-        <v>4</v>
-      </c>
-      <c r="O15" t="n">
-        <v>2</v>
-      </c>
-      <c r="P15" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [101.92, 106.54, 107.25, 108.53, 109.08, 110.51, 110.39, 110.44, 105.96, 108.3, 108.95, 107.04, 102.25, 103.33, 98.25, 96.46, 98.15, 92.39, 95.01, 97.6, 98.33, 99.78, 99.65, 105.81, 106.63, 98.67, 94.75, 100.56, 99.62, 102.79, 104.55, 105.99, 108.29, 112.4, 116.67, 111.35, 112.03, 113.65, 113.75, 113.1, 111.44, 113.91, 117.31, 119.13, 117.02, 126.43, 131.94, 135.57, 136.54, 140.64, 144.99, 148.52, 154.71, 154.22, 162.53, 162.06, 165.87, 167.89, 161.34, 167.75, 182.75, 195.54, 192.24, 186.9, 179.77, 167.76, 164.7, 161.23, 161.93, 172.88, 170.7, 173.23, 169.87, 170.74, 171.21, 168.86, 170.23, 168.26, 169.66, 175.27, 185.73, 190.79, 193.18, 193.98, 199.38, 194.62, 191.12, 198.4, 187.18, 187.91, 210.73, 206.77, 203.76, 203.08, 198.49, 191.15, 188.42, 183.42, 183.28, 180.11], 'signals': ['BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
-        </is>
-      </c>
-      <c r="S15" t="n">
-        <v>180.11</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>JPM</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>68</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>DOWN</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>0.274</v>
-      </c>
-      <c r="E16" t="n">
-        <v>61</v>
-      </c>
-      <c r="F16" t="n">
-        <v>30</v>
-      </c>
-      <c r="G16" t="n">
-        <v>65</v>
-      </c>
-      <c r="H16" t="n">
-        <v>724</v>
-      </c>
-      <c r="I16" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="J16" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>-5.6</v>
-      </c>
-      <c r="L16" t="n">
-        <v>5000</v>
-      </c>
-      <c r="M16" t="n">
-        <v>14</v>
-      </c>
-      <c r="N16" t="n">
-        <v>3</v>
-      </c>
-      <c r="O16" t="n">
-        <v>12</v>
-      </c>
-      <c r="P16" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>5</v>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [296.53, 290.75, 286.71, 287.15, 285.97, 284.77, 280.19, 280.73, 283.43, 284.15, 284.99, 285.22, 283.82, 287.14, 289.61, 292.6, 288.87, 280.14, 281.06, 291.35, 292.56, 291.79, 294.12, 296.07, 306.59, 308.94, 308.48, 312.27, 309.72, 304.56, 308.56, 308.9, 315.57, 311.6, 311.62, 310.29, 306.9, 310.23, 310.05, 307.86, 311.83, 311.07, 306.27, 308.01, 313.49, 304.9, 300.75, 298.65, 303.51, 298.9, 298.57, 296.47, 299.38, 294.37, 300.63, 301.64, 305.01, 305.36, 297.94, 295.4, 297.97, 295.25, 299.61, 299.5, 309.5, 310.97, 309.71, 311.3, 307.75, 312.08, 319.28, 317.97, 329.65, 331.96, 323.76, 329.99, 332.64, 331.95, 333.62, 327.57, 327.91, 325.86, 332.57, 332.97, 337.72, 339.22, 330.62, 335.47, 336.47, 334.53, 342.89, 346.91, 343.15, 341.1, 338.87, 345.23, 348.21, 349.9, 353.21, 356.2], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
-        </is>
-      </c>
-      <c r="S16" t="n">
-        <v>356.2</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>GS</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>60</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UP  </t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>0.644</v>
-      </c>
-      <c r="E17" t="n">
-        <v>60</v>
-      </c>
-      <c r="F17" t="n">
-        <v>100</v>
-      </c>
-      <c r="G17" t="n">
-        <v>65</v>
-      </c>
-      <c r="H17" t="n">
-        <v>739</v>
-      </c>
-      <c r="I17" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="J17" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="K17" t="n">
-        <v>-6.6</v>
-      </c>
-      <c r="L17" t="n">
-        <v>5000</v>
-      </c>
-      <c r="M17" t="n">
-        <v>4</v>
-      </c>
-      <c r="N17" t="n">
-        <v>1</v>
-      </c>
-      <c r="O17" t="n">
-        <v>19</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>19</v>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [863.44, 831.79, 817.82, 828.38, 830.15, 820.15, 784.06, 778.78, 791.28, 803.5, 801.95, 805.95, 809.96, 827.62, 832.05, 838.15, 819.03, 799.37, 804.06, 842.28, 856.44, 859.25, 862.25, 860.36, 901.78, 899.75, 903.82, 886.88, 905.64, 895.54, 896.05, 921.89, 937.61, 922.48, 930.74, 927.21, 922.84, 933.7, 922.48, 901.63, 919.72, 919.66, 899.31, 914.86, 933.24, 921.81, 932.37, 940.71, 941.75, 951.23, 964.71, 944.31, 942.21, 924.66, 977.81, 983.83, 992.36, 990.16, 992.1, 1003.95, 1021.06, 1048.58, 1064.58, 1041.02, 1092.61, 1038.68, 1045.0, 1032.01, 1001.29, 1035.64, 1062.75, 1076.17, 1090.67, 1099.14, 1096.56, 1106.37, 1094.44, 1076.91, 1065.09, 1019.61, 1020.21, 1011.37, 1019.61, 1021.0, 1055.29, 1042.98, 1029.64, 1055.97, 1055.18, 1045.91, 1140.0, 1152.07, 1095.46, 1065.22, 1055.03, 1085.56, 1098.2, 1074.72, 1061.23, 1048.23], 'signals': ['BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
-        </is>
-      </c>
-      <c r="S17" t="n">
-        <v>1048.23</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>COIN</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>51</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>DOWN</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>0.154</v>
-      </c>
-      <c r="E18" t="n">
-        <v>56</v>
-      </c>
-      <c r="F18" t="n">
-        <v>50</v>
-      </c>
-      <c r="G18" t="n">
-        <v>40</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-276</v>
-      </c>
-      <c r="I18" t="n">
-        <v>-5.5</v>
-      </c>
-      <c r="J18" t="n">
-        <v>-19.8</v>
-      </c>
-      <c r="K18" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="L18" t="n">
-        <v>5000</v>
-      </c>
-      <c r="M18" t="n">
-        <v>29</v>
-      </c>
-      <c r="N18" t="n">
-        <v>5</v>
-      </c>
-      <c r="O18" t="n">
-        <v>2</v>
-      </c>
-      <c r="P18" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [208.93, 205.71, 197.22, 199.79, 196.52, 198.63, 193.23, 195.53, 203.32, 210.23, 202.29, 202.91, 197.5, 200.62, 181.04, 181.1, 173.38, 161.14, 160.79, 174.61, 172.99, 171.46, 174.79, 175.18, 175.09, 169.02, 167.85, 174.53, 184.41, 195.9, 199.83, 206.33, 211.63, 195.95, 206.24, 197.93, 199.77, 196.68, 194.1, 181.73, 187.77, 191.25, 202.99, 197.75, 197.96, 192.96, 201.16, 216.6, 207.64, 201.8, 212.01, 195.43, 189.44, 193.45, 191.29, 193.56, 184.99, 180.01, 173.78, 182.25, 189.03, 182.61, 173.99, 163.22, 164.13, 152.4, 162.11, 155.5, 153.97, 160.43, 159.78, 169.62, 169.27, 164.92, 163.26, 164.84, 158.18, 150.11, 142.52, 149.06, 151.65, 146.19, 159.24, 165.48, 168.87, 163.51, 159.36, 158.44, 159.07, 157.37, 161.5, 167.21, 160.49, 157.12, 160.43, 175.85, 166.12, 161.16, 158.29, 167.49], 'signals': ['BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
-        </is>
-      </c>
-      <c r="S18" t="n">
-        <v>167.49</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>LLY</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>54</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>DOWN</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>0.219</v>
-      </c>
-      <c r="E19" t="n">
-        <v>54</v>
-      </c>
-      <c r="F19" t="n">
-        <v>30</v>
-      </c>
-      <c r="G19" t="n">
-        <v>68.40000000000001</v>
-      </c>
-      <c r="H19" t="n">
-        <v>961</v>
-      </c>
-      <c r="I19" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="J19" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="K19" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="L19" t="n">
-        <v>5000</v>
-      </c>
-      <c r="M19" t="n">
-        <v>4</v>
-      </c>
-      <c r="N19" t="n">
-        <v>2</v>
-      </c>
-      <c r="O19" t="n">
-        <v>14</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [1001.85, 981.57, 988.63, 1006.66, 999.63, 998.12, 975.57, 983.39, 987.42, 928.75, 916.47, 915.92, 905.14, 908.99, 901.47, 914.74, 895.46, 876.73, 885.11, 918.19, 952.88, 933.97, 925.47, 929.49, 951.66, 953.55, 937.86, 927.95, 920.91, 903.47, 902.44, 925.44, 918.32, 901.47, 919.9, 916.07, 882.44, 866.78, 872.5, 849.75, 932.99, 961.67, 966.27, 987.17, 985.35, 973.28, 946.82, 965.33, 988.17, 1014.0, 1004.97, 1004.92, 988.09, 1021.41, 1018.87, 1041.65, 1065.0, 1064.74, 1082.92, 1126.8, 1105.0, 1082.2, 1064.15, 1078.78, 1125.27, 1131.42, 1149.15, 1144.68, 1136.37, 1160.95, 1133.0, 1129.35, 1122.5, 1112.0, 1098.57, 1102.08, 1107.08, 1117.26, 1127.69, 1208.12, 1229.93, 1199.43, 1191.74, 1213.91, 1200.06, 1235.56, 1215.83, 1216.95, 1188.58, 1181.87, 1152.54, 1156.63, 1169.17, 1179.11, 1146.9, 1175.41, 1163.01, 1185.87, 1196.03, 1197.53], 'signals': ['BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
-        </is>
-      </c>
-      <c r="S19" t="n">
-        <v>1197.53</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>BA</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>55</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UP  </t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>0.5639999999999999</v>
-      </c>
-      <c r="E20" t="n">
-        <v>57</v>
-      </c>
-      <c r="F20" t="n">
-        <v>40</v>
-      </c>
-      <c r="G20" t="n">
-        <v>42.1</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>-7</v>
-      </c>
-      <c r="K20" t="n">
-        <v>7</v>
-      </c>
-      <c r="L20" t="n">
-        <v>5000</v>
-      </c>
-      <c r="M20" t="n">
-        <v>23</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [227.31, 222.06, 231.11, 225.0, 217.76, 214.1, 204.76, 209.89, 213.47, 210.82, 205.99, 201.18, 195.12, 198.41, 196.42, 199.61, 194.36, 190.52, 189.21, 199.03, 207.32, 208.22, 212.3, 210.0, 217.8, 220.06, 217.63, 222.14, 223.77, 223.93, 218.88, 223.38, 225.08, 219.16, 231.28, 234.15, 232.44, 231.33, 230.72, 224.11, 229.03, 227.38, 221.3, 224.38, 229.93, 231.03, 237.36, 238.21, 236.87, 240.6, 229.21, 220.49, 220.61, 215.01, 222.2, 219.61, 219.02, 218.9, 224.3, 228.78, 231.15, 224.3, 217.7, 210.58, 217.42, 215.45, 215.92, 214.51, 209.0, 221.63, 219.05, 228.95, 227.49, 225.63, 222.72, 220.83, 216.71, 220.25, 218.12, 217.25, 214.69, 216.47, 218.58, 226.49, 234.54, 231.68, 224.95, 223.11, 222.28, 215.51, 217.11, 218.12, 214.34, 214.03, 209.48, 204.8, 208.65, 209.23, 209.52, 211.5], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
-        </is>
-      </c>
-      <c r="S20" t="n">
-        <v>211.5</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>UBER</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>59</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UP  </t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>0.588</v>
-      </c>
-      <c r="E21" t="n">
-        <v>62</v>
-      </c>
-      <c r="F21" t="n">
-        <v>40</v>
-      </c>
-      <c r="G21" t="n">
-        <v>35</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-315</v>
-      </c>
-      <c r="I21" t="n">
-        <v>-6.3</v>
-      </c>
-      <c r="J21" t="n">
-        <v>-11.1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L21" t="n">
-        <v>5000</v>
-      </c>
-      <c r="M21" t="n">
-        <v>73</v>
-      </c>
-      <c r="N21" t="n">
-        <v>5</v>
-      </c>
-      <c r="O21" t="n">
-        <v>6</v>
-      </c>
-      <c r="P21" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [76.65, 75.44, 75.13, 73.84, 72.36, 74.97, 72.97, 73.33, 74.66, 77.79, 76.66, 75.34, 73.89, 75.12, 72.34, 73.08, 70.55, 69.18, 69.91, 71.93, 71.71, 71.84, 72.17, 71.73, 72.38, 71.81, 70.48, 72.34, 72.91, 77.28, 76.48, 77.12, 77.49, 77.26, 75.58, 74.7, 74.64, 76.27, 74.11, 74.47, 74.61, 75.12, 73.93, 72.95, 79.17, 76.73, 75.45, 76.15, 76.36, 74.7, 74.69, 75.09, 75.08, 74.09, 74.6, 73.61, 71.82, 70.12, 70.73, 70.92, 70.4, 73.77, 71.62, 71.69, 72.21, 70.71, 70.06, 70.38, 68.61, 69.55, 68.85, 72.85, 73.25, 70.91, 71.64, 71.43, 69.67, 73.85, 72.25, 76.2, 75.5, 72.16, 72.66, 74.43, 72.42, 74.33, 73.6, 74.35, 74.54, 74.26, 72.08, 72.67, 74.04, 72.46, 72.17, 71.55, 70.33, 68.91, 65.94, 68.18], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'SELL', 'BUY', 'SELL', 'BUY', 'SELL', 'FLAT', 'BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY']}</t>
-        </is>
-      </c>
-      <c r="S21" t="n">
-        <v>68.18000000000001</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>GLW</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>52</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UP  </t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>0.609</v>
-      </c>
-      <c r="E22" t="n">
-        <v>53</v>
-      </c>
-      <c r="F22" t="n">
-        <v>10</v>
-      </c>
-      <c r="G22" t="n">
-        <v>45</v>
-      </c>
-      <c r="H22" t="n">
-        <v>538</v>
-      </c>
-      <c r="I22" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="J22" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="K22" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="L22" t="n">
-        <v>5000</v>
-      </c>
-      <c r="M22" t="n">
-        <v>34</v>
-      </c>
-      <c r="N22" t="n">
-        <v>5</v>
-      </c>
-      <c r="O22" t="n">
-        <v>9</v>
-      </c>
-      <c r="P22" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [144.62, 134.53, 123.1, 128.85, 136.01, 131.56, 129.57, 128.92, 131.85, 129.69, 129.66, 132.88, 124.39, 130.77, 141.79, 146.13, 135.11, 136.6, 128.35, 135.76, 142.16, 147.69, 146.28, 148.29, 164.85, 169.54, 170.98, 174.9, 172.56, 168.01, 165.83, 164.13, 165.13, 165.2, 168.5, 169.24, 175.62, 167.75, 152.82, 151.67, 163.99, 158.02, 159.72, 161.85, 181.29, 182.12, 186.65, 207.07, 197.94, 206.19, 207.96, 191.52, 178.28, 175.56, 180.41, 191.6, 193.75, 195.87, 190.6, 182.69, 181.16, 176.7, 200.4, 200.76, 197.7, 177.58, 187.54, 173.94, 168.17, 176.55, 179.2, 187.88, 177.42, 175.4, 194.92, 209.83, 194.07, 205.83, 228.01, 221.05, 255.69, 255.43, 220.63, 196.79, 194.8, 185.38, 184.03, 192.38, 190.89, 183.11, 187.64, 174.41, 158.39, 154.61, 153.1, 162.41, 154.06, 156.06, 146.65, 143.36], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
-        </is>
-      </c>
-      <c r="S22" t="n">
-        <v>143.36</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>NBIS</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>62</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>DOWN</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>0.304</v>
-      </c>
-      <c r="E23" t="n">
-        <v>51</v>
-      </c>
-      <c r="F23" t="n">
-        <v>70</v>
-      </c>
-      <c r="G23" t="n">
-        <v>50</v>
-      </c>
-      <c r="H23" t="n">
-        <v>728</v>
-      </c>
-      <c r="I23" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="J23" t="n">
-        <v>92.09999999999999</v>
-      </c>
-      <c r="K23" t="n">
-        <v>-77.5</v>
-      </c>
-      <c r="L23" t="n">
-        <v>5000</v>
-      </c>
-      <c r="M23" t="n">
-        <v>26</v>
-      </c>
-      <c r="N23" t="n">
-        <v>4</v>
-      </c>
-      <c r="O23" t="n">
-        <v>13</v>
-      </c>
-      <c r="P23" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>4</v>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [97.78, 95.65, 89.33, 94.94, 96.43, 112.0, 108.04, 112.95, 129.85, 116.33, 118.56, 121.52, 117.62, 114.15, 114.91, 115.09, 105.97, 100.82, 92.26, 103.76, 101.95, 108.82, 112.54, 117.4, 125.0, 136.33, 144.97, 154.56, 161.94, 166.77, 165.34, 157.14, 159.16, 156.55, 156.14, 157.08, 147.16, 144.96, 135.51, 141.19, 138.23, 154.49, 176.42, 175.92, 195.09, 184.77, 177.05, 186.1, 179.11, 207.27, 221.15, 219.94, 199.86, 197.73, 191.82, 219.93, 214.77, 208.06, 208.37, 226.34, 231.09, 264.51, 260.58, 251.68, 259.67, 227.81, 218.0, 220.12, 211.69, 222.24, 232.36, 260.07, 265.1, 280.91, 286.69, 283.61, 275.25, 259.66, 256.63, 240.3, 261.15, 276.17, 229.18, 215.62, 213.02, 195.19, 216.48, 216.2, 219.65, 210.51, 194.09, 199.51, 171.77, 177.71, 182.62, 216.92, 218.16, 220.97, 187.77, 187.88], 'signals': ['BUY', 'SELL', 'BUY', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
-        </is>
-      </c>
-      <c r="S23" t="n">
-        <v>187.88</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>SPMO</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>68</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UP  </t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>0.828</v>
-      </c>
-      <c r="E24" t="n">
-        <v>55</v>
-      </c>
-      <c r="F24" t="n">
-        <v>50</v>
-      </c>
-      <c r="G24" t="n">
-        <v>50</v>
-      </c>
-      <c r="H24" t="n">
-        <v>585</v>
-      </c>
-      <c r="I24" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="J24" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="K24" t="n">
-        <v>-9.199999999999999</v>
-      </c>
-      <c r="L24" t="n">
-        <v>5000</v>
-      </c>
-      <c r="M24" t="n">
-        <v>34</v>
-      </c>
-      <c r="N24" t="n">
-        <v>3</v>
-      </c>
-      <c r="O24" t="n">
-        <v>13</v>
-      </c>
-      <c r="P24" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>5</v>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>{'dates': ['2026-03-04', '2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27'], 'prices': [119.74, 119.13, 117.73, 118.78, 118.56, 118.18, 116.66, 115.67, 116.84, 116.84, 115.56, 115.38, 113.29, 114.35, 114.66, 115.14, 111.17, 110.14, 107.67, 111.94, 114.32, 114.56, 115.49, 116.47, 121.17, 122.57, 123.15, 124.4, 126.46, 126.39, 126.55, 128.1, 127.44, 126.46, 128.91, 129.03, 131.32, 131.91, 129.76, 130.57, 133.59, 134.21, 134.23, 137.67, 141.37, 139.09, 143.59, 145.85, 144.23, 146.07, 147.29, 143.26, 141.2, 140.41, 143.09, 144.47, 144.72, 149.57, 149.37, 149.9, 150.36, 152.09, 154.08, 154.85, 152.6, 144.06, 147.65, 147.28, 143.46, 150.35, 152.25, 157.6, 154.38, 155.25, 159.65, 161.66, 154.34, 153.79, 159.64, 154.2, 158.53, 161.54, 155.32, 150.83, 152.98, 149.42, 150.57, 153.08, 153.75, 149.73, 152.86, 150.0, 145.28, 143.89, 144.52, 149.7, 150.07, 149.83, 146.51, 144.75], 'signals': ['FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
-        </is>
-      </c>
-      <c r="S24" t="n">
-        <v>144.75</v>
+        <v>140.95</v>
       </c>
     </row>
   </sheetData>

--- a/demo_results.xlsx
+++ b/demo_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S12"/>
+  <dimension ref="A1:U12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,6 +512,16 @@
           <t>current_price</t>
         </is>
       </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>ATR_14</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>ADX_14</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -520,7 +530,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -528,7 +538,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.455</v>
+        <v>0.452</v>
       </c>
       <c r="E2" t="n">
         <v>61</v>
@@ -576,6 +586,12 @@
       </c>
       <c r="S2" t="n">
         <v>454.62</v>
+      </c>
+      <c r="T2" t="n">
+        <v>38.41143798828125</v>
+      </c>
+      <c r="U2" t="n">
+        <v>14.03515283276854</v>
       </c>
     </row>
     <row r="3">
@@ -585,15 +601,15 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">UP  </t>
+          <t>DOWN</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.512</v>
+        <v>0.492</v>
       </c>
       <c r="E3" t="n">
         <v>54</v>
@@ -605,16 +621,16 @@
         <v>68.40000000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>1802</v>
+        <v>2335</v>
       </c>
       <c r="I3" t="n">
-        <v>36</v>
+        <v>46.7</v>
       </c>
       <c r="J3" t="n">
         <v>106.8</v>
       </c>
       <c r="K3" t="n">
-        <v>-70.8</v>
+        <v>-60.1</v>
       </c>
       <c r="L3" t="n">
         <v>5000</v>
@@ -626,21 +642,27 @@
         <v>2</v>
       </c>
       <c r="O3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="P3" t="n">
         <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [396.82, 370.09, 389.1, 402.88, 418.45, 405.12, 425.89, 441.55, 461.43, 461.47, 444.02, 422.66, 404.12, 395.3, 381.87, 355.26, 357.02, 321.75, 337.79, 367.79, 366.18, 377.7, 377.52, 406.67, 421.45, 420.53, 426.49, 465.59, 456.16, 457.16, 455.0, 448.35, 449.31, 487.41, 481.65, 496.64, 524.48, 504.21, 518.38, 517.08, 542.13, 576.36, 640.1, 666.49, 646.53, 746.7, 795.21, 766.46, 803.51, 775.89, 724.55, 681.44, 698.63, 731.88, 761.98, 750.88, 895.74, 928.27, 923.38, 970.85, 1035.34, 1063.94, 1079.4, 995.85, 863.88, 949.13, 935.75, 891.74, 995.72, 981.46, 1087.82, 1020.6, 1043.03, 1133.82, 1211.19, 1051.61, 1048.35, 1213.37, 1132.16, 1145.1, 1154.11, 1032.12, 975.41, 984.75, 938.38, 948.8, 991.64, 979.3, 937.0, 983.12, 904.28, 853.2, 848.95, 865.46, 970.82, 959.48, 990.21, 920.95, 900.2, 820.53], 'signals': ['FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [396.82, 370.09, 389.1, 402.88, 418.45, 405.12, 425.89, 441.55, 461.43, 461.47, 444.02, 422.66, 404.12, 395.3, 381.87, 355.26, 357.02, 321.75, 337.79, 367.79, 366.18, 377.7, 377.52, 406.67, 421.45, 420.53, 426.49, 465.59, 456.16, 457.16, 455.0, 448.35, 449.31, 487.41, 481.65, 496.64, 524.48, 504.21, 518.38, 517.08, 542.13, 576.36, 640.1, 666.49, 646.53, 746.7, 795.21, 766.46, 803.51, 775.89, 724.55, 681.44, 698.63, 731.88, 761.98, 750.88, 895.74, 928.27, 923.38, 970.85, 1035.34, 1063.94, 1079.4, 995.85, 863.88, 949.13, 935.75, 891.74, 995.72, 981.46, 1087.82, 1020.6, 1043.03, 1133.82, 1211.19, 1051.61, 1048.35, 1213.37, 1132.16, 1145.1, 1154.11, 1032.12, 975.41, 984.75, 938.38, 948.8, 991.64, 979.3, 937.0, 983.12, 904.28, 853.2, 848.95, 865.46, 970.82, 959.48, 990.21, 920.95, 900.2, 820.53], 'signals': ['FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
       <c r="S3" t="n">
         <v>820.53</v>
+      </c>
+      <c r="T3" t="n">
+        <v>77.43857683454242</v>
+      </c>
+      <c r="U3" t="n">
+        <v>26.25061192614741</v>
       </c>
     </row>
     <row r="4">
@@ -658,28 +680,28 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.727</v>
+        <v>0.732</v>
       </c>
       <c r="E4" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="F4" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="G4" t="n">
         <v>57.1</v>
       </c>
       <c r="H4" t="n">
-        <v>2124</v>
+        <v>1761</v>
       </c>
       <c r="I4" t="n">
-        <v>42.5</v>
+        <v>35.2</v>
       </c>
       <c r="J4" t="n">
         <v>70.59999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>-28.1</v>
+        <v>-35.4</v>
       </c>
       <c r="L4" t="n">
         <v>5000</v>
@@ -691,21 +713,27 @@
         <v>2</v>
       </c>
       <c r="O4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P4" t="n">
         <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [106.54, 107.25, 108.53, 109.08, 110.51, 110.39, 110.44, 105.96, 108.3, 108.95, 107.04, 102.25, 103.33, 98.25, 96.46, 98.15, 92.39, 95.01, 97.6, 98.33, 99.78, 99.65, 105.81, 106.63, 98.67, 94.75, 100.56, 99.62, 102.79, 104.55, 105.99, 108.29, 112.4, 116.67, 111.35, 112.03, 113.65, 113.75, 113.1, 111.44, 113.91, 117.31, 119.13, 117.02, 126.43, 131.94, 135.57, 136.54, 140.64, 144.99, 148.52, 154.71, 154.22, 162.53, 162.06, 165.87, 167.89, 161.34, 167.75, 182.75, 195.54, 192.24, 186.9, 179.77, 167.76, 164.7, 161.23, 161.93, 172.88, 170.7, 173.23, 169.87, 170.74, 171.21, 168.86, 170.23, 168.26, 169.66, 175.27, 185.73, 190.79, 193.18, 193.98, 199.38, 194.62, 191.12, 198.4, 187.18, 187.91, 210.73, 206.77, 203.76, 203.08, 198.49, 191.15, 188.42, 183.42, 183.28, 180.11, 181.8], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [106.54, 107.25, 108.53, 109.08, 110.51, 110.39, 110.44, 105.96, 108.3, 108.95, 107.04, 102.25, 103.33, 98.25, 96.46, 98.15, 92.39, 95.01, 97.6, 98.33, 99.78, 99.65, 105.81, 106.63, 98.67, 94.75, 100.56, 99.62, 102.79, 104.55, 105.99, 108.29, 112.4, 116.67, 111.35, 112.03, 113.65, 113.75, 113.1, 111.44, 113.91, 117.31, 119.13, 117.02, 126.43, 131.94, 135.57, 136.54, 140.64, 144.99, 148.52, 154.71, 154.22, 162.53, 162.06, 165.87, 167.89, 161.34, 167.75, 182.75, 195.54, 192.24, 186.9, 179.77, 167.76, 164.7, 161.23, 161.93, 172.88, 170.7, 173.23, 169.87, 170.74, 171.21, 168.86, 170.23, 168.26, 169.66, 175.27, 185.73, 190.79, 193.18, 193.98, 199.38, 194.62, 191.12, 198.4, 187.18, 187.91, 210.73, 206.77, 203.76, 203.08, 198.49, 191.15, 188.42, 183.42, 183.28, 180.11, 181.8], 'signals': ['FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY']}</t>
         </is>
       </c>
       <c r="S4" t="n">
         <v>181.8</v>
+      </c>
+      <c r="T4" t="n">
+        <v>10.44007001604353</v>
+      </c>
+      <c r="U4" t="n">
+        <v>27.9227001484601</v>
       </c>
     </row>
     <row r="5">
@@ -715,36 +743,36 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DOWN</t>
+          <t xml:space="preserve">UP  </t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.426</v>
+        <v>0.622</v>
       </c>
       <c r="E5" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="F5" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="G5" t="n">
         <v>50</v>
       </c>
       <c r="H5" t="n">
-        <v>836</v>
+        <v>628</v>
       </c>
       <c r="I5" t="n">
-        <v>16.7</v>
+        <v>12.6</v>
       </c>
       <c r="J5" t="n">
         <v>7.6</v>
       </c>
       <c r="K5" t="n">
-        <v>9.1</v>
+        <v>5</v>
       </c>
       <c r="L5" t="n">
         <v>5000</v>
@@ -756,21 +784,27 @@
         <v>4</v>
       </c>
       <c r="O5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="P5" t="n">
         <v>4</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [183.12, 177.6, 182.43, 184.54, 185.81, 182.93, 180.04, 183.01, 181.72, 180.19, 178.35, 172.5, 175.44, 175.0, 178.47, 171.04, 167.32, 164.98, 174.2, 175.55, 177.18, 177.43, 177.89, 181.87, 183.7, 188.41, 189.09, 196.28, 198.64, 198.12, 201.45, 201.82, 199.65, 202.26, 199.41, 208.03, 216.36, 212.92, 209.01, 199.34, 198.22, 198.25, 196.27, 207.59, 211.25, 214.95, 219.18, 220.52, 225.57, 235.47, 225.06, 222.06, 220.35, 223.21, 219.25, 215.08, 214.61, 212.35, 214.0, 210.89, 224.1, 222.56, 214.5, 218.66, 205.1, 208.64, 208.19, 200.42, 204.87, 205.19, 212.45, 207.41, 204.65, 210.69, 208.65, 200.04, 199.0, 195.74, 192.53, 194.97, 200.09, 197.58, 194.83, 195.55, 196.93, 204.12, 202.78, 210.96, 203.53, 211.8, 212.5, 207.4, 202.81, 203.28, 207.29, 212.06, 208.76, 206.84, 196.51, 197.01], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [183.12, 177.6, 182.43, 184.54, 185.81, 182.93, 180.04, 183.01, 181.72, 180.19, 178.35, 172.5, 175.44, 175.0, 178.47, 171.04, 167.32, 164.98, 174.2, 175.55, 177.18, 177.43, 177.89, 181.87, 183.7, 188.41, 189.09, 196.28, 198.64, 198.12, 201.45, 201.82, 199.65, 202.26, 199.41, 208.03, 216.36, 212.92, 209.01, 199.34, 198.22, 198.25, 196.27, 207.59, 211.25, 214.95, 219.18, 220.52, 225.57, 235.47, 225.06, 222.06, 220.35, 223.21, 219.25, 215.08, 214.61, 212.35, 214.0, 210.89, 224.1, 222.56, 214.5, 218.66, 205.1, 208.64, 208.19, 200.42, 204.87, 205.19, 212.45, 207.41, 204.65, 210.69, 208.65, 200.04, 199.0, 195.74, 192.53, 194.97, 200.09, 197.58, 194.83, 195.55, 196.93, 204.12, 202.78, 210.96, 203.53, 211.8, 212.5, 207.4, 202.81, 203.28, 207.29, 212.06, 208.76, 206.84, 196.51, 197.01], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
       <c r="S5" t="n">
         <v>197.01</v>
+      </c>
+      <c r="T5" t="n">
+        <v>7.734284537179129</v>
+      </c>
+      <c r="U5" t="n">
+        <v>23.25884591421792</v>
       </c>
     </row>
     <row r="6">
@@ -780,7 +814,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -788,10 +822,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.435</v>
+        <v>0.401</v>
       </c>
       <c r="E6" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F6" t="n">
         <v>20</v>
@@ -800,16 +834,16 @@
         <v>45</v>
       </c>
       <c r="H6" t="n">
-        <v>698</v>
+        <v>373</v>
       </c>
       <c r="I6" t="n">
-        <v>14</v>
+        <v>7.5</v>
       </c>
       <c r="J6" t="n">
         <v>-19.1</v>
       </c>
       <c r="K6" t="n">
-        <v>33.1</v>
+        <v>26.6</v>
       </c>
       <c r="L6" t="n">
         <v>5000</v>
@@ -821,21 +855,27 @@
         <v>4</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P6" t="n">
         <v>4</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [152.67, 157.16, 156.43, 151.14, 151.6, 153.5, 150.95, 152.72, 155.08, 152.77, 155.68, 150.68, 160.84, 154.78, 154.96, 147.56, 143.06, 137.55, 146.28, 146.49, 148.46, 147.93, 150.07, 140.76, 130.49, 128.06, 132.37, 135.7, 142.15, 142.76, 146.39, 145.89, 145.97, 152.62, 141.57, 143.09, 143.1, 141.18, 137.97, 139.11, 144.07, 146.03, 135.91, 133.79, 137.05, 137.8, 136.89, 136.0, 130.05, 133.73, 133.99, 135.14, 135.26, 137.15, 137.41, 136.88, 136.6, 132.51, 143.34, 156.54, 160.65, 152.17, 142.2, 141.7, 135.53, 136.47, 132.07, 130.21, 131.08, 127.99, 134.71, 133.25, 130.63, 128.47, 119.5, 116.7, 113.5, 107.27, 112.93, 115.7, 116.67, 125.73, 129.3, 132.54, 134.37, 132.22, 129.04, 126.79, 130.04, 133.72, 133.76, 134.44, 132.38, 134.85, 132.66, 124.57, 123.37, 122.92, 131.53, 123.53], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT']}</t>
+          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [152.67, 157.16, 156.43, 151.14, 151.6, 153.5, 150.95, 152.72, 155.08, 152.77, 155.68, 150.68, 160.84, 154.78, 154.96, 147.56, 143.06, 137.55, 146.28, 146.49, 148.46, 147.93, 150.07, 140.76, 130.49, 128.06, 132.37, 135.7, 142.15, 142.76, 146.39, 145.89, 145.97, 152.62, 141.57, 143.09, 143.1, 141.18, 137.97, 139.11, 144.07, 146.03, 135.91, 133.79, 137.05, 137.8, 136.89, 136.0, 130.05, 133.73, 133.99, 135.14, 135.26, 137.15, 137.41, 136.88, 136.6, 132.51, 143.34, 156.54, 160.65, 152.17, 142.2, 141.7, 135.53, 136.47, 132.07, 130.21, 131.08, 127.99, 134.71, 133.25, 130.63, 128.47, 119.5, 116.7, 113.5, 107.27, 112.93, 115.7, 116.67, 125.73, 129.3, 132.54, 134.37, 132.22, 129.04, 126.79, 130.04, 133.72, 133.76, 134.44, 132.38, 134.85, 132.66, 124.57, 123.37, 122.92, 131.53, 123.53], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT']}</t>
         </is>
       </c>
       <c r="S6" t="n">
         <v>123.53</v>
+      </c>
+      <c r="T6" t="n">
+        <v>7.04071535382952</v>
+      </c>
+      <c r="U6" t="n">
+        <v>22.19321356384988</v>
       </c>
     </row>
     <row r="7">
@@ -845,7 +885,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -853,10 +893,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.362</v>
+        <v>0.285</v>
       </c>
       <c r="E7" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F7" t="n">
         <v>40</v>
@@ -896,11 +936,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [205.71, 197.22, 199.79, 196.52, 198.63, 193.23, 195.53, 203.32, 210.23, 202.29, 202.91, 197.5, 200.62, 181.04, 181.1, 173.38, 161.14, 160.79, 174.61, 172.99, 171.46, 174.79, 175.18, 175.09, 169.02, 167.85, 174.53, 184.41, 195.9, 199.83, 206.33, 211.63, 195.95, 206.24, 197.93, 199.77, 196.68, 194.1, 181.73, 187.77, 191.25, 202.99, 197.75, 197.96, 192.96, 201.16, 216.6, 207.64, 201.8, 212.01, 195.43, 189.44, 193.45, 191.29, 193.56, 184.99, 180.01, 173.78, 182.25, 189.03, 182.61, 173.99, 163.22, 164.13, 152.4, 162.11, 155.5, 153.97, 160.43, 159.78, 169.62, 169.27, 164.92, 163.26, 164.84, 158.18, 150.11, 142.52, 149.06, 151.65, 146.19, 159.24, 165.48, 168.87, 163.51, 159.36, 158.44, 159.07, 157.37, 161.5, 167.21, 160.49, 157.12, 160.43, 175.85, 166.12, 161.16, 158.29, 167.49, 167.9], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [205.71, 197.22, 199.79, 196.52, 198.63, 193.23, 195.53, 203.32, 210.23, 202.29, 202.91, 197.5, 200.62, 181.04, 181.1, 173.38, 161.14, 160.79, 174.61, 172.99, 171.46, 174.79, 175.18, 175.09, 169.02, 167.85, 174.53, 184.41, 195.9, 199.83, 206.33, 211.63, 195.95, 206.24, 197.93, 199.77, 196.68, 194.1, 181.73, 187.77, 191.25, 202.99, 197.75, 197.96, 192.96, 201.16, 216.6, 207.64, 201.8, 212.01, 195.43, 189.44, 193.45, 191.29, 193.56, 184.99, 180.01, 173.78, 182.25, 189.03, 182.61, 173.99, 163.22, 164.13, 152.4, 162.11, 155.5, 153.97, 160.43, 159.78, 169.62, 169.27, 164.92, 163.26, 164.84, 158.18, 150.11, 142.52, 149.06, 151.65, 146.19, 159.24, 165.48, 168.87, 163.51, 159.36, 158.44, 159.07, 157.37, 161.5, 167.21, 160.49, 157.12, 160.43, 175.85, 166.12, 161.16, 158.29, 167.49, 167.9], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
       <c r="S7" t="n">
         <v>167.9</v>
+      </c>
+      <c r="T7" t="n">
+        <v>9.024287632533483</v>
+      </c>
+      <c r="U7" t="n">
+        <v>17.05993620111895</v>
       </c>
     </row>
     <row r="8">
@@ -910,7 +956,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -918,16 +964,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.414</v>
+        <v>0.372</v>
       </c>
       <c r="E8" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F8" t="n">
         <v>80</v>
       </c>
       <c r="G8" t="n">
-        <v>33.3</v>
+        <v>30</v>
       </c>
       <c r="H8" t="n">
         <v>-293</v>
@@ -961,11 +1007,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [99.17, 99.02, 98.32, 96.94, 94.89, 94.31, 95.31, 95.2, 94.36, 94.7, 91.74, 91.82, 93.38, 90.92, 92.28, 93.32, 93.43, 92.97, 96.15, 95.55, 98.66, 98.93, 98.82, 99.39, 102.05, 103.01, 103.16, 106.28, 107.71, 107.79, 97.31, 94.83, 92.58, 93.24, 92.82, 92.44, 91.37, 92.27, 92.12, 93.61, 92.06, 91.02, 87.89, 88.27, 88.25, 87.49, 85.45, 87.66, 87.56, 86.94, 87.02, 89.65, 89.33, 88.09, 89.3, 88.6, 87.68, 87.35, 86.36, 86.02, 85.85, 83.33, 81.52, 81.56, 82.18, 82.64, 81.41, 82.0, 81.27, 80.34, 81.67, 78.72, 76.96, 77.38, 72.88, 72.82, 71.84, 70.9, 73.81, 73.78, 71.4, 74.19, 77.65, 76.02, 76.18, 75.59, 75.47, 73.37, 73.83, 73.53, 73.68, 74.35, 68.95, 67.6, 68.67, 68.53, 68.89, 70.09, 70.4, 72.39], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [99.17, 99.02, 98.32, 96.94, 94.89, 94.31, 95.31, 95.2, 94.36, 94.7, 91.74, 91.82, 93.38, 90.92, 92.28, 93.32, 93.43, 92.97, 96.15, 95.55, 98.66, 98.93, 98.82, 99.39, 102.05, 103.01, 103.16, 106.28, 107.71, 107.79, 97.31, 94.83, 92.58, 93.24, 92.82, 92.44, 91.37, 92.27, 92.12, 93.61, 92.06, 91.02, 87.89, 88.27, 88.25, 87.49, 85.45, 87.66, 87.56, 86.94, 87.02, 89.65, 89.33, 88.09, 89.3, 88.6, 87.68, 87.35, 86.36, 86.02, 85.85, 83.33, 81.52, 81.56, 82.18, 82.64, 81.41, 82.0, 81.27, 80.34, 81.67, 78.72, 76.96, 77.38, 72.88, 72.82, 71.84, 70.9, 73.81, 73.78, 71.4, 74.19, 77.65, 76.02, 76.18, 75.59, 75.47, 73.37, 73.83, 73.53, 73.68, 74.35, 68.95, 67.6, 68.67, 68.53, 68.89, 70.09, 70.4, 72.39], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
       <c r="S8" t="n">
         <v>72.39</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.682855878557478</v>
+      </c>
+      <c r="U8" t="n">
+        <v>34.27873709740564</v>
       </c>
     </row>
     <row r="9">
@@ -975,36 +1027,36 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DOWN</t>
+          <t xml:space="preserve">UP  </t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.415</v>
+        <v>0.703</v>
       </c>
       <c r="E9" t="n">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="F9" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="G9" t="n">
         <v>50</v>
       </c>
       <c r="H9" t="n">
-        <v>831</v>
+        <v>742</v>
       </c>
       <c r="I9" t="n">
-        <v>16.6</v>
+        <v>14.8</v>
       </c>
       <c r="J9" t="n">
         <v>30.8</v>
       </c>
       <c r="K9" t="n">
-        <v>-14.2</v>
+        <v>-16</v>
       </c>
       <c r="L9" t="n">
         <v>5000</v>
@@ -1013,24 +1065,30 @@
         <v>14</v>
       </c>
       <c r="N9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.3</v>
+        <v>5.5</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [260.05, 257.22, 259.64, 260.59, 260.57, 255.52, 249.89, 252.59, 254.0, 249.71, 248.73, 247.76, 251.26, 251.41, 252.39, 252.66, 248.57, 246.4, 253.56, 255.39, 255.68, 258.62, 253.27, 258.66, 260.25, 260.24, 258.96, 258.59, 266.18, 263.16, 269.98, 272.8, 265.93, 272.92, 273.18, 270.81, 267.36, 270.46, 269.92, 271.1, 279.88, 276.58, 283.92, 287.25, 287.18, 293.05, 292.68, 294.8, 298.87, 298.21, 300.23, 297.84, 298.97, 302.25, 304.99, 308.82, 308.33, 310.85, 312.51, 312.06, 306.31, 315.2, 310.26, 311.23, 307.34, 301.54, 290.55, 291.58, 295.63, 291.13, 296.42, 299.24, 295.95, 298.01, 297.01, 294.3, 293.08, 275.15, 283.78, 281.74, 289.36, 294.38, 308.63, 312.66, 310.66, 313.39, 316.22, 315.32, 317.31, 314.86, 327.5, 333.26, 333.74, 326.59, 327.74, 325.89, 321.66, 333.02, 336.91, 340.08], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [260.05, 257.22, 259.64, 260.59, 260.57, 255.52, 249.89, 252.59, 254.0, 249.71, 248.73, 247.76, 251.26, 251.41, 252.39, 252.66, 248.57, 246.4, 253.56, 255.39, 255.68, 258.62, 253.27, 258.66, 260.25, 260.24, 258.96, 258.59, 266.18, 263.16, 269.98, 272.8, 265.93, 272.92, 273.18, 270.81, 267.36, 270.46, 269.92, 271.1, 279.88, 276.58, 283.92, 287.25, 287.18, 293.05, 292.68, 294.8, 298.87, 298.21, 300.23, 297.84, 298.97, 302.25, 304.99, 308.82, 308.33, 310.85, 312.51, 312.06, 306.31, 315.2, 310.26, 311.23, 307.34, 301.54, 290.55, 291.58, 295.63, 291.13, 296.42, 299.24, 295.95, 298.01, 297.01, 294.3, 293.08, 275.15, 283.78, 281.74, 289.36, 294.38, 308.63, 312.66, 310.66, 313.39, 316.22, 315.32, 317.31, 314.86, 327.5, 333.26, 333.74, 326.59, 327.74, 325.89, 321.66, 333.02, 336.91, 340.08], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
       <c r="S9" t="n">
         <v>340.08</v>
+      </c>
+      <c r="T9" t="n">
+        <v>7.901430402483259</v>
+      </c>
+      <c r="U9" t="n">
+        <v>43.6905405239262</v>
       </c>
     </row>
     <row r="10">
@@ -1040,7 +1098,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1048,7 +1106,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.607</v>
+        <v>0.644</v>
       </c>
       <c r="E10" t="n">
         <v>53</v>
@@ -1096,6 +1154,12 @@
       </c>
       <c r="S10" t="n">
         <v>126.01</v>
+      </c>
+      <c r="T10" t="n">
+        <v>13.64000047956194</v>
+      </c>
+      <c r="U10" t="n">
+        <v>40.63643316345468</v>
       </c>
     </row>
     <row r="11">
@@ -1113,16 +1177,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.438</v>
+        <v>0.328</v>
       </c>
       <c r="E11" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F11" t="n">
         <v>70</v>
       </c>
       <c r="G11" t="n">
-        <v>66.7</v>
+        <v>65</v>
       </c>
       <c r="H11" t="n">
         <v>1889</v>
@@ -1156,11 +1220,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [95.65, 89.33, 94.94, 96.43, 112.0, 108.04, 112.95, 129.85, 116.33, 118.56, 121.52, 117.62, 114.15, 114.91, 115.09, 105.97, 100.82, 92.26, 103.76, 101.95, 108.82, 112.54, 117.4, 125.0, 136.33, 144.97, 154.56, 161.94, 166.77, 165.34, 157.14, 159.16, 156.55, 156.14, 157.08, 147.16, 144.96, 135.51, 141.19, 138.23, 154.49, 176.42, 175.92, 195.09, 184.77, 177.05, 186.1, 179.11, 207.27, 221.15, 219.94, 199.86, 197.73, 191.82, 219.93, 214.77, 208.06, 208.37, 226.34, 231.09, 264.51, 260.58, 251.68, 259.67, 227.81, 218.0, 220.12, 211.69, 222.24, 232.36, 260.07, 265.1, 280.91, 286.69, 283.61, 275.25, 259.66, 256.63, 240.3, 261.15, 276.17, 229.18, 215.62, 213.02, 195.19, 216.48, 216.2, 219.65, 210.51, 194.09, 199.51, 171.77, 177.71, 182.62, 216.92, 218.16, 220.97, 187.77, 187.88, 169.69], 'signals': ['FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [95.65, 89.33, 94.94, 96.43, 112.0, 108.04, 112.95, 129.85, 116.33, 118.56, 121.52, 117.62, 114.15, 114.91, 115.09, 105.97, 100.82, 92.26, 103.76, 101.95, 108.82, 112.54, 117.4, 125.0, 136.33, 144.97, 154.56, 161.94, 166.77, 165.34, 157.14, 159.16, 156.55, 156.14, 157.08, 147.16, 144.96, 135.51, 141.19, 138.23, 154.49, 176.42, 175.92, 195.09, 184.77, 177.05, 186.1, 179.11, 207.27, 221.15, 219.94, 199.86, 197.73, 191.82, 219.93, 214.77, 208.06, 208.37, 226.34, 231.09, 264.51, 260.58, 251.68, 259.67, 227.81, 218.0, 220.12, 211.69, 222.24, 232.36, 260.07, 265.1, 280.91, 286.69, 283.61, 275.25, 259.66, 256.63, 240.3, 261.15, 276.17, 229.18, 215.62, 213.02, 195.19, 216.48, 216.2, 219.65, 210.51, 194.09, 199.51, 171.77, 177.71, 182.62, 216.92, 218.16, 220.97, 187.77, 187.88, 169.69], 'signals': ['FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
       <c r="S11" t="n">
         <v>169.69</v>
+      </c>
+      <c r="T11" t="n">
+        <v>22.5277829851423</v>
+      </c>
+      <c r="U11" t="n">
+        <v>19.93684147717601</v>
       </c>
     </row>
     <row r="12">
@@ -1170,7 +1240,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1178,10 +1248,10 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.856</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F12" t="n">
         <v>60</v>
@@ -1190,16 +1260,16 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>313</v>
+        <v>402</v>
       </c>
       <c r="I12" t="n">
-        <v>6.3</v>
+        <v>8</v>
       </c>
       <c r="J12" t="n">
         <v>18.3</v>
       </c>
       <c r="K12" t="n">
-        <v>-12</v>
+        <v>-10.3</v>
       </c>
       <c r="L12" t="n">
         <v>5000</v>
@@ -1208,24 +1278,30 @@
         <v>35</v>
       </c>
       <c r="N12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q12" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [119.13, 117.73, 118.78, 118.56, 118.18, 116.66, 115.67, 116.84, 116.84, 115.56, 115.38, 113.29, 114.35, 114.66, 115.14, 111.17, 110.14, 107.67, 111.94, 114.32, 114.56, 115.49, 116.47, 121.17, 122.57, 123.15, 124.4, 126.46, 126.39, 126.55, 128.1, 127.44, 126.46, 128.91, 129.03, 131.32, 131.91, 129.76, 130.57, 133.59, 134.21, 134.23, 137.67, 141.37, 139.09, 143.59, 145.85, 144.23, 146.07, 147.29, 143.26, 141.2, 140.41, 143.09, 144.47, 144.72, 149.57, 149.37, 149.9, 150.36, 152.09, 154.08, 154.85, 152.6, 144.06, 147.65, 147.28, 143.46, 150.35, 152.25, 157.6, 154.38, 155.25, 159.65, 161.66, 154.34, 153.79, 159.64, 154.2, 158.53, 161.54, 155.32, 150.83, 152.98, 149.42, 150.57, 153.08, 153.75, 149.73, 152.86, 150.0, 145.28, 143.89, 144.52, 149.7, 150.07, 149.83, 146.51, 144.75, 140.95], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [119.13, 117.73, 118.78, 118.56, 118.18, 116.66, 115.67, 116.84, 116.84, 115.56, 115.38, 113.29, 114.35, 114.66, 115.14, 111.17, 110.14, 107.67, 111.94, 114.32, 114.56, 115.49, 116.47, 121.17, 122.57, 123.15, 124.4, 126.46, 126.39, 126.55, 128.1, 127.44, 126.46, 128.91, 129.03, 131.32, 131.91, 129.76, 130.57, 133.59, 134.21, 134.23, 137.67, 141.37, 139.09, 143.59, 145.85, 144.23, 146.07, 147.29, 143.26, 141.2, 140.41, 143.09, 144.47, 144.72, 149.57, 149.37, 149.9, 150.36, 152.09, 154.08, 154.85, 152.6, 144.06, 147.65, 147.28, 143.46, 150.35, 152.25, 157.6, 154.38, 155.25, 159.65, 161.66, 154.34, 153.79, 159.64, 154.2, 158.53, 161.54, 155.32, 150.83, 152.98, 149.42, 150.57, 153.08, 153.75, 149.73, 152.86, 150.0, 145.28, 143.89, 144.52, 149.7, 150.07, 149.83, 146.51, 144.75, 140.95], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
       <c r="S12" t="n">
         <v>140.95</v>
+      </c>
+      <c r="T12" t="n">
+        <v>4.625142778669085</v>
+      </c>
+      <c r="U12" t="n">
+        <v>32.31190962718114</v>
       </c>
     </row>
   </sheetData>

--- a/demo_results.xlsx
+++ b/demo_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U12"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -522,6 +522,11 @@
           <t>ADX_14</t>
         </is>
       </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>last_signal</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -538,10 +543,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.452</v>
+        <v>0.473</v>
       </c>
       <c r="E2" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F2" t="n">
         <v>60</v>
@@ -581,7 +586,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [199.45, 192.43, 202.68, 203.23, 204.83, 197.74, 193.39, 196.58, 196.31, 199.46, 205.27, 201.33, 202.68, 205.37, 220.27, 203.77, 201.99, 196.04, 203.43, 210.21, 217.5, 220.18, 221.53, 231.82, 236.64, 245.04, 246.83, 255.07, 258.12, 278.26, 278.39, 274.95, 284.49, 303.46, 305.33, 347.81, 334.63, 323.21, 337.11, 354.49, 360.54, 341.54, 355.26, 421.39, 408.46, 455.19, 458.79, 448.29, 445.5, 449.7, 424.1, 420.99, 414.05, 447.58, 449.59, 467.51, 503.89, 495.54, 518.09, 516.1, 510.13, 521.54, 542.52, 523.2, 466.38, 490.33, 475.51, 452.4, 488.45, 511.57, 547.26, 507.29, 512.48, 537.37, 551.63, 519.85, 519.74, 532.57, 521.58, 539.49, 580.91, 540.88, 517.82, 552.05, 516.11, 517.41, 546.72, 557.89, 534.39, 548.13, 529.14, 500.94, 495.76, 503.57, 544.43, 552.33, 539.69, 521.95, 494.95, 454.62], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [199.45, 192.43, 202.68, 203.23, 204.83, 197.74, 193.39, 196.58, 196.31, 199.46, 205.27, 201.33, 202.68, 205.37, 220.27, 203.77, 201.99, 196.04, 203.43, 210.21, 217.5, 220.18, 221.53, 231.82, 236.64, 245.04, 246.83, 255.07, 258.12, 278.26, 278.39, 274.95, 284.49, 303.46, 305.33, 347.81, 334.63, 323.21, 337.11, 354.49, 360.54, 341.54, 355.26, 421.39, 408.46, 455.19, 458.79, 448.29, 445.5, 449.7, 424.1, 420.99, 414.05, 447.58, 449.59, 467.51, 503.89, 495.54, 518.09, 516.1, 510.13, 521.54, 542.52, 523.2, 466.38, 490.33, 475.51, 452.4, 488.45, 511.57, 547.26, 507.29, 512.48, 537.37, 551.63, 519.85, 519.74, 532.57, 521.58, 539.49, 580.91, 540.88, 517.82, 552.05, 516.11, 517.41, 546.72, 557.89, 534.39, 548.13, 529.14, 500.94, 495.76, 503.57, 544.43, 552.33, 539.69, 521.95, 494.95, 454.62], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
       <c r="S2" t="n">
@@ -592,6 +597,11 @@
       </c>
       <c r="U2" t="n">
         <v>14.03515283276854</v>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -601,7 +611,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -609,13 +619,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.492</v>
+        <v>0.455</v>
       </c>
       <c r="E3" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="G3" t="n">
         <v>68.40000000000001</v>
@@ -652,7 +662,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [396.82, 370.09, 389.1, 402.88, 418.45, 405.12, 425.89, 441.55, 461.43, 461.47, 444.02, 422.66, 404.12, 395.3, 381.87, 355.26, 357.02, 321.75, 337.79, 367.79, 366.18, 377.7, 377.52, 406.67, 421.45, 420.53, 426.49, 465.59, 456.16, 457.16, 455.0, 448.35, 449.31, 487.41, 481.65, 496.64, 524.48, 504.21, 518.38, 517.08, 542.13, 576.36, 640.1, 666.49, 646.53, 746.7, 795.21, 766.46, 803.51, 775.89, 724.55, 681.44, 698.63, 731.88, 761.98, 750.88, 895.74, 928.27, 923.38, 970.85, 1035.34, 1063.94, 1079.4, 995.85, 863.88, 949.13, 935.75, 891.74, 995.72, 981.46, 1087.82, 1020.6, 1043.03, 1133.82, 1211.19, 1051.61, 1048.35, 1213.37, 1132.16, 1145.1, 1154.11, 1032.12, 975.41, 984.75, 938.38, 948.8, 991.64, 979.3, 937.0, 983.12, 904.28, 853.2, 848.95, 865.46, 970.82, 959.48, 990.21, 920.95, 900.2, 820.53], 'signals': ['FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [396.82, 370.09, 389.1, 402.88, 418.45, 405.12, 425.89, 441.55, 461.43, 461.47, 444.02, 422.66, 404.12, 395.3, 381.87, 355.26, 357.02, 321.75, 337.79, 367.79, 366.18, 377.7, 377.52, 406.67, 421.45, 420.53, 426.49, 465.59, 456.16, 457.16, 455.0, 448.35, 449.31, 487.41, 481.65, 496.64, 524.48, 504.21, 518.38, 517.08, 542.13, 576.36, 640.1, 666.49, 646.53, 746.7, 795.21, 766.46, 803.51, 775.89, 724.55, 681.44, 698.63, 731.88, 761.98, 750.88, 895.74, 928.27, 923.38, 970.85, 1035.34, 1063.94, 1079.4, 995.85, 863.88, 949.13, 935.75, 891.74, 995.72, 981.46, 1087.82, 1020.6, 1043.03, 1133.82, 1211.19, 1051.61, 1048.35, 1213.37, 1132.16, 1145.1, 1154.11, 1032.12, 975.41, 984.75, 938.38, 948.8, 991.64, 979.3, 937.0, 983.12, 904.28, 853.2, 848.95, 865.46, 970.82, 959.48, 990.21, 920.95, 900.2, 820.53], 'signals': ['FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
       <c r="S3" t="n">
@@ -662,7 +672,12 @@
         <v>77.43857683454242</v>
       </c>
       <c r="U3" t="n">
-        <v>26.25061192614741</v>
+        <v>26.25061192614724</v>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -680,28 +695,28 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.732</v>
+        <v>0.766</v>
       </c>
       <c r="E4" t="n">
         <v>54</v>
       </c>
       <c r="F4" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="G4" t="n">
         <v>57.1</v>
       </c>
       <c r="H4" t="n">
-        <v>1761</v>
+        <v>2124</v>
       </c>
       <c r="I4" t="n">
-        <v>35.2</v>
+        <v>42.5</v>
       </c>
       <c r="J4" t="n">
         <v>70.59999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>-35.4</v>
+        <v>-28.1</v>
       </c>
       <c r="L4" t="n">
         <v>5000</v>
@@ -713,17 +728,17 @@
         <v>2</v>
       </c>
       <c r="O4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P4" t="n">
         <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [106.54, 107.25, 108.53, 109.08, 110.51, 110.39, 110.44, 105.96, 108.3, 108.95, 107.04, 102.25, 103.33, 98.25, 96.46, 98.15, 92.39, 95.01, 97.6, 98.33, 99.78, 99.65, 105.81, 106.63, 98.67, 94.75, 100.56, 99.62, 102.79, 104.55, 105.99, 108.29, 112.4, 116.67, 111.35, 112.03, 113.65, 113.75, 113.1, 111.44, 113.91, 117.31, 119.13, 117.02, 126.43, 131.94, 135.57, 136.54, 140.64, 144.99, 148.52, 154.71, 154.22, 162.53, 162.06, 165.87, 167.89, 161.34, 167.75, 182.75, 195.54, 192.24, 186.9, 179.77, 167.76, 164.7, 161.23, 161.93, 172.88, 170.7, 173.23, 169.87, 170.74, 171.21, 168.86, 170.23, 168.26, 169.66, 175.27, 185.73, 190.79, 193.18, 193.98, 199.38, 194.62, 191.12, 198.4, 187.18, 187.91, 210.73, 206.77, 203.76, 203.08, 198.49, 191.15, 188.42, 183.42, 183.28, 180.11, 181.8], 'signals': ['FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY']}</t>
+          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [106.54, 107.25, 108.53, 109.08, 110.51, 110.39, 110.44, 105.96, 108.3, 108.95, 107.04, 102.25, 103.33, 98.25, 96.46, 98.15, 92.39, 95.01, 97.6, 98.33, 99.78, 99.65, 105.81, 106.63, 98.67, 94.75, 100.56, 99.62, 102.79, 104.55, 105.99, 108.29, 112.4, 116.67, 111.35, 112.03, 113.65, 113.75, 113.1, 111.44, 113.91, 117.31, 119.13, 117.02, 126.43, 131.94, 135.57, 136.54, 140.64, 144.99, 148.52, 154.71, 154.22, 162.53, 162.06, 165.87, 167.89, 161.34, 167.75, 182.75, 195.54, 192.24, 186.9, 179.77, 167.76, 164.7, 161.23, 161.93, 172.88, 170.7, 173.23, 169.87, 170.74, 171.21, 168.86, 170.23, 168.26, 169.66, 175.27, 185.73, 190.79, 193.18, 193.98, 199.38, 194.62, 191.12, 198.4, 187.18, 187.91, 210.73, 206.77, 203.76, 203.08, 198.49, 191.15, 188.42, 183.42, 183.28, 180.11, 181.8], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
       <c r="S4" t="n">
@@ -734,6 +749,11 @@
       </c>
       <c r="U4" t="n">
         <v>27.9227001484601</v>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -743,7 +763,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -751,10 +771,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.622</v>
+        <v>0.668</v>
       </c>
       <c r="E5" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F5" t="n">
         <v>50</v>
@@ -763,16 +783,16 @@
         <v>50</v>
       </c>
       <c r="H5" t="n">
-        <v>628</v>
+        <v>938</v>
       </c>
       <c r="I5" t="n">
-        <v>12.6</v>
+        <v>18.8</v>
       </c>
       <c r="J5" t="n">
         <v>7.6</v>
       </c>
       <c r="K5" t="n">
-        <v>5</v>
+        <v>11.2</v>
       </c>
       <c r="L5" t="n">
         <v>5000</v>
@@ -781,20 +801,20 @@
         <v>25</v>
       </c>
       <c r="N5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q5" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [183.12, 177.6, 182.43, 184.54, 185.81, 182.93, 180.04, 183.01, 181.72, 180.19, 178.35, 172.5, 175.44, 175.0, 178.47, 171.04, 167.32, 164.98, 174.2, 175.55, 177.18, 177.43, 177.89, 181.87, 183.7, 188.41, 189.09, 196.28, 198.64, 198.12, 201.45, 201.82, 199.65, 202.26, 199.41, 208.03, 216.36, 212.92, 209.01, 199.34, 198.22, 198.25, 196.27, 207.59, 211.25, 214.95, 219.18, 220.52, 225.57, 235.47, 225.06, 222.06, 220.35, 223.21, 219.25, 215.08, 214.61, 212.35, 214.0, 210.89, 224.1, 222.56, 214.5, 218.66, 205.1, 208.64, 208.19, 200.42, 204.87, 205.19, 212.45, 207.41, 204.65, 210.69, 208.65, 200.04, 199.0, 195.74, 192.53, 194.97, 200.09, 197.58, 194.83, 195.55, 196.93, 204.12, 202.78, 210.96, 203.53, 211.8, 212.5, 207.4, 202.81, 203.28, 207.29, 212.06, 208.76, 206.84, 196.51, 197.01], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [183.12, 177.6, 182.43, 184.54, 185.81, 182.93, 180.04, 183.01, 181.72, 180.19, 178.35, 172.5, 175.44, 175.0, 178.47, 171.04, 167.32, 164.98, 174.2, 175.55, 177.18, 177.43, 177.89, 181.87, 183.7, 188.41, 189.09, 196.28, 198.64, 198.12, 201.45, 201.82, 199.65, 202.26, 199.41, 208.03, 216.36, 212.92, 209.01, 199.34, 198.22, 198.25, 196.27, 207.59, 211.25, 214.95, 219.18, 220.52, 225.57, 235.47, 225.06, 222.06, 220.35, 223.21, 219.25, 215.08, 214.61, 212.35, 214.0, 210.89, 224.1, 222.56, 214.5, 218.66, 205.1, 208.64, 208.19, 200.42, 204.87, 205.19, 212.45, 207.41, 204.65, 210.69, 208.65, 200.04, 199.0, 195.74, 192.53, 194.97, 200.09, 197.58, 194.83, 195.55, 196.93, 204.12, 202.78, 210.96, 203.53, 211.8, 212.5, 207.4, 202.81, 203.28, 207.29, 212.06, 208.76, 206.84, 196.51, 197.01], 'signals': ['BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
       <c r="S5" t="n">
@@ -804,7 +824,12 @@
         <v>7.734284537179129</v>
       </c>
       <c r="U5" t="n">
-        <v>23.25884591421792</v>
+        <v>23.25884591416595</v>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -814,7 +839,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -822,7 +847,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.401</v>
+        <v>0.37</v>
       </c>
       <c r="E6" t="n">
         <v>61</v>
@@ -865,7 +890,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [152.67, 157.16, 156.43, 151.14, 151.6, 153.5, 150.95, 152.72, 155.08, 152.77, 155.68, 150.68, 160.84, 154.78, 154.96, 147.56, 143.06, 137.55, 146.28, 146.49, 148.46, 147.93, 150.07, 140.76, 130.49, 128.06, 132.37, 135.7, 142.15, 142.76, 146.39, 145.89, 145.97, 152.62, 141.57, 143.09, 143.1, 141.18, 137.97, 139.11, 144.07, 146.03, 135.91, 133.79, 137.05, 137.8, 136.89, 136.0, 130.05, 133.73, 133.99, 135.14, 135.26, 137.15, 137.41, 136.88, 136.6, 132.51, 143.34, 156.54, 160.65, 152.17, 142.2, 141.7, 135.53, 136.47, 132.07, 130.21, 131.08, 127.99, 134.71, 133.25, 130.63, 128.47, 119.5, 116.7, 113.5, 107.27, 112.93, 115.7, 116.67, 125.73, 129.3, 132.54, 134.37, 132.22, 129.04, 126.79, 130.04, 133.72, 133.76, 134.44, 132.38, 134.85, 132.66, 124.57, 123.37, 122.92, 131.53, 123.53], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT']}</t>
+          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [152.67, 157.16, 156.43, 151.14, 151.6, 153.5, 150.95, 152.72, 155.08, 152.77, 155.68, 150.68, 160.84, 154.78, 154.96, 147.56, 143.06, 137.55, 146.28, 146.49, 148.46, 147.93, 150.07, 140.76, 130.49, 128.06, 132.37, 135.7, 142.15, 142.76, 146.39, 145.89, 145.97, 152.62, 141.57, 143.09, 143.1, 141.18, 137.97, 139.11, 144.07, 146.03, 135.91, 133.79, 137.05, 137.8, 136.89, 136.0, 130.05, 133.73, 133.99, 135.14, 135.26, 137.15, 137.41, 136.88, 136.6, 132.51, 143.34, 156.54, 160.65, 152.17, 142.2, 141.7, 135.53, 136.47, 132.07, 130.21, 131.08, 127.99, 134.71, 133.25, 130.63, 128.47, 119.5, 116.7, 113.5, 107.27, 112.93, 115.7, 116.67, 125.73, 129.3, 132.54, 134.37, 132.22, 129.04, 126.79, 130.04, 133.72, 133.76, 134.44, 132.38, 134.85, 132.66, 124.57, 123.37, 122.92, 131.53, 123.53], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT']}</t>
         </is>
       </c>
       <c r="S6" t="n">
@@ -876,6 +901,11 @@
       </c>
       <c r="U6" t="n">
         <v>22.19321356384988</v>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -885,7 +915,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -893,7 +923,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.285</v>
+        <v>0.207</v>
       </c>
       <c r="E7" t="n">
         <v>52</v>
@@ -947,6 +977,11 @@
       </c>
       <c r="U7" t="n">
         <v>17.05993620111895</v>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -956,7 +991,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -964,7 +999,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.372</v>
+        <v>0.328</v>
       </c>
       <c r="E8" t="n">
         <v>58</v>
@@ -973,19 +1008,19 @@
         <v>80</v>
       </c>
       <c r="G8" t="n">
-        <v>30</v>
+        <v>22.2</v>
       </c>
       <c r="H8" t="n">
-        <v>-293</v>
+        <v>-391</v>
       </c>
       <c r="I8" t="n">
-        <v>-5.9</v>
+        <v>-7.8</v>
       </c>
       <c r="J8" t="n">
         <v>-27</v>
       </c>
       <c r="K8" t="n">
-        <v>21.1</v>
+        <v>19.2</v>
       </c>
       <c r="L8" t="n">
         <v>5000</v>
@@ -997,17 +1032,17 @@
         <v>4</v>
       </c>
       <c r="O8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P8" t="n">
         <v>4</v>
       </c>
       <c r="Q8" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [99.17, 99.02, 98.32, 96.94, 94.89, 94.31, 95.31, 95.2, 94.36, 94.7, 91.74, 91.82, 93.38, 90.92, 92.28, 93.32, 93.43, 92.97, 96.15, 95.55, 98.66, 98.93, 98.82, 99.39, 102.05, 103.01, 103.16, 106.28, 107.71, 107.79, 97.31, 94.83, 92.58, 93.24, 92.82, 92.44, 91.37, 92.27, 92.12, 93.61, 92.06, 91.02, 87.89, 88.27, 88.25, 87.49, 85.45, 87.66, 87.56, 86.94, 87.02, 89.65, 89.33, 88.09, 89.3, 88.6, 87.68, 87.35, 86.36, 86.02, 85.85, 83.33, 81.52, 81.56, 82.18, 82.64, 81.41, 82.0, 81.27, 80.34, 81.67, 78.72, 76.96, 77.38, 72.88, 72.82, 71.84, 70.9, 73.81, 73.78, 71.4, 74.19, 77.65, 76.02, 76.18, 75.59, 75.47, 73.37, 73.83, 73.53, 73.68, 74.35, 68.95, 67.6, 68.67, 68.53, 68.89, 70.09, 70.4, 72.39], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [99.17, 99.02, 98.32, 96.94, 94.89, 94.31, 95.31, 95.2, 94.36, 94.7, 91.74, 91.82, 93.38, 90.92, 92.28, 93.32, 93.43, 92.97, 96.15, 95.55, 98.66, 98.93, 98.82, 99.39, 102.05, 103.01, 103.16, 106.28, 107.71, 107.79, 97.31, 94.83, 92.58, 93.24, 92.82, 92.44, 91.37, 92.27, 92.12, 93.61, 92.06, 91.02, 87.89, 88.27, 88.25, 87.49, 85.45, 87.66, 87.56, 86.94, 87.02, 89.65, 89.33, 88.09, 89.3, 88.6, 87.68, 87.35, 86.36, 86.02, 85.85, 83.33, 81.52, 81.56, 82.18, 82.64, 81.41, 82.0, 81.27, 80.34, 81.67, 78.72, 76.96, 77.38, 72.88, 72.82, 71.84, 70.9, 73.81, 73.78, 71.4, 74.19, 77.65, 76.02, 76.18, 75.59, 75.47, 73.37, 73.83, 73.53, 73.68, 74.35, 68.95, 67.6, 68.67, 68.53, 68.89, 70.09, 70.4, 72.39], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
       <c r="S8" t="n">
@@ -1018,6 +1053,11 @@
       </c>
       <c r="U8" t="n">
         <v>34.27873709740564</v>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -1027,36 +1067,36 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">UP  </t>
+          <t>DOWN</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.703</v>
+        <v>0.252</v>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="F9" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="G9" t="n">
         <v>50</v>
       </c>
       <c r="H9" t="n">
-        <v>742</v>
+        <v>976</v>
       </c>
       <c r="I9" t="n">
-        <v>14.8</v>
+        <v>19.5</v>
       </c>
       <c r="J9" t="n">
         <v>30.8</v>
       </c>
       <c r="K9" t="n">
-        <v>-16</v>
+        <v>-11.3</v>
       </c>
       <c r="L9" t="n">
         <v>5000</v>
@@ -1065,20 +1105,20 @@
         <v>14</v>
       </c>
       <c r="N9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O9" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="P9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [260.05, 257.22, 259.64, 260.59, 260.57, 255.52, 249.89, 252.59, 254.0, 249.71, 248.73, 247.76, 251.26, 251.41, 252.39, 252.66, 248.57, 246.4, 253.56, 255.39, 255.68, 258.62, 253.27, 258.66, 260.25, 260.24, 258.96, 258.59, 266.18, 263.16, 269.98, 272.8, 265.93, 272.92, 273.18, 270.81, 267.36, 270.46, 269.92, 271.1, 279.88, 276.58, 283.92, 287.25, 287.18, 293.05, 292.68, 294.8, 298.87, 298.21, 300.23, 297.84, 298.97, 302.25, 304.99, 308.82, 308.33, 310.85, 312.51, 312.06, 306.31, 315.2, 310.26, 311.23, 307.34, 301.54, 290.55, 291.58, 295.63, 291.13, 296.42, 299.24, 295.95, 298.01, 297.01, 294.3, 293.08, 275.15, 283.78, 281.74, 289.36, 294.38, 308.63, 312.66, 310.66, 313.39, 316.22, 315.32, 317.31, 314.86, 327.5, 333.26, 333.74, 326.59, 327.74, 325.89, 321.66, 333.02, 336.91, 340.08], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [260.05, 257.22, 259.64, 260.59, 260.57, 255.52, 249.89, 252.59, 254.0, 249.71, 248.73, 247.76, 251.26, 251.41, 252.39, 252.66, 248.57, 246.4, 253.56, 255.39, 255.68, 258.62, 253.27, 258.66, 260.25, 260.24, 258.96, 258.59, 266.18, 263.16, 269.98, 272.8, 265.93, 272.92, 273.18, 270.81, 267.36, 270.46, 269.92, 271.1, 279.88, 276.58, 283.92, 287.25, 287.18, 293.05, 292.68, 294.8, 298.87, 298.21, 300.23, 297.84, 298.97, 302.25, 304.99, 308.82, 308.33, 310.85, 312.51, 312.06, 306.31, 315.2, 310.26, 311.23, 307.34, 301.54, 290.55, 291.58, 295.63, 291.13, 296.42, 299.24, 295.95, 298.01, 297.01, 294.3, 293.08, 275.15, 283.78, 281.74, 289.36, 294.38, 308.63, 312.66, 310.66, 313.39, 316.22, 315.32, 317.31, 314.86, 327.5, 333.26, 333.74, 326.59, 327.74, 325.89, 321.66, 333.02, 336.91, 340.08], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
       <c r="S9" t="n">
@@ -1089,6 +1129,11 @@
       </c>
       <c r="U9" t="n">
         <v>43.6905405239262</v>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -1098,7 +1143,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1106,7 +1151,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.644</v>
+        <v>0.67</v>
       </c>
       <c r="E10" t="n">
         <v>53</v>
@@ -1159,7 +1204,12 @@
         <v>13.64000047956194</v>
       </c>
       <c r="U10" t="n">
-        <v>40.63643316345468</v>
+        <v>40.63643316345857</v>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -1169,7 +1219,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1177,10 +1227,10 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.328</v>
+        <v>0.289</v>
       </c>
       <c r="E11" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="F11" t="n">
         <v>70</v>
@@ -1189,16 +1239,16 @@
         <v>65</v>
       </c>
       <c r="H11" t="n">
-        <v>1889</v>
+        <v>2039</v>
       </c>
       <c r="I11" t="n">
-        <v>37.8</v>
+        <v>40.8</v>
       </c>
       <c r="J11" t="n">
         <v>77.40000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>-39.6</v>
+        <v>-36.6</v>
       </c>
       <c r="L11" t="n">
         <v>5000</v>
@@ -1210,17 +1260,17 @@
         <v>4</v>
       </c>
       <c r="O11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P11" t="n">
         <v>4</v>
       </c>
       <c r="Q11" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [95.65, 89.33, 94.94, 96.43, 112.0, 108.04, 112.95, 129.85, 116.33, 118.56, 121.52, 117.62, 114.15, 114.91, 115.09, 105.97, 100.82, 92.26, 103.76, 101.95, 108.82, 112.54, 117.4, 125.0, 136.33, 144.97, 154.56, 161.94, 166.77, 165.34, 157.14, 159.16, 156.55, 156.14, 157.08, 147.16, 144.96, 135.51, 141.19, 138.23, 154.49, 176.42, 175.92, 195.09, 184.77, 177.05, 186.1, 179.11, 207.27, 221.15, 219.94, 199.86, 197.73, 191.82, 219.93, 214.77, 208.06, 208.37, 226.34, 231.09, 264.51, 260.58, 251.68, 259.67, 227.81, 218.0, 220.12, 211.69, 222.24, 232.36, 260.07, 265.1, 280.91, 286.69, 283.61, 275.25, 259.66, 256.63, 240.3, 261.15, 276.17, 229.18, 215.62, 213.02, 195.19, 216.48, 216.2, 219.65, 210.51, 194.09, 199.51, 171.77, 177.71, 182.62, 216.92, 218.16, 220.97, 187.77, 187.88, 169.69], 'signals': ['FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [95.65, 89.33, 94.94, 96.43, 112.0, 108.04, 112.95, 129.85, 116.33, 118.56, 121.52, 117.62, 114.15, 114.91, 115.09, 105.97, 100.82, 92.26, 103.76, 101.95, 108.82, 112.54, 117.4, 125.0, 136.33, 144.97, 154.56, 161.94, 166.77, 165.34, 157.14, 159.16, 156.55, 156.14, 157.08, 147.16, 144.96, 135.51, 141.19, 138.23, 154.49, 176.42, 175.92, 195.09, 184.77, 177.05, 186.1, 179.11, 207.27, 221.15, 219.94, 199.86, 197.73, 191.82, 219.93, 214.77, 208.06, 208.37, 226.34, 231.09, 264.51, 260.58, 251.68, 259.67, 227.81, 218.0, 220.12, 211.69, 222.24, 232.36, 260.07, 265.1, 280.91, 286.69, 283.61, 275.25, 259.66, 256.63, 240.3, 261.15, 276.17, 229.18, 215.62, 213.02, 195.19, 216.48, 216.2, 219.65, 210.51, 194.09, 199.51, 171.77, 177.71, 182.62, 216.92, 218.16, 220.97, 187.77, 187.88, 169.69], 'signals': ['FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
       <c r="S11" t="n">
@@ -1231,6 +1281,11 @@
       </c>
       <c r="U11" t="n">
         <v>19.93684147717601</v>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -1240,7 +1295,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1248,10 +1303,10 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.872</v>
       </c>
       <c r="E12" t="n">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="F12" t="n">
         <v>60</v>
@@ -1260,16 +1315,16 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="I12" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="J12" t="n">
         <v>18.3</v>
       </c>
       <c r="K12" t="n">
-        <v>-10.3</v>
+        <v>-10.2</v>
       </c>
       <c r="L12" t="n">
         <v>5000</v>
@@ -1278,20 +1333,20 @@
         <v>35</v>
       </c>
       <c r="N12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [119.13, 117.73, 118.78, 118.56, 118.18, 116.66, 115.67, 116.84, 116.84, 115.56, 115.38, 113.29, 114.35, 114.66, 115.14, 111.17, 110.14, 107.67, 111.94, 114.32, 114.56, 115.49, 116.47, 121.17, 122.57, 123.15, 124.4, 126.46, 126.39, 126.55, 128.1, 127.44, 126.46, 128.91, 129.03, 131.32, 131.91, 129.76, 130.57, 133.59, 134.21, 134.23, 137.67, 141.37, 139.09, 143.59, 145.85, 144.23, 146.07, 147.29, 143.26, 141.2, 140.41, 143.09, 144.47, 144.72, 149.57, 149.37, 149.9, 150.36, 152.09, 154.08, 154.85, 152.6, 144.06, 147.65, 147.28, 143.46, 150.35, 152.25, 157.6, 154.38, 155.25, 159.65, 161.66, 154.34, 153.79, 159.64, 154.2, 158.53, 161.54, 155.32, 150.83, 152.98, 149.42, 150.57, 153.08, 153.75, 149.73, 152.86, 150.0, 145.28, 143.89, 144.52, 149.7, 150.07, 149.83, 146.51, 144.75, 140.95], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [119.13, 117.73, 118.78, 118.56, 118.18, 116.66, 115.67, 116.84, 116.84, 115.56, 115.38, 113.29, 114.35, 114.66, 115.14, 111.17, 110.14, 107.67, 111.94, 114.32, 114.56, 115.49, 116.47, 121.17, 122.57, 123.15, 124.4, 126.46, 126.39, 126.55, 128.1, 127.44, 126.46, 128.91, 129.03, 131.32, 131.91, 129.76, 130.57, 133.59, 134.21, 134.23, 137.67, 141.37, 139.09, 143.59, 145.85, 144.23, 146.07, 147.29, 143.26, 141.2, 140.41, 143.09, 144.47, 144.72, 149.57, 149.37, 149.9, 150.36, 152.09, 154.08, 154.85, 152.6, 144.06, 147.65, 147.28, 143.46, 150.35, 152.25, 157.6, 154.38, 155.25, 159.65, 161.66, 154.34, 153.79, 159.64, 154.2, 158.53, 161.54, 155.32, 150.83, 152.98, 149.42, 150.57, 153.08, 153.75, 149.73, 152.86, 150.0, 145.28, 143.89, 144.52, 149.7, 150.07, 149.83, 146.51, 144.75, 140.95], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
       <c r="S12" t="n">
@@ -1301,7 +1356,12 @@
         <v>4.625142778669085</v>
       </c>
       <c r="U12" t="n">
-        <v>32.31190962718114</v>
+        <v>32.31190962718118</v>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/demo_results.xlsx
+++ b/demo_results.xlsx
@@ -535,18 +535,18 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DOWN</t>
+          <t xml:space="preserve">UP  </t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.473</v>
+        <v>0.522</v>
       </c>
       <c r="E2" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F2" t="n">
         <v>60</v>
@@ -586,7 +586,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [199.45, 192.43, 202.68, 203.23, 204.83, 197.74, 193.39, 196.58, 196.31, 199.46, 205.27, 201.33, 202.68, 205.37, 220.27, 203.77, 201.99, 196.04, 203.43, 210.21, 217.5, 220.18, 221.53, 231.82, 236.64, 245.04, 246.83, 255.07, 258.12, 278.26, 278.39, 274.95, 284.49, 303.46, 305.33, 347.81, 334.63, 323.21, 337.11, 354.49, 360.54, 341.54, 355.26, 421.39, 408.46, 455.19, 458.79, 448.29, 445.5, 449.7, 424.1, 420.99, 414.05, 447.58, 449.59, 467.51, 503.89, 495.54, 518.09, 516.1, 510.13, 521.54, 542.52, 523.2, 466.38, 490.33, 475.51, 452.4, 488.45, 511.57, 547.26, 507.29, 512.48, 537.37, 551.63, 519.85, 519.74, 532.57, 521.58, 539.49, 580.91, 540.88, 517.82, 552.05, 516.11, 517.41, 546.72, 557.89, 534.39, 548.13, 529.14, 500.94, 495.76, 503.57, 544.43, 552.33, 539.69, 521.95, 494.95, 454.62], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [199.45, 192.43, 202.68, 203.23, 204.83, 197.74, 193.39, 196.58, 196.31, 199.46, 205.27, 201.33, 202.68, 205.37, 220.27, 203.77, 201.99, 196.04, 203.43, 210.21, 217.5, 220.18, 221.53, 231.82, 236.64, 245.04, 246.83, 255.07, 258.12, 278.26, 278.39, 274.95, 284.49, 303.46, 305.33, 347.81, 334.63, 323.21, 337.11, 354.49, 360.54, 341.54, 355.26, 421.39, 408.46, 455.19, 458.79, 448.29, 445.5, 449.7, 424.1, 420.99, 414.05, 447.58, 449.59, 467.51, 503.89, 495.54, 518.09, 516.1, 510.13, 521.54, 542.52, 523.2, 466.38, 490.33, 475.51, 452.4, 488.45, 511.57, 547.26, 507.29, 512.48, 537.37, 551.63, 519.85, 519.74, 532.57, 521.58, 539.49, 580.91, 540.88, 517.82, 552.05, 516.11, 517.41, 546.72, 557.89, 534.39, 548.13, 529.14, 500.94, 495.76, 503.57, 544.43, 552.33, 539.69, 521.95, 494.95, 454.62], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
       <c r="S2" t="n">
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -619,13 +619,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.455</v>
+        <v>0.448</v>
       </c>
       <c r="E3" t="n">
         <v>55</v>
       </c>
       <c r="F3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="G3" t="n">
         <v>68.40000000000001</v>
@@ -662,7 +662,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [396.82, 370.09, 389.1, 402.88, 418.45, 405.12, 425.89, 441.55, 461.43, 461.47, 444.02, 422.66, 404.12, 395.3, 381.87, 355.26, 357.02, 321.75, 337.79, 367.79, 366.18, 377.7, 377.52, 406.67, 421.45, 420.53, 426.49, 465.59, 456.16, 457.16, 455.0, 448.35, 449.31, 487.41, 481.65, 496.64, 524.48, 504.21, 518.38, 517.08, 542.13, 576.36, 640.1, 666.49, 646.53, 746.7, 795.21, 766.46, 803.51, 775.89, 724.55, 681.44, 698.63, 731.88, 761.98, 750.88, 895.74, 928.27, 923.38, 970.85, 1035.34, 1063.94, 1079.4, 995.85, 863.88, 949.13, 935.75, 891.74, 995.72, 981.46, 1087.82, 1020.6, 1043.03, 1133.82, 1211.19, 1051.61, 1048.35, 1213.37, 1132.16, 1145.1, 1154.11, 1032.12, 975.41, 984.75, 938.38, 948.8, 991.64, 979.3, 937.0, 983.12, 904.28, 853.2, 848.95, 865.46, 970.82, 959.48, 990.21, 920.95, 900.2, 820.53], 'signals': ['FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [396.82, 370.09, 389.1, 402.88, 418.45, 405.12, 425.89, 441.55, 461.43, 461.47, 444.02, 422.66, 404.12, 395.3, 381.87, 355.26, 357.02, 321.75, 337.79, 367.79, 366.18, 377.7, 377.52, 406.67, 421.45, 420.53, 426.49, 465.59, 456.16, 457.16, 455.0, 448.35, 449.31, 487.41, 481.65, 496.64, 524.48, 504.21, 518.38, 517.08, 542.13, 576.36, 640.1, 666.49, 646.53, 746.7, 795.21, 766.46, 803.51, 775.89, 724.55, 681.44, 698.63, 731.88, 761.98, 750.88, 895.74, 928.27, 923.38, 970.85, 1035.34, 1063.94, 1079.4, 995.85, 863.88, 949.13, 935.75, 891.74, 995.72, 981.46, 1087.82, 1020.6, 1043.03, 1133.82, 1211.19, 1051.61, 1048.35, 1213.37, 1132.16, 1145.1, 1154.11, 1032.12, 975.41, 984.75, 938.38, 948.8, 991.64, 979.3, 937.0, 983.12, 904.28, 853.2, 848.95, 865.46, 970.82, 959.48, 990.21, 920.95, 900.2, 820.53], 'signals': ['FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
       <c r="S3" t="n">
@@ -672,7 +672,7 @@
         <v>77.43857683454242</v>
       </c>
       <c r="U3" t="n">
-        <v>26.25061192614724</v>
+        <v>26.25061192572846</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -695,28 +695,28 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.766</v>
+        <v>0.611</v>
       </c>
       <c r="E4" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="F4" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="G4" t="n">
         <v>57.1</v>
       </c>
       <c r="H4" t="n">
-        <v>2124</v>
+        <v>657</v>
       </c>
       <c r="I4" t="n">
-        <v>42.5</v>
+        <v>13.1</v>
       </c>
       <c r="J4" t="n">
         <v>70.59999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>-28.1</v>
+        <v>-57.5</v>
       </c>
       <c r="L4" t="n">
         <v>5000</v>
@@ -725,20 +725,20 @@
         <v>27</v>
       </c>
       <c r="N4" t="n">
+        <v>5</v>
+      </c>
+      <c r="O4" t="n">
         <v>2</v>
       </c>
-      <c r="O4" t="n">
-        <v>16</v>
-      </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q4" t="n">
-        <v>8.5</v>
+        <v>1.4</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [106.54, 107.25, 108.53, 109.08, 110.51, 110.39, 110.44, 105.96, 108.3, 108.95, 107.04, 102.25, 103.33, 98.25, 96.46, 98.15, 92.39, 95.01, 97.6, 98.33, 99.78, 99.65, 105.81, 106.63, 98.67, 94.75, 100.56, 99.62, 102.79, 104.55, 105.99, 108.29, 112.4, 116.67, 111.35, 112.03, 113.65, 113.75, 113.1, 111.44, 113.91, 117.31, 119.13, 117.02, 126.43, 131.94, 135.57, 136.54, 140.64, 144.99, 148.52, 154.71, 154.22, 162.53, 162.06, 165.87, 167.89, 161.34, 167.75, 182.75, 195.54, 192.24, 186.9, 179.77, 167.76, 164.7, 161.23, 161.93, 172.88, 170.7, 173.23, 169.87, 170.74, 171.21, 168.86, 170.23, 168.26, 169.66, 175.27, 185.73, 190.79, 193.18, 193.98, 199.38, 194.62, 191.12, 198.4, 187.18, 187.91, 210.73, 206.77, 203.76, 203.08, 198.49, 191.15, 188.42, 183.42, 183.28, 180.11, 181.8], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT']}</t>
+          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [106.54, 107.25, 108.53, 109.08, 110.51, 110.39, 110.44, 105.96, 108.3, 108.95, 107.04, 102.25, 103.33, 98.25, 96.46, 98.15, 92.39, 95.01, 97.6, 98.33, 99.78, 99.65, 105.81, 106.63, 98.67, 94.75, 100.56, 99.62, 102.79, 104.55, 105.99, 108.29, 112.4, 116.67, 111.35, 112.03, 113.65, 113.75, 113.1, 111.44, 113.91, 117.31, 119.13, 117.02, 126.43, 131.94, 135.57, 136.54, 140.64, 144.99, 148.52, 154.71, 154.22, 162.53, 162.06, 165.87, 167.89, 161.34, 167.75, 182.75, 195.54, 192.24, 186.9, 179.77, 167.76, 164.7, 161.23, 161.93, 172.88, 170.7, 173.23, 169.87, 170.74, 171.21, 168.86, 170.23, 168.26, 169.66, 175.27, 185.73, 190.79, 193.18, 193.98, 199.38, 194.62, 191.12, 198.4, 187.18, 187.91, 210.73, 206.77, 203.76, 203.08, 198.49, 191.15, 188.42, 183.42, 183.28, 180.11, 181.8], 'signals': ['BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
       <c r="S4" t="n">
@@ -752,7 +752,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>FLAT</t>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -771,28 +771,28 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.668</v>
+        <v>0.526</v>
       </c>
       <c r="E5" t="n">
         <v>63</v>
       </c>
       <c r="F5" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="G5" t="n">
         <v>50</v>
       </c>
       <c r="H5" t="n">
-        <v>938</v>
+        <v>1014</v>
       </c>
       <c r="I5" t="n">
-        <v>18.8</v>
+        <v>20.3</v>
       </c>
       <c r="J5" t="n">
         <v>7.6</v>
       </c>
       <c r="K5" t="n">
-        <v>11.2</v>
+        <v>12.7</v>
       </c>
       <c r="L5" t="n">
         <v>5000</v>
@@ -801,20 +801,20 @@
         <v>25</v>
       </c>
       <c r="N5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [183.12, 177.6, 182.43, 184.54, 185.81, 182.93, 180.04, 183.01, 181.72, 180.19, 178.35, 172.5, 175.44, 175.0, 178.47, 171.04, 167.32, 164.98, 174.2, 175.55, 177.18, 177.43, 177.89, 181.87, 183.7, 188.41, 189.09, 196.28, 198.64, 198.12, 201.45, 201.82, 199.65, 202.26, 199.41, 208.03, 216.36, 212.92, 209.01, 199.34, 198.22, 198.25, 196.27, 207.59, 211.25, 214.95, 219.18, 220.52, 225.57, 235.47, 225.06, 222.06, 220.35, 223.21, 219.25, 215.08, 214.61, 212.35, 214.0, 210.89, 224.1, 222.56, 214.5, 218.66, 205.1, 208.64, 208.19, 200.42, 204.87, 205.19, 212.45, 207.41, 204.65, 210.69, 208.65, 200.04, 199.0, 195.74, 192.53, 194.97, 200.09, 197.58, 194.83, 195.55, 196.93, 204.12, 202.78, 210.96, 203.53, 211.8, 212.5, 207.4, 202.81, 203.28, 207.29, 212.06, 208.76, 206.84, 196.51, 197.01], 'signals': ['BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [183.12, 177.6, 182.43, 184.54, 185.81, 182.93, 180.04, 183.01, 181.72, 180.19, 178.35, 172.5, 175.44, 175.0, 178.47, 171.04, 167.32, 164.98, 174.2, 175.55, 177.18, 177.43, 177.89, 181.87, 183.7, 188.41, 189.09, 196.28, 198.64, 198.12, 201.45, 201.82, 199.65, 202.26, 199.41, 208.03, 216.36, 212.92, 209.01, 199.34, 198.22, 198.25, 196.27, 207.59, 211.25, 214.95, 219.18, 220.52, 225.57, 235.47, 225.06, 222.06, 220.35, 223.21, 219.25, 215.08, 214.61, 212.35, 214.0, 210.89, 224.1, 222.56, 214.5, 218.66, 205.1, 208.64, 208.19, 200.42, 204.87, 205.19, 212.45, 207.41, 204.65, 210.69, 208.65, 200.04, 199.0, 195.74, 192.53, 194.97, 200.09, 197.58, 194.83, 195.55, 196.93, 204.12, 202.78, 210.96, 203.53, 211.8, 212.5, 207.4, 202.81, 203.28, 207.29, 212.06, 208.76, 206.84, 196.51, 197.01], 'signals': ['BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'BUY', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
       <c r="S5" t="n">
@@ -839,7 +839,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -847,10 +847,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.37</v>
+        <v>0.344</v>
       </c>
       <c r="E6" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F6" t="n">
         <v>20</v>
@@ -890,7 +890,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [152.67, 157.16, 156.43, 151.14, 151.6, 153.5, 150.95, 152.72, 155.08, 152.77, 155.68, 150.68, 160.84, 154.78, 154.96, 147.56, 143.06, 137.55, 146.28, 146.49, 148.46, 147.93, 150.07, 140.76, 130.49, 128.06, 132.37, 135.7, 142.15, 142.76, 146.39, 145.89, 145.97, 152.62, 141.57, 143.09, 143.1, 141.18, 137.97, 139.11, 144.07, 146.03, 135.91, 133.79, 137.05, 137.8, 136.89, 136.0, 130.05, 133.73, 133.99, 135.14, 135.26, 137.15, 137.41, 136.88, 136.6, 132.51, 143.34, 156.54, 160.65, 152.17, 142.2, 141.7, 135.53, 136.47, 132.07, 130.21, 131.08, 127.99, 134.71, 133.25, 130.63, 128.47, 119.5, 116.7, 113.5, 107.27, 112.93, 115.7, 116.67, 125.73, 129.3, 132.54, 134.37, 132.22, 129.04, 126.79, 130.04, 133.72, 133.76, 134.44, 132.38, 134.85, 132.66, 124.57, 123.37, 122.92, 131.53, 123.53], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT']}</t>
+          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [152.67, 157.16, 156.43, 151.14, 151.6, 153.5, 150.95, 152.72, 155.08, 152.77, 155.68, 150.68, 160.84, 154.78, 154.96, 147.56, 143.06, 137.55, 146.28, 146.49, 148.46, 147.93, 150.07, 140.76, 130.49, 128.06, 132.37, 135.7, 142.15, 142.76, 146.39, 145.89, 145.97, 152.62, 141.57, 143.09, 143.1, 141.18, 137.97, 139.11, 144.07, 146.03, 135.91, 133.79, 137.05, 137.8, 136.89, 136.0, 130.05, 133.73, 133.99, 135.14, 135.26, 137.15, 137.41, 136.88, 136.6, 132.51, 143.34, 156.54, 160.65, 152.17, 142.2, 141.7, 135.53, 136.47, 132.07, 130.21, 131.08, 127.99, 134.71, 133.25, 130.63, 128.47, 119.5, 116.7, 113.5, 107.27, 112.93, 115.7, 116.67, 125.73, 129.3, 132.54, 134.37, 132.22, 129.04, 126.79, 130.04, 133.72, 133.76, 134.44, 132.38, 134.85, 132.66, 124.57, 123.37, 122.92, 131.53, 123.53], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT']}</t>
         </is>
       </c>
       <c r="S6" t="n">
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.207</v>
+        <v>0.105</v>
       </c>
       <c r="E7" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="F7" t="n">
         <v>40</v>
@@ -935,16 +935,16 @@
         <v>46.7</v>
       </c>
       <c r="H7" t="n">
-        <v>-422</v>
+        <v>-977</v>
       </c>
       <c r="I7" t="n">
-        <v>-8.4</v>
+        <v>-19.5</v>
       </c>
       <c r="J7" t="n">
         <v>-18.4</v>
       </c>
       <c r="K7" t="n">
-        <v>10</v>
+        <v>-1.1</v>
       </c>
       <c r="L7" t="n">
         <v>5000</v>
@@ -953,20 +953,20 @@
         <v>29</v>
       </c>
       <c r="N7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O7" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="P7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q7" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [205.71, 197.22, 199.79, 196.52, 198.63, 193.23, 195.53, 203.32, 210.23, 202.29, 202.91, 197.5, 200.62, 181.04, 181.1, 173.38, 161.14, 160.79, 174.61, 172.99, 171.46, 174.79, 175.18, 175.09, 169.02, 167.85, 174.53, 184.41, 195.9, 199.83, 206.33, 211.63, 195.95, 206.24, 197.93, 199.77, 196.68, 194.1, 181.73, 187.77, 191.25, 202.99, 197.75, 197.96, 192.96, 201.16, 216.6, 207.64, 201.8, 212.01, 195.43, 189.44, 193.45, 191.29, 193.56, 184.99, 180.01, 173.78, 182.25, 189.03, 182.61, 173.99, 163.22, 164.13, 152.4, 162.11, 155.5, 153.97, 160.43, 159.78, 169.62, 169.27, 164.92, 163.26, 164.84, 158.18, 150.11, 142.52, 149.06, 151.65, 146.19, 159.24, 165.48, 168.87, 163.51, 159.36, 158.44, 159.07, 157.37, 161.5, 167.21, 160.49, 157.12, 160.43, 175.85, 166.12, 161.16, 158.29, 167.49, 167.9], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [205.71, 197.22, 199.79, 196.52, 198.63, 193.23, 195.53, 203.32, 210.23, 202.29, 202.91, 197.5, 200.62, 181.04, 181.1, 173.38, 161.14, 160.79, 174.61, 172.99, 171.46, 174.79, 175.18, 175.09, 169.02, 167.85, 174.53, 184.41, 195.9, 199.83, 206.33, 211.63, 195.95, 206.24, 197.93, 199.77, 196.68, 194.1, 181.73, 187.77, 191.25, 202.99, 197.75, 197.96, 192.96, 201.16, 216.6, 207.64, 201.8, 212.01, 195.43, 189.44, 193.45, 191.29, 193.56, 184.99, 180.01, 173.78, 182.25, 189.03, 182.61, 173.99, 163.22, 164.13, 152.4, 162.11, 155.5, 153.97, 160.43, 159.78, 169.62, 169.27, 164.92, 163.26, 164.84, 158.18, 150.11, 142.52, 149.06, 151.65, 146.19, 159.24, 165.48, 168.87, 163.51, 159.36, 158.44, 159.07, 157.37, 161.5, 167.21, 160.49, 157.12, 160.43, 175.85, 166.12, 161.16, 158.29, 167.49, 167.9], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
       <c r="S7" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>FLAT</t>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -999,28 +999,28 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.328</v>
+        <v>0.272</v>
       </c>
       <c r="E8" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F8" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G8" t="n">
-        <v>22.2</v>
+        <v>30</v>
       </c>
       <c r="H8" t="n">
-        <v>-391</v>
+        <v>-68</v>
       </c>
       <c r="I8" t="n">
-        <v>-7.8</v>
+        <v>-1.4</v>
       </c>
       <c r="J8" t="n">
         <v>-27</v>
       </c>
       <c r="K8" t="n">
-        <v>19.2</v>
+        <v>25.6</v>
       </c>
       <c r="L8" t="n">
         <v>5000</v>
@@ -1038,11 +1038,11 @@
         <v>4</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [99.17, 99.02, 98.32, 96.94, 94.89, 94.31, 95.31, 95.2, 94.36, 94.7, 91.74, 91.82, 93.38, 90.92, 92.28, 93.32, 93.43, 92.97, 96.15, 95.55, 98.66, 98.93, 98.82, 99.39, 102.05, 103.01, 103.16, 106.28, 107.71, 107.79, 97.31, 94.83, 92.58, 93.24, 92.82, 92.44, 91.37, 92.27, 92.12, 93.61, 92.06, 91.02, 87.89, 88.27, 88.25, 87.49, 85.45, 87.66, 87.56, 86.94, 87.02, 89.65, 89.33, 88.09, 89.3, 88.6, 87.68, 87.35, 86.36, 86.02, 85.85, 83.33, 81.52, 81.56, 82.18, 82.64, 81.41, 82.0, 81.27, 80.34, 81.67, 78.72, 76.96, 77.38, 72.88, 72.82, 71.84, 70.9, 73.81, 73.78, 71.4, 74.19, 77.65, 76.02, 76.18, 75.59, 75.47, 73.37, 73.83, 73.53, 73.68, 74.35, 68.95, 67.6, 68.67, 68.53, 68.89, 70.09, 70.4, 72.39], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [99.17, 99.02, 98.32, 96.94, 94.89, 94.31, 95.31, 95.2, 94.36, 94.7, 91.74, 91.82, 93.38, 90.92, 92.28, 93.32, 93.43, 92.97, 96.15, 95.55, 98.66, 98.93, 98.82, 99.39, 102.05, 103.01, 103.16, 106.28, 107.71, 107.79, 97.31, 94.83, 92.58, 93.24, 92.82, 92.44, 91.37, 92.27, 92.12, 93.61, 92.06, 91.02, 87.89, 88.27, 88.25, 87.49, 85.45, 87.66, 87.56, 86.94, 87.02, 89.65, 89.33, 88.09, 89.3, 88.6, 87.68, 87.35, 86.36, 86.02, 85.85, 83.33, 81.52, 81.56, 82.18, 82.64, 81.41, 82.0, 81.27, 80.34, 81.67, 78.72, 76.96, 77.38, 72.88, 72.82, 71.84, 70.9, 73.81, 73.78, 71.4, 74.19, 77.65, 76.02, 76.18, 75.59, 75.47, 73.37, 73.83, 73.53, 73.68, 74.35, 68.95, 67.6, 68.67, 68.53, 68.89, 70.09, 70.4, 72.39], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
       <c r="S8" t="n">
@@ -1067,36 +1067,36 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>55</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UP  </t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.795</v>
+      </c>
+      <c r="E9" t="n">
         <v>54</v>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>DOWN</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>0.252</v>
-      </c>
-      <c r="E9" t="n">
-        <v>60</v>
-      </c>
       <c r="F9" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="G9" t="n">
         <v>50</v>
       </c>
       <c r="H9" t="n">
-        <v>976</v>
+        <v>736</v>
       </c>
       <c r="I9" t="n">
-        <v>19.5</v>
+        <v>14.7</v>
       </c>
       <c r="J9" t="n">
         <v>30.8</v>
       </c>
       <c r="K9" t="n">
-        <v>-11.3</v>
+        <v>-16.1</v>
       </c>
       <c r="L9" t="n">
         <v>5000</v>
@@ -1105,20 +1105,20 @@
         <v>14</v>
       </c>
       <c r="N9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O9" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="P9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.3</v>
+        <v>3.5</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [260.05, 257.22, 259.64, 260.59, 260.57, 255.52, 249.89, 252.59, 254.0, 249.71, 248.73, 247.76, 251.26, 251.41, 252.39, 252.66, 248.57, 246.4, 253.56, 255.39, 255.68, 258.62, 253.27, 258.66, 260.25, 260.24, 258.96, 258.59, 266.18, 263.16, 269.98, 272.8, 265.93, 272.92, 273.18, 270.81, 267.36, 270.46, 269.92, 271.1, 279.88, 276.58, 283.92, 287.25, 287.18, 293.05, 292.68, 294.8, 298.87, 298.21, 300.23, 297.84, 298.97, 302.25, 304.99, 308.82, 308.33, 310.85, 312.51, 312.06, 306.31, 315.2, 310.26, 311.23, 307.34, 301.54, 290.55, 291.58, 295.63, 291.13, 296.42, 299.24, 295.95, 298.01, 297.01, 294.3, 293.08, 275.15, 283.78, 281.74, 289.36, 294.38, 308.63, 312.66, 310.66, 313.39, 316.22, 315.32, 317.31, 314.86, 327.5, 333.26, 333.74, 326.59, 327.74, 325.89, 321.66, 333.02, 336.91, 340.08], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [260.05, 257.22, 259.64, 260.59, 260.57, 255.52, 249.89, 252.59, 254.0, 249.71, 248.73, 247.76, 251.26, 251.41, 252.39, 252.66, 248.57, 246.4, 253.56, 255.39, 255.68, 258.62, 253.27, 258.66, 260.25, 260.24, 258.96, 258.59, 266.18, 263.16, 269.98, 272.8, 265.93, 272.92, 273.18, 270.81, 267.36, 270.46, 269.92, 271.1, 279.88, 276.58, 283.92, 287.25, 287.18, 293.05, 292.68, 294.8, 298.87, 298.21, 300.23, 297.84, 298.97, 302.25, 304.99, 308.82, 308.33, 310.85, 312.51, 312.06, 306.31, 315.2, 310.26, 311.23, 307.34, 301.54, 290.55, 291.58, 295.63, 291.13, 296.42, 299.24, 295.95, 298.01, 297.01, 294.3, 293.08, 275.15, 283.78, 281.74, 289.36, 294.38, 308.63, 312.66, 310.66, 313.39, 316.22, 315.32, 317.31, 314.86, 327.5, 333.26, 333.74, 326.59, 327.74, 325.89, 321.66, 333.02, 336.91, 340.08], 'signals': ['FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
       <c r="S9" t="n">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>FLAT</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.67</v>
+        <v>0.681</v>
       </c>
       <c r="E10" t="n">
         <v>53</v>
@@ -1204,7 +1204,7 @@
         <v>13.64000047956194</v>
       </c>
       <c r="U10" t="n">
-        <v>40.63643316345857</v>
+        <v>40.63643316345468</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.289</v>
+        <v>0.235</v>
       </c>
       <c r="E11" t="n">
         <v>62</v>
@@ -1303,10 +1303,10 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.872</v>
+        <v>0.879</v>
       </c>
       <c r="E12" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="F12" t="n">
         <v>60</v>
@@ -1315,16 +1315,16 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>407</v>
+        <v>102</v>
       </c>
       <c r="I12" t="n">
-        <v>8.1</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
         <v>18.3</v>
       </c>
       <c r="K12" t="n">
-        <v>-10.2</v>
+        <v>-16.3</v>
       </c>
       <c r="L12" t="n">
         <v>5000</v>
@@ -1333,20 +1333,20 @@
         <v>35</v>
       </c>
       <c r="N12" t="n">
+        <v>4</v>
+      </c>
+      <c r="O12" t="n">
         <v>5</v>
       </c>
-      <c r="O12" t="n">
-        <v>8</v>
-      </c>
       <c r="P12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [119.13, 117.73, 118.78, 118.56, 118.18, 116.66, 115.67, 116.84, 116.84, 115.56, 115.38, 113.29, 114.35, 114.66, 115.14, 111.17, 110.14, 107.67, 111.94, 114.32, 114.56, 115.49, 116.47, 121.17, 122.57, 123.15, 124.4, 126.46, 126.39, 126.55, 128.1, 127.44, 126.46, 128.91, 129.03, 131.32, 131.91, 129.76, 130.57, 133.59, 134.21, 134.23, 137.67, 141.37, 139.09, 143.59, 145.85, 144.23, 146.07, 147.29, 143.26, 141.2, 140.41, 143.09, 144.47, 144.72, 149.57, 149.37, 149.9, 150.36, 152.09, 154.08, 154.85, 152.6, 144.06, 147.65, 147.28, 143.46, 150.35, 152.25, 157.6, 154.38, 155.25, 159.65, 161.66, 154.34, 153.79, 159.64, 154.2, 158.53, 161.54, 155.32, 150.83, 152.98, 149.42, 150.57, 153.08, 153.75, 149.73, 152.86, 150.0, 145.28, 143.89, 144.52, 149.7, 150.07, 149.83, 146.51, 144.75, 140.95], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [119.13, 117.73, 118.78, 118.56, 118.18, 116.66, 115.67, 116.84, 116.84, 115.56, 115.38, 113.29, 114.35, 114.66, 115.14, 111.17, 110.14, 107.67, 111.94, 114.32, 114.56, 115.49, 116.47, 121.17, 122.57, 123.15, 124.4, 126.46, 126.39, 126.55, 128.1, 127.44, 126.46, 128.91, 129.03, 131.32, 131.91, 129.76, 130.57, 133.59, 134.21, 134.23, 137.67, 141.37, 139.09, 143.59, 145.85, 144.23, 146.07, 147.29, 143.26, 141.2, 140.41, 143.09, 144.47, 144.72, 149.57, 149.37, 149.9, 150.36, 152.09, 154.08, 154.85, 152.6, 144.06, 147.65, 147.28, 143.46, 150.35, 152.25, 157.6, 154.38, 155.25, 159.65, 161.66, 154.34, 153.79, 159.64, 154.2, 158.53, 161.54, 155.32, 150.83, 152.98, 149.42, 150.57, 153.08, 153.75, 149.73, 152.86, 150.0, 145.28, 143.89, 144.52, 149.7, 150.07, 149.83, 146.51, 144.75, 140.95], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
       <c r="S12" t="n">
@@ -1356,11 +1356,11 @@
         <v>4.625142778669085</v>
       </c>
       <c r="U12" t="n">
-        <v>32.31190962718118</v>
+        <v>32.31190962626408</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>FLAT</t>
         </is>
       </c>
     </row>

--- a/demo_results.xlsx
+++ b/demo_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,19 +531,19 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UP  </t>
+          <t>DOWN</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.522</v>
+        <v>0.17</v>
       </c>
       <c r="E2" t="n">
         <v>59</v>
@@ -552,51 +552,51 @@
         <v>60</v>
       </c>
       <c r="G2" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H2" t="n">
-        <v>2154</v>
+        <v>881</v>
       </c>
       <c r="I2" t="n">
-        <v>43.1</v>
+        <v>17.6</v>
       </c>
       <c r="J2" t="n">
-        <v>127.9</v>
+        <v>30.8</v>
       </c>
       <c r="K2" t="n">
-        <v>-84.8</v>
+        <v>-13.2</v>
       </c>
       <c r="L2" t="n">
         <v>5000</v>
       </c>
       <c r="M2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="N2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O2" t="n">
         <v>15</v>
       </c>
       <c r="P2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q2" t="n">
-        <v>8</v>
+        <v>5.7</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [199.45, 192.43, 202.68, 203.23, 204.83, 197.74, 193.39, 196.58, 196.31, 199.46, 205.27, 201.33, 202.68, 205.37, 220.27, 203.77, 201.99, 196.04, 203.43, 210.21, 217.5, 220.18, 221.53, 231.82, 236.64, 245.04, 246.83, 255.07, 258.12, 278.26, 278.39, 274.95, 284.49, 303.46, 305.33, 347.81, 334.63, 323.21, 337.11, 354.49, 360.54, 341.54, 355.26, 421.39, 408.46, 455.19, 458.79, 448.29, 445.5, 449.7, 424.1, 420.99, 414.05, 447.58, 449.59, 467.51, 503.89, 495.54, 518.09, 516.1, 510.13, 521.54, 542.52, 523.2, 466.38, 490.33, 475.51, 452.4, 488.45, 511.57, 547.26, 507.29, 512.48, 537.37, 551.63, 519.85, 519.74, 532.57, 521.58, 539.49, 580.91, 540.88, 517.82, 552.05, 516.11, 517.41, 546.72, 557.89, 534.39, 548.13, 529.14, 500.94, 495.76, 503.57, 544.43, 552.33, 539.69, 521.95, 494.95, 454.62], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [260.05, 257.22, 259.64, 260.59, 260.57, 255.52, 249.89, 252.59, 254.0, 249.71, 248.73, 247.76, 251.26, 251.41, 252.39, 252.66, 248.57, 246.4, 253.56, 255.39, 255.68, 258.62, 253.27, 258.66, 260.25, 260.24, 258.96, 258.59, 266.18, 263.16, 269.98, 272.8, 265.93, 272.92, 273.18, 270.81, 267.36, 270.46, 269.92, 271.1, 279.88, 276.58, 283.92, 287.25, 287.18, 293.05, 292.68, 294.8, 298.87, 298.21, 300.23, 297.84, 298.97, 302.25, 304.99, 308.82, 308.33, 310.85, 312.51, 312.06, 306.31, 315.2, 310.26, 311.23, 307.34, 301.54, 290.55, 291.58, 295.63, 291.13, 296.42, 299.24, 295.95, 298.01, 297.01, 294.3, 293.08, 275.15, 283.78, 281.74, 289.36, 294.38, 308.63, 312.66, 310.66, 313.39, 316.22, 315.32, 317.31, 314.86, 327.5, 333.26, 333.74, 326.59, 327.74, 325.89, 321.66, 333.02, 336.91, 340.08], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>454.62</v>
+        <v>340.08</v>
       </c>
       <c r="T2" t="n">
-        <v>38.41143798828125</v>
+        <v>7.901430402483259</v>
       </c>
       <c r="U2" t="n">
-        <v>14.03515283276854</v>
+        <v>43.6905405239262</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
@@ -607,72 +607,72 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DOWN</t>
+          <t xml:space="preserve">UP  </t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.448</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="F3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G3" t="n">
-        <v>68.40000000000001</v>
+        <v>66.7</v>
       </c>
       <c r="H3" t="n">
-        <v>2335</v>
+        <v>56</v>
       </c>
       <c r="I3" t="n">
-        <v>46.7</v>
+        <v>1.1</v>
       </c>
       <c r="J3" t="n">
-        <v>106.8</v>
+        <v>-4</v>
       </c>
       <c r="K3" t="n">
-        <v>-60.1</v>
+        <v>5.1</v>
       </c>
       <c r="L3" t="n">
         <v>5000</v>
       </c>
       <c r="M3" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="N3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O3" t="n">
         <v>2</v>
       </c>
-      <c r="O3" t="n">
-        <v>13</v>
-      </c>
       <c r="P3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q3" t="n">
-        <v>7</v>
+        <v>1.5</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [396.82, 370.09, 389.1, 402.88, 418.45, 405.12, 425.89, 441.55, 461.43, 461.47, 444.02, 422.66, 404.12, 395.3, 381.87, 355.26, 357.02, 321.75, 337.79, 367.79, 366.18, 377.7, 377.52, 406.67, 421.45, 420.53, 426.49, 465.59, 456.16, 457.16, 455.0, 448.35, 449.31, 487.41, 481.65, 496.64, 524.48, 504.21, 518.38, 517.08, 542.13, 576.36, 640.1, 666.49, 646.53, 746.7, 795.21, 766.46, 803.51, 775.89, 724.55, 681.44, 698.63, 731.88, 761.98, 750.88, 895.74, 928.27, 923.38, 970.85, 1035.34, 1063.94, 1079.4, 995.85, 863.88, 949.13, 935.75, 891.74, 995.72, 981.46, 1087.82, 1020.6, 1043.03, 1133.82, 1211.19, 1051.61, 1048.35, 1213.37, 1132.16, 1145.1, 1154.11, 1032.12, 975.41, 984.75, 938.38, 948.8, 991.64, 979.3, 937.0, 983.12, 904.28, 853.2, 848.95, 865.46, 970.82, 959.48, 990.21, 920.95, 900.2, 820.53], 'signals': ['FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [409.79, 408.08, 408.53, 404.88, 404.0, 400.99, 394.7, 399.09, 398.55, 390.94, 388.18, 381.04, 382.17, 371.93, 370.24, 365.18, 356.0, 358.18, 369.37, 368.57, 372.65, 372.07, 371.49, 373.52, 372.26, 370.07, 383.54, 392.26, 410.33, 419.35, 421.88, 417.17, 423.24, 431.98, 414.85, 423.7, 423.9, 428.32, 423.54, 406.9, 413.54, 412.73, 410.49, 413.07, 419.86, 414.22, 411.77, 406.89, 404.33, 408.55, 421.01, 422.62, 416.52, 420.15, 419.09, 418.57, 416.03, 412.67, 426.99, 450.24, 460.52, 441.31, 427.34, 428.05, 416.67, 411.74, 403.41, 397.36, 390.34, 390.74, 399.76, 393.83, 378.91, 379.4, 367.34, 373.94, 365.46, 352.83, 372.97, 368.57, 373.02, 384.28, 390.49, 386.74, 388.84, 383.34, 384.36, 385.1, 390.99, 384.93, 395.63, 401.1, 393.82, 402.29, 397.75, 390.34, 381.58, 381.7, 389.1, 393.35], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>820.53</v>
+        <v>393.35</v>
       </c>
       <c r="T3" t="n">
-        <v>77.43857683454242</v>
+        <v>11.6614270891462</v>
       </c>
       <c r="U3" t="n">
-        <v>26.25061192572846</v>
+        <v>17.97354091550426</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
@@ -683,11 +683,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -695,86 +695,86 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.611</v>
+        <v>0.535</v>
       </c>
       <c r="E4" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F4" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G4" t="n">
-        <v>57.1</v>
+        <v>60</v>
       </c>
       <c r="H4" t="n">
-        <v>657</v>
+        <v>248</v>
       </c>
       <c r="I4" t="n">
-        <v>13.1</v>
+        <v>5</v>
       </c>
       <c r="J4" t="n">
-        <v>70.59999999999999</v>
+        <v>11.1</v>
       </c>
       <c r="K4" t="n">
-        <v>-57.5</v>
+        <v>-6.1</v>
       </c>
       <c r="L4" t="n">
         <v>5000</v>
       </c>
       <c r="M4" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="N4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
         <v>2</v>
       </c>
-      <c r="P4" t="n">
-        <v>5</v>
-      </c>
       <c r="Q4" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [106.54, 107.25, 108.53, 109.08, 110.51, 110.39, 110.44, 105.96, 108.3, 108.95, 107.04, 102.25, 103.33, 98.25, 96.46, 98.15, 92.39, 95.01, 97.6, 98.33, 99.78, 99.65, 105.81, 106.63, 98.67, 94.75, 100.56, 99.62, 102.79, 104.55, 105.99, 108.29, 112.4, 116.67, 111.35, 112.03, 113.65, 113.75, 113.1, 111.44, 113.91, 117.31, 119.13, 117.02, 126.43, 131.94, 135.57, 136.54, 140.64, 144.99, 148.52, 154.71, 154.22, 162.53, 162.06, 165.87, 167.89, 161.34, 167.75, 182.75, 195.54, 192.24, 186.9, 179.77, 167.76, 164.7, 161.23, 161.93, 172.88, 170.7, 173.23, 169.87, 170.74, 171.21, 168.86, 170.23, 168.26, 169.66, 175.27, 185.73, 190.79, 193.18, 193.98, 199.38, 194.62, 191.12, 198.4, 187.18, 187.91, 210.73, 206.77, 203.76, 203.08, 198.49, 191.15, 188.42, 183.42, 183.28, 180.11, 181.8], 'signals': ['BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [300.49, 298.13, 306.18, 306.86, 308.52, 303.37, 302.1, 305.38, 310.73, 307.51, 306.95, 300.82, 301.88, 290.27, 290.76, 280.75, 274.18, 273.34, 287.39, 297.21, 295.59, 299.81, 305.28, 317.13, 318.3, 317.05, 321.12, 332.71, 336.92, 335.82, 341.48, 337.22, 332.09, 339.12, 338.69, 344.19, 350.13, 349.57, 349.73, 384.57, 385.46, 383.02, 388.2, 397.8, 397.75, 400.56, 388.41, 387.12, 402.38, 400.83, 396.54, 396.7, 387.43, 388.68, 387.43, 382.74, 388.65, 388.6, 389.9, 380.11, 376.15, 361.63, 358.78, 371.97, 368.31, 363.31, 364.26, 356.38, 357.77, 359.68, 369.35, 373.25, 363.79, 368.03, 349.68, 346.13, 345.29, 343.71, 337.39, 353.65, 357.37, 361.21, 359.91, 366.46, 367.03, 361.92, 358.89, 357.18, 352.51, 359.51, 370.92, 354.46, 346.77, 351.99, 347.15, 342.09, 317.69, 319.74, 326.56, 333.71], 'signals': ['BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL']}</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>181.8</v>
+        <v>333.71</v>
       </c>
       <c r="T4" t="n">
-        <v>10.44007001604353</v>
+        <v>11.90500313895089</v>
       </c>
       <c r="U4" t="n">
-        <v>27.9227001484601</v>
+        <v>20.12126527259463</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">UP  </t>
+          <t>DOWN</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.526</v>
+        <v>0.275</v>
       </c>
       <c r="E5" t="n">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="F5" t="n">
         <v>60</v>
@@ -783,48 +783,48 @@
         <v>50</v>
       </c>
       <c r="H5" t="n">
-        <v>1014</v>
+        <v>-356</v>
       </c>
       <c r="I5" t="n">
-        <v>20.3</v>
+        <v>-7.1</v>
       </c>
       <c r="J5" t="n">
-        <v>7.6</v>
+        <v>5.4</v>
       </c>
       <c r="K5" t="n">
-        <v>12.7</v>
+        <v>-12.5</v>
       </c>
       <c r="L5" t="n">
         <v>5000</v>
       </c>
       <c r="M5" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="N5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O5" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="P5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.8</v>
+        <v>7.5</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [183.12, 177.6, 182.43, 184.54, 185.81, 182.93, 180.04, 183.01, 181.72, 180.19, 178.35, 172.5, 175.44, 175.0, 178.47, 171.04, 167.32, 164.98, 174.2, 175.55, 177.18, 177.43, 177.89, 181.87, 183.7, 188.41, 189.09, 196.28, 198.64, 198.12, 201.45, 201.82, 199.65, 202.26, 199.41, 208.03, 216.36, 212.92, 209.01, 199.34, 198.22, 198.25, 196.27, 207.59, 211.25, 214.95, 219.18, 220.52, 225.57, 235.47, 225.06, 222.06, 220.35, 223.21, 219.25, 215.08, 214.61, 212.35, 214.0, 210.89, 224.1, 222.56, 214.5, 218.66, 205.1, 208.64, 208.19, 200.42, 204.87, 205.19, 212.45, 207.41, 204.65, 210.69, 208.65, 200.04, 199.0, 195.74, 192.53, 194.97, 200.09, 197.58, 194.83, 195.55, 196.93, 204.12, 202.78, 210.96, 203.53, 211.8, 212.5, 207.4, 202.81, 203.28, 207.29, 212.06, 208.76, 206.84, 196.51, 197.01], 'signals': ['BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'BUY', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [218.94, 213.21, 213.49, 214.33, 212.65, 209.53, 207.67, 211.74, 215.2, 209.87, 208.76, 205.37, 210.14, 207.24, 211.71, 207.54, 199.34, 200.95, 208.27, 210.57, 209.77, 212.79, 213.77, 221.25, 233.65, 238.38, 239.89, 249.02, 248.5, 249.7, 250.56, 248.28, 249.91, 255.36, 255.08, 263.99, 261.12, 259.7, 263.04, 265.06, 268.26, 272.05, 273.55, 274.99, 271.17, 272.68, 268.99, 265.82, 270.13, 267.22, 264.14, 264.86, 259.34, 265.01, 268.46, 266.32, 265.29, 271.85, 274.0, 270.64, 261.26, 256.52, 250.02, 253.79, 246.03, 245.22, 244.19, 238.0, 241.51, 238.55, 246.02, 246.0, 237.5, 244.39, 232.79, 234.11, 234.27, 227.01, 232.69, 240.14, 238.34, 241.7, 242.67, 244.16, 245.98, 243.62, 247.04, 245.34, 247.31, 247.49, 254.96, 249.89, 247.23, 249.99, 247.55, 244.85, 233.66, 232.11, 231.39, 230.86], 'signals': ['BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>197.01</v>
+        <v>230.86</v>
       </c>
       <c r="T5" t="n">
-        <v>7.734284537179129</v>
+        <v>6.669285365513393</v>
       </c>
       <c r="U5" t="n">
-        <v>23.25884591416595</v>
+        <v>31.6319588524311</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -835,72 +835,72 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DOWN</t>
+          <t xml:space="preserve">UP  </t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.344</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="F6" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="G6" t="n">
-        <v>45</v>
+        <v>58.3</v>
       </c>
       <c r="H6" t="n">
-        <v>373</v>
+        <v>62</v>
       </c>
       <c r="I6" t="n">
-        <v>7.5</v>
+        <v>1.2</v>
       </c>
       <c r="J6" t="n">
-        <v>-19.1</v>
+        <v>-10</v>
       </c>
       <c r="K6" t="n">
-        <v>26.6</v>
+        <v>11.2</v>
       </c>
       <c r="L6" t="n">
         <v>5000</v>
       </c>
       <c r="M6" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="N6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="P6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.2</v>
+        <v>5</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [152.67, 157.16, 156.43, 151.14, 151.6, 153.5, 150.95, 152.72, 155.08, 152.77, 155.68, 150.68, 160.84, 154.78, 154.96, 147.56, 143.06, 137.55, 146.28, 146.49, 148.46, 147.93, 150.07, 140.76, 130.49, 128.06, 132.37, 135.7, 142.15, 142.76, 146.39, 145.89, 145.97, 152.62, 141.57, 143.09, 143.1, 141.18, 137.97, 139.11, 144.07, 146.03, 135.91, 133.79, 137.05, 137.8, 136.89, 136.0, 130.05, 133.73, 133.99, 135.14, 135.26, 137.15, 137.41, 136.88, 136.6, 132.51, 143.34, 156.54, 160.65, 152.17, 142.2, 141.7, 135.53, 136.47, 132.07, 130.21, 131.08, 127.99, 134.71, 133.25, 130.63, 128.47, 119.5, 116.7, 113.5, 107.27, 112.93, 115.7, 116.67, 125.73, 129.3, 132.54, 134.37, 132.22, 129.04, 126.79, 130.04, 133.72, 133.76, 134.44, 132.38, 134.85, 132.66, 124.57, 123.37, 122.92, 131.53, 123.53], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT']}</t>
+          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [659.39, 643.71, 646.24, 652.91, 653.69, 637.04, 612.62, 626.87, 622.08, 615.11, 606.14, 593.11, 603.5, 592.37, 594.34, 547.03, 525.23, 535.88, 571.6, 578.69, 573.93, 572.49, 574.52, 611.85, 627.81, 629.28, 633.94, 661.88, 670.96, 676.24, 687.91, 670.29, 668.22, 674.1, 658.54, 674.4, 677.99, 670.72, 668.5, 611.34, 608.19, 609.84, 604.4, 612.31, 616.24, 609.07, 598.31, 602.44, 616.06, 617.86, 613.66, 610.64, 602.05, 604.5, 606.82, 609.69, 611.77, 634.67, 634.7, 631.92, 599.91, 597.08, 622.4, 626.99, 592.45, 584.85, 584.05, 570.45, 567.9, 566.45, 593.48, 600.21, 567.58, 577.22, 563.85, 562.2, 557.67, 542.87, 550.25, 562.6, 563.29, 612.91, 582.9, 600.29, 615.58, 603.12, 631.48, 669.21, 656.73, 661.04, 681.31, 664.54, 646.01, 645.85, 643.81, 627.17, 606.1, 595.19, 593.87, 593.41], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>123.53</v>
+        <v>593.41</v>
       </c>
       <c r="T6" t="n">
-        <v>7.04071535382952</v>
+        <v>26.05214582170759</v>
       </c>
       <c r="U6" t="n">
-        <v>22.19321356384988</v>
+        <v>23.67631632710235</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -911,72 +911,72 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DOWN</t>
+          <t xml:space="preserve">UP  </t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.105</v>
+        <v>0.611</v>
       </c>
       <c r="E7" t="n">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="F7" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="G7" t="n">
-        <v>46.7</v>
+        <v>50</v>
       </c>
       <c r="H7" t="n">
-        <v>-977</v>
+        <v>343</v>
       </c>
       <c r="I7" t="n">
-        <v>-19.5</v>
+        <v>6.9</v>
       </c>
       <c r="J7" t="n">
-        <v>-18.4</v>
+        <v>7.6</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.1</v>
+        <v>-0.7</v>
       </c>
       <c r="L7" t="n">
         <v>5000</v>
       </c>
       <c r="M7" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="N7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O7" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="P7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [205.71, 197.22, 199.79, 196.52, 198.63, 193.23, 195.53, 203.32, 210.23, 202.29, 202.91, 197.5, 200.62, 181.04, 181.1, 173.38, 161.14, 160.79, 174.61, 172.99, 171.46, 174.79, 175.18, 175.09, 169.02, 167.85, 174.53, 184.41, 195.9, 199.83, 206.33, 211.63, 195.95, 206.24, 197.93, 199.77, 196.68, 194.1, 181.73, 187.77, 191.25, 202.99, 197.75, 197.96, 192.96, 201.16, 216.6, 207.64, 201.8, 212.01, 195.43, 189.44, 193.45, 191.29, 193.56, 184.99, 180.01, 173.78, 182.25, 189.03, 182.61, 173.99, 163.22, 164.13, 152.4, 162.11, 155.5, 153.97, 160.43, 159.78, 169.62, 169.27, 164.92, 163.26, 164.84, 158.18, 150.11, 142.52, 149.06, 151.65, 146.19, 159.24, 165.48, 168.87, 163.51, 159.36, 158.44, 159.07, 157.37, 161.5, 167.21, 160.49, 157.12, 160.43, 175.85, 166.12, 161.16, 158.29, 167.49, 167.9], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [183.12, 177.6, 182.43, 184.54, 185.81, 182.93, 180.04, 183.01, 181.72, 180.19, 178.35, 172.5, 175.44, 175.0, 178.47, 171.04, 167.32, 164.98, 174.2, 175.55, 177.18, 177.43, 177.89, 181.87, 183.7, 188.41, 189.09, 196.28, 198.64, 198.12, 201.45, 201.82, 199.65, 202.26, 199.41, 208.03, 216.36, 212.92, 209.01, 199.34, 198.22, 198.25, 196.27, 207.59, 211.25, 214.95, 219.18, 220.52, 225.57, 235.47, 225.06, 222.06, 220.35, 223.21, 219.25, 215.08, 214.61, 212.35, 214.0, 210.89, 224.1, 222.56, 214.5, 218.66, 205.1, 208.64, 208.19, 200.42, 204.87, 205.19, 212.45, 207.41, 204.65, 210.69, 208.65, 200.04, 199.0, 195.74, 192.53, 194.97, 200.09, 197.58, 194.83, 195.55, 196.93, 204.12, 202.78, 210.96, 203.53, 211.8, 212.5, 207.4, 202.81, 203.28, 207.29, 212.06, 208.76, 206.84, 196.51, 197.01], 'signals': ['BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'BUY', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>167.9</v>
+        <v>197.01</v>
       </c>
       <c r="T7" t="n">
-        <v>9.024287632533483</v>
+        <v>7.734284537179129</v>
       </c>
       <c r="U7" t="n">
-        <v>17.05993620111895</v>
+        <v>23.25884591416595</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -987,72 +987,72 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DOWN</t>
+          <t xml:space="preserve">UP  </t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.272</v>
+        <v>0.628</v>
       </c>
       <c r="E8" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F8" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G8" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H8" t="n">
-        <v>-68</v>
+        <v>727</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.4</v>
+        <v>14.5</v>
       </c>
       <c r="J8" t="n">
-        <v>-27</v>
+        <v>14.9</v>
       </c>
       <c r="K8" t="n">
-        <v>25.6</v>
+        <v>-0.4</v>
       </c>
       <c r="L8" t="n">
         <v>5000</v>
       </c>
       <c r="M8" t="n">
-        <v>69</v>
+        <v>13</v>
       </c>
       <c r="N8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="P8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [99.17, 99.02, 98.32, 96.94, 94.89, 94.31, 95.31, 95.2, 94.36, 94.7, 91.74, 91.82, 93.38, 90.92, 92.28, 93.32, 93.43, 92.97, 96.15, 95.55, 98.66, 98.93, 98.82, 99.39, 102.05, 103.01, 103.16, 106.28, 107.71, 107.79, 97.31, 94.83, 92.58, 93.24, 92.82, 92.44, 91.37, 92.27, 92.12, 93.61, 92.06, 91.02, 87.89, 88.27, 88.25, 87.49, 85.45, 87.66, 87.56, 86.94, 87.02, 89.65, 89.33, 88.09, 89.3, 88.6, 87.68, 87.35, 86.36, 86.02, 85.85, 83.33, 81.52, 81.56, 82.18, 82.64, 81.41, 82.0, 81.27, 80.34, 81.67, 78.72, 76.96, 77.38, 72.88, 72.82, 71.84, 70.9, 73.81, 73.78, 71.4, 74.19, 77.65, 76.02, 76.18, 75.59, 75.47, 73.37, 73.83, 73.53, 73.68, 74.35, 68.95, 67.6, 68.67, 68.53, 68.89, 70.09, 70.4, 72.39], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [331.55, 329.27, 344.48, 341.32, 340.32, 334.74, 320.98, 323.73, 320.13, 314.77, 318.67, 309.37, 322.0, 317.79, 318.31, 308.93, 300.2, 292.95, 309.02, 312.99, 314.05, 313.93, 333.44, 350.08, 354.35, 370.96, 379.15, 380.18, 396.09, 397.84, 405.9, 399.0, 401.53, 421.98, 419.28, 422.09, 417.54, 399.2, 404.81, 416.77, 420.61, 415.84, 426.68, 424.77, 411.91, 429.32, 427.75, 418.64, 416.13, 439.1, 424.52, 420.05, 410.42, 417.1, 413.91, 413.49, 421.34, 421.19, 425.91, 446.06, 459.24, 480.81, 478.47, 418.25, 385.12, 395.97, 391.54, 371.51, 384.96, 381.47, 393.32, 376.11, 392.28, 410.7, 392.13, 380.15, 382.07, 378.91, 365.02, 372.45, 377.75, 369.34, 360.45, 373.9, 370.78, 388.69, 401.11, 399.97, 384.05, 389.11, 394.28, 374.45, 370.83, 378.16, 386.5, 396.81, 392.47, 381.92, 383.22, 380.91], 'signals': ['BUY', 'HOLD', 'SELL', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>72.39</v>
+        <v>380.91</v>
       </c>
       <c r="T8" t="n">
-        <v>2.682855878557478</v>
+        <v>14.95071193150112</v>
       </c>
       <c r="U8" t="n">
-        <v>34.27873709740564</v>
+        <v>11.7428541065135</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -1063,72 +1063,72 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>ORCL</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">UP  </t>
+          <t>DOWN</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.795</v>
+        <v>0.325</v>
       </c>
       <c r="E9" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F9" t="n">
         <v>40</v>
       </c>
       <c r="G9" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>736</v>
+        <v>1073</v>
       </c>
       <c r="I9" t="n">
-        <v>14.7</v>
+        <v>21.5</v>
       </c>
       <c r="J9" t="n">
-        <v>30.8</v>
+        <v>-22</v>
       </c>
       <c r="K9" t="n">
-        <v>-16.1</v>
+        <v>43.5</v>
       </c>
       <c r="L9" t="n">
         <v>5000</v>
       </c>
       <c r="M9" t="n">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="N9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O9" t="n">
+        <v>4</v>
+      </c>
+      <c r="P9" t="n">
         <v>5</v>
       </c>
-      <c r="P9" t="n">
-        <v>2</v>
-      </c>
       <c r="Q9" t="n">
-        <v>3.5</v>
+        <v>1.8</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [260.05, 257.22, 259.64, 260.59, 260.57, 255.52, 249.89, 252.59, 254.0, 249.71, 248.73, 247.76, 251.26, 251.41, 252.39, 252.66, 248.57, 246.4, 253.56, 255.39, 255.68, 258.62, 253.27, 258.66, 260.25, 260.24, 258.96, 258.59, 266.18, 263.16, 269.98, 272.8, 265.93, 272.92, 273.18, 270.81, 267.36, 270.46, 269.92, 271.1, 279.88, 276.58, 283.92, 287.25, 287.18, 293.05, 292.68, 294.8, 298.87, 298.21, 300.23, 297.84, 298.97, 302.25, 304.99, 308.82, 308.33, 310.85, 312.51, 312.06, 306.31, 315.2, 310.26, 311.23, 307.34, 301.54, 290.55, 291.58, 295.63, 291.13, 296.42, 299.24, 295.95, 298.01, 297.01, 294.3, 293.08, 275.15, 283.78, 281.74, 289.36, 294.38, 308.63, 312.66, 310.66, 313.39, 316.22, 315.32, 317.31, 314.86, 327.5, 333.26, 333.74, 326.59, 327.74, 325.89, 321.66, 333.02, 336.91, 340.08], 'signals': ['FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [153.72, 151.9, 150.51, 148.36, 161.99, 158.06, 154.03, 154.89, 153.62, 151.84, 154.44, 148.64, 153.27, 146.07, 145.01, 141.82, 138.69, 137.84, 146.09, 144.22, 145.36, 144.53, 142.18, 142.66, 137.38, 137.61, 155.08, 162.43, 169.22, 177.72, 174.45, 176.96, 180.54, 186.85, 175.67, 172.68, 172.36, 165.38, 163.26, 160.83, 171.23, 179.66, 184.71, 193.36, 193.92, 195.27, 193.17, 186.18, 189.1, 194.93, 192.28, 185.96, 180.83, 187.51, 189.11, 191.41, 192.39, 190.3, 202.99, 225.0, 247.29, 243.73, 229.53, 235.52, 212.94, 211.09, 205.1, 200.56, 183.46, 183.49, 191.97, 187.68, 182.89, 183.65, 174.46, 164.59, 156.98, 151.93, 148.02, 147.25, 146.04, 142.01, 139.78, 143.26, 141.11, 140.0, 143.72, 140.64, 131.54, 127.94, 132.49, 124.21, 126.41, 121.38, 127.05, 125.84, 120.04, 114.99, 119.9, 119.96], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>340.08</v>
+        <v>119.96</v>
       </c>
       <c r="T9" t="n">
-        <v>7.901430402483259</v>
+        <v>6.947873837857358</v>
       </c>
       <c r="U9" t="n">
-        <v>43.6905405239262</v>
+        <v>55.04654065605482</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -1139,11 +1139,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GLW</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1151,60 +1151,60 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.681</v>
+        <v>0.573</v>
       </c>
       <c r="E10" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="F10" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="G10" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H10" t="n">
-        <v>-332</v>
+        <v>2154</v>
       </c>
       <c r="I10" t="n">
-        <v>-6.6</v>
+        <v>43.1</v>
       </c>
       <c r="J10" t="n">
-        <v>-6.3</v>
+        <v>127.9</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.3</v>
+        <v>-84.8</v>
       </c>
       <c r="L10" t="n">
         <v>5000</v>
       </c>
       <c r="M10" t="n">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O10" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="P10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [134.53, 123.1, 128.85, 136.01, 131.56, 129.57, 128.92, 131.85, 129.69, 129.66, 132.88, 124.39, 130.77, 141.79, 146.13, 135.11, 136.6, 128.35, 135.76, 142.16, 147.69, 146.28, 148.29, 164.85, 169.54, 170.98, 174.9, 172.56, 168.01, 165.83, 164.13, 165.13, 165.2, 168.5, 169.24, 175.62, 167.75, 152.82, 151.67, 163.99, 158.02, 159.72, 161.85, 181.29, 182.12, 186.65, 207.07, 197.94, 206.19, 207.96, 191.52, 178.28, 175.56, 180.41, 191.6, 193.75, 195.87, 190.6, 182.69, 181.16, 176.7, 200.4, 200.76, 197.7, 177.58, 187.54, 173.94, 168.17, 176.55, 179.2, 187.88, 177.42, 175.4, 194.92, 209.83, 194.07, 205.83, 228.01, 221.05, 255.69, 255.43, 220.63, 196.79, 194.8, 185.38, 184.03, 192.38, 190.89, 183.11, 187.64, 174.41, 158.39, 154.61, 153.1, 162.41, 154.06, 156.06, 146.65, 143.36, 126.01], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [199.45, 192.43, 202.68, 203.23, 204.83, 197.74, 193.39, 196.58, 196.31, 199.46, 205.27, 201.33, 202.68, 205.37, 220.27, 203.77, 201.99, 196.04, 203.43, 210.21, 217.5, 220.18, 221.53, 231.82, 236.64, 245.04, 246.83, 255.07, 258.12, 278.26, 278.39, 274.95, 284.49, 303.46, 305.33, 347.81, 334.63, 323.21, 337.11, 354.49, 360.54, 341.54, 355.26, 421.39, 408.46, 455.19, 458.79, 448.29, 445.5, 449.7, 424.1, 420.99, 414.05, 447.58, 449.59, 467.51, 503.89, 495.54, 518.09, 516.1, 510.13, 521.54, 542.52, 523.2, 466.38, 490.33, 475.51, 452.4, 488.45, 511.57, 547.26, 507.29, 512.48, 537.37, 551.63, 519.85, 519.74, 532.57, 521.58, 539.49, 580.91, 540.88, 517.82, 552.05, 516.11, 517.41, 546.72, 557.89, 534.39, 548.13, 529.14, 500.94, 495.76, 503.57, 544.43, 552.33, 539.69, 521.95, 494.95, 454.62], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
       <c r="S10" t="n">
-        <v>126.01</v>
+        <v>454.62</v>
       </c>
       <c r="T10" t="n">
-        <v>13.64000047956194</v>
+        <v>38.41143798828125</v>
       </c>
       <c r="U10" t="n">
-        <v>40.63643316345468</v>
+        <v>14.03515283276854</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -1215,11 +1215,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NBIS</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1227,140 +1227,2724 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.235</v>
+        <v>0.472</v>
       </c>
       <c r="E11" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F11" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="G11" t="n">
-        <v>65</v>
+        <v>44.4</v>
       </c>
       <c r="H11" t="n">
-        <v>2039</v>
+        <v>2454</v>
       </c>
       <c r="I11" t="n">
-        <v>40.8</v>
+        <v>49.1</v>
       </c>
       <c r="J11" t="n">
-        <v>77.40000000000001</v>
+        <v>19.3</v>
       </c>
       <c r="K11" t="n">
-        <v>-36.6</v>
+        <v>29.8</v>
       </c>
       <c r="L11" t="n">
         <v>5000</v>
       </c>
       <c r="M11" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O11" t="n">
         <v>8</v>
       </c>
       <c r="P11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.8</v>
+        <v>9</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [95.65, 89.33, 94.94, 96.43, 112.0, 108.04, 112.95, 129.85, 116.33, 118.56, 121.52, 117.62, 114.15, 114.91, 115.09, 105.97, 100.82, 92.26, 103.76, 101.95, 108.82, 112.54, 117.4, 125.0, 136.33, 144.97, 154.56, 161.94, 166.77, 165.34, 157.14, 159.16, 156.55, 156.14, 157.08, 147.16, 144.96, 135.51, 141.19, 138.23, 154.49, 176.42, 175.92, 195.09, 184.77, 177.05, 186.1, 179.11, 207.27, 221.15, 219.94, 199.86, 197.73, 191.82, 219.93, 214.77, 208.06, 208.37, 226.34, 231.09, 264.51, 260.58, 251.68, 259.67, 227.81, 218.0, 220.12, 211.69, 222.24, 232.36, 260.07, 265.1, 280.91, 286.69, 283.61, 275.25, 259.66, 256.63, 240.3, 261.15, 276.17, 229.18, 215.62, 213.02, 195.19, 216.48, 216.2, 219.65, 210.51, 194.09, 199.51, 171.77, 177.71, 182.62, 216.92, 218.16, 220.97, 187.77, 187.88, 169.69], 'signals': ['FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [136.5, 135.19, 137.6, 134.7, 133.63, 130.67, 129.34, 128.91, 131.11, 129.99, 130.8, 129.42, 127.88, 128.2, 129.87, 130.06, 126.64, 126.6, 128.31, 126.81, 126.33, 125.27, 123.61, 127.04, 127.28, 127.59, 130.76, 132.35, 132.56, 133.98, 135.7, 137.01, 135.06, 135.57, 133.46, 148.3, 149.71, 149.45, 155.43, 178.92, 176.36, 167.76, 185.86, 191.86, 201.8, 218.28, 236.66, 209.54, 212.39, 199.34, 200.75, 202.89, 194.89, 201.76, 212.62, 237.28, 247.9, 232.54, 242.39, 250.1, 228.15, 239.95, 249.09, 242.57, 215.94, 217.77, 205.42, 191.2, 202.96, 211.72, 220.81, 214.07, 212.97, 226.11, 221.9, 204.13, 197.41, 204.9, 189.39, 188.72, 184.79, 181.92, 176.25, 186.48, 182.97, 186.56, 191.11, 189.16, 183.98, 178.1, 177.98, 170.61, 171.78, 170.32, 173.5, 175.63, 171.11, 166.97, 170.04, 162.88], 'signals': ['BUY', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
       <c r="S11" t="n">
-        <v>169.69</v>
+        <v>162.88</v>
       </c>
       <c r="T11" t="n">
-        <v>22.5277829851423</v>
+        <v>7.397143772670201</v>
       </c>
       <c r="U11" t="n">
-        <v>19.93684147717601</v>
+        <v>25.56126716557969</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>FLAT</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SPMO</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">UP  </t>
+          <t>DOWN</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.879</v>
+        <v>0.353</v>
       </c>
       <c r="E12" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="F12" t="n">
         <v>60</v>
       </c>
       <c r="G12" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-510</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-10.2</v>
+      </c>
+      <c r="J12" t="n">
+        <v>-9.4</v>
+      </c>
+      <c r="K12" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="L12" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M12" t="n">
+        <v>27</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" t="n">
+        <v>19</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>19</v>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [200.37, 201.09, 197.78, 193.92, 193.15, 198.27, 191.85, 197.34, 194.32, 193.36, 194.0, 194.39, 194.19, 182.09, 181.04, 184.7, 178.4, 184.09, 185.72, 185.3, 186.23, 184.09, 182.03, 175.48, 170.41, 164.54, 172.38, 170.87, 177.14, 180.75, 181.67, 185.79, 186.63, 189.31, 172.85, 177.7, 179.72, 180.85, 180.75, 176.08, 183.35, 185.0, 186.51, 180.72, 185.86, 181.35, 177.03, 170.87, 165.41, 167.15, 173.06, 179.02, 178.96, 179.64, 175.86, 179.61, 178.62, 177.05, 175.72, 190.61, 209.06, 200.32, 190.12, 188.26, 185.18, 182.08, 174.9, 170.48, 166.45, 165.89, 164.55, 161.71, 155.02, 151.78, 150.12, 153.42, 152.76, 150.19, 158.37, 157.93, 156.66, 163.23, 166.11, 165.65, 169.52, 166.58, 162.5, 163.32, 171.22, 167.56, 167.0, 172.68, 170.77, 173.79, 170.06, 163.0, 156.93, 163.66, 173.6, 181.5], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+        </is>
+      </c>
+      <c r="S12" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="T12" t="n">
+        <v>8.49714115687779</v>
+      </c>
+      <c r="U12" t="n">
+        <v>18.47121041734655</v>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>60</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0.212</v>
+      </c>
+      <c r="E13" t="n">
+        <v>56</v>
+      </c>
+      <c r="F13" t="n">
+        <v>90</v>
+      </c>
+      <c r="G13" t="n">
+        <v>30</v>
+      </c>
+      <c r="H13" t="n">
+        <v>268</v>
+      </c>
+      <c r="I13" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J13" t="n">
+        <v>-27</v>
+      </c>
+      <c r="K13" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="L13" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M13" t="n">
+        <v>69</v>
+      </c>
+      <c r="N13" t="n">
+        <v>4</v>
+      </c>
+      <c r="O13" t="n">
+        <v>9</v>
+      </c>
+      <c r="P13" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [99.17, 99.02, 98.32, 96.94, 94.89, 94.31, 95.31, 95.2, 94.36, 94.7, 91.74, 91.82, 93.38, 90.92, 92.28, 93.32, 93.43, 92.97, 96.15, 95.55, 98.66, 98.93, 98.82, 99.39, 102.05, 103.01, 103.16, 106.28, 107.71, 107.79, 97.31, 94.83, 92.58, 93.24, 92.82, 92.44, 91.37, 92.27, 92.12, 93.61, 92.06, 91.02, 87.89, 88.27, 88.25, 87.49, 85.45, 87.66, 87.56, 86.94, 87.02, 89.65, 89.33, 88.09, 89.3, 88.6, 87.68, 87.35, 86.36, 86.02, 85.85, 83.33, 81.52, 81.56, 82.18, 82.64, 81.41, 82.0, 81.27, 80.34, 81.67, 78.72, 76.96, 77.38, 72.88, 72.82, 71.84, 70.9, 73.81, 73.78, 71.4, 74.19, 77.65, 76.02, 76.18, 75.59, 75.47, 73.37, 73.83, 73.53, 73.68, 74.35, 68.95, 67.6, 68.67, 68.53, 68.89, 70.09, 70.4, 72.39], 'signals': ['FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+        </is>
+      </c>
+      <c r="S13" t="n">
+        <v>72.39</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.682855878557478</v>
+      </c>
+      <c r="U13" t="n">
+        <v>34.27873709740564</v>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>INTC</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>55</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UP  </t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="E14" t="n">
+        <v>54</v>
+      </c>
+      <c r="F14" t="n">
+        <v>80</v>
+      </c>
+      <c r="G14" t="n">
         <v>0</v>
       </c>
-      <c r="H12" t="n">
-        <v>102</v>
-      </c>
-      <c r="I12" t="n">
+      <c r="H14" t="n">
+        <v>2300</v>
+      </c>
+      <c r="I14" t="n">
+        <v>46</v>
+      </c>
+      <c r="J14" t="n">
+        <v>87.8</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-41.8</v>
+      </c>
+      <c r="L14" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M14" t="n">
+        <v>57</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" t="n">
+        <v>19</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>19</v>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [45.95, 43.42, 45.58, 46.78, 47.98, 45.25, 45.77, 45.76, 44.06, 45.03, 46.18, 43.87, 44.01, 44.06, 47.18, 44.1, 43.13, 41.19, 44.13, 48.03, 50.38, 50.78, 52.91, 58.95, 61.72, 62.38, 65.18, 63.81, 64.94, 68.5, 68.5, 65.7, 66.26, 65.27, 66.78, 82.54, 84.99, 84.52, 94.75, 94.48, 99.62, 95.78, 108.15, 113.01, 109.62, 124.92, 129.44, 120.61, 120.29, 115.93, 108.77, 108.17, 110.8, 118.96, 118.5, 119.84, 123.52, 121.77, 120.89, 114.68, 109.33, 107.93, 112.71, 111.78, 99.17, 110.27, 107.92, 107.04, 116.96, 124.57, 127.86, 117.05, 121.1, 133.99, 140.94, 132.28, 131.65, 132.87, 128.32, 131.72, 139.63, 127.02, 120.35, 122.2, 110.39, 110.24, 112.54, 109.84, 103.12, 107.76, 102.99, 96.98, 95.04, 97.06, 105.45, 102.62, 100.23, 92.32, 91.67, 86.3], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+        </is>
+      </c>
+      <c r="S14" t="n">
+        <v>86.3</v>
+      </c>
+      <c r="T14" t="n">
+        <v>7.458571297781808</v>
+      </c>
+      <c r="U14" t="n">
+        <v>38.86366638244701</v>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>MU</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>63</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0.424</v>
+      </c>
+      <c r="E15" t="n">
+        <v>54</v>
+      </c>
+      <c r="F15" t="n">
+        <v>50</v>
+      </c>
+      <c r="G15" t="n">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2335</v>
+      </c>
+      <c r="I15" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="J15" t="n">
+        <v>106.8</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-60.1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M15" t="n">
+        <v>6</v>
+      </c>
+      <c r="N15" t="n">
         <v>2</v>
       </c>
-      <c r="J12" t="n">
+      <c r="O15" t="n">
+        <v>13</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>7</v>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [396.82, 370.09, 389.1, 402.88, 418.45, 405.12, 425.89, 441.55, 461.43, 461.47, 444.02, 422.66, 404.12, 395.3, 381.87, 355.26, 357.02, 321.75, 337.79, 367.79, 366.18, 377.7, 377.52, 406.67, 421.45, 420.53, 426.49, 465.59, 456.16, 457.16, 455.0, 448.35, 449.31, 487.41, 481.65, 496.64, 524.48, 504.21, 518.38, 517.08, 542.13, 576.36, 640.1, 666.49, 646.53, 746.7, 795.21, 766.46, 803.51, 775.89, 724.55, 681.44, 698.63, 731.88, 761.98, 750.88, 895.74, 928.27, 923.38, 970.85, 1035.34, 1063.94, 1079.4, 995.85, 863.88, 949.13, 935.75, 891.74, 995.72, 981.46, 1087.82, 1020.6, 1043.03, 1133.82, 1211.19, 1051.61, 1048.35, 1213.37, 1132.16, 1145.1, 1154.11, 1032.12, 975.41, 984.75, 938.38, 948.8, 991.64, 979.3, 937.0, 983.12, 904.28, 853.2, 848.95, 865.46, 970.82, 959.48, 990.21, 920.95, 900.2, 820.53], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+        </is>
+      </c>
+      <c r="S15" t="n">
+        <v>820.53</v>
+      </c>
+      <c r="T15" t="n">
+        <v>77.43857683454242</v>
+      </c>
+      <c r="U15" t="n">
+        <v>26.25061192572861</v>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>GLW</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>54</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="E16" t="n">
+        <v>53</v>
+      </c>
+      <c r="F16" t="n">
+        <v>20</v>
+      </c>
+      <c r="G16" t="n">
+        <v>60</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-332</v>
+      </c>
+      <c r="I16" t="n">
+        <v>-6.6</v>
+      </c>
+      <c r="J16" t="n">
+        <v>-6.3</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="L16" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M16" t="n">
+        <v>39</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" t="n">
+        <v>19</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>19</v>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [134.53, 123.1, 128.85, 136.01, 131.56, 129.57, 128.92, 131.85, 129.69, 129.66, 132.88, 124.39, 130.77, 141.79, 146.13, 135.11, 136.6, 128.35, 135.76, 142.16, 147.69, 146.28, 148.29, 164.85, 169.54, 170.98, 174.9, 172.56, 168.01, 165.83, 164.13, 165.13, 165.2, 168.5, 169.24, 175.62, 167.75, 152.82, 151.67, 163.99, 158.02, 159.72, 161.85, 181.29, 182.12, 186.65, 207.07, 197.94, 206.19, 207.96, 191.52, 178.28, 175.56, 180.41, 191.6, 193.75, 195.87, 190.6, 182.69, 181.16, 176.7, 200.4, 200.76, 197.7, 177.58, 187.54, 173.94, 168.17, 176.55, 179.2, 187.88, 177.42, 175.4, 194.92, 209.83, 194.07, 205.83, 228.01, 221.05, 255.69, 255.43, 220.63, 196.79, 194.8, 185.38, 184.03, 192.38, 190.89, 183.11, 187.64, 174.41, 158.39, 154.61, 153.1, 162.41, 154.06, 156.06, 146.65, 143.36, 126.01], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+        </is>
+      </c>
+      <c r="S16" t="n">
+        <v>126.01</v>
+      </c>
+      <c r="T16" t="n">
+        <v>13.64000047956194</v>
+      </c>
+      <c r="U16" t="n">
+        <v>40.63643316345468</v>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CRWD</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>61</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UP  </t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0.8139999999999999</v>
+      </c>
+      <c r="E17" t="n">
+        <v>52</v>
+      </c>
+      <c r="F17" t="n">
+        <v>100</v>
+      </c>
+      <c r="G17" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1894</v>
+      </c>
+      <c r="I17" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="J17" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="K17" t="n">
+        <v>-32.7</v>
+      </c>
+      <c r="L17" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M17" t="n">
+        <v>27</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3</v>
+      </c>
+      <c r="O17" t="n">
+        <v>14</v>
+      </c>
+      <c r="P17" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [106.54, 107.25, 108.53, 109.08, 110.51, 110.39, 110.44, 105.96, 108.3, 108.95, 107.04, 102.25, 103.33, 98.25, 96.46, 98.15, 92.39, 95.01, 97.6, 98.33, 99.78, 99.65, 105.81, 106.63, 98.67, 94.75, 100.56, 99.62, 102.79, 104.55, 105.99, 108.29, 112.4, 116.67, 111.35, 112.03, 113.65, 113.75, 113.1, 111.44, 113.91, 117.31, 119.13, 117.02, 126.43, 131.94, 135.57, 136.54, 140.64, 144.99, 148.52, 154.71, 154.22, 162.53, 162.06, 165.87, 167.89, 161.34, 167.75, 182.75, 195.54, 192.24, 186.9, 179.77, 167.76, 164.7, 161.23, 161.93, 172.88, 170.7, 173.23, 169.87, 170.74, 171.21, 168.86, 170.23, 168.26, 169.66, 175.27, 185.73, 190.79, 193.18, 193.98, 199.38, 194.62, 191.12, 198.4, 187.18, 187.91, 210.73, 206.77, 203.76, 203.08, 198.49, 191.15, 188.42, 183.42, 183.28, 180.11, 181.8], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT']}</t>
+        </is>
+      </c>
+      <c r="S17" t="n">
+        <v>181.8</v>
+      </c>
+      <c r="T17" t="n">
+        <v>10.44007001604353</v>
+      </c>
+      <c r="U17" t="n">
+        <v>27.9227001484601</v>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>57</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="E18" t="n">
+        <v>59</v>
+      </c>
+      <c r="F18" t="n">
+        <v>20</v>
+      </c>
+      <c r="G18" t="n">
+        <v>45</v>
+      </c>
+      <c r="H18" t="n">
+        <v>373</v>
+      </c>
+      <c r="I18" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-19.1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="L18" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M18" t="n">
+        <v>40</v>
+      </c>
+      <c r="N18" t="n">
+        <v>4</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1</v>
+      </c>
+      <c r="P18" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [152.67, 157.16, 156.43, 151.14, 151.6, 153.5, 150.95, 152.72, 155.08, 152.77, 155.68, 150.68, 160.84, 154.78, 154.96, 147.56, 143.06, 137.55, 146.28, 146.49, 148.46, 147.93, 150.07, 140.76, 130.49, 128.06, 132.37, 135.7, 142.15, 142.76, 146.39, 145.89, 145.97, 152.62, 141.57, 143.09, 143.1, 141.18, 137.97, 139.11, 144.07, 146.03, 135.91, 133.79, 137.05, 137.8, 136.89, 136.0, 130.05, 133.73, 133.99, 135.14, 135.26, 137.15, 137.41, 136.88, 136.6, 132.51, 143.34, 156.54, 160.65, 152.17, 142.2, 141.7, 135.53, 136.47, 132.07, 130.21, 131.08, 127.99, 134.71, 133.25, 130.63, 128.47, 119.5, 116.7, 113.5, 107.27, 112.93, 115.7, 116.67, 125.73, 129.3, 132.54, 134.37, 132.22, 129.04, 126.79, 130.04, 133.72, 133.76, 134.44, 132.38, 134.85, 132.66, 124.57, 123.37, 122.92, 131.53, 123.53], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT']}</t>
+        </is>
+      </c>
+      <c r="S18" t="n">
+        <v>123.53</v>
+      </c>
+      <c r="T18" t="n">
+        <v>7.04071535382952</v>
+      </c>
+      <c r="U18" t="n">
+        <v>22.19321356384988</v>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>COIN</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>55</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="E19" t="n">
+        <v>52</v>
+      </c>
+      <c r="F19" t="n">
+        <v>40</v>
+      </c>
+      <c r="G19" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-426</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="J19" t="n">
+        <v>-18.4</v>
+      </c>
+      <c r="K19" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="L19" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M19" t="n">
+        <v>29</v>
+      </c>
+      <c r="N19" t="n">
+        <v>3</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2</v>
+      </c>
+      <c r="P19" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [205.71, 197.22, 199.79, 196.52, 198.63, 193.23, 195.53, 203.32, 210.23, 202.29, 202.91, 197.5, 200.62, 181.04, 181.1, 173.38, 161.14, 160.79, 174.61, 172.99, 171.46, 174.79, 175.18, 175.09, 169.02, 167.85, 174.53, 184.41, 195.9, 199.83, 206.33, 211.63, 195.95, 206.24, 197.93, 199.77, 196.68, 194.1, 181.73, 187.77, 191.25, 202.99, 197.75, 197.96, 192.96, 201.16, 216.6, 207.64, 201.8, 212.01, 195.43, 189.44, 193.45, 191.29, 193.56, 184.99, 180.01, 173.78, 182.25, 189.03, 182.61, 173.99, 163.22, 164.13, 152.4, 162.11, 155.5, 153.97, 160.43, 159.78, 169.62, 169.27, 164.92, 163.26, 164.84, 158.18, 150.11, 142.52, 149.06, 151.65, 146.19, 159.24, 165.48, 168.87, 163.51, 159.36, 158.44, 159.07, 157.37, 161.5, 167.21, 160.49, 157.12, 160.43, 175.85, 166.12, 161.16, 158.29, 167.49, 167.9], 'signals': ['BUY', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+        </is>
+      </c>
+      <c r="S19" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="T19" t="n">
+        <v>9.024287632533483</v>
+      </c>
+      <c r="U19" t="n">
+        <v>17.05993620111895</v>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>NBIS</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>59</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0.191</v>
+      </c>
+      <c r="E20" t="n">
+        <v>62</v>
+      </c>
+      <c r="F20" t="n">
+        <v>70</v>
+      </c>
+      <c r="G20" t="n">
+        <v>65</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2039</v>
+      </c>
+      <c r="I20" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="J20" t="n">
+        <v>77.40000000000001</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-36.6</v>
+      </c>
+      <c r="L20" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M20" t="n">
+        <v>29</v>
+      </c>
+      <c r="N20" t="n">
+        <v>4</v>
+      </c>
+      <c r="O20" t="n">
+        <v>8</v>
+      </c>
+      <c r="P20" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [95.65, 89.33, 94.94, 96.43, 112.0, 108.04, 112.95, 129.85, 116.33, 118.56, 121.52, 117.62, 114.15, 114.91, 115.09, 105.97, 100.82, 92.26, 103.76, 101.95, 108.82, 112.54, 117.4, 125.0, 136.33, 144.97, 154.56, 161.94, 166.77, 165.34, 157.14, 159.16, 156.55, 156.14, 157.08, 147.16, 144.96, 135.51, 141.19, 138.23, 154.49, 176.42, 175.92, 195.09, 184.77, 177.05, 186.1, 179.11, 207.27, 221.15, 219.94, 199.86, 197.73, 191.82, 219.93, 214.77, 208.06, 208.37, 226.34, 231.09, 264.51, 260.58, 251.68, 259.67, 227.81, 218.0, 220.12, 211.69, 222.24, 232.36, 260.07, 265.1, 280.91, 286.69, 283.61, 275.25, 259.66, 256.63, 240.3, 261.15, 276.17, 229.18, 215.62, 213.02, 195.19, 216.48, 216.2, 219.65, 210.51, 194.09, 199.51, 171.77, 177.71, 182.62, 216.92, 218.16, 220.97, 187.77, 187.88, 169.69], 'signals': ['FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+        </is>
+      </c>
+      <c r="S20" t="n">
+        <v>169.69</v>
+      </c>
+      <c r="T20" t="n">
+        <v>22.5277829851423</v>
+      </c>
+      <c r="U20" t="n">
+        <v>19.93684147717601</v>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>JPM</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>61</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0.438</v>
+      </c>
+      <c r="E21" t="n">
+        <v>60</v>
+      </c>
+      <c r="F21" t="n">
+        <v>30</v>
+      </c>
+      <c r="G21" t="n">
+        <v>70</v>
+      </c>
+      <c r="H21" t="n">
+        <v>900</v>
+      </c>
+      <c r="I21" t="n">
+        <v>18</v>
+      </c>
+      <c r="J21" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-4.9</v>
+      </c>
+      <c r="L21" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M21" t="n">
+        <v>13</v>
+      </c>
+      <c r="N21" t="n">
+        <v>3</v>
+      </c>
+      <c r="O21" t="n">
+        <v>11</v>
+      </c>
+      <c r="P21" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [290.75, 286.71, 287.15, 285.97, 284.77, 280.19, 280.73, 283.43, 284.15, 284.99, 285.22, 283.82, 287.14, 289.61, 292.6, 288.87, 280.14, 281.06, 291.35, 292.56, 291.79, 294.12, 296.07, 306.59, 308.94, 308.48, 312.27, 309.72, 304.56, 308.56, 308.9, 315.57, 311.6, 311.62, 310.29, 306.9, 310.23, 310.05, 307.86, 311.83, 311.07, 306.27, 308.01, 313.49, 304.9, 300.75, 298.65, 303.51, 298.9, 298.57, 296.47, 299.38, 294.37, 300.63, 301.64, 305.01, 305.36, 297.94, 295.4, 297.97, 295.25, 299.61, 299.5, 309.5, 310.97, 309.71, 311.3, 307.75, 312.08, 319.28, 317.97, 329.65, 331.96, 323.76, 329.99, 332.64, 331.95, 333.62, 327.57, 327.91, 325.86, 332.57, 332.97, 337.72, 339.22, 330.62, 335.47, 336.47, 334.53, 342.89, 346.91, 343.15, 341.1, 338.87, 345.23, 348.21, 349.9, 353.21, 356.2, 357.31], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'SELL', 'BUY', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'BUY', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+        </is>
+      </c>
+      <c r="S21" t="n">
+        <v>357.31</v>
+      </c>
+      <c r="T21" t="n">
+        <v>7.437859671456473</v>
+      </c>
+      <c r="U21" t="n">
+        <v>15.77726239631315</v>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>GS</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>51</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UP  </t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="E22" t="n">
+        <v>60</v>
+      </c>
+      <c r="F22" t="n">
+        <v>80</v>
+      </c>
+      <c r="G22" t="n">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="H22" t="n">
+        <v>426</v>
+      </c>
+      <c r="I22" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="J22" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="K22" t="n">
+        <v>-15.7</v>
+      </c>
+      <c r="L22" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M22" t="n">
+        <v>4</v>
+      </c>
+      <c r="N22" t="n">
+        <v>4</v>
+      </c>
+      <c r="O22" t="n">
+        <v>11</v>
+      </c>
+      <c r="P22" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [831.79, 817.82, 828.38, 830.15, 820.15, 784.06, 778.78, 791.28, 803.5, 801.95, 805.95, 809.96, 827.62, 832.05, 838.15, 819.03, 799.37, 804.06, 842.28, 856.44, 859.25, 862.25, 860.36, 901.78, 899.75, 903.82, 886.88, 905.64, 895.54, 896.05, 921.89, 937.61, 922.48, 930.74, 927.21, 922.84, 933.7, 922.48, 901.63, 919.72, 919.66, 899.31, 914.86, 933.24, 921.81, 932.37, 940.71, 941.75, 951.23, 964.71, 944.31, 942.21, 924.66, 977.81, 983.83, 992.36, 990.16, 992.1, 1003.95, 1021.06, 1048.58, 1064.58, 1041.02, 1092.61, 1038.68, 1045.0, 1032.01, 1001.29, 1035.64, 1062.75, 1076.17, 1090.67, 1099.14, 1096.56, 1106.37, 1094.44, 1076.91, 1065.09, 1019.61, 1020.21, 1011.37, 1019.61, 1021.0, 1055.29, 1042.98, 1029.64, 1055.97, 1055.18, 1045.91, 1140.0, 1152.07, 1095.46, 1065.22, 1055.03, 1085.56, 1098.2, 1074.72, 1061.23, 1048.23, 1033.34], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'SELL', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD']}</t>
+        </is>
+      </c>
+      <c r="S22" t="n">
+        <v>1033.34</v>
+      </c>
+      <c r="T22" t="n">
+        <v>41.01998465401785</v>
+      </c>
+      <c r="U22" t="n">
+        <v>12.904634443049</v>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>52</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0.408</v>
+      </c>
+      <c r="E23" t="n">
+        <v>51</v>
+      </c>
+      <c r="F23" t="n">
+        <v>40</v>
+      </c>
+      <c r="G23" t="n">
+        <v>50</v>
+      </c>
+      <c r="H23" t="n">
+        <v>525</v>
+      </c>
+      <c r="I23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="J23" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-4.4</v>
+      </c>
+      <c r="L23" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M23" t="n">
+        <v>13</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2</v>
+      </c>
+      <c r="O23" t="n">
+        <v>13</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>7</v>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [319.14, 316.7, 315.32, 313.78, 308.32, 305.87, 306.5, 309.47, 307.82, 298.4, 299.09, 301.0, 303.81, 303.13, 304.28, 304.9, 294.91, 298.92, 301.61, 297.89, 300.18, 302.7, 301.92, 308.32, 307.65, 303.73, 308.75, 310.73, 315.26, 314.45, 316.36, 313.29, 309.3, 310.65, 308.24, 308.78, 309.01, 308.66, 334.17, 329.16, 327.35, 326.17, 321.36, 318.14, 320.62, 318.13, 323.19, 326.42, 320.31, 322.52, 325.75, 332.64, 329.91, 330.75, 331.12, 328.88, 326.48, 327.61, 324.95, 326.36, 322.77, 317.32, 312.4, 320.18, 323.57, 319.67, 325.05, 322.96, 319.05, 322.39, 323.82, 333.12, 330.38, 327.24, 326.6, 328.48, 332.23, 330.52, 336.23, 341.65, 343.09, 351.08, 362.13, 357.25, 352.2, 347.53, 348.2, 348.97, 357.75, 356.02, 355.14, 365.14, 358.56, 360.57, 355.82, 353.42, 351.6, 355.74, 362.53, 366.59], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'SELL', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT']}</t>
+        </is>
+      </c>
+      <c r="S23" t="n">
+        <v>366.59</v>
+      </c>
+      <c r="T23" t="n">
+        <v>7.151434762137277</v>
+      </c>
+      <c r="U23" t="n">
+        <v>36.99489980146108</v>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>54</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UP  </t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0.529</v>
+      </c>
+      <c r="E24" t="n">
+        <v>55</v>
+      </c>
+      <c r="F24" t="n">
+        <v>70</v>
+      </c>
+      <c r="G24" t="n">
+        <v>50</v>
+      </c>
+      <c r="H24" t="n">
+        <v>537</v>
+      </c>
+      <c r="I24" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="J24" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L24" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M24" t="n">
+        <v>8</v>
+      </c>
+      <c r="N24" t="n">
+        <v>1</v>
+      </c>
+      <c r="O24" t="n">
+        <v>18</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>18</v>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [522.88, 520.57, 515.97, 512.98, 502.29, 495.63, 496.3, 506.78, 504.86, 486.82, 489.48, 494.64, 498.69, 497.24, 501.06, 499.05, 482.6, 492.33, 497.97, 489.99, 491.77, 499.8, 496.59, 505.4, 502.73, 497.83, 507.73, 512.3, 519.09, 517.67, 520.43, 515.79, 510.49, 509.31, 501.54, 503.33, 505.58, 506.77, 524.35, 502.08, 494.63, 503.9, 496.25, 491.07, 500.1, 494.65, 496.98, 498.97, 489.82, 489.12, 493.37, 504.94, 498.86, 497.21, 498.78, 497.71, 492.18, 494.21, 492.92, 493.15, 494.42, 476.88, 470.76, 480.95, 490.26, 484.86, 494.41, 488.26, 485.7, 489.16, 489.82, 500.49, 492.16, 488.97, 483.28, 487.25, 493.58, 488.1, 498.18, 508.79, 512.74, 521.57, 538.49, 532.21, 530.73, 518.99, 523.2, 526.74, 537.7, 538.02, 535.21, 551.54, 543.6, 547.44, 538.3, 531.98, 530.29, 539.66, 551.71, 562.75], 'signals': ['FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+        </is>
+      </c>
+      <c r="S24" t="n">
+        <v>562.75</v>
+      </c>
+      <c r="T24" t="n">
+        <v>11.26356724330357</v>
+      </c>
+      <c r="U24" t="n">
+        <v>36.03977279178041</v>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>BAC</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>55</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UP  </t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0.584</v>
+      </c>
+      <c r="E25" t="n">
+        <v>62</v>
+      </c>
+      <c r="F25" t="n">
+        <v>60</v>
+      </c>
+      <c r="G25" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="H25" t="n">
+        <v>806</v>
+      </c>
+      <c r="I25" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="J25" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-11</v>
+      </c>
+      <c r="L25" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M25" t="n">
+        <v>79</v>
+      </c>
+      <c r="N25" t="n">
+        <v>2</v>
+      </c>
+      <c r="O25" t="n">
+        <v>17</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>9</v>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [49.27, 48.39, 47.65, 48.31, 48.27, 46.89, 46.48, 46.82, 47.04, 46.59, 46.77, 46.92, 47.27, 47.89, 48.5, 47.99, 46.73, 46.99, 48.5, 49.02, 49.12, 49.8, 50.02, 51.61, 52.44, 52.27, 53.07, 53.07, 54.04, 53.23, 53.63, 53.67, 53.2, 52.85, 52.2, 51.78, 52.36, 52.39, 52.61, 53.18, 52.96, 51.92, 52.85, 53.32, 52.48, 51.04, 50.29, 50.52, 49.58, 49.59, 49.51, 50.43, 50.44, 50.97, 51.22, 51.53, 51.93, 50.84, 50.51, 51.33, 51.24, 52.21, 52.13, 53.89, 53.83, 53.63, 54.42, 54.54, 55.16, 56.02, 55.87, 56.84, 56.53, 56.2, 57.37, 57.91, 57.73, 58.19, 57.88, 57.88, 56.98, 58.36, 58.73, 59.9, 59.86, 58.3, 59.25, 59.67, 59.5, 60.62, 61.59, 61.49, 61.27, 60.42, 61.22, 61.62, 61.28, 62.05, 62.13, 62.62], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'SELL', 'BUY', 'SELL']}</t>
+        </is>
+      </c>
+      <c r="S25" t="n">
+        <v>62.62</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.180000032697405</v>
+      </c>
+      <c r="U25" t="n">
+        <v>27.93985976792047</v>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>51</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>0.227</v>
+      </c>
+      <c r="E26" t="n">
+        <v>52</v>
+      </c>
+      <c r="F26" t="n">
+        <v>80</v>
+      </c>
+      <c r="G26" t="n">
+        <v>70</v>
+      </c>
+      <c r="H26" t="n">
+        <v>403</v>
+      </c>
+      <c r="I26" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="J26" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-22.8</v>
+      </c>
+      <c r="L26" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M26" t="n">
+        <v>23</v>
+      </c>
+      <c r="N26" t="n">
+        <v>4</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1</v>
+      </c>
+      <c r="P26" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [160.8, 158.54, 158.72, 159.02, 159.15, 152.7, 153.2, 154.02, 156.13, 157.22, 156.84, 159.73, 162.55, 164.08, 163.86, 161.47, 156.68, 156.66, 162.79, 164.38, 164.02, 164.75, 166.61, 174.12, 176.24, 175.72, 179.19, 181.36, 189.55, 185.3, 186.78, 188.64, 187.27, 188.99, 186.61, 186.04, 188.13, 188.31, 185.06, 189.55, 189.13, 186.98, 188.21, 192.29, 189.13, 192.03, 190.05, 190.83, 192.77, 193.47, 191.46, 191.64, 188.54, 196.69, 199.41, 199.93, 200.66, 200.51, 202.67, 206.86, 209.85, 213.8, 208.99, 217.08, 210.77, 211.08, 209.1, 205.53, 211.5, 212.87, 216.79, 219.62, 223.73, 221.95, 225.85, 224.79, 218.66, 219.83, 210.87, 210.56, 207.9, 210.7, 212.76, 220.88, 220.82, 216.88, 220.91, 221.06, 219.88, 226.42, 227.3, 217.17, 214.32, 209.79, 215.22, 217.3, 214.0, 213.31, 213.39, 210.42], 'signals': ['BUY', 'SELL', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+        </is>
+      </c>
+      <c r="S26" t="n">
+        <v>210.42</v>
+      </c>
+      <c r="T26" t="n">
+        <v>7.563363625770892</v>
+      </c>
+      <c r="U26" t="n">
+        <v>12.33764110610651</v>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>LLY</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>59</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UP  </t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0.549</v>
+      </c>
+      <c r="E27" t="n">
+        <v>50</v>
+      </c>
+      <c r="F27" t="n">
+        <v>40</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>317</v>
+      </c>
+      <c r="I27" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="J27" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-18.1</v>
+      </c>
+      <c r="L27" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M27" t="n">
+        <v>4</v>
+      </c>
+      <c r="N27" t="n">
+        <v>1</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1</v>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [981.57, 988.63, 1006.66, 999.63, 998.12, 975.57, 983.39, 987.42, 928.75, 916.47, 915.92, 905.14, 908.99, 901.47, 914.74, 895.46, 876.73, 885.11, 918.19, 952.88, 933.97, 925.47, 929.49, 951.66, 953.55, 937.86, 927.95, 920.91, 903.47, 902.44, 925.44, 918.32, 901.47, 919.9, 916.07, 882.44, 866.78, 872.5, 849.75, 932.99, 961.67, 966.27, 987.17, 985.35, 973.28, 946.82, 965.33, 988.17, 1014.0, 1004.97, 1004.92, 988.09, 1021.41, 1018.87, 1041.65, 1065.0, 1064.74, 1082.92, 1126.8, 1105.0, 1082.2, 1064.15, 1078.78, 1125.27, 1131.42, 1149.15, 1144.68, 1136.37, 1160.95, 1133.0, 1129.35, 1122.5, 1112.0, 1098.57, 1102.08, 1107.08, 1117.26, 1127.69, 1208.12, 1229.93, 1199.43, 1191.74, 1213.91, 1200.06, 1235.56, 1215.83, 1216.95, 1188.58, 1181.87, 1152.54, 1156.63, 1169.17, 1179.11, 1146.9, 1175.41, 1163.01, 1185.87, 1196.03, 1197.53, 1220.66], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+        </is>
+      </c>
+      <c r="S27" t="n">
+        <v>1220.66</v>
+      </c>
+      <c r="T27" t="n">
+        <v>34.21641322544643</v>
+      </c>
+      <c r="U27" t="n">
+        <v>15.94042271560643</v>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>UNH</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>50</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UP  </t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="E28" t="n">
+        <v>49</v>
+      </c>
+      <c r="F28" t="n">
+        <v>20</v>
+      </c>
+      <c r="G28" t="n">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="H28" t="n">
+        <v>729</v>
+      </c>
+      <c r="I28" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="J28" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="K28" t="n">
+        <v>-35.9</v>
+      </c>
+      <c r="L28" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M28" t="n">
+        <v>11</v>
+      </c>
+      <c r="N28" t="n">
+        <v>3</v>
+      </c>
+      <c r="O28" t="n">
+        <v>8</v>
+      </c>
+      <c r="P28" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [284.92, 282.66, 283.55, 280.74, 283.63, 275.48, 280.49, 283.87, 285.94, 282.72, 278.85, 274.02, 268.01, 270.73, 269.01, 266.53, 257.55, 260.3, 269.05, 272.42, 275.69, 279.76, 305.98, 304.24, 305.17, 302.6, 311.22, 312.41, 312.27, 314.6, 322.79, 321.64, 344.05, 351.51, 352.55, 352.9, 352.68, 364.69, 368.63, 368.38, 366.69, 368.64, 361.8, 365.19, 367.64, 377.82, 382.26, 394.14, 398.88, 396.82, 391.61, 388.91, 387.03, 381.12, 380.31, 386.26, 374.72, 381.83, 380.36, 378.15, 377.7, 375.77, 374.86, 394.22, 397.2, 404.26, 410.65, 405.15, 403.25, 406.2, 411.04, 407.65, 399.53, 400.96, 406.68, 409.25, 405.8, 415.53, 427.89, 419.82, 415.63, 426.54, 425.36, 417.99, 428.19, 425.6, 431.68, 424.62, 429.09, 425.19, 418.52, 423.38, 426.09, 421.55, 436.35, 431.31, 423.56, 420.74, 417.64, 428.79], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+        </is>
+      </c>
+      <c r="S28" t="n">
+        <v>428.79</v>
+      </c>
+      <c r="T28" t="n">
+        <v>13.48285348074777</v>
+      </c>
+      <c r="U28" t="n">
+        <v>34.94767114622746</v>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>JNJ</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>52</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>0.474</v>
+      </c>
+      <c r="E29" t="n">
+        <v>59</v>
+      </c>
+      <c r="F29" t="n">
+        <v>60</v>
+      </c>
+      <c r="G29" t="n">
+        <v>60</v>
+      </c>
+      <c r="H29" t="n">
+        <v>488</v>
+      </c>
+      <c r="I29" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="J29" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="K29" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="L29" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M29" t="n">
+        <v>18</v>
+      </c>
+      <c r="N29" t="n">
+        <v>3</v>
+      </c>
+      <c r="O29" t="n">
+        <v>6</v>
+      </c>
+      <c r="P29" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>3</v>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [238.26, 239.03, 241.2, 242.32, 241.6, 240.66, 240.14, 241.8, 236.75, 235.92, 236.24, 234.02, 234.07, 233.92, 238.56, 237.87, 239.08, 241.1, 243.04, 242.72, 241.65, 239.59, 237.05, 239.92, 239.93, 237.1, 236.6, 238.73, 237.31, 233.2, 232.84, 229.37, 224.87, 224.81, 229.33, 226.2, 224.05, 226.49, 226.05, 228.54, 225.89, 222.92, 224.26, 223.34, 221.24, 220.05, 220.16, 222.98, 229.1, 229.48, 225.41, 227.61, 228.68, 228.01, 230.4, 233.0, 230.18, 231.29, 230.8, 225.33, 223.51, 222.89, 223.24, 228.17, 232.77, 232.16, 237.0, 238.49, 238.33, 240.87, 235.66, 235.18, 234.2, 228.39, 231.29, 239.08, 241.0, 244.88, 254.66, 258.51, 253.97, 253.98, 263.04, 259.33, 267.24, 263.4, 259.1, 256.98, 257.77, 253.85, 247.02, 249.97, 253.04, 248.82, 250.61, 255.63, 259.27, 263.4, 265.95, 266.73], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD']}</t>
+        </is>
+      </c>
+      <c r="S29" t="n">
+        <v>266.73</v>
+      </c>
+      <c r="T29" t="n">
+        <v>6.252138410295759</v>
+      </c>
+      <c r="U29" t="n">
+        <v>19.45697595859658</v>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>ABBV</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>57</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UP  </t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0.673</v>
+      </c>
+      <c r="E30" t="n">
+        <v>51</v>
+      </c>
+      <c r="F30" t="n">
+        <v>40</v>
+      </c>
+      <c r="G30" t="n">
+        <v>55</v>
+      </c>
+      <c r="H30" t="n">
+        <v>681</v>
+      </c>
+      <c r="I30" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="J30" t="n">
+        <v>15</v>
+      </c>
+      <c r="K30" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="L30" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M30" t="n">
+        <v>18</v>
+      </c>
+      <c r="N30" t="n">
+        <v>2</v>
+      </c>
+      <c r="O30" t="n">
+        <v>14</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>8</v>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [228.81, 226.6, 223.98, 223.55, 224.21, 221.94, 216.33, 218.08, 216.41, 205.17, 203.09, 201.95, 201.81, 202.07, 204.02, 207.9, 206.21, 209.87, 214.18, 211.7, 205.66, 203.54, 203.23, 208.37, 209.16, 204.77, 203.32, 207.06, 206.95, 207.51, 206.91, 202.27, 203.67, 199.08, 199.53, 197.31, 195.99, 196.29, 202.45, 209.83, 205.14, 206.69, 204.65, 203.58, 201.28, 200.13, 201.35, 206.39, 207.03, 209.28, 208.9, 207.93, 212.25, 210.8, 212.98, 214.18, 211.61, 213.88, 217.08, 216.18, 211.43, 213.88, 215.6, 223.35, 225.62, 221.49, 223.83, 223.36, 223.18, 226.12, 220.02, 220.9, 219.67, 214.96, 228.38, 233.1, 233.23, 241.42, 251.56, 252.51, 249.86, 249.29, 259.22, 252.96, 252.85, 250.95, 248.14, 246.33, 246.25, 243.05, 244.11, 254.39, 254.49, 253.38, 256.1, 253.3, 256.92, 259.36, 256.91, 263.2], 'signals': ['FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'SELL', 'BUY', 'SELL', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT']}</t>
+        </is>
+      </c>
+      <c r="S30" t="n">
+        <v>263.2</v>
+      </c>
+      <c r="T30" t="n">
+        <v>5.943890991012275</v>
+      </c>
+      <c r="U30" t="n">
+        <v>36.32423643145558</v>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>MRK</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>55</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UP  </t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="E31" t="n">
+        <v>55</v>
+      </c>
+      <c r="F31" t="n">
+        <v>60</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1078</v>
+      </c>
+      <c r="I31" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="J31" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="K31" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L31" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M31" t="n">
+        <v>37</v>
+      </c>
+      <c r="N31" t="n">
+        <v>5</v>
+      </c>
+      <c r="O31" t="n">
+        <v>6</v>
+      </c>
+      <c r="P31" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>2</v>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [114.39, 114.12, 115.42, 115.4, 114.53, 114.24, 113.94, 114.61, 115.04, 113.68, 113.38, 113.36, 114.85, 115.54, 118.52, 118.08, 118.78, 117.26, 119.43, 119.98, 120.01, 119.99, 118.43, 122.3, 121.8, 120.55, 119.29, 119.1, 117.06, 114.64, 118.22, 116.26, 111.76, 112.08, 113.8, 111.1, 109.44, 109.24, 110.16, 108.4, 111.36, 112.3, 112.34, 112.75, 111.5, 110.58, 110.49, 111.57, 112.64, 112.6, 110.58, 111.76, 113.42, 112.19, 115.05, 121.54, 118.87, 119.38, 119.03, 117.87, 114.35, 114.82, 113.88, 119.4, 119.93, 118.67, 118.75, 118.24, 119.9, 118.2, 114.9, 115.17, 115.44, 113.87, 115.48, 119.6, 120.6, 125.45, 128.66, 129.38, 128.5, 125.37, 129.56, 126.78, 128.86, 125.99, 125.07, 123.54, 124.03, 120.78, 123.61, 127.63, 127.5, 124.4, 126.26, 127.47, 130.48, 131.07, 130.76, 131.82], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+        </is>
+      </c>
+      <c r="S31" t="n">
+        <v>131.82</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3.351428440638951</v>
+      </c>
+      <c r="U31" t="n">
+        <v>17.87088936336508</v>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>61</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UP  </t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>0.619</v>
+      </c>
+      <c r="E32" t="n">
+        <v>60</v>
+      </c>
+      <c r="F32" t="n">
+        <v>20</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>-23</v>
+      </c>
+      <c r="I32" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="J32" t="n">
+        <v>-24.2</v>
+      </c>
+      <c r="K32" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="L32" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M32" t="n">
+        <v>16</v>
+      </c>
+      <c r="N32" t="n">
+        <v>5</v>
+      </c>
+      <c r="O32" t="n">
+        <v>9</v>
+      </c>
+      <c r="P32" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [405.55, 396.73, 398.68, 399.24, 407.82, 395.01, 391.2, 395.56, 399.27, 392.78, 380.3, 367.96, 380.85, 383.03, 385.95, 372.11, 361.83, 355.28, 371.75, 381.26, 360.59, 352.82, 346.65, 343.25, 345.62, 348.95, 352.42, 364.2, 391.95, 388.9, 400.62, 392.5, 386.42, 387.51, 373.72, 376.3, 378.67, 376.02, 372.8, 381.63, 390.82, 392.51, 389.37, 398.73, 411.79, 428.35, 445.0, 433.45, 445.27, 443.3, 422.24, 409.99, 404.11, 417.26, 417.85, 426.01, 433.59, 440.36, 442.1, 435.79, 415.88, 423.74, 423.7, 418.45, 391.0, 408.95, 396.68, 381.59, 399.15, 406.43, 411.15, 404.66, 396.38, 400.49, 405.05, 381.61, 375.53, 375.12, 379.71, 411.84, 420.6, 425.3, 393.45, 419.77, 402.9, 394.06, 406.55, 407.76, 394.76, 396.18, 394.46, 391.06, 380.84, 369.57, 378.93, 374.01, 319.69, 313.03, 309.22, 307.44], 'signals': ['FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+        </is>
+      </c>
+      <c r="S32" t="n">
+        <v>307.44</v>
+      </c>
+      <c r="T32" t="n">
+        <v>16.27285766601562</v>
+      </c>
+      <c r="U32" t="n">
+        <v>44.81763149270454</v>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>HD</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>51</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>0.237</v>
+      </c>
+      <c r="E33" t="n">
+        <v>61</v>
+      </c>
+      <c r="F33" t="n">
+        <v>50</v>
+      </c>
+      <c r="G33" t="n">
+        <v>25</v>
+      </c>
+      <c r="H33" t="n">
+        <v>67</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J33" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="K33" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L33" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M33" t="n">
+        <v>14</v>
+      </c>
+      <c r="N33" t="n">
+        <v>4</v>
+      </c>
+      <c r="O33" t="n">
+        <v>3</v>
+      </c>
+      <c r="P33" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [356.6, 352.9, 348.6, 352.14, 345.92, 336.41, 336.51, 340.03, 338.89, 328.47, 325.77, 318.36, 328.44, 328.45, 330.03, 325.98, 319.26, 321.09, 326.44, 327.11, 319.24, 324.22, 316.4, 333.66, 337.05, 334.83, 338.62, 340.16, 336.39, 334.64, 346.8, 348.38, 341.36, 336.97, 337.63, 333.39, 329.83, 326.61, 320.41, 326.35, 321.47, 310.09, 313.07, 320.64, 320.24, 315.09, 309.08, 308.15, 300.3, 302.08, 295.3, 297.58, 300.19, 308.27, 311.44, 310.74, 308.23, 315.48, 318.82, 314.78, 308.38, 309.2, 310.64, 309.95, 310.78, 309.71, 321.33, 318.92, 326.01, 328.39, 329.82, 337.09, 327.48, 334.28, 326.62, 324.45, 342.86, 345.0, 348.86, 350.81, 352.68, 350.84, 357.9, 350.65, 345.21, 336.21, 338.73, 343.3, 337.11, 337.74, 341.44, 348.02, 338.87, 333.04, 331.6, 331.45, 324.71, 332.98, 336.09, 344.47], 'signals': ['BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+        </is>
+      </c>
+      <c r="S33" t="n">
+        <v>344.47</v>
+      </c>
+      <c r="T33" t="n">
+        <v>8.792144775390625</v>
+      </c>
+      <c r="U33" t="n">
+        <v>18.53730862647758</v>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>MCD</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>65</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UP  </t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>0.623</v>
+      </c>
+      <c r="E34" t="n">
+        <v>65</v>
+      </c>
+      <c r="F34" t="n">
+        <v>50</v>
+      </c>
+      <c r="G34" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="H34" t="n">
+        <v>-324</v>
+      </c>
+      <c r="I34" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="J34" t="n">
+        <v>-16.1</v>
+      </c>
+      <c r="K34" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="L34" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M34" t="n">
+        <v>18</v>
+      </c>
+      <c r="N34" t="n">
+        <v>2</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>1</v>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [325.24, 325.85, 328.57, 325.73, 323.02, 321.73, 324.26, 324.45, 324.1, 313.6, 307.49, 306.77, 306.39, 305.77, 309.6, 306.85, 303.84, 306.45, 308.7, 305.22, 305.07, 307.67, 302.8, 304.94, 307.46, 303.62, 302.46, 301.18, 304.2, 304.89, 309.26, 304.87, 299.81, 298.05, 300.49, 297.34, 288.26, 290.42, 288.13, 291.61, 284.71, 282.19, 283.25, 282.19, 281.79, 273.89, 272.75, 272.99, 273.84, 273.12, 274.53, 280.57, 278.91, 278.38, 282.27, 280.37, 277.38, 279.03, 276.1, 277.32, 274.25, 276.36, 273.29, 272.72, 279.84, 277.78, 282.25, 282.52, 284.77, 284.81, 286.12, 287.93, 283.82, 278.61, 270.1, 271.66, 273.88, 264.54, 269.76, 267.18, 270.31, 269.43, 280.63, 279.5, 282.21, 278.25, 276.49, 274.6, 272.61, 268.94, 264.95, 273.46, 267.71, 267.64, 263.91, 263.57, 262.8, 264.76, 270.67, 273.02], 'signals': ['BUY', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+        </is>
+      </c>
+      <c r="S34" t="n">
+        <v>273.02</v>
+      </c>
+      <c r="T34" t="n">
+        <v>5.601425170898438</v>
+      </c>
+      <c r="U34" t="n">
+        <v>15.24533523291238</v>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>NKE</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>61</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>0.197</v>
+      </c>
+      <c r="E35" t="n">
+        <v>58</v>
+      </c>
+      <c r="F35" t="n">
+        <v>50</v>
+      </c>
+      <c r="G35" t="n">
+        <v>30</v>
+      </c>
+      <c r="H35" t="n">
+        <v>90</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J35" t="n">
+        <v>-25.1</v>
+      </c>
+      <c r="K35" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="L35" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M35" t="n">
+        <v>116</v>
+      </c>
+      <c r="N35" t="n">
+        <v>3</v>
+      </c>
+      <c r="O35" t="n">
+        <v>12</v>
+      </c>
+      <c r="P35" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [57.51, 56.5, 56.03, 55.58, 55.21, 53.65, 53.5, 54.3, 54.63, 53.0, 52.97, 51.91, 52.24, 53.02, 52.51, 51.61, 50.91, 50.79, 52.35, 44.23, 43.8, 43.64, 42.31, 42.75, 43.61, 42.24, 42.53, 43.81, 45.04, 45.29, 45.62, 46.07, 45.98, 45.27, 44.38, 44.29, 44.74, 44.63, 44.0, 43.97, 44.01, 42.71, 42.68, 43.49, 44.02, 43.75, 42.01, 41.97, 41.96, 41.65, 41.51, 42.19, 42.04, 43.8, 44.0, 44.27, 44.54, 45.57, 46.95, 45.82, 45.93, 43.73, 43.81, 43.62, 42.98, 43.23, 44.65, 43.96, 45.96, 44.93, 45.2, 45.04, 44.19, 45.2, 43.19, 42.38, 41.82, 40.9, 40.75, 41.48, 41.05, 43.06, 44.09, 43.34, 43.21, 42.89, 42.78, 44.37, 43.76, 42.86, 42.77, 44.57, 43.76, 43.47, 42.96, 42.21, 40.99, 41.7, 42.14, 43.05], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+        </is>
+      </c>
+      <c r="S35" t="n">
+        <v>43.05</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1.330714634486607</v>
+      </c>
+      <c r="U35" t="n">
+        <v>16.83385087045296</v>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>COST</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>53</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="E36" t="n">
+        <v>52</v>
+      </c>
+      <c r="F36" t="n">
+        <v>90</v>
+      </c>
+      <c r="G36" t="n">
+        <v>60</v>
+      </c>
+      <c r="H36" t="n">
+        <v>61</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J36" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L36" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M36" t="n">
+        <v>5</v>
+      </c>
+      <c r="N36" t="n">
+        <v>2</v>
+      </c>
+      <c r="O36" t="n">
+        <v>3</v>
+      </c>
+      <c r="P36" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>2</v>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [979.59, 995.07, 1002.25, 994.33, 989.22, 1000.28, 1005.37, 998.7, 993.14, 976.95, 971.82, 969.38, 962.8, 970.87, 971.9, 976.68, 980.87, 993.56, 993.41, 993.54, 1011.88, 1015.46, 1010.14, 1027.14, 1028.9, 995.44, 977.87, 971.84, 981.76, 984.21, 996.86, 994.81, 1002.76, 1000.65, 1011.3, 1008.08, 994.98, 990.98, 995.64, 1011.45, 1010.09, 1011.18, 1014.81, 994.17, 1010.45, 1007.19, 997.88, 1020.26, 1031.44, 1039.6, 1047.28, 1074.76, 1092.58, 1072.31, 1048.78, 1026.61, 1001.34, 1002.1, 993.62, 954.8, 944.61, 952.76, 960.3, 970.81, 970.33, 973.2, 967.05, 981.81, 974.14, 980.79, 977.9, 985.11, 964.06, 949.94, 949.84, 956.16, 959.56, 940.74, 951.03, 945.18, 933.98, 923.2, 950.16, 948.74, 946.0, 951.62, 911.52, 914.8, 924.96, 920.29, 915.09, 944.07, 939.38, 934.31, 927.74, 925.84, 924.59, 935.03, 951.58, 966.58], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+        </is>
+      </c>
+      <c r="S36" t="n">
+        <v>966.58</v>
+      </c>
+      <c r="T36" t="n">
+        <v>19.96724082523999</v>
+      </c>
+      <c r="U36" t="n">
+        <v>13.10675445852723</v>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>WMT</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>52</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UP  </t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>0.569</v>
+      </c>
+      <c r="E37" t="n">
+        <v>59</v>
+      </c>
+      <c r="F37" t="n">
+        <v>40</v>
+      </c>
+      <c r="G37" t="n">
+        <v>55</v>
+      </c>
+      <c r="H37" t="n">
+        <v>52</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1</v>
+      </c>
+      <c r="J37" t="n">
+        <v>-7.9</v>
+      </c>
+      <c r="K37" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="L37" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M37" t="n">
+        <v>44</v>
+      </c>
+      <c r="N37" t="n">
+        <v>4</v>
+      </c>
+      <c r="O37" t="n">
+        <v>7</v>
+      </c>
+      <c r="P37" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [122.82, 123.31, 123.85, 124.63, 123.0, 124.84, 126.02, 125.49, 124.59, 121.5, 120.61, 118.79, 120.49, 121.82, 122.83, 121.95, 122.66, 123.26, 124.04, 124.5, 125.55, 126.55, 122.26, 127.02, 128.88, 126.53, 124.33, 124.81, 124.52, 124.58, 127.26, 127.68, 129.35, 129.73, 131.78, 129.67, 127.35, 127.35, 127.77, 131.68, 131.35, 130.08, 130.54, 129.83, 129.95, 130.43, 127.59, 130.35, 131.47, 132.46, 131.45, 133.34, 134.2, 130.85, 121.34, 120.27, 118.57, 118.54, 118.9, 115.75, 114.6, 113.06, 116.89, 117.74, 118.88, 119.83, 118.88, 120.59, 120.5, 121.04, 120.82, 121.03, 118.13, 117.18, 117.18, 119.42, 119.0, 115.78, 115.69, 114.6, 113.26, 108.82, 111.84, 110.65, 111.54, 113.1, 112.21, 113.9, 114.78, 113.7, 112.53, 114.95, 114.24, 112.2, 110.39, 109.33, 108.4, 109.47, 111.74, 113.1], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+        </is>
+      </c>
+      <c r="S37" t="n">
+        <v>113.1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2.587142399379185</v>
+      </c>
+      <c r="U37" t="n">
+        <v>17.72428540632053</v>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>56</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UP  </t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>0.611</v>
+      </c>
+      <c r="E38" t="n">
+        <v>56</v>
+      </c>
+      <c r="F38" t="n">
+        <v>40</v>
+      </c>
+      <c r="G38" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="H38" t="n">
+        <v>-35</v>
+      </c>
+      <c r="I38" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="J38" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L38" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M38" t="n">
+        <v>33</v>
+      </c>
+      <c r="N38" t="n">
+        <v>2</v>
+      </c>
+      <c r="O38" t="n">
+        <v>13</v>
+      </c>
+      <c r="P38" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [151.71, 151.35, 152.92, 153.7, 151.05, 148.27, 148.42, 149.86, 149.23, 144.53, 142.69, 142.14, 141.85, 141.04, 141.79, 140.31, 140.59, 142.57, 142.3, 141.95, 141.0, 140.65, 139.2, 142.75, 144.49, 143.01, 141.45, 142.24, 141.25, 140.99, 144.75, 142.35, 140.21, 140.73, 143.55, 147.08, 147.3, 148.06, 145.37, 146.0, 146.17, 142.36, 143.83, 146.8, 144.98, 145.34, 142.3, 142.84, 141.19, 141.65, 140.52, 141.33, 140.25, 141.38, 142.34, 143.37, 141.9, 146.4, 144.83, 142.5, 139.24, 139.78, 139.15, 139.74, 145.45, 144.02, 147.57, 147.95, 147.24, 148.5, 149.35, 151.36, 149.44, 149.27, 146.59, 149.74, 150.91, 147.4, 147.92, 147.35, 145.55, 146.34, 150.29, 148.2, 151.62, 147.3, 145.76, 145.95, 147.27, 145.0, 146.95, 150.38, 148.87, 148.02, 147.0, 148.02, 145.88, 147.41, 148.63, 148.88], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'BUY', 'SELL', 'BUY', 'SELL', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD']}</t>
+        </is>
+      </c>
+      <c r="S38" t="n">
+        <v>148.88</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3.101778683973277</v>
+      </c>
+      <c r="U38" t="n">
+        <v>13.82053472887988</v>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>KO</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>59</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UP  </t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>0.707</v>
+      </c>
+      <c r="E39" t="n">
+        <v>60</v>
+      </c>
+      <c r="F39" t="n">
+        <v>10</v>
+      </c>
+      <c r="G39" t="n">
+        <v>50</v>
+      </c>
+      <c r="H39" t="n">
+        <v>693</v>
+      </c>
+      <c r="I39" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="J39" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="K39" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="L39" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M39" t="n">
+        <v>56</v>
+      </c>
+      <c r="N39" t="n">
+        <v>4</v>
+      </c>
+      <c r="O39" t="n">
+        <v>7</v>
+      </c>
+      <c r="P39" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [76.01, 76.02, 76.77, 76.85, 76.61, 76.59, 76.84, 77.32, 77.08, 75.48, 75.07, 74.27, 74.63, 74.19, 74.77, 74.21, 75.22, 75.78, 75.56, 75.59, 76.23, 76.72, 75.42, 76.79, 77.68, 76.97, 75.92, 75.41, 74.83, 74.7, 75.25, 75.0, 74.22, 74.15, 75.79, 76.14, 74.96, 77.85, 78.36, 78.25, 78.08, 77.69, 77.98, 78.72, 77.93, 77.92, 78.16, 79.52, 79.75, 79.93, 80.3, 80.68, 81.39, 81.03, 80.65, 80.96, 79.94, 81.1, 79.89, 78.5, 78.14, 77.91, 78.25, 76.33, 78.97, 79.03, 80.82, 83.05, 82.0, 82.09, 80.91, 80.28, 79.93, 79.39, 79.53, 80.31, 80.6, 80.42, 82.63, 82.65, 81.27, 81.29, 84.14, 82.96, 84.05, 83.4, 82.63, 83.49, 84.25, 83.08, 82.45, 84.92, 81.56, 82.12, 81.97, 82.2, 81.17, 82.25, 84.07, 88.27], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL']}</t>
+        </is>
+      </c>
+      <c r="S39" t="n">
+        <v>88.27</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1.992856161934989</v>
+      </c>
+      <c r="U39" t="n">
+        <v>17.47863805298332</v>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>XOM</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>56</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="E40" t="n">
+        <v>54</v>
+      </c>
+      <c r="F40" t="n">
+        <v>90</v>
+      </c>
+      <c r="G40" t="n">
+        <v>50</v>
+      </c>
+      <c r="H40" t="n">
+        <v>105</v>
+      </c>
+      <c r="I40" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J40" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="K40" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="L40" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M40" t="n">
+        <v>32</v>
+      </c>
+      <c r="N40" t="n">
+        <v>1</v>
+      </c>
+      <c r="O40" t="n">
+        <v>19</v>
+      </c>
+      <c r="P40" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>19</v>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [149.74, 150.19, 149.43, 147.13, 150.56, 152.49, 155.07, 156.17, 157.74, 156.53, 157.09, 158.59, 160.04, 164.27, 162.16, 164.31, 169.84, 170.31, 168.52, 159.7, 159.61, 162.27, 162.8, 155.17, 153.99, 151.48, 151.61, 148.23, 148.01, 150.96, 145.45, 146.68, 147.36, 148.49, 149.52, 147.91, 147.19, 149.54, 153.63, 153.29, 151.72, 152.65, 153.84, 147.69, 145.59, 143.6, 148.67, 149.61, 150.55, 151.75, 157.92, 160.49, 162.55, 156.28, 155.29, 154.92, 149.81, 147.9, 146.96, 145.26, 149.38, 149.56, 152.53, 152.04, 149.92, 151.75, 148.91, 150.62, 146.6, 147.01, 140.92, 141.86, 140.74, 137.81, 138.47, 139.73, 136.9, 137.55, 136.54, 136.06, 136.72, 136.28, 137.09, 136.44, 141.69, 141.13, 137.46, 138.88, 144.51, 145.09, 144.51, 145.95, 147.36, 148.36, 151.71, 154.45, 156.89, 156.94, 154.77, 153.04], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+        </is>
+      </c>
+      <c r="S40" t="n">
+        <v>153.04</v>
+      </c>
+      <c r="T40" t="n">
+        <v>3.500714983258928</v>
+      </c>
+      <c r="U40" t="n">
+        <v>49.80775434879472</v>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>CVX</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>52</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UP  </t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="E41" t="n">
+        <v>52</v>
+      </c>
+      <c r="F41" t="n">
+        <v>70</v>
+      </c>
+      <c r="G41" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="H41" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I41" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="J41" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="K41" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="L41" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M41" t="n">
+        <v>26</v>
+      </c>
+      <c r="N41" t="n">
+        <v>3</v>
+      </c>
+      <c r="O41" t="n">
+        <v>5</v>
+      </c>
+      <c r="P41" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [188.18, 188.22, 187.72, 184.6, 190.05, 195.18, 195.03, 195.05, 196.17, 196.81, 199.61, 199.9, 203.35, 204.91, 203.29, 205.9, 209.23, 208.8, 205.02, 195.62, 197.16, 197.06, 199.71, 191.14, 188.63, 186.84, 190.04, 185.32, 183.23, 186.44, 182.32, 181.59, 184.29, 184.63, 185.9, 183.53, 183.1, 186.65, 190.48, 191.56, 188.9, 190.53, 190.89, 183.48, 180.84, 179.97, 183.06, 184.26, 184.31, 184.95, 189.37, 194.34, 197.25, 191.33, 191.01, 191.43, 184.71, 182.4, 183.03, 182.46, 185.83, 187.55, 189.71, 188.35, 187.31, 189.24, 186.76, 189.8, 185.82, 187.22, 180.4, 180.11, 177.58, 173.63, 175.06, 175.98, 171.45, 172.24, 171.06, 168.47, 165.76, 165.69, 169.2, 168.1, 174.01, 175.97, 174.05, 176.4, 182.2, 181.76, 181.6, 183.86, 187.38, 189.71, 191.07, 192.98, 194.42, 194.79, 190.0, 187.58], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+        </is>
+      </c>
+      <c r="S41" t="n">
+        <v>187.58</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3.797142028808594</v>
+      </c>
+      <c r="U41" t="n">
+        <v>54.57269929944235</v>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>60</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UP  </t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="E42" t="n">
+        <v>58</v>
+      </c>
+      <c r="F42" t="n">
+        <v>40</v>
+      </c>
+      <c r="G42" t="n">
+        <v>55</v>
+      </c>
+      <c r="H42" t="n">
+        <v>729</v>
+      </c>
+      <c r="I42" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="J42" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="K42" t="n">
+        <v>-4.9</v>
+      </c>
+      <c r="L42" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M42" t="n">
+        <v>5</v>
+      </c>
+      <c r="N42" t="n">
+        <v>2</v>
+      </c>
+      <c r="O42" t="n">
+        <v>17</v>
+      </c>
+      <c r="P42" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>9</v>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [703.43, 678.35, 702.18, 713.99, 704.94, 698.06, 691.39, 697.16, 699.37, 691.02, 686.07, 678.33, 699.07, 713.94, 716.34, 700.55, 692.79, 664.93, 705.8, 727.58, 714.53, 718.54, 721.72, 768.69, 784.12, 787.7, 788.76, 791.27, 767.28, 769.76, 791.67, 796.92, 798.97, 807.37, 833.69, 829.25, 827.26, 816.36, 808.55, 888.46, 888.02, 873.16, 902.92, 925.21, 894.03, 895.79, 925.07, 910.45, 900.63, 918.52, 886.67, 862.35, 858.56, 870.94, 864.35, 878.26, 906.87, 908.25, 886.03, 874.25, 863.76, 908.13, 924.47, 938.74, 902.61, 913.94, 913.01, 854.57, 895.97, 908.88, 932.2, 943.71, 954.15, 983.99, 1020.39, 982.42, 992.61, 1055.05, 995.62, 1031.28, 1062.93, 989.57, 961.75, 968.12, 938.38, 946.32, 936.65, 950.65, 929.75, 931.61, 912.61, 875.55, 878.65, 864.3, 889.97, 889.31, 894.54, 888.73, 873.28, 840.85], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+        </is>
+      </c>
+      <c r="S42" t="n">
+        <v>840.85</v>
+      </c>
+      <c r="T42" t="n">
+        <v>38.7696911856788</v>
+      </c>
+      <c r="U42" t="n">
+        <v>35.82781971210662</v>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>HON</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>76</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>0.446</v>
+      </c>
+      <c r="E43" t="n">
+        <v>54</v>
+      </c>
+      <c r="F43" t="n">
+        <v>40</v>
+      </c>
+      <c r="G43" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="H43" t="n">
+        <v>750</v>
+      </c>
+      <c r="I43" t="n">
+        <v>15</v>
+      </c>
+      <c r="J43" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="K43" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="L43" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M43" t="n">
+        <v>20</v>
+      </c>
+      <c r="N43" t="n">
+        <v>4</v>
+      </c>
+      <c r="O43" t="n">
+        <v>12</v>
+      </c>
+      <c r="P43" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [248.64, 245.42, 247.81, 250.96, 249.74, 243.44, 244.59, 244.6, 241.38, 239.81, 238.89, 231.03, 232.61, 231.11, 235.51, 234.86, 232.72, 233.1, 235.76, 238.02, 239.32, 238.03, 233.47, 242.47, 246.22, 245.16, 243.69, 243.28, 242.18, 239.25, 243.6, 239.63, 231.78, 229.44, 223.56, 222.34, 221.18, 222.09, 219.35, 223.55, 221.65, 218.61, 218.06, 226.19, 225.37, 222.29, 228.54, 227.94, 227.34, 227.09, 223.64, 227.82, 227.74, 227.99, 234.71, 239.04, 243.02, 242.84, 244.36, 249.46, 248.08, 246.7, 234.15, 228.25, 224.4, 222.13, 226.22, 215.92, 229.81, 231.05, 238.5, 240.68, 239.76, 240.18, 239.23, 233.21, 238.51, 242.52, 243.53, 227.8, 223.9, 221.75, 229.86, 231.18, 225.05, 220.36, 223.42, 226.42, 222.25, 222.68, 222.84, 226.33, 225.02, 226.18, 229.86, 232.99, 246.27, 243.15, 245.75, 247.05], 'signals': ['FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT']}</t>
+        </is>
+      </c>
+      <c r="S43" t="n">
+        <v>247.05</v>
+      </c>
+      <c r="T43" t="n">
+        <v>6.860714503696987</v>
+      </c>
+      <c r="U43" t="n">
+        <v>41.43299410133388</v>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>GE</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>56</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UP  </t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>0.643</v>
+      </c>
+      <c r="E44" t="n">
+        <v>52</v>
+      </c>
+      <c r="F44" t="n">
+        <v>80</v>
+      </c>
+      <c r="G44" t="n">
+        <v>50</v>
+      </c>
+      <c r="H44" t="n">
+        <v>-42</v>
+      </c>
+      <c r="I44" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="J44" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="K44" t="n">
+        <v>-12.3</v>
+      </c>
+      <c r="L44" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M44" t="n">
+        <v>13</v>
+      </c>
+      <c r="N44" t="n">
+        <v>2</v>
+      </c>
+      <c r="O44" t="n">
+        <v>4</v>
+      </c>
+      <c r="P44" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>3</v>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [326.11, 322.24, 321.53, 326.11, 324.75, 306.32, 299.32, 303.62, 301.71, 300.59, 291.25, 286.43, 291.18, 290.27, 296.19, 284.88, 282.46, 272.91, 283.42, 292.32, 280.81, 288.33, 288.24, 307.68, 312.63, 307.97, 311.51, 317.6, 313.54, 297.92, 303.75, 303.22, 286.37, 275.95, 281.99, 284.25, 284.21, 288.84, 283.22, 289.57, 286.15, 280.17, 286.32, 305.45, 302.25, 296.78, 300.4, 297.08, 294.34, 291.18, 281.18, 285.63, 284.92, 299.8, 301.38, 302.46, 314.1, 316.82, 320.42, 323.36, 324.2, 317.32, 314.25, 327.24, 327.59, 321.64, 330.03, 318.31, 332.35, 334.88, 341.83, 351.29, 356.59, 357.19, 354.68, 356.03, 365.42, 370.9, 368.54, 373.24, 373.26, 374.47, 377.05, 378.68, 366.98, 356.03, 359.04, 359.27, 353.42, 353.73, 360.35, 345.73, 348.83, 341.3, 340.7, 341.19, 349.0, 353.73, 361.61, 363.59], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+        </is>
+      </c>
+      <c r="S44" t="n">
+        <v>363.59</v>
+      </c>
+      <c r="T44" t="n">
+        <v>10.2085702078683</v>
+      </c>
+      <c r="U44" t="n">
+        <v>35.91426140311804</v>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>61</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UP  </t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>0.537</v>
+      </c>
+      <c r="E45" t="n">
+        <v>63</v>
+      </c>
+      <c r="F45" t="n">
+        <v>30</v>
+      </c>
+      <c r="G45" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="H45" t="n">
+        <v>512</v>
+      </c>
+      <c r="I45" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="J45" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="K45" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="L45" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M45" t="n">
+        <v>22</v>
+      </c>
+      <c r="N45" t="n">
+        <v>1</v>
+      </c>
+      <c r="O45" t="n">
+        <v>1</v>
+      </c>
+      <c r="P45" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>2</v>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [222.06, 231.11, 225.0, 217.76, 214.1, 204.76, 209.89, 213.47, 210.82, 205.99, 201.18, 195.12, 198.41, 196.42, 199.61, 194.36, 190.52, 189.21, 199.03, 207.32, 208.22, 212.3, 210.0, 217.8, 220.06, 217.63, 222.14, 223.77, 223.93, 218.88, 223.38, 225.08, 219.16, 231.28, 234.15, 232.44, 231.33, 230.72, 224.11, 229.03, 227.38, 221.3, 224.38, 229.93, 231.03, 237.36, 238.21, 236.87, 240.6, 229.21, 220.49, 220.61, 215.01, 222.2, 219.61, 219.02, 218.9, 224.3, 228.78, 231.15, 224.3, 217.7, 210.58, 217.42, 215.45, 215.92, 214.51, 209.0, 221.63, 219.05, 228.95, 227.49, 225.63, 222.72, 220.83, 216.71, 220.25, 218.12, 217.25, 214.69, 216.47, 218.58, 226.49, 234.54, 231.68, 224.95, 223.11, 222.28, 215.51, 217.11, 218.12, 214.34, 214.03, 209.48, 204.8, 208.65, 209.23, 209.52, 211.5, 221.56], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+        </is>
+      </c>
+      <c r="S45" t="n">
+        <v>221.56</v>
+      </c>
+      <c r="T45" t="n">
+        <v>6.032856532505581</v>
+      </c>
+      <c r="U45" t="n">
+        <v>24.42248909025004</v>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>FLAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>SPMO</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>54</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="E46" t="n">
+        <v>49</v>
+      </c>
+      <c r="F46" t="n">
+        <v>80</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>306</v>
+      </c>
+      <c r="I46" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="J46" t="n">
         <v>18.3</v>
       </c>
-      <c r="K12" t="n">
-        <v>-16.3</v>
-      </c>
-      <c r="L12" t="n">
-        <v>5000</v>
-      </c>
-      <c r="M12" t="n">
+      <c r="K46" t="n">
+        <v>-12.2</v>
+      </c>
+      <c r="L46" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M46" t="n">
         <v>35</v>
       </c>
-      <c r="N12" t="n">
+      <c r="N46" t="n">
         <v>4</v>
       </c>
-      <c r="O12" t="n">
-        <v>5</v>
-      </c>
-      <c r="P12" t="n">
+      <c r="O46" t="n">
+        <v>2</v>
+      </c>
+      <c r="P46" t="n">
         <v>4</v>
       </c>
-      <c r="Q12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [119.13, 117.73, 118.78, 118.56, 118.18, 116.66, 115.67, 116.84, 116.84, 115.56, 115.38, 113.29, 114.35, 114.66, 115.14, 111.17, 110.14, 107.67, 111.94, 114.32, 114.56, 115.49, 116.47, 121.17, 122.57, 123.15, 124.4, 126.46, 126.39, 126.55, 128.1, 127.44, 126.46, 128.91, 129.03, 131.32, 131.91, 129.76, 130.57, 133.59, 134.21, 134.23, 137.67, 141.37, 139.09, 143.59, 145.85, 144.23, 146.07, 147.29, 143.26, 141.2, 140.41, 143.09, 144.47, 144.72, 149.57, 149.37, 149.9, 150.36, 152.09, 154.08, 154.85, 152.6, 144.06, 147.65, 147.28, 143.46, 150.35, 152.25, 157.6, 154.38, 155.25, 159.65, 161.66, 154.34, 153.79, 159.64, 154.2, 158.53, 161.54, 155.32, 150.83, 152.98, 149.42, 150.57, 153.08, 153.75, 149.73, 152.86, 150.0, 145.28, 143.89, 144.52, 149.7, 150.07, 149.83, 146.51, 144.75, 140.95], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
-        </is>
-      </c>
-      <c r="S12" t="n">
+      <c r="Q46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [119.13, 117.73, 118.78, 118.56, 118.18, 116.66, 115.67, 116.84, 116.84, 115.56, 115.38, 113.29, 114.35, 114.66, 115.14, 111.17, 110.14, 107.67, 111.94, 114.32, 114.56, 115.49, 116.47, 121.17, 122.57, 123.15, 124.4, 126.46, 126.39, 126.55, 128.1, 127.44, 126.46, 128.91, 129.03, 131.32, 131.91, 129.76, 130.57, 133.59, 134.21, 134.23, 137.67, 141.37, 139.09, 143.59, 145.85, 144.23, 146.07, 147.29, 143.26, 141.2, 140.41, 143.09, 144.47, 144.72, 149.57, 149.37, 149.9, 150.36, 152.09, 154.08, 154.85, 152.6, 144.06, 147.65, 147.28, 143.46, 150.35, 152.25, 157.6, 154.38, 155.25, 159.65, 161.66, 154.34, 153.79, 159.64, 154.2, 158.53, 161.54, 155.32, 150.83, 152.98, 149.42, 150.57, 153.08, 153.75, 149.73, 152.86, 150.0, 145.28, 143.89, 144.52, 149.7, 150.07, 149.83, 146.51, 144.75, 140.95], 'signals': ['FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY']}</t>
+        </is>
+      </c>
+      <c r="S46" t="n">
         <v>140.95</v>
       </c>
-      <c r="T12" t="n">
+      <c r="T46" t="n">
         <v>4.625142778669085</v>
       </c>
-      <c r="U12" t="n">
+      <c r="U46" t="n">
         <v>32.31190962626408</v>
       </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>FLAT</t>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>BUY</t>
         </is>
       </c>
     </row>

--- a/demo_results.xlsx
+++ b/demo_results.xlsx
@@ -535,36 +535,36 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DOWN</t>
+          <t xml:space="preserve">UP  </t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.17</v>
+        <v>0.89</v>
       </c>
       <c r="E2" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F2" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="G2" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H2" t="n">
-        <v>881</v>
+        <v>854</v>
       </c>
       <c r="I2" t="n">
-        <v>17.6</v>
+        <v>17.1</v>
       </c>
       <c r="J2" t="n">
-        <v>30.8</v>
+        <v>31.5</v>
       </c>
       <c r="K2" t="n">
-        <v>-13.2</v>
+        <v>-14.4</v>
       </c>
       <c r="L2" t="n">
         <v>5000</v>
@@ -576,31 +576,31 @@
         <v>3</v>
       </c>
       <c r="O2" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="P2" t="n">
         <v>3</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.7</v>
+        <v>2</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [260.05, 257.22, 259.64, 260.59, 260.57, 255.52, 249.89, 252.59, 254.0, 249.71, 248.73, 247.76, 251.26, 251.41, 252.39, 252.66, 248.57, 246.4, 253.56, 255.39, 255.68, 258.62, 253.27, 258.66, 260.25, 260.24, 258.96, 258.59, 266.18, 263.16, 269.98, 272.8, 265.93, 272.92, 273.18, 270.81, 267.36, 270.46, 269.92, 271.1, 279.88, 276.58, 283.92, 287.25, 287.18, 293.05, 292.68, 294.8, 298.87, 298.21, 300.23, 297.84, 298.97, 302.25, 304.99, 308.82, 308.33, 310.85, 312.51, 312.06, 306.31, 315.2, 310.26, 311.23, 307.34, 301.54, 290.55, 291.58, 295.63, 291.13, 296.42, 299.24, 295.95, 298.01, 297.01, 294.3, 293.08, 275.15, 283.78, 281.74, 289.36, 294.38, 308.63, 312.66, 310.66, 313.39, 316.22, 315.32, 317.31, 314.86, 327.5, 333.26, 333.74, 326.59, 327.74, 325.89, 321.66, 333.02, 336.91, 340.08], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28', '2026-07-29'], 'prices': [257.22, 259.64, 260.59, 260.57, 255.52, 249.89, 252.59, 254.0, 249.71, 248.73, 247.76, 251.26, 251.41, 252.39, 252.66, 248.57, 246.4, 253.56, 255.39, 255.68, 258.62, 253.27, 258.66, 260.25, 260.24, 258.96, 258.59, 266.18, 263.16, 269.98, 272.8, 265.93, 272.92, 273.18, 270.81, 267.36, 270.46, 269.92, 271.1, 279.88, 276.58, 283.92, 287.25, 287.18, 293.05, 292.68, 294.8, 298.87, 298.21, 300.23, 297.84, 298.97, 302.25, 304.99, 308.82, 308.33, 310.85, 312.51, 312.06, 306.31, 315.2, 310.26, 311.23, 307.34, 301.54, 290.55, 291.58, 295.63, 291.13, 296.42, 299.24, 295.95, 298.01, 297.01, 294.3, 293.08, 275.15, 283.78, 281.74, 289.36, 294.38, 308.63, 312.66, 310.66, 313.39, 316.22, 315.32, 317.31, 314.86, 327.5, 333.26, 333.74, 326.59, 327.74, 325.89, 321.66, 333.02, 336.91, 340.08, 338.19], 'signals': ['FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>340.08</v>
+        <v>338.19</v>
       </c>
       <c r="T2" t="n">
-        <v>7.901430402483259</v>
+        <v>7.819287981305804</v>
       </c>
       <c r="U2" t="n">
-        <v>43.6905405239262</v>
+        <v>44.86389850599954</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>FLAT</t>
         </is>
       </c>
     </row>
@@ -611,36 +611,36 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>56</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UP  </t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.709</v>
+      </c>
+      <c r="E3" t="n">
         <v>51</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UP  </t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>0.6929999999999999</v>
-      </c>
-      <c r="E3" t="n">
-        <v>52</v>
       </c>
       <c r="F3" t="n">
         <v>100</v>
       </c>
       <c r="G3" t="n">
-        <v>66.7</v>
+        <v>80</v>
       </c>
       <c r="H3" t="n">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="I3" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J3" t="n">
-        <v>-4</v>
+        <v>-4.3</v>
       </c>
       <c r="K3" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="L3" t="n">
         <v>5000</v>
@@ -662,17 +662,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [409.79, 408.08, 408.53, 404.88, 404.0, 400.99, 394.7, 399.09, 398.55, 390.94, 388.18, 381.04, 382.17, 371.93, 370.24, 365.18, 356.0, 358.18, 369.37, 368.57, 372.65, 372.07, 371.49, 373.52, 372.26, 370.07, 383.54, 392.26, 410.33, 419.35, 421.88, 417.17, 423.24, 431.98, 414.85, 423.7, 423.9, 428.32, 423.54, 406.9, 413.54, 412.73, 410.49, 413.07, 419.86, 414.22, 411.77, 406.89, 404.33, 408.55, 421.01, 422.62, 416.52, 420.15, 419.09, 418.57, 416.03, 412.67, 426.99, 450.24, 460.52, 441.31, 427.34, 428.05, 416.67, 411.74, 403.41, 397.36, 390.34, 390.74, 399.76, 393.83, 378.91, 379.4, 367.34, 373.94, 365.46, 352.83, 372.97, 368.57, 373.02, 384.28, 390.49, 386.74, 388.84, 383.34, 384.36, 385.1, 390.99, 384.93, 395.63, 401.1, 393.82, 402.29, 397.75, 390.34, 381.58, 381.7, 389.1, 393.35], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28', '2026-07-29'], 'prices': [408.08, 408.53, 404.88, 404.0, 400.99, 394.7, 399.09, 398.55, 390.94, 388.18, 381.04, 382.17, 371.93, 370.24, 365.18, 356.0, 358.18, 369.37, 368.57, 372.65, 372.07, 371.49, 373.52, 372.26, 370.07, 383.54, 392.26, 410.33, 419.35, 421.88, 417.17, 423.24, 431.98, 414.85, 423.7, 423.9, 428.32, 423.54, 406.9, 413.54, 412.73, 410.49, 413.07, 419.86, 414.22, 411.77, 406.89, 404.33, 408.55, 421.01, 422.62, 416.52, 420.15, 419.09, 418.57, 416.03, 412.67, 426.99, 450.24, 460.52, 441.31, 427.34, 428.05, 416.67, 411.74, 403.41, 397.36, 390.34, 390.74, 399.76, 393.83, 378.91, 379.4, 367.34, 373.94, 365.46, 352.83, 372.97, 368.57, 373.02, 384.28, 390.49, 386.74, 388.84, 383.34, 384.36, 385.1, 390.99, 384.93, 395.63, 401.1, 393.82, 402.29, 397.75, 390.34, 381.58, 381.7, 389.1, 393.35, 390.54], 'signals': ['FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>393.35</v>
+        <v>390.54</v>
       </c>
       <c r="T3" t="n">
-        <v>11.6614270891462</v>
+        <v>11.74785723005022</v>
       </c>
       <c r="U3" t="n">
-        <v>17.97354091550426</v>
+        <v>18.00916996390183</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
@@ -695,28 +695,28 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.535</v>
+        <v>0.528</v>
       </c>
       <c r="E4" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F4" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
       </c>
       <c r="H4" t="n">
-        <v>248</v>
+        <v>414</v>
       </c>
       <c r="I4" t="n">
-        <v>5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>11.1</v>
+        <v>12.9</v>
       </c>
       <c r="K4" t="n">
-        <v>-6.1</v>
+        <v>-4.6</v>
       </c>
       <c r="L4" t="n">
         <v>5000</v>
@@ -738,21 +738,21 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [300.49, 298.13, 306.18, 306.86, 308.52, 303.37, 302.1, 305.38, 310.73, 307.51, 306.95, 300.82, 301.88, 290.27, 290.76, 280.75, 274.18, 273.34, 287.39, 297.21, 295.59, 299.81, 305.28, 317.13, 318.3, 317.05, 321.12, 332.71, 336.92, 335.82, 341.48, 337.22, 332.09, 339.12, 338.69, 344.19, 350.13, 349.57, 349.73, 384.57, 385.46, 383.02, 388.2, 397.8, 397.75, 400.56, 388.41, 387.12, 402.38, 400.83, 396.54, 396.7, 387.43, 388.68, 387.43, 382.74, 388.65, 388.6, 389.9, 380.11, 376.15, 361.63, 358.78, 371.97, 368.31, 363.31, 364.26, 356.38, 357.77, 359.68, 369.35, 373.25, 363.79, 368.03, 349.68, 346.13, 345.29, 343.71, 337.39, 353.65, 357.37, 361.21, 359.91, 366.46, 367.03, 361.92, 358.89, 357.18, 352.51, 359.51, 370.92, 354.46, 346.77, 351.99, 347.15, 342.09, 317.69, 319.74, 326.56, 333.71], 'signals': ['BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL']}</t>
+          <t>{'dates': ['2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28', '2026-07-29'], 'prices': [298.13, 306.18, 306.86, 308.52, 303.37, 302.1, 305.38, 310.73, 307.51, 306.95, 300.82, 301.88, 290.27, 290.76, 280.75, 274.18, 273.34, 287.39, 297.21, 295.59, 299.81, 305.28, 317.13, 318.3, 317.05, 321.12, 332.71, 336.92, 335.82, 341.48, 337.22, 332.09, 339.12, 338.69, 344.19, 350.13, 349.57, 349.73, 384.57, 385.46, 383.02, 388.2, 397.8, 397.75, 400.56, 388.41, 387.12, 402.38, 400.83, 396.54, 396.7, 387.43, 388.68, 387.43, 382.74, 388.65, 388.6, 389.9, 380.11, 376.15, 361.63, 358.78, 371.97, 368.31, 363.31, 364.26, 356.38, 357.77, 359.68, 369.35, 373.25, 363.79, 368.03, 349.68, 346.13, 345.29, 343.71, 337.39, 353.65, 357.37, 361.21, 359.91, 366.46, 367.03, 361.92, 358.89, 357.18, 352.51, 359.51, 370.92, 354.46, 346.77, 351.99, 347.15, 342.09, 317.69, 319.74, 326.56, 333.71, 336.71], 'signals': ['BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>333.71</v>
+        <v>336.71</v>
       </c>
       <c r="T4" t="n">
-        <v>11.90500313895089</v>
+        <v>11.90785871233259</v>
       </c>
       <c r="U4" t="n">
-        <v>20.12126527259463</v>
+        <v>18.52936616537245</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>FLAT</t>
         </is>
       </c>
     </row>
@@ -763,72 +763,72 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>51</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UP  </t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.765</v>
+      </c>
+      <c r="E5" t="n">
+        <v>60</v>
+      </c>
+      <c r="F5" t="n">
         <v>50</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>DOWN</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="E5" t="n">
-        <v>56</v>
-      </c>
-      <c r="F5" t="n">
-        <v>60</v>
       </c>
       <c r="G5" t="n">
         <v>50</v>
       </c>
       <c r="H5" t="n">
-        <v>-356</v>
+        <v>1400</v>
       </c>
       <c r="I5" t="n">
-        <v>-7.1</v>
+        <v>28</v>
       </c>
       <c r="J5" t="n">
-        <v>5.4</v>
+        <v>6.3</v>
       </c>
       <c r="K5" t="n">
-        <v>-12.5</v>
+        <v>21.7</v>
       </c>
       <c r="L5" t="n">
         <v>5000</v>
       </c>
       <c r="M5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [218.94, 213.21, 213.49, 214.33, 212.65, 209.53, 207.67, 211.74, 215.2, 209.87, 208.76, 205.37, 210.14, 207.24, 211.71, 207.54, 199.34, 200.95, 208.27, 210.57, 209.77, 212.79, 213.77, 221.25, 233.65, 238.38, 239.89, 249.02, 248.5, 249.7, 250.56, 248.28, 249.91, 255.36, 255.08, 263.99, 261.12, 259.7, 263.04, 265.06, 268.26, 272.05, 273.55, 274.99, 271.17, 272.68, 268.99, 265.82, 270.13, 267.22, 264.14, 264.86, 259.34, 265.01, 268.46, 266.32, 265.29, 271.85, 274.0, 270.64, 261.26, 256.52, 250.02, 253.79, 246.03, 245.22, 244.19, 238.0, 241.51, 238.55, 246.02, 246.0, 237.5, 244.39, 232.79, 234.11, 234.27, 227.01, 232.69, 240.14, 238.34, 241.7, 242.67, 244.16, 245.98, 243.62, 247.04, 245.34, 247.31, 247.49, 254.96, 249.89, 247.23, 249.99, 247.55, 244.85, 233.66, 232.11, 231.39, 230.86], 'signals': ['BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28', '2026-07-29'], 'prices': [213.21, 213.49, 214.33, 212.65, 209.53, 207.67, 211.74, 215.2, 209.87, 208.76, 205.37, 210.14, 207.24, 211.71, 207.54, 199.34, 200.95, 208.27, 210.57, 209.77, 212.79, 213.77, 221.25, 233.65, 238.38, 239.89, 249.02, 248.5, 249.7, 250.56, 248.28, 249.91, 255.36, 255.08, 263.99, 261.12, 259.7, 263.04, 265.06, 268.26, 272.05, 273.55, 274.99, 271.17, 272.68, 268.99, 265.82, 270.13, 267.22, 264.14, 264.86, 259.34, 265.01, 268.46, 266.32, 265.29, 271.85, 274.0, 270.64, 261.26, 256.52, 250.02, 253.79, 246.03, 245.22, 244.19, 238.0, 241.51, 238.55, 246.02, 246.0, 237.5, 244.39, 232.79, 234.11, 234.27, 227.01, 232.69, 240.14, 238.34, 241.7, 242.67, 244.16, 245.98, 243.62, 247.04, 245.34, 247.31, 247.49, 254.96, 249.89, 247.23, 249.99, 247.55, 244.85, 233.66, 232.11, 231.39, 230.86, 226.65], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>230.86</v>
+        <v>226.65</v>
       </c>
       <c r="T5" t="n">
-        <v>6.669285365513393</v>
+        <v>6.484285627092634</v>
       </c>
       <c r="U5" t="n">
-        <v>31.6319588524311</v>
+        <v>31.48518670367037</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>FLAT</t>
         </is>
       </c>
     </row>
@@ -847,28 +847,28 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.591</v>
       </c>
       <c r="E6" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F6" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="G6" t="n">
-        <v>58.3</v>
+        <v>50</v>
       </c>
       <c r="H6" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="I6" t="n">
         <v>1.2</v>
       </c>
       <c r="J6" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="K6" t="n">
-        <v>11.2</v>
+        <v>10.2</v>
       </c>
       <c r="L6" t="n">
         <v>5000</v>
@@ -877,30 +877,30 @@
         <v>8</v>
       </c>
       <c r="N6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q6" t="n">
-        <v>5</v>
+        <v>3.8</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [659.39, 643.71, 646.24, 652.91, 653.69, 637.04, 612.62, 626.87, 622.08, 615.11, 606.14, 593.11, 603.5, 592.37, 594.34, 547.03, 525.23, 535.88, 571.6, 578.69, 573.93, 572.49, 574.52, 611.85, 627.81, 629.28, 633.94, 661.88, 670.96, 676.24, 687.91, 670.29, 668.22, 674.1, 658.54, 674.4, 677.99, 670.72, 668.5, 611.34, 608.19, 609.84, 604.4, 612.31, 616.24, 609.07, 598.31, 602.44, 616.06, 617.86, 613.66, 610.64, 602.05, 604.5, 606.82, 609.69, 611.77, 634.67, 634.7, 631.92, 599.91, 597.08, 622.4, 626.99, 592.45, 584.85, 584.05, 570.45, 567.9, 566.45, 593.48, 600.21, 567.58, 577.22, 563.85, 562.2, 557.67, 542.87, 550.25, 562.6, 563.29, 612.91, 582.9, 600.29, 615.58, 603.12, 631.48, 669.21, 656.73, 661.04, 681.31, 664.54, 646.01, 645.85, 643.81, 627.17, 606.1, 595.19, 593.87, 593.41], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+          <t>{'dates': ['2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28', '2026-07-29'], 'prices': [643.71, 646.24, 652.91, 653.69, 637.04, 612.62, 626.87, 622.08, 615.11, 606.14, 593.11, 603.5, 592.37, 594.34, 547.03, 525.23, 535.88, 571.6, 578.69, 573.93, 572.49, 574.52, 611.85, 627.81, 629.28, 633.94, 661.88, 670.96, 676.24, 687.91, 670.29, 668.22, 674.1, 658.54, 674.4, 677.99, 670.72, 668.5, 611.34, 608.19, 609.84, 604.4, 612.31, 616.24, 609.07, 598.31, 602.44, 616.06, 617.86, 613.66, 610.64, 602.05, 604.5, 606.82, 609.69, 611.77, 634.67, 634.7, 631.92, 599.91, 597.08, 622.4, 626.99, 592.45, 584.85, 584.05, 570.45, 567.9, 566.45, 593.48, 600.21, 567.58, 577.22, 563.85, 562.2, 557.67, 542.87, 550.25, 562.6, 563.29, 612.91, 582.9, 600.29, 615.58, 603.12, 631.48, 669.21, 656.73, 661.04, 681.31, 664.54, 646.01, 645.85, 643.81, 627.17, 606.1, 595.19, 593.87, 593.41, 585.61], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>593.41</v>
+        <v>585.61</v>
       </c>
       <c r="T6" t="n">
-        <v>26.05214582170759</v>
+        <v>23.30571637834822</v>
       </c>
       <c r="U6" t="n">
-        <v>23.67631632710235</v>
+        <v>23.3303733232493</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -923,60 +923,60 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.611</v>
+        <v>0.83</v>
       </c>
       <c r="E7" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F7" t="n">
         <v>60</v>
       </c>
       <c r="G7" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H7" t="n">
-        <v>343</v>
+        <v>-39</v>
       </c>
       <c r="I7" t="n">
-        <v>6.9</v>
+        <v>-0.8</v>
       </c>
       <c r="J7" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.7</v>
+        <v>-7.8</v>
       </c>
       <c r="L7" t="n">
         <v>5000</v>
       </c>
       <c r="M7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O7" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [183.12, 177.6, 182.43, 184.54, 185.81, 182.93, 180.04, 183.01, 181.72, 180.19, 178.35, 172.5, 175.44, 175.0, 178.47, 171.04, 167.32, 164.98, 174.2, 175.55, 177.18, 177.43, 177.89, 181.87, 183.7, 188.41, 189.09, 196.28, 198.64, 198.12, 201.45, 201.82, 199.65, 202.26, 199.41, 208.03, 216.36, 212.92, 209.01, 199.34, 198.22, 198.25, 196.27, 207.59, 211.25, 214.95, 219.18, 220.52, 225.57, 235.47, 225.06, 222.06, 220.35, 223.21, 219.25, 215.08, 214.61, 212.35, 214.0, 210.89, 224.1, 222.56, 214.5, 218.66, 205.1, 208.64, 208.19, 200.42, 204.87, 205.19, 212.45, 207.41, 204.65, 210.69, 208.65, 200.04, 199.0, 195.74, 192.53, 194.97, 200.09, 197.58, 194.83, 195.55, 196.93, 204.12, 202.78, 210.96, 203.53, 211.8, 212.5, 207.4, 202.81, 203.28, 207.29, 212.06, 208.76, 206.84, 196.51, 197.01], 'signals': ['BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'BUY', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28', '2026-07-29'], 'prices': [177.6, 182.43, 184.54, 185.81, 182.93, 180.04, 183.01, 181.72, 180.19, 178.35, 172.5, 175.44, 175.0, 178.47, 171.04, 167.32, 164.98, 174.2, 175.55, 177.18, 177.43, 177.89, 181.87, 183.7, 188.41, 189.09, 196.28, 198.64, 198.12, 201.45, 201.82, 199.65, 202.26, 199.41, 208.03, 216.36, 212.92, 209.01, 199.34, 198.22, 198.25, 196.27, 207.59, 211.25, 214.95, 219.18, 220.52, 225.57, 235.47, 225.06, 222.06, 220.35, 223.21, 219.25, 215.08, 214.61, 212.35, 214.0, 210.89, 224.1, 222.56, 214.5, 218.66, 205.1, 208.64, 208.19, 200.42, 204.87, 205.19, 212.45, 207.41, 204.65, 210.69, 208.65, 200.04, 199.0, 195.74, 192.53, 194.97, 200.09, 197.58, 194.83, 195.55, 196.93, 204.12, 202.78, 210.96, 203.53, 211.8, 212.5, 207.4, 202.81, 203.28, 207.29, 212.06, 208.76, 206.84, 196.51, 197.01, 190.01], 'signals': ['BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>197.01</v>
+        <v>190.01</v>
       </c>
       <c r="T7" t="n">
-        <v>7.734284537179129</v>
+        <v>7.836429050990513</v>
       </c>
       <c r="U7" t="n">
-        <v>23.25884591416595</v>
+        <v>22.29241790270129</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -999,28 +999,28 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.628</v>
+        <v>0.641</v>
       </c>
       <c r="E8" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F8" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="G8" t="n">
         <v>50</v>
       </c>
       <c r="H8" t="n">
-        <v>727</v>
+        <v>1550</v>
       </c>
       <c r="I8" t="n">
-        <v>14.5</v>
+        <v>31</v>
       </c>
       <c r="J8" t="n">
-        <v>14.9</v>
+        <v>12.5</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.4</v>
+        <v>18.5</v>
       </c>
       <c r="L8" t="n">
         <v>5000</v>
@@ -1029,34 +1029,34 @@
         <v>13</v>
       </c>
       <c r="N8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [331.55, 329.27, 344.48, 341.32, 340.32, 334.74, 320.98, 323.73, 320.13, 314.77, 318.67, 309.37, 322.0, 317.79, 318.31, 308.93, 300.2, 292.95, 309.02, 312.99, 314.05, 313.93, 333.44, 350.08, 354.35, 370.96, 379.15, 380.18, 396.09, 397.84, 405.9, 399.0, 401.53, 421.98, 419.28, 422.09, 417.54, 399.2, 404.81, 416.77, 420.61, 415.84, 426.68, 424.77, 411.91, 429.32, 427.75, 418.64, 416.13, 439.1, 424.52, 420.05, 410.42, 417.1, 413.91, 413.49, 421.34, 421.19, 425.91, 446.06, 459.24, 480.81, 478.47, 418.25, 385.12, 395.97, 391.54, 371.51, 384.96, 381.47, 393.32, 376.11, 392.28, 410.7, 392.13, 380.15, 382.07, 378.91, 365.02, 372.45, 377.75, 369.34, 360.45, 373.9, 370.78, 388.69, 401.11, 399.97, 384.05, 389.11, 394.28, 374.45, 370.83, 378.16, 386.5, 396.81, 392.47, 381.92, 383.22, 380.91], 'signals': ['BUY', 'HOLD', 'SELL', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28', '2026-07-29'], 'prices': [329.27, 344.48, 341.32, 340.32, 334.74, 320.98, 323.73, 320.13, 314.77, 318.67, 309.37, 322.0, 317.79, 318.31, 308.93, 300.2, 292.95, 309.02, 312.99, 314.05, 313.93, 333.44, 350.08, 354.35, 370.96, 379.15, 380.18, 396.09, 397.84, 405.9, 399.0, 401.53, 421.98, 419.28, 422.09, 417.54, 399.2, 404.81, 416.77, 420.61, 415.84, 426.68, 424.77, 411.91, 429.32, 427.75, 418.64, 416.13, 439.1, 424.52, 420.05, 410.42, 417.1, 413.91, 413.49, 421.34, 421.19, 425.91, 446.06, 459.24, 480.81, 478.47, 418.25, 385.12, 395.97, 391.54, 371.51, 384.96, 381.47, 393.32, 376.11, 392.28, 410.7, 392.13, 380.15, 382.07, 378.91, 365.02, 372.45, 377.75, 369.34, 360.45, 373.9, 370.78, 388.69, 401.11, 399.97, 384.05, 389.11, 394.28, 374.45, 370.83, 378.16, 386.5, 396.81, 392.47, 381.92, 383.22, 380.91, 370.32], 'signals': ['BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY']}</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>380.91</v>
+        <v>370.32</v>
       </c>
       <c r="T8" t="n">
-        <v>14.95071193150112</v>
+        <v>14.73785400390625</v>
       </c>
       <c r="U8" t="n">
-        <v>11.7428541065135</v>
+        <v>15.64409807495208</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>BUY</t>
         </is>
       </c>
     </row>
@@ -1067,7 +1067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1075,34 +1075,34 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.325</v>
+        <v>0.25</v>
       </c>
       <c r="E9" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F9" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="H9" t="n">
-        <v>1073</v>
+        <v>1975</v>
       </c>
       <c r="I9" t="n">
-        <v>21.5</v>
+        <v>39.5</v>
       </c>
       <c r="J9" t="n">
-        <v>-22</v>
+        <v>-22.5</v>
       </c>
       <c r="K9" t="n">
-        <v>43.5</v>
+        <v>62</v>
       </c>
       <c r="L9" t="n">
         <v>5000</v>
       </c>
       <c r="M9" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="N9" t="n">
         <v>5</v>
@@ -1118,17 +1118,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [153.72, 151.9, 150.51, 148.36, 161.99, 158.06, 154.03, 154.89, 153.62, 151.84, 154.44, 148.64, 153.27, 146.07, 145.01, 141.82, 138.69, 137.84, 146.09, 144.22, 145.36, 144.53, 142.18, 142.66, 137.38, 137.61, 155.08, 162.43, 169.22, 177.72, 174.45, 176.96, 180.54, 186.85, 175.67, 172.68, 172.36, 165.38, 163.26, 160.83, 171.23, 179.66, 184.71, 193.36, 193.92, 195.27, 193.17, 186.18, 189.1, 194.93, 192.28, 185.96, 180.83, 187.51, 189.11, 191.41, 192.39, 190.3, 202.99, 225.0, 247.29, 243.73, 229.53, 235.52, 212.94, 211.09, 205.1, 200.56, 183.46, 183.49, 191.97, 187.68, 182.89, 183.65, 174.46, 164.59, 156.98, 151.93, 148.02, 147.25, 146.04, 142.01, 139.78, 143.26, 141.11, 140.0, 143.72, 140.64, 131.54, 127.94, 132.49, 124.21, 126.41, 121.38, 127.05, 125.84, 120.04, 114.99, 119.9, 119.96], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+          <t>{'dates': ['2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28', '2026-07-29'], 'prices': [151.9, 150.51, 148.36, 161.99, 158.06, 154.03, 154.89, 153.62, 151.84, 154.44, 148.64, 153.27, 146.07, 145.01, 141.82, 138.69, 137.84, 146.09, 144.22, 145.36, 144.53, 142.18, 142.66, 137.38, 137.61, 155.08, 162.43, 169.22, 177.72, 174.45, 176.96, 180.54, 186.85, 175.67, 172.68, 172.36, 165.38, 163.26, 160.83, 171.23, 179.66, 184.71, 193.36, 193.92, 195.27, 193.17, 186.18, 189.1, 194.93, 192.28, 185.96, 180.83, 187.51, 189.11, 191.41, 192.39, 190.3, 202.99, 225.0, 247.29, 243.73, 229.53, 235.52, 212.94, 211.09, 205.1, 200.56, 183.46, 183.49, 191.97, 187.68, 182.89, 183.65, 174.46, 164.59, 156.98, 151.93, 148.02, 147.25, 146.04, 142.01, 139.78, 143.26, 141.11, 140.0, 143.72, 140.64, 131.54, 127.94, 132.49, 124.21, 126.41, 121.38, 127.05, 125.84, 120.04, 114.99, 119.9, 119.96, 117.74], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>119.96</v>
+        <v>117.74</v>
       </c>
       <c r="T9" t="n">
-        <v>6.947873837857358</v>
+        <v>6.745713370186942</v>
       </c>
       <c r="U9" t="n">
-        <v>55.04654065605482</v>
+        <v>57.92239247593587</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1151,60 +1151,60 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.573</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F10" t="n">
         <v>60</v>
       </c>
       <c r="G10" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="H10" t="n">
-        <v>2154</v>
+        <v>2321</v>
       </c>
       <c r="I10" t="n">
-        <v>43.1</v>
+        <v>46.4</v>
       </c>
       <c r="J10" t="n">
-        <v>127.9</v>
+        <v>123.2</v>
       </c>
       <c r="K10" t="n">
-        <v>-84.8</v>
+        <v>-76.8</v>
       </c>
       <c r="L10" t="n">
         <v>5000</v>
       </c>
       <c r="M10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O10" t="n">
         <v>15</v>
       </c>
       <c r="P10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q10" t="n">
-        <v>8</v>
+        <v>5.7</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [199.45, 192.43, 202.68, 203.23, 204.83, 197.74, 193.39, 196.58, 196.31, 199.46, 205.27, 201.33, 202.68, 205.37, 220.27, 203.77, 201.99, 196.04, 203.43, 210.21, 217.5, 220.18, 221.53, 231.82, 236.64, 245.04, 246.83, 255.07, 258.12, 278.26, 278.39, 274.95, 284.49, 303.46, 305.33, 347.81, 334.63, 323.21, 337.11, 354.49, 360.54, 341.54, 355.26, 421.39, 408.46, 455.19, 458.79, 448.29, 445.5, 449.7, 424.1, 420.99, 414.05, 447.58, 449.59, 467.51, 503.89, 495.54, 518.09, 516.1, 510.13, 521.54, 542.52, 523.2, 466.38, 490.33, 475.51, 452.4, 488.45, 511.57, 547.26, 507.29, 512.48, 537.37, 551.63, 519.85, 519.74, 532.57, 521.58, 539.49, 580.91, 540.88, 517.82, 552.05, 516.11, 517.41, 546.72, 557.89, 534.39, 548.13, 529.14, 500.94, 495.76, 503.57, 544.43, 552.33, 539.69, 521.95, 494.95, 454.62], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28', '2026-07-29'], 'prices': [192.43, 202.68, 203.23, 204.83, 197.74, 193.39, 196.58, 196.31, 199.46, 205.27, 201.33, 202.68, 205.37, 220.27, 203.77, 201.99, 196.04, 203.43, 210.21, 217.5, 220.18, 221.53, 231.82, 236.64, 245.04, 246.83, 255.07, 258.12, 278.26, 278.39, 274.95, 284.49, 303.46, 305.33, 347.81, 334.63, 323.21, 337.11, 354.49, 360.54, 341.54, 355.26, 421.39, 408.46, 455.19, 458.79, 448.29, 445.5, 449.7, 424.1, 420.99, 414.05, 447.58, 449.59, 467.51, 503.89, 495.54, 518.09, 516.1, 510.13, 521.54, 542.52, 523.2, 466.38, 490.33, 475.51, 452.4, 488.45, 511.57, 547.26, 507.29, 512.48, 537.37, 551.63, 519.85, 519.74, 532.57, 521.58, 539.49, 580.91, 540.88, 517.82, 552.05, 516.11, 517.41, 546.72, 557.89, 534.39, 548.13, 529.14, 500.94, 495.76, 503.57, 544.43, 552.33, 539.69, 521.95, 494.95, 454.62, 429.56], 'signals': ['BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
       <c r="S10" t="n">
-        <v>454.62</v>
+        <v>429.56</v>
       </c>
       <c r="T10" t="n">
-        <v>38.41143798828125</v>
+        <v>37.77572195870535</v>
       </c>
       <c r="U10" t="n">
-        <v>14.03515283276854</v>
+        <v>18.02955595678292</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1227,60 +1227,60 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.472</v>
+        <v>0.395</v>
       </c>
       <c r="E11" t="n">
         <v>63</v>
       </c>
       <c r="F11" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G11" t="n">
-        <v>44.4</v>
+        <v>40</v>
       </c>
       <c r="H11" t="n">
-        <v>2454</v>
+        <v>2758</v>
       </c>
       <c r="I11" t="n">
-        <v>49.1</v>
+        <v>55.2</v>
       </c>
       <c r="J11" t="n">
-        <v>19.3</v>
+        <v>15.2</v>
       </c>
       <c r="K11" t="n">
-        <v>29.8</v>
+        <v>40</v>
       </c>
       <c r="L11" t="n">
         <v>5000</v>
       </c>
       <c r="M11" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O11" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q11" t="n">
-        <v>9</v>
+        <v>2.3</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [136.5, 135.19, 137.6, 134.7, 133.63, 130.67, 129.34, 128.91, 131.11, 129.99, 130.8, 129.42, 127.88, 128.2, 129.87, 130.06, 126.64, 126.6, 128.31, 126.81, 126.33, 125.27, 123.61, 127.04, 127.28, 127.59, 130.76, 132.35, 132.56, 133.98, 135.7, 137.01, 135.06, 135.57, 133.46, 148.3, 149.71, 149.45, 155.43, 178.92, 176.36, 167.76, 185.86, 191.86, 201.8, 218.28, 236.66, 209.54, 212.39, 199.34, 200.75, 202.89, 194.89, 201.76, 212.62, 237.28, 247.9, 232.54, 242.39, 250.1, 228.15, 239.95, 249.09, 242.57, 215.94, 217.77, 205.42, 191.2, 202.96, 211.72, 220.81, 214.07, 212.97, 226.11, 221.9, 204.13, 197.41, 204.9, 189.39, 188.72, 184.79, 181.92, 176.25, 186.48, 182.97, 186.56, 191.11, 189.16, 183.98, 178.1, 177.98, 170.61, 171.78, 170.32, 173.5, 175.63, 171.11, 166.97, 170.04, 162.88], 'signals': ['BUY', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+          <t>{'dates': ['2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28', '2026-07-29'], 'prices': [135.19, 137.6, 134.7, 133.63, 130.67, 129.34, 128.91, 131.11, 129.99, 130.8, 129.42, 127.88, 128.2, 129.87, 130.06, 126.64, 126.6, 128.31, 126.81, 126.33, 125.27, 123.61, 127.04, 127.28, 127.59, 130.76, 132.35, 132.56, 133.98, 135.7, 137.01, 135.06, 135.57, 133.46, 148.3, 149.71, 149.45, 155.43, 178.92, 176.36, 167.76, 185.86, 191.86, 201.8, 218.28, 236.66, 209.54, 212.39, 199.34, 200.75, 202.89, 194.89, 201.76, 212.62, 237.28, 247.9, 232.54, 242.39, 250.1, 228.15, 239.95, 249.09, 242.57, 215.94, 217.77, 205.42, 191.2, 202.96, 211.72, 220.81, 214.07, 212.97, 226.11, 221.9, 204.13, 197.41, 204.9, 189.39, 188.72, 184.79, 181.92, 176.25, 186.48, 182.97, 186.56, 191.11, 189.16, 183.98, 178.1, 177.98, 170.61, 171.78, 170.32, 173.5, 175.63, 171.11, 166.97, 170.04, 162.88, 155.68], 'signals': ['BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
       <c r="S11" t="n">
-        <v>162.88</v>
+        <v>155.68</v>
       </c>
       <c r="T11" t="n">
-        <v>7.397143772670201</v>
+        <v>7.399286542619977</v>
       </c>
       <c r="U11" t="n">
-        <v>25.56126716557969</v>
+        <v>31.35307462613775</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1303,34 +1303,34 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.353</v>
+        <v>0.263</v>
       </c>
       <c r="E12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F12" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G12" t="n">
-        <v>58.3</v>
+        <v>50</v>
       </c>
       <c r="H12" t="n">
-        <v>-510</v>
+        <v>-330</v>
       </c>
       <c r="I12" t="n">
-        <v>-10.2</v>
+        <v>-6.6</v>
       </c>
       <c r="J12" t="n">
-        <v>-9.4</v>
+        <v>-6.3</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.8</v>
+        <v>-0.3</v>
       </c>
       <c r="L12" t="n">
         <v>5000</v>
       </c>
       <c r="M12" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N12" t="n">
         <v>1</v>
@@ -1346,17 +1346,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [200.37, 201.09, 197.78, 193.92, 193.15, 198.27, 191.85, 197.34, 194.32, 193.36, 194.0, 194.39, 194.19, 182.09, 181.04, 184.7, 178.4, 184.09, 185.72, 185.3, 186.23, 184.09, 182.03, 175.48, 170.41, 164.54, 172.38, 170.87, 177.14, 180.75, 181.67, 185.79, 186.63, 189.31, 172.85, 177.7, 179.72, 180.85, 180.75, 176.08, 183.35, 185.0, 186.51, 180.72, 185.86, 181.35, 177.03, 170.87, 165.41, 167.15, 173.06, 179.02, 178.96, 179.64, 175.86, 179.61, 178.62, 177.05, 175.72, 190.61, 209.06, 200.32, 190.12, 188.26, 185.18, 182.08, 174.9, 170.48, 166.45, 165.89, 164.55, 161.71, 155.02, 151.78, 150.12, 153.42, 152.76, 150.19, 158.37, 157.93, 156.66, 163.23, 166.11, 165.65, 169.52, 166.58, 162.5, 163.32, 171.22, 167.56, 167.0, 172.68, 170.77, 173.79, 170.06, 163.0, 156.93, 163.66, 173.6, 181.5], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28', '2026-07-29'], 'prices': [201.09, 197.78, 193.92, 193.15, 198.27, 191.85, 197.34, 194.32, 193.36, 194.0, 194.39, 194.19, 182.09, 181.04, 184.7, 178.4, 184.09, 185.72, 185.3, 186.23, 184.09, 182.03, 175.48, 170.41, 164.54, 172.38, 170.87, 177.14, 180.75, 181.67, 185.79, 186.63, 189.31, 172.85, 177.7, 179.72, 180.85, 180.75, 176.08, 183.35, 185.0, 186.51, 180.72, 185.86, 181.35, 177.03, 170.87, 165.41, 167.15, 173.06, 179.02, 178.96, 179.64, 175.86, 179.61, 178.62, 177.05, 175.72, 190.61, 209.06, 200.32, 190.12, 188.26, 185.18, 182.08, 174.9, 170.48, 166.45, 165.89, 164.55, 161.71, 155.02, 151.78, 150.12, 153.42, 152.76, 150.19, 158.37, 157.93, 156.66, 163.23, 166.11, 165.65, 169.52, 166.58, 162.5, 163.32, 171.22, 167.56, 167.0, 172.68, 170.77, 173.79, 170.06, 163.0, 156.93, 163.66, 173.6, 181.5, 188.38], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
       <c r="S12" t="n">
-        <v>181.5</v>
+        <v>188.38</v>
       </c>
       <c r="T12" t="n">
-        <v>8.49714115687779</v>
+        <v>8.395711626325335</v>
       </c>
       <c r="U12" t="n">
-        <v>18.47121041734655</v>
+        <v>20.42383028916537</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1379,60 +1379,60 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.212</v>
+        <v>0.148</v>
       </c>
       <c r="E13" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F13" t="n">
         <v>90</v>
       </c>
       <c r="G13" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H13" t="n">
-        <v>268</v>
+        <v>-486</v>
       </c>
       <c r="I13" t="n">
-        <v>5.4</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>-27</v>
+        <v>-25.6</v>
       </c>
       <c r="K13" t="n">
-        <v>32.4</v>
+        <v>15.9</v>
       </c>
       <c r="L13" t="n">
         <v>5000</v>
       </c>
       <c r="M13" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="N13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O13" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="P13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [99.17, 99.02, 98.32, 96.94, 94.89, 94.31, 95.31, 95.2, 94.36, 94.7, 91.74, 91.82, 93.38, 90.92, 92.28, 93.32, 93.43, 92.97, 96.15, 95.55, 98.66, 98.93, 98.82, 99.39, 102.05, 103.01, 103.16, 106.28, 107.71, 107.79, 97.31, 94.83, 92.58, 93.24, 92.82, 92.44, 91.37, 92.27, 92.12, 93.61, 92.06, 91.02, 87.89, 88.27, 88.25, 87.49, 85.45, 87.66, 87.56, 86.94, 87.02, 89.65, 89.33, 88.09, 89.3, 88.6, 87.68, 87.35, 86.36, 86.02, 85.85, 83.33, 81.52, 81.56, 82.18, 82.64, 81.41, 82.0, 81.27, 80.34, 81.67, 78.72, 76.96, 77.38, 72.88, 72.82, 71.84, 70.9, 73.81, 73.78, 71.4, 74.19, 77.65, 76.02, 76.18, 75.59, 75.47, 73.37, 73.83, 73.53, 73.68, 74.35, 68.95, 67.6, 68.67, 68.53, 68.89, 70.09, 70.4, 72.39], 'signals': ['FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28', '2026-07-29'], 'prices': [99.02, 98.32, 96.94, 94.89, 94.31, 95.31, 95.2, 94.36, 94.7, 91.74, 91.82, 93.38, 90.92, 92.28, 93.32, 93.43, 92.97, 96.15, 95.55, 98.66, 98.93, 98.82, 99.39, 102.05, 103.01, 103.16, 106.28, 107.71, 107.79, 97.31, 94.83, 92.58, 93.24, 92.82, 92.44, 91.37, 92.27, 92.12, 93.61, 92.06, 91.02, 87.89, 88.27, 88.25, 87.49, 85.45, 87.66, 87.56, 86.94, 87.02, 89.65, 89.33, 88.09, 89.3, 88.6, 87.68, 87.35, 86.36, 86.02, 85.85, 83.33, 81.52, 81.56, 82.18, 82.64, 81.41, 82.0, 81.27, 80.34, 81.67, 78.72, 76.96, 77.38, 72.88, 72.82, 71.84, 70.9, 73.81, 73.78, 71.4, 74.19, 77.65, 76.02, 76.18, 75.59, 75.47, 73.37, 73.83, 73.53, 73.68, 74.35, 68.95, 67.6, 68.67, 68.53, 68.89, 70.09, 70.4, 72.39, 73.63], 'signals': ['FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
       <c r="S13" t="n">
-        <v>72.39</v>
+        <v>73.63</v>
       </c>
       <c r="T13" t="n">
-        <v>2.682855878557478</v>
+        <v>2.712855747767857</v>
       </c>
       <c r="U13" t="n">
-        <v>34.27873709740564</v>
+        <v>32.49090289618915</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -1447,42 +1447,42 @@
         </is>
       </c>
       <c r="B14" t="n">
+        <v>50</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="E14" t="n">
         <v>55</v>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UP  </t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>0.5649999999999999</v>
-      </c>
-      <c r="E14" t="n">
-        <v>54</v>
-      </c>
       <c r="F14" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>55.6</v>
       </c>
       <c r="H14" t="n">
-        <v>2300</v>
+        <v>2346</v>
       </c>
       <c r="I14" t="n">
-        <v>46</v>
+        <v>46.9</v>
       </c>
       <c r="J14" t="n">
-        <v>87.8</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>-41.8</v>
+        <v>-41.7</v>
       </c>
       <c r="L14" t="n">
         <v>5000</v>
       </c>
       <c r="M14" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="N14" t="n">
         <v>1</v>
@@ -1498,17 +1498,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [45.95, 43.42, 45.58, 46.78, 47.98, 45.25, 45.77, 45.76, 44.06, 45.03, 46.18, 43.87, 44.01, 44.06, 47.18, 44.1, 43.13, 41.19, 44.13, 48.03, 50.38, 50.78, 52.91, 58.95, 61.72, 62.38, 65.18, 63.81, 64.94, 68.5, 68.5, 65.7, 66.26, 65.27, 66.78, 82.54, 84.99, 84.52, 94.75, 94.48, 99.62, 95.78, 108.15, 113.01, 109.62, 124.92, 129.44, 120.61, 120.29, 115.93, 108.77, 108.17, 110.8, 118.96, 118.5, 119.84, 123.52, 121.77, 120.89, 114.68, 109.33, 107.93, 112.71, 111.78, 99.17, 110.27, 107.92, 107.04, 116.96, 124.57, 127.86, 117.05, 121.1, 133.99, 140.94, 132.28, 131.65, 132.87, 128.32, 131.72, 139.63, 127.02, 120.35, 122.2, 110.39, 110.24, 112.54, 109.84, 103.12, 107.76, 102.99, 96.98, 95.04, 97.06, 105.45, 102.62, 100.23, 92.32, 91.67, 86.3], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28', '2026-07-29'], 'prices': [43.42, 45.58, 46.78, 47.98, 45.25, 45.77, 45.76, 44.06, 45.03, 46.18, 43.87, 44.01, 44.06, 47.18, 44.1, 43.13, 41.19, 44.13, 48.03, 50.38, 50.78, 52.91, 58.95, 61.72, 62.38, 65.18, 63.81, 64.94, 68.5, 68.5, 65.7, 66.26, 65.27, 66.78, 82.54, 84.99, 84.52, 94.75, 94.48, 99.62, 95.78, 108.15, 113.01, 109.62, 124.92, 129.44, 120.61, 120.29, 115.93, 108.77, 108.17, 110.8, 118.96, 118.5, 119.84, 123.52, 121.77, 120.89, 114.68, 109.33, 107.93, 112.71, 111.78, 99.17, 110.27, 107.92, 107.04, 116.96, 124.57, 127.86, 117.05, 121.1, 133.99, 140.94, 132.28, 131.65, 132.87, 128.32, 131.72, 139.63, 127.02, 120.35, 122.2, 110.39, 110.24, 112.54, 109.84, 103.12, 107.76, 102.99, 96.98, 95.04, 97.06, 105.45, 102.62, 100.23, 92.32, 91.67, 86.3, 81.88], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
       <c r="S14" t="n">
-        <v>86.3</v>
+        <v>81.88</v>
       </c>
       <c r="T14" t="n">
-        <v>7.458571297781808</v>
+        <v>7.469285692487444</v>
       </c>
       <c r="U14" t="n">
-        <v>38.86366638244701</v>
+        <v>41.30813475195399</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.424</v>
+        <v>0.403</v>
       </c>
       <c r="E15" t="n">
         <v>54</v>
@@ -1540,19 +1540,19 @@
         <v>50</v>
       </c>
       <c r="G15" t="n">
-        <v>68.40000000000001</v>
+        <v>60</v>
       </c>
       <c r="H15" t="n">
-        <v>2335</v>
+        <v>1310</v>
       </c>
       <c r="I15" t="n">
-        <v>46.7</v>
+        <v>26.2</v>
       </c>
       <c r="J15" t="n">
-        <v>106.8</v>
+        <v>99.7</v>
       </c>
       <c r="K15" t="n">
-        <v>-60.1</v>
+        <v>-73.5</v>
       </c>
       <c r="L15" t="n">
         <v>5000</v>
@@ -1564,27 +1564,27 @@
         <v>2</v>
       </c>
       <c r="O15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P15" t="n">
         <v>2</v>
       </c>
       <c r="Q15" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [396.82, 370.09, 389.1, 402.88, 418.45, 405.12, 425.89, 441.55, 461.43, 461.47, 444.02, 422.66, 404.12, 395.3, 381.87, 355.26, 357.02, 321.75, 337.79, 367.79, 366.18, 377.7, 377.52, 406.67, 421.45, 420.53, 426.49, 465.59, 456.16, 457.16, 455.0, 448.35, 449.31, 487.41, 481.65, 496.64, 524.48, 504.21, 518.38, 517.08, 542.13, 576.36, 640.1, 666.49, 646.53, 746.7, 795.21, 766.46, 803.51, 775.89, 724.55, 681.44, 698.63, 731.88, 761.98, 750.88, 895.74, 928.27, 923.38, 970.85, 1035.34, 1063.94, 1079.4, 995.85, 863.88, 949.13, 935.75, 891.74, 995.72, 981.46, 1087.82, 1020.6, 1043.03, 1133.82, 1211.19, 1051.61, 1048.35, 1213.37, 1132.16, 1145.1, 1154.11, 1032.12, 975.41, 984.75, 938.38, 948.8, 991.64, 979.3, 937.0, 983.12, 904.28, 853.2, 848.95, 865.46, 970.82, 959.48, 990.21, 920.95, 900.2, 820.53], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28', '2026-07-29'], 'prices': [370.09, 389.1, 402.88, 418.45, 405.12, 425.89, 441.55, 461.43, 461.47, 444.02, 422.66, 404.12, 395.3, 381.87, 355.26, 357.02, 321.75, 337.79, 367.79, 366.18, 377.7, 377.52, 406.67, 421.45, 420.53, 426.49, 465.59, 456.16, 457.16, 455.0, 448.35, 449.31, 487.41, 481.65, 496.64, 524.48, 504.21, 518.38, 517.08, 542.13, 576.36, 640.1, 666.49, 646.53, 746.7, 795.21, 766.46, 803.51, 775.89, 724.55, 681.44, 698.63, 731.88, 761.98, 750.88, 895.74, 928.27, 923.38, 970.85, 1035.34, 1063.94, 1079.4, 995.85, 863.88, 949.13, 935.75, 891.74, 995.72, 981.46, 1087.82, 1020.6, 1043.03, 1133.82, 1211.19, 1051.61, 1048.35, 1213.37, 1132.16, 1145.1, 1154.11, 1032.12, 975.41, 984.75, 938.38, 948.8, 991.64, 979.3, 937.0, 983.12, 904.28, 853.2, 848.95, 865.46, 970.82, 959.48, 990.21, 920.95, 900.2, 820.53, 739.0], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
       <c r="S15" t="n">
-        <v>820.53</v>
+        <v>739</v>
       </c>
       <c r="T15" t="n">
-        <v>77.43857683454242</v>
+        <v>78.66857474190849</v>
       </c>
       <c r="U15" t="n">
-        <v>26.25061192572861</v>
+        <v>29.09572912384758</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -1599,42 +1599,42 @@
         </is>
       </c>
       <c r="B16" t="n">
+        <v>53</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0.282</v>
+      </c>
+      <c r="E16" t="n">
         <v>54</v>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>DOWN</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>0.318</v>
-      </c>
-      <c r="E16" t="n">
-        <v>53</v>
-      </c>
       <c r="F16" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G16" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H16" t="n">
-        <v>-332</v>
+        <v>38</v>
       </c>
       <c r="I16" t="n">
-        <v>-6.6</v>
+        <v>0.8</v>
       </c>
       <c r="J16" t="n">
-        <v>-6.3</v>
+        <v>0.8</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>5000</v>
       </c>
       <c r="M16" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N16" t="n">
         <v>1</v>
@@ -1650,17 +1650,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [134.53, 123.1, 128.85, 136.01, 131.56, 129.57, 128.92, 131.85, 129.69, 129.66, 132.88, 124.39, 130.77, 141.79, 146.13, 135.11, 136.6, 128.35, 135.76, 142.16, 147.69, 146.28, 148.29, 164.85, 169.54, 170.98, 174.9, 172.56, 168.01, 165.83, 164.13, 165.13, 165.2, 168.5, 169.24, 175.62, 167.75, 152.82, 151.67, 163.99, 158.02, 159.72, 161.85, 181.29, 182.12, 186.65, 207.07, 197.94, 206.19, 207.96, 191.52, 178.28, 175.56, 180.41, 191.6, 193.75, 195.87, 190.6, 182.69, 181.16, 176.7, 200.4, 200.76, 197.7, 177.58, 187.54, 173.94, 168.17, 176.55, 179.2, 187.88, 177.42, 175.4, 194.92, 209.83, 194.07, 205.83, 228.01, 221.05, 255.69, 255.43, 220.63, 196.79, 194.8, 185.38, 184.03, 192.38, 190.89, 183.11, 187.64, 174.41, 158.39, 154.61, 153.1, 162.41, 154.06, 156.06, 146.65, 143.36, 126.01], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28', '2026-07-29'], 'prices': [123.1, 128.85, 136.01, 131.56, 129.57, 128.92, 131.85, 129.69, 129.66, 132.88, 124.39, 130.77, 141.79, 146.13, 135.11, 136.6, 128.35, 135.76, 142.16, 147.69, 146.28, 148.29, 164.85, 169.54, 170.98, 174.9, 172.56, 168.01, 165.83, 164.13, 165.13, 165.2, 168.5, 169.24, 175.62, 167.75, 152.82, 151.67, 163.99, 158.02, 159.72, 161.85, 181.29, 182.12, 186.65, 207.07, 197.94, 206.19, 207.96, 191.52, 178.28, 175.56, 180.41, 191.6, 193.75, 195.87, 190.6, 182.69, 181.16, 176.7, 200.4, 200.76, 197.7, 177.58, 187.54, 173.94, 168.17, 176.55, 179.2, 187.88, 177.42, 175.4, 194.92, 209.83, 194.07, 205.83, 228.01, 221.05, 255.69, 255.43, 220.63, 196.79, 194.8, 185.38, 184.03, 192.38, 190.89, 183.11, 187.64, 174.41, 158.39, 154.61, 153.1, 162.41, 154.06, 156.06, 146.65, 143.36, 126.01, 124.05], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
       <c r="S16" t="n">
-        <v>126.01</v>
+        <v>124.05</v>
       </c>
       <c r="T16" t="n">
-        <v>13.64000047956194</v>
+        <v>12.76857158115932</v>
       </c>
       <c r="U16" t="n">
-        <v>40.63643316345468</v>
+        <v>44.79458418939749</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -1683,28 +1683,28 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.699</v>
       </c>
       <c r="E17" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F17" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="G17" t="n">
-        <v>57.1</v>
+        <v>77.8</v>
       </c>
       <c r="H17" t="n">
-        <v>1894</v>
+        <v>829</v>
       </c>
       <c r="I17" t="n">
-        <v>37.9</v>
+        <v>16.6</v>
       </c>
       <c r="J17" t="n">
-        <v>70.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="K17" t="n">
-        <v>-32.7</v>
+        <v>-50.7</v>
       </c>
       <c r="L17" t="n">
         <v>5000</v>
@@ -1713,30 +1713,30 @@
         <v>27</v>
       </c>
       <c r="N17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O17" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="P17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.3</v>
+        <v>3.2</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [106.54, 107.25, 108.53, 109.08, 110.51, 110.39, 110.44, 105.96, 108.3, 108.95, 107.04, 102.25, 103.33, 98.25, 96.46, 98.15, 92.39, 95.01, 97.6, 98.33, 99.78, 99.65, 105.81, 106.63, 98.67, 94.75, 100.56, 99.62, 102.79, 104.55, 105.99, 108.29, 112.4, 116.67, 111.35, 112.03, 113.65, 113.75, 113.1, 111.44, 113.91, 117.31, 119.13, 117.02, 126.43, 131.94, 135.57, 136.54, 140.64, 144.99, 148.52, 154.71, 154.22, 162.53, 162.06, 165.87, 167.89, 161.34, 167.75, 182.75, 195.54, 192.24, 186.9, 179.77, 167.76, 164.7, 161.23, 161.93, 172.88, 170.7, 173.23, 169.87, 170.74, 171.21, 168.86, 170.23, 168.26, 169.66, 175.27, 185.73, 190.79, 193.18, 193.98, 199.38, 194.62, 191.12, 198.4, 187.18, 187.91, 210.73, 206.77, 203.76, 203.08, 198.49, 191.15, 188.42, 183.42, 183.28, 180.11, 181.8], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT']}</t>
+          <t>{'dates': ['2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28', '2026-07-29'], 'prices': [107.25, 108.53, 109.08, 110.51, 110.39, 110.44, 105.96, 108.3, 108.95, 107.04, 102.25, 103.33, 98.25, 96.46, 98.15, 92.39, 95.01, 97.6, 98.33, 99.78, 99.65, 105.81, 106.63, 98.67, 94.75, 100.56, 99.62, 102.79, 104.55, 105.99, 108.29, 112.4, 116.67, 111.35, 112.03, 113.65, 113.75, 113.1, 111.44, 113.91, 117.31, 119.13, 117.02, 126.43, 131.94, 135.57, 136.54, 140.64, 144.99, 148.52, 154.71, 154.22, 162.53, 162.06, 165.87, 167.89, 161.34, 167.75, 182.75, 195.54, 192.24, 186.9, 179.77, 167.76, 164.7, 161.23, 161.93, 172.88, 170.7, 173.23, 169.87, 170.74, 171.21, 168.86, 170.23, 168.26, 169.66, 175.27, 185.73, 190.79, 193.18, 193.98, 199.38, 194.62, 191.12, 198.4, 187.18, 187.91, 210.73, 206.77, 203.76, 203.08, 198.49, 191.15, 188.42, 183.42, 183.28, 180.11, 181.8, 179.38], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
       <c r="S17" t="n">
-        <v>181.8</v>
+        <v>179.38</v>
       </c>
       <c r="T17" t="n">
-        <v>10.44007001604353</v>
+        <v>10.31006949288505</v>
       </c>
       <c r="U17" t="n">
-        <v>27.9227001484601</v>
+        <v>24.26129923862345</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1759,28 +1759,28 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.308</v>
+        <v>0.186</v>
       </c>
       <c r="E18" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F18" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G18" t="n">
         <v>45</v>
       </c>
       <c r="H18" t="n">
-        <v>373</v>
+        <v>894</v>
       </c>
       <c r="I18" t="n">
-        <v>7.5</v>
+        <v>17.9</v>
       </c>
       <c r="J18" t="n">
-        <v>-19.1</v>
+        <v>-21.7</v>
       </c>
       <c r="K18" t="n">
-        <v>26.6</v>
+        <v>39.6</v>
       </c>
       <c r="L18" t="n">
         <v>5000</v>
@@ -1792,27 +1792,27 @@
         <v>4</v>
       </c>
       <c r="O18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P18" t="n">
         <v>4</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [152.67, 157.16, 156.43, 151.14, 151.6, 153.5, 150.95, 152.72, 155.08, 152.77, 155.68, 150.68, 160.84, 154.78, 154.96, 147.56, 143.06, 137.55, 146.28, 146.49, 148.46, 147.93, 150.07, 140.76, 130.49, 128.06, 132.37, 135.7, 142.15, 142.76, 146.39, 145.89, 145.97, 152.62, 141.57, 143.09, 143.1, 141.18, 137.97, 139.11, 144.07, 146.03, 135.91, 133.79, 137.05, 137.8, 136.89, 136.0, 130.05, 133.73, 133.99, 135.14, 135.26, 137.15, 137.41, 136.88, 136.6, 132.51, 143.34, 156.54, 160.65, 152.17, 142.2, 141.7, 135.53, 136.47, 132.07, 130.21, 131.08, 127.99, 134.71, 133.25, 130.63, 128.47, 119.5, 116.7, 113.5, 107.27, 112.93, 115.7, 116.67, 125.73, 129.3, 132.54, 134.37, 132.22, 129.04, 126.79, 130.04, 133.72, 133.76, 134.44, 132.38, 134.85, 132.66, 124.57, 123.37, 122.92, 131.53, 123.53], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT']}</t>
+          <t>{'dates': ['2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28', '2026-07-29'], 'prices': [157.16, 156.43, 151.14, 151.6, 153.5, 150.95, 152.72, 155.08, 152.77, 155.68, 150.68, 160.84, 154.78, 154.96, 147.56, 143.06, 137.55, 146.28, 146.49, 148.46, 147.93, 150.07, 140.76, 130.49, 128.06, 132.37, 135.7, 142.15, 142.76, 146.39, 145.89, 145.97, 152.62, 141.57, 143.09, 143.1, 141.18, 137.97, 139.11, 144.07, 146.03, 135.91, 133.79, 137.05, 137.8, 136.89, 136.0, 130.05, 133.73, 133.99, 135.14, 135.26, 137.15, 137.41, 136.88, 136.6, 132.51, 143.34, 156.54, 160.65, 152.17, 142.2, 141.7, 135.53, 136.47, 132.07, 130.21, 131.08, 127.99, 134.71, 133.25, 130.63, 128.47, 119.5, 116.7, 113.5, 107.27, 112.93, 115.7, 116.67, 125.73, 129.3, 132.54, 134.37, 132.22, 129.04, 126.79, 130.04, 133.72, 133.76, 134.44, 132.38, 134.85, 132.66, 124.57, 123.37, 122.92, 131.53, 123.53, 123.0], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
       <c r="S18" t="n">
-        <v>123.53</v>
+        <v>123</v>
       </c>
       <c r="T18" t="n">
-        <v>7.04071535382952</v>
+        <v>6.856429508754185</v>
       </c>
       <c r="U18" t="n">
-        <v>22.19321356384988</v>
+        <v>20.67152337632379</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1835,60 +1835,60 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.056</v>
+        <v>0.047</v>
       </c>
       <c r="E19" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F19" t="n">
         <v>40</v>
       </c>
       <c r="G19" t="n">
-        <v>46.7</v>
+        <v>50</v>
       </c>
       <c r="H19" t="n">
-        <v>-426</v>
+        <v>29</v>
       </c>
       <c r="I19" t="n">
-        <v>-8.5</v>
+        <v>0.6</v>
       </c>
       <c r="J19" t="n">
-        <v>-18.4</v>
+        <v>-18.8</v>
       </c>
       <c r="K19" t="n">
-        <v>9.9</v>
+        <v>19.4</v>
       </c>
       <c r="L19" t="n">
         <v>5000</v>
       </c>
       <c r="M19" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="N19" t="n">
+        <v>4</v>
+      </c>
+      <c r="O19" t="n">
         <v>3</v>
       </c>
-      <c r="O19" t="n">
-        <v>2</v>
-      </c>
       <c r="P19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [205.71, 197.22, 199.79, 196.52, 198.63, 193.23, 195.53, 203.32, 210.23, 202.29, 202.91, 197.5, 200.62, 181.04, 181.1, 173.38, 161.14, 160.79, 174.61, 172.99, 171.46, 174.79, 175.18, 175.09, 169.02, 167.85, 174.53, 184.41, 195.9, 199.83, 206.33, 211.63, 195.95, 206.24, 197.93, 199.77, 196.68, 194.1, 181.73, 187.77, 191.25, 202.99, 197.75, 197.96, 192.96, 201.16, 216.6, 207.64, 201.8, 212.01, 195.43, 189.44, 193.45, 191.29, 193.56, 184.99, 180.01, 173.78, 182.25, 189.03, 182.61, 173.99, 163.22, 164.13, 152.4, 162.11, 155.5, 153.97, 160.43, 159.78, 169.62, 169.27, 164.92, 163.26, 164.84, 158.18, 150.11, 142.52, 149.06, 151.65, 146.19, 159.24, 165.48, 168.87, 163.51, 159.36, 158.44, 159.07, 157.37, 161.5, 167.21, 160.49, 157.12, 160.43, 175.85, 166.12, 161.16, 158.29, 167.49, 167.9], 'signals': ['BUY', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+          <t>{'dates': ['2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28', '2026-07-29'], 'prices': [197.22, 199.79, 196.52, 198.63, 193.23, 195.53, 203.32, 210.23, 202.29, 202.91, 197.5, 200.62, 181.04, 181.1, 173.38, 161.14, 160.79, 174.61, 172.99, 171.46, 174.79, 175.18, 175.09, 169.02, 167.85, 174.53, 184.41, 195.9, 199.83, 206.33, 211.63, 195.95, 206.24, 197.93, 199.77, 196.68, 194.1, 181.73, 187.77, 191.25, 202.99, 197.75, 197.96, 192.96, 201.16, 216.6, 207.64, 201.8, 212.01, 195.43, 189.44, 193.45, 191.29, 193.56, 184.99, 180.01, 173.78, 182.25, 189.03, 182.61, 173.99, 163.22, 164.13, 152.4, 162.11, 155.5, 153.97, 160.43, 159.78, 169.62, 169.27, 164.92, 163.26, 164.84, 158.18, 150.11, 142.52, 149.06, 151.65, 146.19, 159.24, 165.48, 168.87, 163.51, 159.36, 158.44, 159.07, 157.37, 161.5, 167.21, 160.49, 157.12, 160.43, 175.85, 166.12, 161.16, 158.29, 167.49, 167.9, 160.09], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
       <c r="S19" t="n">
-        <v>167.9</v>
+        <v>160.09</v>
       </c>
       <c r="T19" t="n">
-        <v>9.024287632533483</v>
+        <v>9.362145560128349</v>
       </c>
       <c r="U19" t="n">
-        <v>17.05993620111895</v>
+        <v>17.56600669046751</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -1911,60 +1911,60 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.191</v>
+        <v>0.157</v>
       </c>
       <c r="E20" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F20" t="n">
         <v>70</v>
       </c>
       <c r="G20" t="n">
-        <v>65</v>
+        <v>57.9</v>
       </c>
       <c r="H20" t="n">
-        <v>2039</v>
+        <v>3759</v>
       </c>
       <c r="I20" t="n">
-        <v>40.8</v>
+        <v>75.2</v>
       </c>
       <c r="J20" t="n">
-        <v>77.40000000000001</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>-36.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="L20" t="n">
         <v>5000</v>
       </c>
       <c r="M20" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="N20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [95.65, 89.33, 94.94, 96.43, 112.0, 108.04, 112.95, 129.85, 116.33, 118.56, 121.52, 117.62, 114.15, 114.91, 115.09, 105.97, 100.82, 92.26, 103.76, 101.95, 108.82, 112.54, 117.4, 125.0, 136.33, 144.97, 154.56, 161.94, 166.77, 165.34, 157.14, 159.16, 156.55, 156.14, 157.08, 147.16, 144.96, 135.51, 141.19, 138.23, 154.49, 176.42, 175.92, 195.09, 184.77, 177.05, 186.1, 179.11, 207.27, 221.15, 219.94, 199.86, 197.73, 191.82, 219.93, 214.77, 208.06, 208.37, 226.34, 231.09, 264.51, 260.58, 251.68, 259.67, 227.81, 218.0, 220.12, 211.69, 222.24, 232.36, 260.07, 265.1, 280.91, 286.69, 283.61, 275.25, 259.66, 256.63, 240.3, 261.15, 276.17, 229.18, 215.62, 213.02, 195.19, 216.48, 216.2, 219.65, 210.51, 194.09, 199.51, 171.77, 177.71, 182.62, 216.92, 218.16, 220.97, 187.77, 187.88, 169.69], 'signals': ['FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28', '2026-07-29'], 'prices': [89.33, 94.94, 96.43, 112.0, 108.04, 112.95, 129.85, 116.33, 118.56, 121.52, 117.62, 114.15, 114.91, 115.09, 105.97, 100.82, 92.26, 103.76, 101.95, 108.82, 112.54, 117.4, 125.0, 136.33, 144.97, 154.56, 161.94, 166.77, 165.34, 157.14, 159.16, 156.55, 156.14, 157.08, 147.16, 144.96, 135.51, 141.19, 138.23, 154.49, 176.42, 175.92, 195.09, 184.77, 177.05, 186.1, 179.11, 207.27, 221.15, 219.94, 199.86, 197.73, 191.82, 219.93, 214.77, 208.06, 208.37, 226.34, 231.09, 264.51, 260.58, 251.68, 259.67, 227.81, 218.0, 220.12, 211.69, 222.24, 232.36, 260.07, 265.1, 280.91, 286.69, 283.61, 275.25, 259.66, 256.63, 240.3, 261.15, 276.17, 229.18, 215.62, 213.02, 195.19, 216.48, 216.2, 219.65, 210.51, 194.09, 199.51, 171.77, 177.71, 182.62, 216.92, 218.16, 220.97, 187.77, 187.88, 169.69, 148.22], 'signals': ['BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
       <c r="S20" t="n">
-        <v>169.69</v>
+        <v>148.22</v>
       </c>
       <c r="T20" t="n">
-        <v>22.5277829851423</v>
+        <v>23.1142828805106</v>
       </c>
       <c r="U20" t="n">
-        <v>19.93684147717601</v>
+        <v>23.3181811684695</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1987,64 +1987,64 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.438</v>
+        <v>0.451</v>
       </c>
       <c r="E21" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="F21" t="n">
         <v>30</v>
       </c>
       <c r="G21" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="H21" t="n">
-        <v>900</v>
+        <v>441</v>
       </c>
       <c r="I21" t="n">
-        <v>18</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>22.9</v>
+        <v>20.2</v>
       </c>
       <c r="K21" t="n">
-        <v>-4.9</v>
+        <v>-11.4</v>
       </c>
       <c r="L21" t="n">
         <v>5000</v>
       </c>
       <c r="M21" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O21" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="P21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [290.75, 286.71, 287.15, 285.97, 284.77, 280.19, 280.73, 283.43, 284.15, 284.99, 285.22, 283.82, 287.14, 289.61, 292.6, 288.87, 280.14, 281.06, 291.35, 292.56, 291.79, 294.12, 296.07, 306.59, 308.94, 308.48, 312.27, 309.72, 304.56, 308.56, 308.9, 315.57, 311.6, 311.62, 310.29, 306.9, 310.23, 310.05, 307.86, 311.83, 311.07, 306.27, 308.01, 313.49, 304.9, 300.75, 298.65, 303.51, 298.9, 298.57, 296.47, 299.38, 294.37, 300.63, 301.64, 305.01, 305.36, 297.94, 295.4, 297.97, 295.25, 299.61, 299.5, 309.5, 310.97, 309.71, 311.3, 307.75, 312.08, 319.28, 317.97, 329.65, 331.96, 323.76, 329.99, 332.64, 331.95, 333.62, 327.57, 327.91, 325.86, 332.57, 332.97, 337.72, 339.22, 330.62, 335.47, 336.47, 334.53, 342.89, 346.91, 343.15, 341.1, 338.87, 345.23, 348.21, 349.9, 353.21, 356.2, 357.31], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'SELL', 'BUY', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'BUY', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28', '2026-07-29'], 'prices': [286.71, 287.15, 285.97, 284.77, 280.19, 280.73, 283.43, 284.15, 284.99, 285.22, 283.82, 287.14, 289.61, 292.6, 288.87, 280.14, 281.06, 291.35, 292.56, 291.79, 294.12, 296.07, 306.59, 308.94, 308.48, 312.27, 309.72, 304.56, 308.56, 308.9, 315.57, 311.6, 311.62, 310.29, 306.9, 310.23, 310.05, 307.86, 311.83, 311.07, 306.27, 308.01, 313.49, 304.9, 300.75, 298.65, 303.51, 298.9, 298.57, 296.47, 299.38, 294.37, 300.63, 301.64, 305.01, 305.36, 297.94, 295.4, 297.97, 295.25, 299.61, 299.5, 309.5, 310.97, 309.71, 311.3, 307.75, 312.08, 319.28, 317.97, 329.65, 331.96, 323.76, 329.99, 332.64, 331.95, 333.62, 327.57, 327.91, 325.86, 332.57, 332.97, 337.72, 339.22, 330.62, 335.47, 336.47, 334.53, 342.89, 346.91, 343.15, 341.1, 338.87, 345.23, 348.21, 349.9, 353.21, 356.2, 357.31, 344.71], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'SELL', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'SELL', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
       <c r="S21" t="n">
-        <v>357.31</v>
+        <v>344.71</v>
       </c>
       <c r="T21" t="n">
-        <v>7.437859671456473</v>
+        <v>7.952859061104911</v>
       </c>
       <c r="U21" t="n">
-        <v>15.77726239631315</v>
+        <v>15.26003211212924</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>FLAT</t>
         </is>
       </c>
     </row>
@@ -2055,7 +2055,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2063,64 +2063,64 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.531</v>
+        <v>0.505</v>
       </c>
       <c r="E22" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F22" t="n">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="G22" t="n">
-        <v>68.40000000000001</v>
+        <v>55</v>
       </c>
       <c r="H22" t="n">
-        <v>426</v>
+        <v>353</v>
       </c>
       <c r="I22" t="n">
-        <v>8.5</v>
+        <v>7.1</v>
       </c>
       <c r="J22" t="n">
-        <v>24.2</v>
+        <v>19.9</v>
       </c>
       <c r="K22" t="n">
-        <v>-15.7</v>
+        <v>-12.8</v>
       </c>
       <c r="L22" t="n">
         <v>5000</v>
       </c>
       <c r="M22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N22" t="n">
         <v>4</v>
       </c>
       <c r="O22" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="P22" t="n">
         <v>4</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [831.79, 817.82, 828.38, 830.15, 820.15, 784.06, 778.78, 791.28, 803.5, 801.95, 805.95, 809.96, 827.62, 832.05, 838.15, 819.03, 799.37, 804.06, 842.28, 856.44, 859.25, 862.25, 860.36, 901.78, 899.75, 903.82, 886.88, 905.64, 895.54, 896.05, 921.89, 937.61, 922.48, 930.74, 927.21, 922.84, 933.7, 922.48, 901.63, 919.72, 919.66, 899.31, 914.86, 933.24, 921.81, 932.37, 940.71, 941.75, 951.23, 964.71, 944.31, 942.21, 924.66, 977.81, 983.83, 992.36, 990.16, 992.1, 1003.95, 1021.06, 1048.58, 1064.58, 1041.02, 1092.61, 1038.68, 1045.0, 1032.01, 1001.29, 1035.64, 1062.75, 1076.17, 1090.67, 1099.14, 1096.56, 1106.37, 1094.44, 1076.91, 1065.09, 1019.61, 1020.21, 1011.37, 1019.61, 1021.0, 1055.29, 1042.98, 1029.64, 1055.97, 1055.18, 1045.91, 1140.0, 1152.07, 1095.46, 1065.22, 1055.03, 1085.56, 1098.2, 1074.72, 1061.23, 1048.23, 1033.34], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'SELL', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28', '2026-07-29'], 'prices': [817.82, 828.38, 830.15, 820.15, 784.06, 778.78, 791.28, 803.5, 801.95, 805.95, 809.96, 827.62, 832.05, 838.15, 819.03, 799.37, 804.06, 842.28, 856.44, 859.25, 862.25, 860.36, 901.78, 899.75, 903.82, 886.88, 905.64, 895.54, 896.05, 921.89, 937.61, 922.48, 930.74, 927.21, 922.84, 933.7, 922.48, 901.63, 919.72, 919.66, 899.31, 914.86, 933.24, 921.81, 932.37, 940.71, 941.75, 951.23, 964.71, 944.31, 942.21, 924.66, 977.81, 983.83, 992.36, 990.16, 992.1, 1003.95, 1021.06, 1048.58, 1064.58, 1041.02, 1092.61, 1038.68, 1045.0, 1032.01, 1001.29, 1035.64, 1062.75, 1076.17, 1090.67, 1099.14, 1096.56, 1106.37, 1094.44, 1076.91, 1065.09, 1019.61, 1020.21, 1011.37, 1019.61, 1021.0, 1055.29, 1042.98, 1029.64, 1055.97, 1055.18, 1045.91, 1140.0, 1152.07, 1095.46, 1065.22, 1055.03, 1085.56, 1098.2, 1074.72, 1061.23, 1048.23, 1033.34, 980.75], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
       <c r="S22" t="n">
-        <v>1033.34</v>
+        <v>980.75</v>
       </c>
       <c r="T22" t="n">
-        <v>41.01998465401785</v>
+        <v>42.53926740373884</v>
       </c>
       <c r="U22" t="n">
-        <v>12.904634443049</v>
+        <v>13.90794299192742</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>FLAT</t>
         </is>
       </c>
     </row>
@@ -2131,36 +2131,36 @@
         </is>
       </c>
       <c r="B23" t="n">
+        <v>50</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0.388</v>
+      </c>
+      <c r="E23" t="n">
         <v>52</v>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>DOWN</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>0.408</v>
-      </c>
-      <c r="E23" t="n">
-        <v>51</v>
-      </c>
       <c r="F23" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G23" t="n">
         <v>50</v>
       </c>
       <c r="H23" t="n">
-        <v>525</v>
+        <v>194</v>
       </c>
       <c r="I23" t="n">
-        <v>10.5</v>
+        <v>3.9</v>
       </c>
       <c r="J23" t="n">
-        <v>14.9</v>
+        <v>16.4</v>
       </c>
       <c r="K23" t="n">
-        <v>-4.4</v>
+        <v>-12.5</v>
       </c>
       <c r="L23" t="n">
         <v>5000</v>
@@ -2169,34 +2169,34 @@
         <v>13</v>
       </c>
       <c r="N23" t="n">
+        <v>1</v>
+      </c>
+      <c r="O23" t="n">
         <v>2</v>
       </c>
-      <c r="O23" t="n">
-        <v>13</v>
-      </c>
       <c r="P23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [319.14, 316.7, 315.32, 313.78, 308.32, 305.87, 306.5, 309.47, 307.82, 298.4, 299.09, 301.0, 303.81, 303.13, 304.28, 304.9, 294.91, 298.92, 301.61, 297.89, 300.18, 302.7, 301.92, 308.32, 307.65, 303.73, 308.75, 310.73, 315.26, 314.45, 316.36, 313.29, 309.3, 310.65, 308.24, 308.78, 309.01, 308.66, 334.17, 329.16, 327.35, 326.17, 321.36, 318.14, 320.62, 318.13, 323.19, 326.42, 320.31, 322.52, 325.75, 332.64, 329.91, 330.75, 331.12, 328.88, 326.48, 327.61, 324.95, 326.36, 322.77, 317.32, 312.4, 320.18, 323.57, 319.67, 325.05, 322.96, 319.05, 322.39, 323.82, 333.12, 330.38, 327.24, 326.6, 328.48, 332.23, 330.52, 336.23, 341.65, 343.09, 351.08, 362.13, 357.25, 352.2, 347.53, 348.2, 348.97, 357.75, 356.02, 355.14, 365.14, 358.56, 360.57, 355.82, 353.42, 351.6, 355.74, 362.53, 366.59], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'SELL', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT']}</t>
+          <t>{'dates': ['2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28', '2026-07-29'], 'prices': [316.7, 315.32, 313.78, 308.32, 305.87, 306.5, 309.47, 307.82, 298.4, 299.09, 301.0, 303.81, 303.13, 304.28, 304.9, 294.91, 298.92, 301.61, 297.89, 300.18, 302.7, 301.92, 308.32, 307.65, 303.73, 308.75, 310.73, 315.26, 314.45, 316.36, 313.29, 309.3, 310.65, 308.24, 308.78, 309.01, 308.66, 334.17, 329.16, 327.35, 326.17, 321.36, 318.14, 320.62, 318.13, 323.19, 326.42, 320.31, 322.52, 325.75, 332.64, 329.91, 330.75, 331.12, 328.88, 326.48, 327.61, 324.95, 326.36, 322.77, 317.32, 312.4, 320.18, 323.57, 319.67, 325.05, 322.96, 319.05, 322.39, 323.82, 333.12, 330.38, 327.24, 326.6, 328.48, 332.23, 330.52, 336.23, 341.65, 343.09, 351.08, 362.13, 357.25, 352.2, 347.53, 348.2, 348.97, 357.75, 356.02, 355.14, 365.14, 358.56, 360.57, 355.82, 353.42, 351.6, 355.74, 362.53, 366.59, 368.73], 'signals': ['FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
       <c r="S23" t="n">
-        <v>366.59</v>
+        <v>368.73</v>
       </c>
       <c r="T23" t="n">
-        <v>7.151434762137277</v>
+        <v>8.180720738002233</v>
       </c>
       <c r="U23" t="n">
-        <v>36.99489980146108</v>
+        <v>35.61589859976169</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>FLAT</t>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -2207,7 +2207,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2215,28 +2215,28 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.529</v>
+        <v>0.569</v>
       </c>
       <c r="E24" t="n">
         <v>55</v>
       </c>
       <c r="F24" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="G24" t="n">
-        <v>50</v>
+        <v>37.5</v>
       </c>
       <c r="H24" t="n">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="I24" t="n">
         <v>10.7</v>
       </c>
       <c r="J24" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="L24" t="n">
         <v>5000</v>
@@ -2258,17 +2258,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [522.88, 520.57, 515.97, 512.98, 502.29, 495.63, 496.3, 506.78, 504.86, 486.82, 489.48, 494.64, 498.69, 497.24, 501.06, 499.05, 482.6, 492.33, 497.97, 489.99, 491.77, 499.8, 496.59, 505.4, 502.73, 497.83, 507.73, 512.3, 519.09, 517.67, 520.43, 515.79, 510.49, 509.31, 501.54, 503.33, 505.58, 506.77, 524.35, 502.08, 494.63, 503.9, 496.25, 491.07, 500.1, 494.65, 496.98, 498.97, 489.82, 489.12, 493.37, 504.94, 498.86, 497.21, 498.78, 497.71, 492.18, 494.21, 492.92, 493.15, 494.42, 476.88, 470.76, 480.95, 490.26, 484.86, 494.41, 488.26, 485.7, 489.16, 489.82, 500.49, 492.16, 488.97, 483.28, 487.25, 493.58, 488.1, 498.18, 508.79, 512.74, 521.57, 538.49, 532.21, 530.73, 518.99, 523.2, 526.74, 537.7, 538.02, 535.21, 551.54, 543.6, 547.44, 538.3, 531.98, 530.29, 539.66, 551.71, 562.75], 'signals': ['FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28', '2026-07-29'], 'prices': [520.57, 515.97, 512.98, 502.29, 495.63, 496.3, 506.78, 504.86, 486.82, 489.48, 494.64, 498.69, 497.24, 501.06, 499.05, 482.6, 492.33, 497.97, 489.99, 491.77, 499.8, 496.59, 505.4, 502.73, 497.83, 507.73, 512.3, 519.09, 517.67, 520.43, 515.79, 510.49, 509.31, 501.54, 503.33, 505.58, 506.77, 524.35, 502.08, 494.63, 503.9, 496.25, 491.07, 500.1, 494.65, 496.98, 498.97, 489.82, 489.12, 493.37, 504.94, 498.86, 497.21, 498.78, 497.71, 492.18, 494.21, 492.92, 493.15, 494.42, 476.88, 470.76, 480.95, 490.26, 484.86, 494.41, 488.26, 485.7, 489.16, 489.82, 500.49, 492.16, 488.97, 483.28, 487.25, 493.58, 488.1, 498.18, 508.79, 512.74, 521.57, 538.49, 532.21, 530.73, 518.99, 523.2, 526.74, 537.7, 538.02, 535.21, 551.54, 543.6, 547.44, 538.3, 531.98, 530.29, 539.66, 551.71, 562.75, 563.32], 'signals': ['FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
       <c r="S24" t="n">
-        <v>562.75</v>
+        <v>563.3200000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>11.26356724330357</v>
+        <v>11.75999668666295</v>
       </c>
       <c r="U24" t="n">
-        <v>36.03977279178041</v>
+        <v>38.7227335768313</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -2291,34 +2291,34 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.584</v>
+        <v>0.626</v>
       </c>
       <c r="E25" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F25" t="n">
         <v>60</v>
       </c>
       <c r="G25" t="n">
-        <v>58.3</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>806</v>
+        <v>979</v>
       </c>
       <c r="I25" t="n">
-        <v>16.1</v>
+        <v>19.6</v>
       </c>
       <c r="J25" t="n">
-        <v>27.1</v>
+        <v>26.2</v>
       </c>
       <c r="K25" t="n">
-        <v>-11</v>
+        <v>-6.6</v>
       </c>
       <c r="L25" t="n">
         <v>5000</v>
       </c>
       <c r="M25" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="N25" t="n">
         <v>2</v>
@@ -2334,21 +2334,21 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [49.27, 48.39, 47.65, 48.31, 48.27, 46.89, 46.48, 46.82, 47.04, 46.59, 46.77, 46.92, 47.27, 47.89, 48.5, 47.99, 46.73, 46.99, 48.5, 49.02, 49.12, 49.8, 50.02, 51.61, 52.44, 52.27, 53.07, 53.07, 54.04, 53.23, 53.63, 53.67, 53.2, 52.85, 52.2, 51.78, 52.36, 52.39, 52.61, 53.18, 52.96, 51.92, 52.85, 53.32, 52.48, 51.04, 50.29, 50.52, 49.58, 49.59, 49.51, 50.43, 50.44, 50.97, 51.22, 51.53, 51.93, 50.84, 50.51, 51.33, 51.24, 52.21, 52.13, 53.89, 53.83, 53.63, 54.42, 54.54, 55.16, 56.02, 55.87, 56.84, 56.53, 56.2, 57.37, 57.91, 57.73, 58.19, 57.88, 57.88, 56.98, 58.36, 58.73, 59.9, 59.86, 58.3, 59.25, 59.67, 59.5, 60.62, 61.59, 61.49, 61.27, 60.42, 61.22, 61.62, 61.28, 62.05, 62.13, 62.62], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'SELL', 'BUY', 'SELL']}</t>
+          <t>{'dates': ['2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28', '2026-07-29'], 'prices': [48.39, 47.65, 48.31, 48.27, 46.89, 46.48, 46.82, 47.04, 46.59, 46.77, 46.92, 47.27, 47.89, 48.5, 47.99, 46.73, 46.99, 48.5, 49.02, 49.12, 49.8, 50.02, 51.61, 52.44, 52.27, 53.07, 53.07, 54.04, 53.23, 53.63, 53.67, 53.2, 52.85, 52.2, 51.78, 52.36, 52.39, 52.61, 53.18, 52.96, 51.92, 52.85, 53.32, 52.48, 51.04, 50.29, 50.52, 49.58, 49.59, 49.51, 50.43, 50.44, 50.97, 51.22, 51.53, 51.93, 50.84, 50.51, 51.33, 51.24, 52.21, 52.13, 53.89, 53.83, 53.63, 54.42, 54.54, 55.16, 56.02, 55.87, 56.84, 56.53, 56.2, 57.37, 57.91, 57.73, 58.19, 57.88, 57.88, 56.98, 58.36, 58.73, 59.9, 59.86, 58.3, 59.25, 59.67, 59.5, 60.62, 61.59, 61.49, 61.27, 60.42, 61.22, 61.62, 61.28, 62.05, 62.13, 62.62, 61.07], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'SELL', 'BUY', 'SELL', 'BUY']}</t>
         </is>
       </c>
       <c r="S25" t="n">
-        <v>62.62</v>
+        <v>61.07</v>
       </c>
       <c r="T25" t="n">
-        <v>1.180000032697405</v>
+        <v>1.223571504865374</v>
       </c>
       <c r="U25" t="n">
-        <v>27.93985976792047</v>
+        <v>26.53735291364924</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
     </row>
@@ -2359,7 +2359,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -2367,64 +2367,64 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.227</v>
+        <v>0.205</v>
       </c>
       <c r="E26" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F26" t="n">
         <v>80</v>
       </c>
       <c r="G26" t="n">
-        <v>70</v>
+        <v>52.6</v>
       </c>
       <c r="H26" t="n">
-        <v>403</v>
+        <v>913</v>
       </c>
       <c r="I26" t="n">
-        <v>8.1</v>
+        <v>18.3</v>
       </c>
       <c r="J26" t="n">
-        <v>30.9</v>
+        <v>27.4</v>
       </c>
       <c r="K26" t="n">
-        <v>-22.8</v>
+        <v>-9.1</v>
       </c>
       <c r="L26" t="n">
         <v>5000</v>
       </c>
       <c r="M26" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O26" t="n">
         <v>1</v>
       </c>
       <c r="P26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [160.8, 158.54, 158.72, 159.02, 159.15, 152.7, 153.2, 154.02, 156.13, 157.22, 156.84, 159.73, 162.55, 164.08, 163.86, 161.47, 156.68, 156.66, 162.79, 164.38, 164.02, 164.75, 166.61, 174.12, 176.24, 175.72, 179.19, 181.36, 189.55, 185.3, 186.78, 188.64, 187.27, 188.99, 186.61, 186.04, 188.13, 188.31, 185.06, 189.55, 189.13, 186.98, 188.21, 192.29, 189.13, 192.03, 190.05, 190.83, 192.77, 193.47, 191.46, 191.64, 188.54, 196.69, 199.41, 199.93, 200.66, 200.51, 202.67, 206.86, 209.85, 213.8, 208.99, 217.08, 210.77, 211.08, 209.1, 205.53, 211.5, 212.87, 216.79, 219.62, 223.73, 221.95, 225.85, 224.79, 218.66, 219.83, 210.87, 210.56, 207.9, 210.7, 212.76, 220.88, 220.82, 216.88, 220.91, 221.06, 219.88, 226.42, 227.3, 217.17, 214.32, 209.79, 215.22, 217.3, 214.0, 213.31, 213.39, 210.42], 'signals': ['BUY', 'SELL', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+          <t>{'dates': ['2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28', '2026-07-29'], 'prices': [158.54, 158.72, 159.02, 159.15, 152.7, 153.2, 154.02, 156.13, 157.22, 156.84, 159.73, 162.55, 164.08, 163.86, 161.47, 156.68, 156.66, 162.79, 164.38, 164.02, 164.75, 166.61, 174.12, 176.24, 175.72, 179.19, 181.36, 189.55, 185.3, 186.78, 188.64, 187.27, 188.99, 186.61, 186.04, 188.13, 188.31, 185.06, 189.55, 189.13, 186.98, 188.21, 192.29, 189.13, 192.03, 190.05, 190.83, 192.77, 193.47, 191.46, 191.64, 188.54, 196.69, 199.41, 199.93, 200.66, 200.51, 202.67, 206.86, 209.85, 213.8, 208.99, 217.08, 210.77, 211.08, 209.1, 205.53, 211.5, 212.87, 216.79, 219.62, 223.73, 221.95, 225.85, 224.79, 218.66, 219.83, 210.87, 210.56, 207.9, 210.7, 212.76, 220.88, 220.82, 216.88, 220.91, 221.06, 219.88, 226.42, 227.3, 217.17, 214.32, 209.79, 215.22, 217.3, 214.0, 213.31, 213.39, 210.42, 202.02], 'signals': ['FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY']}</t>
         </is>
       </c>
       <c r="S26" t="n">
-        <v>210.42</v>
+        <v>202.02</v>
       </c>
       <c r="T26" t="n">
-        <v>7.563363625770892</v>
+        <v>7.77931867899251</v>
       </c>
       <c r="U26" t="n">
-        <v>12.33764110610651</v>
+        <v>15.12562781426063</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>FLAT</t>
+          <t>BUY</t>
         </is>
       </c>
     </row>
@@ -2435,36 +2435,36 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">UP  </t>
+          <t>DOWN</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.549</v>
+        <v>0.319</v>
       </c>
       <c r="E27" t="n">
         <v>50</v>
       </c>
       <c r="F27" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H27" t="n">
-        <v>317</v>
+        <v>398</v>
       </c>
       <c r="I27" t="n">
-        <v>6.3</v>
+        <v>8</v>
       </c>
       <c r="J27" t="n">
-        <v>24.4</v>
+        <v>22.4</v>
       </c>
       <c r="K27" t="n">
-        <v>-18.1</v>
+        <v>-14.4</v>
       </c>
       <c r="L27" t="n">
         <v>5000</v>
@@ -2486,17 +2486,17 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [981.57, 988.63, 1006.66, 999.63, 998.12, 975.57, 983.39, 987.42, 928.75, 916.47, 915.92, 905.14, 908.99, 901.47, 914.74, 895.46, 876.73, 885.11, 918.19, 952.88, 933.97, 925.47, 929.49, 951.66, 953.55, 937.86, 927.95, 920.91, 903.47, 902.44, 925.44, 918.32, 901.47, 919.9, 916.07, 882.44, 866.78, 872.5, 849.75, 932.99, 961.67, 966.27, 987.17, 985.35, 973.28, 946.82, 965.33, 988.17, 1014.0, 1004.97, 1004.92, 988.09, 1021.41, 1018.87, 1041.65, 1065.0, 1064.74, 1082.92, 1126.8, 1105.0, 1082.2, 1064.15, 1078.78, 1125.27, 1131.42, 1149.15, 1144.68, 1136.37, 1160.95, 1133.0, 1129.35, 1122.5, 1112.0, 1098.57, 1102.08, 1107.08, 1117.26, 1127.69, 1208.12, 1229.93, 1199.43, 1191.74, 1213.91, 1200.06, 1235.56, 1215.83, 1216.95, 1188.58, 1181.87, 1152.54, 1156.63, 1169.17, 1179.11, 1146.9, 1175.41, 1163.01, 1185.87, 1196.03, 1197.53, 1220.66], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+          <t>{'dates': ['2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28', '2026-07-29'], 'prices': [988.63, 1006.66, 999.63, 998.12, 975.57, 983.39, 987.42, 928.75, 916.47, 915.92, 905.14, 908.99, 901.47, 914.74, 895.46, 876.73, 885.11, 918.19, 952.88, 933.97, 925.47, 929.49, 951.66, 953.55, 937.86, 927.95, 920.91, 903.47, 902.44, 925.44, 918.32, 901.47, 919.9, 916.07, 882.44, 866.78, 872.5, 849.75, 932.99, 961.67, 966.27, 987.17, 985.35, 973.28, 946.82, 965.33, 988.17, 1014.0, 1004.97, 1004.92, 988.09, 1021.41, 1018.87, 1041.65, 1065.0, 1064.74, 1082.92, 1126.8, 1105.0, 1082.2, 1064.15, 1078.78, 1125.27, 1131.42, 1149.15, 1144.68, 1136.37, 1160.95, 1133.0, 1129.35, 1122.5, 1112.0, 1098.57, 1102.08, 1107.08, 1117.26, 1127.69, 1208.12, 1229.93, 1199.43, 1191.74, 1213.91, 1200.06, 1235.56, 1215.83, 1216.95, 1188.58, 1181.87, 1152.54, 1156.63, 1169.17, 1179.11, 1146.9, 1175.41, 1163.01, 1185.87, 1196.03, 1197.53, 1220.66, 1210.02], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
       <c r="S27" t="n">
-        <v>1220.66</v>
+        <v>1210.02</v>
       </c>
       <c r="T27" t="n">
-        <v>34.21641322544643</v>
+        <v>33.84211948939732</v>
       </c>
       <c r="U27" t="n">
-        <v>15.94042271560643</v>
+        <v>14.20074607042792</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
@@ -2511,36 +2511,36 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">UP  </t>
+          <t>DOWN</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.51</v>
+        <v>0.453</v>
       </c>
       <c r="E28" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="F28" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G28" t="n">
-        <v>68.40000000000001</v>
+        <v>61.1</v>
       </c>
       <c r="H28" t="n">
-        <v>729</v>
+        <v>1010</v>
       </c>
       <c r="I28" t="n">
-        <v>14.6</v>
+        <v>20.2</v>
       </c>
       <c r="J28" t="n">
-        <v>50.5</v>
+        <v>48.8</v>
       </c>
       <c r="K28" t="n">
-        <v>-35.9</v>
+        <v>-28.6</v>
       </c>
       <c r="L28" t="n">
         <v>5000</v>
@@ -2549,34 +2549,34 @@
         <v>11</v>
       </c>
       <c r="N28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [284.92, 282.66, 283.55, 280.74, 283.63, 275.48, 280.49, 283.87, 285.94, 282.72, 278.85, 274.02, 268.01, 270.73, 269.01, 266.53, 257.55, 260.3, 269.05, 272.42, 275.69, 279.76, 305.98, 304.24, 305.17, 302.6, 311.22, 312.41, 312.27, 314.6, 322.79, 321.64, 344.05, 351.51, 352.55, 352.9, 352.68, 364.69, 368.63, 368.38, 366.69, 368.64, 361.8, 365.19, 367.64, 377.82, 382.26, 394.14, 398.88, 396.82, 391.61, 388.91, 387.03, 381.12, 380.31, 386.26, 374.72, 381.83, 380.36, 378.15, 377.7, 375.77, 374.86, 394.22, 397.2, 404.26, 410.65, 405.15, 403.25, 406.2, 411.04, 407.65, 399.53, 400.96, 406.68, 409.25, 405.8, 415.53, 427.89, 419.82, 415.63, 426.54, 425.36, 417.99, 428.19, 425.6, 431.68, 424.62, 429.09, 425.19, 418.52, 423.38, 426.09, 421.55, 436.35, 431.31, 423.56, 420.74, 417.64, 428.79], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28', '2026-07-29'], 'prices': [282.66, 283.55, 280.74, 283.63, 275.48, 280.49, 283.87, 285.94, 282.72, 278.85, 274.02, 268.01, 270.73, 269.01, 266.53, 257.55, 260.3, 269.05, 272.42, 275.69, 279.76, 305.98, 304.24, 305.17, 302.6, 311.22, 312.41, 312.27, 314.6, 322.79, 321.64, 344.05, 351.51, 352.55, 352.9, 352.68, 364.69, 368.63, 368.38, 366.69, 368.64, 361.8, 365.19, 367.64, 377.82, 382.26, 394.14, 398.88, 396.82, 391.61, 388.91, 387.03, 381.12, 380.31, 386.26, 374.72, 381.83, 380.36, 378.15, 377.7, 375.77, 374.86, 394.22, 397.2, 404.26, 410.65, 405.15, 403.25, 406.2, 411.04, 407.65, 399.53, 400.96, 406.68, 409.25, 405.8, 415.53, 427.89, 419.82, 415.63, 426.54, 425.36, 417.99, 428.19, 425.6, 431.68, 424.62, 429.09, 425.19, 418.52, 423.38, 426.09, 421.55, 436.35, 431.31, 423.56, 420.74, 417.64, 428.79, 420.57], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
       <c r="S28" t="n">
-        <v>428.79</v>
+        <v>420.57</v>
       </c>
       <c r="T28" t="n">
-        <v>13.48285348074777</v>
+        <v>13.52213832310268</v>
       </c>
       <c r="U28" t="n">
-        <v>34.94767114622746</v>
+        <v>32.74090393722857</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>FLAT</t>
         </is>
       </c>
     </row>
@@ -2587,7 +2587,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -2595,28 +2595,28 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.474</v>
+        <v>0.469</v>
       </c>
       <c r="E29" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F29" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G29" t="n">
-        <v>60</v>
+        <v>52.6</v>
       </c>
       <c r="H29" t="n">
-        <v>488</v>
+        <v>260</v>
       </c>
       <c r="I29" t="n">
-        <v>9.800000000000001</v>
+        <v>5.2</v>
       </c>
       <c r="J29" t="n">
-        <v>11.9</v>
+        <v>11.1</v>
       </c>
       <c r="K29" t="n">
-        <v>-2.1</v>
+        <v>-5.9</v>
       </c>
       <c r="L29" t="n">
         <v>5000</v>
@@ -2628,31 +2628,31 @@
         <v>3</v>
       </c>
       <c r="O29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P29" t="n">
         <v>3</v>
       </c>
       <c r="Q29" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [238.26, 239.03, 241.2, 242.32, 241.6, 240.66, 240.14, 241.8, 236.75, 235.92, 236.24, 234.02, 234.07, 233.92, 238.56, 237.87, 239.08, 241.1, 243.04, 242.72, 241.65, 239.59, 237.05, 239.92, 239.93, 237.1, 236.6, 238.73, 237.31, 233.2, 232.84, 229.37, 224.87, 224.81, 229.33, 226.2, 224.05, 226.49, 226.05, 228.54, 225.89, 222.92, 224.26, 223.34, 221.24, 220.05, 220.16, 222.98, 229.1, 229.48, 225.41, 227.61, 228.68, 228.01, 230.4, 233.0, 230.18, 231.29, 230.8, 225.33, 223.51, 222.89, 223.24, 228.17, 232.77, 232.16, 237.0, 238.49, 238.33, 240.87, 235.66, 235.18, 234.2, 228.39, 231.29, 239.08, 241.0, 244.88, 254.66, 258.51, 253.97, 253.98, 263.04, 259.33, 267.24, 263.4, 259.1, 256.98, 257.77, 253.85, 247.02, 249.97, 253.04, 248.82, 250.61, 255.63, 259.27, 263.4, 265.95, 266.73], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28', '2026-07-29'], 'prices': [239.03, 241.2, 242.32, 241.6, 240.66, 240.14, 241.8, 236.75, 235.92, 236.24, 234.02, 234.07, 233.92, 238.56, 237.87, 239.08, 241.1, 243.04, 242.72, 241.65, 239.59, 237.05, 239.92, 239.93, 237.1, 236.6, 238.73, 237.31, 233.2, 232.84, 229.37, 224.87, 224.81, 229.33, 226.2, 224.05, 226.49, 226.05, 228.54, 225.89, 222.92, 224.26, 223.34, 221.24, 220.05, 220.16, 222.98, 229.1, 229.48, 225.41, 227.61, 228.68, 228.01, 230.4, 233.0, 230.18, 231.29, 230.8, 225.33, 223.51, 222.89, 223.24, 228.17, 232.77, 232.16, 237.0, 238.49, 238.33, 240.87, 235.66, 235.18, 234.2, 228.39, 231.29, 239.08, 241.0, 244.88, 254.66, 258.51, 253.97, 253.98, 263.04, 259.33, 267.24, 263.4, 259.1, 256.98, 257.77, 253.85, 247.02, 249.97, 253.04, 248.82, 250.61, 255.63, 259.27, 263.4, 265.95, 266.73, 265.53], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT']}</t>
         </is>
       </c>
       <c r="S29" t="n">
-        <v>266.73</v>
+        <v>265.53</v>
       </c>
       <c r="T29" t="n">
-        <v>6.252138410295759</v>
+        <v>6.197137015206473</v>
       </c>
       <c r="U29" t="n">
-        <v>19.45697595859658</v>
+        <v>18.33651305217017</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>FLAT</t>
         </is>
       </c>
     </row>
@@ -2671,28 +2671,28 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.673</v>
+        <v>0.748</v>
       </c>
       <c r="E30" t="n">
         <v>51</v>
       </c>
       <c r="F30" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="G30" t="n">
-        <v>55</v>
+        <v>61.1</v>
       </c>
       <c r="H30" t="n">
-        <v>681</v>
+        <v>408</v>
       </c>
       <c r="I30" t="n">
-        <v>13.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J30" t="n">
-        <v>15</v>
+        <v>16.2</v>
       </c>
       <c r="K30" t="n">
-        <v>-1.4</v>
+        <v>-8</v>
       </c>
       <c r="L30" t="n">
         <v>5000</v>
@@ -2701,34 +2701,34 @@
         <v>18</v>
       </c>
       <c r="N30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O30" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [228.81, 226.6, 223.98, 223.55, 224.21, 221.94, 216.33, 218.08, 216.41, 205.17, 203.09, 201.95, 201.81, 202.07, 204.02, 207.9, 206.21, 209.87, 214.18, 211.7, 205.66, 203.54, 203.23, 208.37, 209.16, 204.77, 203.32, 207.06, 206.95, 207.51, 206.91, 202.27, 203.67, 199.08, 199.53, 197.31, 195.99, 196.29, 202.45, 209.83, 205.14, 206.69, 204.65, 203.58, 201.28, 200.13, 201.35, 206.39, 207.03, 209.28, 208.9, 207.93, 212.25, 210.8, 212.98, 214.18, 211.61, 213.88, 217.08, 216.18, 211.43, 213.88, 215.6, 223.35, 225.62, 221.49, 223.83, 223.36, 223.18, 226.12, 220.02, 220.9, 219.67, 214.96, 228.38, 233.1, 233.23, 241.42, 251.56, 252.51, 249.86, 249.29, 259.22, 252.96, 252.85, 250.95, 248.14, 246.33, 246.25, 243.05, 244.11, 254.39, 254.49, 253.38, 256.1, 253.3, 256.92, 259.36, 256.91, 263.2], 'signals': ['FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'SELL', 'BUY', 'SELL', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT']}</t>
+          <t>{'dates': ['2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28', '2026-07-29'], 'prices': [226.6, 223.98, 223.55, 224.21, 221.94, 216.33, 218.08, 216.41, 205.17, 203.09, 201.95, 201.81, 202.07, 204.02, 207.9, 206.21, 209.87, 214.18, 211.7, 205.66, 203.54, 203.23, 208.37, 209.16, 204.77, 203.32, 207.06, 206.95, 207.51, 206.91, 202.27, 203.67, 199.08, 199.53, 197.31, 195.99, 196.29, 202.45, 209.83, 205.14, 206.69, 204.65, 203.58, 201.28, 200.13, 201.35, 206.39, 207.03, 209.28, 208.9, 207.93, 212.25, 210.8, 212.98, 214.18, 211.61, 213.88, 217.08, 216.18, 211.43, 213.88, 215.6, 223.35, 225.62, 221.49, 223.83, 223.36, 223.18, 226.12, 220.02, 220.9, 219.67, 214.96, 228.38, 233.1, 233.23, 241.42, 251.56, 252.51, 249.86, 249.29, 259.22, 252.96, 252.85, 250.95, 248.14, 246.33, 246.25, 243.05, 244.11, 254.39, 254.49, 253.38, 256.1, 253.3, 256.92, 259.36, 256.91, 263.2, 263.3], 'signals': ['BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
       <c r="S30" t="n">
-        <v>263.2</v>
+        <v>263.3</v>
       </c>
       <c r="T30" t="n">
-        <v>5.943890991012275</v>
+        <v>5.793073158790757</v>
       </c>
       <c r="U30" t="n">
-        <v>36.32423643145558</v>
+        <v>39.81020353644736</v>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>FLAT</t>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -2747,60 +2747,60 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.59</v>
+        <v>0.698</v>
       </c>
       <c r="E31" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F31" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1078</v>
+        <v>1034</v>
       </c>
       <c r="I31" t="n">
-        <v>21.6</v>
+        <v>20.7</v>
       </c>
       <c r="J31" t="n">
-        <v>15.2</v>
+        <v>14.2</v>
       </c>
       <c r="K31" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="L31" t="n">
         <v>5000</v>
       </c>
       <c r="M31" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="N31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O31" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="P31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q31" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [114.39, 114.12, 115.42, 115.4, 114.53, 114.24, 113.94, 114.61, 115.04, 113.68, 113.38, 113.36, 114.85, 115.54, 118.52, 118.08, 118.78, 117.26, 119.43, 119.98, 120.01, 119.99, 118.43, 122.3, 121.8, 120.55, 119.29, 119.1, 117.06, 114.64, 118.22, 116.26, 111.76, 112.08, 113.8, 111.1, 109.44, 109.24, 110.16, 108.4, 111.36, 112.3, 112.34, 112.75, 111.5, 110.58, 110.49, 111.57, 112.64, 112.6, 110.58, 111.76, 113.42, 112.19, 115.05, 121.54, 118.87, 119.38, 119.03, 117.87, 114.35, 114.82, 113.88, 119.4, 119.93, 118.67, 118.75, 118.24, 119.9, 118.2, 114.9, 115.17, 115.44, 113.87, 115.48, 119.6, 120.6, 125.45, 128.66, 129.38, 128.5, 125.37, 129.56, 126.78, 128.86, 125.99, 125.07, 123.54, 124.03, 120.78, 123.61, 127.63, 127.5, 124.4, 126.26, 127.47, 130.48, 131.07, 130.76, 131.82], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28', '2026-07-29'], 'prices': [114.12, 115.42, 115.4, 114.53, 114.24, 113.94, 114.61, 115.04, 113.68, 113.38, 113.36, 114.85, 115.54, 118.52, 118.08, 118.78, 117.26, 119.43, 119.98, 120.01, 119.99, 118.43, 122.3, 121.8, 120.55, 119.29, 119.1, 117.06, 114.64, 118.22, 116.26, 111.76, 112.08, 113.8, 111.1, 109.44, 109.24, 110.16, 108.4, 111.36, 112.3, 112.34, 112.75, 111.5, 110.58, 110.49, 111.57, 112.64, 112.6, 110.58, 111.76, 113.42, 112.19, 115.05, 121.54, 118.87, 119.38, 119.03, 117.87, 114.35, 114.82, 113.88, 119.4, 119.93, 118.67, 118.75, 118.24, 119.9, 118.2, 114.9, 115.17, 115.44, 113.87, 115.48, 119.6, 120.6, 125.45, 128.66, 129.38, 128.5, 125.37, 129.56, 126.78, 128.86, 125.99, 125.07, 123.54, 124.03, 120.78, 123.61, 127.63, 127.5, 124.4, 126.26, 127.47, 130.48, 131.07, 130.76, 131.82, 130.36], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
       <c r="S31" t="n">
-        <v>131.82</v>
+        <v>130.36</v>
       </c>
       <c r="T31" t="n">
-        <v>3.351428440638951</v>
+        <v>3.309999738420759</v>
       </c>
       <c r="U31" t="n">
-        <v>17.87088936336508</v>
+        <v>19.55671569331611</v>
       </c>
       <c r="V31" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -2823,28 +2823,28 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.619</v>
+        <v>0.599</v>
       </c>
       <c r="E32" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F32" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-23</v>
+        <v>-493</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.5</v>
+        <v>-9.9</v>
       </c>
       <c r="J32" t="n">
-        <v>-24.2</v>
+        <v>-24.8</v>
       </c>
       <c r="K32" t="n">
-        <v>23.7</v>
+        <v>14.9</v>
       </c>
       <c r="L32" t="n">
         <v>5000</v>
@@ -2853,30 +2853,30 @@
         <v>16</v>
       </c>
       <c r="N32" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O32" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="P32" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.6</v>
+        <v>4</v>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [405.55, 396.73, 398.68, 399.24, 407.82, 395.01, 391.2, 395.56, 399.27, 392.78, 380.3, 367.96, 380.85, 383.03, 385.95, 372.11, 361.83, 355.28, 371.75, 381.26, 360.59, 352.82, 346.65, 343.25, 345.62, 348.95, 352.42, 364.2, 391.95, 388.9, 400.62, 392.5, 386.42, 387.51, 373.72, 376.3, 378.67, 376.02, 372.8, 381.63, 390.82, 392.51, 389.37, 398.73, 411.79, 428.35, 445.0, 433.45, 445.27, 443.3, 422.24, 409.99, 404.11, 417.26, 417.85, 426.01, 433.59, 440.36, 442.1, 435.79, 415.88, 423.74, 423.7, 418.45, 391.0, 408.95, 396.68, 381.59, 399.15, 406.43, 411.15, 404.66, 396.38, 400.49, 405.05, 381.61, 375.53, 375.12, 379.71, 411.84, 420.6, 425.3, 393.45, 419.77, 402.9, 394.06, 406.55, 407.76, 394.76, 396.18, 394.46, 391.06, 380.84, 369.57, 378.93, 374.01, 319.69, 313.03, 309.22, 307.44], 'signals': ['FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28', '2026-07-29'], 'prices': [396.73, 398.68, 399.24, 407.82, 395.01, 391.2, 395.56, 399.27, 392.78, 380.3, 367.96, 380.85, 383.03, 385.95, 372.11, 361.83, 355.28, 371.75, 381.26, 360.59, 352.82, 346.65, 343.25, 345.62, 348.95, 352.42, 364.2, 391.95, 388.9, 400.62, 392.5, 386.42, 387.51, 373.72, 376.3, 378.67, 376.02, 372.8, 381.63, 390.82, 392.51, 389.37, 398.73, 411.79, 428.35, 445.0, 433.45, 445.27, 443.3, 422.24, 409.99, 404.11, 417.26, 417.85, 426.01, 433.59, 440.36, 442.1, 435.79, 415.88, 423.74, 423.7, 418.45, 391.0, 408.95, 396.68, 381.59, 399.15, 406.43, 411.15, 404.66, 396.38, 400.49, 405.05, 381.61, 375.53, 375.12, 379.71, 411.84, 420.6, 425.3, 393.45, 419.77, 402.9, 394.06, 406.55, 407.76, 394.76, 396.18, 394.46, 391.06, 380.84, 369.57, 378.93, 374.01, 319.69, 313.03, 309.22, 307.44, 298.32], 'signals': ['BUY', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
       <c r="S32" t="n">
-        <v>307.44</v>
+        <v>298.32</v>
       </c>
       <c r="T32" t="n">
-        <v>16.27285766601562</v>
+        <v>15.89285714285714</v>
       </c>
       <c r="U32" t="n">
-        <v>44.81763149270454</v>
+        <v>49.98737132746758</v>
       </c>
       <c r="V32" t="inlineStr">
         <is>
@@ -2891,36 +2891,36 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>DOWN</t>
+          <t xml:space="preserve">UP  </t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.237</v>
+        <v>0.77</v>
       </c>
       <c r="E33" t="n">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="F33" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="G33" t="n">
-        <v>25</v>
+        <v>62.5</v>
       </c>
       <c r="H33" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>-3.4</v>
+        <v>-4.1</v>
       </c>
       <c r="K33" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="L33" t="n">
         <v>5000</v>
@@ -2929,30 +2929,30 @@
         <v>14</v>
       </c>
       <c r="N33" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [356.6, 352.9, 348.6, 352.14, 345.92, 336.41, 336.51, 340.03, 338.89, 328.47, 325.77, 318.36, 328.44, 328.45, 330.03, 325.98, 319.26, 321.09, 326.44, 327.11, 319.24, 324.22, 316.4, 333.66, 337.05, 334.83, 338.62, 340.16, 336.39, 334.64, 346.8, 348.38, 341.36, 336.97, 337.63, 333.39, 329.83, 326.61, 320.41, 326.35, 321.47, 310.09, 313.07, 320.64, 320.24, 315.09, 309.08, 308.15, 300.3, 302.08, 295.3, 297.58, 300.19, 308.27, 311.44, 310.74, 308.23, 315.48, 318.82, 314.78, 308.38, 309.2, 310.64, 309.95, 310.78, 309.71, 321.33, 318.92, 326.01, 328.39, 329.82, 337.09, 327.48, 334.28, 326.62, 324.45, 342.86, 345.0, 348.86, 350.81, 352.68, 350.84, 357.9, 350.65, 345.21, 336.21, 338.73, 343.3, 337.11, 337.74, 341.44, 348.02, 338.87, 333.04, 331.6, 331.45, 324.71, 332.98, 336.09, 344.47], 'signals': ['BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+          <t>{'dates': ['2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28', '2026-07-29'], 'prices': [352.9, 348.6, 352.14, 345.92, 336.41, 336.51, 340.03, 338.89, 328.47, 325.77, 318.36, 328.44, 328.45, 330.03, 325.98, 319.26, 321.09, 326.44, 327.11, 319.24, 324.22, 316.4, 333.66, 337.05, 334.83, 338.62, 340.16, 336.39, 334.64, 346.8, 348.38, 341.36, 336.97, 337.63, 333.39, 329.83, 326.61, 320.41, 326.35, 321.47, 310.09, 313.07, 320.64, 320.24, 315.09, 309.08, 308.15, 300.3, 302.08, 295.3, 297.58, 300.19, 308.27, 311.44, 310.74, 308.23, 315.48, 318.82, 314.78, 308.38, 309.2, 310.64, 309.95, 310.78, 309.71, 321.33, 318.92, 326.01, 328.39, 329.82, 337.09, 327.48, 334.28, 326.62, 324.45, 342.86, 345.0, 348.86, 350.81, 352.68, 350.84, 357.9, 350.65, 345.21, 336.21, 338.73, 343.3, 337.11, 337.74, 341.44, 348.02, 338.87, 333.04, 331.6, 331.45, 324.71, 332.98, 336.09, 344.47, 338.27], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
       <c r="S33" t="n">
-        <v>344.47</v>
+        <v>338.27</v>
       </c>
       <c r="T33" t="n">
-        <v>8.792144775390625</v>
+        <v>9.01999991280692</v>
       </c>
       <c r="U33" t="n">
-        <v>18.53730862647758</v>
+        <v>18.79077796570979</v>
       </c>
       <c r="V33" t="inlineStr">
         <is>
@@ -2967,7 +2967,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -2975,28 +2975,28 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0.623</v>
+        <v>0.676</v>
       </c>
       <c r="E34" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F34" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="G34" t="n">
-        <v>38.9</v>
+        <v>29.4</v>
       </c>
       <c r="H34" t="n">
-        <v>-324</v>
+        <v>-253</v>
       </c>
       <c r="I34" t="n">
-        <v>-6.5</v>
+        <v>-5.1</v>
       </c>
       <c r="J34" t="n">
-        <v>-16.1</v>
+        <v>-16.7</v>
       </c>
       <c r="K34" t="n">
-        <v>9.6</v>
+        <v>11.6</v>
       </c>
       <c r="L34" t="n">
         <v>5000</v>
@@ -3005,30 +3005,30 @@
         <v>18</v>
       </c>
       <c r="N34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q34" t="n">
         <v>1</v>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [325.24, 325.85, 328.57, 325.73, 323.02, 321.73, 324.26, 324.45, 324.1, 313.6, 307.49, 306.77, 306.39, 305.77, 309.6, 306.85, 303.84, 306.45, 308.7, 305.22, 305.07, 307.67, 302.8, 304.94, 307.46, 303.62, 302.46, 301.18, 304.2, 304.89, 309.26, 304.87, 299.81, 298.05, 300.49, 297.34, 288.26, 290.42, 288.13, 291.61, 284.71, 282.19, 283.25, 282.19, 281.79, 273.89, 272.75, 272.99, 273.84, 273.12, 274.53, 280.57, 278.91, 278.38, 282.27, 280.37, 277.38, 279.03, 276.1, 277.32, 274.25, 276.36, 273.29, 272.72, 279.84, 277.78, 282.25, 282.52, 284.77, 284.81, 286.12, 287.93, 283.82, 278.61, 270.1, 271.66, 273.88, 264.54, 269.76, 267.18, 270.31, 269.43, 280.63, 279.5, 282.21, 278.25, 276.49, 274.6, 272.61, 268.94, 264.95, 273.46, 267.71, 267.64, 263.91, 263.57, 262.8, 264.76, 270.67, 273.02], 'signals': ['BUY', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+          <t>{'dates': ['2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28', '2026-07-29'], 'prices': [325.85, 328.57, 325.73, 323.02, 321.73, 324.26, 324.45, 324.1, 313.6, 307.49, 306.77, 306.39, 305.77, 309.6, 306.85, 303.84, 306.45, 308.7, 305.22, 305.07, 307.67, 302.8, 304.94, 307.46, 303.62, 302.46, 301.18, 304.2, 304.89, 309.26, 304.87, 299.81, 298.05, 300.49, 297.34, 288.26, 290.42, 288.13, 291.61, 284.71, 282.19, 283.25, 282.19, 281.79, 273.89, 272.75, 272.99, 273.84, 273.12, 274.53, 280.57, 278.91, 278.38, 282.27, 280.37, 277.38, 279.03, 276.1, 277.32, 274.25, 276.36, 273.29, 272.72, 279.84, 277.78, 282.25, 282.52, 284.77, 284.81, 286.12, 287.93, 283.82, 278.61, 270.1, 271.66, 273.88, 264.54, 269.76, 267.18, 270.31, 269.43, 280.63, 279.5, 282.21, 278.25, 276.49, 274.6, 272.61, 268.94, 264.95, 273.46, 267.71, 267.64, 263.91, 263.57, 262.8, 264.76, 270.67, 273.02, 271.52], 'signals': ['FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
       <c r="S34" t="n">
-        <v>273.02</v>
+        <v>271.52</v>
       </c>
       <c r="T34" t="n">
-        <v>5.601425170898438</v>
+        <v>5.419283185686384</v>
       </c>
       <c r="U34" t="n">
-        <v>15.24533523291238</v>
+        <v>15.18425228822849</v>
       </c>
       <c r="V34" t="inlineStr">
         <is>
@@ -3051,64 +3051,64 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0.197</v>
+        <v>0.17</v>
       </c>
       <c r="E35" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="F35" t="n">
         <v>50</v>
       </c>
       <c r="G35" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H35" t="n">
-        <v>90</v>
+        <v>-529</v>
       </c>
       <c r="I35" t="n">
-        <v>1.8</v>
+        <v>-10.6</v>
       </c>
       <c r="J35" t="n">
-        <v>-25.1</v>
+        <v>-23.5</v>
       </c>
       <c r="K35" t="n">
-        <v>26.9</v>
+        <v>12.9</v>
       </c>
       <c r="L35" t="n">
         <v>5000</v>
       </c>
       <c r="M35" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O35" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="P35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.7</v>
+        <v>2</v>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [57.51, 56.5, 56.03, 55.58, 55.21, 53.65, 53.5, 54.3, 54.63, 53.0, 52.97, 51.91, 52.24, 53.02, 52.51, 51.61, 50.91, 50.79, 52.35, 44.23, 43.8, 43.64, 42.31, 42.75, 43.61, 42.24, 42.53, 43.81, 45.04, 45.29, 45.62, 46.07, 45.98, 45.27, 44.38, 44.29, 44.74, 44.63, 44.0, 43.97, 44.01, 42.71, 42.68, 43.49, 44.02, 43.75, 42.01, 41.97, 41.96, 41.65, 41.51, 42.19, 42.04, 43.8, 44.0, 44.27, 44.54, 45.57, 46.95, 45.82, 45.93, 43.73, 43.81, 43.62, 42.98, 43.23, 44.65, 43.96, 45.96, 44.93, 45.2, 45.04, 44.19, 45.2, 43.19, 42.38, 41.82, 40.9, 40.75, 41.48, 41.05, 43.06, 44.09, 43.34, 43.21, 42.89, 42.78, 44.37, 43.76, 42.86, 42.77, 44.57, 43.76, 43.47, 42.96, 42.21, 40.99, 41.7, 42.14, 43.05], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28', '2026-07-29'], 'prices': [56.5, 56.03, 55.58, 55.21, 53.65, 53.5, 54.3, 54.63, 53.0, 52.97, 51.91, 52.24, 53.02, 52.51, 51.61, 50.91, 50.79, 52.35, 44.23, 43.8, 43.64, 42.31, 42.75, 43.61, 42.24, 42.53, 43.81, 45.04, 45.29, 45.62, 46.07, 45.98, 45.27, 44.38, 44.29, 44.74, 44.63, 44.0, 43.97, 44.01, 42.71, 42.68, 43.49, 44.02, 43.75, 42.01, 41.97, 41.96, 41.65, 41.51, 42.19, 42.04, 43.8, 44.0, 44.27, 44.54, 45.57, 46.95, 45.82, 45.93, 43.73, 43.81, 43.62, 42.98, 43.23, 44.65, 43.96, 45.96, 44.93, 45.2, 45.04, 44.19, 45.2, 43.19, 42.38, 41.82, 40.9, 40.75, 41.48, 41.05, 43.06, 44.09, 43.34, 43.21, 42.89, 42.78, 44.37, 43.76, 42.86, 42.77, 44.57, 43.76, 43.47, 42.96, 42.21, 40.99, 41.7, 42.14, 43.05, 43.22], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'SELL', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
       <c r="S35" t="n">
-        <v>43.05</v>
+        <v>43.22</v>
       </c>
       <c r="T35" t="n">
-        <v>1.330714634486607</v>
+        <v>1.356428691319057</v>
       </c>
       <c r="U35" t="n">
-        <v>16.83385087045296</v>
+        <v>15.82056337600136</v>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>FLAT</t>
         </is>
       </c>
     </row>
@@ -3119,36 +3119,36 @@
         </is>
       </c>
       <c r="B36" t="n">
+        <v>51</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>0.404</v>
+      </c>
+      <c r="E36" t="n">
         <v>53</v>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>DOWN</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>0.338</v>
-      </c>
-      <c r="E36" t="n">
-        <v>52</v>
-      </c>
       <c r="F36" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="G36" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H36" t="n">
-        <v>61</v>
+        <v>510</v>
       </c>
       <c r="I36" t="n">
-        <v>1.2</v>
+        <v>10.2</v>
       </c>
       <c r="J36" t="n">
-        <v>-1.3</v>
+        <v>-2.1</v>
       </c>
       <c r="K36" t="n">
-        <v>2.5</v>
+        <v>12.3</v>
       </c>
       <c r="L36" t="n">
         <v>5000</v>
@@ -3157,34 +3157,34 @@
         <v>5</v>
       </c>
       <c r="N36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
         <v>3</v>
       </c>
-      <c r="P36" t="n">
-        <v>2</v>
-      </c>
       <c r="Q36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [979.59, 995.07, 1002.25, 994.33, 989.22, 1000.28, 1005.37, 998.7, 993.14, 976.95, 971.82, 969.38, 962.8, 970.87, 971.9, 976.68, 980.87, 993.56, 993.41, 993.54, 1011.88, 1015.46, 1010.14, 1027.14, 1028.9, 995.44, 977.87, 971.84, 981.76, 984.21, 996.86, 994.81, 1002.76, 1000.65, 1011.3, 1008.08, 994.98, 990.98, 995.64, 1011.45, 1010.09, 1011.18, 1014.81, 994.17, 1010.45, 1007.19, 997.88, 1020.26, 1031.44, 1039.6, 1047.28, 1074.76, 1092.58, 1072.31, 1048.78, 1026.61, 1001.34, 1002.1, 993.62, 954.8, 944.61, 952.76, 960.3, 970.81, 970.33, 973.2, 967.05, 981.81, 974.14, 980.79, 977.9, 985.11, 964.06, 949.94, 949.84, 956.16, 959.56, 940.74, 951.03, 945.18, 933.98, 923.2, 950.16, 948.74, 946.0, 951.62, 911.52, 914.8, 924.96, 920.29, 915.09, 944.07, 939.38, 934.31, 927.74, 925.84, 924.59, 935.03, 951.58, 966.58], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'SELL', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28', '2026-07-29'], 'prices': [995.07, 1002.25, 994.33, 989.22, 1000.28, 1005.37, 998.7, 993.14, 976.95, 971.82, 969.38, 962.8, 970.87, 971.9, 976.68, 980.87, 993.56, 993.41, 993.54, 1011.88, 1015.46, 1010.14, 1027.14, 1028.9, 995.44, 977.87, 971.84, 981.76, 984.21, 996.86, 994.81, 1002.76, 1000.65, 1011.3, 1008.08, 994.98, 990.98, 995.64, 1011.45, 1010.09, 1011.18, 1014.81, 994.17, 1010.45, 1007.19, 997.88, 1020.26, 1031.44, 1039.6, 1047.28, 1074.76, 1092.58, 1072.31, 1048.78, 1026.61, 1001.34, 1002.1, 993.62, 954.8, 944.61, 952.76, 960.3, 970.81, 970.33, 973.2, 967.05, 981.81, 974.14, 980.79, 977.9, 985.11, 964.06, 949.94, 949.84, 956.16, 959.56, 940.74, 951.03, 945.18, 933.98, 923.2, 950.16, 948.74, 946.0, 951.62, 911.52, 914.8, 924.96, 920.29, 915.09, 944.07, 939.38, 934.31, 927.74, 925.84, 924.59, 935.03, 951.58, 966.58, 974.03], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL']}</t>
         </is>
       </c>
       <c r="S36" t="n">
-        <v>966.58</v>
+        <v>974.03</v>
       </c>
       <c r="T36" t="n">
-        <v>19.96724082523999</v>
+        <v>17.85453757258127</v>
       </c>
       <c r="U36" t="n">
-        <v>13.10675445852723</v>
+        <v>19.35813283015113</v>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>SELL</t>
         </is>
       </c>
     </row>
@@ -3199,14 +3199,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">UP  </t>
+          <t>DOWN</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0.569</v>
+        <v>0.422</v>
       </c>
       <c r="E37" t="n">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="F37" t="n">
         <v>40</v>
@@ -3215,52 +3215,52 @@
         <v>55</v>
       </c>
       <c r="H37" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>-7.9</v>
+        <v>-7.4</v>
       </c>
       <c r="K37" t="n">
-        <v>8.9</v>
+        <v>7.4</v>
       </c>
       <c r="L37" t="n">
         <v>5000</v>
       </c>
       <c r="M37" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="N37" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [122.82, 123.31, 123.85, 124.63, 123.0, 124.84, 126.02, 125.49, 124.59, 121.5, 120.61, 118.79, 120.49, 121.82, 122.83, 121.95, 122.66, 123.26, 124.04, 124.5, 125.55, 126.55, 122.26, 127.02, 128.88, 126.53, 124.33, 124.81, 124.52, 124.58, 127.26, 127.68, 129.35, 129.73, 131.78, 129.67, 127.35, 127.35, 127.77, 131.68, 131.35, 130.08, 130.54, 129.83, 129.95, 130.43, 127.59, 130.35, 131.47, 132.46, 131.45, 133.34, 134.2, 130.85, 121.34, 120.27, 118.57, 118.54, 118.9, 115.75, 114.6, 113.06, 116.89, 117.74, 118.88, 119.83, 118.88, 120.59, 120.5, 121.04, 120.82, 121.03, 118.13, 117.18, 117.18, 119.42, 119.0, 115.78, 115.69, 114.6, 113.26, 108.82, 111.84, 110.65, 111.54, 113.1, 112.21, 113.9, 114.78, 113.7, 112.53, 114.95, 114.24, 112.2, 110.39, 109.33, 108.4, 109.47, 111.74, 113.1], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28', '2026-07-29'], 'prices': [123.31, 123.85, 124.63, 123.0, 124.84, 126.02, 125.49, 124.59, 121.5, 120.61, 118.79, 120.49, 121.82, 122.83, 121.95, 122.66, 123.26, 124.04, 124.5, 125.55, 126.55, 122.26, 127.02, 128.88, 126.53, 124.33, 124.81, 124.52, 124.58, 127.26, 127.68, 129.35, 129.73, 131.78, 129.67, 127.35, 127.35, 127.77, 131.68, 131.35, 130.08, 130.54, 129.83, 129.95, 130.43, 127.59, 130.35, 131.47, 132.46, 131.45, 133.34, 134.2, 130.85, 121.34, 120.27, 118.57, 118.54, 118.9, 115.75, 114.6, 113.06, 116.89, 117.74, 118.88, 119.83, 118.88, 120.59, 120.5, 121.04, 120.82, 121.03, 118.13, 117.18, 117.18, 119.42, 119.0, 115.78, 115.69, 114.6, 113.26, 108.82, 111.84, 110.65, 111.54, 113.1, 112.21, 113.9, 114.78, 113.7, 112.53, 114.95, 114.24, 112.2, 110.39, 109.33, 108.4, 109.47, 111.74, 113.1, 114.22], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
       <c r="S37" t="n">
-        <v>113.1</v>
+        <v>114.22</v>
       </c>
       <c r="T37" t="n">
-        <v>2.587142399379185</v>
+        <v>2.60000010899135</v>
       </c>
       <c r="U37" t="n">
-        <v>17.72428540632053</v>
+        <v>17.9808246946824</v>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>FLAT</t>
         </is>
       </c>
     </row>
@@ -3279,60 +3279,60 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0.611</v>
+        <v>0.681</v>
       </c>
       <c r="E38" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F38" t="n">
         <v>40</v>
       </c>
       <c r="G38" t="n">
-        <v>66.7</v>
+        <v>57.1</v>
       </c>
       <c r="H38" t="n">
-        <v>-35</v>
+        <v>123</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.7</v>
+        <v>2.5</v>
       </c>
       <c r="J38" t="n">
-        <v>-1.9</v>
+        <v>-3.5</v>
       </c>
       <c r="K38" t="n">
-        <v>1.2</v>
+        <v>6</v>
       </c>
       <c r="L38" t="n">
         <v>5000</v>
       </c>
       <c r="M38" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O38" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>7.5</v>
+        <v>15</v>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [151.71, 151.35, 152.92, 153.7, 151.05, 148.27, 148.42, 149.86, 149.23, 144.53, 142.69, 142.14, 141.85, 141.04, 141.79, 140.31, 140.59, 142.57, 142.3, 141.95, 141.0, 140.65, 139.2, 142.75, 144.49, 143.01, 141.45, 142.24, 141.25, 140.99, 144.75, 142.35, 140.21, 140.73, 143.55, 147.08, 147.3, 148.06, 145.37, 146.0, 146.17, 142.36, 143.83, 146.8, 144.98, 145.34, 142.3, 142.84, 141.19, 141.65, 140.52, 141.33, 140.25, 141.38, 142.34, 143.37, 141.9, 146.4, 144.83, 142.5, 139.24, 139.78, 139.15, 139.74, 145.45, 144.02, 147.57, 147.95, 147.24, 148.5, 149.35, 151.36, 149.44, 149.27, 146.59, 149.74, 150.91, 147.4, 147.92, 147.35, 145.55, 146.34, 150.29, 148.2, 151.62, 147.3, 145.76, 145.95, 147.27, 145.0, 146.95, 150.38, 148.87, 148.02, 147.0, 148.02, 145.88, 147.41, 148.63, 148.88], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'BUY', 'SELL', 'BUY', 'SELL', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28', '2026-07-29'], 'prices': [151.35, 152.92, 153.7, 151.05, 148.27, 148.42, 149.86, 149.23, 144.53, 142.69, 142.14, 141.85, 141.04, 141.79, 140.31, 140.59, 142.57, 142.3, 141.95, 141.0, 140.65, 139.2, 142.75, 144.49, 143.01, 141.45, 142.24, 141.25, 140.99, 144.75, 142.35, 140.21, 140.73, 143.55, 147.08, 147.3, 148.06, 145.37, 146.0, 146.17, 142.36, 143.83, 146.8, 144.98, 145.34, 142.3, 142.84, 141.19, 141.65, 140.52, 141.33, 140.25, 141.38, 142.34, 143.37, 141.9, 146.4, 144.83, 142.5, 139.24, 139.78, 139.15, 139.74, 145.45, 144.02, 147.57, 147.95, 147.24, 148.5, 149.35, 151.36, 149.44, 149.27, 146.59, 149.74, 150.91, 147.4, 147.92, 147.35, 145.55, 146.34, 150.29, 148.2, 151.62, 147.3, 145.76, 145.95, 147.27, 145.0, 146.95, 150.38, 148.87, 148.02, 147.0, 148.02, 145.88, 147.41, 148.63, 148.88, 146.1], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'BUY', 'SELL', 'BUY', 'SELL', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
       <c r="S38" t="n">
-        <v>148.88</v>
+        <v>146.1</v>
       </c>
       <c r="T38" t="n">
-        <v>3.101778683973277</v>
+        <v>3.523261321021733</v>
       </c>
       <c r="U38" t="n">
-        <v>13.82053472887988</v>
+        <v>12.33007310164555</v>
       </c>
       <c r="V38" t="inlineStr">
         <is>
@@ -3347,7 +3347,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -3355,28 +3355,28 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0.707</v>
+        <v>0.736</v>
       </c>
       <c r="E39" t="n">
         <v>60</v>
       </c>
       <c r="F39" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>50</v>
+        <v>85.7</v>
       </c>
       <c r="H39" t="n">
-        <v>693</v>
+        <v>682</v>
       </c>
       <c r="I39" t="n">
-        <v>13.9</v>
+        <v>13.6</v>
       </c>
       <c r="J39" t="n">
-        <v>16.1</v>
+        <v>17.2</v>
       </c>
       <c r="K39" t="n">
-        <v>-2.2</v>
+        <v>-3.6</v>
       </c>
       <c r="L39" t="n">
         <v>5000</v>
@@ -3385,34 +3385,34 @@
         <v>56</v>
       </c>
       <c r="N39" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O39" t="n">
         <v>7</v>
       </c>
       <c r="P39" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [76.01, 76.02, 76.77, 76.85, 76.61, 76.59, 76.84, 77.32, 77.08, 75.48, 75.07, 74.27, 74.63, 74.19, 74.77, 74.21, 75.22, 75.78, 75.56, 75.59, 76.23, 76.72, 75.42, 76.79, 77.68, 76.97, 75.92, 75.41, 74.83, 74.7, 75.25, 75.0, 74.22, 74.15, 75.79, 76.14, 74.96, 77.85, 78.36, 78.25, 78.08, 77.69, 77.98, 78.72, 77.93, 77.92, 78.16, 79.52, 79.75, 79.93, 80.3, 80.68, 81.39, 81.03, 80.65, 80.96, 79.94, 81.1, 79.89, 78.5, 78.14, 77.91, 78.25, 76.33, 78.97, 79.03, 80.82, 83.05, 82.0, 82.09, 80.91, 80.28, 79.93, 79.39, 79.53, 80.31, 80.6, 80.42, 82.63, 82.65, 81.27, 81.29, 84.14, 82.96, 84.05, 83.4, 82.63, 83.49, 84.25, 83.08, 82.45, 84.92, 81.56, 82.12, 81.97, 82.2, 81.17, 82.25, 84.07, 88.27], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL']}</t>
+          <t>{'dates': ['2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28', '2026-07-29'], 'prices': [76.02, 76.77, 76.85, 76.61, 76.59, 76.84, 77.32, 77.08, 75.48, 75.07, 74.27, 74.63, 74.19, 74.77, 74.21, 75.22, 75.78, 75.56, 75.59, 76.23, 76.72, 75.42, 76.79, 77.68, 76.97, 75.92, 75.41, 74.83, 74.7, 75.25, 75.0, 74.22, 74.15, 75.79, 76.14, 74.96, 77.85, 78.36, 78.25, 78.08, 77.69, 77.98, 78.72, 77.93, 77.92, 78.16, 79.52, 79.75, 79.93, 80.3, 80.68, 81.39, 81.03, 80.65, 80.96, 79.94, 81.1, 79.89, 78.5, 78.14, 77.91, 78.25, 76.33, 78.97, 79.03, 80.82, 83.05, 82.0, 82.09, 80.91, 80.28, 79.93, 79.39, 79.53, 80.31, 80.6, 80.42, 82.63, 82.65, 81.27, 81.29, 84.14, 82.96, 84.05, 83.4, 82.63, 83.49, 84.25, 83.08, 82.45, 84.92, 81.56, 82.12, 81.97, 82.2, 81.17, 82.25, 84.07, 88.27, 89.08], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT']}</t>
         </is>
       </c>
       <c r="S39" t="n">
-        <v>88.27</v>
+        <v>89.08</v>
       </c>
       <c r="T39" t="n">
-        <v>1.992856161934989</v>
+        <v>2.061427525111607</v>
       </c>
       <c r="U39" t="n">
-        <v>17.47863805298332</v>
+        <v>21.17535189231765</v>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>FLAT</t>
         </is>
       </c>
     </row>
@@ -3423,7 +3423,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -3431,34 +3431,34 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0.406</v>
+        <v>0.279</v>
       </c>
       <c r="E40" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F40" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G40" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="H40" t="n">
-        <v>105</v>
+        <v>203</v>
       </c>
       <c r="I40" t="n">
-        <v>2.1</v>
+        <v>4.1</v>
       </c>
       <c r="J40" t="n">
-        <v>2.2</v>
+        <v>4.4</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.1</v>
+        <v>-0.3</v>
       </c>
       <c r="L40" t="n">
         <v>5000</v>
       </c>
       <c r="M40" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="N40" t="n">
         <v>1</v>
@@ -3474,17 +3474,17 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [149.74, 150.19, 149.43, 147.13, 150.56, 152.49, 155.07, 156.17, 157.74, 156.53, 157.09, 158.59, 160.04, 164.27, 162.16, 164.31, 169.84, 170.31, 168.52, 159.7, 159.61, 162.27, 162.8, 155.17, 153.99, 151.48, 151.61, 148.23, 148.01, 150.96, 145.45, 146.68, 147.36, 148.49, 149.52, 147.91, 147.19, 149.54, 153.63, 153.29, 151.72, 152.65, 153.84, 147.69, 145.59, 143.6, 148.67, 149.61, 150.55, 151.75, 157.92, 160.49, 162.55, 156.28, 155.29, 154.92, 149.81, 147.9, 146.96, 145.26, 149.38, 149.56, 152.53, 152.04, 149.92, 151.75, 148.91, 150.62, 146.6, 147.01, 140.92, 141.86, 140.74, 137.81, 138.47, 139.73, 136.9, 137.55, 136.54, 136.06, 136.72, 136.28, 137.09, 136.44, 141.69, 141.13, 137.46, 138.88, 144.51, 145.09, 144.51, 145.95, 147.36, 148.36, 151.71, 154.45, 156.89, 156.94, 154.77, 153.04], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28', '2026-07-29'], 'prices': [150.19, 149.43, 147.13, 150.56, 152.49, 155.07, 156.17, 157.74, 156.53, 157.09, 158.59, 160.04, 164.27, 162.16, 164.31, 169.84, 170.31, 168.52, 159.7, 159.61, 162.27, 162.8, 155.17, 153.99, 151.48, 151.61, 148.23, 148.01, 150.96, 145.45, 146.68, 147.36, 148.49, 149.52, 147.91, 147.19, 149.54, 153.63, 153.29, 151.72, 152.65, 153.84, 147.69, 145.59, 143.6, 148.67, 149.61, 150.55, 151.75, 157.92, 160.49, 162.55, 156.28, 155.29, 154.92, 149.81, 147.9, 146.96, 145.26, 149.38, 149.56, 152.53, 152.04, 149.92, 151.75, 148.91, 150.62, 146.6, 147.01, 140.92, 141.86, 140.74, 137.81, 138.47, 139.73, 136.9, 137.55, 136.54, 136.06, 136.72, 136.28, 137.09, 136.44, 141.69, 141.13, 137.46, 138.88, 144.51, 145.09, 144.51, 145.95, 147.36, 148.36, 151.71, 154.45, 156.89, 156.94, 154.77, 153.04, 156.75], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
       <c r="S40" t="n">
-        <v>153.04</v>
+        <v>156.75</v>
       </c>
       <c r="T40" t="n">
-        <v>3.500714983258928</v>
+        <v>3.645001002720424</v>
       </c>
       <c r="U40" t="n">
-        <v>49.80775434879472</v>
+        <v>51.10393887471235</v>
       </c>
       <c r="V40" t="inlineStr">
         <is>
@@ -3499,36 +3499,36 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve">UP  </t>
+          <t>DOWN</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0.667</v>
+        <v>0.203</v>
       </c>
       <c r="E41" t="n">
         <v>52</v>
       </c>
       <c r="F41" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="G41" t="n">
-        <v>35.7</v>
+        <v>47.4</v>
       </c>
       <c r="H41" t="n">
-        <v>-25</v>
+        <v>499</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.5</v>
+        <v>10</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.3</v>
+        <v>1.9</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.2</v>
+        <v>8.1</v>
       </c>
       <c r="L41" t="n">
         <v>5000</v>
@@ -3550,17 +3550,17 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [188.18, 188.22, 187.72, 184.6, 190.05, 195.18, 195.03, 195.05, 196.17, 196.81, 199.61, 199.9, 203.35, 204.91, 203.29, 205.9, 209.23, 208.8, 205.02, 195.62, 197.16, 197.06, 199.71, 191.14, 188.63, 186.84, 190.04, 185.32, 183.23, 186.44, 182.32, 181.59, 184.29, 184.63, 185.9, 183.53, 183.1, 186.65, 190.48, 191.56, 188.9, 190.53, 190.89, 183.48, 180.84, 179.97, 183.06, 184.26, 184.31, 184.95, 189.37, 194.34, 197.25, 191.33, 191.01, 191.43, 184.71, 182.4, 183.03, 182.46, 185.83, 187.55, 189.71, 188.35, 187.31, 189.24, 186.76, 189.8, 185.82, 187.22, 180.4, 180.11, 177.58, 173.63, 175.06, 175.98, 171.45, 172.24, 171.06, 168.47, 165.76, 165.69, 169.2, 168.1, 174.01, 175.97, 174.05, 176.4, 182.2, 181.76, 181.6, 183.86, 187.38, 189.71, 191.07, 192.98, 194.42, 194.79, 190.0, 187.58], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28', '2026-07-29'], 'prices': [188.22, 187.72, 184.6, 190.05, 195.18, 195.03, 195.05, 196.17, 196.81, 199.61, 199.9, 203.35, 204.91, 203.29, 205.9, 209.23, 208.8, 205.02, 195.62, 197.16, 197.06, 199.71, 191.14, 188.63, 186.84, 190.04, 185.32, 183.23, 186.44, 182.32, 181.59, 184.29, 184.63, 185.9, 183.53, 183.1, 186.65, 190.48, 191.56, 188.9, 190.53, 190.89, 183.48, 180.84, 179.97, 183.06, 184.26, 184.31, 184.95, 189.37, 194.34, 197.25, 191.33, 191.01, 191.43, 184.71, 182.4, 183.03, 182.46, 185.83, 187.55, 189.71, 188.35, 187.31, 189.24, 186.76, 189.8, 185.82, 187.22, 180.4, 180.11, 177.58, 173.63, 175.06, 175.98, 171.45, 172.24, 171.06, 168.47, 165.76, 165.69, 169.2, 168.1, 174.01, 175.97, 174.05, 176.4, 182.2, 181.76, 181.6, 183.86, 187.38, 189.71, 191.07, 192.98, 194.42, 194.79, 190.0, 187.58, 191.86], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
       <c r="S41" t="n">
-        <v>187.58</v>
+        <v>191.86</v>
       </c>
       <c r="T41" t="n">
-        <v>3.797142028808594</v>
+        <v>4.076426914760044</v>
       </c>
       <c r="U41" t="n">
-        <v>54.57269929944235</v>
+        <v>53.30202271583219</v>
       </c>
       <c r="V41" t="inlineStr">
         <is>
@@ -3575,68 +3575,68 @@
         </is>
       </c>
       <c r="B42" t="n">
+        <v>53</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UP  </t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>0.594</v>
+      </c>
+      <c r="E42" t="n">
+        <v>65</v>
+      </c>
+      <c r="F42" t="n">
         <v>60</v>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UP  </t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>0.586</v>
-      </c>
-      <c r="E42" t="n">
-        <v>58</v>
-      </c>
-      <c r="F42" t="n">
-        <v>40</v>
-      </c>
       <c r="G42" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="H42" t="n">
-        <v>729</v>
+        <v>515</v>
       </c>
       <c r="I42" t="n">
-        <v>14.6</v>
+        <v>10.3</v>
       </c>
       <c r="J42" t="n">
-        <v>19.5</v>
+        <v>15.4</v>
       </c>
       <c r="K42" t="n">
-        <v>-4.9</v>
+        <v>-5.1</v>
       </c>
       <c r="L42" t="n">
         <v>5000</v>
       </c>
       <c r="M42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O42" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="P42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q42" t="n">
-        <v>9</v>
+        <v>4.7</v>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [703.43, 678.35, 702.18, 713.99, 704.94, 698.06, 691.39, 697.16, 699.37, 691.02, 686.07, 678.33, 699.07, 713.94, 716.34, 700.55, 692.79, 664.93, 705.8, 727.58, 714.53, 718.54, 721.72, 768.69, 784.12, 787.7, 788.76, 791.27, 767.28, 769.76, 791.67, 796.92, 798.97, 807.37, 833.69, 829.25, 827.26, 816.36, 808.55, 888.46, 888.02, 873.16, 902.92, 925.21, 894.03, 895.79, 925.07, 910.45, 900.63, 918.52, 886.67, 862.35, 858.56, 870.94, 864.35, 878.26, 906.87, 908.25, 886.03, 874.25, 863.76, 908.13, 924.47, 938.74, 902.61, 913.94, 913.01, 854.57, 895.97, 908.88, 932.2, 943.71, 954.15, 983.99, 1020.39, 982.42, 992.61, 1055.05, 995.62, 1031.28, 1062.93, 989.57, 961.75, 968.12, 938.38, 946.32, 936.65, 950.65, 929.75, 931.61, 912.61, 875.55, 878.65, 864.3, 889.97, 889.31, 894.54, 888.73, 873.28, 840.85], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
+          <t>{'dates': ['2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28', '2026-07-29'], 'prices': [678.35, 702.18, 713.99, 704.94, 698.06, 691.39, 697.16, 699.37, 691.02, 686.07, 678.33, 699.07, 713.94, 716.34, 700.55, 692.79, 664.93, 705.8, 727.58, 714.53, 718.54, 721.72, 768.69, 784.12, 787.7, 788.76, 791.27, 767.28, 769.76, 791.67, 796.92, 798.97, 807.37, 833.69, 829.25, 827.26, 816.36, 808.55, 888.46, 888.02, 873.16, 902.92, 925.21, 894.03, 895.79, 925.07, 910.45, 900.63, 918.52, 886.67, 862.35, 858.56, 870.94, 864.35, 878.26, 906.87, 908.25, 886.03, 874.25, 863.76, 908.13, 924.47, 938.74, 902.61, 913.94, 913.01, 854.57, 895.97, 908.88, 932.2, 943.71, 954.15, 983.99, 1020.39, 982.42, 992.61, 1055.05, 995.62, 1031.28, 1062.93, 989.57, 961.75, 968.12, 938.38, 946.32, 936.65, 950.65, 929.75, 931.61, 912.61, 875.55, 878.65, 864.3, 889.97, 889.31, 894.54, 888.73, 873.28, 840.85, 782.71], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
       <c r="S42" t="n">
-        <v>840.85</v>
+        <v>782.71</v>
       </c>
       <c r="T42" t="n">
-        <v>38.7696911856788</v>
+        <v>39.92400067363405</v>
       </c>
       <c r="U42" t="n">
-        <v>35.82781971210662</v>
+        <v>40.3748280036019</v>
       </c>
       <c r="V42" t="inlineStr">
         <is>
@@ -3651,7 +3651,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -3659,28 +3659,28 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0.446</v>
+        <v>0.348</v>
       </c>
       <c r="E43" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F43" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G43" t="n">
-        <v>63.6</v>
+        <v>55.6</v>
       </c>
       <c r="H43" t="n">
-        <v>750</v>
+        <v>386</v>
       </c>
       <c r="I43" t="n">
-        <v>15</v>
+        <v>7.7</v>
       </c>
       <c r="J43" t="n">
-        <v>-0.6</v>
+        <v>-1.8</v>
       </c>
       <c r="K43" t="n">
-        <v>15.6</v>
+        <v>9.5</v>
       </c>
       <c r="L43" t="n">
         <v>5000</v>
@@ -3689,30 +3689,30 @@
         <v>20</v>
       </c>
       <c r="N43" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O43" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P43" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [248.64, 245.42, 247.81, 250.96, 249.74, 243.44, 244.59, 244.6, 241.38, 239.81, 238.89, 231.03, 232.61, 231.11, 235.51, 234.86, 232.72, 233.1, 235.76, 238.02, 239.32, 238.03, 233.47, 242.47, 246.22, 245.16, 243.69, 243.28, 242.18, 239.25, 243.6, 239.63, 231.78, 229.44, 223.56, 222.34, 221.18, 222.09, 219.35, 223.55, 221.65, 218.61, 218.06, 226.19, 225.37, 222.29, 228.54, 227.94, 227.34, 227.09, 223.64, 227.82, 227.74, 227.99, 234.71, 239.04, 243.02, 242.84, 244.36, 249.46, 248.08, 246.7, 234.15, 228.25, 224.4, 222.13, 226.22, 215.92, 229.81, 231.05, 238.5, 240.68, 239.76, 240.18, 239.23, 233.21, 238.51, 242.52, 243.53, 227.8, 223.9, 221.75, 229.86, 231.18, 225.05, 220.36, 223.42, 226.42, 222.25, 222.68, 222.84, 226.33, 225.02, 226.18, 229.86, 232.99, 246.27, 243.15, 245.75, 247.05], 'signals': ['FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT']}</t>
+          <t>{'dates': ['2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28', '2026-07-29'], 'prices': [245.42, 247.81, 250.96, 249.74, 243.44, 244.59, 244.6, 241.38, 239.81, 238.89, 231.03, 232.61, 231.11, 235.51, 234.86, 232.72, 233.1, 235.76, 238.02, 239.32, 238.03, 233.47, 242.47, 246.22, 245.16, 243.69, 243.28, 242.18, 239.25, 243.6, 239.63, 231.78, 229.44, 223.56, 222.34, 221.18, 222.09, 219.35, 223.55, 221.65, 218.61, 218.06, 226.19, 225.37, 222.29, 228.54, 227.94, 227.34, 227.09, 223.64, 227.82, 227.74, 227.99, 234.71, 239.04, 243.02, 242.84, 244.36, 249.46, 248.08, 246.7, 234.15, 228.25, 224.4, 222.13, 226.22, 215.92, 229.81, 231.05, 238.5, 240.68, 239.76, 240.18, 239.23, 233.21, 238.51, 242.52, 243.53, 227.8, 223.9, 221.75, 229.86, 231.18, 225.05, 220.36, 223.42, 226.42, 222.25, 222.68, 222.84, 226.33, 225.02, 226.18, 229.86, 232.99, 246.27, 243.15, 245.75, 247.05, 241.12], 'signals': ['FLAT', 'BUY', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
       <c r="S43" t="n">
-        <v>247.05</v>
+        <v>241.12</v>
       </c>
       <c r="T43" t="n">
-        <v>6.860714503696987</v>
+        <v>6.955714634486607</v>
       </c>
       <c r="U43" t="n">
-        <v>41.43299410133388</v>
+        <v>43.46890822327032</v>
       </c>
       <c r="V43" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -3735,60 +3735,60 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0.643</v>
+        <v>0.668</v>
       </c>
       <c r="E44" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F44" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G44" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="H44" t="n">
-        <v>-42</v>
+        <v>398</v>
       </c>
       <c r="I44" t="n">
+        <v>8</v>
+      </c>
+      <c r="J44" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="K44" t="n">
         <v>-0.8</v>
       </c>
-      <c r="J44" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="K44" t="n">
-        <v>-12.3</v>
-      </c>
       <c r="L44" t="n">
         <v>5000</v>
       </c>
       <c r="M44" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O44" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [326.11, 322.24, 321.53, 326.11, 324.75, 306.32, 299.32, 303.62, 301.71, 300.59, 291.25, 286.43, 291.18, 290.27, 296.19, 284.88, 282.46, 272.91, 283.42, 292.32, 280.81, 288.33, 288.24, 307.68, 312.63, 307.97, 311.51, 317.6, 313.54, 297.92, 303.75, 303.22, 286.37, 275.95, 281.99, 284.25, 284.21, 288.84, 283.22, 289.57, 286.15, 280.17, 286.32, 305.45, 302.25, 296.78, 300.4, 297.08, 294.34, 291.18, 281.18, 285.63, 284.92, 299.8, 301.38, 302.46, 314.1, 316.82, 320.42, 323.36, 324.2, 317.32, 314.25, 327.24, 327.59, 321.64, 330.03, 318.31, 332.35, 334.88, 341.83, 351.29, 356.59, 357.19, 354.68, 356.03, 365.42, 370.9, 368.54, 373.24, 373.26, 374.47, 377.05, 378.68, 366.98, 356.03, 359.04, 359.27, 353.42, 353.73, 360.35, 345.73, 348.83, 341.3, 340.7, 341.19, 349.0, 353.73, 361.61, 363.59], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+          <t>{'dates': ['2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28', '2026-07-29'], 'prices': [322.24, 321.53, 326.11, 324.75, 306.32, 299.32, 303.62, 301.71, 300.59, 291.25, 286.43, 291.18, 290.27, 296.19, 284.88, 282.46, 272.91, 283.42, 292.32, 280.81, 288.33, 288.24, 307.68, 312.63, 307.97, 311.51, 317.6, 313.54, 297.92, 303.75, 303.22, 286.37, 275.95, 281.99, 284.25, 284.21, 288.84, 283.22, 289.57, 286.15, 280.17, 286.32, 305.45, 302.25, 296.78, 300.4, 297.08, 294.34, 291.18, 281.18, 285.63, 284.92, 299.8, 301.38, 302.46, 314.1, 316.82, 320.42, 323.36, 324.2, 317.32, 314.25, 327.24, 327.59, 321.64, 330.03, 318.31, 332.35, 334.88, 341.83, 351.29, 356.59, 357.19, 354.68, 356.03, 365.42, 370.9, 368.54, 373.24, 373.26, 374.47, 377.05, 378.68, 366.98, 356.03, 359.04, 359.27, 353.42, 353.73, 360.35, 345.73, 348.83, 341.3, 340.7, 341.19, 349.0, 353.73, 361.61, 363.59, 350.63], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'SELL', 'BUY', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
       <c r="S44" t="n">
-        <v>363.59</v>
+        <v>350.63</v>
       </c>
       <c r="T44" t="n">
-        <v>10.2085702078683</v>
+        <v>10.81714085170201</v>
       </c>
       <c r="U44" t="n">
-        <v>35.91426140311804</v>
+        <v>33.04658128496997</v>
       </c>
       <c r="V44" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -3811,34 +3811,34 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0.537</v>
+        <v>0.501</v>
       </c>
       <c r="E45" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F45" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G45" t="n">
-        <v>41.2</v>
+        <v>40</v>
       </c>
       <c r="H45" t="n">
-        <v>512</v>
+        <v>727</v>
       </c>
       <c r="I45" t="n">
-        <v>10.2</v>
+        <v>14.5</v>
       </c>
       <c r="J45" t="n">
-        <v>-0.2</v>
+        <v>-7.4</v>
       </c>
       <c r="K45" t="n">
-        <v>10.4</v>
+        <v>21.9</v>
       </c>
       <c r="L45" t="n">
         <v>5000</v>
       </c>
       <c r="M45" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N45" t="n">
         <v>1</v>
@@ -3854,17 +3854,17 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [222.06, 231.11, 225.0, 217.76, 214.1, 204.76, 209.89, 213.47, 210.82, 205.99, 201.18, 195.12, 198.41, 196.42, 199.61, 194.36, 190.52, 189.21, 199.03, 207.32, 208.22, 212.3, 210.0, 217.8, 220.06, 217.63, 222.14, 223.77, 223.93, 218.88, 223.38, 225.08, 219.16, 231.28, 234.15, 232.44, 231.33, 230.72, 224.11, 229.03, 227.38, 221.3, 224.38, 229.93, 231.03, 237.36, 238.21, 236.87, 240.6, 229.21, 220.49, 220.61, 215.01, 222.2, 219.61, 219.02, 218.9, 224.3, 228.78, 231.15, 224.3, 217.7, 210.58, 217.42, 215.45, 215.92, 214.51, 209.0, 221.63, 219.05, 228.95, 227.49, 225.63, 222.72, 220.83, 216.71, 220.25, 218.12, 217.25, 214.69, 216.47, 218.58, 226.49, 234.54, 231.68, 224.95, 223.11, 222.28, 215.51, 217.11, 218.12, 214.34, 214.03, 209.48, 204.8, 208.65, 209.23, 209.52, 211.5, 221.56], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
+          <t>{'dates': ['2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28', '2026-07-29'], 'prices': [231.11, 225.0, 217.76, 214.1, 204.76, 209.89, 213.47, 210.82, 205.99, 201.18, 195.12, 198.41, 196.42, 199.61, 194.36, 190.52, 189.21, 199.03, 207.32, 208.22, 212.3, 210.0, 217.8, 220.06, 217.63, 222.14, 223.77, 223.93, 218.88, 223.38, 225.08, 219.16, 231.28, 234.15, 232.44, 231.33, 230.72, 224.11, 229.03, 227.38, 221.3, 224.38, 229.93, 231.03, 237.36, 238.21, 236.87, 240.6, 229.21, 220.49, 220.61, 215.01, 222.2, 219.61, 219.02, 218.9, 224.3, 228.78, 231.15, 224.3, 217.7, 210.58, 217.42, 215.45, 215.92, 214.51, 209.0, 221.63, 219.05, 228.95, 227.49, 225.63, 222.72, 220.83, 216.71, 220.25, 218.12, 217.25, 214.69, 216.47, 218.58, 226.49, 234.54, 231.68, 224.95, 223.11, 222.28, 215.51, 217.11, 218.12, 214.34, 214.03, 209.48, 204.8, 208.65, 209.23, 209.52, 211.5, 221.56, 214.01], 'signals': ['FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT']}</t>
         </is>
       </c>
       <c r="S45" t="n">
-        <v>221.56</v>
+        <v>214.01</v>
       </c>
       <c r="T45" t="n">
-        <v>6.032856532505581</v>
+        <v>6.619285583496094</v>
       </c>
       <c r="U45" t="n">
-        <v>24.42248909025004</v>
+        <v>22.88090612174586</v>
       </c>
       <c r="V45" t="inlineStr">
         <is>
@@ -3879,72 +3879,72 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>DOWN</t>
+          <t xml:space="preserve">UP  </t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.949</v>
       </c>
       <c r="E46" t="n">
         <v>49</v>
       </c>
       <c r="F46" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>306</v>
+        <v>567</v>
       </c>
       <c r="I46" t="n">
-        <v>6.1</v>
+        <v>11.3</v>
       </c>
       <c r="J46" t="n">
-        <v>18.3</v>
+        <v>15.8</v>
       </c>
       <c r="K46" t="n">
-        <v>-12.2</v>
+        <v>-4.5</v>
       </c>
       <c r="L46" t="n">
         <v>5000</v>
       </c>
       <c r="M46" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="N46" t="n">
         <v>4</v>
       </c>
       <c r="O46" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="P46" t="n">
         <v>4</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.5</v>
+        <v>3.2</v>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>{'dates': ['2026-03-05', '2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28'], 'prices': [119.13, 117.73, 118.78, 118.56, 118.18, 116.66, 115.67, 116.84, 116.84, 115.56, 115.38, 113.29, 114.35, 114.66, 115.14, 111.17, 110.14, 107.67, 111.94, 114.32, 114.56, 115.49, 116.47, 121.17, 122.57, 123.15, 124.4, 126.46, 126.39, 126.55, 128.1, 127.44, 126.46, 128.91, 129.03, 131.32, 131.91, 129.76, 130.57, 133.59, 134.21, 134.23, 137.67, 141.37, 139.09, 143.59, 145.85, 144.23, 146.07, 147.29, 143.26, 141.2, 140.41, 143.09, 144.47, 144.72, 149.57, 149.37, 149.9, 150.36, 152.09, 154.08, 154.85, 152.6, 144.06, 147.65, 147.28, 143.46, 150.35, 152.25, 157.6, 154.38, 155.25, 159.65, 161.66, 154.34, 153.79, 159.64, 154.2, 158.53, 161.54, 155.32, 150.83, 152.98, 149.42, 150.57, 153.08, 153.75, 149.73, 152.86, 150.0, 145.28, 143.89, 144.52, 149.7, 150.07, 149.83, 146.51, 144.75, 140.95], 'signals': ['FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'SELL', 'BUY', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY']}</t>
+          <t>{'dates': ['2026-03-06', '2026-03-09', '2026-03-10', '2026-03-11', '2026-03-12', '2026-03-13', '2026-03-16', '2026-03-17', '2026-03-18', '2026-03-19', '2026-03-20', '2026-03-23', '2026-03-24', '2026-03-25', '2026-03-26', '2026-03-27', '2026-03-30', '2026-03-31', '2026-04-01', '2026-04-02', '2026-04-06', '2026-04-07', '2026-04-08', '2026-04-09', '2026-04-10', '2026-04-13', '2026-04-14', '2026-04-15', '2026-04-16', '2026-04-17', '2026-04-20', '2026-04-21', '2026-04-22', '2026-04-23', '2026-04-24', '2026-04-27', '2026-04-28', '2026-04-29', '2026-04-30', '2026-05-01', '2026-05-04', '2026-05-05', '2026-05-06', '2026-05-07', '2026-05-08', '2026-05-11', '2026-05-12', '2026-05-13', '2026-05-14', '2026-05-15', '2026-05-18', '2026-05-19', '2026-05-20', '2026-05-21', '2026-05-22', '2026-05-26', '2026-05-27', '2026-05-28', '2026-05-29', '2026-06-01', '2026-06-02', '2026-06-03', '2026-06-04', '2026-06-05', '2026-06-08', '2026-06-09', '2026-06-10', '2026-06-11', '2026-06-12', '2026-06-15', '2026-06-16', '2026-06-17', '2026-06-18', '2026-06-22', '2026-06-23', '2026-06-24', '2026-06-25', '2026-06-26', '2026-06-29', '2026-06-30', '2026-07-01', '2026-07-02', '2026-07-06', '2026-07-07', '2026-07-08', '2026-07-09', '2026-07-10', '2026-07-13', '2026-07-14', '2026-07-15', '2026-07-16', '2026-07-17', '2026-07-20', '2026-07-21', '2026-07-22', '2026-07-23', '2026-07-24', '2026-07-27', '2026-07-28', '2026-07-29'], 'prices': [117.73, 118.78, 118.56, 118.18, 116.66, 115.67, 116.84, 116.84, 115.56, 115.38, 113.29, 114.35, 114.66, 115.14, 111.17, 110.14, 107.67, 111.94, 114.32, 114.56, 115.49, 116.47, 121.17, 122.57, 123.15, 124.4, 126.46, 126.39, 126.55, 128.1, 127.44, 126.46, 128.91, 129.03, 131.32, 131.91, 129.76, 130.57, 133.59, 134.21, 134.23, 137.67, 141.37, 139.09, 143.59, 145.85, 144.23, 146.07, 147.29, 143.26, 141.2, 140.41, 143.09, 144.47, 144.72, 149.57, 149.37, 149.9, 150.36, 152.09, 154.08, 154.85, 152.6, 144.06, 147.65, 147.28, 143.46, 150.35, 152.25, 157.6, 154.38, 155.25, 159.65, 161.66, 154.34, 153.79, 159.64, 154.2, 158.53, 161.54, 155.32, 150.83, 152.98, 149.42, 150.57, 153.08, 153.75, 149.73, 152.86, 150.0, 145.28, 143.89, 144.52, 149.7, 150.07, 149.83, 146.51, 144.75, 140.95, 136.37], 'signals': ['BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'FLAT', 'BUY', 'SELL', 'FLAT', 'FLAT', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'SELL', 'BUY', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD', 'HOLD']}</t>
         </is>
       </c>
       <c r="S46" t="n">
-        <v>140.95</v>
+        <v>136.37</v>
       </c>
       <c r="T46" t="n">
-        <v>4.625142778669085</v>
+        <v>4.696929931640625</v>
       </c>
       <c r="U46" t="n">
-        <v>32.31190962626408</v>
+        <v>35.8437931378929</v>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>HOLD</t>
         </is>
       </c>
     </row>

--- a/demo_results.xlsx
+++ b/demo_results.xlsx
@@ -543,7 +543,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.89</v>
+        <v>0.921</v>
       </c>
       <c r="E2" t="n">
         <v>55</v>
@@ -596,11 +596,11 @@
         <v>7.819287981305804</v>
       </c>
       <c r="U2" t="n">
-        <v>44.86389850599954</v>
+        <v>44.86389216038151</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>FLAT</t>
+          <t>BUY</t>
         </is>
       </c>
     </row>
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.709</v>
+        <v>0.701</v>
       </c>
       <c r="E3" t="n">
         <v>51</v>
@@ -672,11 +672,11 @@
         <v>11.74785723005022</v>
       </c>
       <c r="U3" t="n">
-        <v>18.00916996390183</v>
+        <v>18.00916553095785</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>BUY</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.528</v>
+        <v>0.508</v>
       </c>
       <c r="E4" t="n">
         <v>53</v>
@@ -748,7 +748,7 @@
         <v>11.90785871233259</v>
       </c>
       <c r="U4" t="n">
-        <v>18.52936616537245</v>
+        <v>18.52935678096906</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.765</v>
+        <v>0.745</v>
       </c>
       <c r="E5" t="n">
         <v>60</v>
@@ -824,7 +824,7 @@
         <v>6.484285627092634</v>
       </c>
       <c r="U5" t="n">
-        <v>31.48518670367037</v>
+        <v>31.48519225056321</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.591</v>
+        <v>0.582</v>
       </c>
       <c r="E6" t="n">
         <v>54</v>
@@ -900,11 +900,11 @@
         <v>23.30571637834822</v>
       </c>
       <c r="U6" t="n">
-        <v>23.3303733232493</v>
+        <v>23.33037713965981</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>FLAT</t>
+          <t>BUY</t>
         </is>
       </c>
     </row>
@@ -923,7 +923,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.83</v>
+        <v>0.988</v>
       </c>
       <c r="E7" t="n">
         <v>60</v>
@@ -976,11 +976,11 @@
         <v>7.836429050990513</v>
       </c>
       <c r="U7" t="n">
-        <v>22.29241790270129</v>
+        <v>22.29242032225401</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>BUY</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.641</v>
+        <v>0.742</v>
       </c>
       <c r="E8" t="n">
         <v>54</v>
@@ -1052,7 +1052,7 @@
         <v>14.73785400390625</v>
       </c>
       <c r="U8" t="n">
-        <v>15.64409807495208</v>
+        <v>15.64410484939716</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.25</v>
+        <v>0.252</v>
       </c>
       <c r="E9" t="n">
         <v>59</v>
@@ -1128,7 +1128,7 @@
         <v>6.745713370186942</v>
       </c>
       <c r="U9" t="n">
-        <v>57.92239247593587</v>
+        <v>57.92238752588118</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="E10" t="n">
         <v>61</v>
@@ -1204,11 +1204,11 @@
         <v>37.77572195870535</v>
       </c>
       <c r="U10" t="n">
-        <v>18.02955595678292</v>
+        <v>18.0295473424826</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>BUY</t>
         </is>
       </c>
     </row>
@@ -1280,11 +1280,11 @@
         <v>7.399286542619977</v>
       </c>
       <c r="U11" t="n">
-        <v>31.35307462613775</v>
+        <v>31.35306035797163</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>FLAT</t>
+          <t>BUY</t>
         </is>
       </c>
     </row>
@@ -1356,11 +1356,11 @@
         <v>8.395711626325335</v>
       </c>
       <c r="U12" t="n">
-        <v>20.42383028916537</v>
+        <v>20.42383481724592</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>BUY</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.148</v>
+        <v>0.154</v>
       </c>
       <c r="E13" t="n">
         <v>58</v>
@@ -1432,11 +1432,11 @@
         <v>2.712855747767857</v>
       </c>
       <c r="U13" t="n">
-        <v>32.49090289618915</v>
+        <v>32.49093026100213</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>BUY</t>
         </is>
       </c>
     </row>
@@ -1451,11 +1451,11 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>DOWN</t>
+          <t xml:space="preserve">UP  </t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.49</v>
+        <v>0.537</v>
       </c>
       <c r="E14" t="n">
         <v>55</v>
@@ -1508,11 +1508,11 @@
         <v>7.469285692487444</v>
       </c>
       <c r="U14" t="n">
-        <v>41.30813475195399</v>
+        <v>41.30812486462463</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>BUY</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.403</v>
+        <v>0.368</v>
       </c>
       <c r="E15" t="n">
         <v>54</v>
@@ -1584,11 +1584,11 @@
         <v>78.66857474190849</v>
       </c>
       <c r="U15" t="n">
-        <v>29.09572912384758</v>
+        <v>29.09572499176581</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>BUY</t>
         </is>
       </c>
     </row>
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.282</v>
+        <v>0.299</v>
       </c>
       <c r="E16" t="n">
         <v>54</v>
@@ -1660,11 +1660,11 @@
         <v>12.76857158115932</v>
       </c>
       <c r="U16" t="n">
-        <v>44.79458418939749</v>
+        <v>44.79456926405228</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>FLAT</t>
         </is>
       </c>
     </row>
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.699</v>
+        <v>0.926</v>
       </c>
       <c r="E17" t="n">
         <v>54</v>
@@ -1736,7 +1736,7 @@
         <v>10.31006949288505</v>
       </c>
       <c r="U17" t="n">
-        <v>24.26129923862345</v>
+        <v>24.2612896976041</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.186</v>
+        <v>0.275</v>
       </c>
       <c r="E18" t="n">
         <v>60</v>
@@ -1812,11 +1812,11 @@
         <v>6.856429508754185</v>
       </c>
       <c r="U18" t="n">
-        <v>20.67152337632379</v>
+        <v>20.67153670323982</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>FLAT</t>
+          <t>BUY</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.047</v>
+        <v>0.041</v>
       </c>
       <c r="E19" t="n">
         <v>53</v>
@@ -1888,7 +1888,7 @@
         <v>9.362145560128349</v>
       </c>
       <c r="U19" t="n">
-        <v>17.56600669046751</v>
+        <v>17.56602061996384</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.157</v>
+        <v>0.119</v>
       </c>
       <c r="E20" t="n">
         <v>61</v>
@@ -1964,11 +1964,11 @@
         <v>23.1142828805106</v>
       </c>
       <c r="U20" t="n">
-        <v>23.3181811684695</v>
+        <v>23.31818175533295</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>FLAT</t>
         </is>
       </c>
     </row>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.451</v>
+        <v>0.482</v>
       </c>
       <c r="E21" t="n">
         <v>51</v>
@@ -2040,11 +2040,11 @@
         <v>7.952859061104911</v>
       </c>
       <c r="U21" t="n">
-        <v>15.26003211212924</v>
+        <v>15.26003192946961</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>FLAT</t>
+          <t>BUY</t>
         </is>
       </c>
     </row>
@@ -2059,11 +2059,11 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">UP  </t>
+          <t>DOWN</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.505</v>
+        <v>0.471</v>
       </c>
       <c r="E22" t="n">
         <v>56</v>
@@ -2116,11 +2116,11 @@
         <v>42.53926740373884</v>
       </c>
       <c r="U22" t="n">
-        <v>13.90794299192742</v>
+        <v>13.90795018034147</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>FLAT</t>
+          <t>BUY</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.388</v>
+        <v>0.402</v>
       </c>
       <c r="E23" t="n">
         <v>52</v>
@@ -2192,11 +2192,11 @@
         <v>8.180720738002233</v>
       </c>
       <c r="U23" t="n">
-        <v>35.61589859976169</v>
+        <v>35.61589119010961</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>BUY</t>
         </is>
       </c>
     </row>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.569</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="E24" t="n">
         <v>55</v>
@@ -2268,11 +2268,11 @@
         <v>11.75999668666295</v>
       </c>
       <c r="U24" t="n">
-        <v>38.7227335768313</v>
+        <v>38.72272508287848</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>FLAT</t>
         </is>
       </c>
     </row>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.626</v>
+        <v>0.658</v>
       </c>
       <c r="E25" t="n">
         <v>65</v>
@@ -2344,7 +2344,7 @@
         <v>1.223571504865374</v>
       </c>
       <c r="U25" t="n">
-        <v>26.53735291364924</v>
+        <v>26.53735411017642</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.205</v>
+        <v>0.143</v>
       </c>
       <c r="E26" t="n">
         <v>50</v>
@@ -2420,11 +2420,11 @@
         <v>7.77931867899251</v>
       </c>
       <c r="U26" t="n">
-        <v>15.12562781426063</v>
+        <v>15.12562412687604</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>FLAT</t>
         </is>
       </c>
     </row>
@@ -2443,7 +2443,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.319</v>
+        <v>0.273</v>
       </c>
       <c r="E27" t="n">
         <v>50</v>
@@ -2496,11 +2496,11 @@
         <v>33.84211948939732</v>
       </c>
       <c r="U27" t="n">
-        <v>14.20074607042792</v>
+        <v>14.20074640067542</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>FLAT</t>
+          <t>BUY</t>
         </is>
       </c>
     </row>
@@ -2519,7 +2519,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.453</v>
+        <v>0.42</v>
       </c>
       <c r="E28" t="n">
         <v>57</v>
@@ -2572,11 +2572,11 @@
         <v>13.52213832310268</v>
       </c>
       <c r="U28" t="n">
-        <v>32.74090393722857</v>
+        <v>32.74089261243533</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>FLAT</t>
+          <t>BUY</t>
         </is>
       </c>
     </row>
@@ -2595,7 +2595,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.469</v>
+        <v>0.466</v>
       </c>
       <c r="E29" t="n">
         <v>56</v>
@@ -2648,7 +2648,7 @@
         <v>6.197137015206473</v>
       </c>
       <c r="U29" t="n">
-        <v>18.33651305217017</v>
+        <v>18.33649302516931</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.748</v>
+        <v>0.675</v>
       </c>
       <c r="E30" t="n">
         <v>51</v>
@@ -2724,11 +2724,11 @@
         <v>5.793073158790757</v>
       </c>
       <c r="U30" t="n">
-        <v>39.81020353644736</v>
+        <v>39.81020385411369</v>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>BUY</t>
         </is>
       </c>
     </row>
@@ -2747,7 +2747,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.698</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="E31" t="n">
         <v>57</v>
@@ -2800,11 +2800,11 @@
         <v>3.309999738420759</v>
       </c>
       <c r="U31" t="n">
-        <v>19.55671569331611</v>
+        <v>19.55670471479557</v>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>FLAT</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.599</v>
+        <v>0.699</v>
       </c>
       <c r="E32" t="n">
         <v>58</v>
@@ -2876,11 +2876,11 @@
         <v>15.89285714285714</v>
       </c>
       <c r="U32" t="n">
-        <v>49.98737132746758</v>
+        <v>49.98737546476139</v>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>FLAT</t>
         </is>
       </c>
     </row>
@@ -2899,7 +2899,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.77</v>
+        <v>0.806</v>
       </c>
       <c r="E33" t="n">
         <v>50</v>
@@ -2952,7 +2952,7 @@
         <v>9.01999991280692</v>
       </c>
       <c r="U33" t="n">
-        <v>18.79077796570979</v>
+        <v>18.79079684896699</v>
       </c>
       <c r="V33" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0.676</v>
+        <v>0.697</v>
       </c>
       <c r="E34" t="n">
         <v>63</v>
@@ -3028,11 +3028,11 @@
         <v>5.419283185686384</v>
       </c>
       <c r="U34" t="n">
-        <v>15.18425228822849</v>
+        <v>15.18424028177808</v>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>FLAT</t>
+          <t>BUY</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0.17</v>
+        <v>0.167</v>
       </c>
       <c r="E35" t="n">
         <v>52</v>
@@ -3104,11 +3104,11 @@
         <v>1.356428691319057</v>
       </c>
       <c r="U35" t="n">
-        <v>15.82056337600136</v>
+        <v>15.82055601965544</v>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>FLAT</t>
+          <t>BUY</t>
         </is>
       </c>
     </row>
@@ -3127,7 +3127,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0.404</v>
+        <v>0.418</v>
       </c>
       <c r="E36" t="n">
         <v>53</v>
@@ -3180,11 +3180,11 @@
         <v>17.85453757258127</v>
       </c>
       <c r="U36" t="n">
-        <v>19.35813283015113</v>
+        <v>19.35812679931411</v>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>FLAT</t>
         </is>
       </c>
     </row>
@@ -3203,7 +3203,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0.422</v>
+        <v>0.337</v>
       </c>
       <c r="E37" t="n">
         <v>53</v>
@@ -3256,7 +3256,7 @@
         <v>2.60000010899135</v>
       </c>
       <c r="U37" t="n">
-        <v>17.9808246946824</v>
+        <v>17.98083422258512</v>
       </c>
       <c r="V37" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0.681</v>
+        <v>0.749</v>
       </c>
       <c r="E38" t="n">
         <v>55</v>
@@ -3332,11 +3332,11 @@
         <v>3.523261321021733</v>
       </c>
       <c r="U38" t="n">
-        <v>12.33007310164555</v>
+        <v>12.33005943885835</v>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>BUY</t>
         </is>
       </c>
     </row>
@@ -3355,7 +3355,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0.736</v>
+        <v>0.576</v>
       </c>
       <c r="E39" t="n">
         <v>60</v>
@@ -3408,11 +3408,11 @@
         <v>2.061427525111607</v>
       </c>
       <c r="U39" t="n">
-        <v>21.17535189231765</v>
+        <v>21.17534303841171</v>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>FLAT</t>
+          <t>BUY</t>
         </is>
       </c>
     </row>
@@ -3431,7 +3431,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0.279</v>
+        <v>0.283</v>
       </c>
       <c r="E40" t="n">
         <v>53</v>
@@ -3484,11 +3484,11 @@
         <v>3.645001002720424</v>
       </c>
       <c r="U40" t="n">
-        <v>51.10393887471235</v>
+        <v>51.1039254107608</v>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>BUY</t>
         </is>
       </c>
     </row>
@@ -3560,11 +3560,11 @@
         <v>4.076426914760044</v>
       </c>
       <c r="U41" t="n">
-        <v>53.30202271583219</v>
+        <v>53.30200713030153</v>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>FLAT</t>
         </is>
       </c>
     </row>
@@ -3583,7 +3583,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0.594</v>
+        <v>0.595</v>
       </c>
       <c r="E42" t="n">
         <v>65</v>
@@ -3636,11 +3636,11 @@
         <v>39.92400067363405</v>
       </c>
       <c r="U42" t="n">
-        <v>40.3748280036019</v>
+        <v>40.37482638065851</v>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>BUY</t>
         </is>
       </c>
     </row>
@@ -3659,7 +3659,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0.348</v>
+        <v>0.379</v>
       </c>
       <c r="E43" t="n">
         <v>53</v>
@@ -3712,11 +3712,11 @@
         <v>6.955714634486607</v>
       </c>
       <c r="U43" t="n">
-        <v>43.46890822327032</v>
+        <v>43.46888915481561</v>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>FLAT</t>
+          <t>BUY</t>
         </is>
       </c>
     </row>
@@ -3735,7 +3735,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0.668</v>
+        <v>0.635</v>
       </c>
       <c r="E44" t="n">
         <v>53</v>
@@ -3788,11 +3788,11 @@
         <v>10.81714085170201</v>
       </c>
       <c r="U44" t="n">
-        <v>33.04658128496997</v>
+        <v>33.04656993135467</v>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>FLAT</t>
+          <t>BUY</t>
         </is>
       </c>
     </row>
@@ -3807,11 +3807,11 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">UP  </t>
+          <t>DOWN</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0.501</v>
+        <v>0.43</v>
       </c>
       <c r="E45" t="n">
         <v>60</v>
@@ -3864,7 +3864,7 @@
         <v>6.619285583496094</v>
       </c>
       <c r="U45" t="n">
-        <v>22.88090612174586</v>
+        <v>22.88091816972282</v>
       </c>
       <c r="V45" t="inlineStr">
         <is>
@@ -3887,7 +3887,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>0.949</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="E46" t="n">
         <v>49</v>
@@ -3940,11 +3940,11 @@
         <v>4.696929931640625</v>
       </c>
       <c r="U46" t="n">
-        <v>35.8437931378929</v>
+        <v>35.84378533715343</v>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>BUY</t>
         </is>
       </c>
     </row>

--- a/demo_results.xlsx
+++ b/demo_results.xlsx
@@ -543,7 +543,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.921</v>
+        <v>0.926</v>
       </c>
       <c r="E2" t="n">
         <v>55</v>
@@ -590,13 +590,13 @@
         </is>
       </c>
       <c r="S2" t="n">
-        <v>338.19</v>
+        <v>333.43</v>
       </c>
       <c r="T2" t="n">
-        <v>7.819287981305804</v>
+        <v>8.095003400530134</v>
       </c>
       <c r="U2" t="n">
-        <v>44.86389216038151</v>
+        <v>43.55962499290484</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.701</v>
+        <v>0.66</v>
       </c>
       <c r="E3" t="n">
         <v>51</v>
@@ -666,17 +666,17 @@
         </is>
       </c>
       <c r="S3" t="n">
-        <v>390.54</v>
+        <v>451.1</v>
       </c>
       <c r="T3" t="n">
-        <v>11.74785723005022</v>
+        <v>15.8721422467913</v>
       </c>
       <c r="U3" t="n">
-        <v>18.00916553095785</v>
+        <v>22.49790546280589</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>FLAT</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.508</v>
+        <v>0.513</v>
       </c>
       <c r="E4" t="n">
         <v>53</v>
@@ -742,13 +742,13 @@
         </is>
       </c>
       <c r="S4" t="n">
-        <v>336.71</v>
+        <v>333.66</v>
       </c>
       <c r="T4" t="n">
-        <v>11.90785871233259</v>
+        <v>11.92428588867188</v>
       </c>
       <c r="U4" t="n">
-        <v>18.52935678096906</v>
+        <v>17.30751840575186</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.745</v>
+        <v>0.721</v>
       </c>
       <c r="E5" t="n">
         <v>60</v>
@@ -818,17 +818,17 @@
         </is>
       </c>
       <c r="S5" t="n">
-        <v>226.65</v>
+        <v>235.5</v>
       </c>
       <c r="T5" t="n">
-        <v>6.484285627092634</v>
+        <v>6.952144077845982</v>
       </c>
       <c r="U5" t="n">
-        <v>31.48519225056321</v>
+        <v>30.06672789285297</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>FLAT</t>
+          <t>BUY</t>
         </is>
       </c>
     </row>
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.582</v>
+        <v>0.545</v>
       </c>
       <c r="E6" t="n">
         <v>54</v>
@@ -894,13 +894,13 @@
         </is>
       </c>
       <c r="S6" t="n">
-        <v>585.61</v>
+        <v>539.03</v>
       </c>
       <c r="T6" t="n">
-        <v>23.30571637834822</v>
+        <v>24.35857282366072</v>
       </c>
       <c r="U6" t="n">
-        <v>23.33037713965981</v>
+        <v>30.20183307466251</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.988</v>
+        <v>0.992</v>
       </c>
       <c r="E7" t="n">
         <v>60</v>
@@ -970,13 +970,13 @@
         </is>
       </c>
       <c r="S7" t="n">
-        <v>190.01</v>
+        <v>195.04</v>
       </c>
       <c r="T7" t="n">
-        <v>7.836429050990513</v>
+        <v>7.705000741141183</v>
       </c>
       <c r="U7" t="n">
-        <v>22.29242032225401</v>
+        <v>24.19408347477319</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.742</v>
+        <v>0.705</v>
       </c>
       <c r="E8" t="n">
         <v>54</v>
@@ -1046,13 +1046,13 @@
         </is>
       </c>
       <c r="S8" t="n">
-        <v>370.32</v>
+        <v>387.84</v>
       </c>
       <c r="T8" t="n">
-        <v>14.73785400390625</v>
+        <v>15.56785365513393</v>
       </c>
       <c r="U8" t="n">
-        <v>15.64410484939716</v>
+        <v>18.46278620843924</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.252</v>
+        <v>0.245</v>
       </c>
       <c r="E9" t="n">
         <v>59</v>
@@ -1122,13 +1122,13 @@
         </is>
       </c>
       <c r="S9" t="n">
-        <v>117.74</v>
+        <v>127.56</v>
       </c>
       <c r="T9" t="n">
-        <v>6.745713370186942</v>
+        <v>7.044284820556641</v>
       </c>
       <c r="U9" t="n">
-        <v>57.92238752588118</v>
+        <v>56.86454138593247</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -1198,13 +1198,13 @@
         </is>
       </c>
       <c r="S10" t="n">
-        <v>429.56</v>
+        <v>485.39</v>
       </c>
       <c r="T10" t="n">
-        <v>37.77572195870535</v>
+        <v>41.23572213309152</v>
       </c>
       <c r="U10" t="n">
-        <v>18.0295473424826</v>
+        <v>19.08639431571746</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.395</v>
+        <v>0.429</v>
       </c>
       <c r="E11" t="n">
         <v>63</v>
@@ -1274,17 +1274,17 @@
         </is>
       </c>
       <c r="S11" t="n">
-        <v>155.68</v>
+        <v>151.6</v>
       </c>
       <c r="T11" t="n">
-        <v>7.399286542619977</v>
+        <v>7.705714634486607</v>
       </c>
       <c r="U11" t="n">
-        <v>31.35306035797163</v>
+        <v>36.9450260765756</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>FLAT</t>
         </is>
       </c>
     </row>
@@ -1303,7 +1303,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.263</v>
+        <v>0.279</v>
       </c>
       <c r="E12" t="n">
         <v>50</v>
@@ -1350,13 +1350,13 @@
         </is>
       </c>
       <c r="S12" t="n">
-        <v>188.38</v>
+        <v>180.71</v>
       </c>
       <c r="T12" t="n">
-        <v>8.395711626325335</v>
+        <v>9.009997776576451</v>
       </c>
       <c r="U12" t="n">
-        <v>20.42383481724592</v>
+        <v>20.00262651284124</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.154</v>
+        <v>0.152</v>
       </c>
       <c r="E13" t="n">
         <v>58</v>
@@ -1426,13 +1426,13 @@
         </is>
       </c>
       <c r="S13" t="n">
-        <v>73.63</v>
+        <v>73.17</v>
       </c>
       <c r="T13" t="n">
-        <v>2.712855747767857</v>
+        <v>2.704998561314174</v>
       </c>
       <c r="U13" t="n">
-        <v>32.49093026100213</v>
+        <v>30.76932919283882</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.537</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="E14" t="n">
         <v>55</v>
@@ -1502,13 +1502,13 @@
         </is>
       </c>
       <c r="S14" t="n">
-        <v>81.88</v>
+        <v>91.13</v>
       </c>
       <c r="T14" t="n">
-        <v>7.469285692487444</v>
+        <v>7.978571210588727</v>
       </c>
       <c r="U14" t="n">
-        <v>41.30812486462463</v>
+        <v>40.94121396634576</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.368</v>
+        <v>0.378</v>
       </c>
       <c r="E15" t="n">
         <v>54</v>
@@ -1578,17 +1578,17 @@
         </is>
       </c>
       <c r="S15" t="n">
-        <v>739</v>
+        <v>874.66</v>
       </c>
       <c r="T15" t="n">
-        <v>78.66857474190849</v>
+        <v>85.78500366210938</v>
       </c>
       <c r="U15" t="n">
-        <v>29.09572499176581</v>
+        <v>29.91670705443948</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>FLAT</t>
         </is>
       </c>
     </row>
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.299</v>
+        <v>0.275</v>
       </c>
       <c r="E16" t="n">
         <v>54</v>
@@ -1654,13 +1654,13 @@
         </is>
       </c>
       <c r="S16" t="n">
-        <v>124.05</v>
+        <v>135.22</v>
       </c>
       <c r="T16" t="n">
-        <v>12.76857158115932</v>
+        <v>13.17357036045619</v>
       </c>
       <c r="U16" t="n">
-        <v>44.79456926405228</v>
+        <v>47.11123187605465</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.926</v>
+        <v>0.923</v>
       </c>
       <c r="E17" t="n">
         <v>54</v>
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="S17" t="n">
-        <v>179.38</v>
+        <v>185.22</v>
       </c>
       <c r="T17" t="n">
-        <v>10.31006949288505</v>
+        <v>10.0095705304827</v>
       </c>
       <c r="U17" t="n">
-        <v>24.2612896976041</v>
+        <v>21.19041197548062</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.275</v>
+        <v>0.193</v>
       </c>
       <c r="E18" t="n">
         <v>60</v>
@@ -1806,13 +1806,13 @@
         </is>
       </c>
       <c r="S18" t="n">
-        <v>123</v>
+        <v>122.26</v>
       </c>
       <c r="T18" t="n">
-        <v>6.856429508754185</v>
+        <v>6.634286608014788</v>
       </c>
       <c r="U18" t="n">
-        <v>20.67153670323982</v>
+        <v>21.13808717597969</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.041</v>
+        <v>0.04</v>
       </c>
       <c r="E19" t="n">
         <v>53</v>
@@ -1882,17 +1882,17 @@
         </is>
       </c>
       <c r="S19" t="n">
-        <v>160.09</v>
+        <v>163.58</v>
       </c>
       <c r="T19" t="n">
-        <v>9.362145560128349</v>
+        <v>9.071431841169085</v>
       </c>
       <c r="U19" t="n">
-        <v>17.56602061996384</v>
+        <v>16.87455769491832</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>FLAT</t>
+          <t>BUY</t>
         </is>
       </c>
     </row>
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.119</v>
+        <v>0.104</v>
       </c>
       <c r="E20" t="n">
         <v>61</v>
@@ -1958,13 +1958,13 @@
         </is>
       </c>
       <c r="S20" t="n">
-        <v>148.22</v>
+        <v>188.43</v>
       </c>
       <c r="T20" t="n">
-        <v>23.1142828805106</v>
+        <v>25.30199759347098</v>
       </c>
       <c r="U20" t="n">
-        <v>23.31818175533295</v>
+        <v>23.49697081592769</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.482</v>
+        <v>0.478</v>
       </c>
       <c r="E21" t="n">
         <v>51</v>
@@ -2034,13 +2034,13 @@
         </is>
       </c>
       <c r="S21" t="n">
-        <v>344.71</v>
+        <v>350.85</v>
       </c>
       <c r="T21" t="n">
-        <v>7.952859061104911</v>
+        <v>8.270717075892858</v>
       </c>
       <c r="U21" t="n">
-        <v>15.26003192946961</v>
+        <v>15.2774574351021</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.471</v>
+        <v>0.465</v>
       </c>
       <c r="E22" t="n">
         <v>56</v>
@@ -2110,13 +2110,13 @@
         </is>
       </c>
       <c r="S22" t="n">
-        <v>980.75</v>
+        <v>1024.86</v>
       </c>
       <c r="T22" t="n">
-        <v>42.53926740373884</v>
+        <v>44.67283848353794</v>
       </c>
       <c r="U22" t="n">
-        <v>13.90795018034147</v>
+        <v>14.8571592481857</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.402</v>
+        <v>0.372</v>
       </c>
       <c r="E23" t="n">
         <v>52</v>
@@ -2186,13 +2186,13 @@
         </is>
       </c>
       <c r="S23" t="n">
-        <v>368.73</v>
+        <v>366.27</v>
       </c>
       <c r="T23" t="n">
-        <v>8.180720738002233</v>
+        <v>8.33357674734933</v>
       </c>
       <c r="U23" t="n">
-        <v>35.61589119010961</v>
+        <v>33.92816719954008</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="E24" t="n">
         <v>55</v>
@@ -2262,13 +2262,13 @@
         </is>
       </c>
       <c r="S24" t="n">
-        <v>563.3200000000001</v>
+        <v>577.35</v>
       </c>
       <c r="T24" t="n">
-        <v>11.75999668666295</v>
+        <v>12.47499738420759</v>
       </c>
       <c r="U24" t="n">
-        <v>38.72272508287848</v>
+        <v>41.46780053512246</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.658</v>
+        <v>0.66</v>
       </c>
       <c r="E25" t="n">
         <v>65</v>
@@ -2338,17 +2338,17 @@
         </is>
       </c>
       <c r="S25" t="n">
-        <v>61.07</v>
+        <v>61.73</v>
       </c>
       <c r="T25" t="n">
-        <v>1.223571504865374</v>
+        <v>1.24357169015067</v>
       </c>
       <c r="U25" t="n">
-        <v>26.53735411017642</v>
+        <v>24.61460448774746</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>FLAT</t>
         </is>
       </c>
     </row>
@@ -2367,7 +2367,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.143</v>
+        <v>0.144</v>
       </c>
       <c r="E26" t="n">
         <v>50</v>
@@ -2414,13 +2414,13 @@
         </is>
       </c>
       <c r="S26" t="n">
-        <v>202.02</v>
+        <v>208.91</v>
       </c>
       <c r="T26" t="n">
-        <v>7.77931867899251</v>
+        <v>8.071993361255181</v>
       </c>
       <c r="U26" t="n">
-        <v>15.12562412687604</v>
+        <v>17.66080894470807</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.273</v>
+        <v>0.256</v>
       </c>
       <c r="E27" t="n">
         <v>50</v>
@@ -2490,13 +2490,13 @@
         </is>
       </c>
       <c r="S27" t="n">
-        <v>1210.02</v>
+        <v>1154.97</v>
       </c>
       <c r="T27" t="n">
-        <v>33.84211948939732</v>
+        <v>35.14569091796875</v>
       </c>
       <c r="U27" t="n">
-        <v>14.20074640067542</v>
+        <v>13.96302339102815</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.42</v>
+        <v>0.432</v>
       </c>
       <c r="E28" t="n">
         <v>57</v>
@@ -2566,13 +2566,13 @@
         </is>
       </c>
       <c r="S28" t="n">
-        <v>420.57</v>
+        <v>421.47</v>
       </c>
       <c r="T28" t="n">
-        <v>13.52213832310268</v>
+        <v>14.01070949009487</v>
       </c>
       <c r="U28" t="n">
-        <v>32.74089261243533</v>
+        <v>29.35980583614995</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
@@ -2642,13 +2642,13 @@
         </is>
       </c>
       <c r="S29" t="n">
-        <v>265.53</v>
+        <v>255.82</v>
       </c>
       <c r="T29" t="n">
-        <v>6.197137015206473</v>
+        <v>6.567852565220424</v>
       </c>
       <c r="U29" t="n">
-        <v>18.33649302516931</v>
+        <v>16.51311320166337</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.675</v>
+        <v>0.676</v>
       </c>
       <c r="E30" t="n">
         <v>51</v>
@@ -2718,13 +2718,13 @@
         </is>
       </c>
       <c r="S30" t="n">
-        <v>263.3</v>
+        <v>257.41</v>
       </c>
       <c r="T30" t="n">
-        <v>5.793073158790757</v>
+        <v>6.023552402698909</v>
       </c>
       <c r="U30" t="n">
-        <v>39.81020385411369</v>
+        <v>39.42908742733275</v>
       </c>
       <c r="V30" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.697</v>
       </c>
       <c r="E31" t="n">
         <v>57</v>
@@ -2794,17 +2794,17 @@
         </is>
       </c>
       <c r="S31" t="n">
-        <v>130.36</v>
+        <v>129.79</v>
       </c>
       <c r="T31" t="n">
-        <v>3.309999738420759</v>
+        <v>3.342142922537668</v>
       </c>
       <c r="U31" t="n">
-        <v>19.55670471479557</v>
+        <v>20.44710701243111</v>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>FLAT</t>
+          <t>BUY</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.699</v>
+        <v>0.678</v>
       </c>
       <c r="E32" t="n">
         <v>58</v>
@@ -2870,13 +2870,13 @@
         </is>
       </c>
       <c r="S32" t="n">
-        <v>298.32</v>
+        <v>308.85</v>
       </c>
       <c r="T32" t="n">
-        <v>15.89285714285714</v>
+        <v>16.0499986921038</v>
       </c>
       <c r="U32" t="n">
-        <v>49.98737546476139</v>
+        <v>55.21478820778726</v>
       </c>
       <c r="V32" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.806</v>
+        <v>0.774</v>
       </c>
       <c r="E33" t="n">
         <v>50</v>
@@ -2946,17 +2946,17 @@
         </is>
       </c>
       <c r="S33" t="n">
-        <v>338.27</v>
+        <v>333.35</v>
       </c>
       <c r="T33" t="n">
-        <v>9.01999991280692</v>
+        <v>9.128570556640625</v>
       </c>
       <c r="U33" t="n">
-        <v>18.79079684896699</v>
+        <v>16.93161260666767</v>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>FLAT</t>
+          <t>BUY</t>
         </is>
       </c>
     </row>
@@ -2975,7 +2975,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0.697</v>
+        <v>0.681</v>
       </c>
       <c r="E34" t="n">
         <v>63</v>
@@ -3022,13 +3022,13 @@
         </is>
       </c>
       <c r="S34" t="n">
-        <v>271.52</v>
+        <v>268.44</v>
       </c>
       <c r="T34" t="n">
-        <v>5.419283185686384</v>
+        <v>5.389997209821429</v>
       </c>
       <c r="U34" t="n">
-        <v>15.18424028177808</v>
+        <v>13.42161066206626</v>
       </c>
       <c r="V34" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0.167</v>
+        <v>0.173</v>
       </c>
       <c r="E35" t="n">
         <v>52</v>
@@ -3098,13 +3098,13 @@
         </is>
       </c>
       <c r="S35" t="n">
-        <v>43.22</v>
+        <v>42.29</v>
       </c>
       <c r="T35" t="n">
-        <v>1.356428691319057</v>
+        <v>1.366428647722517</v>
       </c>
       <c r="U35" t="n">
-        <v>15.82055601965544</v>
+        <v>16.73002819887689</v>
       </c>
       <c r="V35" t="inlineStr">
         <is>
@@ -3127,7 +3127,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0.418</v>
+        <v>0.492</v>
       </c>
       <c r="E36" t="n">
         <v>53</v>
@@ -3174,13 +3174,13 @@
         </is>
       </c>
       <c r="S36" t="n">
-        <v>974.03</v>
+        <v>954.17</v>
       </c>
       <c r="T36" t="n">
-        <v>17.85453757258127</v>
+        <v>18.91490830381247</v>
       </c>
       <c r="U36" t="n">
-        <v>19.35812679931411</v>
+        <v>23.00303798689565</v>
       </c>
       <c r="V36" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0.337</v>
+        <v>0.321</v>
       </c>
       <c r="E37" t="n">
         <v>53</v>
@@ -3250,13 +3250,13 @@
         </is>
       </c>
       <c r="S37" t="n">
-        <v>114.22</v>
+        <v>111.1</v>
       </c>
       <c r="T37" t="n">
-        <v>2.60000010899135</v>
+        <v>2.710714067731585</v>
       </c>
       <c r="U37" t="n">
-        <v>17.98083422258512</v>
+        <v>16.18841739566438</v>
       </c>
       <c r="V37" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0.749</v>
+        <v>0.718</v>
       </c>
       <c r="E38" t="n">
         <v>55</v>
@@ -3326,13 +3326,13 @@
         </is>
       </c>
       <c r="S38" t="n">
-        <v>146.1</v>
+        <v>143.96</v>
       </c>
       <c r="T38" t="n">
-        <v>3.523261321021733</v>
+        <v>3.664971796191852</v>
       </c>
       <c r="U38" t="n">
-        <v>12.33005943885835</v>
+        <v>10.70017192570193</v>
       </c>
       <c r="V38" t="inlineStr">
         <is>
@@ -3355,7 +3355,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0.576</v>
+        <v>0.586</v>
       </c>
       <c r="E39" t="n">
         <v>60</v>
@@ -3402,13 +3402,13 @@
         </is>
       </c>
       <c r="S39" t="n">
-        <v>89.08</v>
+        <v>88.48999999999999</v>
       </c>
       <c r="T39" t="n">
-        <v>2.061427525111607</v>
+        <v>2.099999564034598</v>
       </c>
       <c r="U39" t="n">
-        <v>21.17534303841171</v>
+        <v>22.53427397990382</v>
       </c>
       <c r="V39" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0.283</v>
+        <v>0.287</v>
       </c>
       <c r="E40" t="n">
         <v>53</v>
@@ -3478,13 +3478,13 @@
         </is>
       </c>
       <c r="S40" t="n">
-        <v>156.75</v>
+        <v>156.97</v>
       </c>
       <c r="T40" t="n">
-        <v>3.645001002720424</v>
+        <v>3.746429443359375</v>
       </c>
       <c r="U40" t="n">
-        <v>51.1039254107608</v>
+        <v>51.36374098173501</v>
       </c>
       <c r="V40" t="inlineStr">
         <is>
@@ -3507,7 +3507,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0.203</v>
+        <v>0.209</v>
       </c>
       <c r="E41" t="n">
         <v>52</v>
@@ -3554,13 +3554,13 @@
         </is>
       </c>
       <c r="S41" t="n">
-        <v>191.86</v>
+        <v>192.31</v>
       </c>
       <c r="T41" t="n">
-        <v>4.076426914760044</v>
+        <v>4.140712193080357</v>
       </c>
       <c r="U41" t="n">
-        <v>53.30200713030153</v>
+        <v>51.20421599097634</v>
       </c>
       <c r="V41" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0.595</v>
+        <v>0.599</v>
       </c>
       <c r="E42" t="n">
         <v>65</v>
@@ -3630,13 +3630,13 @@
         </is>
       </c>
       <c r="S42" t="n">
-        <v>782.71</v>
+        <v>809.14</v>
       </c>
       <c r="T42" t="n">
-        <v>39.92400067363405</v>
+        <v>40.6821866246699</v>
       </c>
       <c r="U42" t="n">
-        <v>40.37482638065851</v>
+        <v>44.21457486821886</v>
       </c>
       <c r="V42" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0.379</v>
+        <v>0.392</v>
       </c>
       <c r="E43" t="n">
         <v>53</v>
@@ -3706,13 +3706,13 @@
         </is>
       </c>
       <c r="S43" t="n">
-        <v>241.12</v>
+        <v>241.91</v>
       </c>
       <c r="T43" t="n">
-        <v>6.955714634486607</v>
+        <v>6.840714590890067</v>
       </c>
       <c r="U43" t="n">
-        <v>43.46888915481561</v>
+        <v>43.15297123850183</v>
       </c>
       <c r="V43" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0.635</v>
+        <v>0.619</v>
       </c>
       <c r="E44" t="n">
         <v>53</v>
@@ -3782,13 +3782,13 @@
         </is>
       </c>
       <c r="S44" t="n">
-        <v>350.63</v>
+        <v>355.04</v>
       </c>
       <c r="T44" t="n">
-        <v>10.81714085170201</v>
+        <v>10.96142578125</v>
       </c>
       <c r="U44" t="n">
-        <v>33.04656993135467</v>
+        <v>29.98759797127441</v>
       </c>
       <c r="V44" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0.43</v>
+        <v>0.403</v>
       </c>
       <c r="E45" t="n">
         <v>60</v>
@@ -3858,13 +3858,13 @@
         </is>
       </c>
       <c r="S45" t="n">
-        <v>214.01</v>
+        <v>220.9</v>
       </c>
       <c r="T45" t="n">
-        <v>6.619285583496094</v>
+        <v>6.931429181780134</v>
       </c>
       <c r="U45" t="n">
-        <v>22.88091816972282</v>
+        <v>19.904579251369</v>
       </c>
       <c r="V45" t="inlineStr">
         <is>
@@ -3887,7 +3887,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.917</v>
       </c>
       <c r="E46" t="n">
         <v>49</v>
@@ -3934,13 +3934,13 @@
         </is>
       </c>
       <c r="S46" t="n">
-        <v>136.37</v>
+        <v>143.42</v>
       </c>
       <c r="T46" t="n">
-        <v>4.696929931640625</v>
+        <v>5.005859375</v>
       </c>
       <c r="U46" t="n">
-        <v>35.84378533715343</v>
+        <v>37.42925994057484</v>
       </c>
       <c r="V46" t="inlineStr">
         <is>
